--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="1989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="1990">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,313 +38,313 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24674606323242</t>
+    <t xml:space="preserve">4.24674654006958</t>
   </si>
   <si>
     <t xml:space="preserve">ANIM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33184671401978</t>
+    <t xml:space="preserve">4.33184623718262</t>
   </si>
   <si>
     <t xml:space="preserve">4.13419580459595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96948575973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95301604270935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94203519821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07380247116089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93105506896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8267388343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76085591316223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67850089073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73889398574829</t>
+    <t xml:space="preserve">3.96948671340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95301556587219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94203495979309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07380294799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93105459213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82673859596252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76085567474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6784999370575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73889374732971</t>
   </si>
   <si>
     <t xml:space="preserve">3.40398621559143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53300762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7690908908844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79379725456238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79928684234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88438677787781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67575526237488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7059531211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64006876945496</t>
+    <t xml:space="preserve">3.53300833702087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76909041404724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79379677772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79928731918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88438725471497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67575550079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70595288276672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64006853103638</t>
   </si>
   <si>
     <t xml:space="preserve">3.57967519760132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35731816291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45065259933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37653398513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0663321018219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95652651786804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1953547000885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9839780330658</t>
+    <t xml:space="preserve">3.35731863975525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4506528377533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37653470039368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06633234024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95652675628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19535422325134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98397850990295</t>
   </si>
   <si>
     <t xml:space="preserve">3.2420220375061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20084476470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48634004592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38202452659607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31065058708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38751482963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26672768592834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1129994392395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08554792404175</t>
+    <t xml:space="preserve">3.20084500312805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48633933067322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38202428817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31065082550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38751530647278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2667281627655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11299967765808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08554840087891</t>
   </si>
   <si>
     <t xml:space="preserve">3.07182240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06084227561951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15692234039307</t>
+    <t xml:space="preserve">3.06084203720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15692162513733</t>
   </si>
   <si>
     <t xml:space="preserve">3.302414894104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43967270851135</t>
+    <t xml:space="preserve">3.43967247009277</t>
   </si>
   <si>
     <t xml:space="preserve">3.35182785987854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.283198595047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22280597686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25300216674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57692956924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47261452674866</t>
+    <t xml:space="preserve">3.28319883346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2228057384491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25300288200378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57693004608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">3.46437931060791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59065580368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56320452690125</t>
+    <t xml:space="preserve">3.590656042099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56320476531982</t>
   </si>
   <si>
     <t xml:space="preserve">3.61261677742004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51653695106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4341824054718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37104368209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45888948440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53026342391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3298671245575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2722179889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09103870391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23653101921082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34084749221802</t>
+    <t xml:space="preserve">3.51653647422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43418216705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37104344367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45888900756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5302631855011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32986640930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27221846580505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0910382270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23653149604797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34084725379944</t>
   </si>
   <si>
     <t xml:space="preserve">3.28594446182251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31888675689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23927664756775</t>
+    <t xml:space="preserve">3.31888556480408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23927688598633</t>
   </si>
   <si>
     <t xml:space="preserve">3.42594695091248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41771101951599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40947556495667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41496634483337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44241738319397</t>
+    <t xml:space="preserve">3.41771173477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40947604179382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41496658325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44241762161255</t>
   </si>
   <si>
     <t xml:space="preserve">3.4616334438324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44790816307068</t>
+    <t xml:space="preserve">3.44790887832642</t>
   </si>
   <si>
     <t xml:space="preserve">3.49732089042664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39300584793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37378907203674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26123833656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26947379112244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15417742729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16241264343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01966500282288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94829154014587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82201385498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93181991577148</t>
+    <t xml:space="preserve">3.39300560951233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3737895488739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26123809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26947355270386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15417766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16241240501404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0196647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94829130172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82201409339905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93182015419006</t>
   </si>
   <si>
     <t xml:space="preserve">3.06907749176025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00044846534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91809439659119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87417197227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85221076011658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89064264297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97133874893188</t>
+    <t xml:space="preserve">3.00044870376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91809391975403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8741717338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.852210521698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89064288139343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97133898735046</t>
   </si>
   <si>
     <t xml:space="preserve">3.06356287002563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23648309707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24224662780762</t>
+    <t xml:space="preserve">3.23648262023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24224638938904</t>
   </si>
   <si>
     <t xml:space="preserve">3.29988622665405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17884278297424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15866923332214</t>
+    <t xml:space="preserve">3.17884302139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15866851806641</t>
   </si>
   <si>
     <t xml:space="preserve">3.04050707817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97998523712158</t>
+    <t xml:space="preserve">2.97998452186584</t>
   </si>
   <si>
     <t xml:space="preserve">2.96269297599792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0232150554657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00015950202942</t>
+    <t xml:space="preserve">3.02321481704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00015902519226</t>
   </si>
   <si>
     <t xml:space="preserve">2.95692825317383</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">2.81859278678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7966902256012</t>
+    <t xml:space="preserve">2.79668998718262</t>
   </si>
   <si>
     <t xml:space="preserve">2.66988158226013</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">2.70331287384033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75288319587708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90505313873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92234492301941</t>
+    <t xml:space="preserve">2.75288414955139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90505337715149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92234444618225</t>
   </si>
   <si>
     <t xml:space="preserve">2.96845698356628</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">2.53615689277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26179122924805</t>
+    <t xml:space="preserve">2.26179146766663</t>
   </si>
   <si>
     <t xml:space="preserve">2.49004507064819</t>
@@ -392,31 +392,31 @@
     <t xml:space="preserve">2.41972422599792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4266414642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49235057830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36900091171265</t>
+    <t xml:space="preserve">2.42664122581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49235081672668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36900115013123</t>
   </si>
   <si>
     <t xml:space="preserve">2.28830575942993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29752779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30559778213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35747337341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43240475654602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61108899116516</t>
+    <t xml:space="preserve">2.29752731323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30559754371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35747313499451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4324049949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61108875274658</t>
   </si>
   <si>
     <t xml:space="preserve">2.59379720687866</t>
@@ -428,55 +428,55 @@
     <t xml:space="preserve">2.59725522994995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60647821426392</t>
+    <t xml:space="preserve">2.60647797584534</t>
   </si>
   <si>
     <t xml:space="preserve">2.56958794593811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62838077545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62261724472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59494972229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6168532371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54653239250183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63414525985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58226919174194</t>
+    <t xml:space="preserve">2.62838125228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62261700630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59494996070862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61685347557068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54653215408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63414573669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58226895332336</t>
   </si>
   <si>
     <t xml:space="preserve">2.40358519554138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41511344909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43816947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55114364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58572793006897</t>
+    <t xml:space="preserve">2.41511368751526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4381697177887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55114388465881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58572769165039</t>
   </si>
   <si>
     <t xml:space="preserve">2.65143704414368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65489530563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60417246818542</t>
+    <t xml:space="preserve">2.65489506721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.604172706604</t>
   </si>
   <si>
     <t xml:space="preserve">2.54307413101196</t>
@@ -485,19 +485,19 @@
     <t xml:space="preserve">2.41857147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37015390396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39321064949036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51310157775879</t>
+    <t xml:space="preserve">2.37015414237976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39321041107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51310133934021</t>
   </si>
   <si>
     <t xml:space="preserve">2.50964260101318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46122479438782</t>
+    <t xml:space="preserve">2.46122527122498</t>
   </si>
   <si>
     <t xml:space="preserve">2.4485445022583</t>
@@ -506,25 +506,25 @@
     <t xml:space="preserve">2.50733709335327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50157332420349</t>
+    <t xml:space="preserve">2.50157356262207</t>
   </si>
   <si>
     <t xml:space="preserve">2.49696230888367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51540660858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53039312362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57304716110229</t>
+    <t xml:space="preserve">2.51540684700012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53039336204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57304739952087</t>
   </si>
   <si>
     <t xml:space="preserve">2.66181230545044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62722826004028</t>
+    <t xml:space="preserve">2.62722849845886</t>
   </si>
   <si>
     <t xml:space="preserve">2.73789715766907</t>
@@ -536,67 +536,67 @@
     <t xml:space="preserve">2.7909255027771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67449331283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65604829788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64797902107239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65720105171204</t>
+    <t xml:space="preserve">2.67449307441711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6560480594635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64797878265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65720081329346</t>
   </si>
   <si>
     <t xml:space="preserve">2.6456732749939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52001786231995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51886534690857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49580955505371</t>
+    <t xml:space="preserve">2.5200183391571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51886510848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49580931663513</t>
   </si>
   <si>
     <t xml:space="preserve">2.5211706161499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52462911605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54192161560059</t>
+    <t xml:space="preserve">2.52462887763977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54192185401917</t>
   </si>
   <si>
     <t xml:space="preserve">2.47275328636169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46929502487183</t>
+    <t xml:space="preserve">2.46929526329041</t>
   </si>
   <si>
     <t xml:space="preserve">2.39436316490173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32173681259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32519483566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24795794487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26524949073792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32634782791138</t>
+    <t xml:space="preserve">2.32173657417297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32519507408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24795746803284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26524901390076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32634806632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.38629293441772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44393301010132</t>
+    <t xml:space="preserve">2.44393348693848</t>
   </si>
   <si>
     <t xml:space="preserve">2.44623875617981</t>
@@ -605,82 +605,82 @@
     <t xml:space="preserve">2.5707414150238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57996368408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56267118453979</t>
+    <t xml:space="preserve">2.57996320724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56267142295837</t>
   </si>
   <si>
     <t xml:space="preserve">2.55806040763855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5038788318634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50503134727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38168239593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60993647575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59956097602844</t>
+    <t xml:space="preserve">2.50387859344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50503158569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38168215751648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60993623733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59956073760986</t>
   </si>
   <si>
     <t xml:space="preserve">2.55344891548157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70907735824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67910480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58111643791199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80130100250244</t>
+    <t xml:space="preserve">2.70907688140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6791045665741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58111596107483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80130124092102</t>
   </si>
   <si>
     <t xml:space="preserve">2.81282949447632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72291111946106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78285646438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82551002502441</t>
+    <t xml:space="preserve">2.7229106426239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78285622596741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82550978660583</t>
   </si>
   <si>
     <t xml:space="preserve">2.92522692680359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96557450294495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91081666946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00592303276062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03474259376526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99727654457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98574900627136</t>
+    <t xml:space="preserve">2.96557426452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91081690788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00592279434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03474283218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9972767829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98574805259705</t>
   </si>
   <si>
     <t xml:space="preserve">2.94828271865845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93963670730591</t>
+    <t xml:space="preserve">2.93963694572449</t>
   </si>
   <si>
     <t xml:space="preserve">2.97422075271606</t>
@@ -695,64 +695,64 @@
     <t xml:space="preserve">3.03186082839966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16155052185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13849496841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11255669593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12984871864319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2047803401947</t>
+    <t xml:space="preserve">3.16155028343201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13849472999573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11255645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12984848022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20478081703186</t>
   </si>
   <si>
     <t xml:space="preserve">3.16443204879761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19613456726074</t>
+    <t xml:space="preserve">3.19613432884216</t>
   </si>
   <si>
     <t xml:space="preserve">3.1990168094635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12408518791199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14137673377991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08373737335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30276846885681</t>
+    <t xml:space="preserve">3.12408494949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14137649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08373689651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30276918411255</t>
   </si>
   <si>
     <t xml:space="preserve">3.26242089271545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18748879432678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28547644615173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22783660888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17596054077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2480103969574</t>
+    <t xml:space="preserve">3.1874885559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28547620773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2278368473053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17596077919006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24800992012024</t>
   </si>
   <si>
     <t xml:space="preserve">3.26818442344666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23936438560486</t>
+    <t xml:space="preserve">3.23936462402344</t>
   </si>
   <si>
     <t xml:space="preserve">3.09238266944885</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">3.10102844238281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05491709709167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08085465431213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11832046508789</t>
+    <t xml:space="preserve">3.05491662025452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08085441589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11832070350647</t>
   </si>
   <si>
     <t xml:space="preserve">3.15002274513245</t>
@@ -776,112 +776,112 @@
     <t xml:space="preserve">3.01168704032898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92810893058777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95404696464539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78516149520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91369915008545</t>
+    <t xml:space="preserve">2.92810869216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95404672622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7851619720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91369867324829</t>
   </si>
   <si>
     <t xml:space="preserve">2.98863077163696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0030403137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0260968208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07797312736511</t>
+    <t xml:space="preserve">3.00304055213928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02609705924988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07797265052795</t>
   </si>
   <si>
     <t xml:space="preserve">3.05779886245728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18172454833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17019724845886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23360061645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2451286315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25089263916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27106714248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27394890785217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28259491920471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25665640830994</t>
+    <t xml:space="preserve">3.18172430992126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17019701004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23360085487366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24512839317322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25089240074158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27106690406799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27394914627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28259468078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25665616989136</t>
   </si>
   <si>
     <t xml:space="preserve">3.18460655212402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29412269592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10391068458557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34023451805115</t>
+    <t xml:space="preserve">3.29412245750427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10391116142273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34023427963257</t>
   </si>
   <si>
     <t xml:space="preserve">3.4439868927002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4324586391449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46416044235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45839619636536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49298048019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44686818122864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50450825691223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60249638557434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51603579521179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46992421150208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44110488891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42381286621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4122838973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39499282836914</t>
+    <t xml:space="preserve">3.43245816230774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46415996551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45839667320251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49298024177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44686841964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50450849533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60249614715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51603627204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46992444992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44110441207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42381238937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41228413581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39499258995056</t>
   </si>
   <si>
     <t xml:space="preserve">3.37193632125854</t>
@@ -890,115 +890,115 @@
     <t xml:space="preserve">3.4893524646759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49236273765564</t>
+    <t xml:space="preserve">3.49236226081848</t>
   </si>
   <si>
     <t xml:space="preserve">3.59472560882568</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72117304801941</t>
+    <t xml:space="preserve">3.72117328643799</t>
   </si>
   <si>
     <t xml:space="preserve">3.71515226364136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58870410919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46827745437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41107511520386</t>
+    <t xml:space="preserve">3.58870387077332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4682776927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41107535362244</t>
   </si>
   <si>
     <t xml:space="preserve">3.49838447570801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54053330421448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50440573692322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51644849777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54956459999084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70912981033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72418355941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64891719818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75127935409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72719407081604</t>
+    <t xml:space="preserve">3.5405330657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5044059753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51644897460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54956531524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70913028717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72418403625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64891672134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75127911567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72719383239746</t>
   </si>
   <si>
     <t xml:space="preserve">3.76332211494446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73923707008362</t>
+    <t xml:space="preserve">3.73923659324646</t>
   </si>
   <si>
     <t xml:space="preserve">3.74525809288025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71214151382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70310926437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75730061531067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77536416053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77837562561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84159970283508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85966324806213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82654595375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09750509262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14266490936279</t>
+    <t xml:space="preserve">3.7121410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7031090259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75730085372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7753643989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77837514877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84159898757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85966348648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82654571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09750604629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14266538619995</t>
   </si>
   <si>
     <t xml:space="preserve">4.19685649871826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17277193069458</t>
+    <t xml:space="preserve">4.17277145385742</t>
   </si>
   <si>
     <t xml:space="preserve">4.19083547592163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22094202041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19986820220947</t>
+    <t xml:space="preserve">4.22094249725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19986724853516</t>
   </si>
   <si>
     <t xml:space="preserve">4.24502754211426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26911306381226</t>
+    <t xml:space="preserve">4.2691125869751</t>
   </si>
   <si>
     <t xml:space="preserve">4.26309156417847</t>
@@ -1010,106 +1010,106 @@
     <t xml:space="preserve">4.15470790863037</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14567613601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13664436340332</t>
+    <t xml:space="preserve">4.145676612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13664388656616</t>
   </si>
   <si>
     <t xml:space="preserve">4.22395324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22696304321289</t>
+    <t xml:space="preserve">4.22696352005005</t>
   </si>
   <si>
     <t xml:space="preserve">4.33534717559814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25104904174805</t>
+    <t xml:space="preserve">4.25104856491089</t>
   </si>
   <si>
     <t xml:space="preserve">4.28717613220215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11858034133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25405979156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09449529647827</t>
+    <t xml:space="preserve">4.11857938766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25405931472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09449481964111</t>
   </si>
   <si>
     <t xml:space="preserve">4.08847284317017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04030227661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05234479904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95901489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86267375946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86568403244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94396162033081</t>
+    <t xml:space="preserve">4.04030275344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05234527587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95901536941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86267328262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86568450927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94396209716797</t>
   </si>
   <si>
     <t xml:space="preserve">3.94697213172913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95600438117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98008990287781</t>
+    <t xml:space="preserve">3.95600414276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98008966445923</t>
   </si>
   <si>
     <t xml:space="preserve">3.97406840324402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07342004776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06438779830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98912167549133</t>
+    <t xml:space="preserve">4.07341957092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06438827514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98912119865417</t>
   </si>
   <si>
     <t xml:space="preserve">3.96202516555786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01320695877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0342812538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00417470932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00116395950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90783405303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88977003097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95299339294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0101957321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11255836486816</t>
+    <t xml:space="preserve">4.01320648193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03428077697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00417423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00116348266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90783429145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88977026939392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95299315452576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01019620895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11255788803101</t>
   </si>
   <si>
     <t xml:space="preserve">4.15771865844727</t>
@@ -1118,31 +1118,31 @@
     <t xml:space="preserve">4.06739902496338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98611116409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93191933631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9018120765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87471628189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85364198684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82353472709656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579129219055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84762001037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8325674533844</t>
+    <t xml:space="preserve">3.98611092567444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93191885948181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90181159973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87471699714661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85364127159119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82353496551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579105377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84762072563171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83256793022156</t>
   </si>
   <si>
     <t xml:space="preserve">3.88073825836182</t>
@@ -1151,85 +1151,85 @@
     <t xml:space="preserve">3.88374805450439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9258975982666</t>
+    <t xml:space="preserve">3.92589712142944</t>
   </si>
   <si>
     <t xml:space="preserve">3.92890810966492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88675904273987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91385531425476</t>
+    <t xml:space="preserve">3.88675951957703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9138548374176</t>
   </si>
   <si>
     <t xml:space="preserve">3.91084456443787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84460997581482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82052516937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69106650352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70611906051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55558657646179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47429895401001</t>
+    <t xml:space="preserve">3.84460973739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82052564620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69106602668762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70611977577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55558705329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47429871559143</t>
   </si>
   <si>
     <t xml:space="preserve">3.33580851554871</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40204310417175</t>
+    <t xml:space="preserve">3.40204262733459</t>
   </si>
   <si>
     <t xml:space="preserve">3.52246928215027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54354381561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53150105476379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57365083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60074663162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57666182518005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53752326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55257654190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50139451026917</t>
+    <t xml:space="preserve">3.54354405403137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53150153160095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57365036010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60074639320374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5766613483429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53752303123474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55257558822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50139427185059</t>
   </si>
   <si>
     <t xml:space="preserve">3.45021390914917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51042628288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48634147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43817138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40806460380554</t>
+    <t xml:space="preserve">3.51042675971985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48634171485901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43817186355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40806484222412</t>
   </si>
   <si>
     <t xml:space="preserve">3.53451204299927</t>
@@ -1238,22 +1238,22 @@
     <t xml:space="preserve">3.60977840423584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35387277603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42612791061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4441921710968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32376575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39000034332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61278891563416</t>
+    <t xml:space="preserve">3.35387229919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42612862586975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44419264793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32376599311829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39000010490417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61278939247131</t>
   </si>
   <si>
     <t xml:space="preserve">3.73020482063293</t>
@@ -1262,127 +1262,127 @@
     <t xml:space="preserve">3.6669807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64590692520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.633864402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81450271606445</t>
+    <t xml:space="preserve">3.64590716362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63386416435242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81450247764587</t>
   </si>
   <si>
     <t xml:space="preserve">3.86869549751282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93492937088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04331302642822</t>
+    <t xml:space="preserve">3.93492960929871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04331350326538</t>
   </si>
   <si>
     <t xml:space="preserve">3.99213194847107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98309969902039</t>
+    <t xml:space="preserve">3.9831006526947</t>
   </si>
   <si>
     <t xml:space="preserve">4.06137704849243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12460136413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.160728931427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07040929794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08245182037354</t>
+    <t xml:space="preserve">4.1246018409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16072940826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07040977478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08245229721069</t>
   </si>
   <si>
     <t xml:space="preserve">3.80848240852356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89880228042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91987681388855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78439593315125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77235436439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79945063591003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73622584342957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75429081916809</t>
+    <t xml:space="preserve">3.89880180358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91987752914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78439617156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77235412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79945039749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73622608184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75429034233093</t>
   </si>
   <si>
     <t xml:space="preserve">3.76633238792419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63988494873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56160855293274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6699914932251</t>
+    <t xml:space="preserve">3.63988471031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56160807609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66999220848083</t>
   </si>
   <si>
     <t xml:space="preserve">3.96503615379333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79342889785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74224710464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79164981842041</t>
+    <t xml:space="preserve">3.7934296131134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74224781990051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79164910316467</t>
   </si>
   <si>
     <t xml:space="preserve">3.77612233161926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78854417800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70469880104065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58359003067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55914306640625</t>
+    <t xml:space="preserve">3.78854370117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70469903945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58358931541443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55914282798767</t>
   </si>
   <si>
     <t xml:space="preserve">3.55258846282959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51326131820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61157989501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58536124229431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76888966560364</t>
+    <t xml:space="preserve">3.51326107978821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61157965660095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58536171913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76888990402222</t>
   </si>
   <si>
     <t xml:space="preserve">3.89998149871826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342737197876</t>
+    <t xml:space="preserve">3.8934268951416</t>
   </si>
   <si>
     <t xml:space="preserve">3.85082268714905</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">3.81149458885193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63779759407043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75578117370605</t>
+    <t xml:space="preserve">3.63779830932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7557806968689</t>
   </si>
   <si>
     <t xml:space="preserve">3.73939418792725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8606538772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099006652832</t>
+    <t xml:space="preserve">3.86065435409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099054336548</t>
   </si>
   <si>
     <t xml:space="preserve">3.81804919242859</t>
@@ -1412,31 +1412,31 @@
     <t xml:space="preserve">3.96552801132202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98846888542175</t>
+    <t xml:space="preserve">3.98846840858459</t>
   </si>
   <si>
     <t xml:space="preserve">3.93275499343872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86720848083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84426712989807</t>
+    <t xml:space="preserve">3.86720895767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84426760673523</t>
   </si>
   <si>
     <t xml:space="preserve">3.91309070587158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8213267326355</t>
+    <t xml:space="preserve">3.82132625579834</t>
   </si>
   <si>
     <t xml:space="preserve">4.03107309341431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04418325424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0245189666748</t>
+    <t xml:space="preserve">4.04418277740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02451848983765</t>
   </si>
   <si>
     <t xml:space="preserve">3.98191380500793</t>
@@ -1451,19 +1451,19 @@
     <t xml:space="preserve">3.77544450759888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76561212539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71973085403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71645283699036</t>
+    <t xml:space="preserve">3.76561236381531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71973037719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71645331382751</t>
   </si>
   <si>
     <t xml:space="preserve">3.56897497177124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50670647621155</t>
+    <t xml:space="preserve">3.50670623779297</t>
   </si>
   <si>
     <t xml:space="preserve">3.46737861633301</t>
@@ -1475,139 +1475,139 @@
     <t xml:space="preserve">2.93645691871643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03477597236633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19077515602112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42149615287781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41494202613831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33628678321838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31662321090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35595083236694</t>
+    <t xml:space="preserve">3.03477573394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19077467918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42149639129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41494178771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33628726005554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3166229724884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35595035552979</t>
   </si>
   <si>
     <t xml:space="preserve">3.21174955368042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30023622512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32645440101624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39855551719666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33956432342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29040455818176</t>
+    <t xml:space="preserve">3.30023646354675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32645511627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3985550403595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33956408500671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29040503501892</t>
   </si>
   <si>
     <t xml:space="preserve">3.27729558944702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28057265281677</t>
+    <t xml:space="preserve">3.28057289123535</t>
   </si>
   <si>
     <t xml:space="preserve">3.1829092502594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12260723114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07148098945618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01511192321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89975070953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01904439926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01380085945129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0491955280304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97971749305725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02690982818604</t>
+    <t xml:space="preserve">3.12260746955872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07148146629333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01511168479919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89975094795227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01904463768005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01380109786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04919576644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97971725463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02691006660461</t>
   </si>
   <si>
     <t xml:space="preserve">3.13440537452698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10425400733948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04264163970947</t>
+    <t xml:space="preserve">3.10425448417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04264116287231</t>
   </si>
   <si>
     <t xml:space="preserve">3.00200247764587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00462436676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98233914375305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98627209663391</t>
+    <t xml:space="preserve">3.00462460517883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98233890533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98627161979675</t>
   </si>
   <si>
     <t xml:space="preserve">2.92072582244873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92728066444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00069165229797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01249051094055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03739738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95612025260925</t>
+    <t xml:space="preserve">2.92728042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00069189071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01249027252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03739762306213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95612072944641</t>
   </si>
   <si>
     <t xml:space="preserve">2.92465877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84469294548035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97709536552429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00724601745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89057421684265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77259206771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79487752914429</t>
+    <t xml:space="preserve">2.84469270706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97709488868713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00724577903748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89057469367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77259182929993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79487776756287</t>
   </si>
   <si>
     <t xml:space="preserve">2.73064279556274</t>
@@ -1616,22 +1616,22 @@
     <t xml:space="preserve">2.71228981018066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70049118995667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77914667129517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76997041702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7371973991394</t>
+    <t xml:space="preserve">2.70049142837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77914619445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76996994018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73719763755798</t>
   </si>
   <si>
     <t xml:space="preserve">2.72146606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6900041103363</t>
+    <t xml:space="preserve">2.69000434875488</t>
   </si>
   <si>
     <t xml:space="preserve">2.63625645637512</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">2.62052536010742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67689490318298</t>
+    <t xml:space="preserve">2.67689514160156</t>
   </si>
   <si>
     <t xml:space="preserve">2.7201554775238</t>
@@ -1652,94 +1652,94 @@
     <t xml:space="preserve">2.87615466117859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85124659538269</t>
+    <t xml:space="preserve">2.85124707221985</t>
   </si>
   <si>
     <t xml:space="preserve">2.86697840690613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93907856941223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91154980659485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91679263114929</t>
+    <t xml:space="preserve">2.93907904624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91154956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91679286956787</t>
   </si>
   <si>
     <t xml:space="preserve">2.92596960067749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94170069694519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99806976318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04133009910583</t>
+    <t xml:space="preserve">2.94170022010803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99807000160217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04133033752441</t>
   </si>
   <si>
     <t xml:space="preserve">2.99675893783569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99413752555847</t>
+    <t xml:space="preserve">2.99413728713989</t>
   </si>
   <si>
     <t xml:space="preserve">2.96267509460449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96005344390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91285991668701</t>
+    <t xml:space="preserve">2.96005296707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91286015510559</t>
   </si>
   <si>
     <t xml:space="preserve">2.77521419525146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70704627037048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68869352340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70573472976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74244117736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64674377441406</t>
+    <t xml:space="preserve">2.70704650878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68869376182556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70573496818542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74244070053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64674401283264</t>
   </si>
   <si>
     <t xml:space="preserve">2.64150023460388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692907333374</t>
+    <t xml:space="preserve">2.59692883491516</t>
   </si>
   <si>
     <t xml:space="preserve">2.38193845748901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46714806556702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44879508018494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4907443523407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4710807800293</t>
+    <t xml:space="preserve">2.4671483039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44879531860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49074482917786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47108101844788</t>
   </si>
   <si>
     <t xml:space="preserve">2.48681211471558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41995477676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31639218330383</t>
+    <t xml:space="preserve">2.4199550151825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31639266014099</t>
   </si>
   <si>
     <t xml:space="preserve">2.25871229171753</t>
@@ -1754,43 +1754,43 @@
     <t xml:space="preserve">2.28493046760559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38587141036987</t>
+    <t xml:space="preserve">2.38587117195129</t>
   </si>
   <si>
     <t xml:space="preserve">2.39242577552795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42519903182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45928263664246</t>
+    <t xml:space="preserve">2.42519879341125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45928287506104</t>
   </si>
   <si>
     <t xml:space="preserve">2.54973578453064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47239184379578</t>
+    <t xml:space="preserve">2.47239208221436</t>
   </si>
   <si>
     <t xml:space="preserve">2.44617342948914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45797181129456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.475013256073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54842519760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43044257164001</t>
+    <t xml:space="preserve">2.4579713344574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47501373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54842495918274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43044209480286</t>
   </si>
   <si>
     <t xml:space="preserve">2.40815687179565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33998894691467</t>
+    <t xml:space="preserve">2.33998918533325</t>
   </si>
   <si>
     <t xml:space="preserve">2.28886365890503</t>
@@ -1808,34 +1808,34 @@
     <t xml:space="preserve">2.18661165237427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13155293464661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29410672187805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35178709030151</t>
+    <t xml:space="preserve">2.13155317306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29410696029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35178732872009</t>
   </si>
   <si>
     <t xml:space="preserve">2.39766955375671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44748449325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42388796806335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40946769714355</t>
+    <t xml:space="preserve">2.44748425483704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42388772964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40946745872498</t>
   </si>
   <si>
     <t xml:space="preserve">2.40029120445251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21938467025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19447708129883</t>
+    <t xml:space="preserve">2.21938443183899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19447684288025</t>
   </si>
   <si>
     <t xml:space="preserve">2.25477933883667</t>
@@ -1844,16 +1844,16 @@
     <t xml:space="preserve">2.31901431083679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32687997817993</t>
+    <t xml:space="preserve">2.32687973976135</t>
   </si>
   <si>
     <t xml:space="preserve">2.26264500617981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17743515968323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12893104553223</t>
+    <t xml:space="preserve">2.17743563652039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12893128395081</t>
   </si>
   <si>
     <t xml:space="preserve">2.14597320556641</t>
@@ -1865,19 +1865,19 @@
     <t xml:space="preserve">2.12368750572205</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10271310806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11713314056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14728403091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15121698379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23904848098755</t>
+    <t xml:space="preserve">2.10271286964417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11713290214539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14728379249573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15121674537659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23904800415039</t>
   </si>
   <si>
     <t xml:space="preserve">2.20758628845215</t>
@@ -1886,19 +1886,19 @@
     <t xml:space="preserve">2.36489629745483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34785437583923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37407255172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25084614753723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39504766464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35572004318237</t>
+    <t xml:space="preserve">2.34785461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37407302856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25084662437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39504742622375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35572028160095</t>
   </si>
   <si>
     <t xml:space="preserve">2.41340017318726</t>
@@ -1919,16 +1919,16 @@
     <t xml:space="preserve">2.38456034660339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35309815406799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34654378890991</t>
+    <t xml:space="preserve">2.35309839248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34654355049133</t>
   </si>
   <si>
     <t xml:space="preserve">2.35440921783447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37145113945007</t>
+    <t xml:space="preserve">2.37145090103149</t>
   </si>
   <si>
     <t xml:space="preserve">2.28755235671997</t>
@@ -1937,31 +1937,31 @@
     <t xml:space="preserve">2.26788854598999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31114912033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37931656837463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40291309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40553498268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37014031410217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33605623245239</t>
+    <t xml:space="preserve">2.31114888191223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37931680679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40291285514832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4055347442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37014007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33605647087097</t>
   </si>
   <si>
     <t xml:space="preserve">2.39898061752319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37669491767883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50123167037964</t>
+    <t xml:space="preserve">2.37669467926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50123190879822</t>
   </si>
   <si>
     <t xml:space="preserve">2.54318141937256</t>
@@ -1970,10 +1970,10 @@
     <t xml:space="preserve">2.52613949775696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5038537979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49336624145508</t>
+    <t xml:space="preserve">2.50385355949402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49336647987366</t>
   </si>
   <si>
     <t xml:space="preserve">2.42782044410706</t>
@@ -1982,19 +1982,19 @@
     <t xml:space="preserve">2.39635848999023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38718175888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37276220321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37800550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33867812156677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29935026168823</t>
+    <t xml:space="preserve">2.38718199729919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37276172637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37800574302673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33867788314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29935073852539</t>
   </si>
   <si>
     <t xml:space="preserve">2.38062763214111</t>
@@ -2003,31 +2003,31 @@
     <t xml:space="preserve">2.30459427833557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38849282264709</t>
+    <t xml:space="preserve">2.38849329948425</t>
   </si>
   <si>
     <t xml:space="preserve">2.45666074752808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40160202980042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34130024909973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34392189979553</t>
+    <t xml:space="preserve">2.40160226821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34129977226257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34392166137695</t>
   </si>
   <si>
     <t xml:space="preserve">2.38324928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32556891441345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30328297615051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30590486526489</t>
+    <t xml:space="preserve">2.32556867599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30328321456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30590510368347</t>
   </si>
   <si>
     <t xml:space="preserve">2.34523272514343</t>
@@ -2036,49 +2036,49 @@
     <t xml:space="preserve">2.32425808906555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30983781814575</t>
+    <t xml:space="preserve">2.30983805656433</t>
   </si>
   <si>
     <t xml:space="preserve">2.21545171737671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19054460525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09091472625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08698201179504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99783957004547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03978872299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9768648147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99128472805023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97817528247833</t>
+    <t xml:space="preserve">2.19054412841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09091448783875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08698177337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9978392124176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03978848457336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97686457633972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9912850856781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9781756401062</t>
   </si>
   <si>
     <t xml:space="preserve">1.98996269702911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99966990947723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97470879554749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94420039653778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9192396402359</t>
+    <t xml:space="preserve">1.99967014789581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97470915317535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94420051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91923928260803</t>
   </si>
   <si>
     <t xml:space="preserve">1.89843845367432</t>
@@ -2087,25 +2087,25 @@
     <t xml:space="preserve">1.86377012729645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82632839679718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87625074386597</t>
+    <t xml:space="preserve">1.82632827758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87625086307526</t>
   </si>
   <si>
     <t xml:space="preserve">1.87902426719666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83742225170135</t>
+    <t xml:space="preserve">1.83742249011993</t>
   </si>
   <si>
     <t xml:space="preserve">1.95113444328308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92755961418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89982533454895</t>
+    <t xml:space="preserve">1.92755997180939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89982497692108</t>
   </si>
   <si>
     <t xml:space="preserve">1.92062628269196</t>
@@ -2117,19 +2117,19 @@
     <t xml:space="preserve">1.90675890445709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88734447956085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88873159885406</t>
+    <t xml:space="preserve">1.88734459877014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88873136043549</t>
   </si>
   <si>
     <t xml:space="preserve">1.88179767131805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02879190444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98302912712097</t>
+    <t xml:space="preserve">2.02879166603088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98302924633026</t>
   </si>
   <si>
     <t xml:space="preserve">2.03156495094299</t>
@@ -2138,25 +2138,25 @@
     <t xml:space="preserve">1.98857605457306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95945453643799</t>
+    <t xml:space="preserve">1.95945477485657</t>
   </si>
   <si>
     <t xml:space="preserve">2.00660371780396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00521683692932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07177996635437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0939679145813</t>
+    <t xml:space="preserve">2.0052170753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07178020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09396815299988</t>
   </si>
   <si>
     <t xml:space="preserve">2.14943718910217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2270941734314</t>
+    <t xml:space="preserve">2.22709441184998</t>
   </si>
   <si>
     <t xml:space="preserve">2.25344228744507</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">2.25898909568787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26453614234924</t>
+    <t xml:space="preserve">2.26453638076782</t>
   </si>
   <si>
     <t xml:space="preserve">2.21461391448975</t>
@@ -2180,22 +2180,22 @@
     <t xml:space="preserve">2.31445860862732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30059146881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30891180038452</t>
+    <t xml:space="preserve">2.30059123039246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30891156196594</t>
   </si>
   <si>
     <t xml:space="preserve">2.31307196617126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27424311637878</t>
+    <t xml:space="preserve">2.27424335479736</t>
   </si>
   <si>
     <t xml:space="preserve">2.2215473651886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24789547920227</t>
+    <t xml:space="preserve">2.24789524078369</t>
   </si>
   <si>
     <t xml:space="preserve">2.24650859832764</t>
@@ -2204,55 +2204,55 @@
     <t xml:space="preserve">2.24512195587158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28811025619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32277917861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37824845314026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30613803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23125433921814</t>
+    <t xml:space="preserve">2.28811049461365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32277870178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37824869155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30613851547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23125457763672</t>
   </si>
   <si>
     <t xml:space="preserve">2.18687915802002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17162489891052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17439842224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22432112693787</t>
+    <t xml:space="preserve">2.1716251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17439818382263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22432088851929</t>
   </si>
   <si>
     <t xml:space="preserve">2.12170267105103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10783529281616</t>
+    <t xml:space="preserve">2.10783505439758</t>
   </si>
   <si>
     <t xml:space="preserve">2.12863612174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09812808036804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12724947929382</t>
+    <t xml:space="preserve">2.09812831878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1272497177124</t>
   </si>
   <si>
     <t xml:space="preserve">2.17717218399048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19103956222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23680138587952</t>
+    <t xml:space="preserve">2.19103932380676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2368016242981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20629334449768</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">2.18549227714539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25760245323181</t>
+    <t xml:space="preserve">2.25760269165039</t>
   </si>
   <si>
     <t xml:space="preserve">2.25621581077576</t>
@@ -2273,46 +2273,46 @@
     <t xml:space="preserve">2.23957490921021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35606074333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38102149963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3671543598175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38379549980164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43510484695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5155348777771</t>
+    <t xml:space="preserve">2.35606050491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38102173805237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36715459823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38379526138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43510437011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51553511619568</t>
   </si>
   <si>
     <t xml:space="preserve">2.49889421463013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42955756187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42817068099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44897198677063</t>
+    <t xml:space="preserve">2.42955780029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42817091941833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44897174835205</t>
   </si>
   <si>
     <t xml:space="preserve">2.45867896080017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39766240119934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38795566558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37131452560425</t>
+    <t xml:space="preserve">2.39766263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3879554271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37131500244141</t>
   </si>
   <si>
     <t xml:space="preserve">2.382408618927</t>
@@ -2321,19 +2321,19 @@
     <t xml:space="preserve">2.41707682609558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42401051521301</t>
+    <t xml:space="preserve">2.42401075363159</t>
   </si>
   <si>
     <t xml:space="preserve">2.37408828735352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32693934440613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2992045879364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31723213195801</t>
+    <t xml:space="preserve">2.32693910598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29920434951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31723189353943</t>
   </si>
   <si>
     <t xml:space="preserve">2.34496665000916</t>
@@ -2342,19 +2342,19 @@
     <t xml:space="preserve">2.34635353088379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41153001785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46977257728577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48502707481384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56961798667908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61537981033325</t>
+    <t xml:space="preserve">2.4115297794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46977281570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48502659797668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5696177482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61538004875183</t>
   </si>
   <si>
     <t xml:space="preserve">2.6763961315155</t>
@@ -2363,16 +2363,16 @@
     <t xml:space="preserve">2.73879909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70690417289734</t>
+    <t xml:space="preserve">2.70690441131592</t>
   </si>
   <si>
     <t xml:space="preserve">2.74711942672729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72770524024963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75266623497009</t>
+    <t xml:space="preserve">2.72770547866821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75266647338867</t>
   </si>
   <si>
     <t xml:space="preserve">2.76237368583679</t>
@@ -2381,13 +2381,13 @@
     <t xml:space="preserve">2.7859480381012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77208042144775</t>
+    <t xml:space="preserve">2.77208065986633</t>
   </si>
   <si>
     <t xml:space="preserve">2.69581031799316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70413112640381</t>
+    <t xml:space="preserve">2.70413064956665</t>
   </si>
   <si>
     <t xml:space="preserve">2.7207715511322</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">2.80120205879211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78733491897583</t>
+    <t xml:space="preserve">2.78733468055725</t>
   </si>
   <si>
     <t xml:space="preserve">2.82893657684326</t>
@@ -2408,19 +2408,19 @@
     <t xml:space="preserve">2.9468092918396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01614546775818</t>
+    <t xml:space="preserve">3.01614570617676</t>
   </si>
   <si>
     <t xml:space="preserve">3.02723979949951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04804086685181</t>
+    <t xml:space="preserve">3.04804062843323</t>
   </si>
   <si>
     <t xml:space="preserve">3.07993578910828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13679194450378</t>
+    <t xml:space="preserve">3.13679218292236</t>
   </si>
   <si>
     <t xml:space="preserve">3.14649868011475</t>
@@ -2429,40 +2429,40 @@
     <t xml:space="preserve">3.17562007904053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14511203765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23108959197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24773049354553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26298427581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2615978717804</t>
+    <t xml:space="preserve">3.14511227607727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23108911514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24773025512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26298451423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26159763336182</t>
   </si>
   <si>
     <t xml:space="preserve">3.2255425453186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18532705307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18394088745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2560510635376</t>
+    <t xml:space="preserve">3.18532729148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18394064903259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25605058670044</t>
   </si>
   <si>
     <t xml:space="preserve">3.21028876304626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25327682495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22831654548645</t>
+    <t xml:space="preserve">3.25327730178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22831630706787</t>
   </si>
   <si>
     <t xml:space="preserve">3.20196795463562</t>
@@ -2471,73 +2471,73 @@
     <t xml:space="preserve">3.24218368530273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26575803756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21306180953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19919466972351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20890140533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22415614128113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1908745765686</t>
+    <t xml:space="preserve">3.26575827598572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21306204795837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19919443130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20890164375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22415566444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19087433815002</t>
   </si>
   <si>
     <t xml:space="preserve">3.20335483551025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06606841087341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09241628646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14788556098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20612859725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17839360237122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17145991325378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03694725036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15343236923218</t>
+    <t xml:space="preserve">3.06606817245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09241604804993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1478853225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20612835884094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17839384078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17146015167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03694677352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1534321308136</t>
   </si>
   <si>
     <t xml:space="preserve">3.16868686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.970383644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03555989265442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14095211029053</t>
+    <t xml:space="preserve">2.97038340568542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.035560131073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14095187187195</t>
   </si>
   <si>
     <t xml:space="preserve">3.12985777854919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14927220344543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17007303237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12708425521851</t>
+    <t xml:space="preserve">3.14927196502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17007327079773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12708473205566</t>
   </si>
   <si>
     <t xml:space="preserve">3.10073685646057</t>
@@ -2546,55 +2546,55 @@
     <t xml:space="preserve">3.07854890823364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11044406890869</t>
+    <t xml:space="preserve">3.11044359207153</t>
   </si>
   <si>
     <t xml:space="preserve">3.08964276313782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28239917755127</t>
+    <t xml:space="preserve">3.28239870071411</t>
   </si>
   <si>
     <t xml:space="preserve">3.34202837944031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34896183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93987536430359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97315740585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.863605260849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73741245269775</t>
+    <t xml:space="preserve">3.34896159172058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93987512588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97315716743469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86360549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73741221427917</t>
   </si>
   <si>
     <t xml:space="preserve">2.58487176895142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55159020423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49473404884338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29227066040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07039380073547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95668148994446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99134957790375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6904284954071</t>
+    <t xml:space="preserve">2.55158996582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49473428726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29227089881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07039356231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95668137073517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99134945869446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69042861461639</t>
   </si>
   <si>
     <t xml:space="preserve">1.78472626209259</t>
@@ -2603,13 +2603,13 @@
     <t xml:space="preserve">1.65576004981995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52818071842194</t>
+    <t xml:space="preserve">1.52818048000336</t>
   </si>
   <si>
     <t xml:space="preserve">1.41030824184418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.485191822052</t>
+    <t xml:space="preserve">1.48519170284271</t>
   </si>
   <si>
     <t xml:space="preserve">1.49489891529083</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">1.72648358345032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68904161453247</t>
+    <t xml:space="preserve">1.68904197216034</t>
   </si>
   <si>
     <t xml:space="preserve">1.69736206531525</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">1.72371029853821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75421822071075</t>
+    <t xml:space="preserve">1.75421810150146</t>
   </si>
   <si>
     <t xml:space="preserve">1.78888654708862</t>
@@ -2648,43 +2648,43 @@
     <t xml:space="preserve">2.06207299232483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05375289916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99412286281586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609543800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96638834476471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94142711162567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8596099615097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86793041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92339968681335</t>
+    <t xml:space="preserve">2.05375242233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99412274360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609567642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.966388463974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94142723083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85960984230042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8679301738739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92339944839478</t>
   </si>
   <si>
     <t xml:space="preserve">1.90121173858643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14805054664612</t>
+    <t xml:space="preserve">2.1480507850647</t>
   </si>
   <si>
     <t xml:space="preserve">2.26730966567993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23818802833557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22570776939392</t>
+    <t xml:space="preserve">2.23818850517273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22570753097534</t>
   </si>
   <si>
     <t xml:space="preserve">2.13418316841125</t>
@@ -2696,13 +2696,13 @@
     <t xml:space="preserve">2.35744738578796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40043592453003</t>
+    <t xml:space="preserve">2.40043640136719</t>
   </si>
   <si>
     <t xml:space="preserve">2.3435800075531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30752491950989</t>
+    <t xml:space="preserve">2.30752515792847</t>
   </si>
   <si>
     <t xml:space="preserve">2.48411750793457</t>
@@ -2714,31 +2714,31 @@
     <t xml:space="preserve">2.49150609970093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49741721153259</t>
+    <t xml:space="preserve">2.49741768836975</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456218719482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5713050365448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72647023200989</t>
+    <t xml:space="preserve">2.57130527496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72647047042847</t>
   </si>
   <si>
     <t xml:space="preserve">2.75750327110291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80774712562561</t>
+    <t xml:space="preserve">2.80774736404419</t>
   </si>
   <si>
     <t xml:space="preserve">2.86537981033325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87572407722473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86833548545837</t>
+    <t xml:space="preserve">2.87572431564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86833524703979</t>
   </si>
   <si>
     <t xml:space="preserve">2.97473430633545</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">3.14024376869202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93483448028564</t>
+    <t xml:space="preserve">2.93483471870422</t>
   </si>
   <si>
     <t xml:space="preserve">2.9363124370575</t>
@@ -2762,28 +2762,28 @@
     <t xml:space="preserve">2.94222378730774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99837851524353</t>
+    <t xml:space="preserve">2.99837875366211</t>
   </si>
   <si>
     <t xml:space="preserve">3.00281167030334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95847916603088</t>
+    <t xml:space="preserve">2.9584789276123</t>
   </si>
   <si>
     <t xml:space="preserve">2.88606834411621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92744588851929</t>
+    <t xml:space="preserve">2.92744612693787</t>
   </si>
   <si>
     <t xml:space="preserve">2.83582472801208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8905017375946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88459062576294</t>
+    <t xml:space="preserve">2.89050197601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88459086418152</t>
   </si>
   <si>
     <t xml:space="preserve">2.85946869850159</t>
@@ -2792,10 +2792,10 @@
     <t xml:space="preserve">2.82843589782715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86242461204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93779039382935</t>
+    <t xml:space="preserve">2.86242437362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93779015541077</t>
   </si>
   <si>
     <t xml:space="preserve">2.99542284011841</t>
@@ -2804,43 +2804,43 @@
     <t xml:space="preserve">3.03236699104309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04418873786926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01906681060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92005681991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93040132522583</t>
+    <t xml:space="preserve">3.04418897628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01906728744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92005705833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93040156364441</t>
   </si>
   <si>
     <t xml:space="preserve">2.97916769981384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98212313652039</t>
+    <t xml:space="preserve">2.98212289810181</t>
   </si>
   <si>
     <t xml:space="preserve">2.99394512176514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98951196670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95404529571533</t>
+    <t xml:space="preserve">2.98951172828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95404577255249</t>
   </si>
   <si>
     <t xml:space="preserve">2.95552325248718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94665694236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03384447097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09591102600098</t>
+    <t xml:space="preserve">2.94665670394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03384494781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0959107875824</t>
   </si>
   <si>
     <t xml:space="preserve">3.01758933067322</t>
@@ -2858,10 +2858,10 @@
     <t xml:space="preserve">2.75602555274963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81365847587585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85503554344177</t>
+    <t xml:space="preserve">2.81365823745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85503578186035</t>
   </si>
   <si>
     <t xml:space="preserve">2.8535578250885</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">2.894935131073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87720227241516</t>
+    <t xml:space="preserve">2.87720203399658</t>
   </si>
   <si>
     <t xml:space="preserve">2.92153477668762</t>
@@ -2888,13 +2888,13 @@
     <t xml:space="preserve">2.84616899490356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80479145050049</t>
+    <t xml:space="preserve">2.80479192733765</t>
   </si>
   <si>
     <t xml:space="preserve">2.76784777641296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75307035446167</t>
+    <t xml:space="preserve">2.75307011604309</t>
   </si>
   <si>
     <t xml:space="preserve">2.78410315513611</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">2.79888105392456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7486367225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77523636817932</t>
+    <t xml:space="preserve">2.74863696098328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7752366065979</t>
   </si>
   <si>
     <t xml:space="preserve">2.72351503372192</t>
@@ -2915,25 +2915,25 @@
     <t xml:space="preserve">2.76636981964111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79296946525574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73681449890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69987058639526</t>
+    <t xml:space="preserve">2.79296970367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73681473731995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69987082481384</t>
   </si>
   <si>
     <t xml:space="preserve">2.79592514038086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74272561073303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75454783439636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74715876579285</t>
+    <t xml:space="preserve">2.74272537231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75454759597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74715924263</t>
   </si>
   <si>
     <t xml:space="preserve">2.71612596511841</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">2.61268281936646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57573866844177</t>
+    <t xml:space="preserve">2.57573843002319</t>
   </si>
   <si>
     <t xml:space="preserve">2.52549481391907</t>
@@ -2960,10 +2960,10 @@
     <t xml:space="preserve">2.53436136245728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58460521697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52697253227234</t>
+    <t xml:space="preserve">2.5846049785614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52697229385376</t>
   </si>
   <si>
     <t xml:space="preserve">2.47525072097778</t>
@@ -2972,52 +2972,52 @@
     <t xml:space="preserve">2.50037288665771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43091821670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52992820739746</t>
+    <t xml:space="preserve">2.43091773986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52992796897888</t>
   </si>
   <si>
     <t xml:space="preserve">2.61120462417603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54618334770203</t>
+    <t xml:space="preserve">2.54618358612061</t>
   </si>
   <si>
     <t xml:space="preserve">2.55209422111511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67179322242737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60972738265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5432276725769</t>
+    <t xml:space="preserve">2.67179298400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60972690582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54322791099548</t>
   </si>
   <si>
     <t xml:space="preserve">2.52845025062561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47377300262451</t>
+    <t xml:space="preserve">2.47377324104309</t>
   </si>
   <si>
     <t xml:space="preserve">2.6289381980896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6570155620575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63632702827454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60677170753479</t>
+    <t xml:space="preserve">2.65701532363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63632678985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60677194595337</t>
   </si>
   <si>
     <t xml:space="preserve">2.53140592575073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52253913879395</t>
+    <t xml:space="preserve">2.52253937721252</t>
   </si>
   <si>
     <t xml:space="preserve">2.36441898345947</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">2.31713032722473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37180757522583</t>
+    <t xml:space="preserve">2.37180733680725</t>
   </si>
   <si>
     <t xml:space="preserve">2.51662826538086</t>
@@ -3044,10 +3044,10 @@
     <t xml:space="preserve">2.615638256073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6525821685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63041591644287</t>
+    <t xml:space="preserve">2.65258240699768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63041567802429</t>
   </si>
   <si>
     <t xml:space="preserve">2.71317028999329</t>
@@ -3056,16 +3056,16 @@
     <t xml:space="preserve">2.72794795036316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74568104743958</t>
+    <t xml:space="preserve">2.74568128585815</t>
   </si>
   <si>
     <t xml:space="preserve">2.83139157295227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79149198532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7885365486145</t>
+    <t xml:space="preserve">2.79149174690247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78853607177734</t>
   </si>
   <si>
     <t xml:space="preserve">2.75898122787476</t>
@@ -3083,31 +3083,31 @@
     <t xml:space="preserve">2.64519333839417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.680659532547</t>
+    <t xml:space="preserve">2.68065977096558</t>
   </si>
   <si>
     <t xml:space="preserve">2.64962673187256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68213748931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6259822845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65849351882935</t>
+    <t xml:space="preserve">2.68213725090027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62598252296448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65849328041077</t>
   </si>
   <si>
     <t xml:space="preserve">2.72055912017822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85651302337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92301297187805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90380167961121</t>
+    <t xml:space="preserve">2.85651350021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92301249504089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90380191802979</t>
   </si>
   <si>
     <t xml:space="preserve">2.90084624290466</t>
@@ -3119,37 +3119,37 @@
     <t xml:space="preserve">3.0146336555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03975582122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07374405860901</t>
+    <t xml:space="preserve">3.03975558280945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07374429702759</t>
   </si>
   <si>
     <t xml:space="preserve">3.11807727813721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06044483184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02350044250488</t>
+    <t xml:space="preserve">3.06044459342957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02350068092346</t>
   </si>
   <si>
     <t xml:space="preserve">3.02941131591797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89345765113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86390209197998</t>
+    <t xml:space="preserve">2.89345741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86390233039856</t>
   </si>
   <si>
     <t xml:space="preserve">2.90675711631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87129068374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83434700965881</t>
+    <t xml:space="preserve">2.87129092216492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83434677124023</t>
   </si>
   <si>
     <t xml:space="preserve">2.91710162162781</t>
@@ -3161,10 +3161,10 @@
     <t xml:space="preserve">3.1328547000885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10034394264221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1771879196167</t>
+    <t xml:space="preserve">3.10034418106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17718768119812</t>
   </si>
   <si>
     <t xml:space="preserve">3.10625529289246</t>
@@ -3182,22 +3182,22 @@
     <t xml:space="preserve">2.9451789855957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9998562335968</t>
+    <t xml:space="preserve">2.99985647201538</t>
   </si>
   <si>
     <t xml:space="preserve">2.97177863121033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93926763534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08999991416931</t>
+    <t xml:space="preserve">2.93926811218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08999967575073</t>
   </si>
   <si>
     <t xml:space="preserve">3.09147763252258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07669997215271</t>
+    <t xml:space="preserve">3.07669973373413</t>
   </si>
   <si>
     <t xml:space="preserve">3.08704423904419</t>
@@ -3206,25 +3206,25 @@
     <t xml:space="preserve">3.08852171897888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12694382667542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24664258956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20526480674744</t>
+    <t xml:space="preserve">3.12694358825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24664235115051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20526528358459</t>
   </si>
   <si>
     <t xml:space="preserve">3.21856474876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33235239982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33826351165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34121918678284</t>
+    <t xml:space="preserve">3.33235263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33826375007629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34121894836426</t>
   </si>
   <si>
     <t xml:space="preserve">3.31166410446167</t>
@@ -3233,52 +3233,52 @@
     <t xml:space="preserve">3.26142024993896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32496380805969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30131936073303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2924530506134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28801941871643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31609749794006</t>
+    <t xml:space="preserve">3.32496404647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30131959915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29245281219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28801965713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31609702110291</t>
   </si>
   <si>
     <t xml:space="preserve">3.29393076896667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27324151992798</t>
+    <t xml:space="preserve">3.27324223518372</t>
   </si>
   <si>
     <t xml:space="preserve">3.24516487121582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32274723052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30649161338806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3101863861084</t>
+    <t xml:space="preserve">3.32274746894836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30649185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31018614768982</t>
   </si>
   <si>
     <t xml:space="preserve">3.29540872573853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25107598304749</t>
+    <t xml:space="preserve">3.25107574462891</t>
   </si>
   <si>
     <t xml:space="preserve">3.28358626365662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28654217720032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27915358543396</t>
+    <t xml:space="preserve">3.28654193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27915334701538</t>
   </si>
   <si>
     <t xml:space="preserve">3.24073147773743</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">3.28136968612671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18531537055969</t>
+    <t xml:space="preserve">3.18531513214111</t>
   </si>
   <si>
     <t xml:space="preserve">3.13433265686035</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">3.10329961776733</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16314888000488</t>
+    <t xml:space="preserve">3.16314911842346</t>
   </si>
   <si>
     <t xml:space="preserve">3.13507151603699</t>
@@ -3314,19 +3314,19 @@
     <t xml:space="preserve">3.15354347229004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13654899597168</t>
+    <t xml:space="preserve">3.1365487575531</t>
   </si>
   <si>
     <t xml:space="preserve">3.21043729782104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26511478424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22743153572083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.239253282547</t>
+    <t xml:space="preserve">3.26511454582214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2274317741394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23925375938416</t>
   </si>
   <si>
     <t xml:space="preserve">3.24738144874573</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">3.31979179382324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33974146842957</t>
+    <t xml:space="preserve">3.33974123001099</t>
   </si>
   <si>
     <t xml:space="preserve">3.41362953186035</t>
@@ -3344,13 +3344,13 @@
     <t xml:space="preserve">3.3205304145813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32939720153809</t>
+    <t xml:space="preserve">3.32939696311951</t>
   </si>
   <si>
     <t xml:space="preserve">3.31535816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38761758804321</t>
+    <t xml:space="preserve">3.38761734962463</t>
   </si>
   <si>
     <t xml:space="preserve">3.31846618652344</t>
@@ -3362,7 +3362,7 @@
     <t xml:space="preserve">3.33322882652283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33944487571716</t>
+    <t xml:space="preserve">3.33944439888</t>
   </si>
   <si>
     <t xml:space="preserve">3.33633685112</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">3.40471076965332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60206270217896</t>
+    <t xml:space="preserve">3.60206246376038</t>
   </si>
   <si>
     <t xml:space="preserve">3.64868140220642</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">3.55855202674866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52203369140625</t>
+    <t xml:space="preserve">3.52203416824341</t>
   </si>
   <si>
     <t xml:space="preserve">3.51037955284119</t>
@@ -3398,7 +3398,7 @@
     <t xml:space="preserve">3.44200563430786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47619271278381</t>
+    <t xml:space="preserve">3.47619247436523</t>
   </si>
   <si>
     <t xml:space="preserve">3.44977521896362</t>
@@ -3419,22 +3419,22 @@
     <t xml:space="preserve">3.27417898178101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29904174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25630831718445</t>
+    <t xml:space="preserve">3.2990415096283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25630807876587</t>
   </si>
   <si>
     <t xml:space="preserve">3.26407790184021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24776148796082</t>
+    <t xml:space="preserve">3.24776124954224</t>
   </si>
   <si>
     <t xml:space="preserve">3.2788405418396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25786209106445</t>
+    <t xml:space="preserve">3.25786185264587</t>
   </si>
   <si>
     <t xml:space="preserve">3.24076867103577</t>
@@ -3446,10 +3446,10 @@
     <t xml:space="preserve">3.25009250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28738713264465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27184772491455</t>
+    <t xml:space="preserve">3.28738737106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27184748649597</t>
   </si>
   <si>
     <t xml:space="preserve">3.24620747566223</t>
@@ -3461,34 +3461,34 @@
     <t xml:space="preserve">3.16540193557739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02632308006287</t>
+    <t xml:space="preserve">3.02632331848145</t>
   </si>
   <si>
     <t xml:space="preserve">3.03098511695862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09158945083618</t>
+    <t xml:space="preserve">3.0915892124176</t>
   </si>
   <si>
     <t xml:space="preserve">3.11956024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18016457557678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22678303718567</t>
+    <t xml:space="preserve">3.1801643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22678327560425</t>
   </si>
   <si>
     <t xml:space="preserve">3.19570398330688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21202039718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22989130020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23066806793213</t>
+    <t xml:space="preserve">3.21202063560486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22989106178284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23066782951355</t>
   </si>
   <si>
     <t xml:space="preserve">3.31458139419556</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">3.33478260040283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36120009422302</t>
+    <t xml:space="preserve">3.3612003326416</t>
   </si>
   <si>
     <t xml:space="preserve">3.34954524040222</t>
@@ -3530,10 +3530,10 @@
     <t xml:space="preserve">3.36819291114807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36508464813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39227938652039</t>
+    <t xml:space="preserve">3.36508440971375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39227914810181</t>
   </si>
   <si>
     <t xml:space="preserve">3.41248083114624</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">3.37207770347595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39150190353394</t>
+    <t xml:space="preserve">3.39150166511536</t>
   </si>
   <si>
     <t xml:space="preserve">3.39849495887756</t>
@@ -3551,7 +3551,7 @@
     <t xml:space="preserve">3.35032224655151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3534300327301</t>
+    <t xml:space="preserve">3.35343027114868</t>
   </si>
   <si>
     <t xml:space="preserve">3.31535863876343</t>
@@ -3569,37 +3569,37 @@
     <t xml:space="preserve">3.32312798500061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28971815109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18715763092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19725775718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29282569885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28661012649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22056722640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21745944023132</t>
+    <t xml:space="preserve">3.28971838951111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18715739250183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19725751876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29282593727112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28661036491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22056746482849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21745920181274</t>
   </si>
   <si>
     <t xml:space="preserve">3.21279764175415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20891308784485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17627954483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30758881568909</t>
+    <t xml:space="preserve">3.20891284942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17627930641174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30758857727051</t>
   </si>
   <si>
     <t xml:space="preserve">3.33012080192566</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">3.36741590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39460968971252</t>
+    <t xml:space="preserve">3.3946099281311</t>
   </si>
   <si>
     <t xml:space="preserve">3.32623624801636</t>
@@ -3617,19 +3617,19 @@
     <t xml:space="preserve">3.43268179893494</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45443725585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48085451126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50183296203613</t>
+    <t xml:space="preserve">3.45443749427795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48085427284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50183272361755</t>
   </si>
   <si>
     <t xml:space="preserve">3.61682558059692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57797622680664</t>
+    <t xml:space="preserve">3.57797646522522</t>
   </si>
   <si>
     <t xml:space="preserve">3.58652329444885</t>
@@ -3638,7 +3638,7 @@
     <t xml:space="preserve">3.58963108062744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5958468914032</t>
+    <t xml:space="preserve">3.59584665298462</t>
   </si>
   <si>
     <t xml:space="preserve">3.57176089286804</t>
@@ -3647,10 +3647,10 @@
     <t xml:space="preserve">3.57642245292664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.566321849823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58108496665955</t>
+    <t xml:space="preserve">3.56632208824158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58108448982239</t>
   </si>
   <si>
     <t xml:space="preserve">3.68753004074097</t>
@@ -3665,19 +3665,19 @@
     <t xml:space="preserve">3.64246535301208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62071013450623</t>
+    <t xml:space="preserve">3.62070989608765</t>
   </si>
   <si>
     <t xml:space="preserve">3.62692594528198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62148714065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61294054985046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61060929298401</t>
+    <t xml:space="preserve">3.62148666381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61294031143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61060953140259</t>
   </si>
   <si>
     <t xml:space="preserve">3.57409167289734</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">3.45132899284363</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39694094657898</t>
+    <t xml:space="preserve">3.39694118499756</t>
   </si>
   <si>
     <t xml:space="preserve">3.3953869342804</t>
@@ -3701,22 +3701,22 @@
     <t xml:space="preserve">3.26330089569092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22833704948425</t>
+    <t xml:space="preserve">3.22833728790283</t>
   </si>
   <si>
     <t xml:space="preserve">3.23999166488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40004897117615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33711361885071</t>
+    <t xml:space="preserve">3.40004873275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33711385726929</t>
   </si>
   <si>
     <t xml:space="preserve">3.36586141586304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37363171577454</t>
+    <t xml:space="preserve">3.37363147735596</t>
   </si>
   <si>
     <t xml:space="preserve">3.41791963577271</t>
@@ -3728,22 +3728,22 @@
     <t xml:space="preserve">3.31380438804626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42025017738342</t>
+    <t xml:space="preserve">3.42024993896484</t>
   </si>
   <si>
     <t xml:space="preserve">3.42957425117493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4816312789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4971706867218</t>
+    <t xml:space="preserve">3.48163151741028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49717116355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.48707008361816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48862385749817</t>
+    <t xml:space="preserve">3.48862409591675</t>
   </si>
   <si>
     <t xml:space="preserve">3.51814913749695</t>
@@ -3755,16 +3755,16 @@
     <t xml:space="preserve">3.52436494827271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48551630973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49794745445251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64635038375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70151615142822</t>
+    <t xml:space="preserve">3.48551607131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49794769287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64635014533997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70151591300964</t>
   </si>
   <si>
     <t xml:space="preserve">3.6960768699646</t>
@@ -3773,19 +3773,19 @@
     <t xml:space="preserve">3.64712738990784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65567398071289</t>
+    <t xml:space="preserve">3.65567374229431</t>
   </si>
   <si>
     <t xml:space="preserve">3.56865262985229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52824974060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49639391899109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35420680046082</t>
+    <t xml:space="preserve">3.52824950218201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49639415740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35420727729797</t>
   </si>
   <si>
     <t xml:space="preserve">3.40237998962402</t>
@@ -3794,34 +3794,34 @@
     <t xml:space="preserve">3.41092658042908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41558837890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46531510353088</t>
+    <t xml:space="preserve">3.41558814048767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4653148651123</t>
   </si>
   <si>
     <t xml:space="preserve">3.48240828514099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49017810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47075366973877</t>
+    <t xml:space="preserve">3.49017834663391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47075390815735</t>
   </si>
   <si>
     <t xml:space="preserve">3.45366048812866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54301238059998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56321382522583</t>
+    <t xml:space="preserve">3.54301261901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56321406364441</t>
   </si>
   <si>
     <t xml:space="preserve">3.75978922843933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62614846229553</t>
+    <t xml:space="preserve">3.62614893913269</t>
   </si>
   <si>
     <t xml:space="preserve">3.79708361625671</t>
@@ -3830,10 +3830,10 @@
     <t xml:space="preserve">3.75124216079712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65878200531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66188979148865</t>
+    <t xml:space="preserve">3.65878248214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66188931465149</t>
   </si>
   <si>
     <t xml:space="preserve">3.54612016677856</t>
@@ -3842,16 +3842,16 @@
     <t xml:space="preserve">3.55622148513794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38373231887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4225811958313</t>
+    <t xml:space="preserve">3.38373208045959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42258143424988</t>
   </si>
   <si>
     <t xml:space="preserve">3.16384768486023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06361818313599</t>
+    <t xml:space="preserve">3.06361794471741</t>
   </si>
   <si>
     <t xml:space="preserve">2.87481260299683</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">2.74505758285522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82042455673218</t>
+    <t xml:space="preserve">2.8204243183136</t>
   </si>
   <si>
     <t xml:space="preserve">2.93308615684509</t>
@@ -3884,13 +3884,13 @@
     <t xml:space="preserve">3.0783805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05118656158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05895614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06284117698669</t>
+    <t xml:space="preserve">3.05118680000305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05895638465881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06284093856812</t>
   </si>
   <si>
     <t xml:space="preserve">3.1622941493988</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">3.10246682167053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09780478477478</t>
+    <t xml:space="preserve">3.09780502319336</t>
   </si>
   <si>
     <t xml:space="preserve">3.13199210166931</t>
@@ -3914,10 +3914,10 @@
     <t xml:space="preserve">3.24853849411011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17161750793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20269703865051</t>
+    <t xml:space="preserve">3.17161774635315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20269727706909</t>
   </si>
   <si>
     <t xml:space="preserve">3.09236621856689</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">3.35498428344727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36275386810303</t>
+    <t xml:space="preserve">3.36275434494019</t>
   </si>
   <si>
     <t xml:space="preserve">3.37984728813171</t>
@@ -3938,16 +3938,16 @@
     <t xml:space="preserve">3.42335820198059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53058075904846</t>
+    <t xml:space="preserve">3.53058099746704</t>
   </si>
   <si>
     <t xml:space="preserve">3.59273934364319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51970362663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52747273445129</t>
+    <t xml:space="preserve">3.51970338821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52747249603271</t>
   </si>
   <si>
     <t xml:space="preserve">3.59740114212036</t>
@@ -3956,16 +3956,16 @@
     <t xml:space="preserve">3.6113862991333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69374632835388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63624954223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6098325252533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36430811882019</t>
+    <t xml:space="preserve">3.6937460899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63624930381775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60983228683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36430788040161</t>
   </si>
   <si>
     <t xml:space="preserve">3.30059599876404</t>
@@ -3977,7 +3977,7 @@
     <t xml:space="preserve">3.46686887741089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51659536361694</t>
+    <t xml:space="preserve">3.51659512519836</t>
   </si>
   <si>
     <t xml:space="preserve">3.53524279594421</t>
@@ -3992,13 +3992,13 @@
     <t xml:space="preserve">3.51193332672119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63948941230774</t>
+    <t xml:space="preserve">3.63948965072632</t>
   </si>
   <si>
     <t xml:space="preserve">3.6378333568573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65771150588989</t>
+    <t xml:space="preserve">3.65771174430847</t>
   </si>
   <si>
     <t xml:space="preserve">3.71403574943542</t>
@@ -4019,7 +4019,7 @@
     <t xml:space="preserve">3.64942908287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59310555458069</t>
+    <t xml:space="preserve">3.59310579299927</t>
   </si>
   <si>
     <t xml:space="preserve">3.59807538986206</t>
@@ -4037,13 +4037,13 @@
     <t xml:space="preserve">2.97686076164246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01993155479431</t>
+    <t xml:space="preserve">3.01993131637573</t>
   </si>
   <si>
     <t xml:space="preserve">3.0828812122345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97520399093628</t>
+    <t xml:space="preserve">2.97520422935486</t>
   </si>
   <si>
     <t xml:space="preserve">2.96692132949829</t>
@@ -4052,13 +4052,13 @@
     <t xml:space="preserve">3.01330518722534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98514366149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0000524520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96195125579834</t>
+    <t xml:space="preserve">2.98514342308044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00005269050598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96195149421692</t>
   </si>
   <si>
     <t xml:space="preserve">3.05968928337097</t>
@@ -4067,13 +4067,13 @@
     <t xml:space="preserve">3.03318405151367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04809308052063</t>
+    <t xml:space="preserve">3.04809331893921</t>
   </si>
   <si>
     <t xml:space="preserve">3.00999212265015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89734482765198</t>
+    <t xml:space="preserve">2.89734506607056</t>
   </si>
   <si>
     <t xml:space="preserve">2.90397143363953</t>
@@ -4094,13 +4094,13 @@
     <t xml:space="preserve">2.80457711219788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71512222290039</t>
+    <t xml:space="preserve">2.71512246131897</t>
   </si>
   <si>
     <t xml:space="preserve">2.70683932304382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69193029403687</t>
+    <t xml:space="preserve">2.69193005561829</t>
   </si>
   <si>
     <t xml:space="preserve">2.52792954444885</t>
@@ -4109,13 +4109,13 @@
     <t xml:space="preserve">2.64885926246643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71346569061279</t>
+    <t xml:space="preserve">2.71346545219421</t>
   </si>
   <si>
     <t xml:space="preserve">2.81120347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78138518333435</t>
+    <t xml:space="preserve">2.78138494491577</t>
   </si>
   <si>
     <t xml:space="preserve">2.79132437705994</t>
@@ -4130,7 +4130,7 @@
     <t xml:space="preserve">2.71843552589417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71677875518799</t>
+    <t xml:space="preserve">2.71677851676941</t>
   </si>
   <si>
     <t xml:space="preserve">2.7747585773468</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">2.83770871162415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84599161148071</t>
+    <t xml:space="preserve">2.84599137306213</t>
   </si>
   <si>
     <t xml:space="preserve">2.92385029792786</t>
@@ -4151,7 +4151,7 @@
     <t xml:space="preserve">2.97354745864868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95035552978516</t>
+    <t xml:space="preserve">2.95035576820374</t>
   </si>
   <si>
     <t xml:space="preserve">2.91225433349609</t>
@@ -4163,22 +4163,22 @@
     <t xml:space="preserve">2.93047666549683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98183035850525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98017406463623</t>
+    <t xml:space="preserve">2.98183012008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98017382621765</t>
   </si>
   <si>
     <t xml:space="preserve">2.92219400405884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93544602394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8542742729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75984978675842</t>
+    <t xml:space="preserve">2.93544626235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85427451133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75984954833984</t>
   </si>
   <si>
     <t xml:space="preserve">2.79960751533508</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">2.68696045875549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69358682632446</t>
+    <t xml:space="preserve">2.69358706474304</t>
   </si>
   <si>
     <t xml:space="preserve">2.64223313331604</t>
@@ -4238,25 +4238,25 @@
     <t xml:space="preserve">2.51799011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53621244430542</t>
+    <t xml:space="preserve">2.536212682724</t>
   </si>
   <si>
     <t xml:space="preserve">2.46663618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44344425201416</t>
+    <t xml:space="preserve">2.44344449043274</t>
   </si>
   <si>
     <t xml:space="preserve">2.37221193313599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42687892913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65051579475403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67702102661133</t>
+    <t xml:space="preserve">2.4268786907196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65051603317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67702126502991</t>
   </si>
   <si>
     <t xml:space="preserve">2.58259654045105</t>
@@ -4268,10 +4268,10 @@
     <t xml:space="preserve">2.53124260902405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52461647987366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42190885543823</t>
+    <t xml:space="preserve">2.52461624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42190909385681</t>
   </si>
   <si>
     <t xml:space="preserve">2.48651528358459</t>
@@ -4298,7 +4298,7 @@
     <t xml:space="preserve">2.59750533103943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62235403060913</t>
+    <t xml:space="preserve">2.62235426902771</t>
   </si>
   <si>
     <t xml:space="preserve">2.60413193702698</t>
@@ -4322,10 +4322,10 @@
     <t xml:space="preserve">2.86587023735046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95366859436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99839615821838</t>
+    <t xml:space="preserve">2.95366883277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9983959197998</t>
   </si>
   <si>
     <t xml:space="preserve">2.99342632293701</t>
@@ -4337,13 +4337,13 @@
     <t xml:space="preserve">2.98679995536804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00170946121216</t>
+    <t xml:space="preserve">3.00170922279358</t>
   </si>
   <si>
     <t xml:space="preserve">3.00833559036255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98348665237427</t>
+    <t xml:space="preserve">2.98348689079285</t>
   </si>
   <si>
     <t xml:space="preserve">3.00336575508118</t>
@@ -4352,22 +4352,22 @@
     <t xml:space="preserve">3.03484082221985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06631565093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04478025436401</t>
+    <t xml:space="preserve">3.06631541252136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04478001594543</t>
   </si>
   <si>
     <t xml:space="preserve">3.10441660881042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08619451522827</t>
+    <t xml:space="preserve">3.08619475364685</t>
   </si>
   <si>
     <t xml:space="preserve">2.94869875907898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91722416877747</t>
+    <t xml:space="preserve">2.91722393035889</t>
   </si>
   <si>
     <t xml:space="preserve">2.86255717277527</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">2.99176979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99673938751221</t>
+    <t xml:space="preserve">2.99673962593079</t>
   </si>
   <si>
     <t xml:space="preserve">3.03649711608887</t>
@@ -4406,22 +4406,22 @@
     <t xml:space="preserve">3.21375060081482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2518515586853</t>
+    <t xml:space="preserve">3.25185179710388</t>
   </si>
   <si>
     <t xml:space="preserve">3.22865962982178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.225346326828</t>
+    <t xml:space="preserve">3.22534656524658</t>
   </si>
   <si>
     <t xml:space="preserve">3.26013445854187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23031616210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20215463638306</t>
+    <t xml:space="preserve">3.23031640052795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20215439796448</t>
   </si>
   <si>
     <t xml:space="preserve">3.20546746253967</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">3.18724536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23528599739075</t>
+    <t xml:space="preserve">3.23528575897217</t>
   </si>
   <si>
     <t xml:space="preserve">3.2816698551178</t>
@@ -4439,28 +4439,28 @@
     <t xml:space="preserve">3.29657912254333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34627628326416</t>
+    <t xml:space="preserve">3.34627652168274</t>
   </si>
   <si>
     <t xml:space="preserve">3.32805395126343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34793281555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37443804740906</t>
+    <t xml:space="preserve">3.34793257713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37443780899048</t>
   </si>
   <si>
     <t xml:space="preserve">3.43904447555542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44235777854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29160952568054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29492235183716</t>
+    <t xml:space="preserve">3.44235754013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29160928726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29492259025574</t>
   </si>
   <si>
     <t xml:space="preserve">3.31811451911926</t>
@@ -4481,7 +4481,7 @@
     <t xml:space="preserve">3.49536776542664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43573093414307</t>
+    <t xml:space="preserve">3.43573117256165</t>
   </si>
   <si>
     <t xml:space="preserve">3.38437747955322</t>
@@ -4496,28 +4496,28 @@
     <t xml:space="preserve">3.34958958625793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38106393814087</t>
+    <t xml:space="preserve">3.38106417655945</t>
   </si>
   <si>
     <t xml:space="preserve">3.387690782547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39266037940979</t>
+    <t xml:space="preserve">3.39266061782837</t>
   </si>
   <si>
     <t xml:space="preserve">3.41088271141052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42082238197327</t>
+    <t xml:space="preserve">3.42082214355469</t>
   </si>
   <si>
     <t xml:space="preserve">3.42247867584229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37609457969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37775135040283</t>
+    <t xml:space="preserve">3.37609481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37775111198425</t>
   </si>
   <si>
     <t xml:space="preserve">3.34130644798279</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">3.13092184066772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02324485778809</t>
+    <t xml:space="preserve">3.02324461936951</t>
   </si>
   <si>
     <t xml:space="preserve">3.07625508308411</t>
@@ -4541,22 +4541,22 @@
     <t xml:space="preserve">3.13423490524292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1060733795166</t>
+    <t xml:space="preserve">3.10607314109802</t>
   </si>
   <si>
     <t xml:space="preserve">3.01164865493774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06465888023376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1093864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07459807395935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08453798294067</t>
+    <t xml:space="preserve">3.06465911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10938620567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07459831237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08453774452209</t>
   </si>
   <si>
     <t xml:space="preserve">3.11269927024841</t>
@@ -4574,7 +4574,7 @@
     <t xml:space="preserve">3.18393230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20381093025208</t>
+    <t xml:space="preserve">3.20381116867065</t>
   </si>
   <si>
     <t xml:space="preserve">3.14914417266846</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">3.11932587623596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04146695137024</t>
+    <t xml:space="preserve">3.04146671295166</t>
   </si>
   <si>
     <t xml:space="preserve">3.07294201850891</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">3.0514063835144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08785104751587</t>
+    <t xml:space="preserve">3.08785080909729</t>
   </si>
   <si>
     <t xml:space="preserve">3.053062915802</t>
@@ -5979,6 +5979,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.21500015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10500001907349</t>
   </si>
 </sst>
 </file>
@@ -71005,7 +71008,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6496527778</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>158611</v>
@@ -71026,6 +71029,32 @@
         <v>1965</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6520138889</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>183694</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>6.18499994277954</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>6.1100001335144</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>6.10500001907349</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1989</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24674654006958</t>
+    <t xml:space="preserve">4.24674606323242</t>
   </si>
   <si>
     <t xml:space="preserve">ANIM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33184623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13419580459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96948671340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95301556587219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94203495979309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07380294799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93105459213257</t>
+    <t xml:space="preserve">4.33184719085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13419628143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96948599815369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95301532745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94203519821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07380247116089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93105530738831</t>
   </si>
   <si>
     <t xml:space="preserve">3.82673859596252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76085567474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6784999370575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73889374732971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40398621559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53300833702087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76909041404724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79379677772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79928731918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88438725471497</t>
+    <t xml:space="preserve">3.76085519790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67850089073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73889446258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40398573875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53300738334656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76909065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79379725456238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79928708076477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8843879699707</t>
   </si>
   <si>
     <t xml:space="preserve">3.67575550079346</t>
@@ -101,124 +101,124 @@
     <t xml:space="preserve">3.70595288276672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64006853103638</t>
+    <t xml:space="preserve">3.6400682926178</t>
   </si>
   <si>
     <t xml:space="preserve">3.57967519760132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35731863975525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4506528377533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37653470039368</t>
+    <t xml:space="preserve">3.35731792449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45065307617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37653493881226</t>
   </si>
   <si>
     <t xml:space="preserve">3.06633234024048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95652675628662</t>
+    <t xml:space="preserve">2.95652627944946</t>
   </si>
   <si>
     <t xml:space="preserve">3.19535422325134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98397850990295</t>
+    <t xml:space="preserve">2.98397779464722</t>
   </si>
   <si>
     <t xml:space="preserve">3.2420220375061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20084500312805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48633933067322</t>
+    <t xml:space="preserve">3.20084476470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48634028434753</t>
   </si>
   <si>
     <t xml:space="preserve">3.38202428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31065082550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38751530647278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2667281627655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11299967765808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08554840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07182240486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06084203720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15692162513733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.302414894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43967247009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35182785987854</t>
+    <t xml:space="preserve">3.31065058708191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3875150680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26672792434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11299991607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08554816246033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07182288169861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06084227561951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15692234039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30241465568542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43967318534851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35182762145996</t>
   </si>
   <si>
     <t xml:space="preserve">3.28319883346558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2228057384491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25300288200378</t>
+    <t xml:space="preserve">3.22280550003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25300264358521</t>
   </si>
   <si>
     <t xml:space="preserve">3.57693004608154</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47261500358582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46437931060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.590656042099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56320476531982</t>
+    <t xml:space="preserve">3.47261476516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46437954902649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59065556526184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56320452690125</t>
   </si>
   <si>
     <t xml:space="preserve">3.61261677742004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51653647422791</t>
+    <t xml:space="preserve">3.51653671264648</t>
   </si>
   <si>
     <t xml:space="preserve">3.43418216705322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37104344367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45888900756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5302631855011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32986640930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27221846580505</t>
+    <t xml:space="preserve">3.37104368209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45888876914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53026294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32986617088318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27221870422363</t>
   </si>
   <si>
     <t xml:space="preserve">3.0910382270813</t>
@@ -233,103 +233,103 @@
     <t xml:space="preserve">3.28594446182251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31888556480408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23927688598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42594695091248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41771173477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40947604179382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41496658325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44241762161255</t>
+    <t xml:space="preserve">3.31888604164124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23927617073059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4259467124939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41771149635315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4094762802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41496562957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44241738319397</t>
   </si>
   <si>
     <t xml:space="preserve">3.4616334438324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44790887832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49732089042664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39300560951233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3737895488739</t>
+    <t xml:space="preserve">3.4479079246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49732112884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39300513267517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37378978729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.26123809814453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26947355270386</t>
+    <t xml:space="preserve">3.26947331428528</t>
   </si>
   <si>
     <t xml:space="preserve">3.15417766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16241240501404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0196647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94829130172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82201409339905</t>
+    <t xml:space="preserve">3.1624128818512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01966500282288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94829106330872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82201433181763</t>
   </si>
   <si>
     <t xml:space="preserve">2.93182015419006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06907749176025</t>
+    <t xml:space="preserve">3.06907725334167</t>
   </si>
   <si>
     <t xml:space="preserve">3.00044870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91809391975403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8741717338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.852210521698</t>
+    <t xml:space="preserve">2.91809439659119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87417197227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85221028327942</t>
   </si>
   <si>
     <t xml:space="preserve">2.89064288139343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97133898735046</t>
+    <t xml:space="preserve">2.97133874893188</t>
   </si>
   <si>
     <t xml:space="preserve">3.06356287002563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23648262023926</t>
+    <t xml:space="preserve">3.23648285865784</t>
   </si>
   <si>
     <t xml:space="preserve">3.24224638938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29988622665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17884302139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15866851806641</t>
+    <t xml:space="preserve">3.29988598823547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17884278297424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15866875648499</t>
   </si>
   <si>
     <t xml:space="preserve">3.04050707817078</t>
@@ -338,16 +338,16 @@
     <t xml:space="preserve">2.97998452186584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96269297599792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02321481704712</t>
+    <t xml:space="preserve">2.9626932144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02321457862854</t>
   </si>
   <si>
     <t xml:space="preserve">3.00015902519226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95692825317383</t>
+    <t xml:space="preserve">2.95692849159241</t>
   </si>
   <si>
     <t xml:space="preserve">2.81859278678894</t>
@@ -359,37 +359,37 @@
     <t xml:space="preserve">2.66988158226013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61454749107361</t>
+    <t xml:space="preserve">2.61454725265503</t>
   </si>
   <si>
     <t xml:space="preserve">2.54768514633179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70331287384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75288414955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90505337715149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92234444618225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96845698356628</t>
+    <t xml:space="preserve">2.70331263542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75288343429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90505290031433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92234492301941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96845674514771</t>
   </si>
   <si>
     <t xml:space="preserve">2.53615689277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26179146766663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49004507064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41972422599792</t>
+    <t xml:space="preserve">2.26179122924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49004530906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4197244644165</t>
   </si>
   <si>
     <t xml:space="preserve">2.42664122581482</t>
@@ -398,55 +398,55 @@
     <t xml:space="preserve">2.49235081672668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36900115013123</t>
+    <t xml:space="preserve">2.3690013885498</t>
   </si>
   <si>
     <t xml:space="preserve">2.28830575942993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29752731323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30559754371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35747313499451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4324049949646</t>
+    <t xml:space="preserve">2.29752779006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30559730529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35747289657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43240523338318</t>
   </si>
   <si>
     <t xml:space="preserve">2.61108875274658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59379720687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68025708198547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59725522994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60647797584534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56958794593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62838125228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62261700630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59494996070862</t>
+    <t xml:space="preserve">2.59379696846008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68025684356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59725546836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60647821426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56958842277527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62838101387024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62261724472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5949501991272</t>
   </si>
   <si>
     <t xml:space="preserve">2.61685347557068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54653215408325</t>
+    <t xml:space="preserve">2.54653239250183</t>
   </si>
   <si>
     <t xml:space="preserve">2.63414573669434</t>
@@ -455,16 +455,16 @@
     <t xml:space="preserve">2.58226895332336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40358519554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41511368751526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4381697177887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55114388465881</t>
+    <t xml:space="preserve">2.4035849571228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4151132106781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43816947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55114364624023</t>
   </si>
   <si>
     <t xml:space="preserve">2.58572769165039</t>
@@ -479,19 +479,19 @@
     <t xml:space="preserve">2.604172706604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54307413101196</t>
+    <t xml:space="preserve">2.54307436943054</t>
   </si>
   <si>
     <t xml:space="preserve">2.41857147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37015414237976</t>
+    <t xml:space="preserve">2.37015438079834</t>
   </si>
   <si>
     <t xml:space="preserve">2.39321041107178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51310133934021</t>
+    <t xml:space="preserve">2.51310157775879</t>
   </si>
   <si>
     <t xml:space="preserve">2.50964260101318</t>
@@ -500,16 +500,16 @@
     <t xml:space="preserve">2.46122527122498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4485445022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50733709335327</t>
+    <t xml:space="preserve">2.44854426383972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50733685493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.50157356262207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49696230888367</t>
+    <t xml:space="preserve">2.49696254730225</t>
   </si>
   <si>
     <t xml:space="preserve">2.51540684700012</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">2.53039336204529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57304739952087</t>
+    <t xml:space="preserve">2.57304716110229</t>
   </si>
   <si>
     <t xml:space="preserve">2.66181230545044</t>
@@ -527,46 +527,46 @@
     <t xml:space="preserve">2.62722849845886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73789715766907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83012104034424</t>
+    <t xml:space="preserve">2.73789691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83012080192566</t>
   </si>
   <si>
     <t xml:space="preserve">2.7909255027771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67449307441711</t>
+    <t xml:space="preserve">2.67449331283569</t>
   </si>
   <si>
     <t xml:space="preserve">2.6560480594635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64797878265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65720081329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6456732749939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5200183391571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51886510848999</t>
+    <t xml:space="preserve">2.64797925949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65720105171204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64567351341248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52001786231995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51886487007141</t>
   </si>
   <si>
     <t xml:space="preserve">2.49580931663513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5211706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52462887763977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54192185401917</t>
+    <t xml:space="preserve">2.52117085456848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52462911605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54192161560059</t>
   </si>
   <si>
     <t xml:space="preserve">2.47275328636169</t>
@@ -581,22 +581,22 @@
     <t xml:space="preserve">2.32173657417297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32519507408142</t>
+    <t xml:space="preserve">2.32519483566284</t>
   </si>
   <si>
     <t xml:space="preserve">2.24795746803284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26524901390076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32634806632996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38629293441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44393348693848</t>
+    <t xml:space="preserve">2.26524972915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32634782791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3862931728363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4439332485199</t>
   </si>
   <si>
     <t xml:space="preserve">2.44623875617981</t>
@@ -605,55 +605,55 @@
     <t xml:space="preserve">2.5707414150238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57996320724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56267142295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55806040763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50387859344482</t>
+    <t xml:space="preserve">2.57996344566345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56267166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55806064605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5038788318634</t>
   </si>
   <si>
     <t xml:space="preserve">2.50503158569336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38168215751648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60993623733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59956073760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55344891548157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70907688140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6791045665741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58111596107483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80130124092102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81282949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7229106426239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78285622596741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82550978660583</t>
+    <t xml:space="preserve">2.38168239593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60993599891663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59956097602844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55344915390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70907735824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67910432815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58111667633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80130100250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81282925605774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72291111946106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78285598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82551026344299</t>
   </si>
   <si>
     <t xml:space="preserve">2.92522692680359</t>
@@ -668,22 +668,22 @@
     <t xml:space="preserve">3.00592279434204</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03474283218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9972767829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98574805259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94828271865845</t>
+    <t xml:space="preserve">3.03474307060242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99727630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98574876785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94828295707703</t>
   </si>
   <si>
     <t xml:space="preserve">2.93963694572449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97422075271606</t>
+    <t xml:space="preserve">2.9742214679718</t>
   </si>
   <si>
     <t xml:space="preserve">2.99151301383972</t>
@@ -695,115 +695,115 @@
     <t xml:space="preserve">3.03186082839966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16155028343201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13849472999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11255645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12984848022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20478081703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16443204879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19613432884216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1990168094635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12408494949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14137649536133</t>
+    <t xml:space="preserve">3.16155076026917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13849496841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11255693435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12984871864319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2047803401947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16443252563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19613480567932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19901704788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12408518791199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14137697219849</t>
   </si>
   <si>
     <t xml:space="preserve">3.08373689651489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30276918411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26242089271545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1874885559082</t>
+    <t xml:space="preserve">3.30276894569397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2624204158783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18748903274536</t>
   </si>
   <si>
     <t xml:space="preserve">3.28547620773315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2278368473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17596077919006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24800992012024</t>
+    <t xml:space="preserve">3.22783637046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17596054077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2480103969574</t>
   </si>
   <si>
     <t xml:space="preserve">3.26818442344666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23936462402344</t>
+    <t xml:space="preserve">3.23936414718628</t>
   </si>
   <si>
     <t xml:space="preserve">3.09238266944885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10102844238281</t>
+    <t xml:space="preserve">3.10102891921997</t>
   </si>
   <si>
     <t xml:space="preserve">3.05491662025452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08085441589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11832070350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15002274513245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01168704032898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92810869216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95404672622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7851619720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91369867324829</t>
+    <t xml:space="preserve">3.08085465431213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11832094192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15002250671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0116868019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92810893058777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95404696464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78516173362732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91369891166687</t>
   </si>
   <si>
     <t xml:space="preserve">2.98863077163696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00304055213928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02609705924988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07797265052795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05779886245728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18172430992126</t>
+    <t xml:space="preserve">3.0030403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02609658241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07797312736511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05779910087585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18172407150269</t>
   </si>
   <si>
     <t xml:space="preserve">3.17019701004028</t>
@@ -815,70 +815,70 @@
     <t xml:space="preserve">3.24512839317322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25089240074158</t>
+    <t xml:space="preserve">3.250892162323</t>
   </si>
   <si>
     <t xml:space="preserve">3.27106690406799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27394914627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28259468078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25665616989136</t>
+    <t xml:space="preserve">3.27394843101501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28259515762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25665593147278</t>
   </si>
   <si>
     <t xml:space="preserve">3.18460655212402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29412245750427</t>
+    <t xml:space="preserve">3.29412269592285</t>
   </si>
   <si>
     <t xml:space="preserve">3.10391116142273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34023427963257</t>
+    <t xml:space="preserve">3.34023451805115</t>
   </si>
   <si>
     <t xml:space="preserve">3.4439868927002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43245816230774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46415996551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45839667320251</t>
+    <t xml:space="preserve">3.4324586391449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46416020393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45839691162109</t>
   </si>
   <si>
     <t xml:space="preserve">3.49298024177551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44686841964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50450849533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60249614715576</t>
+    <t xml:space="preserve">3.44686818122864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50450801849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60249638557434</t>
   </si>
   <si>
     <t xml:space="preserve">3.51603627204895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46992444992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44110441207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42381238937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41228413581848</t>
+    <t xml:space="preserve">3.46992468833923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44110417366028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42381286621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41228461265564</t>
   </si>
   <si>
     <t xml:space="preserve">3.39499258995056</t>
@@ -890,52 +890,52 @@
     <t xml:space="preserve">3.4893524646759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49236226081848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59472560882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72117328643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71515226364136</t>
+    <t xml:space="preserve">3.4923632144928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5947253704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72117304801941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71515202522278</t>
   </si>
   <si>
     <t xml:space="preserve">3.58870387077332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4682776927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41107535362244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49838447570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5405330657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5044059753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51644897460938</t>
+    <t xml:space="preserve">3.46827793121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41107559204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49838423728943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54053330421448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50440573692322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51644849777222</t>
   </si>
   <si>
     <t xml:space="preserve">3.54956531524658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70913028717041</t>
+    <t xml:space="preserve">3.70912981033325</t>
   </si>
   <si>
     <t xml:space="preserve">3.72418403625488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64891672134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75127911567688</t>
+    <t xml:space="preserve">3.64891695976257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75127959251404</t>
   </si>
   <si>
     <t xml:space="preserve">3.72719383239746</t>
@@ -944,58 +944,58 @@
     <t xml:space="preserve">3.76332211494446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73923659324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74525809288025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7121410369873</t>
+    <t xml:space="preserve">3.73923707008362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74525785446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71214175224304</t>
   </si>
   <si>
     <t xml:space="preserve">3.7031090259552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75730085372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7753643989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77837514877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84159898757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85966348648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82654571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09750604629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14266538619995</t>
+    <t xml:space="preserve">3.75730013847351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77536463737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77837562561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84159970283508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85966300964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82654619216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09750652313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14266490936279</t>
   </si>
   <si>
     <t xml:space="preserve">4.19685649871826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17277145385742</t>
+    <t xml:space="preserve">4.17277193069458</t>
   </si>
   <si>
     <t xml:space="preserve">4.19083547592163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22094249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19986724853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24502754211426</t>
+    <t xml:space="preserve">4.22094202041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19986772537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24502658843994</t>
   </si>
   <si>
     <t xml:space="preserve">4.2691125869751</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">4.26309156417847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21492147445679</t>
+    <t xml:space="preserve">4.21492099761963</t>
   </si>
   <si>
     <t xml:space="preserve">4.15470790863037</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">4.145676612854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13664388656616</t>
+    <t xml:space="preserve">4.13664436340332</t>
   </si>
   <si>
     <t xml:space="preserve">4.22395324707031</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">4.25104856491089</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28717613220215</t>
+    <t xml:space="preserve">4.28717660903931</t>
   </si>
   <si>
     <t xml:space="preserve">4.11857938766479</t>
@@ -1037,160 +1037,160 @@
     <t xml:space="preserve">4.25405931472778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09449481964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08847284317017</t>
+    <t xml:space="preserve">4.09449434280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08847332000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.04030275344849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05234527587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95901536941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86267328262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86568450927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94396209716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94697213172913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95600414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98008966445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97406840324402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07341957092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06438827514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98912119865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96202516555786</t>
+    <t xml:space="preserve">4.05234479904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95901489257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86267352104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86568474769592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94396185874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94697260856628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95600366592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98008942604065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97406792640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07342052459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06438779830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98912191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96202564239502</t>
   </si>
   <si>
     <t xml:space="preserve">4.01320648193359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03428077697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00417423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00116348266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90783429145813</t>
+    <t xml:space="preserve">4.03428173065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00417470932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00116395950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90783357620239</t>
   </si>
   <si>
     <t xml:space="preserve">3.88977026939392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95299315452576</t>
+    <t xml:space="preserve">3.95299363136292</t>
   </si>
   <si>
     <t xml:space="preserve">4.01019620895386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11255788803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15771865844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06739902496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98611092567444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93191885948181</t>
+    <t xml:space="preserve">4.11255836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15771818161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06739854812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9861114025116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93191862106323</t>
   </si>
   <si>
     <t xml:space="preserve">3.90181159973145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87471699714661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85364127159119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82353496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579105377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84762072563171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83256793022156</t>
+    <t xml:space="preserve">3.87471675872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85364151000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82353544235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579129219055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84762096405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83256769180298</t>
   </si>
   <si>
     <t xml:space="preserve">3.88073825836182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88374805450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92589712142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92890810966492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88675951957703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9138548374176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91084456443787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84460973739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82052564620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69106602668762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70611977577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55558705329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47429871559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33580851554871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40204262733459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52246928215027</t>
+    <t xml:space="preserve">3.88374853134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92589735984802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92890858650208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88675928115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91385507583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91084480285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84460926055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8205246925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69106674194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70611929893494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55558657646179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47429895401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33580827713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40204286575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52246952056885</t>
   </si>
   <si>
     <t xml:space="preserve">3.54354405403137</t>
@@ -1199,103 +1199,103 @@
     <t xml:space="preserve">3.53150153160095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57365036010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60074639320374</t>
+    <t xml:space="preserve">3.57365083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60074687004089</t>
   </si>
   <si>
     <t xml:space="preserve">3.5766613483429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53752303123474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55257558822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50139427185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45021390914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51042675971985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48634171485901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43817186355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40806484222412</t>
+    <t xml:space="preserve">3.53752326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55257606506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50139451026917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45021462440491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51042628288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48634195327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43817138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40806436538696</t>
   </si>
   <si>
     <t xml:space="preserve">3.53451204299927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60977840423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35387229919434</t>
+    <t xml:space="preserve">3.60977816581726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35387253761292</t>
   </si>
   <si>
     <t xml:space="preserve">3.42612862586975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44419264793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32376599311829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39000010490417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61278939247131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73020482063293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6669807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64590716362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63386416435242</t>
+    <t xml:space="preserve">3.4441921710968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32376575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39000058174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61278915405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73020505905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66698098182678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64590668678284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63386392593384</t>
   </si>
   <si>
     <t xml:space="preserve">3.81450247764587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86869549751282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93492960929871</t>
+    <t xml:space="preserve">3.86869502067566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93492937088013</t>
   </si>
   <si>
     <t xml:space="preserve">4.04331350326538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99213194847107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9831006526947</t>
+    <t xml:space="preserve">3.99213218688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98310017585754</t>
   </si>
   <si>
     <t xml:space="preserve">4.06137704849243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1246018409729</t>
+    <t xml:space="preserve">4.12460088729858</t>
   </si>
   <si>
     <t xml:space="preserve">4.16072940826416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07040977478027</t>
+    <t xml:space="preserve">4.07040882110596</t>
   </si>
   <si>
     <t xml:space="preserve">4.08245229721069</t>
@@ -1304,91 +1304,91 @@
     <t xml:space="preserve">3.80848240852356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89880180358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91987752914429</t>
+    <t xml:space="preserve">3.89880204200745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91987681388855</t>
   </si>
   <si>
     <t xml:space="preserve">3.78439617156982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77235412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79945039749146</t>
+    <t xml:space="preserve">3.77235388755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7994499206543</t>
   </si>
   <si>
     <t xml:space="preserve">3.73622608184814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75429034233093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76633238792419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63988471031189</t>
+    <t xml:space="preserve">3.75429081916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76633310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63988518714905</t>
   </si>
   <si>
     <t xml:space="preserve">3.56160807609558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66999220848083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96503615379333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7934296131134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74224781990051</t>
+    <t xml:space="preserve">3.66999101638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96503591537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79342889785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74224710464478</t>
   </si>
   <si>
     <t xml:space="preserve">3.79164910316467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77612233161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78854370117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70469903945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58358931541443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55914282798767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55258846282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51326107978821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61157965660095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58536171913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76888990402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89998149871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8934268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85082268714905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81149458885193</t>
+    <t xml:space="preserve">3.77612257003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78854441642761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70469927787781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58358979225159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55914306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55258822441101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51326131820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61158013343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58536148071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76888966560364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89998173713684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89342761039734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85082221031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81149530410767</t>
   </si>
   <si>
     <t xml:space="preserve">3.63779830932617</t>
@@ -1397,133 +1397,133 @@
     <t xml:space="preserve">3.7557806968689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73939418792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86065435409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099054336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81804919242859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96552801132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98846840858459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93275499343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86720895767212</t>
+    <t xml:space="preserve">3.73939442634583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86065411567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099078178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81804943084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9655282497406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98846888542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93275475502014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86720871925354</t>
   </si>
   <si>
     <t xml:space="preserve">3.84426760673523</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91309070587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82132625579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03107309341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04418277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02451848983765</t>
+    <t xml:space="preserve">3.91309094429016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82132649421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03107404708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04418325424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0245189666748</t>
   </si>
   <si>
     <t xml:space="preserve">3.98191380500793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90653610229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99830055236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77544450759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76561236381531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71973037719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71645331382751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56897497177124</t>
+    <t xml:space="preserve">3.90653681755066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99830031394958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77544474601746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76561307907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71973085403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71645283699036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56897473335266</t>
   </si>
   <si>
     <t xml:space="preserve">3.50670623779297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46737861633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27467370033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93645691871643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03477573394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19077467918396</t>
+    <t xml:space="preserve">3.46737909317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27467346191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93645715713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03477597236633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19077491760254</t>
   </si>
   <si>
     <t xml:space="preserve">3.42149639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41494178771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33628726005554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3166229724884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35595035552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21174955368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30023646354675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32645511627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3985550403595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33956408500671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29040503501892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27729558944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28057289123535</t>
+    <t xml:space="preserve">3.41494226455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3362865447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31662321090698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35595059394836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.211749792099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30023598670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32645463943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39855551719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33956384658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29040455818176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2772958278656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28057312965393</t>
   </si>
   <si>
     <t xml:space="preserve">3.1829092502594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12260746955872</t>
+    <t xml:space="preserve">3.12260723114014</t>
   </si>
   <si>
     <t xml:space="preserve">3.07148146629333</t>
@@ -1532,40 +1532,40 @@
     <t xml:space="preserve">3.01511168479919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89975094795227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01904463768005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01380109786987</t>
+    <t xml:space="preserve">2.89975118637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01904487609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01380085945129</t>
   </si>
   <si>
     <t xml:space="preserve">3.04919576644897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97971725463867</t>
+    <t xml:space="preserve">2.97971701622009</t>
   </si>
   <si>
     <t xml:space="preserve">3.02691006660461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13440537452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10425448417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04264116287231</t>
+    <t xml:space="preserve">3.13440561294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10425424575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04264163970947</t>
   </si>
   <si>
     <t xml:space="preserve">3.00200247764587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00462460517883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98233890533447</t>
+    <t xml:space="preserve">3.00462484359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98233938217163</t>
   </si>
   <si>
     <t xml:space="preserve">2.98627161979675</t>
@@ -1574,16 +1574,16 @@
     <t xml:space="preserve">2.92072582244873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92728042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00069189071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01249027252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03739762306213</t>
+    <t xml:space="preserve">2.92728018760681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00069165229797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01249003410339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03739738464355</t>
   </si>
   <si>
     <t xml:space="preserve">2.95612072944641</t>
@@ -1592,10 +1592,10 @@
     <t xml:space="preserve">2.92465877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84469270706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97709488868713</t>
+    <t xml:space="preserve">2.84469223022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97709536552429</t>
   </si>
   <si>
     <t xml:space="preserve">3.00724577903748</t>
@@ -1604,10 +1604,10 @@
     <t xml:space="preserve">2.89057469367981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77259182929993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79487776756287</t>
+    <t xml:space="preserve">2.77259206771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79487752914429</t>
   </si>
   <si>
     <t xml:space="preserve">2.73064279556274</t>
@@ -1616,28 +1616,28 @@
     <t xml:space="preserve">2.71228981018066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70049142837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77914619445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76996994018555</t>
+    <t xml:space="preserve">2.70049166679382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77914643287659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76997017860413</t>
   </si>
   <si>
     <t xml:space="preserve">2.73719763755798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72146606445312</t>
+    <t xml:space="preserve">2.7214663028717</t>
   </si>
   <si>
     <t xml:space="preserve">2.69000434875488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63625645637512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64936566352844</t>
+    <t xml:space="preserve">2.63625621795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64936542510986</t>
   </si>
   <si>
     <t xml:space="preserve">2.62052536010742</t>
@@ -1646,88 +1646,88 @@
     <t xml:space="preserve">2.67689514160156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7201554775238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87615466117859</t>
+    <t xml:space="preserve">2.72015523910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87615442276001</t>
   </si>
   <si>
     <t xml:space="preserve">2.85124707221985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86697840690613</t>
+    <t xml:space="preserve">2.86697816848755</t>
   </si>
   <si>
     <t xml:space="preserve">2.93907904624939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91154956817627</t>
+    <t xml:space="preserve">2.91154932975769</t>
   </si>
   <si>
     <t xml:space="preserve">2.91679286956787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92596960067749</t>
+    <t xml:space="preserve">2.92596983909607</t>
   </si>
   <si>
     <t xml:space="preserve">2.94170022010803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99807000160217</t>
+    <t xml:space="preserve">2.99807024002075</t>
   </si>
   <si>
     <t xml:space="preserve">3.04133033752441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99675893783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99413728713989</t>
+    <t xml:space="preserve">2.99675917625427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99413681030273</t>
   </si>
   <si>
     <t xml:space="preserve">2.96267509460449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96005296707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91286015510559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77521419525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70704650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68869376182556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70573496818542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74244070053101</t>
+    <t xml:space="preserve">2.96005320549011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91286039352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77521395683289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70704627037048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68869352340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.705735206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74244093894958</t>
   </si>
   <si>
     <t xml:space="preserve">2.64674401283264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64150023460388</t>
+    <t xml:space="preserve">2.6414999961853</t>
   </si>
   <si>
     <t xml:space="preserve">2.59692883491516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38193845748901</t>
+    <t xml:space="preserve">2.38193821907043</t>
   </si>
   <si>
     <t xml:space="preserve">2.4671483039856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44879531860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49074482917786</t>
+    <t xml:space="preserve">2.44879555702209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49074459075928</t>
   </si>
   <si>
     <t xml:space="preserve">2.47108101844788</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">2.4199550151825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31639266014099</t>
+    <t xml:space="preserve">2.31639218330383</t>
   </si>
   <si>
     <t xml:space="preserve">2.25871229171753</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">2.20365357398987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25215744972229</t>
+    <t xml:space="preserve">2.25215768814087</t>
   </si>
   <si>
     <t xml:space="preserve">2.28493046760559</t>
@@ -1760,22 +1760,22 @@
     <t xml:space="preserve">2.39242577552795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42519879341125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45928287506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54973578453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47239208221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44617342948914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4579713344574</t>
+    <t xml:space="preserve">2.42519855499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45928263664246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54973602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47239184379578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44617366790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45797157287598</t>
   </si>
   <si>
     <t xml:space="preserve">2.47501373291016</t>
@@ -1784,37 +1784,37 @@
     <t xml:space="preserve">2.54842495918274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43044209480286</t>
+    <t xml:space="preserve">2.43044233322144</t>
   </si>
   <si>
     <t xml:space="preserve">2.40815687179565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33998918533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28886365890503</t>
+    <t xml:space="preserve">2.33998870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28886318206787</t>
   </si>
   <si>
     <t xml:space="preserve">2.27968668937683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25740122795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17612409591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18661165237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13155317306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29410696029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35178732872009</t>
+    <t xml:space="preserve">2.25740098953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17612433433533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18661141395569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13155293464661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29410672187805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35178756713867</t>
   </si>
   <si>
     <t xml:space="preserve">2.39766955375671</t>
@@ -1826,40 +1826,40 @@
     <t xml:space="preserve">2.42388772964478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40946745872498</t>
+    <t xml:space="preserve">2.40946769714355</t>
   </si>
   <si>
     <t xml:space="preserve">2.40029120445251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21938443183899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19447684288025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25477933883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31901431083679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32687973976135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26264500617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17743563652039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12893128395081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14597320556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12237668037415</t>
+    <t xml:space="preserve">2.21938467025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19447708129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25477957725525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31901478767395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32687950134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26264452934265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17743492126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12893152236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14597296714783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12237644195557</t>
   </si>
   <si>
     <t xml:space="preserve">2.12368750572205</t>
@@ -1871,19 +1871,19 @@
     <t xml:space="preserve">2.11713290214539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14728379249573</t>
+    <t xml:space="preserve">2.14728403091431</t>
   </si>
   <si>
     <t xml:space="preserve">2.15121674537659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23904800415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20758628845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36489629745483</t>
+    <t xml:space="preserve">2.23904824256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20758652687073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36489677429199</t>
   </si>
   <si>
     <t xml:space="preserve">2.34785461425781</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">2.37407302856445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25084662437439</t>
+    <t xml:space="preserve">2.25084686279297</t>
   </si>
   <si>
     <t xml:space="preserve">2.39504742622375</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">2.41340017318726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43306398391724</t>
+    <t xml:space="preserve">2.43306422233582</t>
   </si>
   <si>
     <t xml:space="preserve">2.44486260414124</t>
@@ -1913,22 +1913,22 @@
     <t xml:space="preserve">2.44224071502686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43175339698792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38456034660339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35309839248657</t>
+    <t xml:space="preserve">2.43175315856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38456010818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35309791564941</t>
   </si>
   <si>
     <t xml:space="preserve">2.34654355049133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35440921783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37145090103149</t>
+    <t xml:space="preserve">2.35440897941589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37145113945007</t>
   </si>
   <si>
     <t xml:space="preserve">2.28755235671997</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">2.31114888191223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37931680679321</t>
+    <t xml:space="preserve">2.37931656837463</t>
   </si>
   <si>
     <t xml:space="preserve">2.40291285514832</t>
@@ -1949,25 +1949,25 @@
     <t xml:space="preserve">2.4055347442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37014007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33605647087097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39898061752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37669467926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50123190879822</t>
+    <t xml:space="preserve">2.37014031410217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33605575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39898014068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37669444084167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5012321472168</t>
   </si>
   <si>
     <t xml:space="preserve">2.54318141937256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52613949775696</t>
+    <t xml:space="preserve">2.52613925933838</t>
   </si>
   <si>
     <t xml:space="preserve">2.50385355949402</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">2.49336647987366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42782044410706</t>
+    <t xml:space="preserve">2.42782068252563</t>
   </si>
   <si>
     <t xml:space="preserve">2.39635848999023</t>
@@ -1985,25 +1985,25 @@
     <t xml:space="preserve">2.38718199729919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37276172637939</t>
+    <t xml:space="preserve">2.37276148796082</t>
   </si>
   <si>
     <t xml:space="preserve">2.37800574302673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33867788314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29935073852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38062763214111</t>
+    <t xml:space="preserve">2.33867835998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29935050010681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38062739372253</t>
   </si>
   <si>
     <t xml:space="preserve">2.30459427833557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38849329948425</t>
+    <t xml:space="preserve">2.38849282264709</t>
   </si>
   <si>
     <t xml:space="preserve">2.45666074752808</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">2.40160226821899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34129977226257</t>
+    <t xml:space="preserve">2.34130001068115</t>
   </si>
   <si>
     <t xml:space="preserve">2.34392166137695</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">2.38324928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32556867599487</t>
+    <t xml:space="preserve">2.32556915283203</t>
   </si>
   <si>
     <t xml:space="preserve">2.30328321456909</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">2.32425808906555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30983805656433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21545171737671</t>
+    <t xml:space="preserve">2.30983781814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21545195579529</t>
   </si>
   <si>
     <t xml:space="preserve">2.19054412841797</t>
@@ -2048,25 +2048,25 @@
     <t xml:space="preserve">2.09091448783875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08698177337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9978392124176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03978848457336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97686457633972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9912850856781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9781756401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98996269702911</t>
+    <t xml:space="preserve">2.08698201179504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99783957004547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03978872299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97686469554901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99128472805023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97817552089691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9899628162384</t>
   </si>
   <si>
     <t xml:space="preserve">1.99967014789581</t>
@@ -2075,37 +2075,37 @@
     <t xml:space="preserve">1.97470915317535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94420051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91923928260803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89843845367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86377012729645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82632827758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87625086307526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87902426719666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83742249011993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95113444328308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92755997180939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89982497692108</t>
+    <t xml:space="preserve">1.94420075416565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91923952102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89843833446503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86376988887787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8263281583786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87625098228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87902414798737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83742237091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95113432407379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9275598526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89982521533966</t>
   </si>
   <si>
     <t xml:space="preserve">1.92062628269196</t>
@@ -2114,13 +2114,13 @@
     <t xml:space="preserve">1.90953242778778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90675890445709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88734459877014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88873136043549</t>
+    <t xml:space="preserve">1.9067587852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88734436035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88873147964478</t>
   </si>
   <si>
     <t xml:space="preserve">1.88179767131805</t>
@@ -2135,22 +2135,22 @@
     <t xml:space="preserve">2.03156495094299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98857605457306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95945477485657</t>
+    <t xml:space="preserve">1.98857641220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95945465564728</t>
   </si>
   <si>
     <t xml:space="preserve">2.00660371780396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0052170753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07178020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09396815299988</t>
+    <t xml:space="preserve">2.00521683692932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07177996635437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0939679145813</t>
   </si>
   <si>
     <t xml:space="preserve">2.14943718910217</t>
@@ -2168,13 +2168,13 @@
     <t xml:space="preserve">2.26453638076782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21461391448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21184015274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24928212165833</t>
+    <t xml:space="preserve">2.21461367607117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21184039115906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24928188323975</t>
   </si>
   <si>
     <t xml:space="preserve">2.31445860862732</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">2.30891156196594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31307196617126</t>
+    <t xml:space="preserve">2.31307172775269</t>
   </si>
   <si>
     <t xml:space="preserve">2.27424335479736</t>
@@ -2195,25 +2195,25 @@
     <t xml:space="preserve">2.2215473651886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24789524078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24650859832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24512195587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28811049461365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32277870178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37824869155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30613851547241</t>
+    <t xml:space="preserve">2.24789547920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24650835990906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.245121717453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28811097145081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32277894020081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37824821472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30613827705383</t>
   </si>
   <si>
     <t xml:space="preserve">2.23125457763672</t>
@@ -2222,10 +2222,10 @@
     <t xml:space="preserve">2.18687915802002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1716251373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17439818382263</t>
+    <t xml:space="preserve">2.17162466049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17439842224121</t>
   </si>
   <si>
     <t xml:space="preserve">2.22432088851929</t>
@@ -2234,16 +2234,16 @@
     <t xml:space="preserve">2.12170267105103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10783505439758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12863612174988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09812831878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1272497177124</t>
+    <t xml:space="preserve">2.10783529281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12863636016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09812808036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12724947929382</t>
   </si>
   <si>
     <t xml:space="preserve">2.17717218399048</t>
@@ -2261,58 +2261,58 @@
     <t xml:space="preserve">2.19935965538025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18549227714539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25760269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25621581077576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23957490921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35606050491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38102173805237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36715459823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38379526138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43510437011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51553511619568</t>
+    <t xml:space="preserve">2.18549251556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25760245323181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25621557235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23957514762878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35606026649475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38102197647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3671543598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38379549980164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43510460853577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5155348777771</t>
   </si>
   <si>
     <t xml:space="preserve">2.49889421463013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42955780029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42817091941833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44897174835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45867896080017</t>
+    <t xml:space="preserve">2.42955756187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42817068099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44897198677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45867872238159</t>
   </si>
   <si>
     <t xml:space="preserve">2.39766263961792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3879554271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37131500244141</t>
+    <t xml:space="preserve">2.38795566558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37131476402283</t>
   </si>
   <si>
     <t xml:space="preserve">2.382408618927</t>
@@ -2321,16 +2321,16 @@
     <t xml:space="preserve">2.41707682609558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42401075363159</t>
+    <t xml:space="preserve">2.42401051521301</t>
   </si>
   <si>
     <t xml:space="preserve">2.37408828735352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32693910598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29920434951782</t>
+    <t xml:space="preserve">2.32693934440613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2992045879364</t>
   </si>
   <si>
     <t xml:space="preserve">2.31723189353943</t>
@@ -2348,16 +2348,16 @@
     <t xml:space="preserve">2.46977281570435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48502659797668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5696177482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61538004875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6763961315155</t>
+    <t xml:space="preserve">2.48502707481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56961750984192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61537981033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67639589309692</t>
   </si>
   <si>
     <t xml:space="preserve">2.73879909515381</t>
@@ -2369,13 +2369,13 @@
     <t xml:space="preserve">2.74711942672729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72770547866821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75266647338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76237368583679</t>
+    <t xml:space="preserve">2.72770524024963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75266623497009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76237344741821</t>
   </si>
   <si>
     <t xml:space="preserve">2.7859480381012</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">2.77208065986633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69581031799316</t>
+    <t xml:space="preserve">2.69581055641174</t>
   </si>
   <si>
     <t xml:space="preserve">2.70413064956665</t>
@@ -2396,10 +2396,10 @@
     <t xml:space="preserve">2.80120205879211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78733468055725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82893657684326</t>
+    <t xml:space="preserve">2.78733491897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82893705368042</t>
   </si>
   <si>
     <t xml:space="preserve">2.85528469085693</t>
@@ -2408,34 +2408,34 @@
     <t xml:space="preserve">2.9468092918396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01614570617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02723979949951</t>
+    <t xml:space="preserve">3.01614594459534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02724027633667</t>
   </si>
   <si>
     <t xml:space="preserve">3.04804062843323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07993578910828</t>
+    <t xml:space="preserve">3.07993531227112</t>
   </si>
   <si>
     <t xml:space="preserve">3.13679218292236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14649868011475</t>
+    <t xml:space="preserve">3.1464991569519</t>
   </si>
   <si>
     <t xml:space="preserve">3.17562007904053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14511227607727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23108911514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24773025512695</t>
+    <t xml:space="preserve">3.14511203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2310893535614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24773073196411</t>
   </si>
   <si>
     <t xml:space="preserve">3.26298451423645</t>
@@ -2444,16 +2444,16 @@
     <t xml:space="preserve">3.26159763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2255425453186</t>
+    <t xml:space="preserve">3.22554278373718</t>
   </si>
   <si>
     <t xml:space="preserve">3.18532729148865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18394064903259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25605058670044</t>
+    <t xml:space="preserve">3.18394112586975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2560510635376</t>
   </si>
   <si>
     <t xml:space="preserve">3.21028876304626</t>
@@ -2462,46 +2462,46 @@
     <t xml:space="preserve">3.25327730178833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22831630706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20196795463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24218368530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26575827598572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21306204795837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19919443130493</t>
+    <t xml:space="preserve">3.22831606864929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2019681930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24218344688416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26575779914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21306180953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19919466972351</t>
   </si>
   <si>
     <t xml:space="preserve">3.20890164375305</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22415566444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19087433815002</t>
+    <t xml:space="preserve">3.22415614128113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1908745765686</t>
   </si>
   <si>
     <t xml:space="preserve">3.20335483551025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06606817245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09241604804993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1478853225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20612835884094</t>
+    <t xml:space="preserve">3.06606841087341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09241628646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14788579940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20612812042236</t>
   </si>
   <si>
     <t xml:space="preserve">3.17839384078979</t>
@@ -2510,13 +2510,13 @@
     <t xml:space="preserve">3.17146015167236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03694677352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1534321308136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16868686676025</t>
+    <t xml:space="preserve">3.03694725036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15343236923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16868662834167</t>
   </si>
   <si>
     <t xml:space="preserve">2.97038340568542</t>
@@ -2528,13 +2528,13 @@
     <t xml:space="preserve">3.14095187187195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12985777854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14927196502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17007327079773</t>
+    <t xml:space="preserve">3.12985801696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14927244186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17007350921631</t>
   </si>
   <si>
     <t xml:space="preserve">3.12708473205566</t>
@@ -2549,37 +2549,37 @@
     <t xml:space="preserve">3.11044359207153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08964276313782</t>
+    <t xml:space="preserve">3.0896430015564</t>
   </si>
   <si>
     <t xml:space="preserve">3.28239870071411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34202837944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34896159172058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93987512588501</t>
+    <t xml:space="preserve">3.34202885627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34896206855774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93987536430359</t>
   </si>
   <si>
     <t xml:space="preserve">2.97315716743469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86360549926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73741221427917</t>
+    <t xml:space="preserve">2.863605260849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73741245269775</t>
   </si>
   <si>
     <t xml:space="preserve">2.58487176895142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55158996582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49473428726196</t>
+    <t xml:space="preserve">2.55159020423889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49473404884338</t>
   </si>
   <si>
     <t xml:space="preserve">2.29227089881897</t>
@@ -2588,25 +2588,25 @@
     <t xml:space="preserve">2.07039356231689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95668137073517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99134945869446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69042861461639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78472626209259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65576004981995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52818048000336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41030824184418</t>
+    <t xml:space="preserve">1.95668148994446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99134969711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69042837619781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7847261428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65576016902924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52818036079407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41030812263489</t>
   </si>
   <si>
     <t xml:space="preserve">1.48519170284271</t>
@@ -2615,10 +2615,10 @@
     <t xml:space="preserve">1.49489891529083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60583770275116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67933440208435</t>
+    <t xml:space="preserve">1.60583758354187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67933452129364</t>
   </si>
   <si>
     <t xml:space="preserve">1.67656111717224</t>
@@ -2627,19 +2627,19 @@
     <t xml:space="preserve">1.72648358345032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68904197216034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69736206531525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72371029853821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75421810150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78888654708862</t>
+    <t xml:space="preserve">1.68904161453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69736194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72371006011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75421822071075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78888642787933</t>
   </si>
   <si>
     <t xml:space="preserve">2.02185773849487</t>
@@ -2648,40 +2648,40 @@
     <t xml:space="preserve">2.06207299232483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05375242233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99412274360657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609567642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.966388463974</t>
+    <t xml:space="preserve">2.05375266075134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99412298202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609543800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96638822555542</t>
   </si>
   <si>
     <t xml:space="preserve">1.94142723083496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85960984230042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8679301738739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92339944839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90121173858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1480507850647</t>
+    <t xml:space="preserve">1.85960972309113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86793041229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92339980602264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90121209621429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14805030822754</t>
   </si>
   <si>
     <t xml:space="preserve">2.26730966567993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23818850517273</t>
+    <t xml:space="preserve">2.23818826675415</t>
   </si>
   <si>
     <t xml:space="preserve">2.22570753097534</t>
@@ -2690,19 +2690,19 @@
     <t xml:space="preserve">2.13418316841125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28117728233337</t>
+    <t xml:space="preserve">2.28117704391479</t>
   </si>
   <si>
     <t xml:space="preserve">2.35744738578796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40043640136719</t>
+    <t xml:space="preserve">2.40043592453003</t>
   </si>
   <si>
     <t xml:space="preserve">2.3435800075531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30752515792847</t>
+    <t xml:space="preserve">2.30752491950989</t>
   </si>
   <si>
     <t xml:space="preserve">2.48411750793457</t>
@@ -2714,10 +2714,10 @@
     <t xml:space="preserve">2.49150609970093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49741768836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45456218719482</t>
+    <t xml:space="preserve">2.49741721153259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45456194877625</t>
   </si>
   <si>
     <t xml:space="preserve">2.57130527496338</t>
@@ -2726,43 +2726,43 @@
     <t xml:space="preserve">2.72647047042847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75750327110291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80774736404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86537981033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87572431564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86833524703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97473430633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20230984687805</t>
+    <t xml:space="preserve">2.75750350952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80774712562561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86538004875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87572407722473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86833548545837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97473454475403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20230960845947</t>
   </si>
   <si>
     <t xml:space="preserve">3.16979885101318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14024376869202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93483471870422</t>
+    <t xml:space="preserve">3.14024353027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93483448028564</t>
   </si>
   <si>
     <t xml:space="preserve">2.9363124370575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94222378730774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99837875366211</t>
+    <t xml:space="preserve">2.94222402572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99837827682495</t>
   </si>
   <si>
     <t xml:space="preserve">3.00281167030334</t>
@@ -2771,34 +2771,34 @@
     <t xml:space="preserve">2.9584789276123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88606834411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92744612693787</t>
+    <t xml:space="preserve">2.88606858253479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92744565010071</t>
   </si>
   <si>
     <t xml:space="preserve">2.83582472801208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89050197601318</t>
+    <t xml:space="preserve">2.89050221443176</t>
   </si>
   <si>
     <t xml:space="preserve">2.88459086418152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85946869850159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82843589782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86242437362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93779015541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99542284011841</t>
+    <t xml:space="preserve">2.85946893692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82843613624573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86242461204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93779039382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99542307853699</t>
   </si>
   <si>
     <t xml:space="preserve">3.03236699104309</t>
@@ -2807,10 +2807,10 @@
     <t xml:space="preserve">3.04418897628784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01906728744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92005705833435</t>
+    <t xml:space="preserve">3.01906704902649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92005729675293</t>
   </si>
   <si>
     <t xml:space="preserve">2.93040156364441</t>
@@ -2819,52 +2819,52 @@
     <t xml:space="preserve">2.97916769981384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98212289810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99394512176514</t>
+    <t xml:space="preserve">2.98212313652039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99394536018372</t>
   </si>
   <si>
     <t xml:space="preserve">2.98951172828674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95404577255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95552325248718</t>
+    <t xml:space="preserve">2.95404553413391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95552349090576</t>
   </si>
   <si>
     <t xml:space="preserve">2.94665670394897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03384494781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0959107875824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758933067322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99098968505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93335700035095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91857933998108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75602555274963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81365823745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85503578186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8535578250885</t>
+    <t xml:space="preserve">3.03384470939636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09591054916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0175895690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99098944664001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93335723876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9185791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75602579116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81365847587585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85503554344177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85355806350708</t>
   </si>
   <si>
     <t xml:space="preserve">2.894935131073</t>
@@ -2876,31 +2876,31 @@
     <t xml:space="preserve">2.92153477668762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9629123210907</t>
+    <t xml:space="preserve">2.96291255950928</t>
   </si>
   <si>
     <t xml:space="preserve">2.91266822814941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87424635887146</t>
+    <t xml:space="preserve">2.87424659729004</t>
   </si>
   <si>
     <t xml:space="preserve">2.84616899490356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80479192733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76784777641296</t>
+    <t xml:space="preserve">2.80479145050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76784753799438</t>
   </si>
   <si>
     <t xml:space="preserve">2.75307011604309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78410315513611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79888105392456</t>
+    <t xml:space="preserve">2.78410291671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7988805770874</t>
   </si>
   <si>
     <t xml:space="preserve">2.74863696098328</t>
@@ -2915,28 +2915,28 @@
     <t xml:space="preserve">2.76636981964111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79296970367432</t>
+    <t xml:space="preserve">2.79296946525574</t>
   </si>
   <si>
     <t xml:space="preserve">2.73681473731995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69987082481384</t>
+    <t xml:space="preserve">2.69987058639526</t>
   </si>
   <si>
     <t xml:space="preserve">2.79592514038086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74272537231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75454759597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74715924263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71612596511841</t>
+    <t xml:space="preserve">2.74272584915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75454783439636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74715900421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71612620353699</t>
   </si>
   <si>
     <t xml:space="preserve">2.70873713493347</t>
@@ -2945,13 +2945,13 @@
     <t xml:space="preserve">2.7072594165802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61268281936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57573843002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52549481391907</t>
+    <t xml:space="preserve">2.61268258094788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57573890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52549457550049</t>
   </si>
   <si>
     <t xml:space="preserve">2.54175019264221</t>
@@ -2960,52 +2960,52 @@
     <t xml:space="preserve">2.53436136245728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5846049785614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52697229385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47525072097778</t>
+    <t xml:space="preserve">2.58460521697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52697277069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47525095939636</t>
   </si>
   <si>
     <t xml:space="preserve">2.50037288665771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43091773986816</t>
+    <t xml:space="preserve">2.43091797828674</t>
   </si>
   <si>
     <t xml:space="preserve">2.52992796897888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61120462417603</t>
+    <t xml:space="preserve">2.6112048625946</t>
   </si>
   <si>
     <t xml:space="preserve">2.54618358612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55209422111511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67179298400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60972690582275</t>
+    <t xml:space="preserve">2.55209445953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67179322242737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60972714424133</t>
   </si>
   <si>
     <t xml:space="preserve">2.54322791099548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52845025062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47377324104309</t>
+    <t xml:space="preserve">2.52845001220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47377300262451</t>
   </si>
   <si>
     <t xml:space="preserve">2.6289381980896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65701532363892</t>
+    <t xml:space="preserve">2.6570155620575</t>
   </si>
   <si>
     <t xml:space="preserve">2.63632678985596</t>
@@ -3014,40 +3014,40 @@
     <t xml:space="preserve">2.60677194595337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53140592575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52253937721252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36441898345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31713032722473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37180733680725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51662826538086</t>
+    <t xml:space="preserve">2.53140568733215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52253913879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36441874504089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31713008880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37180757522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51662802696228</t>
   </si>
   <si>
     <t xml:space="preserve">2.58312749862671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64223790168762</t>
+    <t xml:space="preserve">2.64223766326904</t>
   </si>
   <si>
     <t xml:space="preserve">2.49298405647278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.615638256073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65258240699768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63041567802429</t>
+    <t xml:space="preserve">2.61563801765442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6525821685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63041591644287</t>
   </si>
   <si>
     <t xml:space="preserve">2.71317028999329</t>
@@ -3062,19 +3062,19 @@
     <t xml:space="preserve">2.83139157295227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79149174690247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78853607177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75898122787476</t>
+    <t xml:space="preserve">2.79149198532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78853631019592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7589807510376</t>
   </si>
   <si>
     <t xml:space="preserve">2.68361520767212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67031526565552</t>
+    <t xml:space="preserve">2.6703155040741</t>
   </si>
   <si>
     <t xml:space="preserve">2.66440439224243</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">2.64962673187256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68213725090027</t>
+    <t xml:space="preserve">2.68213748931885</t>
   </si>
   <si>
     <t xml:space="preserve">2.62598252296448</t>
@@ -3101,10 +3101,10 @@
     <t xml:space="preserve">2.72055912017822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85651350021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92301249504089</t>
+    <t xml:space="preserve">2.85651302337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92301273345947</t>
   </si>
   <si>
     <t xml:space="preserve">2.90380191802979</t>
@@ -3116,13 +3116,13 @@
     <t xml:space="preserve">2.98064517974854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0146336555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03975558280945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07374429702759</t>
+    <t xml:space="preserve">3.01463389396667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03975582122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07374405860901</t>
   </si>
   <si>
     <t xml:space="preserve">3.11807727813721</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">3.06044459342957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02350068092346</t>
+    <t xml:space="preserve">3.0235002040863</t>
   </si>
   <si>
     <t xml:space="preserve">3.02941131591797</t>
@@ -3140,13 +3140,13 @@
     <t xml:space="preserve">2.89345741271973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86390233039856</t>
+    <t xml:space="preserve">2.86390209197998</t>
   </si>
   <si>
     <t xml:space="preserve">2.90675711631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87129092216492</t>
+    <t xml:space="preserve">2.8712911605835</t>
   </si>
   <si>
     <t xml:space="preserve">2.83434677124023</t>
@@ -3155,46 +3155,46 @@
     <t xml:space="preserve">2.91710162162781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04714465141296</t>
+    <t xml:space="preserve">3.04714488983154</t>
   </si>
   <si>
     <t xml:space="preserve">3.1328547000885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10034418106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17718768119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10625529289246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13581037521362</t>
+    <t xml:space="preserve">3.10034394264221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1771879196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10625505447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13581013679504</t>
   </si>
   <si>
     <t xml:space="preserve">3.08408856391907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00133371353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9451789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99985647201538</t>
+    <t xml:space="preserve">3.00133395195007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94517922401428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9998562335968</t>
   </si>
   <si>
     <t xml:space="preserve">2.97177863121033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93926811218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08999967575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09147763252258</t>
+    <t xml:space="preserve">2.93926787376404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08999991416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.091477394104</t>
   </si>
   <si>
     <t xml:space="preserve">3.07669973373413</t>
@@ -3203,25 +3203,25 @@
     <t xml:space="preserve">3.08704423904419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08852171897888</t>
+    <t xml:space="preserve">3.08852195739746</t>
   </si>
   <si>
     <t xml:space="preserve">3.12694358825684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24664235115051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20526528358459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21856474876404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33235263824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33826375007629</t>
+    <t xml:space="preserve">3.24664258956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20526480674744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21856498718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33235287666321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33826398849487</t>
   </si>
   <si>
     <t xml:space="preserve">3.34121894836426</t>
@@ -3233,13 +3233,13 @@
     <t xml:space="preserve">3.26142024993896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32496404647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30131959915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29245281219482</t>
+    <t xml:space="preserve">3.32496356964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30131983757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29245328903198</t>
   </si>
   <si>
     <t xml:space="preserve">3.28801965713501</t>
@@ -3248,10 +3248,10 @@
     <t xml:space="preserve">3.31609702110291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29393076896667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27324223518372</t>
+    <t xml:space="preserve">3.29393100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27324175834656</t>
   </si>
   <si>
     <t xml:space="preserve">3.24516487121582</t>
@@ -3260,25 +3260,25 @@
     <t xml:space="preserve">3.32274746894836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30649185180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31018614768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29540872573853</t>
+    <t xml:space="preserve">3.30649161338806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3101863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29540848731995</t>
   </si>
   <si>
     <t xml:space="preserve">3.25107574462891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28358626365662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28654193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27915334701538</t>
+    <t xml:space="preserve">3.2835865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28654217720032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27915358543396</t>
   </si>
   <si>
     <t xml:space="preserve">3.24073147773743</t>
@@ -3287,16 +3287,16 @@
     <t xml:space="preserve">3.27767539024353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28136968612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18531513214111</t>
+    <t xml:space="preserve">3.28136944770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18531560897827</t>
   </si>
   <si>
     <t xml:space="preserve">3.13433265686035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10329961776733</t>
+    <t xml:space="preserve">3.10329937934875</t>
   </si>
   <si>
     <t xml:space="preserve">3.16314911842346</t>
@@ -3314,22 +3314,22 @@
     <t xml:space="preserve">3.15354347229004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1365487575531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21043729782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26511454582214</t>
+    <t xml:space="preserve">3.13654923439026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21043705940247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26511478424072</t>
   </si>
   <si>
     <t xml:space="preserve">3.2274317741394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23925375938416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24738144874573</t>
+    <t xml:space="preserve">3.239253282547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24738121032715</t>
   </si>
   <si>
     <t xml:space="preserve">3.31979179382324</t>
@@ -3338,22 +3338,22 @@
     <t xml:space="preserve">3.33974123001099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41362953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3205304145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32939696311951</t>
+    <t xml:space="preserve">3.41362905502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32053065299988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32939720153809</t>
   </si>
   <si>
     <t xml:space="preserve">3.31535816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38761734962463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31846618652344</t>
+    <t xml:space="preserve">3.38761711120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31846594810486</t>
   </si>
   <si>
     <t xml:space="preserve">3.33789086341858</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">3.33322882652283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33944439888</t>
+    <t xml:space="preserve">3.33944463729858</t>
   </si>
   <si>
     <t xml:space="preserve">3.33633685112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41325736045837</t>
+    <t xml:space="preserve">3.41325759887695</t>
   </si>
   <si>
     <t xml:space="preserve">3.37751650810242</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">3.40471076965332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60206246376038</t>
+    <t xml:space="preserve">3.60206270217896</t>
   </si>
   <si>
     <t xml:space="preserve">3.64868140220642</t>
@@ -3386,22 +3386,22 @@
     <t xml:space="preserve">3.57098364830017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55855202674866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52203416824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51037955284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44200563430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47619247436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44977521896362</t>
+    <t xml:space="preserve">3.55855178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52203392982483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51037979125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4420051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47619223594666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4497754573822</t>
   </si>
   <si>
     <t xml:space="preserve">3.38917112350464</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">3.32545924186707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34876823425293</t>
+    <t xml:space="preserve">3.34876847267151</t>
   </si>
   <si>
     <t xml:space="preserve">3.27417898178101</t>
@@ -3425,37 +3425,37 @@
     <t xml:space="preserve">3.25630807876587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26407790184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24776124954224</t>
+    <t xml:space="preserve">3.26407814025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24776148796082</t>
   </si>
   <si>
     <t xml:space="preserve">3.2788405418396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25786185264587</t>
+    <t xml:space="preserve">3.25786209106445</t>
   </si>
   <si>
     <t xml:space="preserve">3.24076867103577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19337344169617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25009250640869</t>
+    <t xml:space="preserve">3.19337320327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25009226799011</t>
   </si>
   <si>
     <t xml:space="preserve">3.28738737106323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27184748649597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24620747566223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2058048248291</t>
+    <t xml:space="preserve">3.27184772491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24620771408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20580458641052</t>
   </si>
   <si>
     <t xml:space="preserve">3.16540193557739</t>
@@ -3467,49 +3467,49 @@
     <t xml:space="preserve">3.03098511695862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0915892124176</t>
+    <t xml:space="preserve">3.09158897399902</t>
   </si>
   <si>
     <t xml:space="preserve">3.11956024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1801643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22678327560425</t>
+    <t xml:space="preserve">3.18016457557678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22678303718567</t>
   </si>
   <si>
     <t xml:space="preserve">3.19570398330688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21202063560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22989106178284</t>
+    <t xml:space="preserve">3.21202039718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22989130020142</t>
   </si>
   <si>
     <t xml:space="preserve">3.23066782951355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31458139419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23299884796143</t>
+    <t xml:space="preserve">3.31458115577698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23299860954285</t>
   </si>
   <si>
     <t xml:space="preserve">3.28894090652466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30370378494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.379070520401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3355598449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38606309890747</t>
+    <t xml:space="preserve">3.30370354652405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37907028198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33556008338928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38606286048889</t>
   </si>
   <si>
     <t xml:space="preserve">3.33245182037354</t>
@@ -3521,19 +3521,19 @@
     <t xml:space="preserve">3.33478260040283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3612003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34954524040222</t>
+    <t xml:space="preserve">3.36120009422302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3495454788208</t>
   </si>
   <si>
     <t xml:space="preserve">3.36819291114807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36508440971375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39227914810181</t>
+    <t xml:space="preserve">3.3650848865509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39227938652039</t>
   </si>
   <si>
     <t xml:space="preserve">3.41248083114624</t>
@@ -3542,73 +3542,73 @@
     <t xml:space="preserve">3.37207770347595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39150166511536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39849495887756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35032224655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35343027114868</t>
+    <t xml:space="preserve">3.39150214195251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39849472045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35032200813293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3534300327301</t>
   </si>
   <si>
     <t xml:space="preserve">3.31535863876343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34721446037292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32157444953918</t>
+    <t xml:space="preserve">3.3472146987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32157421112061</t>
   </si>
   <si>
     <t xml:space="preserve">3.33089804649353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32312798500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28971838951111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18715739250183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19725751876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29282593727112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28661036491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22056746482849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21745920181274</t>
+    <t xml:space="preserve">3.32312846183777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28971815109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18715763092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19725775718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2928261756897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28661012649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22056722640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21745944023132</t>
   </si>
   <si>
     <t xml:space="preserve">3.21279764175415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20891284942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17627930641174</t>
+    <t xml:space="preserve">3.20891261100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17627954483032</t>
   </si>
   <si>
     <t xml:space="preserve">3.30758857727051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33012080192566</t>
+    <t xml:space="preserve">3.33012104034424</t>
   </si>
   <si>
     <t xml:space="preserve">3.36741590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3946099281311</t>
+    <t xml:space="preserve">3.39461016654968</t>
   </si>
   <si>
     <t xml:space="preserve">3.32623624801636</t>
@@ -3617,28 +3617,28 @@
     <t xml:space="preserve">3.43268179893494</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45443749427795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48085427284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50183272361755</t>
+    <t xml:space="preserve">3.45443725585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48085451126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50183296203613</t>
   </si>
   <si>
     <t xml:space="preserve">3.61682558059692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57797646522522</t>
+    <t xml:space="preserve">3.5779767036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.58652329444885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58963108062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59584665298462</t>
+    <t xml:space="preserve">3.58963084220886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5958468914032</t>
   </si>
   <si>
     <t xml:space="preserve">3.57176089286804</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">3.57642245292664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56632208824158</t>
+    <t xml:space="preserve">3.566321849823</t>
   </si>
   <si>
     <t xml:space="preserve">3.58108448982239</t>
@@ -3656,34 +3656,34 @@
     <t xml:space="preserve">3.68753004074097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63469552993774</t>
+    <t xml:space="preserve">3.63469529151917</t>
   </si>
   <si>
     <t xml:space="preserve">3.65178894996643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64246535301208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62070989608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62692594528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62148666381836</t>
+    <t xml:space="preserve">3.64246582984924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6207103729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62692618370056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62148714065552</t>
   </si>
   <si>
     <t xml:space="preserve">3.61294031143188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61060953140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57409167289734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50260996818542</t>
+    <t xml:space="preserve">3.61060905456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57409143447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50260949134827</t>
   </si>
   <si>
     <t xml:space="preserve">3.4482216835022</t>
@@ -3692,13 +3692,13 @@
     <t xml:space="preserve">3.45132899284363</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39694118499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3953869342804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26330089569092</t>
+    <t xml:space="preserve">3.39694094657898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39538669586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26330065727234</t>
   </si>
   <si>
     <t xml:space="preserve">3.22833728790283</t>
@@ -3707,67 +3707,67 @@
     <t xml:space="preserve">3.23999166488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40004873275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33711385726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36586141586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37363147735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41791963577271</t>
+    <t xml:space="preserve">3.40004897117615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33711361885071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3658618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37363171577454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41791939735413</t>
   </si>
   <si>
     <t xml:space="preserve">3.4365668296814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31380438804626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42024993896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42957425117493</t>
+    <t xml:space="preserve">3.31380462646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42025017738342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42957401275635</t>
   </si>
   <si>
     <t xml:space="preserve">3.48163151741028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49717116355896</t>
+    <t xml:space="preserve">3.49717092514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.48707008361816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48862409591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51814913749695</t>
+    <t xml:space="preserve">3.48862433433533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51814889907837</t>
   </si>
   <si>
     <t xml:space="preserve">3.54145860671997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52436494827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48551607131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49794769287109</t>
+    <t xml:space="preserve">3.52436518669128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48551630973816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49794793128967</t>
   </si>
   <si>
     <t xml:space="preserve">3.64635014533997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70151591300964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6960768699646</t>
+    <t xml:space="preserve">3.70151567459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69607663154602</t>
   </si>
   <si>
     <t xml:space="preserve">3.64712738990784</t>
@@ -3776,16 +3776,16 @@
     <t xml:space="preserve">3.65567374229431</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56865262985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52824950218201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49639415740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35420727729797</t>
+    <t xml:space="preserve">3.56865286827087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52824974060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49639368057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35420680046082</t>
   </si>
   <si>
     <t xml:space="preserve">3.40237998962402</t>
@@ -3809,22 +3809,22 @@
     <t xml:space="preserve">3.47075390815735</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45366048812866</t>
+    <t xml:space="preserve">3.45366024971008</t>
   </si>
   <si>
     <t xml:space="preserve">3.54301261901855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56321406364441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75978922843933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62614893913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79708361625671</t>
+    <t xml:space="preserve">3.56321382522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75978899002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62614870071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79708385467529</t>
   </si>
   <si>
     <t xml:space="preserve">3.75124216079712</t>
@@ -3833,28 +3833,28 @@
     <t xml:space="preserve">3.65878248214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66188931465149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54612016677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55622148513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38373208045959</t>
+    <t xml:space="preserve">3.66188979148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54612064361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55622124671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38373255729675</t>
   </si>
   <si>
     <t xml:space="preserve">3.42258143424988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16384768486023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06361794471741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87481260299683</t>
+    <t xml:space="preserve">3.16384816169739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06361818313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87481284141541</t>
   </si>
   <si>
     <t xml:space="preserve">2.63395023345947</t>
@@ -3866,28 +3866,28 @@
     <t xml:space="preserve">2.64715886116028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83751797676086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74505758285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8204243183136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93308615684509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91366147994995</t>
+    <t xml:space="preserve">2.83751773834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7450578212738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82042455673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93308591842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91366171836853</t>
   </si>
   <si>
     <t xml:space="preserve">3.0783805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05118680000305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05895638465881</t>
+    <t xml:space="preserve">3.05118656158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05895614624023</t>
   </si>
   <si>
     <t xml:space="preserve">3.06284093856812</t>
@@ -3896,13 +3896,13 @@
     <t xml:space="preserve">3.1622941493988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14131593704224</t>
+    <t xml:space="preserve">3.14131569862366</t>
   </si>
   <si>
     <t xml:space="preserve">3.10246682167053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09780502319336</t>
+    <t xml:space="preserve">3.09780526161194</t>
   </si>
   <si>
     <t xml:space="preserve">3.13199210166931</t>
@@ -3911,22 +3911,22 @@
     <t xml:space="preserve">3.23843789100647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24853849411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17161774635315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20269727706909</t>
+    <t xml:space="preserve">3.24853873252869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17161750793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20269703865051</t>
   </si>
   <si>
     <t xml:space="preserve">3.09236621856689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35498428344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36275434494019</t>
+    <t xml:space="preserve">3.35498404502869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36275386810303</t>
   </si>
   <si>
     <t xml:space="preserve">3.37984728813171</t>
@@ -3938,31 +3938,31 @@
     <t xml:space="preserve">3.42335820198059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53058099746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59273934364319</t>
+    <t xml:space="preserve">3.53058075904846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59273910522461</t>
   </si>
   <si>
     <t xml:space="preserve">3.51970338821411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52747249603271</t>
+    <t xml:space="preserve">3.52747297286987</t>
   </si>
   <si>
     <t xml:space="preserve">3.59740114212036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6113862991333</t>
+    <t xml:space="preserve">3.61138582229614</t>
   </si>
   <si>
     <t xml:space="preserve">3.6937460899353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63624930381775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60983228683472</t>
+    <t xml:space="preserve">3.63624954223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60983204841614</t>
   </si>
   <si>
     <t xml:space="preserve">3.36430788040161</t>
@@ -3971,19 +3971,19 @@
     <t xml:space="preserve">3.30059599876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38140177726746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46686887741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51659512519836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53524279594421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55078268051147</t>
+    <t xml:space="preserve">3.38140153884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46686863899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51659536361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53524303436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5507824420929</t>
   </si>
   <si>
     <t xml:space="preserve">3.56942963600159</t>
@@ -3992,40 +3992,40 @@
     <t xml:space="preserve">3.51193332672119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63948965072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6378333568573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65771174430847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71403574943542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70740914344788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75876307487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71569180488586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64611577987671</t>
+    <t xml:space="preserve">3.6394898891449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63783311843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65771198272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71403551101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70740866661072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7587628364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71569228172302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64611625671387</t>
   </si>
   <si>
     <t xml:space="preserve">3.64942908287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59310579299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59807538986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48377156257629</t>
+    <t xml:space="preserve">3.59310531616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59807515144348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48377180099487</t>
   </si>
   <si>
     <t xml:space="preserve">3.38272094726562</t>
@@ -4037,13 +4037,13 @@
     <t xml:space="preserve">2.97686076164246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01993131637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0828812122345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97520422935486</t>
+    <t xml:space="preserve">3.01993155479431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08288097381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97520399093628</t>
   </si>
   <si>
     <t xml:space="preserve">2.96692132949829</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">3.01330518722534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98514342308044</t>
+    <t xml:space="preserve">2.98514366149902</t>
   </si>
   <si>
     <t xml:space="preserve">3.00005269050598</t>
@@ -4073,16 +4073,16 @@
     <t xml:space="preserve">3.00999212265015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89734506607056</t>
+    <t xml:space="preserve">2.89734530448914</t>
   </si>
   <si>
     <t xml:space="preserve">2.90397143363953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90065836906433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69690012931824</t>
+    <t xml:space="preserve">2.90065860748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69689989089966</t>
   </si>
   <si>
     <t xml:space="preserve">2.6587986946106</t>
@@ -4094,7 +4094,7 @@
     <t xml:space="preserve">2.80457711219788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71512246131897</t>
+    <t xml:space="preserve">2.71512222290039</t>
   </si>
   <si>
     <t xml:space="preserve">2.70683932304382</t>
@@ -4103,7 +4103,7 @@
     <t xml:space="preserve">2.69193005561829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52792954444885</t>
+    <t xml:space="preserve">2.52792978286743</t>
   </si>
   <si>
     <t xml:space="preserve">2.64885926246643</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">2.81120347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78138494491577</t>
+    <t xml:space="preserve">2.78138518333435</t>
   </si>
   <si>
     <t xml:space="preserve">2.79132437705994</t>
@@ -4127,22 +4127,22 @@
     <t xml:space="preserve">2.76813244819641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71843552589417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71677851676941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7747585773468</t>
+    <t xml:space="preserve">2.71843528747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71677875518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77475881576538</t>
   </si>
   <si>
     <t xml:space="preserve">2.83108234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83770871162415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84599137306213</t>
+    <t xml:space="preserve">2.83770847320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84599161148071</t>
   </si>
   <si>
     <t xml:space="preserve">2.92385029792786</t>
@@ -4151,7 +4151,7 @@
     <t xml:space="preserve">2.97354745864868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95035576820374</t>
+    <t xml:space="preserve">2.95035552978516</t>
   </si>
   <si>
     <t xml:space="preserve">2.91225433349609</t>
@@ -4163,28 +4163,28 @@
     <t xml:space="preserve">2.93047666549683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98183012008667</t>
+    <t xml:space="preserve">2.98183035850525</t>
   </si>
   <si>
     <t xml:space="preserve">2.98017382621765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92219400405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93544626235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85427451133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75984954833984</t>
+    <t xml:space="preserve">2.92219376564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9354465007782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8542742729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75984978675842</t>
   </si>
   <si>
     <t xml:space="preserve">2.79960751533508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78469800949097</t>
+    <t xml:space="preserve">2.78469824790955</t>
   </si>
   <si>
     <t xml:space="preserve">2.8277690410614</t>
@@ -4199,10 +4199,10 @@
     <t xml:space="preserve">2.68696045875549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69358706474304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64223313331604</t>
+    <t xml:space="preserve">2.69358682632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64223289489746</t>
   </si>
   <si>
     <t xml:space="preserve">2.68199062347412</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">2.73168802261353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83439540863037</t>
+    <t xml:space="preserve">2.83439517021179</t>
   </si>
   <si>
     <t xml:space="preserve">2.79629421234131</t>
@@ -4220,25 +4220,25 @@
     <t xml:space="preserve">2.76150631904602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6803343296051</t>
+    <t xml:space="preserve">2.68033409118652</t>
   </si>
   <si>
     <t xml:space="preserve">2.71015238761902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61738443374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59419250488281</t>
+    <t xml:space="preserve">2.61738467216492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59419226646423</t>
   </si>
   <si>
     <t xml:space="preserve">2.57762670516968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51799011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.536212682724</t>
+    <t xml:space="preserve">2.51798987388611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53621244430542</t>
   </si>
   <si>
     <t xml:space="preserve">2.46663618087769</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">2.44344449043274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37221193313599</t>
+    <t xml:space="preserve">2.37221169471741</t>
   </si>
   <si>
     <t xml:space="preserve">2.4268786907196</t>
@@ -4256,55 +4256,55 @@
     <t xml:space="preserve">2.65051603317261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67702126502991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58259654045105</t>
+    <t xml:space="preserve">2.67702102661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58259630203247</t>
   </si>
   <si>
     <t xml:space="preserve">2.54780840873718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53124260902405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52461624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42190909385681</t>
+    <t xml:space="preserve">2.53124284744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52461647987366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42190885543823</t>
   </si>
   <si>
     <t xml:space="preserve">2.48651528358459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4815456867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54118227958679</t>
+    <t xml:space="preserve">2.48154544830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54118204116821</t>
   </si>
   <si>
     <t xml:space="preserve">2.57100057601929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53952574729919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52295994758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48817157745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59750533103943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62235426902771</t>
+    <t xml:space="preserve">2.53952527046204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52295970916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48817181587219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59750556945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62235403060913</t>
   </si>
   <si>
     <t xml:space="preserve">2.60413193702698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61407113075256</t>
+    <t xml:space="preserve">2.61407136917114</t>
   </si>
   <si>
     <t xml:space="preserve">2.61075806617737</t>
@@ -4313,16 +4313,16 @@
     <t xml:space="preserve">2.61572790145874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68861699104309</t>
+    <t xml:space="preserve">2.68861722946167</t>
   </si>
   <si>
     <t xml:space="preserve">2.84930443763733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86587023735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95366883277893</t>
+    <t xml:space="preserve">2.86587047576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95366859436035</t>
   </si>
   <si>
     <t xml:space="preserve">2.9983959197998</t>
@@ -4331,25 +4331,25 @@
     <t xml:space="preserve">2.99342632293701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03152751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98679995536804</t>
+    <t xml:space="preserve">3.03152775764465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98680019378662</t>
   </si>
   <si>
     <t xml:space="preserve">3.00170922279358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00833559036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98348689079285</t>
+    <t xml:space="preserve">3.00833535194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98348712921143</t>
   </si>
   <si>
     <t xml:space="preserve">3.00336575508118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03484082221985</t>
+    <t xml:space="preserve">3.03484058380127</t>
   </si>
   <si>
     <t xml:space="preserve">3.06631541252136</t>
@@ -4361,16 +4361,16 @@
     <t xml:space="preserve">3.10441660881042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08619475364685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94869875907898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91722393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86255717277527</t>
+    <t xml:space="preserve">3.08619451522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94869899749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91722416877747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86255741119385</t>
   </si>
   <si>
     <t xml:space="preserve">2.89900183677673</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">2.99176979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99673962593079</t>
+    <t xml:space="preserve">2.99673938751221</t>
   </si>
   <si>
     <t xml:space="preserve">3.03649711608887</t>
@@ -4388,16 +4388,16 @@
     <t xml:space="preserve">3.01496195793152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0779116153717</t>
+    <t xml:space="preserve">3.07791137695312</t>
   </si>
   <si>
     <t xml:space="preserve">3.09944701194763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13754844665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19055843353271</t>
+    <t xml:space="preserve">3.13754820823669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19055867195129</t>
   </si>
   <si>
     <t xml:space="preserve">3.16736626625061</t>
@@ -4406,22 +4406,22 @@
     <t xml:space="preserve">3.21375060081482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25185179710388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22865962982178</t>
+    <t xml:space="preserve">3.2518515586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22865986824036</t>
   </si>
   <si>
     <t xml:space="preserve">3.22534656524658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26013445854187</t>
+    <t xml:space="preserve">3.26013469696045</t>
   </si>
   <si>
     <t xml:space="preserve">3.23031640052795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20215439796448</t>
+    <t xml:space="preserve">3.2021541595459</t>
   </si>
   <si>
     <t xml:space="preserve">3.20546746253967</t>
@@ -4439,37 +4439,37 @@
     <t xml:space="preserve">3.29657912254333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34627652168274</t>
+    <t xml:space="preserve">3.34627628326416</t>
   </si>
   <si>
     <t xml:space="preserve">3.32805395126343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34793257713318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37443780899048</t>
+    <t xml:space="preserve">3.34793281555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37443804740906</t>
   </si>
   <si>
     <t xml:space="preserve">3.43904447555542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44235754013062</t>
+    <t xml:space="preserve">3.44235777854919</t>
   </si>
   <si>
     <t xml:space="preserve">3.29160928726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29492259025574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31811451911926</t>
+    <t xml:space="preserve">3.29492235183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31811475753784</t>
   </si>
   <si>
     <t xml:space="preserve">3.25516486167908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35124588012695</t>
+    <t xml:space="preserve">3.35124611854553</t>
   </si>
   <si>
     <t xml:space="preserve">3.45395350456238</t>
@@ -4478,10 +4478,10 @@
     <t xml:space="preserve">3.4506402015686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49536776542664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43573117256165</t>
+    <t xml:space="preserve">3.49536752700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43573093414307</t>
   </si>
   <si>
     <t xml:space="preserve">3.38437747955322</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">3.31480145454407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40922617912292</t>
+    <t xml:space="preserve">3.40922594070435</t>
   </si>
   <si>
     <t xml:space="preserve">3.34958958625793</t>
@@ -4502,10 +4502,10 @@
     <t xml:space="preserve">3.387690782547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39266061782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41088271141052</t>
+    <t xml:space="preserve">3.39266037940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41088247299194</t>
   </si>
   <si>
     <t xml:space="preserve">3.42082214355469</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">3.42247867584229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37609481811523</t>
+    <t xml:space="preserve">3.37609457969666</t>
   </si>
   <si>
     <t xml:space="preserve">3.37775111198425</t>
@@ -4523,25 +4523,25 @@
     <t xml:space="preserve">3.34130644798279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10276007652283</t>
+    <t xml:space="preserve">3.10276031494141</t>
   </si>
   <si>
     <t xml:space="preserve">3.13092184066772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02324461936951</t>
+    <t xml:space="preserve">3.02324485778809</t>
   </si>
   <si>
     <t xml:space="preserve">3.07625508308411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17399263381958</t>
+    <t xml:space="preserve">3.17399287223816</t>
   </si>
   <si>
     <t xml:space="preserve">3.13423490524292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10607314109802</t>
+    <t xml:space="preserve">3.1060733795166</t>
   </si>
   <si>
     <t xml:space="preserve">3.01164865493774</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">3.06465911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10938620567322</t>
+    <t xml:space="preserve">3.1093864440918</t>
   </si>
   <si>
     <t xml:space="preserve">3.07459831237793</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">3.08453774452209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11269927024841</t>
+    <t xml:space="preserve">3.11269950866699</t>
   </si>
   <si>
     <t xml:space="preserve">3.14748764038086</t>
@@ -4568,19 +4568,19 @@
     <t xml:space="preserve">3.17233610153198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17730569839478</t>
+    <t xml:space="preserve">3.17730593681335</t>
   </si>
   <si>
     <t xml:space="preserve">3.18393230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20381116867065</t>
+    <t xml:space="preserve">3.20381093025208</t>
   </si>
   <si>
     <t xml:space="preserve">3.14914417266846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19387149810791</t>
+    <t xml:space="preserve">3.19387173652649</t>
   </si>
   <si>
     <t xml:space="preserve">3.19718480110168</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">3.17896270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14583110809326</t>
+    <t xml:space="preserve">3.14583134651184</t>
   </si>
   <si>
     <t xml:space="preserve">3.09779047966003</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">3.11932587623596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04146671295166</t>
+    <t xml:space="preserve">3.04146695137024</t>
   </si>
   <si>
     <t xml:space="preserve">3.07294201850891</t>
@@ -4610,28 +4610,28 @@
     <t xml:space="preserve">3.08785080909729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.053062915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04974985122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10612893104553</t>
+    <t xml:space="preserve">3.05306315422058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04974961280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10612869262695</t>
   </si>
   <si>
     <t xml:space="preserve">3.05855894088745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96165752410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94403910636902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97751450538635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93523001670837</t>
+    <t xml:space="preserve">2.96165776252747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9440393447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97751426696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93523025512695</t>
   </si>
   <si>
     <t xml:space="preserve">2.90351676940918</t>
@@ -4652,7 +4652,7 @@
     <t xml:space="preserve">2.99513268470764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9968945980072</t>
+    <t xml:space="preserve">2.99689435958862</t>
   </si>
   <si>
     <t xml:space="preserve">3.03741693496704</t>
@@ -4664,7 +4664,7 @@
     <t xml:space="preserve">3.0286078453064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03213143348694</t>
+    <t xml:space="preserve">3.03213119506836</t>
   </si>
   <si>
     <t xml:space="preserve">3.06736826896667</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">3.03565526008606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99865627288818</t>
+    <t xml:space="preserve">2.99865651130676</t>
   </si>
   <si>
     <t xml:space="preserve">2.97575235366821</t>
@@ -4691,7 +4691,7 @@
     <t xml:space="preserve">2.90880250930786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88942193984985</t>
+    <t xml:space="preserve">2.88942217826843</t>
   </si>
   <si>
     <t xml:space="preserve">2.92994451522827</t>
@@ -4712,10 +4712,10 @@
     <t xml:space="preserve">2.86299443244934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88413667678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95284843444824</t>
+    <t xml:space="preserve">2.88413643836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95284867286682</t>
   </si>
   <si>
     <t xml:space="preserve">2.9916090965271</t>
@@ -4736,13 +4736,13 @@
     <t xml:space="preserve">2.93170642852783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00922727584839</t>
+    <t xml:space="preserve">3.00922751426697</t>
   </si>
   <si>
     <t xml:space="preserve">3.11317610740662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12198519706726</t>
+    <t xml:space="preserve">3.12198543548584</t>
   </si>
   <si>
     <t xml:space="preserve">3.08851027488708</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">3.25764727592468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32812118530273</t>
+    <t xml:space="preserve">3.32812094688416</t>
   </si>
   <si>
     <t xml:space="preserve">3.32635927200317</t>
@@ -4778,34 +4778,34 @@
     <t xml:space="preserve">3.2840747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22945761680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23121953010559</t>
+    <t xml:space="preserve">3.22945785522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23121976852417</t>
   </si>
   <si>
     <t xml:space="preserve">3.20655393600464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21712493896484</t>
+    <t xml:space="preserve">3.21712470054626</t>
   </si>
   <si>
     <t xml:space="preserve">3.22593402862549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25412368774414</t>
+    <t xml:space="preserve">3.25412344932556</t>
   </si>
   <si>
     <t xml:space="preserve">3.27526569366455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29112243652344</t>
+    <t xml:space="preserve">3.29112219810486</t>
   </si>
   <si>
     <t xml:space="preserve">3.34397768974304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34750127792358</t>
+    <t xml:space="preserve">3.347501039505</t>
   </si>
   <si>
     <t xml:space="preserve">3.3774528503418</t>
@@ -4820,7 +4820,7 @@
     <t xml:space="preserve">3.29816961288452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32988286018372</t>
+    <t xml:space="preserve">3.32988262176514</t>
   </si>
   <si>
     <t xml:space="preserve">3.39330911636353</t>
@@ -4859,25 +4859,25 @@
     <t xml:space="preserve">3.53954219818115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51487636566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47083020210266</t>
+    <t xml:space="preserve">3.51487612724304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47083044052124</t>
   </si>
   <si>
     <t xml:space="preserve">3.49725794792175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46378302574158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43735504150391</t>
+    <t xml:space="preserve">3.463782787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43735527992249</t>
   </si>
   <si>
     <t xml:space="preserve">3.42502236366272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52897095680237</t>
+    <t xml:space="preserve">3.52897119522095</t>
   </si>
   <si>
     <t xml:space="preserve">3.54130387306213</t>
@@ -4892,16 +4892,16 @@
     <t xml:space="preserve">3.48316311836243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42149877548218</t>
+    <t xml:space="preserve">3.4214985370636</t>
   </si>
   <si>
     <t xml:space="preserve">3.4355936050415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39507126808167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36159586906433</t>
+    <t xml:space="preserve">3.39507102966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36159610748291</t>
   </si>
   <si>
     <t xml:space="preserve">3.37569069862366</t>
@@ -4913,13 +4913,13 @@
     <t xml:space="preserve">3.37216711044312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39683270454407</t>
+    <t xml:space="preserve">3.39683294296265</t>
   </si>
   <si>
     <t xml:space="preserve">3.35278677940369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40388035774231</t>
+    <t xml:space="preserve">3.40388011932373</t>
   </si>
   <si>
     <t xml:space="preserve">3.58535027503967</t>
@@ -4931,25 +4931,25 @@
     <t xml:space="preserve">3.53778004646301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45144987106323</t>
+    <t xml:space="preserve">3.45145010948181</t>
   </si>
   <si>
     <t xml:space="preserve">3.5624463558197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54306554794312</t>
+    <t xml:space="preserve">3.54306578636169</t>
   </si>
   <si>
     <t xml:space="preserve">3.58182644844055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58711171150208</t>
+    <t xml:space="preserve">3.58711194992065</t>
   </si>
   <si>
     <t xml:space="preserve">3.55716061592102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51840019226074</t>
+    <t xml:space="preserve">3.51839995384216</t>
   </si>
   <si>
     <t xml:space="preserve">3.46730661392212</t>
@@ -4958,7 +4958,7 @@
     <t xml:space="preserve">3.4690682888031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4162130355835</t>
+    <t xml:space="preserve">3.41621327400208</t>
   </si>
   <si>
     <t xml:space="preserve">3.40211844444275</t>
@@ -4970,10 +4970,10 @@
     <t xml:space="preserve">3.45497369766235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43383145332336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45849752426147</t>
+    <t xml:space="preserve">3.43383169174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4584972858429</t>
   </si>
   <si>
     <t xml:space="preserve">3.42678427696228</t>
@@ -4997,10 +4997,10 @@
     <t xml:space="preserve">3.5677318572998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5642077922821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55187511444092</t>
+    <t xml:space="preserve">3.56420803070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55187487602234</t>
   </si>
   <si>
     <t xml:space="preserve">3.46554470062256</t>
@@ -5012,7 +5012,7 @@
     <t xml:space="preserve">3.47611594200134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55892252922058</t>
+    <t xml:space="preserve">3.558922290802</t>
   </si>
   <si>
     <t xml:space="preserve">3.5536367893219</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">3.57301735877991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57654094696045</t>
+    <t xml:space="preserve">3.57654070854187</t>
   </si>
   <si>
     <t xml:space="preserve">3.5483512878418</t>
@@ -5039,7 +5039,7 @@
     <t xml:space="preserve">3.73510646820068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69986987113953</t>
+    <t xml:space="preserve">3.69986963272095</t>
   </si>
   <si>
     <t xml:space="preserve">3.80029511451721</t>
@@ -5048,7 +5048,7 @@
     <t xml:space="preserve">3.72277355194092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71396446228027</t>
+    <t xml:space="preserve">3.71396470069885</t>
   </si>
   <si>
     <t xml:space="preserve">3.66815662384033</t>
@@ -5060,7 +5060,7 @@
     <t xml:space="preserve">3.69458413124084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78796195983887</t>
+    <t xml:space="preserve">3.78796219825745</t>
   </si>
   <si>
     <t xml:space="preserve">3.77210545539856</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">3.64701437950134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70867919921875</t>
+    <t xml:space="preserve">3.70867896080017</t>
   </si>
   <si>
     <t xml:space="preserve">3.64172887802124</t>
@@ -5102,79 +5102,79 @@
     <t xml:space="preserve">3.71220302581787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68577527999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67168068885803</t>
+    <t xml:space="preserve">3.6857750415802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67168045043945</t>
   </si>
   <si>
     <t xml:space="preserve">3.65229988098145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65582370758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71748828887939</t>
+    <t xml:space="preserve">3.65582394599915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71748805046082</t>
   </si>
   <si>
     <t xml:space="preserve">3.69634628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63468170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62587261199951</t>
+    <t xml:space="preserve">3.63468146324158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62587237358093</t>
   </si>
   <si>
     <t xml:space="preserve">3.70163178443909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72453594207764</t>
+    <t xml:space="preserve">3.72453570365906</t>
   </si>
   <si>
     <t xml:space="preserve">3.72982144355774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76858139038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81615114212036</t>
+    <t xml:space="preserve">3.76858162879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81615138053894</t>
   </si>
   <si>
     <t xml:space="preserve">3.81967520713806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88133978843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85138845443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83905529975891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87781572341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87605404853821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84610295295715</t>
+    <t xml:space="preserve">3.88133955001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85138869285583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83905553817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87781620025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87605428695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84610271453857</t>
   </si>
   <si>
     <t xml:space="preserve">3.89895820617676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82672262191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77915287017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80205655097961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76329612731934</t>
+    <t xml:space="preserve">3.82672214508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77915263175964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80205678939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76329588890076</t>
   </si>
   <si>
     <t xml:space="preserve">3.74920153617859</t>
@@ -5183,28 +5183,28 @@
     <t xml:space="preserve">3.74039196968079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67344212532043</t>
+    <t xml:space="preserve">3.67344236373901</t>
   </si>
   <si>
     <t xml:space="preserve">3.73158311843872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85843563079834</t>
+    <t xml:space="preserve">3.8584361076355</t>
   </si>
   <si>
     <t xml:space="preserve">3.82496070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81086611747742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88662528991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91833806037903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90071988105774</t>
+    <t xml:space="preserve">3.81086587905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88662552833557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91833829879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90071964263916</t>
   </si>
   <si>
     <t xml:space="preserve">4.06633329391479</t>
@@ -71034,7 +71034,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6520138889</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>183694</v>
@@ -71043,7 +71043,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="D2490" t="n">
-        <v>6.1100001335144</v>
+        <v>6.10500001907349</v>
       </c>
       <c r="E2490" t="n">
         <v>6.17999982833862</v>
@@ -71055,6 +71055,32 @@
         <v>1989</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6495601852</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>125949</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>6.15500020980835</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>6.08500003814697</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>6.13000011444092</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>6.13000011444092</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1972</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -44,94 +44,94 @@
     <t xml:space="preserve">ANIM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33184719085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13419628143311</t>
+    <t xml:space="preserve">4.33184623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13419580459595</t>
   </si>
   <si>
     <t xml:space="preserve">3.96948599815369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95301532745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94203519821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07380247116089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93105530738831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82673859596252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76085519790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67850089073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73889446258545</t>
+    <t xml:space="preserve">3.95301556587219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94203448295593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07380199432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93105459213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8267388343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76085591316223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67850112915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73889374732971</t>
   </si>
   <si>
     <t xml:space="preserve">3.40398573875427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53300738334656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76909065246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79379725456238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79928708076477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8843879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67575550079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70595288276672</t>
+    <t xml:space="preserve">3.53300762176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76909160614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7937970161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79928731918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88438701629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67575597763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70595216751099</t>
   </si>
   <si>
     <t xml:space="preserve">3.6400682926178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57967519760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35731792449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45065307617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37653493881226</t>
+    <t xml:space="preserve">3.57967567443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35731816291809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45065331459045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37653470039368</t>
   </si>
   <si>
     <t xml:space="preserve">3.06633234024048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95652627944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19535422325134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98397779464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2420220375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20084476470947</t>
+    <t xml:space="preserve">2.95652651786804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19535446166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9839780330658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24202156066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20084428787231</t>
   </si>
   <si>
     <t xml:space="preserve">3.48634028434753</t>
@@ -140,190 +140,190 @@
     <t xml:space="preserve">3.38202428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31065058708191</t>
+    <t xml:space="preserve">3.31065011024475</t>
   </si>
   <si>
     <t xml:space="preserve">3.3875150680542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26672792434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11299991607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08554816246033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07182288169861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06084227561951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15692234039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30241465568542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43967318534851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35182762145996</t>
+    <t xml:space="preserve">3.2667281627655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11299967765808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08554863929749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07182264328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06084156036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15692186355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.302414894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43967247009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3518283367157</t>
   </si>
   <si>
     <t xml:space="preserve">3.28319883346558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22280550003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25300264358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57693004608154</t>
+    <t xml:space="preserve">3.22280597686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25300288200378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57693028450012</t>
   </si>
   <si>
     <t xml:space="preserve">3.47261476516724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46437954902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59065556526184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56320452690125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61261677742004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51653671264648</t>
+    <t xml:space="preserve">3.46437978744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59065628051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56320428848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61261701583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51653647422791</t>
   </si>
   <si>
     <t xml:space="preserve">3.43418216705322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37104368209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45888876914978</t>
+    <t xml:space="preserve">3.37104415893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45888900756836</t>
   </si>
   <si>
     <t xml:space="preserve">3.53026294708252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32986617088318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27221870422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0910382270813</t>
+    <t xml:space="preserve">3.32986664772034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27221822738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09103918075562</t>
   </si>
   <si>
     <t xml:space="preserve">3.23653149604797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34084725379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28594446182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31888604164124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23927617073059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4259467124939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41771149635315</t>
+    <t xml:space="preserve">3.34084749221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28594398498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31888580322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23927712440491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42594647407532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41771197319031</t>
   </si>
   <si>
     <t xml:space="preserve">3.4094762802124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41496562957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44241738319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4616334438324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4479079246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49732112884521</t>
+    <t xml:space="preserve">3.41496610641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44241762161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46163368225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44790863990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49732041358948</t>
   </si>
   <si>
     <t xml:space="preserve">3.39300513267517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37378978729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26123809814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26947331428528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15417766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1624128818512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01966500282288</t>
+    <t xml:space="preserve">3.37378931045532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26123833656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26947355270386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15417742729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16241264343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0196647644043</t>
   </si>
   <si>
     <t xml:space="preserve">2.94829106330872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82201433181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93182015419006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06907725334167</t>
+    <t xml:space="preserve">2.82201385498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93182039260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0690770149231</t>
   </si>
   <si>
     <t xml:space="preserve">3.00044870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91809439659119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87417197227478</t>
+    <t xml:space="preserve">2.91809415817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87417149543762</t>
   </si>
   <si>
     <t xml:space="preserve">2.85221028327942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89064288139343</t>
+    <t xml:space="preserve">2.89064264297485</t>
   </si>
   <si>
     <t xml:space="preserve">2.97133874893188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06356287002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23648285865784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24224638938904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29988598823547</t>
+    <t xml:space="preserve">3.06356310844421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23648262023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24224662780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29988646507263</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884278297424</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">3.04050707817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97998452186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9626932144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02321457862854</t>
+    <t xml:space="preserve">2.97998523712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96269273757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02321481704712</t>
   </si>
   <si>
     <t xml:space="preserve">3.00015902519226</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">2.81859278678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79668998718262</t>
+    <t xml:space="preserve">2.79668974876404</t>
   </si>
   <si>
     <t xml:space="preserve">2.66988158226013</t>
@@ -365,112 +365,112 @@
     <t xml:space="preserve">2.54768514633179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70331263542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75288343429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90505290031433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92234492301941</t>
+    <t xml:space="preserve">2.70331287384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75288367271423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90505337715149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92234468460083</t>
   </si>
   <si>
     <t xml:space="preserve">2.96845674514771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53615689277649</t>
+    <t xml:space="preserve">2.53615665435791</t>
   </si>
   <si>
     <t xml:space="preserve">2.26179122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49004530906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4197244644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42664122581482</t>
+    <t xml:space="preserve">2.49004507064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41972422599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42664170265198</t>
   </si>
   <si>
     <t xml:space="preserve">2.49235081672668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3690013885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28830575942993</t>
+    <t xml:space="preserve">2.36900115013123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28830552101135</t>
   </si>
   <si>
     <t xml:space="preserve">2.29752779006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30559730529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35747289657593</t>
+    <t xml:space="preserve">2.30559778213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35747337341309</t>
   </si>
   <si>
     <t xml:space="preserve">2.43240523338318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61108875274658</t>
+    <t xml:space="preserve">2.611088514328</t>
   </si>
   <si>
     <t xml:space="preserve">2.59379696846008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68025684356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59725546836853</t>
+    <t xml:space="preserve">2.68025755882263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59725522994995</t>
   </si>
   <si>
     <t xml:space="preserve">2.60647821426392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56958842277527</t>
+    <t xml:space="preserve">2.56958818435669</t>
   </si>
   <si>
     <t xml:space="preserve">2.62838101387024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62261724472046</t>
+    <t xml:space="preserve">2.6226167678833</t>
   </si>
   <si>
     <t xml:space="preserve">2.5949501991272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61685347557068</t>
+    <t xml:space="preserve">2.61685371398926</t>
   </si>
   <si>
     <t xml:space="preserve">2.54653239250183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63414573669434</t>
+    <t xml:space="preserve">2.63414549827576</t>
   </si>
   <si>
     <t xml:space="preserve">2.58226895332336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4035849571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4151132106781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43816947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55114364624023</t>
+    <t xml:space="preserve">2.40358543395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41511344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4381697177887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55114388465881</t>
   </si>
   <si>
     <t xml:space="preserve">2.58572769165039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65143704414368</t>
+    <t xml:space="preserve">2.65143728256226</t>
   </si>
   <si>
     <t xml:space="preserve">2.65489506721497</t>
@@ -479,49 +479,49 @@
     <t xml:space="preserve">2.604172706604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54307436943054</t>
+    <t xml:space="preserve">2.54307413101196</t>
   </si>
   <si>
     <t xml:space="preserve">2.41857147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37015438079834</t>
+    <t xml:space="preserve">2.37015414237976</t>
   </si>
   <si>
     <t xml:space="preserve">2.39321041107178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51310157775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50964260101318</t>
+    <t xml:space="preserve">2.51310133934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5096423625946</t>
   </si>
   <si>
     <t xml:space="preserve">2.46122527122498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44854426383972</t>
+    <t xml:space="preserve">2.4485445022583</t>
   </si>
   <si>
     <t xml:space="preserve">2.50733685493469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50157356262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49696254730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51540684700012</t>
+    <t xml:space="preserve">2.50157332420349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49696207046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5154070854187</t>
   </si>
   <si>
     <t xml:space="preserve">2.53039336204529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57304716110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66181230545044</t>
+    <t xml:space="preserve">2.57304739952087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66181254386902</t>
   </si>
   <si>
     <t xml:space="preserve">2.62722849845886</t>
@@ -533,16 +533,16 @@
     <t xml:space="preserve">2.83012080192566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7909255027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67449331283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6560480594635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64797925949097</t>
+    <t xml:space="preserve">2.79092574119568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67449355125427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65604782104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64797854423523</t>
   </si>
   <si>
     <t xml:space="preserve">2.65720105171204</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">2.64567351341248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52001786231995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51886487007141</t>
+    <t xml:space="preserve">2.52001810073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51886510848999</t>
   </si>
   <si>
     <t xml:space="preserve">2.49580931663513</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">2.52117085456848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52462911605835</t>
+    <t xml:space="preserve">2.52462887763977</t>
   </si>
   <si>
     <t xml:space="preserve">2.54192161560059</t>
@@ -575,28 +575,28 @@
     <t xml:space="preserve">2.46929526329041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39436316490173</t>
+    <t xml:space="preserve">2.39436292648315</t>
   </si>
   <si>
     <t xml:space="preserve">2.32173657417297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32519483566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24795746803284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26524972915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32634782791138</t>
+    <t xml:space="preserve">2.32519507408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24795770645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26524925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32634806632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.3862931728363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4439332485199</t>
+    <t xml:space="preserve">2.44393348693848</t>
   </si>
   <si>
     <t xml:space="preserve">2.44623875617981</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">2.5707414150238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57996344566345</t>
+    <t xml:space="preserve">2.57996296882629</t>
   </si>
   <si>
     <t xml:space="preserve">2.56267166137695</t>
@@ -626,157 +626,157 @@
     <t xml:space="preserve">2.60993599891663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59956097602844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55344915390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70907735824585</t>
+    <t xml:space="preserve">2.59956073760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55344891548157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70907688140869</t>
   </si>
   <si>
     <t xml:space="preserve">2.67910432815552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58111667633057</t>
+    <t xml:space="preserve">2.58111596107483</t>
   </si>
   <si>
     <t xml:space="preserve">2.80130100250244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81282925605774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72291111946106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78285598754883</t>
+    <t xml:space="preserve">2.81282901763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7229106426239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78285622596741</t>
   </si>
   <si>
     <t xml:space="preserve">2.82551026344299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92522692680359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96557426452637</t>
+    <t xml:space="preserve">2.92522668838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96557474136353</t>
   </si>
   <si>
     <t xml:space="preserve">2.91081690788269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00592279434204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03474307060242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99727630615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98574876785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94828295707703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93963694572449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9742214679718</t>
+    <t xml:space="preserve">3.00592255592346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03474235534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9972767829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98574829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94828271865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93963670730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97422099113464</t>
   </si>
   <si>
     <t xml:space="preserve">2.99151301383972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.014568567276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03186082839966</t>
+    <t xml:space="preserve">3.01456928253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0318603515625</t>
   </si>
   <si>
     <t xml:space="preserve">3.16155076026917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13849496841431</t>
+    <t xml:space="preserve">3.13849449157715</t>
   </si>
   <si>
     <t xml:space="preserve">3.11255693435669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12984871864319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2047803401947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16443252563477</t>
+    <t xml:space="preserve">3.12984848022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20478081703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16443204879761</t>
   </si>
   <si>
     <t xml:space="preserve">3.19613480567932</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19901704788208</t>
+    <t xml:space="preserve">3.1990168094635</t>
   </si>
   <si>
     <t xml:space="preserve">3.12408518791199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14137697219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08373689651489</t>
+    <t xml:space="preserve">3.14137625694275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08373665809631</t>
   </si>
   <si>
     <t xml:space="preserve">3.30276894569397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2624204158783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18748903274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28547620773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22783637046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17596054077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2480103969574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26818442344666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23936414718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09238266944885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10102891921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05491662025452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08085465431213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11832094192505</t>
+    <t xml:space="preserve">3.26242065429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1874885559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28547644615173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22783708572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17596006393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24800992012024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26818418502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23936438560486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09238219261169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10102868080139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05491709709167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08085441589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11832070350647</t>
   </si>
   <si>
     <t xml:space="preserve">3.15002250671387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0116868019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92810893058777</t>
+    <t xml:space="preserve">3.01168704032898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92810845375061</t>
   </si>
   <si>
     <t xml:space="preserve">2.95404696464539</t>
@@ -788,19 +788,19 @@
     <t xml:space="preserve">2.91369891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98863077163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0030403137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02609658241272</t>
+    <t xml:space="preserve">2.98863101005554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00304079055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0260968208313</t>
   </si>
   <si>
     <t xml:space="preserve">3.07797312736511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05779910087585</t>
+    <t xml:space="preserve">3.0577986240387</t>
   </si>
   <si>
     <t xml:space="preserve">3.18172407150269</t>
@@ -809,40 +809,40 @@
     <t xml:space="preserve">3.17019701004028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23360085487366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24512839317322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.250892162323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27106690406799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27394843101501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28259515762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25665593147278</t>
+    <t xml:space="preserve">3.23360061645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2451286315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25089263916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27106642723083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27394866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28259468078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25665616989136</t>
   </si>
   <si>
     <t xml:space="preserve">3.18460655212402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29412269592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10391116142273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34023451805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4439868927002</t>
+    <t xml:space="preserve">3.29412245750427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10391092300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34023499488831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44398617744446</t>
   </si>
   <si>
     <t xml:space="preserve">3.4324586391449</t>
@@ -851,76 +851,76 @@
     <t xml:space="preserve">3.46416020393372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45839691162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49298024177551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44686818122864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50450801849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60249638557434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51603627204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46992468833923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44110417366028</t>
+    <t xml:space="preserve">3.45839643478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49297976493835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44686794281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50450825691223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60249662399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51603603363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46992421150208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44110488891602</t>
   </si>
   <si>
     <t xml:space="preserve">3.42381286621094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41228461265564</t>
+    <t xml:space="preserve">3.41228437423706</t>
   </si>
   <si>
     <t xml:space="preserve">3.39499258995056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37193632125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4893524646759</t>
+    <t xml:space="preserve">3.37193584442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48935270309448</t>
   </si>
   <si>
     <t xml:space="preserve">3.4923632144928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5947253704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72117304801941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71515202522278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58870387077332</t>
+    <t xml:space="preserve">3.59472584724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72117280960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7151517868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58870339393616</t>
   </si>
   <si>
     <t xml:space="preserve">3.46827793121338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41107559204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49838423728943</t>
+    <t xml:space="preserve">3.41107535362244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49838447570801</t>
   </si>
   <si>
     <t xml:space="preserve">3.54053330421448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50440573692322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51644849777222</t>
+    <t xml:space="preserve">3.50440549850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5164487361908</t>
   </si>
   <si>
     <t xml:space="preserve">3.54956531524658</t>
@@ -929,19 +929,19 @@
     <t xml:space="preserve">3.70912981033325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72418403625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64891695976257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75127959251404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72719383239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76332211494446</t>
+    <t xml:space="preserve">3.72418332099915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64891672134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75127935409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72719430923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76332259178162</t>
   </si>
   <si>
     <t xml:space="preserve">3.73923707008362</t>
@@ -950,16 +950,16 @@
     <t xml:space="preserve">3.74525785446167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71214175224304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7031090259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75730013847351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77536463737488</t>
+    <t xml:space="preserve">3.71214127540588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70310950279236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75730061531067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7753643989563</t>
   </si>
   <si>
     <t xml:space="preserve">3.77837562561035</t>
@@ -968,13 +968,13 @@
     <t xml:space="preserve">3.84159970283508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85966300964355</t>
+    <t xml:space="preserve">3.85966348648071</t>
   </si>
   <si>
     <t xml:space="preserve">3.82654619216919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09750652313232</t>
+    <t xml:space="preserve">4.09750604629517</t>
   </si>
   <si>
     <t xml:space="preserve">4.14266490936279</t>
@@ -986,19 +986,19 @@
     <t xml:space="preserve">4.17277193069458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19083547592163</t>
+    <t xml:space="preserve">4.19083595275879</t>
   </si>
   <si>
     <t xml:space="preserve">4.22094202041626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19986772537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24502658843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2691125869751</t>
+    <t xml:space="preserve">4.19986724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24502754211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26911306381226</t>
   </si>
   <si>
     <t xml:space="preserve">4.26309156417847</t>
@@ -1010,13 +1010,13 @@
     <t xml:space="preserve">4.15470790863037</t>
   </si>
   <si>
-    <t xml:space="preserve">4.145676612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13664436340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22395324707031</t>
+    <t xml:space="preserve">4.14567613601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13664388656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22395277023315</t>
   </si>
   <si>
     <t xml:space="preserve">4.22696352005005</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">4.33534717559814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25104856491089</t>
+    <t xml:space="preserve">4.25104904174805</t>
   </si>
   <si>
     <t xml:space="preserve">4.28717660903931</t>
@@ -1034,61 +1034,61 @@
     <t xml:space="preserve">4.11857938766479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25405931472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09449434280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08847332000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04030275344849</t>
+    <t xml:space="preserve">4.25405979156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09449529647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08847284317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04030227661133</t>
   </si>
   <si>
     <t xml:space="preserve">4.05234479904175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95901489257812</t>
+    <t xml:space="preserve">3.95901465415955</t>
   </si>
   <si>
     <t xml:space="preserve">3.86267352104187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86568474769592</t>
+    <t xml:space="preserve">3.86568450927734</t>
   </si>
   <si>
     <t xml:space="preserve">3.94396185874939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94697260856628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95600366592407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98008942604065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97406792640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07342052459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06438779830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98912191390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96202564239502</t>
+    <t xml:space="preserve">3.94697237014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95600414276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98008966445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97406816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07342004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06438827514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98912167549133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96202516555786</t>
   </si>
   <si>
     <t xml:space="preserve">4.01320648193359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03428173065186</t>
+    <t xml:space="preserve">4.0342812538147</t>
   </si>
   <si>
     <t xml:space="preserve">4.00417470932007</t>
@@ -1097,70 +1097,70 @@
     <t xml:space="preserve">4.00116395950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90783357620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88977026939392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95299363136292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01019620895386</t>
+    <t xml:space="preserve">3.90783381462097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8897705078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95299315452576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0101957321167</t>
   </si>
   <si>
     <t xml:space="preserve">4.11255836486816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15771818161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06739854812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9861114025116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93191862106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90181159973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87471675872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85364151000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82353544235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579129219055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84762096405029</t>
+    <t xml:space="preserve">4.15771865844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06739902496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98611068725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93191933631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9018120765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87471604347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85364198684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82353568077087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579153060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84762072563171</t>
   </si>
   <si>
     <t xml:space="preserve">3.83256769180298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88073825836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88374853134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92589735984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92890858650208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88675928115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91385507583618</t>
+    <t xml:space="preserve">3.88073801994324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88374805450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92589783668518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92890882492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88675904273987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9138548374176</t>
   </si>
   <si>
     <t xml:space="preserve">3.91084480285645</t>
@@ -1172,82 +1172,82 @@
     <t xml:space="preserve">3.8205246925354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69106674194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70611929893494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55558657646179</t>
+    <t xml:space="preserve">3.69106650352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70611953735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55558633804321</t>
   </si>
   <si>
     <t xml:space="preserve">3.47429895401001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33580827713013</t>
+    <t xml:space="preserve">3.33580851554871</t>
   </si>
   <si>
     <t xml:space="preserve">3.40204286575317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52246952056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54354405403137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53150153160095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57365083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60074687004089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5766613483429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53752326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55257606506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50139451026917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45021462440491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51042628288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48634195327759</t>
+    <t xml:space="preserve">3.52246904373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54354429244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53150105476379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57365036010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60074615478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57666158676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53752255439758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55257630348206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50139498710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45021390914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51042652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48634219169617</t>
   </si>
   <si>
     <t xml:space="preserve">3.43817138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40806436538696</t>
+    <t xml:space="preserve">3.40806460380554</t>
   </si>
   <si>
     <t xml:space="preserve">3.53451204299927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60977816581726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35387253761292</t>
+    <t xml:space="preserve">3.60977864265442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35387206077576</t>
   </si>
   <si>
     <t xml:space="preserve">3.42612862586975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4441921710968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32376575469971</t>
+    <t xml:space="preserve">3.44419264793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32376551628113</t>
   </si>
   <si>
     <t xml:space="preserve">3.39000058174133</t>
@@ -1259,52 +1259,52 @@
     <t xml:space="preserve">3.73020505905151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66698098182678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64590668678284</t>
+    <t xml:space="preserve">3.6669807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64590716362</t>
   </si>
   <si>
     <t xml:space="preserve">3.63386392593384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81450247764587</t>
+    <t xml:space="preserve">3.81450271606445</t>
   </si>
   <si>
     <t xml:space="preserve">3.86869502067566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93492937088013</t>
+    <t xml:space="preserve">3.93492984771729</t>
   </si>
   <si>
     <t xml:space="preserve">4.04331350326538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99213218688965</t>
+    <t xml:space="preserve">3.99213171005249</t>
   </si>
   <si>
     <t xml:space="preserve">3.98310017585754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06137704849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12460088729858</t>
+    <t xml:space="preserve">4.06137752532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12460136413574</t>
   </si>
   <si>
     <t xml:space="preserve">4.16072940826416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07040882110596</t>
+    <t xml:space="preserve">4.07040929794312</t>
   </si>
   <si>
     <t xml:space="preserve">4.08245229721069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80848240852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89880204200745</t>
+    <t xml:space="preserve">3.80848169326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89880228042603</t>
   </si>
   <si>
     <t xml:space="preserve">3.91987681388855</t>
@@ -1313,67 +1313,67 @@
     <t xml:space="preserve">3.78439617156982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77235388755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7994499206543</t>
+    <t xml:space="preserve">3.77235436439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79945015907288</t>
   </si>
   <si>
     <t xml:space="preserve">3.73622608184814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75429081916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76633310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63988518714905</t>
+    <t xml:space="preserve">3.75429058074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76633286476135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63988494873047</t>
   </si>
   <si>
     <t xml:space="preserve">3.56160807609558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66999101638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96503591537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79342889785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74224710464478</t>
+    <t xml:space="preserve">3.66999220848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96503567695618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79342865943909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74224734306335</t>
   </si>
   <si>
     <t xml:space="preserve">3.79164910316467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77612257003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78854441642761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70469927787781</t>
+    <t xml:space="preserve">3.77612209320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78854393959045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70469880104065</t>
   </si>
   <si>
     <t xml:space="preserve">3.58358979225159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55914306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55258822441101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51326131820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61158013343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58536148071289</t>
+    <t xml:space="preserve">3.55914258956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55258846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51326060295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61157965660095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58536076545715</t>
   </si>
   <si>
     <t xml:space="preserve">3.76888966560364</t>
@@ -1382,16 +1382,16 @@
     <t xml:space="preserve">3.89998173713684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342761039734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85082221031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81149530410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63779830932617</t>
+    <t xml:space="preserve">3.89342713356018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85082292556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81149506568909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63779878616333</t>
   </si>
   <si>
     <t xml:space="preserve">3.7557806968689</t>
@@ -1400,142 +1400,142 @@
     <t xml:space="preserve">3.73939442634583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86065411567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099078178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81804943084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9655282497406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98846888542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93275475502014</t>
+    <t xml:space="preserve">3.86065435409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099006652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81804871559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96552777290344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98846864700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93275451660156</t>
   </si>
   <si>
     <t xml:space="preserve">3.86720871925354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84426760673523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91309094429016</t>
+    <t xml:space="preserve">3.84426784515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91308999061584</t>
   </si>
   <si>
     <t xml:space="preserve">3.82132649421692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03107404708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04418325424194</t>
+    <t xml:space="preserve">4.03107309341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04418277740479</t>
   </si>
   <si>
     <t xml:space="preserve">4.0245189666748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98191380500793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90653681755066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99830031394958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77544474601746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76561307907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71973085403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71645283699036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56897473335266</t>
+    <t xml:space="preserve">3.98191428184509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90653657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99830055236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7754442691803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76561236381531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71973037719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71645355224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56897497177124</t>
   </si>
   <si>
     <t xml:space="preserve">3.50670623779297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46737909317017</t>
+    <t xml:space="preserve">3.46737837791443</t>
   </si>
   <si>
     <t xml:space="preserve">3.27467346191406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93645715713501</t>
+    <t xml:space="preserve">2.93645668029785</t>
   </si>
   <si>
     <t xml:space="preserve">3.03477597236633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19077491760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42149639129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41494226455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3362865447998</t>
+    <t xml:space="preserve">3.19077467918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42149686813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41494202613831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33628678321838</t>
   </si>
   <si>
     <t xml:space="preserve">3.31662321090698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35595059394836</t>
+    <t xml:space="preserve">3.35595107078552</t>
   </si>
   <si>
     <t xml:space="preserve">3.211749792099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30023598670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32645463943481</t>
+    <t xml:space="preserve">3.30023622512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32645487785339</t>
   </si>
   <si>
     <t xml:space="preserve">3.39855551719666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33956384658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29040455818176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2772958278656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28057312965393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1829092502594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12260723114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07148146629333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01511168479919</t>
+    <t xml:space="preserve">3.33956408500671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29040503501892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27729535102844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28057289123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18290948867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12260699272156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07148098945618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01511192321777</t>
   </si>
   <si>
     <t xml:space="preserve">2.89975118637085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01904487609863</t>
+    <t xml:space="preserve">3.01904463768005</t>
   </si>
   <si>
     <t xml:space="preserve">3.01380085945129</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">3.04919576644897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97971701622009</t>
+    <t xml:space="preserve">2.97971725463867</t>
   </si>
   <si>
     <t xml:space="preserve">3.02691006660461</t>
@@ -1556,28 +1556,28 @@
     <t xml:space="preserve">3.10425424575806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04264163970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00200247764587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00462484359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98233938217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98627161979675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92072582244873</t>
+    <t xml:space="preserve">3.04264116287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00200295448303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00462436676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98233914375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98627185821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92072558403015</t>
   </si>
   <si>
     <t xml:space="preserve">2.92728018760681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00069165229797</t>
+    <t xml:space="preserve">3.00069212913513</t>
   </si>
   <si>
     <t xml:space="preserve">3.01249003410339</t>
@@ -1586,34 +1586,34 @@
     <t xml:space="preserve">3.03739738464355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95612072944641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92465877532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84469223022461</t>
+    <t xml:space="preserve">2.95612049102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92465829849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84469270706177</t>
   </si>
   <si>
     <t xml:space="preserve">2.97709536552429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00724577903748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89057469367981</t>
+    <t xml:space="preserve">3.00724601745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89057493209839</t>
   </si>
   <si>
     <t xml:space="preserve">2.77259206771851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79487752914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73064279556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71228981018066</t>
+    <t xml:space="preserve">2.79487729072571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73064255714417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71229004859924</t>
   </si>
   <si>
     <t xml:space="preserve">2.70049166679382</t>
@@ -1625,82 +1625,82 @@
     <t xml:space="preserve">2.76997017860413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73719763755798</t>
+    <t xml:space="preserve">2.7371973991394</t>
   </si>
   <si>
     <t xml:space="preserve">2.7214663028717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69000434875488</t>
+    <t xml:space="preserve">2.6900041103363</t>
   </si>
   <si>
     <t xml:space="preserve">2.63625621795654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64936542510986</t>
+    <t xml:space="preserve">2.64936566352844</t>
   </si>
   <si>
     <t xml:space="preserve">2.62052536010742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67689514160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72015523910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87615442276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85124707221985</t>
+    <t xml:space="preserve">2.67689490318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7201554775238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87615489959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85124683380127</t>
   </si>
   <si>
     <t xml:space="preserve">2.86697816848755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93907904624939</t>
+    <t xml:space="preserve">2.93907880783081</t>
   </si>
   <si>
     <t xml:space="preserve">2.91154932975769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91679286956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92596983909607</t>
+    <t xml:space="preserve">2.91679263114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92596960067749</t>
   </si>
   <si>
     <t xml:space="preserve">2.94170022010803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99807024002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04133033752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99675917625427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99413681030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96267509460449</t>
+    <t xml:space="preserve">2.99807000160217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04133009910583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99675893783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99413704872131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96267533302307</t>
   </si>
   <si>
     <t xml:space="preserve">2.96005320549011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91286039352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77521395683289</t>
+    <t xml:space="preserve">2.91285991668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77521419525146</t>
   </si>
   <si>
     <t xml:space="preserve">2.70704627037048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68869352340698</t>
+    <t xml:space="preserve">2.6886932849884</t>
   </si>
   <si>
     <t xml:space="preserve">2.705735206604</t>
@@ -1709,40 +1709,40 @@
     <t xml:space="preserve">2.74244093894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64674401283264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6414999961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59692883491516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38193821907043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4671483039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44879555702209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49074459075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47108101844788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48681211471558</t>
+    <t xml:space="preserve">2.64674377441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64150023460388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59692907333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38193869590759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46714806556702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44879531860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49074482917786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4710807800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48681163787842</t>
   </si>
   <si>
     <t xml:space="preserve">2.4199550151825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31639218330383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25871229171753</t>
+    <t xml:space="preserve">2.31639242172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25871205329895</t>
   </si>
   <si>
     <t xml:space="preserve">2.20365357398987</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">2.28493046760559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38587117195129</t>
+    <t xml:space="preserve">2.38587141036987</t>
   </si>
   <si>
     <t xml:space="preserve">2.39242577552795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42519855499268</t>
+    <t xml:space="preserve">2.42519879341125</t>
   </si>
   <si>
     <t xml:space="preserve">2.45928263664246</t>
@@ -1769,28 +1769,28 @@
     <t xml:space="preserve">2.54973602294922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47239184379578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44617366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45797157287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47501373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54842495918274</t>
+    <t xml:space="preserve">2.4723916053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44617342948914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45797181129456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47501349449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54842519760132</t>
   </si>
   <si>
     <t xml:space="preserve">2.43044233322144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40815687179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33998870849609</t>
+    <t xml:space="preserve">2.40815663337708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33998894691467</t>
   </si>
   <si>
     <t xml:space="preserve">2.28886318206787</t>
@@ -1799,10 +1799,10 @@
     <t xml:space="preserve">2.27968668937683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25740098953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17612433433533</t>
+    <t xml:space="preserve">2.25740122795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17612409591675</t>
   </si>
   <si>
     <t xml:space="preserve">2.18661141395569</t>
@@ -1811,19 +1811,19 @@
     <t xml:space="preserve">2.13155293464661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29410672187805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35178756713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766955375671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44748425483704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42388772964478</t>
+    <t xml:space="preserve">2.29410696029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35178732872009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766931533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44748449325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42388796806335</t>
   </si>
   <si>
     <t xml:space="preserve">2.40946769714355</t>
@@ -1832,34 +1832,34 @@
     <t xml:space="preserve">2.40029120445251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21938467025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19447708129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25477957725525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31901478767395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32687950134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26264452934265</t>
+    <t xml:space="preserve">2.21938443183899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19447731971741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25477933883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31901454925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32687997817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26264476776123</t>
   </si>
   <si>
     <t xml:space="preserve">2.17743492126465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12893152236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14597296714783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12237644195557</t>
+    <t xml:space="preserve">2.12893104553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14597320556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12237668037415</t>
   </si>
   <si>
     <t xml:space="preserve">2.12368750572205</t>
@@ -1868,22 +1868,22 @@
     <t xml:space="preserve">2.10271286964417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11713290214539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14728403091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15121674537659</t>
+    <t xml:space="preserve">2.11713314056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14728426933289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15121698379517</t>
   </si>
   <si>
     <t xml:space="preserve">2.23904824256897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20758652687073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36489677429199</t>
+    <t xml:space="preserve">2.20758628845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36489653587341</t>
   </si>
   <si>
     <t xml:space="preserve">2.34785461425781</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">2.37407302856445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25084686279297</t>
+    <t xml:space="preserve">2.25084662437439</t>
   </si>
   <si>
     <t xml:space="preserve">2.39504742622375</t>
@@ -1907,22 +1907,22 @@
     <t xml:space="preserve">2.43306422233582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44486260414124</t>
+    <t xml:space="preserve">2.44486284255981</t>
   </si>
   <si>
     <t xml:space="preserve">2.44224071502686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43175315856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38456010818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35309791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34654355049133</t>
+    <t xml:space="preserve">2.43175339698792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38455986976624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35309815406799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34654331207275</t>
   </si>
   <si>
     <t xml:space="preserve">2.35440897941589</t>
@@ -1931,13 +1931,13 @@
     <t xml:space="preserve">2.37145113945007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28755235671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26788854598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31114888191223</t>
+    <t xml:space="preserve">2.28755211830139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26788878440857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31114912033081</t>
   </si>
   <si>
     <t xml:space="preserve">2.37931656837463</t>
@@ -1946,19 +1946,19 @@
     <t xml:space="preserve">2.40291285514832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4055347442627</t>
+    <t xml:space="preserve">2.40553498268127</t>
   </si>
   <si>
     <t xml:space="preserve">2.37014031410217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33605575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39898014068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37669444084167</t>
+    <t xml:space="preserve">2.33605599403381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39898037910461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37669467926025</t>
   </si>
   <si>
     <t xml:space="preserve">2.5012321472168</t>
@@ -1970,13 +1970,13 @@
     <t xml:space="preserve">2.52613925933838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50385355949402</t>
+    <t xml:space="preserve">2.50385403633118</t>
   </si>
   <si>
     <t xml:space="preserve">2.49336647987366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42782068252563</t>
+    <t xml:space="preserve">2.42782020568848</t>
   </si>
   <si>
     <t xml:space="preserve">2.39635848999023</t>
@@ -1985,34 +1985,34 @@
     <t xml:space="preserve">2.38718199729919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37276148796082</t>
+    <t xml:space="preserve">2.37276196479797</t>
   </si>
   <si>
     <t xml:space="preserve">2.37800574302673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33867835998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29935050010681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38062739372253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30459427833557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38849282264709</t>
+    <t xml:space="preserve">2.33867812156677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29935073852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38062763214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30459451675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38849306106567</t>
   </si>
   <si>
     <t xml:space="preserve">2.45666074752808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40160226821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34130001068115</t>
+    <t xml:space="preserve">2.40160250663757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34129977226257</t>
   </si>
   <si>
     <t xml:space="preserve">2.34392166137695</t>
@@ -2021,19 +2021,19 @@
     <t xml:space="preserve">2.38324928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32556915283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30328321456909</t>
+    <t xml:space="preserve">2.32556891441345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30328297615051</t>
   </si>
   <si>
     <t xml:space="preserve">2.30590510368347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34523272514343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32425808906555</t>
+    <t xml:space="preserve">2.34523296356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32425832748413</t>
   </si>
   <si>
     <t xml:space="preserve">2.30983781814575</t>
@@ -2042,13 +2042,13 @@
     <t xml:space="preserve">2.21545195579529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19054412841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09091448783875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08698201179504</t>
+    <t xml:space="preserve">2.19054436683655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09091472625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08698177337646</t>
   </si>
   <si>
     <t xml:space="preserve">1.99783957004547</t>
@@ -2057,37 +2057,37 @@
     <t xml:space="preserve">2.03978872299194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97686469554901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99128472805023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97817552089691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9899628162384</t>
+    <t xml:space="preserve">1.97686433792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99128484725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97817528247833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98996269702911</t>
   </si>
   <si>
     <t xml:space="preserve">1.99967014789581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97470915317535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94420075416565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91923952102661</t>
+    <t xml:space="preserve">1.97470891475677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94420051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91923928260803</t>
   </si>
   <si>
     <t xml:space="preserve">1.89843833446503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86376988887787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8263281583786</t>
+    <t xml:space="preserve">1.86377012729645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82632839679718</t>
   </si>
   <si>
     <t xml:space="preserve">1.87625098228455</t>
@@ -2096,58 +2096,58 @@
     <t xml:space="preserve">1.87902414798737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83742237091064</t>
+    <t xml:space="preserve">1.83742213249207</t>
   </si>
   <si>
     <t xml:space="preserve">1.95113432407379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9275598526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89982521533966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92062628269196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90953242778778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9067587852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88734436035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88873147964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88179767131805</t>
+    <t xml:space="preserve">1.92755973339081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89982509613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92062640190125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90953207015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90675866603851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88734459877014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8887312412262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88179755210876</t>
   </si>
   <si>
     <t xml:space="preserve">2.02879166603088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98302924633026</t>
+    <t xml:space="preserve">1.98302936553955</t>
   </si>
   <si>
     <t xml:space="preserve">2.03156495094299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98857641220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95945465564728</t>
+    <t xml:space="preserve">1.98857629299164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95945477485657</t>
   </si>
   <si>
     <t xml:space="preserve">2.00660371780396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00521683692932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07177996635437</t>
+    <t xml:space="preserve">2.0052170753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07178020477295</t>
   </si>
   <si>
     <t xml:space="preserve">2.0939679145813</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">2.21461367607117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21184039115906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24928188323975</t>
+    <t xml:space="preserve">2.21184015274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24928212165833</t>
   </si>
   <si>
     <t xml:space="preserve">2.31445860862732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30059123039246</t>
+    <t xml:space="preserve">2.30059146881104</t>
   </si>
   <si>
     <t xml:space="preserve">2.30891156196594</t>
@@ -2195,22 +2195,22 @@
     <t xml:space="preserve">2.2215473651886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24789547920227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24650835990906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.245121717453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28811097145081</t>
+    <t xml:space="preserve">2.24789524078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24650859832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24512195587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28811049461365</t>
   </si>
   <si>
     <t xml:space="preserve">2.32277894020081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37824821472168</t>
+    <t xml:space="preserve">2.37824845314026</t>
   </si>
   <si>
     <t xml:space="preserve">2.30613827705383</t>
@@ -2222,7 +2222,7 @@
     <t xml:space="preserve">2.18687915802002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17162466049194</t>
+    <t xml:space="preserve">2.17162489891052</t>
   </si>
   <si>
     <t xml:space="preserve">2.17439842224121</t>
@@ -2237,10 +2237,10 @@
     <t xml:space="preserve">2.10783529281616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12863636016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09812808036804</t>
+    <t xml:space="preserve">2.12863612174988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09812831878662</t>
   </si>
   <si>
     <t xml:space="preserve">2.12724947929382</t>
@@ -2255,13 +2255,13 @@
     <t xml:space="preserve">2.2368016242981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20629334449768</t>
+    <t xml:space="preserve">2.20629358291626</t>
   </si>
   <si>
     <t xml:space="preserve">2.19935965538025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18549251556396</t>
+    <t xml:space="preserve">2.18549227714539</t>
   </si>
   <si>
     <t xml:space="preserve">2.25760245323181</t>
@@ -2273,28 +2273,28 @@
     <t xml:space="preserve">2.23957514762878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35606026649475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38102197647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3671543598175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38379549980164</t>
+    <t xml:space="preserve">2.35606074333191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38102173805237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36715459823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38379526138306</t>
   </si>
   <si>
     <t xml:space="preserve">2.43510460853577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5155348777771</t>
+    <t xml:space="preserve">2.51553511619568</t>
   </si>
   <si>
     <t xml:space="preserve">2.49889421463013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42955756187439</t>
+    <t xml:space="preserve">2.42955732345581</t>
   </si>
   <si>
     <t xml:space="preserve">2.42817068099976</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">2.44897198677063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45867872238159</t>
+    <t xml:space="preserve">2.45867896080017</t>
   </si>
   <si>
     <t xml:space="preserve">2.39766263961792</t>
@@ -2312,31 +2312,31 @@
     <t xml:space="preserve">2.38795566558838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37131476402283</t>
+    <t xml:space="preserve">2.37131500244141</t>
   </si>
   <si>
     <t xml:space="preserve">2.382408618927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41707682609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42401051521301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37408828735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32693934440613</t>
+    <t xml:space="preserve">2.41707706451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42401075363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37408804893494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32693910598755</t>
   </si>
   <si>
     <t xml:space="preserve">2.2992045879364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31723189353943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34496665000916</t>
+    <t xml:space="preserve">2.31723213195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34496641159058</t>
   </si>
   <si>
     <t xml:space="preserve">2.34635353088379</t>
@@ -2363,16 +2363,16 @@
     <t xml:space="preserve">2.73879909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70690441131592</t>
+    <t xml:space="preserve">2.70690417289734</t>
   </si>
   <si>
     <t xml:space="preserve">2.74711942672729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72770524024963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75266623497009</t>
+    <t xml:space="preserve">2.72770500183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75266647338867</t>
   </si>
   <si>
     <t xml:space="preserve">2.76237344741821</t>
@@ -2387,79 +2387,79 @@
     <t xml:space="preserve">2.69581055641174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70413064956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7207715511322</t>
+    <t xml:space="preserve">2.70413088798523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72077178955078</t>
   </si>
   <si>
     <t xml:space="preserve">2.80120205879211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78733491897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82893705368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85528469085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9468092918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01614594459534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02724027633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04804062843323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07993531227112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13679218292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1464991569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17562007904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14511203765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2310893535614</t>
+    <t xml:space="preserve">2.78733468055725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82893657684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85528492927551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94680905342102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01614570617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02724003791809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04804039001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0799355506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13679170608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14649868011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17562055587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14511179924011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23108959197998</t>
   </si>
   <si>
     <t xml:space="preserve">3.24773073196411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26298451423645</t>
+    <t xml:space="preserve">3.26298427581787</t>
   </si>
   <si>
     <t xml:space="preserve">3.26159763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22554278373718</t>
+    <t xml:space="preserve">3.2255425453186</t>
   </si>
   <si>
     <t xml:space="preserve">3.18532729148865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18394112586975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2560510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21028876304626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25327730178833</t>
+    <t xml:space="preserve">3.18394088745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25605130195618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21028900146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25327706336975</t>
   </si>
   <si>
     <t xml:space="preserve">3.22831606864929</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">3.21306180953979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19919466972351</t>
+    <t xml:space="preserve">3.19919490814209</t>
   </si>
   <si>
     <t xml:space="preserve">3.20890164375305</t>
@@ -2489,52 +2489,52 @@
     <t xml:space="preserve">3.1908745765686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20335483551025</t>
+    <t xml:space="preserve">3.2033543586731</t>
   </si>
   <si>
     <t xml:space="preserve">3.06606841087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09241628646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14788579940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20612812042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17839384078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17146015167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03694725036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15343236923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16868662834167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97038340568542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.035560131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14095187187195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12985801696777</t>
+    <t xml:space="preserve">3.09241652488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14788556098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20612835884094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17839336395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17146039009094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03694701194763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15343260765076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16868686676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.970383644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03555965423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14095211029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12985825538635</t>
   </si>
   <si>
     <t xml:space="preserve">3.14927244186401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17007350921631</t>
+    <t xml:space="preserve">3.17007327079773</t>
   </si>
   <si>
     <t xml:space="preserve">3.12708473205566</t>
@@ -2543,25 +2543,25 @@
     <t xml:space="preserve">3.10073685646057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07854890823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11044359207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0896430015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28239870071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34202885627747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34896206855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93987536430359</t>
+    <t xml:space="preserve">3.07854914665222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11044383049011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08964252471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28239917755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34202837944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34896159172058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93987560272217</t>
   </si>
   <si>
     <t xml:space="preserve">2.97315716743469</t>
@@ -2573,19 +2573,19 @@
     <t xml:space="preserve">2.73741245269775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58487176895142</t>
+    <t xml:space="preserve">2.58487153053284</t>
   </si>
   <si>
     <t xml:space="preserve">2.55159020423889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49473404884338</t>
+    <t xml:space="preserve">2.49473428726196</t>
   </si>
   <si>
     <t xml:space="preserve">2.29227089881897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07039356231689</t>
+    <t xml:space="preserve">2.07039332389832</t>
   </si>
   <si>
     <t xml:space="preserve">1.95668148994446</t>
@@ -2594,25 +2594,25 @@
     <t xml:space="preserve">1.99134969711304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69042837619781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7847261428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65576016902924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52818036079407</t>
+    <t xml:space="preserve">1.6904284954071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78472638130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65576004981995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52818059921265</t>
   </si>
   <si>
     <t xml:space="preserve">1.41030812263489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48519170284271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49489891529083</t>
+    <t xml:space="preserve">1.485191822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49489879608154</t>
   </si>
   <si>
     <t xml:space="preserve">1.60583758354187</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">1.72648358345032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68904161453247</t>
+    <t xml:space="preserve">1.68904185295105</t>
   </si>
   <si>
     <t xml:space="preserve">1.69736194610596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72371006011963</t>
+    <t xml:space="preserve">1.72371017932892</t>
   </si>
   <si>
     <t xml:space="preserve">1.75421822071075</t>
@@ -2654,46 +2654,46 @@
     <t xml:space="preserve">1.99412298202515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97609543800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96638822555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94142723083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85960972309113</t>
+    <t xml:space="preserve">1.97609531879425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96638834476471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94142735004425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85960984230042</t>
   </si>
   <si>
     <t xml:space="preserve">1.86793041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92339980602264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90121209621429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14805030822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26730966567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23818826675415</t>
+    <t xml:space="preserve">1.92339944839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90121221542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1480507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26730942726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23818802833557</t>
   </si>
   <si>
     <t xml:space="preserve">2.22570753097534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13418316841125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28117704391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35744738578796</t>
+    <t xml:space="preserve">2.13418340682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28117680549622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35744714736938</t>
   </si>
   <si>
     <t xml:space="preserve">2.40043592453003</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">2.3435800075531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30752491950989</t>
+    <t xml:space="preserve">2.30752515792847</t>
   </si>
   <si>
     <t xml:space="preserve">2.48411750793457</t>
@@ -2711,37 +2711,37 @@
     <t xml:space="preserve">2.51219487190247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49150609970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49741721153259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45456194877625</t>
+    <t xml:space="preserve">2.49150633811951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49741744995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45456218719482</t>
   </si>
   <si>
     <t xml:space="preserve">2.57130527496338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72647047042847</t>
+    <t xml:space="preserve">2.72647023200989</t>
   </si>
   <si>
     <t xml:space="preserve">2.75750350952148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80774712562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86538004875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87572407722473</t>
+    <t xml:space="preserve">2.80774736404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86537981033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87572431564331</t>
   </si>
   <si>
     <t xml:space="preserve">2.86833548545837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97473454475403</t>
+    <t xml:space="preserve">2.97473430633545</t>
   </si>
   <si>
     <t xml:space="preserve">3.20230960845947</t>
@@ -2756,13 +2756,13 @@
     <t xml:space="preserve">2.93483448028564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9363124370575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94222402572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99837827682495</t>
+    <t xml:space="preserve">2.93631267547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94222354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99837851524353</t>
   </si>
   <si>
     <t xml:space="preserve">3.00281167030334</t>
@@ -2780,19 +2780,19 @@
     <t xml:space="preserve">2.83582472801208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89050221443176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88459086418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85946893692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82843613624573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86242461204529</t>
+    <t xml:space="preserve">2.8905017375946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8845911026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85946869850159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82843589782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86242437362671</t>
   </si>
   <si>
     <t xml:space="preserve">2.93779039382935</t>
@@ -2807,10 +2807,10 @@
     <t xml:space="preserve">3.04418897628784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01906704902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92005729675293</t>
+    <t xml:space="preserve">3.01906728744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92005681991577</t>
   </si>
   <si>
     <t xml:space="preserve">2.93040156364441</t>
@@ -2825,13 +2825,13 @@
     <t xml:space="preserve">2.99394536018372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98951172828674</t>
+    <t xml:space="preserve">2.98951196670532</t>
   </si>
   <si>
     <t xml:space="preserve">2.95404553413391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95552349090576</t>
+    <t xml:space="preserve">2.95552325248718</t>
   </si>
   <si>
     <t xml:space="preserve">2.94665670394897</t>
@@ -2840,25 +2840,25 @@
     <t xml:space="preserve">3.03384470939636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09591054916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0175895690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99098944664001</t>
+    <t xml:space="preserve">3.0959107875824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758933067322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99098968505859</t>
   </si>
   <si>
     <t xml:space="preserve">2.93335723876953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9185791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75602579116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81365847587585</t>
+    <t xml:space="preserve">2.91857933998108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75602555274963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81365823745728</t>
   </si>
   <si>
     <t xml:space="preserve">2.85503554344177</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">2.92153477668762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96291255950928</t>
+    <t xml:space="preserve">2.9629123210907</t>
   </si>
   <si>
     <t xml:space="preserve">2.91266822814941</t>
@@ -2888,19 +2888,19 @@
     <t xml:space="preserve">2.84616899490356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80479145050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76784753799438</t>
+    <t xml:space="preserve">2.80479192733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76784777641296</t>
   </si>
   <si>
     <t xml:space="preserve">2.75307011604309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78410291671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7988805770874</t>
+    <t xml:space="preserve">2.78410267829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79888081550598</t>
   </si>
   <si>
     <t xml:space="preserve">2.74863696098328</t>
@@ -2909,25 +2909,25 @@
     <t xml:space="preserve">2.7752366065979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72351503372192</t>
+    <t xml:space="preserve">2.7235152721405</t>
   </si>
   <si>
     <t xml:space="preserve">2.76636981964111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79296946525574</t>
+    <t xml:space="preserve">2.79296970367432</t>
   </si>
   <si>
     <t xml:space="preserve">2.73681473731995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69987058639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79592514038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74272584915161</t>
+    <t xml:space="preserve">2.69987082481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79592537879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74272537231445</t>
   </si>
   <si>
     <t xml:space="preserve">2.75454783439636</t>
@@ -2936,37 +2936,37 @@
     <t xml:space="preserve">2.74715900421143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71612620353699</t>
+    <t xml:space="preserve">2.71612596511841</t>
   </si>
   <si>
     <t xml:space="preserve">2.70873713493347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7072594165802</t>
+    <t xml:space="preserve">2.70725965499878</t>
   </si>
   <si>
     <t xml:space="preserve">2.61268258094788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57573890686035</t>
+    <t xml:space="preserve">2.57573866844177</t>
   </si>
   <si>
     <t xml:space="preserve">2.52549457550049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54175019264221</t>
+    <t xml:space="preserve">2.54174995422363</t>
   </si>
   <si>
     <t xml:space="preserve">2.53436136245728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58460521697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52697277069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47525095939636</t>
+    <t xml:space="preserve">2.5846049785614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52697229385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47525072097778</t>
   </si>
   <si>
     <t xml:space="preserve">2.50037288665771</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">2.54618358612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55209445953369</t>
+    <t xml:space="preserve">2.55209469795227</t>
   </si>
   <si>
     <t xml:space="preserve">2.67179322242737</t>
@@ -2993,31 +2993,31 @@
     <t xml:space="preserve">2.60972714424133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54322791099548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52845001220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47377300262451</t>
+    <t xml:space="preserve">2.5432276725769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52845025062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47377324104309</t>
   </si>
   <si>
     <t xml:space="preserve">2.6289381980896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6570155620575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63632678985596</t>
+    <t xml:space="preserve">2.65701532363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63632702827454</t>
   </si>
   <si>
     <t xml:space="preserve">2.60677194595337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53140568733215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52253913879395</t>
+    <t xml:space="preserve">2.53140616416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52253937721252</t>
   </si>
   <si>
     <t xml:space="preserve">2.36441874504089</t>
@@ -3035,19 +3035,19 @@
     <t xml:space="preserve">2.58312749862671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64223766326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49298405647278</t>
+    <t xml:space="preserve">2.64223790168762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4929838180542</t>
   </si>
   <si>
     <t xml:space="preserve">2.61563801765442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6525821685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63041591644287</t>
+    <t xml:space="preserve">2.65258240699768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63041567802429</t>
   </si>
   <si>
     <t xml:space="preserve">2.71317028999329</t>
@@ -3059,28 +3059,28 @@
     <t xml:space="preserve">2.74568128585815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83139157295227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79149198532104</t>
+    <t xml:space="preserve">2.83139133453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79149174690247</t>
   </si>
   <si>
     <t xml:space="preserve">2.78853631019592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7589807510376</t>
+    <t xml:space="preserve">2.75898098945618</t>
   </si>
   <si>
     <t xml:space="preserve">2.68361520767212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6703155040741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66440439224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64519333839417</t>
+    <t xml:space="preserve">2.67031526565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66440415382385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64519357681274</t>
   </si>
   <si>
     <t xml:space="preserve">2.68065977096558</t>
@@ -3092,28 +3092,28 @@
     <t xml:space="preserve">2.68213748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62598252296448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65849328041077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72055912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85651302337646</t>
+    <t xml:space="preserve">2.6259822845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65849351882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7205593585968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85651326179504</t>
   </si>
   <si>
     <t xml:space="preserve">2.92301273345947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90380191802979</t>
+    <t xml:space="preserve">2.90380167961121</t>
   </si>
   <si>
     <t xml:space="preserve">2.90084624290466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98064517974854</t>
+    <t xml:space="preserve">2.98064541816711</t>
   </si>
   <si>
     <t xml:space="preserve">3.01463389396667</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">3.03975582122803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07374405860901</t>
+    <t xml:space="preserve">3.07374429702759</t>
   </si>
   <si>
     <t xml:space="preserve">3.11807727813721</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">3.06044459342957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0235002040863</t>
+    <t xml:space="preserve">3.02350044250488</t>
   </si>
   <si>
     <t xml:space="preserve">3.02941131591797</t>
@@ -3143,124 +3143,124 @@
     <t xml:space="preserve">2.86390209197998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90675711631775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8712911605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83434677124023</t>
+    <t xml:space="preserve">2.90675735473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87129068374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83434700965881</t>
   </si>
   <si>
     <t xml:space="preserve">2.91710162162781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04714488983154</t>
+    <t xml:space="preserve">3.04714465141296</t>
   </si>
   <si>
     <t xml:space="preserve">3.1328547000885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10034394264221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1771879196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10625505447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13581013679504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08408856391907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00133395195007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94517922401428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9998562335968</t>
+    <t xml:space="preserve">3.10034418106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17718768119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1062548160553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13581037521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08408832550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00133371353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9451789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99985599517822</t>
   </si>
   <si>
     <t xml:space="preserve">2.97177863121033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93926787376404</t>
+    <t xml:space="preserve">2.9392683506012</t>
   </si>
   <si>
     <t xml:space="preserve">3.08999991416931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.091477394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07669973373413</t>
+    <t xml:space="preserve">3.09147763252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07670021057129</t>
   </si>
   <si>
     <t xml:space="preserve">3.08704423904419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08852195739746</t>
+    <t xml:space="preserve">3.08852171897888</t>
   </si>
   <si>
     <t xml:space="preserve">3.12694358825684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24664258956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20526480674744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21856498718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33235287666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33826398849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34121894836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31166410446167</t>
+    <t xml:space="preserve">3.24664235115051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20526528358459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21856474876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33235263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33826375007629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34121942520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31166386604309</t>
   </si>
   <si>
     <t xml:space="preserve">3.26142024993896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32496356964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30131983757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29245328903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28801965713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31609702110291</t>
+    <t xml:space="preserve">3.32496404647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30131959915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2924530506134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28801941871643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31609725952148</t>
   </si>
   <si>
     <t xml:space="preserve">3.29393100738525</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27324175834656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24516487121582</t>
+    <t xml:space="preserve">3.27324199676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2451651096344</t>
   </si>
   <si>
     <t xml:space="preserve">3.32274746894836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30649161338806</t>
+    <t xml:space="preserve">3.30649185180664</t>
   </si>
   <si>
     <t xml:space="preserve">3.3101863861084</t>
@@ -3272,16 +3272,16 @@
     <t xml:space="preserve">3.25107574462891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2835865020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28654217720032</t>
+    <t xml:space="preserve">3.28358626365662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28654193878174</t>
   </si>
   <si>
     <t xml:space="preserve">3.27915358543396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24073147773743</t>
+    <t xml:space="preserve">3.24073123931885</t>
   </si>
   <si>
     <t xml:space="preserve">3.27767539024353</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">3.28136944770813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18531560897827</t>
+    <t xml:space="preserve">3.18531513214111</t>
   </si>
   <si>
     <t xml:space="preserve">3.13433265686035</t>
@@ -3308,25 +3308,25 @@
     <t xml:space="preserve">3.17940425872803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09664964675903</t>
+    <t xml:space="preserve">3.09664940834045</t>
   </si>
   <si>
     <t xml:space="preserve">3.15354347229004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13654923439026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21043705940247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26511478424072</t>
+    <t xml:space="preserve">3.1365487575531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21043729782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26511454582214</t>
   </si>
   <si>
     <t xml:space="preserve">3.2274317741394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.239253282547</t>
+    <t xml:space="preserve">3.23925375938416</t>
   </si>
   <si>
     <t xml:space="preserve">3.24738121032715</t>
@@ -3338,22 +3338,22 @@
     <t xml:space="preserve">3.33974123001099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41362905502319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32053065299988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32939720153809</t>
+    <t xml:space="preserve">3.41362953186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32053017616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32939696311951</t>
   </si>
   <si>
     <t xml:space="preserve">3.31535816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38761711120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31846594810486</t>
+    <t xml:space="preserve">3.38761758804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31846618652344</t>
   </si>
   <si>
     <t xml:space="preserve">3.33789086341858</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">3.37751650810242</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40471076965332</t>
+    <t xml:space="preserve">3.4047110080719</t>
   </si>
   <si>
     <t xml:space="preserve">3.60206270217896</t>
@@ -3386,37 +3386,37 @@
     <t xml:space="preserve">3.57098364830017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55855178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52203392982483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51037979125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4420051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47619223594666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4497754573822</t>
+    <t xml:space="preserve">3.55855202674866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52203416824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51037955284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44200539588928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47619247436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44977521896362</t>
   </si>
   <si>
     <t xml:space="preserve">3.38917112350464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34022164344788</t>
+    <t xml:space="preserve">3.3402214050293</t>
   </si>
   <si>
     <t xml:space="preserve">3.32545924186707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34876847267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27417898178101</t>
+    <t xml:space="preserve">3.34876823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27417874336243</t>
   </si>
   <si>
     <t xml:space="preserve">3.2990415096283</t>
@@ -3425,55 +3425,55 @@
     <t xml:space="preserve">3.25630807876587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26407814025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24776148796082</t>
+    <t xml:space="preserve">3.26407790184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24776124954224</t>
   </si>
   <si>
     <t xml:space="preserve">3.2788405418396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25786209106445</t>
+    <t xml:space="preserve">3.25786185264587</t>
   </si>
   <si>
     <t xml:space="preserve">3.24076867103577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19337320327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25009226799011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28738737106323</t>
+    <t xml:space="preserve">3.19337344169617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25009250640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28738713264465</t>
   </si>
   <si>
     <t xml:space="preserve">3.27184772491455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24620771408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20580458641052</t>
+    <t xml:space="preserve">3.24620747566223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2058048248291</t>
   </si>
   <si>
     <t xml:space="preserve">3.16540193557739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02632331848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03098511695862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09158897399902</t>
+    <t xml:space="preserve">3.02632308006287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03098487854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0915892124176</t>
   </si>
   <si>
     <t xml:space="preserve">3.11956024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18016457557678</t>
+    <t xml:space="preserve">3.1801643371582</t>
   </si>
   <si>
     <t xml:space="preserve">3.22678303718567</t>
@@ -3485,70 +3485,70 @@
     <t xml:space="preserve">3.21202039718628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22989130020142</t>
+    <t xml:space="preserve">3.22989106178284</t>
   </si>
   <si>
     <t xml:space="preserve">3.23066782951355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31458115577698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23299860954285</t>
+    <t xml:space="preserve">3.31458139419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23299884796143</t>
   </si>
   <si>
     <t xml:space="preserve">3.28894090652466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30370354652405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37907028198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33556008338928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38606286048889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33245182037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31302738189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33478260040283</t>
+    <t xml:space="preserve">3.30370378494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.379070520401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3355598449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38606309890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33245205879211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31302762031555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33478236198425</t>
   </si>
   <si>
     <t xml:space="preserve">3.36120009422302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3495454788208</t>
+    <t xml:space="preserve">3.34954524040222</t>
   </si>
   <si>
     <t xml:space="preserve">3.36819291114807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3650848865509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39227938652039</t>
+    <t xml:space="preserve">3.36508464813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39227914810181</t>
   </si>
   <si>
     <t xml:space="preserve">3.41248083114624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37207770347595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39150214195251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39849472045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35032200813293</t>
+    <t xml:space="preserve">3.37207794189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39150190353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39849495887756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35032224655151</t>
   </si>
   <si>
     <t xml:space="preserve">3.3534300327301</t>
@@ -3557,34 +3557,34 @@
     <t xml:space="preserve">3.31535863876343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3472146987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32157421112061</t>
+    <t xml:space="preserve">3.34721446037292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32157444953918</t>
   </si>
   <si>
     <t xml:space="preserve">3.33089804649353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32312846183777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28971815109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18715763092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19725775718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2928261756897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28661012649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22056722640991</t>
+    <t xml:space="preserve">3.32312798500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28971838951111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18715739250183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19725751876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29282593727112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28661036491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22056746482849</t>
   </si>
   <si>
     <t xml:space="preserve">3.21745944023132</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">3.21279764175415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20891261100769</t>
+    <t xml:space="preserve">3.20891284942627</t>
   </si>
   <si>
     <t xml:space="preserve">3.17627954483032</t>
@@ -3602,22 +3602,22 @@
     <t xml:space="preserve">3.30758857727051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33012104034424</t>
+    <t xml:space="preserve">3.33012080192566</t>
   </si>
   <si>
     <t xml:space="preserve">3.36741590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39461016654968</t>
+    <t xml:space="preserve">3.39460968971252</t>
   </si>
   <si>
     <t xml:space="preserve">3.32623624801636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43268179893494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45443725585938</t>
+    <t xml:space="preserve">3.43268203735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45443749427795</t>
   </si>
   <si>
     <t xml:space="preserve">3.48085451126099</t>
@@ -3629,76 +3629,76 @@
     <t xml:space="preserve">3.61682558059692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5779767036438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58652329444885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58963084220886</t>
+    <t xml:space="preserve">3.57797646522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58652353286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58963108062744</t>
   </si>
   <si>
     <t xml:space="preserve">3.5958468914032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57176089286804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57642245292664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.566321849823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58108448982239</t>
+    <t xml:space="preserve">3.57176065444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57642221450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56632208824158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58108496665955</t>
   </si>
   <si>
     <t xml:space="preserve">3.68753004074097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63469529151917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65178894996643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64246582984924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6207103729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62692618370056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62148714065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61294031143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61060905456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57409143447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50260949134827</t>
+    <t xml:space="preserve">3.63469576835632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65178918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64246559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62071013450623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62692594528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62148666381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61294007301331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61060929298401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57409167289734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50260996818542</t>
   </si>
   <si>
     <t xml:space="preserve">3.4482216835022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45132899284363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39694094657898</t>
+    <t xml:space="preserve">3.45132923126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39694118499756</t>
   </si>
   <si>
     <t xml:space="preserve">3.39538669586182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26330065727234</t>
+    <t xml:space="preserve">3.26330089569092</t>
   </si>
   <si>
     <t xml:space="preserve">3.22833728790283</t>
@@ -3710,31 +3710,31 @@
     <t xml:space="preserve">3.40004897117615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33711361885071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3658618927002</t>
+    <t xml:space="preserve">3.33711385726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36586141586304</t>
   </si>
   <si>
     <t xml:space="preserve">3.37363171577454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41791939735413</t>
+    <t xml:space="preserve">3.41791963577271</t>
   </si>
   <si>
     <t xml:space="preserve">3.4365668296814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31380462646484</t>
+    <t xml:space="preserve">3.31380438804626</t>
   </si>
   <si>
     <t xml:space="preserve">3.42025017738342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42957401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48163151741028</t>
+    <t xml:space="preserve">3.42957425117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4816312789917</t>
   </si>
   <si>
     <t xml:space="preserve">3.49717092514038</t>
@@ -3743,55 +3743,55 @@
     <t xml:space="preserve">3.48707008361816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48862433433533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51814889907837</t>
+    <t xml:space="preserve">3.48862409591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51814913749695</t>
   </si>
   <si>
     <t xml:space="preserve">3.54145860671997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52436518669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48551630973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49794793128967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64635014533997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70151567459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69607663154602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64712738990784</t>
+    <t xml:space="preserve">3.52436494827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48551607131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49794745445251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64635038375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70151591300964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69607710838318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64712715148926</t>
   </si>
   <si>
     <t xml:space="preserve">3.65567374229431</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56865286827087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52824974060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49639368057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35420680046082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40237998962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41092658042908</t>
+    <t xml:space="preserve">3.56865262985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52824997901917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49639415740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35420727729797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40237975120544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4109263420105</t>
   </si>
   <si>
     <t xml:space="preserve">3.41558814048767</t>
@@ -3809,52 +3809,52 @@
     <t xml:space="preserve">3.47075390815735</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45366024971008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54301261901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56321382522583</t>
+    <t xml:space="preserve">3.45366048812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54301238059998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56321406364441</t>
   </si>
   <si>
     <t xml:space="preserve">3.75978899002075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62614870071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79708385467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75124216079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65878248214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66188979148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54612064361572</t>
+    <t xml:space="preserve">3.62614893913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79708409309387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75124192237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65878224372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66188955307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54612040519714</t>
   </si>
   <si>
     <t xml:space="preserve">3.55622124671936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38373255729675</t>
+    <t xml:space="preserve">3.38373231887817</t>
   </si>
   <si>
     <t xml:space="preserve">3.42258143424988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16384816169739</t>
+    <t xml:space="preserve">3.16384792327881</t>
   </si>
   <si>
     <t xml:space="preserve">3.06361818313599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87481284141541</t>
+    <t xml:space="preserve">2.87481260299683</t>
   </si>
   <si>
     <t xml:space="preserve">2.63395023345947</t>
@@ -3863,28 +3863,28 @@
     <t xml:space="preserve">2.59898638725281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64715886116028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83751773834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7450578212738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82042455673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93308591842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91366171836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0783805847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05118656158447</t>
+    <t xml:space="preserve">2.6471586227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83751797676086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74505758285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8204243183136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93308615684509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91366147994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07838034629822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05118680000305</t>
   </si>
   <si>
     <t xml:space="preserve">3.05895614624023</t>
@@ -3896,13 +3896,13 @@
     <t xml:space="preserve">3.1622941493988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14131569862366</t>
+    <t xml:space="preserve">3.14131593704224</t>
   </si>
   <si>
     <t xml:space="preserve">3.10246682167053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09780526161194</t>
+    <t xml:space="preserve">3.09780502319336</t>
   </si>
   <si>
     <t xml:space="preserve">3.13199210166931</t>
@@ -3911,13 +3911,13 @@
     <t xml:space="preserve">3.23843789100647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24853873252869</t>
+    <t xml:space="preserve">3.24853849411011</t>
   </si>
   <si>
     <t xml:space="preserve">3.17161750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20269703865051</t>
+    <t xml:space="preserve">3.20269727706909</t>
   </si>
   <si>
     <t xml:space="preserve">3.09236621856689</t>
@@ -3926,43 +3926,43 @@
     <t xml:space="preserve">3.35498404502869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36275386810303</t>
+    <t xml:space="preserve">3.36275410652161</t>
   </si>
   <si>
     <t xml:space="preserve">3.37984728813171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40937256813049</t>
+    <t xml:space="preserve">3.40937232971191</t>
   </si>
   <si>
     <t xml:space="preserve">3.42335820198059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53058075904846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59273910522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51970338821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52747297286987</t>
+    <t xml:space="preserve">3.53058123588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59273934364319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51970314979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52747273445129</t>
   </si>
   <si>
     <t xml:space="preserve">3.59740114212036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61138582229614</t>
+    <t xml:space="preserve">3.6113862991333</t>
   </si>
   <si>
     <t xml:space="preserve">3.6937460899353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63624954223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60983204841614</t>
+    <t xml:space="preserve">3.63624906539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6098325252533</t>
   </si>
   <si>
     <t xml:space="preserve">3.36430788040161</t>
@@ -3980,52 +3980,52 @@
     <t xml:space="preserve">3.51659536361694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53524303436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5507824420929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56942963600159</t>
+    <t xml:space="preserve">3.53524279594421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55078220367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56942987442017</t>
   </si>
   <si>
     <t xml:space="preserve">3.51193332672119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6394898891449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63783311843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65771198272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71403551101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70740866661072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7587628364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71569228172302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64611625671387</t>
+    <t xml:space="preserve">3.63948965072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6378333568573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65771174430847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71403574943542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70740914344788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75876307487488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71569180488586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64611577987671</t>
   </si>
   <si>
     <t xml:space="preserve">3.64942908287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59310531616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59807515144348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48377180099487</t>
+    <t xml:space="preserve">3.59310579299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59807538986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48377156257629</t>
   </si>
   <si>
     <t xml:space="preserve">3.38272094726562</t>
@@ -4037,13 +4037,13 @@
     <t xml:space="preserve">2.97686076164246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01993155479431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08288097381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97520399093628</t>
+    <t xml:space="preserve">3.01993131637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0828812122345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97520422935486</t>
   </si>
   <si>
     <t xml:space="preserve">2.96692132949829</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">3.01330518722534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98514366149902</t>
+    <t xml:space="preserve">2.98514342308044</t>
   </si>
   <si>
     <t xml:space="preserve">3.00005269050598</t>
@@ -4073,16 +4073,16 @@
     <t xml:space="preserve">3.00999212265015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89734530448914</t>
+    <t xml:space="preserve">2.89734506607056</t>
   </si>
   <si>
     <t xml:space="preserve">2.90397143363953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90065860748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69689989089966</t>
+    <t xml:space="preserve">2.90065836906433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69690012931824</t>
   </si>
   <si>
     <t xml:space="preserve">2.6587986946106</t>
@@ -4094,7 +4094,7 @@
     <t xml:space="preserve">2.80457711219788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71512222290039</t>
+    <t xml:space="preserve">2.71512246131897</t>
   </si>
   <si>
     <t xml:space="preserve">2.70683932304382</t>
@@ -4103,7 +4103,7 @@
     <t xml:space="preserve">2.69193005561829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52792978286743</t>
+    <t xml:space="preserve">2.52792954444885</t>
   </si>
   <si>
     <t xml:space="preserve">2.64885926246643</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">2.81120347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78138518333435</t>
+    <t xml:space="preserve">2.78138494491577</t>
   </si>
   <si>
     <t xml:space="preserve">2.79132437705994</t>
@@ -4127,22 +4127,22 @@
     <t xml:space="preserve">2.76813244819641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71843528747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71677875518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77475881576538</t>
+    <t xml:space="preserve">2.71843552589417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71677851676941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7747585773468</t>
   </si>
   <si>
     <t xml:space="preserve">2.83108234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83770847320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84599161148071</t>
+    <t xml:space="preserve">2.83770871162415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84599137306213</t>
   </si>
   <si>
     <t xml:space="preserve">2.92385029792786</t>
@@ -4151,7 +4151,7 @@
     <t xml:space="preserve">2.97354745864868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95035552978516</t>
+    <t xml:space="preserve">2.95035576820374</t>
   </si>
   <si>
     <t xml:space="preserve">2.91225433349609</t>
@@ -4163,28 +4163,28 @@
     <t xml:space="preserve">2.93047666549683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98183035850525</t>
+    <t xml:space="preserve">2.98183012008667</t>
   </si>
   <si>
     <t xml:space="preserve">2.98017382621765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92219376564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9354465007782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8542742729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75984978675842</t>
+    <t xml:space="preserve">2.92219400405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93544626235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85427451133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75984954833984</t>
   </si>
   <si>
     <t xml:space="preserve">2.79960751533508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78469824790955</t>
+    <t xml:space="preserve">2.78469800949097</t>
   </si>
   <si>
     <t xml:space="preserve">2.8277690410614</t>
@@ -4199,10 +4199,10 @@
     <t xml:space="preserve">2.68696045875549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69358682632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64223289489746</t>
+    <t xml:space="preserve">2.69358706474304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64223313331604</t>
   </si>
   <si>
     <t xml:space="preserve">2.68199062347412</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">2.73168802261353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83439517021179</t>
+    <t xml:space="preserve">2.83439540863037</t>
   </si>
   <si>
     <t xml:space="preserve">2.79629421234131</t>
@@ -4220,25 +4220,25 @@
     <t xml:space="preserve">2.76150631904602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68033409118652</t>
+    <t xml:space="preserve">2.6803343296051</t>
   </si>
   <si>
     <t xml:space="preserve">2.71015238761902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61738467216492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59419226646423</t>
+    <t xml:space="preserve">2.61738443374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59419250488281</t>
   </si>
   <si>
     <t xml:space="preserve">2.57762670516968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51798987388611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53621244430542</t>
+    <t xml:space="preserve">2.51799011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.536212682724</t>
   </si>
   <si>
     <t xml:space="preserve">2.46663618087769</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">2.44344449043274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37221169471741</t>
+    <t xml:space="preserve">2.37221193313599</t>
   </si>
   <si>
     <t xml:space="preserve">2.4268786907196</t>
@@ -4256,55 +4256,55 @@
     <t xml:space="preserve">2.65051603317261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67702102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58259630203247</t>
+    <t xml:space="preserve">2.67702126502991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58259654045105</t>
   </si>
   <si>
     <t xml:space="preserve">2.54780840873718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53124284744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52461647987366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42190885543823</t>
+    <t xml:space="preserve">2.53124260902405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52461624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42190909385681</t>
   </si>
   <si>
     <t xml:space="preserve">2.48651528358459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48154544830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54118204116821</t>
+    <t xml:space="preserve">2.4815456867218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54118227958679</t>
   </si>
   <si>
     <t xml:space="preserve">2.57100057601929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53952527046204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52295970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48817181587219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59750556945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62235403060913</t>
+    <t xml:space="preserve">2.53952574729919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52295994758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48817157745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59750533103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62235426902771</t>
   </si>
   <si>
     <t xml:space="preserve">2.60413193702698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61407136917114</t>
+    <t xml:space="preserve">2.61407113075256</t>
   </si>
   <si>
     <t xml:space="preserve">2.61075806617737</t>
@@ -4313,16 +4313,16 @@
     <t xml:space="preserve">2.61572790145874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68861722946167</t>
+    <t xml:space="preserve">2.68861699104309</t>
   </si>
   <si>
     <t xml:space="preserve">2.84930443763733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86587047576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95366859436035</t>
+    <t xml:space="preserve">2.86587023735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95366883277893</t>
   </si>
   <si>
     <t xml:space="preserve">2.9983959197998</t>
@@ -4331,25 +4331,25 @@
     <t xml:space="preserve">2.99342632293701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03152775764465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98680019378662</t>
+    <t xml:space="preserve">3.03152751922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98679995536804</t>
   </si>
   <si>
     <t xml:space="preserve">3.00170922279358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00833535194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98348712921143</t>
+    <t xml:space="preserve">3.00833559036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98348689079285</t>
   </si>
   <si>
     <t xml:space="preserve">3.00336575508118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03484058380127</t>
+    <t xml:space="preserve">3.03484082221985</t>
   </si>
   <si>
     <t xml:space="preserve">3.06631541252136</t>
@@ -4361,16 +4361,16 @@
     <t xml:space="preserve">3.10441660881042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08619451522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94869899749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91722416877747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86255741119385</t>
+    <t xml:space="preserve">3.08619475364685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94869875907898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91722393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86255717277527</t>
   </si>
   <si>
     <t xml:space="preserve">2.89900183677673</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">2.99176979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99673938751221</t>
+    <t xml:space="preserve">2.99673962593079</t>
   </si>
   <si>
     <t xml:space="preserve">3.03649711608887</t>
@@ -4388,16 +4388,16 @@
     <t xml:space="preserve">3.01496195793152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07791137695312</t>
+    <t xml:space="preserve">3.0779116153717</t>
   </si>
   <si>
     <t xml:space="preserve">3.09944701194763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13754820823669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19055867195129</t>
+    <t xml:space="preserve">3.13754844665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19055843353271</t>
   </si>
   <si>
     <t xml:space="preserve">3.16736626625061</t>
@@ -4406,22 +4406,22 @@
     <t xml:space="preserve">3.21375060081482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2518515586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22865986824036</t>
+    <t xml:space="preserve">3.25185179710388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22865962982178</t>
   </si>
   <si>
     <t xml:space="preserve">3.22534656524658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26013469696045</t>
+    <t xml:space="preserve">3.26013445854187</t>
   </si>
   <si>
     <t xml:space="preserve">3.23031640052795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2021541595459</t>
+    <t xml:space="preserve">3.20215439796448</t>
   </si>
   <si>
     <t xml:space="preserve">3.20546746253967</t>
@@ -4439,37 +4439,37 @@
     <t xml:space="preserve">3.29657912254333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34627628326416</t>
+    <t xml:space="preserve">3.34627652168274</t>
   </si>
   <si>
     <t xml:space="preserve">3.32805395126343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34793281555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37443804740906</t>
+    <t xml:space="preserve">3.34793257713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37443780899048</t>
   </si>
   <si>
     <t xml:space="preserve">3.43904447555542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44235777854919</t>
+    <t xml:space="preserve">3.44235754013062</t>
   </si>
   <si>
     <t xml:space="preserve">3.29160928726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29492235183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31811475753784</t>
+    <t xml:space="preserve">3.29492259025574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31811451911926</t>
   </si>
   <si>
     <t xml:space="preserve">3.25516486167908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35124611854553</t>
+    <t xml:space="preserve">3.35124588012695</t>
   </si>
   <si>
     <t xml:space="preserve">3.45395350456238</t>
@@ -4478,10 +4478,10 @@
     <t xml:space="preserve">3.4506402015686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49536752700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43573093414307</t>
+    <t xml:space="preserve">3.49536776542664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43573117256165</t>
   </si>
   <si>
     <t xml:space="preserve">3.38437747955322</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">3.31480145454407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40922594070435</t>
+    <t xml:space="preserve">3.40922617912292</t>
   </si>
   <si>
     <t xml:space="preserve">3.34958958625793</t>
@@ -4502,10 +4502,10 @@
     <t xml:space="preserve">3.387690782547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39266037940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41088247299194</t>
+    <t xml:space="preserve">3.39266061782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41088271141052</t>
   </si>
   <si>
     <t xml:space="preserve">3.42082214355469</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">3.42247867584229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37609457969666</t>
+    <t xml:space="preserve">3.37609481811523</t>
   </si>
   <si>
     <t xml:space="preserve">3.37775111198425</t>
@@ -4523,25 +4523,25 @@
     <t xml:space="preserve">3.34130644798279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10276031494141</t>
+    <t xml:space="preserve">3.10276007652283</t>
   </si>
   <si>
     <t xml:space="preserve">3.13092184066772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02324485778809</t>
+    <t xml:space="preserve">3.02324461936951</t>
   </si>
   <si>
     <t xml:space="preserve">3.07625508308411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17399287223816</t>
+    <t xml:space="preserve">3.17399263381958</t>
   </si>
   <si>
     <t xml:space="preserve">3.13423490524292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1060733795166</t>
+    <t xml:space="preserve">3.10607314109802</t>
   </si>
   <si>
     <t xml:space="preserve">3.01164865493774</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">3.06465911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1093864440918</t>
+    <t xml:space="preserve">3.10938620567322</t>
   </si>
   <si>
     <t xml:space="preserve">3.07459831237793</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">3.08453774452209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11269950866699</t>
+    <t xml:space="preserve">3.11269927024841</t>
   </si>
   <si>
     <t xml:space="preserve">3.14748764038086</t>
@@ -4568,19 +4568,19 @@
     <t xml:space="preserve">3.17233610153198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17730593681335</t>
+    <t xml:space="preserve">3.17730569839478</t>
   </si>
   <si>
     <t xml:space="preserve">3.18393230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20381093025208</t>
+    <t xml:space="preserve">3.20381116867065</t>
   </si>
   <si>
     <t xml:space="preserve">3.14914417266846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19387173652649</t>
+    <t xml:space="preserve">3.19387149810791</t>
   </si>
   <si>
     <t xml:space="preserve">3.19718480110168</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">3.17896270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14583134651184</t>
+    <t xml:space="preserve">3.14583110809326</t>
   </si>
   <si>
     <t xml:space="preserve">3.09779047966003</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">3.11932587623596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04146695137024</t>
+    <t xml:space="preserve">3.04146671295166</t>
   </si>
   <si>
     <t xml:space="preserve">3.07294201850891</t>
@@ -4610,28 +4610,28 @@
     <t xml:space="preserve">3.08785080909729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05306315422058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04974961280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10612869262695</t>
+    <t xml:space="preserve">3.053062915802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04974985122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10612893104553</t>
   </si>
   <si>
     <t xml:space="preserve">3.05855894088745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96165776252747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9440393447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97751426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93523025512695</t>
+    <t xml:space="preserve">2.96165752410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94403910636902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97751450538635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93523001670837</t>
   </si>
   <si>
     <t xml:space="preserve">2.90351676940918</t>
@@ -4652,7 +4652,7 @@
     <t xml:space="preserve">2.99513268470764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99689435958862</t>
+    <t xml:space="preserve">2.9968945980072</t>
   </si>
   <si>
     <t xml:space="preserve">3.03741693496704</t>
@@ -4664,7 +4664,7 @@
     <t xml:space="preserve">3.0286078453064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03213119506836</t>
+    <t xml:space="preserve">3.03213143348694</t>
   </si>
   <si>
     <t xml:space="preserve">3.06736826896667</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">3.03565526008606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99865651130676</t>
+    <t xml:space="preserve">2.99865627288818</t>
   </si>
   <si>
     <t xml:space="preserve">2.97575235366821</t>
@@ -4691,7 +4691,7 @@
     <t xml:space="preserve">2.90880250930786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88942217826843</t>
+    <t xml:space="preserve">2.88942193984985</t>
   </si>
   <si>
     <t xml:space="preserve">2.92994451522827</t>
@@ -4712,10 +4712,10 @@
     <t xml:space="preserve">2.86299443244934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88413643836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95284867286682</t>
+    <t xml:space="preserve">2.88413667678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95284843444824</t>
   </si>
   <si>
     <t xml:space="preserve">2.9916090965271</t>
@@ -4736,13 +4736,13 @@
     <t xml:space="preserve">2.93170642852783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00922751426697</t>
+    <t xml:space="preserve">3.00922727584839</t>
   </si>
   <si>
     <t xml:space="preserve">3.11317610740662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12198543548584</t>
+    <t xml:space="preserve">3.12198519706726</t>
   </si>
   <si>
     <t xml:space="preserve">3.08851027488708</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">3.25764727592468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32812094688416</t>
+    <t xml:space="preserve">3.32812118530273</t>
   </si>
   <si>
     <t xml:space="preserve">3.32635927200317</t>
@@ -4778,34 +4778,34 @@
     <t xml:space="preserve">3.2840747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22945785522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23121976852417</t>
+    <t xml:space="preserve">3.22945761680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23121953010559</t>
   </si>
   <si>
     <t xml:space="preserve">3.20655393600464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21712470054626</t>
+    <t xml:space="preserve">3.21712493896484</t>
   </si>
   <si>
     <t xml:space="preserve">3.22593402862549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25412344932556</t>
+    <t xml:space="preserve">3.25412368774414</t>
   </si>
   <si>
     <t xml:space="preserve">3.27526569366455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29112219810486</t>
+    <t xml:space="preserve">3.29112243652344</t>
   </si>
   <si>
     <t xml:space="preserve">3.34397768974304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.347501039505</t>
+    <t xml:space="preserve">3.34750127792358</t>
   </si>
   <si>
     <t xml:space="preserve">3.3774528503418</t>
@@ -4820,7 +4820,7 @@
     <t xml:space="preserve">3.29816961288452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32988262176514</t>
+    <t xml:space="preserve">3.32988286018372</t>
   </si>
   <si>
     <t xml:space="preserve">3.39330911636353</t>
@@ -4859,25 +4859,25 @@
     <t xml:space="preserve">3.53954219818115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51487612724304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47083044052124</t>
+    <t xml:space="preserve">3.51487636566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47083020210266</t>
   </si>
   <si>
     <t xml:space="preserve">3.49725794792175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.463782787323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43735527992249</t>
+    <t xml:space="preserve">3.46378302574158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43735504150391</t>
   </si>
   <si>
     <t xml:space="preserve">3.42502236366272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52897119522095</t>
+    <t xml:space="preserve">3.52897095680237</t>
   </si>
   <si>
     <t xml:space="preserve">3.54130387306213</t>
@@ -4892,16 +4892,16 @@
     <t xml:space="preserve">3.48316311836243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4214985370636</t>
+    <t xml:space="preserve">3.42149877548218</t>
   </si>
   <si>
     <t xml:space="preserve">3.4355936050415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39507102966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36159610748291</t>
+    <t xml:space="preserve">3.39507126808167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36159586906433</t>
   </si>
   <si>
     <t xml:space="preserve">3.37569069862366</t>
@@ -4913,13 +4913,13 @@
     <t xml:space="preserve">3.37216711044312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39683294296265</t>
+    <t xml:space="preserve">3.39683270454407</t>
   </si>
   <si>
     <t xml:space="preserve">3.35278677940369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40388011932373</t>
+    <t xml:space="preserve">3.40388035774231</t>
   </si>
   <si>
     <t xml:space="preserve">3.58535027503967</t>
@@ -4931,25 +4931,25 @@
     <t xml:space="preserve">3.53778004646301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45145010948181</t>
+    <t xml:space="preserve">3.45144987106323</t>
   </si>
   <si>
     <t xml:space="preserve">3.5624463558197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54306578636169</t>
+    <t xml:space="preserve">3.54306554794312</t>
   </si>
   <si>
     <t xml:space="preserve">3.58182644844055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58711194992065</t>
+    <t xml:space="preserve">3.58711171150208</t>
   </si>
   <si>
     <t xml:space="preserve">3.55716061592102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51839995384216</t>
+    <t xml:space="preserve">3.51840019226074</t>
   </si>
   <si>
     <t xml:space="preserve">3.46730661392212</t>
@@ -4958,7 +4958,7 @@
     <t xml:space="preserve">3.4690682888031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41621327400208</t>
+    <t xml:space="preserve">3.4162130355835</t>
   </si>
   <si>
     <t xml:space="preserve">3.40211844444275</t>
@@ -4970,10 +4970,10 @@
     <t xml:space="preserve">3.45497369766235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43383169174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4584972858429</t>
+    <t xml:space="preserve">3.43383145332336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45849752426147</t>
   </si>
   <si>
     <t xml:space="preserve">3.42678427696228</t>
@@ -4997,10 +4997,10 @@
     <t xml:space="preserve">3.5677318572998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56420803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55187487602234</t>
+    <t xml:space="preserve">3.5642077922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55187511444092</t>
   </si>
   <si>
     <t xml:space="preserve">3.46554470062256</t>
@@ -5012,7 +5012,7 @@
     <t xml:space="preserve">3.47611594200134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.558922290802</t>
+    <t xml:space="preserve">3.55892252922058</t>
   </si>
   <si>
     <t xml:space="preserve">3.5536367893219</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">3.57301735877991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57654070854187</t>
+    <t xml:space="preserve">3.57654094696045</t>
   </si>
   <si>
     <t xml:space="preserve">3.5483512878418</t>
@@ -5039,7 +5039,7 @@
     <t xml:space="preserve">3.73510646820068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69986963272095</t>
+    <t xml:space="preserve">3.69986987113953</t>
   </si>
   <si>
     <t xml:space="preserve">3.80029511451721</t>
@@ -5048,7 +5048,7 @@
     <t xml:space="preserve">3.72277355194092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71396470069885</t>
+    <t xml:space="preserve">3.71396446228027</t>
   </si>
   <si>
     <t xml:space="preserve">3.66815662384033</t>
@@ -5060,7 +5060,7 @@
     <t xml:space="preserve">3.69458413124084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78796219825745</t>
+    <t xml:space="preserve">3.78796195983887</t>
   </si>
   <si>
     <t xml:space="preserve">3.77210545539856</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">3.64701437950134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70867896080017</t>
+    <t xml:space="preserve">3.70867919921875</t>
   </si>
   <si>
     <t xml:space="preserve">3.64172887802124</t>
@@ -5102,79 +5102,79 @@
     <t xml:space="preserve">3.71220302581787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6857750415802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67168045043945</t>
+    <t xml:space="preserve">3.68577527999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67168068885803</t>
   </si>
   <si>
     <t xml:space="preserve">3.65229988098145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65582394599915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71748805046082</t>
+    <t xml:space="preserve">3.65582370758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71748828887939</t>
   </si>
   <si>
     <t xml:space="preserve">3.69634628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63468146324158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62587237358093</t>
+    <t xml:space="preserve">3.63468170166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62587261199951</t>
   </si>
   <si>
     <t xml:space="preserve">3.70163178443909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72453570365906</t>
+    <t xml:space="preserve">3.72453594207764</t>
   </si>
   <si>
     <t xml:space="preserve">3.72982144355774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76858162879944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81615138053894</t>
+    <t xml:space="preserve">3.76858139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81615114212036</t>
   </si>
   <si>
     <t xml:space="preserve">3.81967520713806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88133955001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85138869285583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83905553817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87781620025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87605428695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84610271453857</t>
+    <t xml:space="preserve">3.88133978843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85138845443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83905529975891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87781572341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87605404853821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84610295295715</t>
   </si>
   <si>
     <t xml:space="preserve">3.89895820617676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82672214508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77915263175964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80205678939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76329588890076</t>
+    <t xml:space="preserve">3.82672262191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77915287017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80205655097961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76329612731934</t>
   </si>
   <si>
     <t xml:space="preserve">3.74920153617859</t>
@@ -5183,28 +5183,28 @@
     <t xml:space="preserve">3.74039196968079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67344236373901</t>
+    <t xml:space="preserve">3.67344212532043</t>
   </si>
   <si>
     <t xml:space="preserve">3.73158311843872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8584361076355</t>
+    <t xml:space="preserve">3.85843563079834</t>
   </si>
   <si>
     <t xml:space="preserve">3.82496070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81086587905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88662552833557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91833829879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90071964263916</t>
+    <t xml:space="preserve">3.81086611747742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88662528991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91833806037903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90071988105774</t>
   </si>
   <si>
     <t xml:space="preserve">4.06633329391479</t>
@@ -71060,7 +71060,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6495601852</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>125949</v>
@@ -71081,6 +71081,32 @@
         <v>1972</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6496296296</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>214544</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>6.11499977111816</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>6.05499982833862</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>6.1100001335144</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>6.07999992370605</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1979</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24674606323242</t>
+    <t xml:space="preserve">4.2467474937439</t>
   </si>
   <si>
     <t xml:space="preserve">ANIM.MI</t>
@@ -50,76 +50,76 @@
     <t xml:space="preserve">4.13419580459595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96948599815369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95301556587219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94203448295593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07380199432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93105459213257</t>
+    <t xml:space="preserve">3.96948647499084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95301604270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94203543663025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07380294799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93105483055115</t>
   </si>
   <si>
     <t xml:space="preserve">3.8267388343811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76085591316223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67850112915039</t>
+    <t xml:space="preserve">3.76085495948792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67850160598755</t>
   </si>
   <si>
     <t xml:space="preserve">3.73889374732971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40398573875427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53300762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76909160614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7937970161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79928731918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88438701629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67575597763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70595216751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6400682926178</t>
+    <t xml:space="preserve">3.40398597717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53300786018372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76909065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79379725456238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79928708076477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88438653945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67575621604919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70595192909241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64006853103638</t>
   </si>
   <si>
     <t xml:space="preserve">3.57967567443848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35731816291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45065331459045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37653470039368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06633234024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95652651786804</t>
+    <t xml:space="preserve">3.35731887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45065259933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3765344619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0663321018219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95652675628662</t>
   </si>
   <si>
     <t xml:space="preserve">3.19535446166992</t>
@@ -128,34 +128,34 @@
     <t xml:space="preserve">2.9839780330658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24202156066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20084428787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48634028434753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38202428817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31065011024475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3875150680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2667281627655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11299967765808</t>
+    <t xml:space="preserve">3.2420220375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20084452629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48633980751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38202452659607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31065058708191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38751482963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26672840118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1129994392395</t>
   </si>
   <si>
     <t xml:space="preserve">3.08554863929749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07182264328003</t>
+    <t xml:space="preserve">3.07182216644287</t>
   </si>
   <si>
     <t xml:space="preserve">3.06084156036377</t>
@@ -167,61 +167,61 @@
     <t xml:space="preserve">3.302414894104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43967247009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3518283367157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28319883346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22280597686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25300288200378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57693028450012</t>
+    <t xml:space="preserve">3.43967294692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35182857513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28319907188416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22280526161194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25300264358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57692980766296</t>
   </si>
   <si>
     <t xml:space="preserve">3.47261476516724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46437978744507</t>
+    <t xml:space="preserve">3.46437954902649</t>
   </si>
   <si>
     <t xml:space="preserve">3.59065628051758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56320428848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61261701583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51653647422791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43418216705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37104415893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45888900756836</t>
+    <t xml:space="preserve">3.56320476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61261653900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51653623580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43418288230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37104344367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45888924598694</t>
   </si>
   <si>
     <t xml:space="preserve">3.53026294708252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32986664772034</t>
+    <t xml:space="preserve">3.32986640930176</t>
   </si>
   <si>
     <t xml:space="preserve">3.27221822738647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09103918075562</t>
+    <t xml:space="preserve">3.09103894233704</t>
   </si>
   <si>
     <t xml:space="preserve">3.23653149604797</t>
@@ -230,25 +230,25 @@
     <t xml:space="preserve">3.34084749221802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28594398498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31888580322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23927712440491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42594647407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41771197319031</t>
+    <t xml:space="preserve">3.28594470024109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31888556480408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23927664756775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4259467124939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41771149635315</t>
   </si>
   <si>
     <t xml:space="preserve">3.4094762802124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41496610641479</t>
+    <t xml:space="preserve">3.41496586799622</t>
   </si>
   <si>
     <t xml:space="preserve">3.44241762161255</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">3.49732041358948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39300513267517</t>
+    <t xml:space="preserve">3.39300537109375</t>
   </si>
   <si>
     <t xml:space="preserve">3.37378931045532</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">3.26123833656311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26947355270386</t>
+    <t xml:space="preserve">3.26947331428528</t>
   </si>
   <si>
     <t xml:space="preserve">3.15417742729187</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">3.16241264343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0196647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94829106330872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82201385498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93182039260864</t>
+    <t xml:space="preserve">3.01966524124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94829082489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82201409339905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93182015419006</t>
   </si>
   <si>
     <t xml:space="preserve">3.0690770149231</t>
@@ -302,64 +302,64 @@
     <t xml:space="preserve">2.91809415817261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87417149543762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85221028327942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89064264297485</t>
+    <t xml:space="preserve">2.8741717338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.852210521698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89064288139343</t>
   </si>
   <si>
     <t xml:space="preserve">2.97133874893188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06356310844421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23648262023926</t>
+    <t xml:space="preserve">3.06356263160706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23648285865784</t>
   </si>
   <si>
     <t xml:space="preserve">3.24224662780762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29988646507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17884278297424</t>
+    <t xml:space="preserve">3.29988622665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17884302139282</t>
   </si>
   <si>
     <t xml:space="preserve">3.15866875648499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04050707817078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97998523712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96269273757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02321481704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00015902519226</t>
+    <t xml:space="preserve">3.04050755500793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97998452186584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96269297599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02321457862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00015926361084</t>
   </si>
   <si>
     <t xml:space="preserve">2.95692849159241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81859278678894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79668974876404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66988158226013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61454725265503</t>
+    <t xml:space="preserve">2.81859302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79668998718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66988205909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61454749107361</t>
   </si>
   <si>
     <t xml:space="preserve">2.54768514633179</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">2.75288367271423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90505337715149</t>
+    <t xml:space="preserve">2.90505313873291</t>
   </si>
   <si>
     <t xml:space="preserve">2.92234468460083</t>
@@ -380,49 +380,49 @@
     <t xml:space="preserve">2.96845674514771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53615665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26179122924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49004507064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41972422599792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42664170265198</t>
+    <t xml:space="preserve">2.53615713119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26179099082947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49004554748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4197244644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42664122581482</t>
   </si>
   <si>
     <t xml:space="preserve">2.49235081672668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36900115013123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28830552101135</t>
+    <t xml:space="preserve">2.36900162696838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28830575942993</t>
   </si>
   <si>
     <t xml:space="preserve">2.29752779006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30559778213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35747337341309</t>
+    <t xml:space="preserve">2.30559754371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35747313499451</t>
   </si>
   <si>
     <t xml:space="preserve">2.43240523338318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.611088514328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59379696846008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68025755882263</t>
+    <t xml:space="preserve">2.61108899116516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59379720687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68025732040405</t>
   </si>
   <si>
     <t xml:space="preserve">2.59725522994995</t>
@@ -434,28 +434,28 @@
     <t xml:space="preserve">2.56958818435669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62838101387024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6226167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5949501991272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61685371398926</t>
+    <t xml:space="preserve">2.62838077545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62261700630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59494972229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6168532371521</t>
   </si>
   <si>
     <t xml:space="preserve">2.54653239250183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63414549827576</t>
+    <t xml:space="preserve">2.63414573669434</t>
   </si>
   <si>
     <t xml:space="preserve">2.58226895332336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40358543395996</t>
+    <t xml:space="preserve">2.4035849571228</t>
   </si>
   <si>
     <t xml:space="preserve">2.41511344909668</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">2.4381697177887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55114388465881</t>
+    <t xml:space="preserve">2.55114364624023</t>
   </si>
   <si>
     <t xml:space="preserve">2.58572769165039</t>
@@ -473,28 +473,28 @@
     <t xml:space="preserve">2.65143728256226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65489506721497</t>
+    <t xml:space="preserve">2.65489530563354</t>
   </si>
   <si>
     <t xml:space="preserve">2.604172706604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54307413101196</t>
+    <t xml:space="preserve">2.54307436943054</t>
   </si>
   <si>
     <t xml:space="preserve">2.41857147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37015414237976</t>
+    <t xml:space="preserve">2.37015390396118</t>
   </si>
   <si>
     <t xml:space="preserve">2.39321041107178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51310133934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5096423625946</t>
+    <t xml:space="preserve">2.51310157775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50964283943176</t>
   </si>
   <si>
     <t xml:space="preserve">2.46122527122498</t>
@@ -503,46 +503,46 @@
     <t xml:space="preserve">2.4485445022583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50733685493469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50157332420349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49696207046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5154070854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53039336204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57304739952087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66181254386902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62722849845886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73789691925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83012080192566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79092574119568</t>
+    <t xml:space="preserve">2.50733709335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50157308578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49696230888367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51540684700012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53039312362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57304692268372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66181230545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62722826004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73789715766907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83012127876282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7909255027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.67449355125427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65604782104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64797854423523</t>
+    <t xml:space="preserve">2.6560480594635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64797902107239</t>
   </si>
   <si>
     <t xml:space="preserve">2.65720105171204</t>
@@ -551,25 +551,25 @@
     <t xml:space="preserve">2.64567351341248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52001810073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51886510848999</t>
+    <t xml:space="preserve">2.52001786231995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51886534690857</t>
   </si>
   <si>
     <t xml:space="preserve">2.49580931663513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52117085456848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52462887763977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54192161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47275328636169</t>
+    <t xml:space="preserve">2.52117109298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52462911605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54192137718201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47275352478027</t>
   </si>
   <si>
     <t xml:space="preserve">2.46929526329041</t>
@@ -587,16 +587,16 @@
     <t xml:space="preserve">2.24795770645142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26524925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32634806632996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3862931728363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44393348693848</t>
+    <t xml:space="preserve">2.26524949073792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3263475894928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38629293441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4439332485199</t>
   </si>
   <si>
     <t xml:space="preserve">2.44623875617981</t>
@@ -605,25 +605,25 @@
     <t xml:space="preserve">2.5707414150238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57996296882629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56267166137695</t>
+    <t xml:space="preserve">2.57996320724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56267142295837</t>
   </si>
   <si>
     <t xml:space="preserve">2.55806064605713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5038788318634</t>
+    <t xml:space="preserve">2.50387835502625</t>
   </si>
   <si>
     <t xml:space="preserve">2.50503158569336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38168239593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60993599891663</t>
+    <t xml:space="preserve">2.38168215751648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60993647575378</t>
   </si>
   <si>
     <t xml:space="preserve">2.59956073760986</t>
@@ -635,70 +635,70 @@
     <t xml:space="preserve">2.70907688140869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67910432815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58111596107483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80130100250244</t>
+    <t xml:space="preserve">2.6791045665741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58111572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8013014793396</t>
   </si>
   <si>
     <t xml:space="preserve">2.81282901763916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7229106426239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78285622596741</t>
+    <t xml:space="preserve">2.72291111946106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78285646438599</t>
   </si>
   <si>
     <t xml:space="preserve">2.82551026344299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92522668838501</t>
+    <t xml:space="preserve">2.92522692680359</t>
   </si>
   <si>
     <t xml:space="preserve">2.96557474136353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91081690788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00592255592346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03474235534668</t>
+    <t xml:space="preserve">2.91081666946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00592303276062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03474283218384</t>
   </si>
   <si>
     <t xml:space="preserve">2.9972767829895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98574829101562</t>
+    <t xml:space="preserve">2.98574876785278</t>
   </si>
   <si>
     <t xml:space="preserve">2.94828271865845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93963670730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97422099113464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99151301383972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01456928253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0318603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16155076026917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13849449157715</t>
+    <t xml:space="preserve">2.93963694572449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97422122955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99151349067688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01456904411316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03186058998108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16155099868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13849472999573</t>
   </si>
   <si>
     <t xml:space="preserve">3.11255693435669</t>
@@ -707,88 +707,88 @@
     <t xml:space="preserve">3.12984848022461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20478081703186</t>
+    <t xml:space="preserve">3.2047803401947</t>
   </si>
   <si>
     <t xml:space="preserve">3.16443204879761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19613480567932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1990168094635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12408518791199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14137625694275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08373665809631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30276894569397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26242065429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1874885559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28547644615173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22783708572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17596006393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24800992012024</t>
+    <t xml:space="preserve">3.19613456726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19901657104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12408494949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14137721061707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08373689651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30276870727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26242089271545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18748903274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28547596931458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22783637046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17596054077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24801015853882</t>
   </si>
   <si>
     <t xml:space="preserve">3.26818418502808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23936438560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09238219261169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10102868080139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05491709709167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08085441589355</t>
+    <t xml:space="preserve">3.23936486244202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09238243103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10102844238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05491662025452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08085417747498</t>
   </si>
   <si>
     <t xml:space="preserve">3.11832070350647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15002250671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01168704032898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92810845375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95404696464539</t>
+    <t xml:space="preserve">3.15002274513245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01168727874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92810893058777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95404672622681</t>
   </si>
   <si>
     <t xml:space="preserve">2.78516173362732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91369891166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98863101005554</t>
+    <t xml:space="preserve">2.91369915008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98863077163696</t>
   </si>
   <si>
     <t xml:space="preserve">3.00304079055786</t>
@@ -797,13 +797,13 @@
     <t xml:space="preserve">3.0260968208313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07797312736511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0577986240387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18172407150269</t>
+    <t xml:space="preserve">3.07797288894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05779886245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18172430992126</t>
   </si>
   <si>
     <t xml:space="preserve">3.17019701004028</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">3.23360061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2451286315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25089263916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27106642723083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27394866943359</t>
+    <t xml:space="preserve">3.24512887001038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25089240074158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27106714248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27394890785217</t>
   </si>
   <si>
     <t xml:space="preserve">3.28259468078613</t>
@@ -830,43 +830,43 @@
     <t xml:space="preserve">3.25665616989136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18460655212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29412245750427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10391092300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34023499488831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44398617744446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4324586391449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46416020393372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45839643478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49297976493835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44686794281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50450825691223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60249662399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51603603363037</t>
+    <t xml:space="preserve">3.18460607528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29412221908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10391116142273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34023451805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44398665428162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43245816230774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46415996551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45839595794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49298048019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44686818122864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50450873374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60249614715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51603627204895</t>
   </si>
   <si>
     <t xml:space="preserve">3.46992421150208</t>
@@ -881,22 +881,22 @@
     <t xml:space="preserve">3.41228437423706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39499258995056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37193584442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48935270309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4923632144928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59472584724426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72117280960083</t>
+    <t xml:space="preserve">3.39499282836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37193655967712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4893524646759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49236226081848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59472560882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72117352485657</t>
   </si>
   <si>
     <t xml:space="preserve">3.7151517868042</t>
@@ -905,49 +905,49 @@
     <t xml:space="preserve">3.58870339393616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46827793121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41107535362244</t>
+    <t xml:space="preserve">3.4682776927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41107559204102</t>
   </si>
   <si>
     <t xml:space="preserve">3.49838447570801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54053330421448</t>
+    <t xml:space="preserve">3.54053282737732</t>
   </si>
   <si>
     <t xml:space="preserve">3.50440549850464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5164487361908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54956531524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70912981033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72418332099915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64891672134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75127935409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72719430923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76332259178162</t>
+    <t xml:space="preserve">3.51644897460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54956555366516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70913028717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72418308258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64891719818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7512788772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72719407081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76332211494446</t>
   </si>
   <si>
     <t xml:space="preserve">3.73923707008362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74525785446167</t>
+    <t xml:space="preserve">3.74525761604309</t>
   </si>
   <si>
     <t xml:space="preserve">3.71214127540588</t>
@@ -962,22 +962,22 @@
     <t xml:space="preserve">3.7753643989563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77837562561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84159970283508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85966348648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82654619216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09750604629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14266490936279</t>
+    <t xml:space="preserve">3.77837514877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84159922599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85966372489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82654595375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09750509262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14266538619995</t>
   </si>
   <si>
     <t xml:space="preserve">4.19685649871826</t>
@@ -986,25 +986,25 @@
     <t xml:space="preserve">4.17277193069458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19083595275879</t>
+    <t xml:space="preserve">4.19083547592163</t>
   </si>
   <si>
     <t xml:space="preserve">4.22094202041626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19986724853516</t>
+    <t xml:space="preserve">4.19986772537231</t>
   </si>
   <si>
     <t xml:space="preserve">4.24502754211426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26911306381226</t>
+    <t xml:space="preserve">4.2691125869751</t>
   </si>
   <si>
     <t xml:space="preserve">4.26309156417847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21492099761963</t>
+    <t xml:space="preserve">4.21492147445679</t>
   </si>
   <si>
     <t xml:space="preserve">4.15470790863037</t>
@@ -1016,16 +1016,16 @@
     <t xml:space="preserve">4.13664388656616</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22395277023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22696352005005</t>
+    <t xml:space="preserve">4.22395324707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22696399688721</t>
   </si>
   <si>
     <t xml:space="preserve">4.33534717559814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25104904174805</t>
+    <t xml:space="preserve">4.25104856491089</t>
   </si>
   <si>
     <t xml:space="preserve">4.28717660903931</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.25405979156494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09449529647827</t>
+    <t xml:space="preserve">4.09449434280396</t>
   </si>
   <si>
     <t xml:space="preserve">4.08847284317017</t>
@@ -1046,76 +1046,76 @@
     <t xml:space="preserve">4.04030227661133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05234479904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95901465415955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86267352104187</t>
+    <t xml:space="preserve">4.05234575271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95901489257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86267256736755</t>
   </si>
   <si>
     <t xml:space="preserve">3.86568450927734</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94396185874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94697237014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95600414276123</t>
+    <t xml:space="preserve">3.94396162033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94697260856628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95600438117981</t>
   </si>
   <si>
     <t xml:space="preserve">3.98008966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97406816482544</t>
+    <t xml:space="preserve">3.97406840324402</t>
   </si>
   <si>
     <t xml:space="preserve">4.07342004776001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06438827514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98912167549133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96202516555786</t>
+    <t xml:space="preserve">4.06438779830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98912143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9620246887207</t>
   </si>
   <si>
     <t xml:space="preserve">4.01320648193359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0342812538147</t>
+    <t xml:space="preserve">4.03428220748901</t>
   </si>
   <si>
     <t xml:space="preserve">4.00417470932007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00116395950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90783381462097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8897705078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95299315452576</t>
+    <t xml:space="preserve">4.00116348266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90783405303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88976955413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95299339294434</t>
   </si>
   <si>
     <t xml:space="preserve">4.0101957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11255836486816</t>
+    <t xml:space="preserve">4.11255884170532</t>
   </si>
   <si>
     <t xml:space="preserve">4.15771865844727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06739902496338</t>
+    <t xml:space="preserve">4.06739807128906</t>
   </si>
   <si>
     <t xml:space="preserve">3.98611068725586</t>
@@ -1124,73 +1124,73 @@
     <t xml:space="preserve">3.93191933631897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9018120765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87471604347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85364198684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82353568077087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579153060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84762072563171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83256769180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88073801994324</t>
+    <t xml:space="preserve">3.90181231498718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87471628189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85364174842834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82353472709656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579129219055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84762096405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83256793022156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88073778152466</t>
   </si>
   <si>
     <t xml:space="preserve">3.88374805450439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92589783668518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92890882492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88675904273987</t>
+    <t xml:space="preserve">3.92589807510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92890858650208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88675999641418</t>
   </si>
   <si>
     <t xml:space="preserve">3.9138548374176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91084480285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84460926055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8205246925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69106650352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70611953735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55558633804321</t>
+    <t xml:space="preserve">3.91084456443787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84460997581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82052516937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69106602668762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70611929893494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55558681488037</t>
   </si>
   <si>
     <t xml:space="preserve">3.47429895401001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33580851554871</t>
+    <t xml:space="preserve">3.33580827713013</t>
   </si>
   <si>
     <t xml:space="preserve">3.40204286575317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52246904373169</t>
+    <t xml:space="preserve">3.52246975898743</t>
   </si>
   <si>
     <t xml:space="preserve">3.54354429244995</t>
@@ -1202,97 +1202,97 @@
     <t xml:space="preserve">3.57365036010742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60074615478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57666158676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53752255439758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55257630348206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50139498710632</t>
+    <t xml:space="preserve">3.60074639320374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57666182518005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53752326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55257606506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50139474868774</t>
   </si>
   <si>
     <t xml:space="preserve">3.45021390914917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51042652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48634219169617</t>
+    <t xml:space="preserve">3.51042675971985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48634123802185</t>
   </si>
   <si>
     <t xml:space="preserve">3.43817138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40806460380554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53451204299927</t>
+    <t xml:space="preserve">3.40806484222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53451156616211</t>
   </si>
   <si>
     <t xml:space="preserve">3.60977864265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35387206077576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42612862586975</t>
+    <t xml:space="preserve">3.35387253761292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42612814903259</t>
   </si>
   <si>
     <t xml:space="preserve">3.44419264793396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32376551628113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39000058174133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61278915405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73020505905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6669807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64590716362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63386392593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81450271606445</t>
+    <t xml:space="preserve">3.32376575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39000082015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61278891563416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73020482063293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66698050498962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64590668678284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.633864402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81450343132019</t>
   </si>
   <si>
     <t xml:space="preserve">3.86869502067566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93492984771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04331350326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99213171005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98310017585754</t>
+    <t xml:space="preserve">3.93492937088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04331398010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99213194847107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9831006526947</t>
   </si>
   <si>
     <t xml:space="preserve">4.06137752532959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12460136413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16072940826416</t>
+    <t xml:space="preserve">4.12460088729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.160728931427</t>
   </si>
   <si>
     <t xml:space="preserve">4.07040929794312</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">4.08245229721069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80848169326782</t>
+    <t xml:space="preserve">3.80848240852356</t>
   </si>
   <si>
     <t xml:space="preserve">3.89880228042603</t>
@@ -1310,133 +1310,133 @@
     <t xml:space="preserve">3.91987681388855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78439617156982</t>
+    <t xml:space="preserve">3.78439593315125</t>
   </si>
   <si>
     <t xml:space="preserve">3.77235436439514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79945015907288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73622608184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75429058074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76633286476135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63988494873047</t>
+    <t xml:space="preserve">3.79945063591003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73622584342957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75429081916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76633310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63988447189331</t>
   </si>
   <si>
     <t xml:space="preserve">3.56160807609558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66999220848083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96503567695618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79342865943909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74224734306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79164910316467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77612209320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78854393959045</t>
+    <t xml:space="preserve">3.6699914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96503663063049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79342937469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74224805831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79164934158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77612233161926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78854370117188</t>
   </si>
   <si>
     <t xml:space="preserve">3.70469880104065</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58358979225159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55914258956909</t>
+    <t xml:space="preserve">3.58359003067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55914330482483</t>
   </si>
   <si>
     <t xml:space="preserve">3.55258846282959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51326060295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61157965660095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58536076545715</t>
+    <t xml:space="preserve">3.51326107978821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61157989501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58536124229431</t>
   </si>
   <si>
     <t xml:space="preserve">3.76888966560364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89998173713684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89342713356018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85082292556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81149506568909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63779878616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7557806968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73939442634583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86065435409546</t>
+    <t xml:space="preserve">3.89998197555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89342737197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85082173347473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81149458885193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63779830932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75578045845032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7393946647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86065340042114</t>
   </si>
   <si>
     <t xml:space="preserve">3.84099006652832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81804871559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96552777290344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98846864700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93275451660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86720871925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84426784515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91308999061584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82132649421692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03107309341431</t>
+    <t xml:space="preserve">3.81804919242859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96552801132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98846888542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93275499343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86720895767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84426712989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91309118270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8213267326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03107357025146</t>
   </si>
   <si>
     <t xml:space="preserve">4.04418277740479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0245189666748</t>
+    <t xml:space="preserve">4.02451848983765</t>
   </si>
   <si>
     <t xml:space="preserve">3.98191428184509</t>
@@ -1445,97 +1445,97 @@
     <t xml:space="preserve">3.90653657913208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99830055236816</t>
+    <t xml:space="preserve">3.99830102920532</t>
   </si>
   <si>
     <t xml:space="preserve">3.7754442691803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76561236381531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71973037719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71645355224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56897497177124</t>
+    <t xml:space="preserve">3.76561212539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71973085403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71645331382751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56897473335266</t>
   </si>
   <si>
     <t xml:space="preserve">3.50670623779297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46737837791443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27467346191406</t>
+    <t xml:space="preserve">3.46737861633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27467370033264</t>
   </si>
   <si>
     <t xml:space="preserve">2.93645668029785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03477597236633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19077467918396</t>
+    <t xml:space="preserve">3.03477621078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19077491760254</t>
   </si>
   <si>
     <t xml:space="preserve">3.42149686813354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41494202613831</t>
+    <t xml:space="preserve">3.41494226455688</t>
   </si>
   <si>
     <t xml:space="preserve">3.33628678321838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31662321090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35595107078552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.211749792099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30023622512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32645487785339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39855551719666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33956408500671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29040503501892</t>
+    <t xml:space="preserve">3.3166229724884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35595035552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21174955368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30023646354675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32645463943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39855575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33956384658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29040479660034</t>
   </si>
   <si>
     <t xml:space="preserve">3.27729535102844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28057289123535</t>
+    <t xml:space="preserve">3.28057312965393</t>
   </si>
   <si>
     <t xml:space="preserve">3.18290948867798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12260699272156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07148098945618</t>
+    <t xml:space="preserve">3.12260746955872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07148122787476</t>
   </si>
   <si>
     <t xml:space="preserve">3.01511192321777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89975118637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01904463768005</t>
+    <t xml:space="preserve">2.89975070953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01904487609863</t>
   </si>
   <si>
     <t xml:space="preserve">3.01380085945129</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">3.02691006660461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13440561294556</t>
+    <t xml:space="preserve">3.1344051361084</t>
   </si>
   <si>
     <t xml:space="preserve">3.10425424575806</t>
@@ -1559,10 +1559,10 @@
     <t xml:space="preserve">3.04264116287231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00200295448303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00462436676025</t>
+    <t xml:space="preserve">3.00200247764587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00462460517883</t>
   </si>
   <si>
     <t xml:space="preserve">2.98233914375305</t>
@@ -1571,52 +1571,52 @@
     <t xml:space="preserve">2.98627185821533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92072558403015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92728018760681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00069212913513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01249003410339</t>
+    <t xml:space="preserve">2.92072534561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92728066444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00069189071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01249027252197</t>
   </si>
   <si>
     <t xml:space="preserve">3.03739738464355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95612049102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92465829849243</t>
+    <t xml:space="preserve">2.95612072944641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92465877532959</t>
   </si>
   <si>
     <t xml:space="preserve">2.84469270706177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97709536552429</t>
+    <t xml:space="preserve">2.97709512710571</t>
   </si>
   <si>
     <t xml:space="preserve">3.00724601745605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89057493209839</t>
+    <t xml:space="preserve">2.89057469367981</t>
   </si>
   <si>
     <t xml:space="preserve">2.77259206771851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79487729072571</t>
+    <t xml:space="preserve">2.79487752914429</t>
   </si>
   <si>
     <t xml:space="preserve">2.73064255714417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71229004859924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70049166679382</t>
+    <t xml:space="preserve">2.71228957176208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70049142837524</t>
   </si>
   <si>
     <t xml:space="preserve">2.77914643287659</t>
@@ -1628,19 +1628,19 @@
     <t xml:space="preserve">2.7371973991394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7214663028717</t>
+    <t xml:space="preserve">2.72146606445312</t>
   </si>
   <si>
     <t xml:space="preserve">2.6900041103363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63625621795654</t>
+    <t xml:space="preserve">2.63625645637512</t>
   </si>
   <si>
     <t xml:space="preserve">2.64936566352844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62052536010742</t>
+    <t xml:space="preserve">2.620525598526</t>
   </si>
   <si>
     <t xml:space="preserve">2.67689490318298</t>
@@ -1649,10 +1649,10 @@
     <t xml:space="preserve">2.7201554775238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87615489959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85124683380127</t>
+    <t xml:space="preserve">2.87615466117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85124731063843</t>
   </si>
   <si>
     <t xml:space="preserve">2.86697816848755</t>
@@ -1661,34 +1661,34 @@
     <t xml:space="preserve">2.93907880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91154932975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91679263114929</t>
+    <t xml:space="preserve">2.91154956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91679286956787</t>
   </si>
   <si>
     <t xml:space="preserve">2.92596960067749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94170022010803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99807000160217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04133009910583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99675893783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99413704872131</t>
+    <t xml:space="preserve">2.94170045852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99806952476501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04133057594299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99675917625427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99413681030273</t>
   </si>
   <si>
     <t xml:space="preserve">2.96267533302307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96005320549011</t>
+    <t xml:space="preserve">2.96005344390869</t>
   </si>
   <si>
     <t xml:space="preserve">2.91285991668701</t>
@@ -1700,13 +1700,13 @@
     <t xml:space="preserve">2.70704627037048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6886932849884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.705735206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74244093894958</t>
+    <t xml:space="preserve">2.68869352340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70573496818542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74244117736816</t>
   </si>
   <si>
     <t xml:space="preserve">2.64674377441406</t>
@@ -1718,22 +1718,22 @@
     <t xml:space="preserve">2.59692907333374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38193869590759</t>
+    <t xml:space="preserve">2.38193845748901</t>
   </si>
   <si>
     <t xml:space="preserve">2.46714806556702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44879531860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49074482917786</t>
+    <t xml:space="preserve">2.44879484176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49074459075928</t>
   </si>
   <si>
     <t xml:space="preserve">2.4710807800293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48681163787842</t>
+    <t xml:space="preserve">2.486811876297</t>
   </si>
   <si>
     <t xml:space="preserve">2.4199550151825</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">2.31639242172241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25871205329895</t>
+    <t xml:space="preserve">2.25871229171753</t>
   </si>
   <si>
     <t xml:space="preserve">2.20365357398987</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">2.28493046760559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38587141036987</t>
+    <t xml:space="preserve">2.38587117195129</t>
   </si>
   <si>
     <t xml:space="preserve">2.39242577552795</t>
@@ -1766,13 +1766,13 @@
     <t xml:space="preserve">2.45928263664246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54973602294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4723916053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44617342948914</t>
+    <t xml:space="preserve">2.54973578453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47239208221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44617366790771</t>
   </si>
   <si>
     <t xml:space="preserve">2.45797181129456</t>
@@ -1781,25 +1781,25 @@
     <t xml:space="preserve">2.47501349449158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54842519760132</t>
+    <t xml:space="preserve">2.54842495918274</t>
   </si>
   <si>
     <t xml:space="preserve">2.43044233322144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40815663337708</t>
+    <t xml:space="preserve">2.40815687179565</t>
   </si>
   <si>
     <t xml:space="preserve">2.33998894691467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28886318206787</t>
+    <t xml:space="preserve">2.28886342048645</t>
   </si>
   <si>
     <t xml:space="preserve">2.27968668937683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25740122795105</t>
+    <t xml:space="preserve">2.25740098953247</t>
   </si>
   <si>
     <t xml:space="preserve">2.17612409591675</t>
@@ -1808,22 +1808,22 @@
     <t xml:space="preserve">2.18661141395569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13155293464661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29410696029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35178732872009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766931533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44748449325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42388796806335</t>
+    <t xml:space="preserve">2.13155317306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29410672187805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35178756713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766955375671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44748425483704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42388772964478</t>
   </si>
   <si>
     <t xml:space="preserve">2.40946769714355</t>
@@ -1835,25 +1835,25 @@
     <t xml:space="preserve">2.21938443183899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19447731971741</t>
+    <t xml:space="preserve">2.19447708129883</t>
   </si>
   <si>
     <t xml:space="preserve">2.25477933883667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31901454925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32687997817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26264476776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17743492126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12893104553223</t>
+    <t xml:space="preserve">2.31901431083679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32687973976135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26264500617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17743515968323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12893152236938</t>
   </si>
   <si>
     <t xml:space="preserve">2.14597320556641</t>
@@ -1865,19 +1865,19 @@
     <t xml:space="preserve">2.12368750572205</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10271286964417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11713314056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14728426933289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15121698379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23904824256897</t>
+    <t xml:space="preserve">2.10271263122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11713290214539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14728403091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15121674537659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23904800415039</t>
   </si>
   <si>
     <t xml:space="preserve">2.20758628845215</t>
@@ -1886,16 +1886,16 @@
     <t xml:space="preserve">2.36489653587341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34785461425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37407302856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25084662437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39504742622375</t>
+    <t xml:space="preserve">2.34785437583923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37407279014587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25084638595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39504766464233</t>
   </si>
   <si>
     <t xml:space="preserve">2.35572028160095</t>
@@ -1910,34 +1910,34 @@
     <t xml:space="preserve">2.44486284255981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44224071502686</t>
+    <t xml:space="preserve">2.44224047660828</t>
   </si>
   <si>
     <t xml:space="preserve">2.43175339698792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38455986976624</t>
+    <t xml:space="preserve">2.38456034660339</t>
   </si>
   <si>
     <t xml:space="preserve">2.35309815406799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34654331207275</t>
+    <t xml:space="preserve">2.34654355049133</t>
   </si>
   <si>
     <t xml:space="preserve">2.35440897941589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37145113945007</t>
+    <t xml:space="preserve">2.37145090103149</t>
   </si>
   <si>
     <t xml:space="preserve">2.28755211830139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26788878440857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31114912033081</t>
+    <t xml:space="preserve">2.26788854598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31114864349365</t>
   </si>
   <si>
     <t xml:space="preserve">2.37931656837463</t>
@@ -1946,88 +1946,88 @@
     <t xml:space="preserve">2.40291285514832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40553498268127</t>
+    <t xml:space="preserve">2.40553522109985</t>
   </si>
   <si>
     <t xml:space="preserve">2.37014031410217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33605599403381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39898037910461</t>
+    <t xml:space="preserve">2.33605623245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39898061752319</t>
   </si>
   <si>
     <t xml:space="preserve">2.37669467926025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5012321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54318141937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52613925933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50385403633118</t>
+    <t xml:space="preserve">2.50123190879822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54318165779114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52613949775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50385355949402</t>
   </si>
   <si>
     <t xml:space="preserve">2.49336647987366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42782020568848</t>
+    <t xml:space="preserve">2.42782068252563</t>
   </si>
   <si>
     <t xml:space="preserve">2.39635848999023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38718199729919</t>
+    <t xml:space="preserve">2.38718175888062</t>
   </si>
   <si>
     <t xml:space="preserve">2.37276196479797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37800574302673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33867812156677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29935073852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38062763214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30459451675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38849306106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45666074752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40160250663757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34129977226257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34392166137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38324928283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32556891441345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30328297615051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30590510368347</t>
+    <t xml:space="preserve">2.37800550460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33867788314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29935050010681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38062739372253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30459427833557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38849282264709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4566605091095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40160226821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34130001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34392189979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38324952125549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32556867599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30328321456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30590486526489</t>
   </si>
   <si>
     <t xml:space="preserve">2.34523296356201</t>
@@ -2036,19 +2036,19 @@
     <t xml:space="preserve">2.32425832748413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30983781814575</t>
+    <t xml:space="preserve">2.30983805656433</t>
   </si>
   <si>
     <t xml:space="preserve">2.21545195579529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19054436683655</t>
+    <t xml:space="preserve">2.19054412841797</t>
   </si>
   <si>
     <t xml:space="preserve">2.09091472625732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08698177337646</t>
+    <t xml:space="preserve">2.08698201179504</t>
   </si>
   <si>
     <t xml:space="preserve">1.99783957004547</t>
@@ -2057,88 +2057,88 @@
     <t xml:space="preserve">2.03978872299194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97686433792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99128484725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97817528247833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98996269702911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99967014789581</t>
+    <t xml:space="preserve">1.9768648147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9912850856781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97817552089691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98996293544769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99966990947723</t>
   </si>
   <si>
     <t xml:space="preserve">1.97470891475677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94420051574707</t>
+    <t xml:space="preserve">1.94420087337494</t>
   </si>
   <si>
     <t xml:space="preserve">1.91923928260803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89843833446503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86377012729645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82632839679718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87625098228455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87902414798737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83742213249207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95113432407379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92755973339081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89982509613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92062640190125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90953207015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90675866603851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88734459877014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8887312412262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88179755210876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02879166603088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98302936553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03156495094299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98857629299164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95945477485657</t>
+    <t xml:space="preserve">1.8984386920929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86376988887787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82632851600647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87625074386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87902426719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83742225170135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9511342048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92755961418152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89982533454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92062628269196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9095321893692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90675890445709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88734447956085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88873136043549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88179767131805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02879190444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98302912712097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03156542778015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98857617378235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95945453643799</t>
   </si>
   <si>
     <t xml:space="preserve">2.00660371780396</t>
@@ -2150,13 +2150,13 @@
     <t xml:space="preserve">2.07178020477295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0939679145813</t>
+    <t xml:space="preserve">2.09396767616272</t>
   </si>
   <si>
     <t xml:space="preserve">2.14943718910217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22709441184998</t>
+    <t xml:space="preserve">2.2270941734314</t>
   </si>
   <si>
     <t xml:space="preserve">2.25344228744507</t>
@@ -2165,13 +2165,13 @@
     <t xml:space="preserve">2.25898909568787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26453638076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21461367607117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21184015274048</t>
+    <t xml:space="preserve">2.26453590393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21461391448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21184039115906</t>
   </si>
   <si>
     <t xml:space="preserve">2.24928212165833</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">2.31445860862732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30059146881104</t>
+    <t xml:space="preserve">2.30059170722961</t>
   </si>
   <si>
     <t xml:space="preserve">2.30891156196594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31307172775269</t>
+    <t xml:space="preserve">2.31307196617126</t>
   </si>
   <si>
     <t xml:space="preserve">2.27424335479736</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">2.2215473651886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24789524078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24650859832764</t>
+    <t xml:space="preserve">2.24789571762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24650883674622</t>
   </si>
   <si>
     <t xml:space="preserve">2.24512195587158</t>
@@ -2213,19 +2213,19 @@
     <t xml:space="preserve">2.37824845314026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30613827705383</t>
+    <t xml:space="preserve">2.30613803863525</t>
   </si>
   <si>
     <t xml:space="preserve">2.23125457763672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18687915802002</t>
+    <t xml:space="preserve">2.1868793964386</t>
   </si>
   <si>
     <t xml:space="preserve">2.17162489891052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17439842224121</t>
+    <t xml:space="preserve">2.17439818382263</t>
   </si>
   <si>
     <t xml:space="preserve">2.22432088851929</t>
@@ -2240,103 +2240,103 @@
     <t xml:space="preserve">2.12863612174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09812831878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12724947929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17717218399048</t>
+    <t xml:space="preserve">2.09812808036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12724924087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1771719455719</t>
   </si>
   <si>
     <t xml:space="preserve">2.19103932380676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2368016242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20629358291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19935965538025</t>
+    <t xml:space="preserve">2.23680138587952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20629334449768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19935941696167</t>
   </si>
   <si>
     <t xml:space="preserve">2.18549227714539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25760245323181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25621557235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23957514762878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35606074333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38102173805237</t>
+    <t xml:space="preserve">2.25760269165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25621581077576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23957490921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35606050491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38102197647095</t>
   </si>
   <si>
     <t xml:space="preserve">2.36715459823608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38379526138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43510460853577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51553511619568</t>
+    <t xml:space="preserve">2.38379549980164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43510484695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51553535461426</t>
   </si>
   <si>
     <t xml:space="preserve">2.49889421463013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42955732345581</t>
+    <t xml:space="preserve">2.42955756187439</t>
   </si>
   <si>
     <t xml:space="preserve">2.42817068099976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44897198677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45867896080017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38795566558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37131500244141</t>
+    <t xml:space="preserve">2.44897174835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45867919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766240119934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3879554271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37131452560425</t>
   </si>
   <si>
     <t xml:space="preserve">2.382408618927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41707706451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42401075363159</t>
+    <t xml:space="preserve">2.41707682609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42401051521301</t>
   </si>
   <si>
     <t xml:space="preserve">2.37408804893494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32693910598755</t>
+    <t xml:space="preserve">2.32693934440613</t>
   </si>
   <si>
     <t xml:space="preserve">2.2992045879364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31723213195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34496641159058</t>
+    <t xml:space="preserve">2.31723165512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34496665000916</t>
   </si>
   <si>
     <t xml:space="preserve">2.34635353088379</t>
@@ -2351,13 +2351,13 @@
     <t xml:space="preserve">2.48502707481384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56961750984192</t>
+    <t xml:space="preserve">2.56961798667908</t>
   </si>
   <si>
     <t xml:space="preserve">2.61537981033325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67639589309692</t>
+    <t xml:space="preserve">2.6763961315155</t>
   </si>
   <si>
     <t xml:space="preserve">2.73879909515381</t>
@@ -2366,10 +2366,10 @@
     <t xml:space="preserve">2.70690417289734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74711942672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72770500183105</t>
+    <t xml:space="preserve">2.74711966514587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72770524024963</t>
   </si>
   <si>
     <t xml:space="preserve">2.75266647338867</t>
@@ -2384,22 +2384,22 @@
     <t xml:space="preserve">2.77208065986633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69581055641174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70413088798523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72077178955078</t>
+    <t xml:space="preserve">2.69581031799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70413112640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7207715511322</t>
   </si>
   <si>
     <t xml:space="preserve">2.80120205879211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78733468055725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82893657684326</t>
+    <t xml:space="preserve">2.78733491897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82893681526184</t>
   </si>
   <si>
     <t xml:space="preserve">2.85528492927551</t>
@@ -2408,88 +2408,88 @@
     <t xml:space="preserve">2.94680905342102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01614570617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02724003791809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04804039001465</t>
+    <t xml:space="preserve">3.01614594459534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02723979949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04804062843323</t>
   </si>
   <si>
     <t xml:space="preserve">3.0799355506897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13679170608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14649868011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17562055587769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14511179924011</t>
+    <t xml:space="preserve">3.13679194450378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14649891853333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17562007904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14511203765869</t>
   </si>
   <si>
     <t xml:space="preserve">3.23108959197998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24773073196411</t>
+    <t xml:space="preserve">3.24773049354553</t>
   </si>
   <si>
     <t xml:space="preserve">3.26298427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26159763336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2255425453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18532729148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18394088745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25605130195618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21028900146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25327706336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22831606864929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2019681930542</t>
+    <t xml:space="preserve">3.2615978717804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22554278373718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18532752990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18394041061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25605082511902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21028852462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25327730178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22831654548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20196795463562</t>
   </si>
   <si>
     <t xml:space="preserve">3.24218344688416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26575779914856</t>
+    <t xml:space="preserve">3.26575803756714</t>
   </si>
   <si>
     <t xml:space="preserve">3.21306180953979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19919490814209</t>
+    <t xml:space="preserve">3.19919466972351</t>
   </si>
   <si>
     <t xml:space="preserve">3.20890164375305</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22415614128113</t>
+    <t xml:space="preserve">3.22415590286255</t>
   </si>
   <si>
     <t xml:space="preserve">3.1908745765686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2033543586731</t>
+    <t xml:space="preserve">3.20335483551025</t>
   </si>
   <si>
     <t xml:space="preserve">3.06606841087341</t>
@@ -2501,13 +2501,13 @@
     <t xml:space="preserve">3.14788556098938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20612835884094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17839336395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17146039009094</t>
+    <t xml:space="preserve">3.2061288356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17839407920837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17145991325378</t>
   </si>
   <si>
     <t xml:space="preserve">3.03694701194763</t>
@@ -2519,40 +2519,40 @@
     <t xml:space="preserve">3.16868686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.970383644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03555965423584</t>
+    <t xml:space="preserve">2.97038340568542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03555989265442</t>
   </si>
   <si>
     <t xml:space="preserve">3.14095211029053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12985825538635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14927244186401</t>
+    <t xml:space="preserve">3.12985801696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14927196502686</t>
   </si>
   <si>
     <t xml:space="preserve">3.17007327079773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12708473205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10073685646057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07854914665222</t>
+    <t xml:space="preserve">3.12708449363708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10073661804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07854866981506</t>
   </si>
   <si>
     <t xml:space="preserve">3.11044383049011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08964252471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28239917755127</t>
+    <t xml:space="preserve">3.08964276313782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28239870071411</t>
   </si>
   <si>
     <t xml:space="preserve">3.34202837944031</t>
@@ -2561,13 +2561,13 @@
     <t xml:space="preserve">3.34896159172058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93987560272217</t>
+    <t xml:space="preserve">2.93987512588501</t>
   </si>
   <si>
     <t xml:space="preserve">2.97315716743469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.863605260849</t>
+    <t xml:space="preserve">2.86360549926758</t>
   </si>
   <si>
     <t xml:space="preserve">2.73741245269775</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">2.58487153053284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55159020423889</t>
+    <t xml:space="preserve">2.55158996582031</t>
   </si>
   <si>
     <t xml:space="preserve">2.49473428726196</t>
@@ -2585,34 +2585,34 @@
     <t xml:space="preserve">2.29227089881897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07039332389832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95668148994446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99134969711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6904284954071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78472638130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65576004981995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52818059921265</t>
+    <t xml:space="preserve">2.07039356231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9566810131073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99134957790375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69042837619781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7847261428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65576016902924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52818048000336</t>
   </si>
   <si>
     <t xml:space="preserve">1.41030812263489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.485191822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49489879608154</t>
+    <t xml:space="preserve">1.48519170284271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49489891529083</t>
   </si>
   <si>
     <t xml:space="preserve">1.60583758354187</t>
@@ -2621,25 +2621,25 @@
     <t xml:space="preserve">1.67933452129364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67656111717224</t>
+    <t xml:space="preserve">1.67656099796295</t>
   </si>
   <si>
     <t xml:space="preserve">1.72648358345032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68904185295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69736194610596</t>
+    <t xml:space="preserve">1.68904173374176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69736218452454</t>
   </si>
   <si>
     <t xml:space="preserve">1.72371017932892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75421822071075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78888642787933</t>
+    <t xml:space="preserve">1.75421833992004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78888654708862</t>
   </si>
   <si>
     <t xml:space="preserve">2.02185773849487</t>
@@ -2648,49 +2648,49 @@
     <t xml:space="preserve">2.06207299232483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05375266075134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99412298202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609531879425</t>
+    <t xml:space="preserve">2.05375242233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99412286281586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609567642212</t>
   </si>
   <si>
     <t xml:space="preserve">1.96638834476471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94142735004425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85960984230042</t>
+    <t xml:space="preserve">1.94142711162567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85960972309113</t>
   </si>
   <si>
     <t xml:space="preserve">1.86793041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92339944839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90121221542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1480507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26730942726135</t>
+    <t xml:space="preserve">1.92339992523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.901211977005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14805054664612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26730966567993</t>
   </si>
   <si>
     <t xml:space="preserve">2.23818802833557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22570753097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13418340682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28117680549622</t>
+    <t xml:space="preserve">2.22570729255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13418316841125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28117704391479</t>
   </si>
   <si>
     <t xml:space="preserve">2.35744714736938</t>
@@ -2702,10 +2702,10 @@
     <t xml:space="preserve">2.3435800075531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30752515792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48411750793457</t>
+    <t xml:space="preserve">2.30752491950989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48411726951599</t>
   </si>
   <si>
     <t xml:space="preserve">2.51219487190247</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">2.49150633811951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49741744995117</t>
+    <t xml:space="preserve">2.49741721153259</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456218719482</t>
@@ -2726,13 +2726,13 @@
     <t xml:space="preserve">2.72647023200989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75750350952148</t>
+    <t xml:space="preserve">2.75750327110291</t>
   </si>
   <si>
     <t xml:space="preserve">2.80774736404419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86537981033325</t>
+    <t xml:space="preserve">2.86538004875183</t>
   </si>
   <si>
     <t xml:space="preserve">2.87572431564331</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">3.14024353027344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93483448028564</t>
+    <t xml:space="preserve">2.93483471870422</t>
   </si>
   <si>
     <t xml:space="preserve">2.93631267547607</t>
@@ -2762,58 +2762,58 @@
     <t xml:space="preserve">2.94222354888916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99837851524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00281167030334</t>
+    <t xml:space="preserve">2.99837827682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00281190872192</t>
   </si>
   <si>
     <t xml:space="preserve">2.9584789276123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88606858253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92744565010071</t>
+    <t xml:space="preserve">2.88606834411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92744588851929</t>
   </si>
   <si>
     <t xml:space="preserve">2.83582472801208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8905017375946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8845911026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85946869850159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82843589782715</t>
+    <t xml:space="preserve">2.89050197601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88459062576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85946893692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82843565940857</t>
   </si>
   <si>
     <t xml:space="preserve">2.86242437362671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93779039382935</t>
+    <t xml:space="preserve">2.93779015541077</t>
   </si>
   <si>
     <t xml:space="preserve">2.99542307853699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03236699104309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04418897628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01906728744507</t>
+    <t xml:space="preserve">3.03236722946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04418873786926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01906704902649</t>
   </si>
   <si>
     <t xml:space="preserve">2.92005681991577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93040156364441</t>
+    <t xml:space="preserve">2.93040132522583</t>
   </si>
   <si>
     <t xml:space="preserve">2.97916769981384</t>
@@ -2834,13 +2834,13 @@
     <t xml:space="preserve">2.95552325248718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94665670394897</t>
+    <t xml:space="preserve">2.94665694236755</t>
   </si>
   <si>
     <t xml:space="preserve">3.03384470939636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0959107875824</t>
+    <t xml:space="preserve">3.09591102600098</t>
   </si>
   <si>
     <t xml:space="preserve">3.01758933067322</t>
@@ -2864,16 +2864,16 @@
     <t xml:space="preserve">2.85503554344177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85355806350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.894935131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87720203399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92153477668762</t>
+    <t xml:space="preserve">2.85355758666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89493536949158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87720227241516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9215350151062</t>
   </si>
   <si>
     <t xml:space="preserve">2.9629123210907</t>
@@ -2882,13 +2882,13 @@
     <t xml:space="preserve">2.91266822814941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87424659729004</t>
+    <t xml:space="preserve">2.87424635887146</t>
   </si>
   <si>
     <t xml:space="preserve">2.84616899490356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80479192733765</t>
+    <t xml:space="preserve">2.80479168891907</t>
   </si>
   <si>
     <t xml:space="preserve">2.76784777641296</t>
@@ -2897,19 +2897,19 @@
     <t xml:space="preserve">2.75307011604309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78410267829895</t>
+    <t xml:space="preserve">2.78410315513611</t>
   </si>
   <si>
     <t xml:space="preserve">2.79888081550598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74863696098328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7752366065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7235152721405</t>
+    <t xml:space="preserve">2.7486367225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77523636817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72351503372192</t>
   </si>
   <si>
     <t xml:space="preserve">2.76636981964111</t>
@@ -2918,22 +2918,22 @@
     <t xml:space="preserve">2.79296970367432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73681473731995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69987082481384</t>
+    <t xml:space="preserve">2.73681449890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69987058639526</t>
   </si>
   <si>
     <t xml:space="preserve">2.79592537879944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74272537231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75454783439636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74715900421143</t>
+    <t xml:space="preserve">2.74272561073303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75454759597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74715876579285</t>
   </si>
   <si>
     <t xml:space="preserve">2.71612596511841</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">2.52549457550049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54174995422363</t>
+    <t xml:space="preserve">2.54175019264221</t>
   </si>
   <si>
     <t xml:space="preserve">2.53436136245728</t>
@@ -2978,25 +2978,25 @@
     <t xml:space="preserve">2.52992796897888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6112048625946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54618358612061</t>
+    <t xml:space="preserve">2.61120462417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54618334770203</t>
   </si>
   <si>
     <t xml:space="preserve">2.55209469795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67179322242737</t>
+    <t xml:space="preserve">2.67179298400879</t>
   </si>
   <si>
     <t xml:space="preserve">2.60972714424133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5432276725769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52845025062561</t>
+    <t xml:space="preserve">2.54322791099548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52845001220703</t>
   </si>
   <si>
     <t xml:space="preserve">2.47377324104309</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">2.6289381980896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65701532363892</t>
+    <t xml:space="preserve">2.6570155620575</t>
   </si>
   <si>
     <t xml:space="preserve">2.63632702827454</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">2.60677194595337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53140616416931</t>
+    <t xml:space="preserve">2.53140592575073</t>
   </si>
   <si>
     <t xml:space="preserve">2.52253937721252</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">2.31713008880615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37180757522583</t>
+    <t xml:space="preserve">2.37180733680725</t>
   </si>
   <si>
     <t xml:space="preserve">2.51662802696228</t>
@@ -3035,16 +3035,16 @@
     <t xml:space="preserve">2.58312749862671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64223790168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4929838180542</t>
+    <t xml:space="preserve">2.64223766326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49298405647278</t>
   </si>
   <si>
     <t xml:space="preserve">2.61563801765442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65258240699768</t>
+    <t xml:space="preserve">2.6525821685791</t>
   </si>
   <si>
     <t xml:space="preserve">2.63041567802429</t>
@@ -3059,16 +3059,16 @@
     <t xml:space="preserve">2.74568128585815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83139133453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79149174690247</t>
+    <t xml:space="preserve">2.83139157295227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79149198532104</t>
   </si>
   <si>
     <t xml:space="preserve">2.78853631019592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75898098945618</t>
+    <t xml:space="preserve">2.75898122787476</t>
   </si>
   <si>
     <t xml:space="preserve">2.68361520767212</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">2.67031526565552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66440415382385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64519357681274</t>
+    <t xml:space="preserve">2.66440439224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64519333839417</t>
   </si>
   <si>
     <t xml:space="preserve">2.68065977096558</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">2.68213748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6259822845459</t>
+    <t xml:space="preserve">2.62598252296448</t>
   </si>
   <si>
     <t xml:space="preserve">2.65849351882935</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">2.90084624290466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98064541816711</t>
+    <t xml:space="preserve">2.98064517974854</t>
   </si>
   <si>
     <t xml:space="preserve">3.01463389396667</t>
@@ -3122,10 +3122,10 @@
     <t xml:space="preserve">3.03975582122803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07374429702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11807727813721</t>
+    <t xml:space="preserve">3.07374405860901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11807703971863</t>
   </si>
   <si>
     <t xml:space="preserve">3.06044459342957</t>
@@ -3152,13 +3152,13 @@
     <t xml:space="preserve">2.83434700965881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91710162162781</t>
+    <t xml:space="preserve">2.91710138320923</t>
   </si>
   <si>
     <t xml:space="preserve">3.04714465141296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1328547000885</t>
+    <t xml:space="preserve">3.13285446166992</t>
   </si>
   <si>
     <t xml:space="preserve">3.10034418106079</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">3.17718768119812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1062548160553</t>
+    <t xml:space="preserve">3.10625505447388</t>
   </si>
   <si>
     <t xml:space="preserve">3.13581037521362</t>
@@ -3179,16 +3179,16 @@
     <t xml:space="preserve">3.00133371353149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9451789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99985599517822</t>
+    <t xml:space="preserve">2.94517922401428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9998562335968</t>
   </si>
   <si>
     <t xml:space="preserve">2.97177863121033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9392683506012</t>
+    <t xml:space="preserve">2.93926811218262</t>
   </si>
   <si>
     <t xml:space="preserve">3.08999991416931</t>
@@ -3197,13 +3197,13 @@
     <t xml:space="preserve">3.09147763252258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07670021057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08704423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08852171897888</t>
+    <t xml:space="preserve">3.07669997215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08704400062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08852195739746</t>
   </si>
   <si>
     <t xml:space="preserve">3.12694358825684</t>
@@ -3245,28 +3245,28 @@
     <t xml:space="preserve">3.28801941871643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31609725952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29393100738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27324199676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2451651096344</t>
+    <t xml:space="preserve">3.31609702110291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29393076896667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27324223518372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24516487121582</t>
   </si>
   <si>
     <t xml:space="preserve">3.32274746894836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30649185180664</t>
+    <t xml:space="preserve">3.30649161338806</t>
   </si>
   <si>
     <t xml:space="preserve">3.3101863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29540848731995</t>
+    <t xml:space="preserve">3.29540872573853</t>
   </si>
   <si>
     <t xml:space="preserve">3.25107574462891</t>
@@ -3281,25 +3281,25 @@
     <t xml:space="preserve">3.27915358543396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24073123931885</t>
+    <t xml:space="preserve">3.24073147773743</t>
   </si>
   <si>
     <t xml:space="preserve">3.27767539024353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28136944770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18531513214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13433265686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10329937934875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16314911842346</t>
+    <t xml:space="preserve">3.28136968612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18531537055969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13433289527893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10329961776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16314888000488</t>
   </si>
   <si>
     <t xml:space="preserve">3.13507151603699</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">3.17940425872803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09664940834045</t>
+    <t xml:space="preserve">3.09664964675903</t>
   </si>
   <si>
     <t xml:space="preserve">3.15354347229004</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">3.26511454582214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2274317741394</t>
+    <t xml:space="preserve">3.22743153572083</t>
   </si>
   <si>
     <t xml:space="preserve">3.23925375938416</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">3.31979179382324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33974123001099</t>
+    <t xml:space="preserve">3.33974146842957</t>
   </si>
   <si>
     <t xml:space="preserve">3.41362953186035</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">3.32053017616272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32939696311951</t>
+    <t xml:space="preserve">3.32939720153809</t>
   </si>
   <si>
     <t xml:space="preserve">3.31535816192627</t>
@@ -3362,19 +3362,19 @@
     <t xml:space="preserve">3.33322882652283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33944463729858</t>
+    <t xml:space="preserve">3.33944487571716</t>
   </si>
   <si>
     <t xml:space="preserve">3.33633685112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41325759887695</t>
+    <t xml:space="preserve">3.41325736045837</t>
   </si>
   <si>
     <t xml:space="preserve">3.37751650810242</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4047110080719</t>
+    <t xml:space="preserve">3.40471076965332</t>
   </si>
   <si>
     <t xml:space="preserve">3.60206270217896</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">3.51037955284119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44200539588928</t>
+    <t xml:space="preserve">3.44200563430786</t>
   </si>
   <si>
     <t xml:space="preserve">3.47619247436523</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">3.38917112350464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3402214050293</t>
+    <t xml:space="preserve">3.34022164344788</t>
   </si>
   <si>
     <t xml:space="preserve">3.32545924186707</t>
@@ -3419,22 +3419,22 @@
     <t xml:space="preserve">3.27417874336243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2990415096283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25630807876587</t>
+    <t xml:space="preserve">3.29904174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25630831718445</t>
   </si>
   <si>
     <t xml:space="preserve">3.26407790184021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24776124954224</t>
+    <t xml:space="preserve">3.24776148796082</t>
   </si>
   <si>
     <t xml:space="preserve">3.2788405418396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25786185264587</t>
+    <t xml:space="preserve">3.25786209106445</t>
   </si>
   <si>
     <t xml:space="preserve">3.24076867103577</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">3.11956024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1801643371582</t>
+    <t xml:space="preserve">3.18016457557678</t>
   </si>
   <si>
     <t xml:space="preserve">3.22678303718567</t>
@@ -3485,10 +3485,10 @@
     <t xml:space="preserve">3.21202039718628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22989106178284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23066782951355</t>
+    <t xml:space="preserve">3.22989130020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23066806793213</t>
   </si>
   <si>
     <t xml:space="preserve">3.31458139419556</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">3.23299884796143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28894090652466</t>
+    <t xml:space="preserve">3.28894114494324</t>
   </si>
   <si>
     <t xml:space="preserve">3.30370378494263</t>
@@ -3512,10 +3512,10 @@
     <t xml:space="preserve">3.38606309890747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33245205879211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31302762031555</t>
+    <t xml:space="preserve">3.33245182037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31302738189697</t>
   </si>
   <si>
     <t xml:space="preserve">3.33478236198425</t>
@@ -3536,10 +3536,10 @@
     <t xml:space="preserve">3.39227914810181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41248083114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37207794189453</t>
+    <t xml:space="preserve">3.41248059272766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37207770347595</t>
   </si>
   <si>
     <t xml:space="preserve">3.39150190353394</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">3.31535863876343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34721446037292</t>
+    <t xml:space="preserve">3.34721422195435</t>
   </si>
   <si>
     <t xml:space="preserve">3.32157444953918</t>
@@ -3572,16 +3572,16 @@
     <t xml:space="preserve">3.28971838951111</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18715739250183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19725751876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29282593727112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28661036491394</t>
+    <t xml:space="preserve">3.18715763092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19725775718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29282569885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28661012649536</t>
   </si>
   <si>
     <t xml:space="preserve">3.22056746482849</t>
@@ -3593,13 +3593,13 @@
     <t xml:space="preserve">3.21279764175415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20891284942627</t>
+    <t xml:space="preserve">3.20891308784485</t>
   </si>
   <si>
     <t xml:space="preserve">3.17627954483032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30758857727051</t>
+    <t xml:space="preserve">3.30758881568909</t>
   </si>
   <si>
     <t xml:space="preserve">3.33012080192566</t>
@@ -3614,10 +3614,10 @@
     <t xml:space="preserve">3.32623624801636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43268203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45443749427795</t>
+    <t xml:space="preserve">3.43268179893494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45443725585938</t>
   </si>
   <si>
     <t xml:space="preserve">3.48085451126099</t>
@@ -3647,13 +3647,13 @@
     <t xml:space="preserve">3.57642221450806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56632208824158</t>
+    <t xml:space="preserve">3.566321849823</t>
   </si>
   <si>
     <t xml:space="preserve">3.58108496665955</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68753004074097</t>
+    <t xml:space="preserve">3.68752980232239</t>
   </si>
   <si>
     <t xml:space="preserve">3.63469576835632</t>
@@ -3671,10 +3671,10 @@
     <t xml:space="preserve">3.62692594528198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62148666381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61294007301331</t>
+    <t xml:space="preserve">3.62148690223694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61294031143188</t>
   </si>
   <si>
     <t xml:space="preserve">3.61060929298401</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">3.45132923126221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39694118499756</t>
+    <t xml:space="preserve">3.39694094657898</t>
   </si>
   <si>
     <t xml:space="preserve">3.39538669586182</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">3.22833728790283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23999166488647</t>
+    <t xml:space="preserve">3.23999190330505</t>
   </si>
   <si>
     <t xml:space="preserve">3.40004897117615</t>
@@ -3737,13 +3737,13 @@
     <t xml:space="preserve">3.4816312789917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49717092514038</t>
+    <t xml:space="preserve">3.4971706867218</t>
   </si>
   <si>
     <t xml:space="preserve">3.48707008361816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48862409591675</t>
+    <t xml:space="preserve">3.48862385749817</t>
   </si>
   <si>
     <t xml:space="preserve">3.51814913749695</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">3.54145860671997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52436494827271</t>
+    <t xml:space="preserve">3.52436470985413</t>
   </si>
   <si>
     <t xml:space="preserve">3.48551607131958</t>
@@ -3767,13 +3767,13 @@
     <t xml:space="preserve">3.70151591300964</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69607710838318</t>
+    <t xml:space="preserve">3.6960768699646</t>
   </si>
   <si>
     <t xml:space="preserve">3.64712715148926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65567374229431</t>
+    <t xml:space="preserve">3.65567398071289</t>
   </si>
   <si>
     <t xml:space="preserve">3.56865262985229</t>
@@ -3785,22 +3785,22 @@
     <t xml:space="preserve">3.49639415740967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35420727729797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40237975120544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4109263420105</t>
+    <t xml:space="preserve">3.35420703887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40237998962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41092658042908</t>
   </si>
   <si>
     <t xml:space="preserve">3.41558814048767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4653148651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48240828514099</t>
+    <t xml:space="preserve">3.46531510353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48240852355957</t>
   </si>
   <si>
     <t xml:space="preserve">3.49017834663391</t>
@@ -3818,34 +3818,34 @@
     <t xml:space="preserve">3.56321406364441</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75978899002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62614893913269</t>
+    <t xml:space="preserve">3.75978922843933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62614870071411</t>
   </si>
   <si>
     <t xml:space="preserve">3.79708409309387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75124192237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65878224372864</t>
+    <t xml:space="preserve">3.75124216079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65878200531006</t>
   </si>
   <si>
     <t xml:space="preserve">3.66188955307007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54612040519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55622124671936</t>
+    <t xml:space="preserve">3.54612016677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55622100830078</t>
   </si>
   <si>
     <t xml:space="preserve">3.38373231887817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42258143424988</t>
+    <t xml:space="preserve">3.4225811958313</t>
   </si>
   <si>
     <t xml:space="preserve">3.16384792327881</t>
@@ -3854,10 +3854,10 @@
     <t xml:space="preserve">3.06361818313599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87481260299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63395023345947</t>
+    <t xml:space="preserve">2.87481284141541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63394999504089</t>
   </si>
   <si>
     <t xml:space="preserve">2.59898638725281</t>
@@ -3866,25 +3866,25 @@
     <t xml:space="preserve">2.6471586227417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83751797676086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74505758285522</t>
+    <t xml:space="preserve">2.83751773834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7450578212738</t>
   </si>
   <si>
     <t xml:space="preserve">2.8204243183136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93308615684509</t>
+    <t xml:space="preserve">2.93308591842651</t>
   </si>
   <si>
     <t xml:space="preserve">2.91366147994995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07838034629822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05118680000305</t>
+    <t xml:space="preserve">3.0783805847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05118656158447</t>
   </si>
   <si>
     <t xml:space="preserve">3.05895614624023</t>
@@ -3905,10 +3905,10 @@
     <t xml:space="preserve">3.09780502319336</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13199210166931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23843789100647</t>
+    <t xml:space="preserve">3.13199186325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23843812942505</t>
   </si>
   <si>
     <t xml:space="preserve">3.24853849411011</t>
@@ -3917,22 +3917,22 @@
     <t xml:space="preserve">3.17161750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20269727706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09236621856689</t>
+    <t xml:space="preserve">3.20269703865051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09236598014832</t>
   </si>
   <si>
     <t xml:space="preserve">3.35498404502869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36275410652161</t>
+    <t xml:space="preserve">3.36275386810303</t>
   </si>
   <si>
     <t xml:space="preserve">3.37984728813171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40937232971191</t>
+    <t xml:space="preserve">3.40937256813049</t>
   </si>
   <si>
     <t xml:space="preserve">3.42335820198059</t>
@@ -3944,37 +3944,37 @@
     <t xml:space="preserve">3.59273934364319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51970314979553</t>
+    <t xml:space="preserve">3.51970338821411</t>
   </si>
   <si>
     <t xml:space="preserve">3.52747273445129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59740114212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6113862991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6937460899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63624906539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6098325252533</t>
+    <t xml:space="preserve">3.59740090370178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61138653755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69374632835388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63624930381775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60983276367188</t>
   </si>
   <si>
     <t xml:space="preserve">3.36430788040161</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30059599876404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38140153884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46686863899231</t>
+    <t xml:space="preserve">3.30059623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38140177726746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46686887741089</t>
   </si>
   <si>
     <t xml:space="preserve">3.51659536361694</t>
@@ -3983,7 +3983,7 @@
     <t xml:space="preserve">3.53524279594421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55078220367432</t>
+    <t xml:space="preserve">3.5507824420929</t>
   </si>
   <si>
     <t xml:space="preserve">3.56942987442017</t>
@@ -3992,13 +3992,13 @@
     <t xml:space="preserve">3.51193332672119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63948965072632</t>
+    <t xml:space="preserve">3.63948941230774</t>
   </si>
   <si>
     <t xml:space="preserve">3.6378333568573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65771174430847</t>
+    <t xml:space="preserve">3.65771150588989</t>
   </si>
   <si>
     <t xml:space="preserve">3.71403574943542</t>
@@ -4019,7 +4019,7 @@
     <t xml:space="preserve">3.64942908287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59310579299927</t>
+    <t xml:space="preserve">3.59310555458069</t>
   </si>
   <si>
     <t xml:space="preserve">3.59807538986206</t>
@@ -4037,13 +4037,13 @@
     <t xml:space="preserve">2.97686076164246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01993131637573</t>
+    <t xml:space="preserve">3.01993155479431</t>
   </si>
   <si>
     <t xml:space="preserve">3.0828812122345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97520422935486</t>
+    <t xml:space="preserve">2.97520399093628</t>
   </si>
   <si>
     <t xml:space="preserve">2.96692132949829</t>
@@ -4052,13 +4052,13 @@
     <t xml:space="preserve">3.01330518722534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98514342308044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00005269050598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96195149421692</t>
+    <t xml:space="preserve">2.98514366149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0000524520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96195125579834</t>
   </si>
   <si>
     <t xml:space="preserve">3.05968928337097</t>
@@ -4067,13 +4067,13 @@
     <t xml:space="preserve">3.03318405151367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04809331893921</t>
+    <t xml:space="preserve">3.04809308052063</t>
   </si>
   <si>
     <t xml:space="preserve">3.00999212265015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89734506607056</t>
+    <t xml:space="preserve">2.89734482765198</t>
   </si>
   <si>
     <t xml:space="preserve">2.90397143363953</t>
@@ -4094,13 +4094,13 @@
     <t xml:space="preserve">2.80457711219788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71512246131897</t>
+    <t xml:space="preserve">2.71512222290039</t>
   </si>
   <si>
     <t xml:space="preserve">2.70683932304382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69193005561829</t>
+    <t xml:space="preserve">2.69193029403687</t>
   </si>
   <si>
     <t xml:space="preserve">2.52792954444885</t>
@@ -4109,13 +4109,13 @@
     <t xml:space="preserve">2.64885926246643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71346545219421</t>
+    <t xml:space="preserve">2.71346569061279</t>
   </si>
   <si>
     <t xml:space="preserve">2.81120347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78138494491577</t>
+    <t xml:space="preserve">2.78138518333435</t>
   </si>
   <si>
     <t xml:space="preserve">2.79132437705994</t>
@@ -4130,7 +4130,7 @@
     <t xml:space="preserve">2.71843552589417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71677851676941</t>
+    <t xml:space="preserve">2.71677875518799</t>
   </si>
   <si>
     <t xml:space="preserve">2.7747585773468</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">2.83770871162415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84599137306213</t>
+    <t xml:space="preserve">2.84599161148071</t>
   </si>
   <si>
     <t xml:space="preserve">2.92385029792786</t>
@@ -4151,7 +4151,7 @@
     <t xml:space="preserve">2.97354745864868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95035576820374</t>
+    <t xml:space="preserve">2.95035552978516</t>
   </si>
   <si>
     <t xml:space="preserve">2.91225433349609</t>
@@ -4163,22 +4163,22 @@
     <t xml:space="preserve">2.93047666549683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98183012008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98017382621765</t>
+    <t xml:space="preserve">2.98183035850525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98017406463623</t>
   </si>
   <si>
     <t xml:space="preserve">2.92219400405884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93544626235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85427451133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75984954833984</t>
+    <t xml:space="preserve">2.93544602394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8542742729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75984978675842</t>
   </si>
   <si>
     <t xml:space="preserve">2.79960751533508</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">2.68696045875549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69358706474304</t>
+    <t xml:space="preserve">2.69358682632446</t>
   </si>
   <si>
     <t xml:space="preserve">2.64223313331604</t>
@@ -4238,25 +4238,25 @@
     <t xml:space="preserve">2.51799011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.536212682724</t>
+    <t xml:space="preserve">2.53621244430542</t>
   </si>
   <si>
     <t xml:space="preserve">2.46663618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44344449043274</t>
+    <t xml:space="preserve">2.44344425201416</t>
   </si>
   <si>
     <t xml:space="preserve">2.37221193313599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4268786907196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65051603317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67702126502991</t>
+    <t xml:space="preserve">2.42687892913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65051579475403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67702102661133</t>
   </si>
   <si>
     <t xml:space="preserve">2.58259654045105</t>
@@ -4268,10 +4268,10 @@
     <t xml:space="preserve">2.53124260902405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52461624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42190909385681</t>
+    <t xml:space="preserve">2.52461647987366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42190885543823</t>
   </si>
   <si>
     <t xml:space="preserve">2.48651528358459</t>
@@ -4298,7 +4298,7 @@
     <t xml:space="preserve">2.59750533103943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62235426902771</t>
+    <t xml:space="preserve">2.62235403060913</t>
   </si>
   <si>
     <t xml:space="preserve">2.60413193702698</t>
@@ -4322,10 +4322,10 @@
     <t xml:space="preserve">2.86587023735046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95366883277893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9983959197998</t>
+    <t xml:space="preserve">2.95366859436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99839615821838</t>
   </si>
   <si>
     <t xml:space="preserve">2.99342632293701</t>
@@ -4337,13 +4337,13 @@
     <t xml:space="preserve">2.98679995536804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00170922279358</t>
+    <t xml:space="preserve">3.00170946121216</t>
   </si>
   <si>
     <t xml:space="preserve">3.00833559036255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98348689079285</t>
+    <t xml:space="preserve">2.98348665237427</t>
   </si>
   <si>
     <t xml:space="preserve">3.00336575508118</t>
@@ -4352,22 +4352,22 @@
     <t xml:space="preserve">3.03484082221985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06631541252136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04478001594543</t>
+    <t xml:space="preserve">3.06631565093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04478025436401</t>
   </si>
   <si>
     <t xml:space="preserve">3.10441660881042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08619475364685</t>
+    <t xml:space="preserve">3.08619451522827</t>
   </si>
   <si>
     <t xml:space="preserve">2.94869875907898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91722393035889</t>
+    <t xml:space="preserve">2.91722416877747</t>
   </si>
   <si>
     <t xml:space="preserve">2.86255717277527</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">2.99176979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99673962593079</t>
+    <t xml:space="preserve">2.99673938751221</t>
   </si>
   <si>
     <t xml:space="preserve">3.03649711608887</t>
@@ -4406,22 +4406,22 @@
     <t xml:space="preserve">3.21375060081482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25185179710388</t>
+    <t xml:space="preserve">3.2518515586853</t>
   </si>
   <si>
     <t xml:space="preserve">3.22865962982178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22534656524658</t>
+    <t xml:space="preserve">3.225346326828</t>
   </si>
   <si>
     <t xml:space="preserve">3.26013445854187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23031640052795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20215439796448</t>
+    <t xml:space="preserve">3.23031616210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20215463638306</t>
   </si>
   <si>
     <t xml:space="preserve">3.20546746253967</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">3.18724536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23528575897217</t>
+    <t xml:space="preserve">3.23528599739075</t>
   </si>
   <si>
     <t xml:space="preserve">3.2816698551178</t>
@@ -4439,28 +4439,28 @@
     <t xml:space="preserve">3.29657912254333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34627652168274</t>
+    <t xml:space="preserve">3.34627628326416</t>
   </si>
   <si>
     <t xml:space="preserve">3.32805395126343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34793257713318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37443780899048</t>
+    <t xml:space="preserve">3.34793281555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37443804740906</t>
   </si>
   <si>
     <t xml:space="preserve">3.43904447555542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44235754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29160928726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29492259025574</t>
+    <t xml:space="preserve">3.44235777854919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29160952568054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29492235183716</t>
   </si>
   <si>
     <t xml:space="preserve">3.31811451911926</t>
@@ -4481,7 +4481,7 @@
     <t xml:space="preserve">3.49536776542664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43573117256165</t>
+    <t xml:space="preserve">3.43573093414307</t>
   </si>
   <si>
     <t xml:space="preserve">3.38437747955322</t>
@@ -4496,28 +4496,28 @@
     <t xml:space="preserve">3.34958958625793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38106417655945</t>
+    <t xml:space="preserve">3.38106393814087</t>
   </si>
   <si>
     <t xml:space="preserve">3.387690782547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39266061782837</t>
+    <t xml:space="preserve">3.39266037940979</t>
   </si>
   <si>
     <t xml:space="preserve">3.41088271141052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42082214355469</t>
+    <t xml:space="preserve">3.42082238197327</t>
   </si>
   <si>
     <t xml:space="preserve">3.42247867584229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37609481811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37775111198425</t>
+    <t xml:space="preserve">3.37609457969666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37775135040283</t>
   </si>
   <si>
     <t xml:space="preserve">3.34130644798279</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">3.13092184066772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02324461936951</t>
+    <t xml:space="preserve">3.02324485778809</t>
   </si>
   <si>
     <t xml:space="preserve">3.07625508308411</t>
@@ -4541,22 +4541,22 @@
     <t xml:space="preserve">3.13423490524292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10607314109802</t>
+    <t xml:space="preserve">3.1060733795166</t>
   </si>
   <si>
     <t xml:space="preserve">3.01164865493774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06465911865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10938620567322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07459831237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08453774452209</t>
+    <t xml:space="preserve">3.06465888023376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1093864440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07459807395935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08453798294067</t>
   </si>
   <si>
     <t xml:space="preserve">3.11269927024841</t>
@@ -4574,7 +4574,7 @@
     <t xml:space="preserve">3.18393230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20381116867065</t>
+    <t xml:space="preserve">3.20381093025208</t>
   </si>
   <si>
     <t xml:space="preserve">3.14914417266846</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">3.11932587623596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04146671295166</t>
+    <t xml:space="preserve">3.04146695137024</t>
   </si>
   <si>
     <t xml:space="preserve">3.07294201850891</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">3.0514063835144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08785080909729</t>
+    <t xml:space="preserve">3.08785104751587</t>
   </si>
   <si>
     <t xml:space="preserve">3.053062915802</t>
@@ -71086,7 +71086,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6496296296</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>214544</v>
@@ -71107,6 +71107,32 @@
         <v>1979</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6495138889</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>139801</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>6.15500020980835</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>6.1100001335144</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>6.17500019073486</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1962</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -38,136 +38,136 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2467474937439</t>
+    <t xml:space="preserve">4.24674654006958</t>
   </si>
   <si>
     <t xml:space="preserve">ANIM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33184623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13419580459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96948647499084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95301604270935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94203543663025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07380294799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93105483055115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8267388343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76085495948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67850160598755</t>
+    <t xml:space="preserve">4.33184671401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13419628143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96948623657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95301556587219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94203495979309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07380247116089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93105459213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82673907279968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76085567474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67850112915039</t>
   </si>
   <si>
     <t xml:space="preserve">3.73889374732971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40398597717285</t>
+    <t xml:space="preserve">3.40398550033569</t>
   </si>
   <si>
     <t xml:space="preserve">3.53300786018372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76909065246582</t>
+    <t xml:space="preserve">3.76909041404724</t>
   </si>
   <si>
     <t xml:space="preserve">3.79379725456238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79928708076477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88438653945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67575621604919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70595192909241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64006853103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57967567443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35731887817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45065259933472</t>
+    <t xml:space="preserve">3.79928779602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88438725471497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67575526237488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70595288276672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6400682926178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5796754360199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35731840133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4506528377533</t>
   </si>
   <si>
     <t xml:space="preserve">3.3765344619751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0663321018219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95652675628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19535446166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9839780330658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2420220375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20084452629089</t>
+    <t xml:space="preserve">3.06633186340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9565269947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19535422325134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98397779464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24202179908752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20084428787231</t>
   </si>
   <si>
     <t xml:space="preserve">3.48633980751038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38202452659607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31065058708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38751482963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26672840118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1129994392395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08554863929749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07182216644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06084156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15692186355591</t>
+    <t xml:space="preserve">3.38202428817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31065011024475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3875150680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26672863960266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11299967765808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08554840087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07182288169861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06084203720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15692162513733</t>
   </si>
   <si>
     <t xml:space="preserve">3.302414894104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43967294692993</t>
+    <t xml:space="preserve">3.43967247009277</t>
   </si>
   <si>
     <t xml:space="preserve">3.35182857513428</t>
@@ -176,103 +176,103 @@
     <t xml:space="preserve">3.28319907188416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22280526161194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25300264358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57692980766296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47261476516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46437954902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59065628051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56320476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61261653900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51653623580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43418288230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37104344367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45888924598694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53026294708252</t>
+    <t xml:space="preserve">3.2228057384491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25300312042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57693004608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47261500358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46437859535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.590656042099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56320405006409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61261701583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51653695106506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43418216705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37104463577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45888948440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53026270866394</t>
   </si>
   <si>
     <t xml:space="preserve">3.32986640930176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27221822738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09103894233704</t>
+    <t xml:space="preserve">3.27221846580505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09103918075562</t>
   </si>
   <si>
     <t xml:space="preserve">3.23653149604797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34084749221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28594470024109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31888556480408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23927664756775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4259467124939</t>
+    <t xml:space="preserve">3.34084725379944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28594374656677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31888580322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23927688598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42594695091248</t>
   </si>
   <si>
     <t xml:space="preserve">3.41771149635315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4094762802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41496586799622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44241762161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46163368225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44790863990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49732041358948</t>
+    <t xml:space="preserve">3.40947604179382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41496634483337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44241786003113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46163392066956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44790816307068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49732112884521</t>
   </si>
   <si>
     <t xml:space="preserve">3.39300537109375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37378931045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26123833656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26947331428528</t>
+    <t xml:space="preserve">3.37378859519958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26123809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26947379112244</t>
   </si>
   <si>
     <t xml:space="preserve">3.15417742729187</t>
@@ -281,70 +281,70 @@
     <t xml:space="preserve">3.16241264343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01966524124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94829082489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82201409339905</t>
+    <t xml:space="preserve">3.0196647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94829106330872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82201433181763</t>
   </si>
   <si>
     <t xml:space="preserve">2.93182015419006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0690770149231</t>
+    <t xml:space="preserve">3.06907725334167</t>
   </si>
   <si>
     <t xml:space="preserve">3.00044870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91809415817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8741717338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.852210521698</t>
+    <t xml:space="preserve">2.91809391975403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87417149543762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85221028327942</t>
   </si>
   <si>
     <t xml:space="preserve">2.89064288139343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97133874893188</t>
+    <t xml:space="preserve">2.97133922576904</t>
   </si>
   <si>
     <t xml:space="preserve">3.06356263160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23648285865784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24224662780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29988622665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17884302139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15866875648499</t>
+    <t xml:space="preserve">3.2364821434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2422468662262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29988694190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17884254455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15866851806641</t>
   </si>
   <si>
     <t xml:space="preserve">3.04050755500793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97998452186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96269297599792</t>
+    <t xml:space="preserve">2.979984998703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9626932144165</t>
   </si>
   <si>
     <t xml:space="preserve">3.02321457862854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00015926361084</t>
+    <t xml:space="preserve">3.00015902519226</t>
   </si>
   <si>
     <t xml:space="preserve">2.95692849159241</t>
@@ -359,13 +359,13 @@
     <t xml:space="preserve">2.66988205909729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61454749107361</t>
+    <t xml:space="preserve">2.61454725265503</t>
   </si>
   <si>
     <t xml:space="preserve">2.54768514633179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70331287384033</t>
+    <t xml:space="preserve">2.70331263542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.75288367271423</t>
@@ -377,46 +377,46 @@
     <t xml:space="preserve">2.92234468460083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96845674514771</t>
+    <t xml:space="preserve">2.96845698356628</t>
   </si>
   <si>
     <t xml:space="preserve">2.53615713119507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26179099082947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49004554748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4197244644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42664122581482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49235081672668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36900162696838</t>
+    <t xml:space="preserve">2.26179122924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49004530906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41972422599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4266414642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49235057830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3690013885498</t>
   </si>
   <si>
     <t xml:space="preserve">2.28830575942993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29752779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30559754371643</t>
+    <t xml:space="preserve">2.297527551651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30559730529785</t>
   </si>
   <si>
     <t xml:space="preserve">2.35747313499451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43240523338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61108899116516</t>
+    <t xml:space="preserve">2.4324049949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61108875274658</t>
   </si>
   <si>
     <t xml:space="preserve">2.59379720687866</t>
@@ -425,13 +425,13 @@
     <t xml:space="preserve">2.68025732040405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59725522994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60647821426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56958818435669</t>
+    <t xml:space="preserve">2.59725546836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60647797584534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56958794593811</t>
   </si>
   <si>
     <t xml:space="preserve">2.62838077545166</t>
@@ -443,28 +443,28 @@
     <t xml:space="preserve">2.59494972229004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6168532371521</t>
+    <t xml:space="preserve">2.61685347557068</t>
   </si>
   <si>
     <t xml:space="preserve">2.54653239250183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63414573669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58226895332336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4035849571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41511344909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4381697177887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55114364624023</t>
+    <t xml:space="preserve">2.63414525985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58226871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40358543395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4151132106781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43816947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55114388465881</t>
   </si>
   <si>
     <t xml:space="preserve">2.58572769165039</t>
@@ -473,19 +473,19 @@
     <t xml:space="preserve">2.65143728256226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65489530563354</t>
+    <t xml:space="preserve">2.65489506721497</t>
   </si>
   <si>
     <t xml:space="preserve">2.604172706604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54307436943054</t>
+    <t xml:space="preserve">2.54307413101196</t>
   </si>
   <si>
     <t xml:space="preserve">2.41857147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37015390396118</t>
+    <t xml:space="preserve">2.37015414237976</t>
   </si>
   <si>
     <t xml:space="preserve">2.39321041107178</t>
@@ -497,16 +497,16 @@
     <t xml:space="preserve">2.50964283943176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46122527122498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4485445022583</t>
+    <t xml:space="preserve">2.4612250328064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44854426383972</t>
   </si>
   <si>
     <t xml:space="preserve">2.50733709335327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50157308578491</t>
+    <t xml:space="preserve">2.50157332420349</t>
   </si>
   <si>
     <t xml:space="preserve">2.49696230888367</t>
@@ -515,10 +515,10 @@
     <t xml:space="preserve">2.51540684700012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53039312362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57304692268372</t>
+    <t xml:space="preserve">2.53039336204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57304716110229</t>
   </si>
   <si>
     <t xml:space="preserve">2.66181230545044</t>
@@ -530,52 +530,52 @@
     <t xml:space="preserve">2.73789715766907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83012127876282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7909255027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67449355125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6560480594635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64797902107239</t>
+    <t xml:space="preserve">2.83012080192566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79092574119568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67449283599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65604829788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64797878265381</t>
   </si>
   <si>
     <t xml:space="preserve">2.65720105171204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64567351341248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52001786231995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51886534690857</t>
+    <t xml:space="preserve">2.64567375183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5200183391571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51886510848999</t>
   </si>
   <si>
     <t xml:space="preserve">2.49580931663513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52117109298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52462911605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54192137718201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47275352478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46929526329041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39436292648315</t>
+    <t xml:space="preserve">2.5211706161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52462887763977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54192161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47275328636169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46929550170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39436316490173</t>
   </si>
   <si>
     <t xml:space="preserve">2.32173657417297</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">2.32519507408142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24795770645142</t>
+    <t xml:space="preserve">2.24795722961426</t>
   </si>
   <si>
     <t xml:space="preserve">2.26524949073792</t>
@@ -593,46 +593,46 @@
     <t xml:space="preserve">2.3263475894928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38629293441772</t>
+    <t xml:space="preserve">2.3862931728363</t>
   </si>
   <si>
     <t xml:space="preserve">2.4439332485199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44623875617981</t>
+    <t xml:space="preserve">2.44623851776123</t>
   </si>
   <si>
     <t xml:space="preserve">2.5707414150238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57996320724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56267142295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55806064605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50387835502625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50503158569336</t>
+    <t xml:space="preserve">2.57996344566345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56267166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55806040763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5038788318634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50503134727478</t>
   </si>
   <si>
     <t xml:space="preserve">2.38168215751648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60993647575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59956073760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55344891548157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70907688140869</t>
+    <t xml:space="preserve">2.60993623733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59956097602844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55344915390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70907735824585</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
@@ -641,31 +641,31 @@
     <t xml:space="preserve">2.58111572265625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8013014793396</t>
+    <t xml:space="preserve">2.80130100250244</t>
   </si>
   <si>
     <t xml:space="preserve">2.81282901763916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72291111946106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78285646438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82551026344299</t>
+    <t xml:space="preserve">2.72291088104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78285622596741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82551002502441</t>
   </si>
   <si>
     <t xml:space="preserve">2.92522692680359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96557474136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91081666946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00592303276062</t>
+    <t xml:space="preserve">2.96557402610779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91081690788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00592255592346</t>
   </si>
   <si>
     <t xml:space="preserve">3.03474283218384</t>
@@ -674,22 +674,22 @@
     <t xml:space="preserve">2.9972767829895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98574876785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94828271865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93963694572449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97422122955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99151349067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01456904411316</t>
+    <t xml:space="preserve">2.98574829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94828248023987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93963646888733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97422099113464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99151277542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.014568567276</t>
   </si>
   <si>
     <t xml:space="preserve">3.03186058998108</t>
@@ -698,73 +698,73 @@
     <t xml:space="preserve">3.16155099868774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13849472999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11255693435669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12984848022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2047803401947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16443204879761</t>
+    <t xml:space="preserve">3.13849496841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11255669593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12984871864319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20478010177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16443228721619</t>
   </si>
   <si>
     <t xml:space="preserve">3.19613456726074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19901657104492</t>
+    <t xml:space="preserve">3.1990168094635</t>
   </si>
   <si>
     <t xml:space="preserve">3.12408494949341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14137721061707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08373689651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30276870727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26242089271545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18748903274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28547596931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22783637046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17596054077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24801015853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26818418502808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23936486244202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09238243103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10102844238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05491662025452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08085417747498</t>
+    <t xml:space="preserve">3.14137649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08373641967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30276846885681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26242065429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18748879432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28547620773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22783660888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17596077919006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2480103969574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26818442344666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23936462402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09238290786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10102820396423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05491709709167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08085441589355</t>
   </si>
   <si>
     <t xml:space="preserve">3.11832070350647</t>
@@ -773,28 +773,28 @@
     <t xml:space="preserve">3.15002274513245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01168727874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92810893058777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95404672622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78516173362732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91369915008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98863077163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00304079055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0260968208313</t>
+    <t xml:space="preserve">3.01168704032898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92810845375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95404696464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7851619720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91369867324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98863101005554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00304102897644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02609705924988</t>
   </si>
   <si>
     <t xml:space="preserve">3.07797288894653</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">3.05779886245728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18172430992126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17019701004028</t>
+    <t xml:space="preserve">3.18172454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17019653320312</t>
   </si>
   <si>
     <t xml:space="preserve">3.23360061645508</t>
@@ -815,22 +815,22 @@
     <t xml:space="preserve">3.24512887001038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25089240074158</t>
+    <t xml:space="preserve">3.250892162323</t>
   </si>
   <si>
     <t xml:space="preserve">3.27106714248657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27394890785217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28259468078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25665616989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18460607528687</t>
+    <t xml:space="preserve">3.27394866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28259491920471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25665593147278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1846067905426</t>
   </si>
   <si>
     <t xml:space="preserve">3.29412221908569</t>
@@ -839,19 +839,19 @@
     <t xml:space="preserve">3.10391116142273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34023451805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44398665428162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43245816230774</t>
+    <t xml:space="preserve">3.34023427963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4439868927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4324586391449</t>
   </si>
   <si>
     <t xml:space="preserve">3.46415996551514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45839595794678</t>
+    <t xml:space="preserve">3.45839667320251</t>
   </si>
   <si>
     <t xml:space="preserve">3.49298048019409</t>
@@ -860,124 +860,124 @@
     <t xml:space="preserve">3.44686818122864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50450873374939</t>
+    <t xml:space="preserve">3.50450825691223</t>
   </si>
   <si>
     <t xml:space="preserve">3.60249614715576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51603627204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46992421150208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44110488891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42381286621094</t>
+    <t xml:space="preserve">3.51603603363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46992444992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44110441207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42381262779236</t>
   </si>
   <si>
     <t xml:space="preserve">3.41228437423706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39499282836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37193655967712</t>
+    <t xml:space="preserve">3.39499306678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37193608283997</t>
   </si>
   <si>
     <t xml:space="preserve">3.4893524646759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49236226081848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59472560882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72117352485657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7151517868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58870339393616</t>
+    <t xml:space="preserve">3.49236249923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5947253704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72117280960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71515250205994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58870363235474</t>
   </si>
   <si>
     <t xml:space="preserve">3.4682776927948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41107559204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49838447570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54053282737732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50440549850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51644897460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54956555366516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70913028717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72418308258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64891719818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7512788772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72719407081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76332211494446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73923707008362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74525761604309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71214127540588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70310950279236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75730061531067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7753643989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77837514877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84159922599792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85966372489929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82654595375061</t>
+    <t xml:space="preserve">3.41107583045959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49838471412659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54053330421448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50440573692322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5164487361908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54956483840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70913052558899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72418427467346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64891695976257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75127935409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7271945476532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76332187652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73923659324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74525809288025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71214151382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70310926437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75730037689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77536416053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77837538719177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8415994644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85966300964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82654571533203</t>
   </si>
   <si>
     <t xml:space="preserve">4.09750509262085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14266538619995</t>
+    <t xml:space="preserve">4.14266490936279</t>
   </si>
   <si>
     <t xml:space="preserve">4.19685649871826</t>
@@ -992,22 +992,22 @@
     <t xml:space="preserve">4.22094202041626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19986772537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24502754211426</t>
+    <t xml:space="preserve">4.19986724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2450270652771</t>
   </si>
   <si>
     <t xml:space="preserve">4.2691125869751</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26309156417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21492147445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15470790863037</t>
+    <t xml:space="preserve">4.26309061050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21492195129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15470743179321</t>
   </si>
   <si>
     <t xml:space="preserve">4.14567613601685</t>
@@ -1016,10 +1016,10 @@
     <t xml:space="preserve">4.13664388656616</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22395324707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22696399688721</t>
+    <t xml:space="preserve">4.22395372390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22696352005005</t>
   </si>
   <si>
     <t xml:space="preserve">4.33534717559814</t>
@@ -1028,31 +1028,31 @@
     <t xml:space="preserve">4.25104856491089</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28717660903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11857938766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25405979156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09449434280396</t>
+    <t xml:space="preserve">4.28717613220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11858034133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25405931472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09449481964111</t>
   </si>
   <si>
     <t xml:space="preserve">4.08847284317017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04030227661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05234575271606</t>
+    <t xml:space="preserve">4.04030275344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05234479904175</t>
   </si>
   <si>
     <t xml:space="preserve">3.95901489257812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86267256736755</t>
+    <t xml:space="preserve">3.86267280578613</t>
   </si>
   <si>
     <t xml:space="preserve">3.86568450927734</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.94396162033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94697260856628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95600438117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98008966445923</t>
+    <t xml:space="preserve">3.94697213172913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95600414276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98009014129639</t>
   </si>
   <si>
     <t xml:space="preserve">3.97406840324402</t>
@@ -1076,34 +1076,34 @@
     <t xml:space="preserve">4.07342004776001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06438779830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98912143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9620246887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01320648193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03428220748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00417470932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00116348266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90783405303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88976955413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95299339294434</t>
+    <t xml:space="preserve">4.06438827514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98912167549133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96202564239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01320600509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0342812538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00417423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00116395950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90783381462097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88976979255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95299363136292</t>
   </si>
   <si>
     <t xml:space="preserve">4.0101957321167</t>
@@ -1112,244 +1112,244 @@
     <t xml:space="preserve">4.11255884170532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15771865844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06739807128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98611068725586</t>
+    <t xml:space="preserve">4.15771770477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06739902496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9861114025116</t>
   </si>
   <si>
     <t xml:space="preserve">3.93191933631897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90181231498718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87471628189087</t>
+    <t xml:space="preserve">3.90181255340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87471652030945</t>
   </si>
   <si>
     <t xml:space="preserve">3.85364174842834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82353472709656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579129219055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84762096405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83256793022156</t>
+    <t xml:space="preserve">3.82353544235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579105377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84762072563171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83256840705872</t>
   </si>
   <si>
     <t xml:space="preserve">3.88073778152466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88374805450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92589807510376</t>
+    <t xml:space="preserve">3.88374757766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92589735984802</t>
   </si>
   <si>
     <t xml:space="preserve">3.92890858650208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88675999641418</t>
+    <t xml:space="preserve">3.88675904273987</t>
   </si>
   <si>
     <t xml:space="preserve">3.9138548374176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91084456443787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84460997581482</t>
+    <t xml:space="preserve">3.91084504127502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84460973739624</t>
   </si>
   <si>
     <t xml:space="preserve">3.82052516937256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69106602668762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70611929893494</t>
+    <t xml:space="preserve">3.69106674194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70611977577209</t>
   </si>
   <si>
     <t xml:space="preserve">3.55558681488037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47429895401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33580827713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40204286575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52246975898743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54354429244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53150105476379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57365036010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60074639320374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57666182518005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53752326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55257606506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50139474868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45021390914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51042675971985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48634123802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43817138671875</t>
+    <t xml:space="preserve">3.47429919242859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33580851554871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40204262733459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52246928215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54354405403137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53150153160095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.573650598526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60074615478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57666158676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5375235080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5525758266449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50139451026917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45021367073059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51042652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48634147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43817210197449</t>
   </si>
   <si>
     <t xml:space="preserve">3.40806484222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53451156616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60977864265442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35387253761292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42612814903259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44419264793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32376575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39000082015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61278891563416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73020482063293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66698050498962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64590668678284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.633864402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81450343132019</t>
+    <t xml:space="preserve">3.53451228141785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60977816581726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35387229919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42612838745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44419240951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32376599311829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39000058174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61278915405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73020458221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6669807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64590716362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63386416435242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81450390815735</t>
   </si>
   <si>
     <t xml:space="preserve">3.86869502067566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93492937088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04331398010254</t>
+    <t xml:space="preserve">3.93492960929871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04331350326538</t>
   </si>
   <si>
     <t xml:space="preserve">3.99213194847107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9831006526947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06137752532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12460088729858</t>
+    <t xml:space="preserve">3.98310041427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06137704849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12460136413574</t>
   </si>
   <si>
     <t xml:space="preserve">4.160728931427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07040929794312</t>
+    <t xml:space="preserve">4.07040882110596</t>
   </si>
   <si>
     <t xml:space="preserve">4.08245229721069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80848240852356</t>
+    <t xml:space="preserve">3.8084819316864</t>
   </si>
   <si>
     <t xml:space="preserve">3.89880228042603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91987681388855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78439593315125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77235436439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79945063591003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73622584342957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75429081916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76633310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63988447189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56160807609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6699914932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96503663063049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79342937469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74224805831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79164934158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77612233161926</t>
+    <t xml:space="preserve">3.91987705230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78439569473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7723536491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7994499206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73622632026672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75429034233093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76633238792419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63988518714905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56160831451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66999173164368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96503615379333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79342913627625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74224758148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79164910316467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77612257003784</t>
   </si>
   <si>
     <t xml:space="preserve">3.78854370117188</t>
@@ -1358,52 +1358,52 @@
     <t xml:space="preserve">3.70469880104065</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58359003067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55914330482483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55258846282959</t>
+    <t xml:space="preserve">3.58358955383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55914282798767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55258870124817</t>
   </si>
   <si>
     <t xml:space="preserve">3.51326107978821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61157989501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58536124229431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76888966560364</t>
+    <t xml:space="preserve">3.61157965660095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58536076545715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76888990402222</t>
   </si>
   <si>
     <t xml:space="preserve">3.89998197555542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342737197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85082173347473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81149458885193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63779830932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75578045845032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7393946647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86065340042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099006652832</t>
+    <t xml:space="preserve">3.8934268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85082268714905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81149482727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63779854774475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75578141212463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73939418792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8606538772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099054336548</t>
   </si>
   <si>
     <t xml:space="preserve">3.81804919242859</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">3.96552801132202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98846888542175</t>
+    <t xml:space="preserve">3.98846840858459</t>
   </si>
   <si>
     <t xml:space="preserve">3.93275499343872</t>
@@ -1421,121 +1421,121 @@
     <t xml:space="preserve">3.86720895767212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84426712989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91309118270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8213267326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03107357025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04418277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02451848983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98191428184509</t>
+    <t xml:space="preserve">3.84426760673523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91309070587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82132625579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03107309341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04418230056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0245189666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98191356658936</t>
   </si>
   <si>
     <t xml:space="preserve">3.90653657913208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99830102920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7754442691803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76561212539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71973085403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71645331382751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56897473335266</t>
+    <t xml:space="preserve">3.99830055236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77544498443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76561188697815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71972990036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71645307540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56897497177124</t>
   </si>
   <si>
     <t xml:space="preserve">3.50670623779297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46737861633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27467370033264</t>
+    <t xml:space="preserve">3.46737885475159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27467346191406</t>
   </si>
   <si>
     <t xml:space="preserve">2.93645668029785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03477621078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19077491760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42149686813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41494226455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33628678321838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3166229724884</t>
+    <t xml:space="preserve">3.03477597236633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19077444076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42149662971497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41494178771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33628702163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31662321090698</t>
   </si>
   <si>
     <t xml:space="preserve">3.35595035552979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21174955368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30023646354675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32645463943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39855575561523</t>
+    <t xml:space="preserve">3.211749792099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30023670196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32645487785339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39855527877808</t>
   </si>
   <si>
     <t xml:space="preserve">3.33956384658813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29040479660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27729535102844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28057312965393</t>
+    <t xml:space="preserve">3.29040503501892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27729558944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28057289123535</t>
   </si>
   <si>
     <t xml:space="preserve">3.18290948867798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12260746955872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07148122787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01511192321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89975070953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01904487609863</t>
+    <t xml:space="preserve">3.12260699272156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07148170471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01511168479919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89975094795227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01904463768005</t>
   </si>
   <si>
     <t xml:space="preserve">3.01380085945129</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">3.04919576644897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97971725463867</t>
+    <t xml:space="preserve">2.97971701622009</t>
   </si>
   <si>
     <t xml:space="preserve">3.02691006660461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1344051361084</t>
+    <t xml:space="preserve">3.13440561294556</t>
   </si>
   <si>
     <t xml:space="preserve">3.10425424575806</t>
@@ -1559,22 +1559,22 @@
     <t xml:space="preserve">3.04264116287231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00200247764587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00462460517883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98233914375305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98627185821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92072534561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92728066444397</t>
+    <t xml:space="preserve">3.00200271606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00462436676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98233866691589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98627209663391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92072558403015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92728018760681</t>
   </si>
   <si>
     <t xml:space="preserve">3.00069189071655</t>
@@ -1583,13 +1583,13 @@
     <t xml:space="preserve">3.01249027252197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03739738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95612072944641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92465877532959</t>
+    <t xml:space="preserve">3.03739762306213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95612049102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92465829849243</t>
   </si>
   <si>
     <t xml:space="preserve">2.84469270706177</t>
@@ -1613,10 +1613,10 @@
     <t xml:space="preserve">2.73064255714417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71228957176208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70049142837524</t>
+    <t xml:space="preserve">2.71229004859924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70049166679382</t>
   </si>
   <si>
     <t xml:space="preserve">2.77914643287659</t>
@@ -1628,31 +1628,31 @@
     <t xml:space="preserve">2.7371973991394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72146606445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6900041103363</t>
+    <t xml:space="preserve">2.72146654129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69000434875488</t>
   </si>
   <si>
     <t xml:space="preserve">2.63625645637512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64936566352844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.620525598526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67689490318298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7201554775238</t>
+    <t xml:space="preserve">2.64936590194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62052536010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67689514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72015523910522</t>
   </si>
   <si>
     <t xml:space="preserve">2.87615466117859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85124731063843</t>
+    <t xml:space="preserve">2.85124683380127</t>
   </si>
   <si>
     <t xml:space="preserve">2.86697816848755</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">2.93907880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91154956817627</t>
+    <t xml:space="preserve">2.91154932975769</t>
   </si>
   <si>
     <t xml:space="preserve">2.91679286956787</t>
@@ -1673,40 +1673,40 @@
     <t xml:space="preserve">2.94170045852661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99806952476501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04133057594299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99675917625427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99413681030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96267533302307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96005344390869</t>
+    <t xml:space="preserve">2.99807000160217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04133009910583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99675893783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99413704872131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96267509460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96005296707153</t>
   </si>
   <si>
     <t xml:space="preserve">2.91285991668701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77521419525146</t>
+    <t xml:space="preserve">2.77521395683289</t>
   </si>
   <si>
     <t xml:space="preserve">2.70704627037048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68869352340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70573496818542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74244117736816</t>
+    <t xml:space="preserve">2.68869376182556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.705735206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74244093894958</t>
   </si>
   <si>
     <t xml:space="preserve">2.64674377441406</t>
@@ -1715,19 +1715,19 @@
     <t xml:space="preserve">2.64150023460388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692907333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38193845748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46714806556702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44879484176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49074459075928</t>
+    <t xml:space="preserve">2.59692883491516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38193821907043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4671483039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44879531860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49074482917786</t>
   </si>
   <si>
     <t xml:space="preserve">2.4710807800293</t>
@@ -1736,7 +1736,7 @@
     <t xml:space="preserve">2.486811876297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4199550151825</t>
+    <t xml:space="preserve">2.41995525360107</t>
   </si>
   <si>
     <t xml:space="preserve">2.31639242172241</t>
@@ -1745,19 +1745,19 @@
     <t xml:space="preserve">2.25871229171753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20365357398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25215768814087</t>
+    <t xml:space="preserve">2.20365333557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25215744972229</t>
   </si>
   <si>
     <t xml:space="preserve">2.28493046760559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38587117195129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39242577552795</t>
+    <t xml:space="preserve">2.38587141036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39242553710938</t>
   </si>
   <si>
     <t xml:space="preserve">2.42519879341125</t>
@@ -1766,76 +1766,76 @@
     <t xml:space="preserve">2.45928263664246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54973578453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47239208221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44617366790771</t>
+    <t xml:space="preserve">2.54973602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47239184379578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44617342948914</t>
   </si>
   <si>
     <t xml:space="preserve">2.45797181129456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47501349449158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54842495918274</t>
+    <t xml:space="preserve">2.47501373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54842519760132</t>
   </si>
   <si>
     <t xml:space="preserve">2.43044233322144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40815687179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33998894691467</t>
+    <t xml:space="preserve">2.40815663337708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33998918533325</t>
   </si>
   <si>
     <t xml:space="preserve">2.28886342048645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27968668937683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25740098953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17612409591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18661141395569</t>
+    <t xml:space="preserve">2.27968692779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25740122795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17612433433533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18661165237427</t>
   </si>
   <si>
     <t xml:space="preserve">2.13155317306519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29410672187805</t>
+    <t xml:space="preserve">2.29410719871521</t>
   </si>
   <si>
     <t xml:space="preserve">2.35178756713867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39766955375671</t>
+    <t xml:space="preserve">2.39766931533813</t>
   </si>
   <si>
     <t xml:space="preserve">2.44748425483704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42388772964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40946769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40029120445251</t>
+    <t xml:space="preserve">2.4238874912262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40946817398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40029096603394</t>
   </si>
   <si>
     <t xml:space="preserve">2.21938443183899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19447708129883</t>
+    <t xml:space="preserve">2.19447731971741</t>
   </si>
   <si>
     <t xml:space="preserve">2.25477933883667</t>
@@ -1847,28 +1847,28 @@
     <t xml:space="preserve">2.32687973976135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26264500617981</t>
+    <t xml:space="preserve">2.26264476776123</t>
   </si>
   <si>
     <t xml:space="preserve">2.17743515968323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12893152236938</t>
+    <t xml:space="preserve">2.12893128395081</t>
   </si>
   <si>
     <t xml:space="preserve">2.14597320556641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12237668037415</t>
+    <t xml:space="preserve">2.12237644195557</t>
   </si>
   <si>
     <t xml:space="preserve">2.12368750572205</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10271263122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11713290214539</t>
+    <t xml:space="preserve">2.10271286964417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11713314056396</t>
   </si>
   <si>
     <t xml:space="preserve">2.14728403091431</t>
@@ -1880,25 +1880,25 @@
     <t xml:space="preserve">2.23904800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20758628845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36489653587341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34785437583923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37407279014587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25084638595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39504766464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35572028160095</t>
+    <t xml:space="preserve">2.20758605003357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36489629745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34785461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37407302856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25084662437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39504742622375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35572004318237</t>
   </si>
   <si>
     <t xml:space="preserve">2.41340017318726</t>
@@ -1907,16 +1907,16 @@
     <t xml:space="preserve">2.43306422233582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44486284255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44224047660828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43175339698792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38456034660339</t>
+    <t xml:space="preserve">2.44486260414124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44224071502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43175315856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38456010818481</t>
   </si>
   <si>
     <t xml:space="preserve">2.35309815406799</t>
@@ -1928,118 +1928,118 @@
     <t xml:space="preserve">2.35440897941589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37145090103149</t>
+    <t xml:space="preserve">2.37145113945007</t>
   </si>
   <si>
     <t xml:space="preserve">2.28755211830139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26788854598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31114864349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37931656837463</t>
+    <t xml:space="preserve">2.26788878440857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31114888191223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37931632995605</t>
   </si>
   <si>
     <t xml:space="preserve">2.40291285514832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40553522109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37014031410217</t>
+    <t xml:space="preserve">2.40553498268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37014007568359</t>
   </si>
   <si>
     <t xml:space="preserve">2.33605623245239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39898061752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37669467926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50123190879822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54318165779114</t>
+    <t xml:space="preserve">2.39898037910461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37669444084167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5012321472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54318141937256</t>
   </si>
   <si>
     <t xml:space="preserve">2.52613949775696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50385355949402</t>
+    <t xml:space="preserve">2.5038537979126</t>
   </si>
   <si>
     <t xml:space="preserve">2.49336647987366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42782068252563</t>
+    <t xml:space="preserve">2.42782044410706</t>
   </si>
   <si>
     <t xml:space="preserve">2.39635848999023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38718175888062</t>
+    <t xml:space="preserve">2.38718199729919</t>
   </si>
   <si>
     <t xml:space="preserve">2.37276196479797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37800550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33867788314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29935050010681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38062739372253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30459427833557</t>
+    <t xml:space="preserve">2.37800574302673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33867835998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29935073852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38062763214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30459475517273</t>
   </si>
   <si>
     <t xml:space="preserve">2.38849282264709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4566605091095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40160226821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34130001068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34392189979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38324952125549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32556867599487</t>
+    <t xml:space="preserve">2.45666098594666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40160202980042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34129977226257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34392166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38324928283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32556891441345</t>
   </si>
   <si>
     <t xml:space="preserve">2.30328321456909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30590486526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34523296356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32425832748413</t>
+    <t xml:space="preserve">2.30590510368347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34523272514343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32425808906555</t>
   </si>
   <si>
     <t xml:space="preserve">2.30983805656433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21545195579529</t>
+    <t xml:space="preserve">2.21545171737671</t>
   </si>
   <si>
     <t xml:space="preserve">2.19054412841797</t>
@@ -2048,109 +2048,109 @@
     <t xml:space="preserve">2.09091472625732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08698201179504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99783957004547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03978872299194</t>
+    <t xml:space="preserve">2.08698177337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99783945083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03978848457336</t>
   </si>
   <si>
     <t xml:space="preserve">1.9768648147583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9912850856781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97817552089691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98996293544769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99966990947723</t>
+    <t xml:space="preserve">1.99128484725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97817540168762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98996305465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99967014789581</t>
   </si>
   <si>
     <t xml:space="preserve">1.97470891475677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94420087337494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91923928260803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8984386920929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86376988887787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82632851600647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87625074386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87902426719666</t>
+    <t xml:space="preserve">1.94420051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91923952102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89843857288361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86377000808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82632839679718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87625098228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87902438640594</t>
   </si>
   <si>
     <t xml:space="preserve">1.83742225170135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9511342048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92755961418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89982533454895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92062628269196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9095321893692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90675890445709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88734447956085</t>
+    <t xml:space="preserve">1.95113444328308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9275598526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89982497692108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92062604427338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90953242778778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90675902366638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88734459877014</t>
   </si>
   <si>
     <t xml:space="preserve">1.88873136043549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88179767131805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02879190444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98302912712097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03156542778015</t>
+    <t xml:space="preserve">1.88179790973663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02879166603088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98302900791168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03156495094299</t>
   </si>
   <si>
     <t xml:space="preserve">1.98857617378235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95945453643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00660371780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0052170753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07178020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09396767616272</t>
+    <t xml:space="preserve">1.95945489406586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00660395622253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00521683692932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07177996635437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0939679145813</t>
   </si>
   <si>
     <t xml:space="preserve">2.14943718910217</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">2.25898909568787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26453590393066</t>
+    <t xml:space="preserve">2.26453614234924</t>
   </si>
   <si>
     <t xml:space="preserve">2.21461391448975</t>
@@ -2177,79 +2177,79 @@
     <t xml:space="preserve">2.24928212165833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31445860862732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30059170722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30891156196594</t>
+    <t xml:space="preserve">2.31445837020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30059123039246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30891132354736</t>
   </si>
   <si>
     <t xml:space="preserve">2.31307196617126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27424335479736</t>
+    <t xml:space="preserve">2.27424311637878</t>
   </si>
   <si>
     <t xml:space="preserve">2.2215473651886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24789571762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24650883674622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24512195587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28811049461365</t>
+    <t xml:space="preserve">2.24789547920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24650859832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.245121717453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28811073303223</t>
   </si>
   <si>
     <t xml:space="preserve">2.32277894020081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37824845314026</t>
+    <t xml:space="preserve">2.37824821472168</t>
   </si>
   <si>
     <t xml:space="preserve">2.30613803863525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23125457763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1868793964386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17162489891052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17439818382263</t>
+    <t xml:space="preserve">2.23125433921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18687891960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1716251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17439866065979</t>
   </si>
   <si>
     <t xml:space="preserve">2.22432088851929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12170267105103</t>
+    <t xml:space="preserve">2.12170243263245</t>
   </si>
   <si>
     <t xml:space="preserve">2.10783529281616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12863612174988</t>
+    <t xml:space="preserve">2.12863636016846</t>
   </si>
   <si>
     <t xml:space="preserve">2.09812808036804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12724924087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1771719455719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19103932380676</t>
+    <t xml:space="preserve">2.12724947929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17717218399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19103956222534</t>
   </si>
   <si>
     <t xml:space="preserve">2.23680138587952</t>
@@ -2258,61 +2258,61 @@
     <t xml:space="preserve">2.20629334449768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19935941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18549227714539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25760269165039</t>
+    <t xml:space="preserve">2.19935989379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18549251556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25760245323181</t>
   </si>
   <si>
     <t xml:space="preserve">2.25621581077576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23957490921021</t>
+    <t xml:space="preserve">2.23957514762878</t>
   </si>
   <si>
     <t xml:space="preserve">2.35606050491333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38102197647095</t>
+    <t xml:space="preserve">2.38102173805237</t>
   </si>
   <si>
     <t xml:space="preserve">2.36715459823608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38379549980164</t>
+    <t xml:space="preserve">2.38379526138306</t>
   </si>
   <si>
     <t xml:space="preserve">2.43510484695435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51553535461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49889421463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42955756187439</t>
+    <t xml:space="preserve">2.51553511619568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49889445304871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42955732345581</t>
   </si>
   <si>
     <t xml:space="preserve">2.42817068099976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44897174835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45867919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766240119934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3879554271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37131452560425</t>
+    <t xml:space="preserve">2.44897198677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45867896080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38795566558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37131476402283</t>
   </si>
   <si>
     <t xml:space="preserve">2.382408618927</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">2.41707682609558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42401051521301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37408804893494</t>
+    <t xml:space="preserve">2.42401075363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37408828735352</t>
   </si>
   <si>
     <t xml:space="preserve">2.32693934440613</t>
@@ -2333,16 +2333,16 @@
     <t xml:space="preserve">2.2992045879364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31723165512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34496665000916</t>
+    <t xml:space="preserve">2.31723189353943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34496641159058</t>
   </si>
   <si>
     <t xml:space="preserve">2.34635353088379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4115297794342</t>
+    <t xml:space="preserve">2.41153001785278</t>
   </si>
   <si>
     <t xml:space="preserve">2.46977281570435</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">2.48502707481384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56961798667908</t>
+    <t xml:space="preserve">2.5696177482605</t>
   </si>
   <si>
     <t xml:space="preserve">2.61537981033325</t>
@@ -2363,10 +2363,10 @@
     <t xml:space="preserve">2.73879909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70690417289734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74711966514587</t>
+    <t xml:space="preserve">2.70690441131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74711942672729</t>
   </si>
   <si>
     <t xml:space="preserve">2.72770524024963</t>
@@ -2375,22 +2375,22 @@
     <t xml:space="preserve">2.75266647338867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76237344741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7859480381012</t>
+    <t xml:space="preserve">2.76237368583679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594779968262</t>
   </si>
   <si>
     <t xml:space="preserve">2.77208065986633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69581031799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70413112640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7207715511322</t>
+    <t xml:space="preserve">2.69581055641174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70413088798523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72077178955078</t>
   </si>
   <si>
     <t xml:space="preserve">2.80120205879211</t>
@@ -2408,115 +2408,115 @@
     <t xml:space="preserve">2.94680905342102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01614594459534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02723979949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04804062843323</t>
+    <t xml:space="preserve">3.01614546775818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02724003791809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04804086685181</t>
   </si>
   <si>
     <t xml:space="preserve">3.0799355506897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13679194450378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14649891853333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17562007904053</t>
+    <t xml:space="preserve">3.13679170608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14649868011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17562031745911</t>
   </si>
   <si>
     <t xml:space="preserve">3.14511203765869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23108959197998</t>
+    <t xml:space="preserve">3.2310893535614</t>
   </si>
   <si>
     <t xml:space="preserve">3.24773049354553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26298427581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2615978717804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22554278373718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18532752990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18394041061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25605082511902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21028852462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25327730178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22831654548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20196795463562</t>
+    <t xml:space="preserve">3.26298451423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26159763336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2255425453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18532729148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18394064903259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2560510635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21028900146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25327706336975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22831583023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2019681930542</t>
   </si>
   <si>
     <t xml:space="preserve">3.24218344688416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26575803756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21306180953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19919466972351</t>
+    <t xml:space="preserve">3.26575779914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21306204795837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19919490814209</t>
   </si>
   <si>
     <t xml:space="preserve">3.20890164375305</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22415590286255</t>
+    <t xml:space="preserve">3.22415614128113</t>
   </si>
   <si>
     <t xml:space="preserve">3.1908745765686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20335483551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06606841087341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09241652488708</t>
+    <t xml:space="preserve">3.20335459709167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06606817245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09241628646851</t>
   </si>
   <si>
     <t xml:space="preserve">3.14788556098938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2061288356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17839407920837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17145991325378</t>
+    <t xml:space="preserve">3.20612835884094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17839360237122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17146015167236</t>
   </si>
   <si>
     <t xml:space="preserve">3.03694701194763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15343260765076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16868686676025</t>
+    <t xml:space="preserve">3.15343236923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16868710517883</t>
   </si>
   <si>
     <t xml:space="preserve">2.97038340568542</t>
@@ -2525,13 +2525,13 @@
     <t xml:space="preserve">3.03555989265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14095211029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12985801696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14927196502686</t>
+    <t xml:space="preserve">3.14095187187195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12985777854919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14927220344543</t>
   </si>
   <si>
     <t xml:space="preserve">3.17007327079773</t>
@@ -2543,43 +2543,43 @@
     <t xml:space="preserve">3.10073661804199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07854866981506</t>
+    <t xml:space="preserve">3.07854890823364</t>
   </si>
   <si>
     <t xml:space="preserve">3.11044383049011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08964276313782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28239870071411</t>
+    <t xml:space="preserve">3.08964252471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28239893913269</t>
   </si>
   <si>
     <t xml:space="preserve">3.34202837944031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34896159172058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93987512588501</t>
+    <t xml:space="preserve">3.34896183013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93987536430359</t>
   </si>
   <si>
     <t xml:space="preserve">2.97315716743469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86360549926758</t>
+    <t xml:space="preserve">2.863605260849</t>
   </si>
   <si>
     <t xml:space="preserve">2.73741245269775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58487153053284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55158996582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49473428726196</t>
+    <t xml:space="preserve">2.58487176895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55159020423889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49473404884338</t>
   </si>
   <si>
     <t xml:space="preserve">2.29227089881897</t>
@@ -2588,16 +2588,16 @@
     <t xml:space="preserve">2.07039356231689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9566810131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99134957790375</t>
+    <t xml:space="preserve">1.95668148994446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99134945869446</t>
   </si>
   <si>
     <t xml:space="preserve">1.69042837619781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7847261428833</t>
+    <t xml:space="preserve">1.78472650051117</t>
   </si>
   <si>
     <t xml:space="preserve">1.65576016902924</t>
@@ -2630,16 +2630,16 @@
     <t xml:space="preserve">1.68904173374176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69736218452454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72371017932892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75421833992004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78888654708862</t>
+    <t xml:space="preserve">1.69736194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72371006011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75421822071075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78888618946075</t>
   </si>
   <si>
     <t xml:space="preserve">2.02185773849487</t>
@@ -2648,19 +2648,19 @@
     <t xml:space="preserve">2.06207299232483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05375242233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99412286281586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609567642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96638834476471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94142711162567</t>
+    <t xml:space="preserve">2.05375266075134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99412298202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609543800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96638870239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94142723083496</t>
   </si>
   <si>
     <t xml:space="preserve">1.85960972309113</t>
@@ -2669,10 +2669,10 @@
     <t xml:space="preserve">1.86793041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92339992523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.901211977005</t>
+    <t xml:space="preserve">1.92339956760406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90121221542358</t>
   </si>
   <si>
     <t xml:space="preserve">2.14805054664612</t>
@@ -2684,16 +2684,16 @@
     <t xml:space="preserve">2.23818802833557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22570729255676</t>
+    <t xml:space="preserve">2.22570776939392</t>
   </si>
   <si>
     <t xml:space="preserve">2.13418316841125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28117704391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35744714736938</t>
+    <t xml:space="preserve">2.28117656707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35744738578796</t>
   </si>
   <si>
     <t xml:space="preserve">2.40043592453003</t>
@@ -2705,64 +2705,64 @@
     <t xml:space="preserve">2.30752491950989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48411726951599</t>
+    <t xml:space="preserve">2.48411750793457</t>
   </si>
   <si>
     <t xml:space="preserve">2.51219487190247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49150633811951</t>
+    <t xml:space="preserve">2.49150609970093</t>
   </si>
   <si>
     <t xml:space="preserve">2.49741721153259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45456218719482</t>
+    <t xml:space="preserve">2.45456194877625</t>
   </si>
   <si>
     <t xml:space="preserve">2.57130527496338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72647023200989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75750327110291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80774736404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86538004875183</t>
+    <t xml:space="preserve">2.72647047042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75750350952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80774712562561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86537981033325</t>
   </si>
   <si>
     <t xml:space="preserve">2.87572431564331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86833548545837</t>
+    <t xml:space="preserve">2.86833572387695</t>
   </si>
   <si>
     <t xml:space="preserve">2.97473430633545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20230960845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16979885101318</t>
+    <t xml:space="preserve">3.20230984687805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16979908943176</t>
   </si>
   <si>
     <t xml:space="preserve">3.14024353027344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93483471870422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93631267547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94222354888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99837827682495</t>
+    <t xml:space="preserve">2.93483448028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9363124370575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94222402572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99837851524353</t>
   </si>
   <si>
     <t xml:space="preserve">3.00281190872192</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">2.9584789276123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88606834411621</t>
+    <t xml:space="preserve">2.88606858253479</t>
   </si>
   <si>
     <t xml:space="preserve">2.92744588851929</t>
@@ -2780,40 +2780,40 @@
     <t xml:space="preserve">2.83582472801208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89050197601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88459062576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85946893692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82843565940857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86242437362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93779015541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99542307853699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03236722946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04418873786926</t>
+    <t xml:space="preserve">2.8905017375946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88459086418152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85946869850159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82843589782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86242461204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93779039382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99542284011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03236699104309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04418897628784</t>
   </si>
   <si>
     <t xml:space="preserve">3.01906704902649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92005681991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93040132522583</t>
+    <t xml:space="preserve">2.92005705833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93040156364441</t>
   </si>
   <si>
     <t xml:space="preserve">2.97916769981384</t>
@@ -2822,16 +2822,16 @@
     <t xml:space="preserve">2.98212313652039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99394536018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98951196670532</t>
+    <t xml:space="preserve">2.99394512176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98951172828674</t>
   </si>
   <si>
     <t xml:space="preserve">2.95404553413391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95552325248718</t>
+    <t xml:space="preserve">2.95552349090576</t>
   </si>
   <si>
     <t xml:space="preserve">2.94665694236755</t>
@@ -2843,13 +2843,13 @@
     <t xml:space="preserve">3.09591102600098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01758933067322</t>
+    <t xml:space="preserve">3.0175895690918</t>
   </si>
   <si>
     <t xml:space="preserve">2.99098968505859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93335723876953</t>
+    <t xml:space="preserve">2.93335676193237</t>
   </si>
   <si>
     <t xml:space="preserve">2.91857933998108</t>
@@ -2858,22 +2858,22 @@
     <t xml:space="preserve">2.75602555274963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81365823745728</t>
+    <t xml:space="preserve">2.81365871429443</t>
   </si>
   <si>
     <t xml:space="preserve">2.85503554344177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85355758666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89493536949158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87720227241516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9215350151062</t>
+    <t xml:space="preserve">2.85355806350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.894935131073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87720203399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92153477668762</t>
   </si>
   <si>
     <t xml:space="preserve">2.9629123210907</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">2.91266822814941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87424635887146</t>
+    <t xml:space="preserve">2.87424659729004</t>
   </si>
   <si>
     <t xml:space="preserve">2.84616899490356</t>
@@ -2891,13 +2891,13 @@
     <t xml:space="preserve">2.80479168891907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76784777641296</t>
+    <t xml:space="preserve">2.76784753799438</t>
   </si>
   <si>
     <t xml:space="preserve">2.75307011604309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78410315513611</t>
+    <t xml:space="preserve">2.78410291671753</t>
   </si>
   <si>
     <t xml:space="preserve">2.79888081550598</t>
@@ -2915,31 +2915,31 @@
     <t xml:space="preserve">2.76636981964111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79296970367432</t>
+    <t xml:space="preserve">2.79296946525574</t>
   </si>
   <si>
     <t xml:space="preserve">2.73681449890137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69987058639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79592537879944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74272561073303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75454759597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74715876579285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71612596511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70873713493347</t>
+    <t xml:space="preserve">2.69987082481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79592514038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74272584915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75454783439636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74715900421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71612620353699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70873737335205</t>
   </si>
   <si>
     <t xml:space="preserve">2.70725965499878</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">2.61268258094788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57573866844177</t>
+    <t xml:space="preserve">2.57573890686035</t>
   </si>
   <si>
     <t xml:space="preserve">2.52549457550049</t>
@@ -2963,13 +2963,13 @@
     <t xml:space="preserve">2.5846049785614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52697229385376</t>
+    <t xml:space="preserve">2.52697253227234</t>
   </si>
   <si>
     <t xml:space="preserve">2.47525072097778</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50037288665771</t>
+    <t xml:space="preserve">2.50037312507629</t>
   </si>
   <si>
     <t xml:space="preserve">2.43091797828674</t>
@@ -2978,19 +2978,19 @@
     <t xml:space="preserve">2.52992796897888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61120462417603</t>
+    <t xml:space="preserve">2.6112048625946</t>
   </si>
   <si>
     <t xml:space="preserve">2.54618334770203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55209469795227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67179298400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60972714424133</t>
+    <t xml:space="preserve">2.55209445953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67179322242737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60972738265991</t>
   </si>
   <si>
     <t xml:space="preserve">2.54322791099548</t>
@@ -2999,34 +2999,34 @@
     <t xml:space="preserve">2.52845001220703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47377324104309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6289381980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6570155620575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63632702827454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60677194595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53140592575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52253937721252</t>
+    <t xml:space="preserve">2.47377300262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62893843650818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65701532363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63632678985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60677170753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53140616416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52253913879395</t>
   </si>
   <si>
     <t xml:space="preserve">2.36441874504089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31713008880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37180733680725</t>
+    <t xml:space="preserve">2.31713032722473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37180781364441</t>
   </si>
   <si>
     <t xml:space="preserve">2.51662802696228</t>
@@ -3035,19 +3035,19 @@
     <t xml:space="preserve">2.58312749862671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64223766326904</t>
+    <t xml:space="preserve">2.64223790168762</t>
   </si>
   <si>
     <t xml:space="preserve">2.49298405647278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61563801765442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6525821685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63041567802429</t>
+    <t xml:space="preserve">2.61563849449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65258240699768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63041591644287</t>
   </si>
   <si>
     <t xml:space="preserve">2.71317028999329</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">2.75898122787476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68361520767212</t>
+    <t xml:space="preserve">2.6836154460907</t>
   </si>
   <si>
     <t xml:space="preserve">2.67031526565552</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">2.66440439224243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64519333839417</t>
+    <t xml:space="preserve">2.64519357681274</t>
   </si>
   <si>
     <t xml:space="preserve">2.68065977096558</t>
@@ -3092,16 +3092,16 @@
     <t xml:space="preserve">2.68213748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62598252296448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65849351882935</t>
+    <t xml:space="preserve">2.6259822845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65849328041077</t>
   </si>
   <si>
     <t xml:space="preserve">2.7205593585968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85651326179504</t>
+    <t xml:space="preserve">2.85651350021362</t>
   </si>
   <si>
     <t xml:space="preserve">2.92301273345947</t>
@@ -3116,10 +3116,10 @@
     <t xml:space="preserve">2.98064517974854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01463389396667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03975582122803</t>
+    <t xml:space="preserve">3.0146336555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03975605964661</t>
   </si>
   <si>
     <t xml:space="preserve">3.07374405860901</t>
@@ -3137,58 +3137,58 @@
     <t xml:space="preserve">3.02941131591797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89345741271973</t>
+    <t xml:space="preserve">2.89345765113831</t>
   </si>
   <si>
     <t xml:space="preserve">2.86390209197998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90675735473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87129068374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83434700965881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91710138320923</t>
+    <t xml:space="preserve">2.90675759315491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87129092216492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83434677124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91710162162781</t>
   </si>
   <si>
     <t xml:space="preserve">3.04714465141296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13285446166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10034418106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17718768119812</t>
+    <t xml:space="preserve">3.1328547000885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10034394264221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1771879196167</t>
   </si>
   <si>
     <t xml:space="preserve">3.10625505447388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13581037521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08408832550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00133371353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94517922401428</t>
+    <t xml:space="preserve">3.13581013679504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08408856391907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00133395195007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9451789855957</t>
   </si>
   <si>
     <t xml:space="preserve">2.9998562335968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97177863121033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93926811218262</t>
+    <t xml:space="preserve">2.97177839279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93926787376404</t>
   </si>
   <si>
     <t xml:space="preserve">3.08999991416931</t>
@@ -3206,13 +3206,13 @@
     <t xml:space="preserve">3.08852195739746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12694358825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24664235115051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20526528358459</t>
+    <t xml:space="preserve">3.12694382667542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24664211273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20526504516602</t>
   </si>
   <si>
     <t xml:space="preserve">3.21856474876404</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">3.33826375007629</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34121942520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31166386604309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26142024993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32496404647827</t>
+    <t xml:space="preserve">3.34121918678284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31166410446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26142048835754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32496380805969</t>
   </si>
   <si>
     <t xml:space="preserve">3.30131959915161</t>
@@ -3242,16 +3242,16 @@
     <t xml:space="preserve">3.2924530506134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28801941871643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31609702110291</t>
+    <t xml:space="preserve">3.28801965713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31609725952148</t>
   </si>
   <si>
     <t xml:space="preserve">3.29393076896667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27324223518372</t>
+    <t xml:space="preserve">3.27324175834656</t>
   </si>
   <si>
     <t xml:space="preserve">3.24516487121582</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">3.29540872573853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25107574462891</t>
+    <t xml:space="preserve">3.25107550621033</t>
   </si>
   <si>
     <t xml:space="preserve">3.28358626365662</t>
@@ -3281,22 +3281,22 @@
     <t xml:space="preserve">3.27915358543396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24073147773743</t>
+    <t xml:space="preserve">3.24073171615601</t>
   </si>
   <si>
     <t xml:space="preserve">3.27767539024353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28136968612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18531537055969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13433289527893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10329961776733</t>
+    <t xml:space="preserve">3.28136944770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18531560897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13433265686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10329937934875</t>
   </si>
   <si>
     <t xml:space="preserve">3.16314888000488</t>
@@ -3314,34 +3314,34 @@
     <t xml:space="preserve">3.15354347229004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1365487575531</t>
+    <t xml:space="preserve">3.13654923439026</t>
   </si>
   <si>
     <t xml:space="preserve">3.21043729782104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26511454582214</t>
+    <t xml:space="preserve">3.26511478424072</t>
   </si>
   <si>
     <t xml:space="preserve">3.22743153572083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23925375938416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24738121032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31979179382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33974146842957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41362953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32053017616272</t>
+    <t xml:space="preserve">3.23925352096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24738144874573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31979203224182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33974099159241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41362929344177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3205304145813</t>
   </si>
   <si>
     <t xml:space="preserve">3.32939720153809</t>
@@ -3350,28 +3350,28 @@
     <t xml:space="preserve">3.31535816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38761758804321</t>
+    <t xml:space="preserve">3.38761734962463</t>
   </si>
   <si>
     <t xml:space="preserve">3.31846618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33789086341858</t>
+    <t xml:space="preserve">3.337890625</t>
   </si>
   <si>
     <t xml:space="preserve">3.33322882652283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33944487571716</t>
+    <t xml:space="preserve">3.33944439888</t>
   </si>
   <si>
     <t xml:space="preserve">3.33633685112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41325736045837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37751650810242</t>
+    <t xml:space="preserve">3.41325759887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.377516746521</t>
   </si>
   <si>
     <t xml:space="preserve">3.40471076965332</t>
@@ -3392,40 +3392,40 @@
     <t xml:space="preserve">3.52203416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51037955284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44200563430786</t>
+    <t xml:space="preserve">3.51037979125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44200539588928</t>
   </si>
   <si>
     <t xml:space="preserve">3.47619247436523</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44977521896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38917112350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34022164344788</t>
+    <t xml:space="preserve">3.4497754573822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38917088508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3402214050293</t>
   </si>
   <si>
     <t xml:space="preserve">3.32545924186707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34876823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27417874336243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29904174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25630831718445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26407790184021</t>
+    <t xml:space="preserve">3.34876847267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27417898178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2990415096283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25630807876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26407814025879</t>
   </si>
   <si>
     <t xml:space="preserve">3.24776148796082</t>
@@ -3434,40 +3434,40 @@
     <t xml:space="preserve">3.2788405418396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25786209106445</t>
+    <t xml:space="preserve">3.25786185264587</t>
   </si>
   <si>
     <t xml:space="preserve">3.24076867103577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19337344169617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25009250640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28738713264465</t>
+    <t xml:space="preserve">3.19337320327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25009226799011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28738737106323</t>
   </si>
   <si>
     <t xml:space="preserve">3.27184772491455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24620747566223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2058048248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16540193557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02632308006287</t>
+    <t xml:space="preserve">3.24620771408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20580458641052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16540217399597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02632331848145</t>
   </si>
   <si>
     <t xml:space="preserve">3.03098487854004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0915892124176</t>
+    <t xml:space="preserve">3.09158897399902</t>
   </si>
   <si>
     <t xml:space="preserve">3.11956024169922</t>
@@ -3488,10 +3488,10 @@
     <t xml:space="preserve">3.22989130020142</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23066806793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31458139419556</t>
+    <t xml:space="preserve">3.23066782951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31458115577698</t>
   </si>
   <si>
     <t xml:space="preserve">3.23299884796143</t>
@@ -3500,13 +3500,13 @@
     <t xml:space="preserve">3.28894114494324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30370378494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.379070520401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3355598449707</t>
+    <t xml:space="preserve">3.30370354652405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37907028198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33556008338928</t>
   </si>
   <si>
     <t xml:space="preserve">3.38606309890747</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">3.31302738189697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33478236198425</t>
+    <t xml:space="preserve">3.33478260040283</t>
   </si>
   <si>
     <t xml:space="preserve">3.36120009422302</t>
@@ -3530,10 +3530,10 @@
     <t xml:space="preserve">3.36819291114807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36508464813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39227914810181</t>
+    <t xml:space="preserve">3.3650848865509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39227890968323</t>
   </si>
   <si>
     <t xml:space="preserve">3.41248059272766</t>
@@ -3542,16 +3542,16 @@
     <t xml:space="preserve">3.37207770347595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39150190353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39849495887756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35032224655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3534300327301</t>
+    <t xml:space="preserve">3.39150214195251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39849472045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35032200813293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35343027114868</t>
   </si>
   <si>
     <t xml:space="preserve">3.31535863876343</t>
@@ -3560,13 +3560,13 @@
     <t xml:space="preserve">3.34721422195435</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32157444953918</t>
+    <t xml:space="preserve">3.32157397270203</t>
   </si>
   <si>
     <t xml:space="preserve">3.33089804649353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32312798500061</t>
+    <t xml:space="preserve">3.32312822341919</t>
   </si>
   <si>
     <t xml:space="preserve">3.28971838951111</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">3.19725775718689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29282569885254</t>
+    <t xml:space="preserve">3.2928261756897</t>
   </si>
   <si>
     <t xml:space="preserve">3.28661012649536</t>
@@ -3593,46 +3593,46 @@
     <t xml:space="preserve">3.21279764175415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20891308784485</t>
+    <t xml:space="preserve">3.20891261100769</t>
   </si>
   <si>
     <t xml:space="preserve">3.17627954483032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30758881568909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33012080192566</t>
+    <t xml:space="preserve">3.30758857727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33012104034424</t>
   </si>
   <si>
     <t xml:space="preserve">3.36741590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39460968971252</t>
+    <t xml:space="preserve">3.39461016654968</t>
   </si>
   <si>
     <t xml:space="preserve">3.32623624801636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43268179893494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45443725585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48085451126099</t>
+    <t xml:space="preserve">3.43268203735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4544370174408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48085427284241</t>
   </si>
   <si>
     <t xml:space="preserve">3.50183296203613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61682558059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57797646522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58652353286743</t>
+    <t xml:space="preserve">3.61682510375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5779767036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58652329444885</t>
   </si>
   <si>
     <t xml:space="preserve">3.58963108062744</t>
@@ -3641,58 +3641,58 @@
     <t xml:space="preserve">3.5958468914032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57176065444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57642221450806</t>
+    <t xml:space="preserve">3.57176041603088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57642245292664</t>
   </si>
   <si>
     <t xml:space="preserve">3.566321849823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58108496665955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68752980232239</t>
+    <t xml:space="preserve">3.58108448982239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68753004074097</t>
   </si>
   <si>
     <t xml:space="preserve">3.63469576835632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65178918838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64246559143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62071013450623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62692594528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62148690223694</t>
+    <t xml:space="preserve">3.65178894996643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64246535301208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62070989608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62692642211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62148714065552</t>
   </si>
   <si>
     <t xml:space="preserve">3.61294031143188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61060929298401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57409167289734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50260996818542</t>
+    <t xml:space="preserve">3.61060905456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57409143447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50260972976685</t>
   </si>
   <si>
     <t xml:space="preserve">3.4482216835022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45132923126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39694094657898</t>
+    <t xml:space="preserve">3.45132946968079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39694118499756</t>
   </si>
   <si>
     <t xml:space="preserve">3.39538669586182</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">3.22833728790283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23999190330505</t>
+    <t xml:space="preserve">3.23999166488647</t>
   </si>
   <si>
     <t xml:space="preserve">3.40004897117615</t>
@@ -3713,13 +3713,13 @@
     <t xml:space="preserve">3.33711385726929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36586141586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37363171577454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41791963577271</t>
+    <t xml:space="preserve">3.3658618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37363147735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41791939735413</t>
   </si>
   <si>
     <t xml:space="preserve">3.4365668296814</t>
@@ -3728,13 +3728,13 @@
     <t xml:space="preserve">3.31380438804626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42025017738342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42957425117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4816312789917</t>
+    <t xml:space="preserve">3.420250415802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42957401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48163151741028</t>
   </si>
   <si>
     <t xml:space="preserve">3.4971706867218</t>
@@ -3746,31 +3746,31 @@
     <t xml:space="preserve">3.48862385749817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51814913749695</t>
+    <t xml:space="preserve">3.51814889907837</t>
   </si>
   <si>
     <t xml:space="preserve">3.54145860671997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52436470985413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48551607131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49794745445251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64635038375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70151591300964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6960768699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64712715148926</t>
+    <t xml:space="preserve">3.52436494827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48551654815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49794769287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64635014533997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70151567459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69607663154602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64712738990784</t>
   </si>
   <si>
     <t xml:space="preserve">3.65567398071289</t>
@@ -3779,19 +3779,19 @@
     <t xml:space="preserve">3.56865262985229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52824997901917</t>
+    <t xml:space="preserve">3.52824950218201</t>
   </si>
   <si>
     <t xml:space="preserve">3.49639415740967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35420703887939</t>
+    <t xml:space="preserve">3.35420727729797</t>
   </si>
   <si>
     <t xml:space="preserve">3.40237998962402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41092658042908</t>
+    <t xml:space="preserve">3.4109263420105</t>
   </si>
   <si>
     <t xml:space="preserve">3.41558814048767</t>
@@ -3800,31 +3800,31 @@
     <t xml:space="preserve">3.46531510353088</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48240852355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49017834663391</t>
+    <t xml:space="preserve">3.48240828514099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49017810821533</t>
   </si>
   <si>
     <t xml:space="preserve">3.47075390815735</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45366048812866</t>
+    <t xml:space="preserve">3.45366024971008</t>
   </si>
   <si>
     <t xml:space="preserve">3.54301238059998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56321406364441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75978922843933</t>
+    <t xml:space="preserve">3.56321382522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75978899002075</t>
   </si>
   <si>
     <t xml:space="preserve">3.62614870071411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79708409309387</t>
+    <t xml:space="preserve">3.79708385467529</t>
   </si>
   <si>
     <t xml:space="preserve">3.75124216079712</t>
@@ -3833,22 +3833,22 @@
     <t xml:space="preserve">3.65878200531006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66188955307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54612016677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55622100830078</t>
+    <t xml:space="preserve">3.66188931465149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54612064361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55622148513794</t>
   </si>
   <si>
     <t xml:space="preserve">3.38373231887817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4225811958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16384792327881</t>
+    <t xml:space="preserve">3.42258143424988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16384816169739</t>
   </si>
   <si>
     <t xml:space="preserve">3.06361818313599</t>
@@ -3857,10 +3857,10 @@
     <t xml:space="preserve">2.87481284141541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63394999504089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59898638725281</t>
+    <t xml:space="preserve">2.63395023345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59898614883423</t>
   </si>
   <si>
     <t xml:space="preserve">2.6471586227417</t>
@@ -3878,7 +3878,7 @@
     <t xml:space="preserve">2.93308591842651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91366147994995</t>
+    <t xml:space="preserve">2.91366171836853</t>
   </si>
   <si>
     <t xml:space="preserve">3.0783805847168</t>
@@ -3896,22 +3896,22 @@
     <t xml:space="preserve">3.1622941493988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14131593704224</t>
+    <t xml:space="preserve">3.14131569862366</t>
   </si>
   <si>
     <t xml:space="preserve">3.10246682167053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09780502319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13199186325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23843812942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24853849411011</t>
+    <t xml:space="preserve">3.09780526161194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13199210166931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23843789100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24853873252869</t>
   </si>
   <si>
     <t xml:space="preserve">3.17161750793457</t>
@@ -3920,61 +3920,61 @@
     <t xml:space="preserve">3.20269703865051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09236598014832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35498404502869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36275386810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37984728813171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40937256813049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42335820198059</t>
+    <t xml:space="preserve">3.09236621856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35498428344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36275410652161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37984752655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40937232971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42335796356201</t>
   </si>
   <si>
     <t xml:space="preserve">3.53058123588562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59273934364319</t>
+    <t xml:space="preserve">3.59273910522461</t>
   </si>
   <si>
     <t xml:space="preserve">3.51970338821411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52747273445129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59740090370178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61138653755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69374632835388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63624930381775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60983276367188</t>
+    <t xml:space="preserve">3.52747321128845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5974006652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6113862991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6937460899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63624906539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6098325252533</t>
   </si>
   <si>
     <t xml:space="preserve">3.36430788040161</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30059623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38140177726746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46686887741089</t>
+    <t xml:space="preserve">3.30059599876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38140153884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46686863899231</t>
   </si>
   <si>
     <t xml:space="preserve">3.51659536361694</t>
@@ -3986,46 +3986,46 @@
     <t xml:space="preserve">3.5507824420929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56942987442017</t>
+    <t xml:space="preserve">3.56942963600159</t>
   </si>
   <si>
     <t xml:space="preserve">3.51193332672119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63948941230774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6378333568573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65771150588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71403574943542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70740914344788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75876307487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71569180488586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64611577987671</t>
+    <t xml:space="preserve">3.6394898891449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63783311843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65771198272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71403551101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70740866661072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7587628364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71569228172302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64611625671387</t>
   </si>
   <si>
     <t xml:space="preserve">3.64942908287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59310555458069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59807538986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48377156257629</t>
+    <t xml:space="preserve">3.59310531616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59807515144348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48377180099487</t>
   </si>
   <si>
     <t xml:space="preserve">3.38272094726562</t>
@@ -4040,7 +4040,7 @@
     <t xml:space="preserve">3.01993155479431</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0828812122345</t>
+    <t xml:space="preserve">3.08288097381592</t>
   </si>
   <si>
     <t xml:space="preserve">2.97520399093628</t>
@@ -4055,10 +4055,10 @@
     <t xml:space="preserve">2.98514366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0000524520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96195125579834</t>
+    <t xml:space="preserve">3.00005269050598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96195149421692</t>
   </si>
   <si>
     <t xml:space="preserve">3.05968928337097</t>
@@ -4067,22 +4067,22 @@
     <t xml:space="preserve">3.03318405151367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04809308052063</t>
+    <t xml:space="preserve">3.04809331893921</t>
   </si>
   <si>
     <t xml:space="preserve">3.00999212265015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89734482765198</t>
+    <t xml:space="preserve">2.89734530448914</t>
   </si>
   <si>
     <t xml:space="preserve">2.90397143363953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90065836906433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69690012931824</t>
+    <t xml:space="preserve">2.90065860748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69689989089966</t>
   </si>
   <si>
     <t xml:space="preserve">2.6587986946106</t>
@@ -4100,16 +4100,16 @@
     <t xml:space="preserve">2.70683932304382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69193029403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52792954444885</t>
+    <t xml:space="preserve">2.69193005561829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52792978286743</t>
   </si>
   <si>
     <t xml:space="preserve">2.64885926246643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71346569061279</t>
+    <t xml:space="preserve">2.71346545219421</t>
   </si>
   <si>
     <t xml:space="preserve">2.81120347976685</t>
@@ -4127,19 +4127,19 @@
     <t xml:space="preserve">2.76813244819641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71843552589417</t>
+    <t xml:space="preserve">2.71843528747559</t>
   </si>
   <si>
     <t xml:space="preserve">2.71677875518799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7747585773468</t>
+    <t xml:space="preserve">2.77475881576538</t>
   </si>
   <si>
     <t xml:space="preserve">2.83108234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83770871162415</t>
+    <t xml:space="preserve">2.83770847320557</t>
   </si>
   <si>
     <t xml:space="preserve">2.84599161148071</t>
@@ -4166,13 +4166,13 @@
     <t xml:space="preserve">2.98183035850525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98017406463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92219400405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93544602394104</t>
+    <t xml:space="preserve">2.98017382621765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92219376564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9354465007782</t>
   </si>
   <si>
     <t xml:space="preserve">2.8542742729187</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">2.79960751533508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78469800949097</t>
+    <t xml:space="preserve">2.78469824790955</t>
   </si>
   <si>
     <t xml:space="preserve">2.8277690410614</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">2.69358682632446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64223313331604</t>
+    <t xml:space="preserve">2.64223289489746</t>
   </si>
   <si>
     <t xml:space="preserve">2.68199062347412</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">2.73168802261353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83439540863037</t>
+    <t xml:space="preserve">2.83439517021179</t>
   </si>
   <si>
     <t xml:space="preserve">2.79629421234131</t>
@@ -4220,22 +4220,22 @@
     <t xml:space="preserve">2.76150631904602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6803343296051</t>
+    <t xml:space="preserve">2.68033409118652</t>
   </si>
   <si>
     <t xml:space="preserve">2.71015238761902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61738443374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59419250488281</t>
+    <t xml:space="preserve">2.61738467216492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59419226646423</t>
   </si>
   <si>
     <t xml:space="preserve">2.57762670516968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51799011230469</t>
+    <t xml:space="preserve">2.51798987388611</t>
   </si>
   <si>
     <t xml:space="preserve">2.53621244430542</t>
@@ -4244,28 +4244,28 @@
     <t xml:space="preserve">2.46663618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44344425201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37221193313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42687892913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65051579475403</t>
+    <t xml:space="preserve">2.44344449043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37221169471741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4268786907196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65051603317261</t>
   </si>
   <si>
     <t xml:space="preserve">2.67702102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58259654045105</t>
+    <t xml:space="preserve">2.58259630203247</t>
   </si>
   <si>
     <t xml:space="preserve">2.54780840873718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53124260902405</t>
+    <t xml:space="preserve">2.53124284744263</t>
   </si>
   <si>
     <t xml:space="preserve">2.52461647987366</t>
@@ -4277,25 +4277,25 @@
     <t xml:space="preserve">2.48651528358459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4815456867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54118227958679</t>
+    <t xml:space="preserve">2.48154544830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54118204116821</t>
   </si>
   <si>
     <t xml:space="preserve">2.57100057601929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53952574729919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52295994758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48817157745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59750533103943</t>
+    <t xml:space="preserve">2.53952527046204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52295970916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48817181587219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59750556945801</t>
   </si>
   <si>
     <t xml:space="preserve">2.62235403060913</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">2.60413193702698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61407113075256</t>
+    <t xml:space="preserve">2.61407136917114</t>
   </si>
   <si>
     <t xml:space="preserve">2.61075806617737</t>
@@ -4313,49 +4313,49 @@
     <t xml:space="preserve">2.61572790145874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68861699104309</t>
+    <t xml:space="preserve">2.68861722946167</t>
   </si>
   <si>
     <t xml:space="preserve">2.84930443763733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86587023735046</t>
+    <t xml:space="preserve">2.86587047576904</t>
   </si>
   <si>
     <t xml:space="preserve">2.95366859436035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99839615821838</t>
+    <t xml:space="preserve">2.9983959197998</t>
   </si>
   <si>
     <t xml:space="preserve">2.99342632293701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03152751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98679995536804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00170946121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00833559036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98348665237427</t>
+    <t xml:space="preserve">3.03152775764465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98680019378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00170922279358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00833535194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98348712921143</t>
   </si>
   <si>
     <t xml:space="preserve">3.00336575508118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03484082221985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06631565093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04478025436401</t>
+    <t xml:space="preserve">3.03484058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06631541252136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04478001594543</t>
   </si>
   <si>
     <t xml:space="preserve">3.10441660881042</t>
@@ -4364,13 +4364,13 @@
     <t xml:space="preserve">3.08619451522827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94869875907898</t>
+    <t xml:space="preserve">2.94869899749756</t>
   </si>
   <si>
     <t xml:space="preserve">2.91722416877747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86255717277527</t>
+    <t xml:space="preserve">2.86255741119385</t>
   </si>
   <si>
     <t xml:space="preserve">2.89900183677673</t>
@@ -4388,16 +4388,16 @@
     <t xml:space="preserve">3.01496195793152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0779116153717</t>
+    <t xml:space="preserve">3.07791137695312</t>
   </si>
   <si>
     <t xml:space="preserve">3.09944701194763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13754844665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19055843353271</t>
+    <t xml:space="preserve">3.13754820823669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19055867195129</t>
   </si>
   <si>
     <t xml:space="preserve">3.16736626625061</t>
@@ -4409,19 +4409,19 @@
     <t xml:space="preserve">3.2518515586853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22865962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.225346326828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26013445854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23031616210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20215463638306</t>
+    <t xml:space="preserve">3.22865986824036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22534656524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26013469696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23031640052795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2021541595459</t>
   </si>
   <si>
     <t xml:space="preserve">3.20546746253967</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">3.18724536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23528599739075</t>
+    <t xml:space="preserve">3.23528575897217</t>
   </si>
   <si>
     <t xml:space="preserve">3.2816698551178</t>
@@ -4457,19 +4457,19 @@
     <t xml:space="preserve">3.44235777854919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29160952568054</t>
+    <t xml:space="preserve">3.29160928726196</t>
   </si>
   <si>
     <t xml:space="preserve">3.29492235183716</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31811451911926</t>
+    <t xml:space="preserve">3.31811475753784</t>
   </si>
   <si>
     <t xml:space="preserve">3.25516486167908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35124588012695</t>
+    <t xml:space="preserve">3.35124611854553</t>
   </si>
   <si>
     <t xml:space="preserve">3.45395350456238</t>
@@ -4478,7 +4478,7 @@
     <t xml:space="preserve">3.4506402015686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49536776542664</t>
+    <t xml:space="preserve">3.49536752700806</t>
   </si>
   <si>
     <t xml:space="preserve">3.43573093414307</t>
@@ -4490,13 +4490,13 @@
     <t xml:space="preserve">3.31480145454407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40922617912292</t>
+    <t xml:space="preserve">3.40922594070435</t>
   </si>
   <si>
     <t xml:space="preserve">3.34958958625793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38106393814087</t>
+    <t xml:space="preserve">3.38106417655945</t>
   </si>
   <si>
     <t xml:space="preserve">3.387690782547</t>
@@ -4505,10 +4505,10 @@
     <t xml:space="preserve">3.39266037940979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41088271141052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42082238197327</t>
+    <t xml:space="preserve">3.41088247299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42082214355469</t>
   </si>
   <si>
     <t xml:space="preserve">3.42247867584229</t>
@@ -4517,13 +4517,13 @@
     <t xml:space="preserve">3.37609457969666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37775135040283</t>
+    <t xml:space="preserve">3.37775111198425</t>
   </si>
   <si>
     <t xml:space="preserve">3.34130644798279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10276007652283</t>
+    <t xml:space="preserve">3.10276031494141</t>
   </si>
   <si>
     <t xml:space="preserve">3.13092184066772</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">3.07625508308411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17399263381958</t>
+    <t xml:space="preserve">3.17399287223816</t>
   </si>
   <si>
     <t xml:space="preserve">3.13423490524292</t>
@@ -4547,19 +4547,19 @@
     <t xml:space="preserve">3.01164865493774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06465888023376</t>
+    <t xml:space="preserve">3.06465911865234</t>
   </si>
   <si>
     <t xml:space="preserve">3.1093864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07459807395935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08453798294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11269927024841</t>
+    <t xml:space="preserve">3.07459831237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08453774452209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11269950866699</t>
   </si>
   <si>
     <t xml:space="preserve">3.14748764038086</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">3.17233610153198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17730569839478</t>
+    <t xml:space="preserve">3.17730593681335</t>
   </si>
   <si>
     <t xml:space="preserve">3.18393230438232</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">3.14914417266846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19387149810791</t>
+    <t xml:space="preserve">3.19387173652649</t>
   </si>
   <si>
     <t xml:space="preserve">3.19718480110168</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">3.17896270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14583110809326</t>
+    <t xml:space="preserve">3.14583134651184</t>
   </si>
   <si>
     <t xml:space="preserve">3.09779047966003</t>
@@ -4607,31 +4607,31 @@
     <t xml:space="preserve">3.0514063835144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08785104751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.053062915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04974985122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10612893104553</t>
+    <t xml:space="preserve">3.08785080909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05306315422058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04974961280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10612869262695</t>
   </si>
   <si>
     <t xml:space="preserve">3.05855894088745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96165752410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94403910636902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97751450538635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93523001670837</t>
+    <t xml:space="preserve">2.96165776252747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9440393447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97751426696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93523025512695</t>
   </si>
   <si>
     <t xml:space="preserve">2.90351676940918</t>
@@ -4652,7 +4652,7 @@
     <t xml:space="preserve">2.99513268470764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9968945980072</t>
+    <t xml:space="preserve">2.99689435958862</t>
   </si>
   <si>
     <t xml:space="preserve">3.03741693496704</t>
@@ -4664,7 +4664,7 @@
     <t xml:space="preserve">3.0286078453064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03213143348694</t>
+    <t xml:space="preserve">3.03213119506836</t>
   </si>
   <si>
     <t xml:space="preserve">3.06736826896667</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">3.03565526008606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99865627288818</t>
+    <t xml:space="preserve">2.99865651130676</t>
   </si>
   <si>
     <t xml:space="preserve">2.97575235366821</t>
@@ -4691,7 +4691,7 @@
     <t xml:space="preserve">2.90880250930786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88942193984985</t>
+    <t xml:space="preserve">2.88942217826843</t>
   </si>
   <si>
     <t xml:space="preserve">2.92994451522827</t>
@@ -4712,10 +4712,10 @@
     <t xml:space="preserve">2.86299443244934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88413667678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95284843444824</t>
+    <t xml:space="preserve">2.88413643836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95284867286682</t>
   </si>
   <si>
     <t xml:space="preserve">2.9916090965271</t>
@@ -4736,13 +4736,13 @@
     <t xml:space="preserve">2.93170642852783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00922727584839</t>
+    <t xml:space="preserve">3.00922751426697</t>
   </si>
   <si>
     <t xml:space="preserve">3.11317610740662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12198519706726</t>
+    <t xml:space="preserve">3.12198543548584</t>
   </si>
   <si>
     <t xml:space="preserve">3.08851027488708</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">3.25764727592468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32812118530273</t>
+    <t xml:space="preserve">3.32812094688416</t>
   </si>
   <si>
     <t xml:space="preserve">3.32635927200317</t>
@@ -4778,34 +4778,34 @@
     <t xml:space="preserve">3.2840747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22945761680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23121953010559</t>
+    <t xml:space="preserve">3.22945785522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23121976852417</t>
   </si>
   <si>
     <t xml:space="preserve">3.20655393600464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21712493896484</t>
+    <t xml:space="preserve">3.21712470054626</t>
   </si>
   <si>
     <t xml:space="preserve">3.22593402862549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25412368774414</t>
+    <t xml:space="preserve">3.25412344932556</t>
   </si>
   <si>
     <t xml:space="preserve">3.27526569366455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29112243652344</t>
+    <t xml:space="preserve">3.29112219810486</t>
   </si>
   <si>
     <t xml:space="preserve">3.34397768974304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34750127792358</t>
+    <t xml:space="preserve">3.347501039505</t>
   </si>
   <si>
     <t xml:space="preserve">3.3774528503418</t>
@@ -4820,7 +4820,7 @@
     <t xml:space="preserve">3.29816961288452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32988286018372</t>
+    <t xml:space="preserve">3.32988262176514</t>
   </si>
   <si>
     <t xml:space="preserve">3.39330911636353</t>
@@ -4859,25 +4859,25 @@
     <t xml:space="preserve">3.53954219818115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51487636566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47083020210266</t>
+    <t xml:space="preserve">3.51487612724304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47083044052124</t>
   </si>
   <si>
     <t xml:space="preserve">3.49725794792175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46378302574158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43735504150391</t>
+    <t xml:space="preserve">3.463782787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43735527992249</t>
   </si>
   <si>
     <t xml:space="preserve">3.42502236366272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52897095680237</t>
+    <t xml:space="preserve">3.52897119522095</t>
   </si>
   <si>
     <t xml:space="preserve">3.54130387306213</t>
@@ -4892,16 +4892,16 @@
     <t xml:space="preserve">3.48316311836243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42149877548218</t>
+    <t xml:space="preserve">3.4214985370636</t>
   </si>
   <si>
     <t xml:space="preserve">3.4355936050415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39507126808167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36159586906433</t>
+    <t xml:space="preserve">3.39507102966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36159610748291</t>
   </si>
   <si>
     <t xml:space="preserve">3.37569069862366</t>
@@ -4913,13 +4913,13 @@
     <t xml:space="preserve">3.37216711044312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39683270454407</t>
+    <t xml:space="preserve">3.39683294296265</t>
   </si>
   <si>
     <t xml:space="preserve">3.35278677940369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40388035774231</t>
+    <t xml:space="preserve">3.40388011932373</t>
   </si>
   <si>
     <t xml:space="preserve">3.58535027503967</t>
@@ -4931,25 +4931,25 @@
     <t xml:space="preserve">3.53778004646301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45144987106323</t>
+    <t xml:space="preserve">3.45145010948181</t>
   </si>
   <si>
     <t xml:space="preserve">3.5624463558197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54306554794312</t>
+    <t xml:space="preserve">3.54306578636169</t>
   </si>
   <si>
     <t xml:space="preserve">3.58182644844055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58711171150208</t>
+    <t xml:space="preserve">3.58711194992065</t>
   </si>
   <si>
     <t xml:space="preserve">3.55716061592102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51840019226074</t>
+    <t xml:space="preserve">3.51839995384216</t>
   </si>
   <si>
     <t xml:space="preserve">3.46730661392212</t>
@@ -4958,7 +4958,7 @@
     <t xml:space="preserve">3.4690682888031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4162130355835</t>
+    <t xml:space="preserve">3.41621327400208</t>
   </si>
   <si>
     <t xml:space="preserve">3.40211844444275</t>
@@ -4970,10 +4970,10 @@
     <t xml:space="preserve">3.45497369766235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43383145332336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45849752426147</t>
+    <t xml:space="preserve">3.43383169174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4584972858429</t>
   </si>
   <si>
     <t xml:space="preserve">3.42678427696228</t>
@@ -4997,10 +4997,10 @@
     <t xml:space="preserve">3.5677318572998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5642077922821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55187511444092</t>
+    <t xml:space="preserve">3.56420803070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55187487602234</t>
   </si>
   <si>
     <t xml:space="preserve">3.46554470062256</t>
@@ -5012,7 +5012,7 @@
     <t xml:space="preserve">3.47611594200134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55892252922058</t>
+    <t xml:space="preserve">3.558922290802</t>
   </si>
   <si>
     <t xml:space="preserve">3.5536367893219</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">3.57301735877991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57654094696045</t>
+    <t xml:space="preserve">3.57654070854187</t>
   </si>
   <si>
     <t xml:space="preserve">3.5483512878418</t>
@@ -5039,7 +5039,7 @@
     <t xml:space="preserve">3.73510646820068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69986987113953</t>
+    <t xml:space="preserve">3.69986963272095</t>
   </si>
   <si>
     <t xml:space="preserve">3.80029511451721</t>
@@ -5048,7 +5048,7 @@
     <t xml:space="preserve">3.72277355194092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71396446228027</t>
+    <t xml:space="preserve">3.71396470069885</t>
   </si>
   <si>
     <t xml:space="preserve">3.66815662384033</t>
@@ -5060,7 +5060,7 @@
     <t xml:space="preserve">3.69458413124084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78796195983887</t>
+    <t xml:space="preserve">3.78796219825745</t>
   </si>
   <si>
     <t xml:space="preserve">3.77210545539856</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">3.64701437950134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70867919921875</t>
+    <t xml:space="preserve">3.70867896080017</t>
   </si>
   <si>
     <t xml:space="preserve">3.64172887802124</t>
@@ -5102,79 +5102,79 @@
     <t xml:space="preserve">3.71220302581787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68577527999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67168068885803</t>
+    <t xml:space="preserve">3.6857750415802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67168045043945</t>
   </si>
   <si>
     <t xml:space="preserve">3.65229988098145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65582370758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71748828887939</t>
+    <t xml:space="preserve">3.65582394599915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71748805046082</t>
   </si>
   <si>
     <t xml:space="preserve">3.69634628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63468170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62587261199951</t>
+    <t xml:space="preserve">3.63468146324158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62587237358093</t>
   </si>
   <si>
     <t xml:space="preserve">3.70163178443909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72453594207764</t>
+    <t xml:space="preserve">3.72453570365906</t>
   </si>
   <si>
     <t xml:space="preserve">3.72982144355774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76858139038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81615114212036</t>
+    <t xml:space="preserve">3.76858162879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81615138053894</t>
   </si>
   <si>
     <t xml:space="preserve">3.81967520713806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88133978843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85138845443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83905529975891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87781572341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87605404853821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84610295295715</t>
+    <t xml:space="preserve">3.88133955001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85138869285583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83905553817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87781620025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87605428695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84610271453857</t>
   </si>
   <si>
     <t xml:space="preserve">3.89895820617676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82672262191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77915287017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80205655097961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76329612731934</t>
+    <t xml:space="preserve">3.82672214508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77915263175964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80205678939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76329588890076</t>
   </si>
   <si>
     <t xml:space="preserve">3.74920153617859</t>
@@ -5183,28 +5183,28 @@
     <t xml:space="preserve">3.74039196968079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67344212532043</t>
+    <t xml:space="preserve">3.67344236373901</t>
   </si>
   <si>
     <t xml:space="preserve">3.73158311843872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85843563079834</t>
+    <t xml:space="preserve">3.8584361076355</t>
   </si>
   <si>
     <t xml:space="preserve">3.82496070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81086611747742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88662528991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91833806037903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90071988105774</t>
+    <t xml:space="preserve">3.81086587905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88662552833557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91833829879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90071964263916</t>
   </si>
   <si>
     <t xml:space="preserve">4.06633329391479</t>
@@ -71112,13 +71112,13 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6495138889</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>139801</v>
       </c>
       <c r="C2493" t="n">
-        <v>6.15500020980835</v>
+        <v>6.17500019073486</v>
       </c>
       <c r="D2493" t="n">
         <v>6.09999990463257</v>
@@ -71133,6 +71133,32 @@
         <v>1962</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6495138889</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>193931</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>6.21500015258789</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>6.17500019073486</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>6.18499994277954</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1983</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -44,43 +44,43 @@
     <t xml:space="preserve">ANIM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33184671401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13419628143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96948623657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95301556587219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94203495979309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07380247116089</t>
+    <t xml:space="preserve">4.33184719085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13419580459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96948647499084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95301604270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94203543663025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07380294799805</t>
   </si>
   <si>
     <t xml:space="preserve">3.93105459213257</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82673907279968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76085567474365</t>
+    <t xml:space="preserve">3.8267388343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76085519790649</t>
   </si>
   <si>
     <t xml:space="preserve">3.67850112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73889374732971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40398550033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53300786018372</t>
+    <t xml:space="preserve">3.73889327049255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40398645401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53300809860229</t>
   </si>
   <si>
     <t xml:space="preserve">3.76909041404724</t>
@@ -89,40 +89,40 @@
     <t xml:space="preserve">3.79379725456238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79928779602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88438725471497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67575526237488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70595288276672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6400682926178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5796754360199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35731840133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4506528377533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3765344619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06633186340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9565269947052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19535422325134</t>
+    <t xml:space="preserve">3.79928731918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88438701629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67575621604919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70595264434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64006853103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57967591285706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35731816291809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45065307617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37653398513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06633234024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95652627944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19535398483276</t>
   </si>
   <si>
     <t xml:space="preserve">2.98397779464722</t>
@@ -131,91 +131,91 @@
     <t xml:space="preserve">3.24202179908752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20084428787231</t>
+    <t xml:space="preserve">3.20084452629089</t>
   </si>
   <si>
     <t xml:space="preserve">3.48633980751038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38202428817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31065011024475</t>
+    <t xml:space="preserve">3.38202452659607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31065034866333</t>
   </si>
   <si>
     <t xml:space="preserve">3.3875150680542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26672863960266</t>
+    <t xml:space="preserve">3.26672840118408</t>
   </si>
   <si>
     <t xml:space="preserve">3.11299967765808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08554840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07182288169861</t>
+    <t xml:space="preserve">3.08554863929749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07182264328003</t>
   </si>
   <si>
     <t xml:space="preserve">3.06084203720093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15692162513733</t>
+    <t xml:space="preserve">3.15692186355591</t>
   </si>
   <si>
     <t xml:space="preserve">3.302414894104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43967247009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35182857513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28319907188416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2228057384491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25300312042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57693004608154</t>
+    <t xml:space="preserve">3.43967294692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35182785987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28319931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22280597686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25300240516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57692956924438</t>
   </si>
   <si>
     <t xml:space="preserve">3.47261500358582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46437859535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.590656042099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56320405006409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61261701583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51653695106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43418216705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37104463577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45888948440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53026270866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32986640930176</t>
+    <t xml:space="preserve">3.46437907218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59065628051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56320476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61261677742004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51653671264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4341824054718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37104296684265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45888924598694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53026294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32986617088318</t>
   </si>
   <si>
     <t xml:space="preserve">3.27221846580505</t>
@@ -227,19 +227,19 @@
     <t xml:space="preserve">3.23653149604797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34084725379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28594374656677</t>
+    <t xml:space="preserve">3.34084749221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28594446182251</t>
   </si>
   <si>
     <t xml:space="preserve">3.31888580322266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23927688598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42594695091248</t>
+    <t xml:space="preserve">3.23927664756775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42594623565674</t>
   </si>
   <si>
     <t xml:space="preserve">3.41771149635315</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">3.40947604179382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41496634483337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44241786003113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46163392066956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44790816307068</t>
+    <t xml:space="preserve">3.41496610641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44241762161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46163368225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44790840148926</t>
   </si>
   <si>
     <t xml:space="preserve">3.49732112884521</t>
@@ -266,64 +266,64 @@
     <t xml:space="preserve">3.39300537109375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37378859519958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26123809814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26947379112244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15417742729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16241264343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0196647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94829106330872</t>
+    <t xml:space="preserve">3.3737895488739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26123833656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26947331428528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15417766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16241240501404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01966524124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94829130172729</t>
   </si>
   <si>
     <t xml:space="preserve">2.82201433181763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93182015419006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06907725334167</t>
+    <t xml:space="preserve">2.93181991577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06907773017883</t>
   </si>
   <si>
     <t xml:space="preserve">3.00044870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91809391975403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87417149543762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85221028327942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89064288139343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97133922576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06356263160706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2364821434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2422468662262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29988694190979</t>
+    <t xml:space="preserve">2.91809439659119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87417197227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.852210521698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89064311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97133898735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06356287002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23648238182068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24224662780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29988646507263</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884254455566</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">3.15866851806641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04050755500793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.979984998703</t>
+    <t xml:space="preserve">3.04050707817078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97998476028442</t>
   </si>
   <si>
     <t xml:space="preserve">2.9626932144165</t>
@@ -347,43 +347,43 @@
     <t xml:space="preserve">3.00015902519226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95692849159241</t>
+    <t xml:space="preserve">2.95692825317383</t>
   </si>
   <si>
     <t xml:space="preserve">2.81859302520752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79668998718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66988205909729</t>
+    <t xml:space="preserve">2.79668974876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66988182067871</t>
   </si>
   <si>
     <t xml:space="preserve">2.61454725265503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54768514633179</t>
+    <t xml:space="preserve">2.54768538475037</t>
   </si>
   <si>
     <t xml:space="preserve">2.70331263542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75288367271423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90505313873291</t>
+    <t xml:space="preserve">2.75288391113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90505337715149</t>
   </si>
   <si>
     <t xml:space="preserve">2.92234468460083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96845698356628</t>
+    <t xml:space="preserve">2.96845650672913</t>
   </si>
   <si>
     <t xml:space="preserve">2.53615713119507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26179122924805</t>
+    <t xml:space="preserve">2.26179099082947</t>
   </si>
   <si>
     <t xml:space="preserve">2.49004530906677</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">2.41972422599792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4266414642334</t>
+    <t xml:space="preserve">2.42664098739624</t>
   </si>
   <si>
     <t xml:space="preserve">2.49235057830811</t>
@@ -407,61 +407,61 @@
     <t xml:space="preserve">2.297527551651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30559730529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35747313499451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4324049949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61108875274658</t>
+    <t xml:space="preserve">2.30559754371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35747337341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43240523338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61108899116516</t>
   </si>
   <si>
     <t xml:space="preserve">2.59379720687866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68025732040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59725546836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60647797584534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56958794593811</t>
+    <t xml:space="preserve">2.68025684356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59725522994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60647821426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56958842277527</t>
   </si>
   <si>
     <t xml:space="preserve">2.62838077545166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62261700630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59494972229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61685347557068</t>
+    <t xml:space="preserve">2.62261724472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59494996070862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6168532371521</t>
   </si>
   <si>
     <t xml:space="preserve">2.54653239250183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63414525985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58226871490479</t>
+    <t xml:space="preserve">2.63414573669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58226895332336</t>
   </si>
   <si>
     <t xml:space="preserve">2.40358543395996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4151132106781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43816947937012</t>
+    <t xml:space="preserve">2.41511344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4381697177887</t>
   </si>
   <si>
     <t xml:space="preserve">2.55114388465881</t>
@@ -470,10 +470,10 @@
     <t xml:space="preserve">2.58572769165039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65143728256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65489506721497</t>
+    <t xml:space="preserve">2.65143704414368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65489530563354</t>
   </si>
   <si>
     <t xml:space="preserve">2.604172706604</t>
@@ -494,64 +494,64 @@
     <t xml:space="preserve">2.51310157775879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50964283943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4612250328064</t>
+    <t xml:space="preserve">2.50964260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46122527122498</t>
   </si>
   <si>
     <t xml:space="preserve">2.44854426383972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50733709335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50157332420349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49696230888367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51540684700012</t>
+    <t xml:space="preserve">2.50733685493469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50157308578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49696207046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51540660858154</t>
   </si>
   <si>
     <t xml:space="preserve">2.53039336204529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57304716110229</t>
+    <t xml:space="preserve">2.57304739952087</t>
   </si>
   <si>
     <t xml:space="preserve">2.66181230545044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62722826004028</t>
+    <t xml:space="preserve">2.62722849845886</t>
   </si>
   <si>
     <t xml:space="preserve">2.73789715766907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83012080192566</t>
+    <t xml:space="preserve">2.83012104034424</t>
   </si>
   <si>
     <t xml:space="preserve">2.79092574119568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67449283599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65604829788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64797878265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65720105171204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64567375183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5200183391571</t>
+    <t xml:space="preserve">2.67449355125427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6560480594635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64797902107239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65720081329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6456732749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52001810073853</t>
   </si>
   <si>
     <t xml:space="preserve">2.51886510848999</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">2.49580931663513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5211706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52462887763977</t>
+    <t xml:space="preserve">2.52117085456848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52462911605835</t>
   </si>
   <si>
     <t xml:space="preserve">2.54192161560059</t>
@@ -572,10 +572,10 @@
     <t xml:space="preserve">2.47275328636169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46929550170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39436316490173</t>
+    <t xml:space="preserve">2.46929502487183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39436292648315</t>
   </si>
   <si>
     <t xml:space="preserve">2.32173657417297</t>
@@ -584,22 +584,22 @@
     <t xml:space="preserve">2.32519507408142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24795722961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26524949073792</t>
+    <t xml:space="preserve">2.24795770645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26524925231934</t>
   </si>
   <si>
     <t xml:space="preserve">2.3263475894928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3862931728363</t>
+    <t xml:space="preserve">2.38629293441772</t>
   </si>
   <si>
     <t xml:space="preserve">2.4439332485199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44623851776123</t>
+    <t xml:space="preserve">2.44623875617981</t>
   </si>
   <si>
     <t xml:space="preserve">2.5707414150238</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">2.57996344566345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56267166137695</t>
+    <t xml:space="preserve">2.56267142295837</t>
   </si>
   <si>
     <t xml:space="preserve">2.55806040763855</t>
@@ -617,10 +617,10 @@
     <t xml:space="preserve">2.5038788318634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50503134727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38168215751648</t>
+    <t xml:space="preserve">2.50503158569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38168263435364</t>
   </si>
   <si>
     <t xml:space="preserve">2.60993623733521</t>
@@ -629,112 +629,112 @@
     <t xml:space="preserve">2.59956097602844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55344915390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70907735824585</t>
+    <t xml:space="preserve">2.55344891548157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70907711982727</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58111572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80130100250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81282901763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72291088104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78285622596741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82551002502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92522692680359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96557402610779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91081690788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00592255592346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03474283218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9972767829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98574829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94828248023987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93963646888733</t>
+    <t xml:space="preserve">2.58111596107483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8013014793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81282925605774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7229106426239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78285646438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82551026344299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92522668838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96557474136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91081666946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00592231750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03474307060242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99727654457092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9857485294342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94828271865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93963694572449</t>
   </si>
   <si>
     <t xml:space="preserve">2.97422099113464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99151277542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.014568567276</t>
+    <t xml:space="preserve">2.9915132522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01456880569458</t>
   </si>
   <si>
     <t xml:space="preserve">3.03186058998108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16155099868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13849496841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11255669593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12984871864319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20478010177612</t>
+    <t xml:space="preserve">3.16155076026917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13849449157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11255693435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12984848022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2047803401947</t>
   </si>
   <si>
     <t xml:space="preserve">3.16443228721619</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19613456726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1990168094635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12408494949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14137649536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08373641967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30276846885681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26242065429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18748879432678</t>
+    <t xml:space="preserve">3.19613432884216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19901657104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12408518791199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14137673377991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08373713493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30276918411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26242089271545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18748903274536</t>
   </si>
   <si>
     <t xml:space="preserve">3.28547620773315</t>
@@ -746,25 +746,25 @@
     <t xml:space="preserve">3.17596077919006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2480103969574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26818442344666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23936462402344</t>
+    <t xml:space="preserve">3.24801015853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26818418502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23936486244202</t>
   </si>
   <si>
     <t xml:space="preserve">3.09238290786743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10102820396423</t>
+    <t xml:space="preserve">3.10102844238281</t>
   </si>
   <si>
     <t xml:space="preserve">3.05491709709167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08085441589355</t>
+    <t xml:space="preserve">3.08085417747498</t>
   </si>
   <si>
     <t xml:space="preserve">3.11832070350647</t>
@@ -773,76 +773,76 @@
     <t xml:space="preserve">3.15002274513245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01168704032898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92810845375061</t>
+    <t xml:space="preserve">3.0116868019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92810893058777</t>
   </si>
   <si>
     <t xml:space="preserve">2.95404696464539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7851619720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91369867324829</t>
+    <t xml:space="preserve">2.78516149520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91369891166687</t>
   </si>
   <si>
     <t xml:space="preserve">2.98863101005554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00304102897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02609705924988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07797288894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05779886245728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18172454833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17019653320312</t>
+    <t xml:space="preserve">3.00304079055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0260968208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07797265052795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0577986240387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18172430992126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17019701004028</t>
   </si>
   <si>
     <t xml:space="preserve">3.23360061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24512887001038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.250892162323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27106714248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27394866943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28259491920471</t>
+    <t xml:space="preserve">3.24512910842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25089240074158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27106690406799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27394890785217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28259468078613</t>
   </si>
   <si>
     <t xml:space="preserve">3.25665593147278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1846067905426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29412221908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10391116142273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34023427963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4439868927002</t>
+    <t xml:space="preserve">3.18460655212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29412245750427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10391092300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34023475646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44398617744446</t>
   </si>
   <si>
     <t xml:space="preserve">3.4324586391449</t>
@@ -851,112 +851,112 @@
     <t xml:space="preserve">3.46415996551514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45839667320251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49298048019409</t>
+    <t xml:space="preserve">3.45839595794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49298024177551</t>
   </si>
   <si>
     <t xml:space="preserve">3.44686818122864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50450825691223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60249614715576</t>
+    <t xml:space="preserve">3.50450873374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60249638557434</t>
   </si>
   <si>
     <t xml:space="preserve">3.51603603363037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46992444992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44110441207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42381262779236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41228437423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39499306678772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37193608283997</t>
+    <t xml:space="preserve">3.46992468833923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44110488891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42381286621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41228413581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39499282836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37193655967712</t>
   </si>
   <si>
     <t xml:space="preserve">3.4893524646759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49236249923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5947253704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72117280960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71515250205994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58870363235474</t>
+    <t xml:space="preserve">3.4923620223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59472584724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72117328643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71515154838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58870339393616</t>
   </si>
   <si>
     <t xml:space="preserve">3.4682776927948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41107583045959</t>
+    <t xml:space="preserve">3.41107559204102</t>
   </si>
   <si>
     <t xml:space="preserve">3.49838471412659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54053330421448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50440573692322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5164487361908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54956483840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70913052558899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72418427467346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64891695976257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75127935409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7271945476532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76332187652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73923659324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74525809288025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71214151382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70310926437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75730037689209</t>
+    <t xml:space="preserve">3.5405330657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50440549850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51644897460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54956555366516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70913028717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72418332099915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64891743659973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75127911567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72719383239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76332235336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7392373085022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74525761604309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71214127540588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7031090259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75730061531067</t>
   </si>
   <si>
     <t xml:space="preserve">3.77536416053772</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">3.77837538719177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8415994644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85966300964355</t>
+    <t xml:space="preserve">3.84159970283508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85966348648071</t>
   </si>
   <si>
     <t xml:space="preserve">3.82654571533203</t>
@@ -977,22 +977,22 @@
     <t xml:space="preserve">4.09750509262085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14266490936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19685649871826</t>
+    <t xml:space="preserve">4.14266538619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19685697555542</t>
   </si>
   <si>
     <t xml:space="preserve">4.17277193069458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19083547592163</t>
+    <t xml:space="preserve">4.19083595275879</t>
   </si>
   <si>
     <t xml:space="preserve">4.22094202041626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19986724853516</t>
+    <t xml:space="preserve">4.19986772537231</t>
   </si>
   <si>
     <t xml:space="preserve">4.2450270652771</t>
@@ -1001,22 +1001,22 @@
     <t xml:space="preserve">4.2691125869751</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26309061050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21492195129395</t>
+    <t xml:space="preserve">4.26309108734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21492147445679</t>
   </si>
   <si>
     <t xml:space="preserve">4.15470743179321</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14567613601685</t>
+    <t xml:space="preserve">4.145676612854</t>
   </si>
   <si>
     <t xml:space="preserve">4.13664388656616</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22395372390747</t>
+    <t xml:space="preserve">4.22395324707031</t>
   </si>
   <si>
     <t xml:space="preserve">4.22696352005005</t>
@@ -1028,40 +1028,40 @@
     <t xml:space="preserve">4.25104856491089</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28717613220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11858034133911</t>
+    <t xml:space="preserve">4.28717660903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11857986450195</t>
   </si>
   <si>
     <t xml:space="preserve">4.25405931472778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09449481964111</t>
+    <t xml:space="preserve">4.09449434280396</t>
   </si>
   <si>
     <t xml:space="preserve">4.08847284317017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04030275344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05234479904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95901489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86267280578613</t>
+    <t xml:space="preserve">4.04030227661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05234527587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9590151309967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86267256736755</t>
   </si>
   <si>
     <t xml:space="preserve">3.86568450927734</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94396162033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94697213172913</t>
+    <t xml:space="preserve">3.94396185874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94697260856628</t>
   </si>
   <si>
     <t xml:space="preserve">3.95600414276123</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">3.98009014129639</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97406840324402</t>
+    <t xml:space="preserve">3.97406816482544</t>
   </si>
   <si>
     <t xml:space="preserve">4.07342004776001</t>
@@ -1079,214 +1079,214 @@
     <t xml:space="preserve">4.06438827514648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98912167549133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96202564239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01320600509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0342812538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00417423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00116395950317</t>
+    <t xml:space="preserve">3.98912119865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96202516555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01320695877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03428173065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00417470932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00116348266602</t>
   </si>
   <si>
     <t xml:space="preserve">3.90783381462097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88976979255676</t>
+    <t xml:space="preserve">3.88976955413818</t>
   </si>
   <si>
     <t xml:space="preserve">3.95299363136292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0101957321167</t>
+    <t xml:space="preserve">4.01019620895386</t>
   </si>
   <si>
     <t xml:space="preserve">4.11255884170532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15771770477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06739902496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9861114025116</t>
+    <t xml:space="preserve">4.15771865844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06739854812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98611116409302</t>
   </si>
   <si>
     <t xml:space="preserve">3.93191933631897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90181255340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87471652030945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85364174842834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82353544235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579105377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84762072563171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83256840705872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88073778152466</t>
+    <t xml:space="preserve">3.90181231498718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87471699714661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85364127159119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82353520393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579153060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84762096405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83256769180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88073754310608</t>
   </si>
   <si>
     <t xml:space="preserve">3.88374757766724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92589735984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92890858650208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88675904273987</t>
+    <t xml:space="preserve">3.92589831352234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92890882492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88675951957703</t>
   </si>
   <si>
     <t xml:space="preserve">3.9138548374176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91084504127502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84460973739624</t>
+    <t xml:space="preserve">3.91084432601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8446102142334</t>
   </si>
   <si>
     <t xml:space="preserve">3.82052516937256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69106674194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70611977577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55558681488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47429919242859</t>
+    <t xml:space="preserve">3.69106602668762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70611929893494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55558705329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47429895401001</t>
   </si>
   <si>
     <t xml:space="preserve">3.33580851554871</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40204262733459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52246928215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54354405403137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53150153160095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.573650598526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60074615478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57666158676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5375235080719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5525758266449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50139451026917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45021367073059</t>
+    <t xml:space="preserve">3.40204286575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52246975898743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54354429244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53150105476379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57365083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60074663162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5766613483429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53752326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55257606506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50139474868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45021390914917</t>
   </si>
   <si>
     <t xml:space="preserve">3.51042652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48634147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43817210197449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40806484222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53451228141785</t>
+    <t xml:space="preserve">3.48634171485901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43817162513733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40806460380554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53451180458069</t>
   </si>
   <si>
     <t xml:space="preserve">3.60977816581726</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35387229919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42612838745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44419240951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32376599311829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39000058174133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61278915405273</t>
+    <t xml:space="preserve">3.35387253761292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42612791061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44419264793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32376575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39000129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61278891563416</t>
   </si>
   <si>
     <t xml:space="preserve">3.73020458221436</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6669807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64590716362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63386416435242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81450390815735</t>
+    <t xml:space="preserve">3.66698026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64590692520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.633864402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81450319290161</t>
   </si>
   <si>
     <t xml:space="preserve">3.86869502067566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93492960929871</t>
+    <t xml:space="preserve">3.93492937088013</t>
   </si>
   <si>
     <t xml:space="preserve">4.04331350326538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99213194847107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98310041427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06137704849243</t>
+    <t xml:space="preserve">3.99213171005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9831006526947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06137752532959</t>
   </si>
   <si>
     <t xml:space="preserve">4.12460136413574</t>
@@ -1295,58 +1295,58 @@
     <t xml:space="preserve">4.160728931427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07040882110596</t>
+    <t xml:space="preserve">4.07040929794312</t>
   </si>
   <si>
     <t xml:space="preserve">4.08245229721069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8084819316864</t>
+    <t xml:space="preserve">3.80848264694214</t>
   </si>
   <si>
     <t xml:space="preserve">3.89880228042603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91987705230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78439569473267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7723536491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7994499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73622632026672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75429034233093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76633238792419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63988518714905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56160831451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66999173164368</t>
+    <t xml:space="preserve">3.91987681388855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78439593315125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77235412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79945015907288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73622584342957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75429058074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76633334159851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63988471031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56160807609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6699914932251</t>
   </si>
   <si>
     <t xml:space="preserve">3.96503615379333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79342913627625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74224758148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79164910316467</t>
+    <t xml:space="preserve">3.79342937469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74224781990051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79164934158325</t>
   </si>
   <si>
     <t xml:space="preserve">3.77612257003784</t>
@@ -1355,46 +1355,46 @@
     <t xml:space="preserve">3.78854370117188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70469880104065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58358955383301</t>
+    <t xml:space="preserve">3.70469903945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58358979225159</t>
   </si>
   <si>
     <t xml:space="preserve">3.55914282798767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55258870124817</t>
+    <t xml:space="preserve">3.55258822441101</t>
   </si>
   <si>
     <t xml:space="preserve">3.51326107978821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61157965660095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58536076545715</t>
+    <t xml:space="preserve">3.61158013343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58536148071289</t>
   </si>
   <si>
     <t xml:space="preserve">3.76888990402222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89998197555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8934268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85082268714905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81149482727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63779854774475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75578141212463</t>
+    <t xml:space="preserve">3.89998173713684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89342761039734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85082197189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81149458885193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63779830932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7557806968689</t>
   </si>
   <si>
     <t xml:space="preserve">3.73939418792725</t>
@@ -1403,67 +1403,67 @@
     <t xml:space="preserve">3.8606538772583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84099054336548</t>
+    <t xml:space="preserve">3.84099006652832</t>
   </si>
   <si>
     <t xml:space="preserve">3.81804919242859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96552801132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98846840858459</t>
+    <t xml:space="preserve">3.9655282497406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98846912384033</t>
   </si>
   <si>
     <t xml:space="preserve">3.93275499343872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86720895767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84426760673523</t>
+    <t xml:space="preserve">3.86720871925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84426736831665</t>
   </si>
   <si>
     <t xml:space="preserve">3.91309070587158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82132625579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03107309341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04418230056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0245189666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98191356658936</t>
+    <t xml:space="preserve">3.82132649421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03107357025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04418325424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02451848983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98191428184509</t>
   </si>
   <si>
     <t xml:space="preserve">3.90653657913208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99830055236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77544498443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76561188697815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71972990036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71645307540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56897497177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50670623779297</t>
+    <t xml:space="preserve">3.99830102920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7754442691803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76561212539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71973061561584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71645283699036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56897521018982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50670647621155</t>
   </si>
   <si>
     <t xml:space="preserve">3.46737885475159</t>
@@ -1475,19 +1475,19 @@
     <t xml:space="preserve">2.93645668029785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03477597236633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19077444076538</t>
+    <t xml:space="preserve">3.03477621078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19077491760254</t>
   </si>
   <si>
     <t xml:space="preserve">3.42149662971497</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41494178771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33628702163696</t>
+    <t xml:space="preserve">3.41494226455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33628678321838</t>
   </si>
   <si>
     <t xml:space="preserve">3.31662321090698</t>
@@ -1496,88 +1496,88 @@
     <t xml:space="preserve">3.35595035552979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.211749792099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30023670196533</t>
+    <t xml:space="preserve">3.21174955368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30023646354675</t>
   </si>
   <si>
     <t xml:space="preserve">3.32645487785339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39855527877808</t>
+    <t xml:space="preserve">3.39855551719666</t>
   </si>
   <si>
     <t xml:space="preserve">3.33956384658813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29040503501892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27729558944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28057289123535</t>
+    <t xml:space="preserve">3.29040479660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27729535102844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28057312965393</t>
   </si>
   <si>
     <t xml:space="preserve">3.18290948867798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12260699272156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07148170471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01511168479919</t>
+    <t xml:space="preserve">3.12260746955872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07148146629333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01511192321777</t>
   </si>
   <si>
     <t xml:space="preserve">2.89975094795227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01904463768005</t>
+    <t xml:space="preserve">3.01904487609863</t>
   </si>
   <si>
     <t xml:space="preserve">3.01380085945129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04919576644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97971701622009</t>
+    <t xml:space="preserve">3.0491955280304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97971725463867</t>
   </si>
   <si>
     <t xml:space="preserve">3.02691006660461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13440561294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10425424575806</t>
+    <t xml:space="preserve">3.1344051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10425448417664</t>
   </si>
   <si>
     <t xml:space="preserve">3.04264116287231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00200271606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00462436676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98233866691589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98627209663391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92072558403015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92728018760681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00069189071655</t>
+    <t xml:space="preserve">3.00200247764587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00462460517883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98233890533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98627185821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92072510719299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92728066444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00069212913513</t>
   </si>
   <si>
     <t xml:space="preserve">3.01249027252197</t>
@@ -1586,22 +1586,22 @@
     <t xml:space="preserve">3.03739762306213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95612049102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92465829849243</t>
+    <t xml:space="preserve">2.95612072944641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92465877532959</t>
   </si>
   <si>
     <t xml:space="preserve">2.84469270706177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97709512710571</t>
+    <t xml:space="preserve">2.97709488868713</t>
   </si>
   <si>
     <t xml:space="preserve">3.00724601745605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89057469367981</t>
+    <t xml:space="preserve">2.89057493209839</t>
   </si>
   <si>
     <t xml:space="preserve">2.77259206771851</t>
@@ -1613,49 +1613,49 @@
     <t xml:space="preserve">2.73064255714417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71229004859924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70049166679382</t>
+    <t xml:space="preserve">2.71228957176208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70049142837524</t>
   </si>
   <si>
     <t xml:space="preserve">2.77914643287659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76997017860413</t>
+    <t xml:space="preserve">2.76997041702271</t>
   </si>
   <si>
     <t xml:space="preserve">2.7371973991394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72146654129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69000434875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63625645637512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64936590194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62052536010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67689514160156</t>
+    <t xml:space="preserve">2.7214663028717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69000387191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63625621795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64936566352844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.620525598526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67689490318298</t>
   </si>
   <si>
     <t xml:space="preserve">2.72015523910522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87615466117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85124683380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86697816848755</t>
+    <t xml:space="preserve">2.87615442276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85124731063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86697793006897</t>
   </si>
   <si>
     <t xml:space="preserve">2.93907880783081</t>
@@ -1664,19 +1664,19 @@
     <t xml:space="preserve">2.91154932975769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91679286956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92596960067749</t>
+    <t xml:space="preserve">2.91679310798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92596936225891</t>
   </si>
   <si>
     <t xml:space="preserve">2.94170045852661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99807000160217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04133009910583</t>
+    <t xml:space="preserve">2.99806976318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04133033752441</t>
   </si>
   <si>
     <t xml:space="preserve">2.99675893783569</t>
@@ -1685,16 +1685,16 @@
     <t xml:space="preserve">2.99413704872131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96267509460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96005296707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91285991668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77521395683289</t>
+    <t xml:space="preserve">2.96267557144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96005344390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91286015510559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77521419525146</t>
   </si>
   <si>
     <t xml:space="preserve">2.70704627037048</t>
@@ -1706,10 +1706,10 @@
     <t xml:space="preserve">2.705735206604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74244093894958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64674377441406</t>
+    <t xml:space="preserve">2.74244117736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64674401283264</t>
   </si>
   <si>
     <t xml:space="preserve">2.64150023460388</t>
@@ -1718,43 +1718,43 @@
     <t xml:space="preserve">2.59692883491516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38193821907043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4671483039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44879531860352</t>
+    <t xml:space="preserve">2.38193845748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46714782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44879508018494</t>
   </si>
   <si>
     <t xml:space="preserve">2.49074482917786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4710807800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.486811876297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41995525360107</t>
+    <t xml:space="preserve">2.47108054161072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48681163787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41995477676392</t>
   </si>
   <si>
     <t xml:space="preserve">2.31639242172241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25871229171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20365333557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25215744972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28493046760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38587141036987</t>
+    <t xml:space="preserve">2.25871205329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20365357398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25215768814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28493022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38587117195129</t>
   </si>
   <si>
     <t xml:space="preserve">2.39242553710938</t>
@@ -1769,22 +1769,22 @@
     <t xml:space="preserve">2.54973602294922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47239184379578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44617342948914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45797181129456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47501373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54842519760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43044233322144</t>
+    <t xml:space="preserve">2.47239208221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44617366790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45797157287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47501349449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54842495918274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43044209480286</t>
   </si>
   <si>
     <t xml:space="preserve">2.40815663337708</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">2.28886342048645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27968692779541</t>
+    <t xml:space="preserve">2.27968645095825</t>
   </si>
   <si>
     <t xml:space="preserve">2.25740122795105</t>
@@ -1805,16 +1805,16 @@
     <t xml:space="preserve">2.17612433433533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18661165237427</t>
+    <t xml:space="preserve">2.18661141395569</t>
   </si>
   <si>
     <t xml:space="preserve">2.13155317306519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29410719871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35178756713867</t>
+    <t xml:space="preserve">2.29410696029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35178732872009</t>
   </si>
   <si>
     <t xml:space="preserve">2.39766931533813</t>
@@ -1823,55 +1823,55 @@
     <t xml:space="preserve">2.44748425483704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4238874912262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40946817398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40029096603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21938443183899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19447731971741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25477933883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31901431083679</t>
+    <t xml:space="preserve">2.42388796806335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40946769714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40029120445251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21938467025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19447708129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25477957725525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31901454925537</t>
   </si>
   <si>
     <t xml:space="preserve">2.32687973976135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26264476776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17743515968323</t>
+    <t xml:space="preserve">2.26264500617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17743492126465</t>
   </si>
   <si>
     <t xml:space="preserve">2.12893128395081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14597320556641</t>
+    <t xml:space="preserve">2.14597296714783</t>
   </si>
   <si>
     <t xml:space="preserve">2.12237644195557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12368750572205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10271286964417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11713314056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14728403091431</t>
+    <t xml:space="preserve">2.12368726730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10271263122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11713290214539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14728426933289</t>
   </si>
   <si>
     <t xml:space="preserve">2.15121674537659</t>
@@ -1880,19 +1880,19 @@
     <t xml:space="preserve">2.23904800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20758605003357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36489629745483</t>
+    <t xml:space="preserve">2.20758628845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36489653587341</t>
   </si>
   <si>
     <t xml:space="preserve">2.34785461425781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37407302856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25084662437439</t>
+    <t xml:space="preserve">2.37407279014587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25084638595581</t>
   </si>
   <si>
     <t xml:space="preserve">2.39504742622375</t>
@@ -1907,16 +1907,16 @@
     <t xml:space="preserve">2.43306422233582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44486260414124</t>
+    <t xml:space="preserve">2.44486284255981</t>
   </si>
   <si>
     <t xml:space="preserve">2.44224071502686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43175315856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38456010818481</t>
+    <t xml:space="preserve">2.43175339698792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38456034660339</t>
   </si>
   <si>
     <t xml:space="preserve">2.35309815406799</t>
@@ -1934,34 +1934,34 @@
     <t xml:space="preserve">2.28755211830139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26788878440857</t>
+    <t xml:space="preserve">2.26788854598999</t>
   </si>
   <si>
     <t xml:space="preserve">2.31114888191223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37931632995605</t>
+    <t xml:space="preserve">2.37931656837463</t>
   </si>
   <si>
     <t xml:space="preserve">2.40291285514832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40553498268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37014007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33605623245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39898037910461</t>
+    <t xml:space="preserve">2.4055347442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37014031410217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33605599403381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39898061752319</t>
   </si>
   <si>
     <t xml:space="preserve">2.37669444084167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5012321472168</t>
+    <t xml:space="preserve">2.50123190879822</t>
   </si>
   <si>
     <t xml:space="preserve">2.54318141937256</t>
@@ -1970,16 +1970,16 @@
     <t xml:space="preserve">2.52613949775696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5038537979126</t>
+    <t xml:space="preserve">2.50385355949402</t>
   </si>
   <si>
     <t xml:space="preserve">2.49336647987366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42782044410706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39635848999023</t>
+    <t xml:space="preserve">2.42782068252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39635872840881</t>
   </si>
   <si>
     <t xml:space="preserve">2.38718199729919</t>
@@ -1991,25 +1991,25 @@
     <t xml:space="preserve">2.37800574302673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33867835998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29935073852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38062763214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30459475517273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38849282264709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45666098594666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40160202980042</t>
+    <t xml:space="preserve">2.33867764472961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29935050010681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38062739372253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30459427833557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38849306106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4566605091095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40160226821899</t>
   </si>
   <si>
     <t xml:space="preserve">2.34129977226257</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">2.30590510368347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34523272514343</t>
+    <t xml:space="preserve">2.34523296356201</t>
   </si>
   <si>
     <t xml:space="preserve">2.32425808906555</t>
@@ -2039,133 +2039,133 @@
     <t xml:space="preserve">2.30983805656433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21545171737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19054412841797</t>
+    <t xml:space="preserve">2.21545195579529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19054436683655</t>
   </si>
   <si>
     <t xml:space="preserve">2.09091472625732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08698177337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99783945083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03978848457336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9768648147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99128484725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97817540168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98996305465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99967014789581</t>
+    <t xml:space="preserve">2.08698201179504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99783933162689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03978872299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97686457633972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99128496646881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97817552089691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98996293544769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99966990947723</t>
   </si>
   <si>
     <t xml:space="preserve">1.97470891475677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94420051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91923952102661</t>
+    <t xml:space="preserve">1.94420075416565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91923928260803</t>
   </si>
   <si>
     <t xml:space="preserve">1.89843857288361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86377000808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82632839679718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87625098228455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87902438640594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83742225170135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95113444328308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9275598526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89982497692108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92062604427338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90953242778778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90675902366638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88734459877014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88873136043549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88179790973663</t>
+    <t xml:space="preserve">1.86376988887787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82632863521576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87625074386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87902426719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83742237091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95113432407379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92755949497223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89982509613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92062640190125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90953230857849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90675914287567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88734447956085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88873147964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88179755210876</t>
   </si>
   <si>
     <t xml:space="preserve">2.02879166603088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98302900791168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03156495094299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98857617378235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95945489406586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00660395622253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00521683692932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07177996635437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0939679145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14943718910217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2270941734314</t>
+    <t xml:space="preserve">1.98302912712097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03156518936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98857629299164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95945453643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00660371780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0052170753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07178020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09396767616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14943742752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22709441184998</t>
   </si>
   <si>
     <t xml:space="preserve">2.25344228744507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25898909568787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26453614234924</t>
+    <t xml:space="preserve">2.25898933410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26453638076782</t>
   </si>
   <si>
     <t xml:space="preserve">2.21461391448975</t>
@@ -2177,16 +2177,16 @@
     <t xml:space="preserve">2.24928212165833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31445837020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30059123039246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30891132354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31307196617126</t>
+    <t xml:space="preserve">2.31445860862732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30059146881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30891156196594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31307220458984</t>
   </si>
   <si>
     <t xml:space="preserve">2.27424311637878</t>
@@ -2198,10 +2198,10 @@
     <t xml:space="preserve">2.24789547920227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24650859832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.245121717453</t>
+    <t xml:space="preserve">2.24650883674622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24512195587158</t>
   </si>
   <si>
     <t xml:space="preserve">2.28811073303223</t>
@@ -2210,67 +2210,67 @@
     <t xml:space="preserve">2.32277894020081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37824821472168</t>
+    <t xml:space="preserve">2.37824845314026</t>
   </si>
   <si>
     <t xml:space="preserve">2.30613803863525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23125433921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18687891960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1716251373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17439866065979</t>
+    <t xml:space="preserve">2.23125457763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18687915802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17162489891052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17439818382263</t>
   </si>
   <si>
     <t xml:space="preserve">2.22432088851929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12170243263245</t>
+    <t xml:space="preserve">2.12170267105103</t>
   </si>
   <si>
     <t xml:space="preserve">2.10783529281616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12863636016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09812808036804</t>
+    <t xml:space="preserve">2.1286358833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09812831878662</t>
   </si>
   <si>
     <t xml:space="preserve">2.12724947929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17717218399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19103956222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23680138587952</t>
+    <t xml:space="preserve">2.1771719455719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19103908538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23680114746094</t>
   </si>
   <si>
     <t xml:space="preserve">2.20629334449768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19935989379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18549251556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25760245323181</t>
+    <t xml:space="preserve">2.19935965538025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18549227714539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25760269165039</t>
   </si>
   <si>
     <t xml:space="preserve">2.25621581077576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23957514762878</t>
+    <t xml:space="preserve">2.23957490921021</t>
   </si>
   <si>
     <t xml:space="preserve">2.35606050491333</t>
@@ -2285,31 +2285,31 @@
     <t xml:space="preserve">2.38379526138306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43510484695435</t>
+    <t xml:space="preserve">2.43510460853577</t>
   </si>
   <si>
     <t xml:space="preserve">2.51553511619568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49889445304871</t>
+    <t xml:space="preserve">2.49889421463013</t>
   </si>
   <si>
     <t xml:space="preserve">2.42955732345581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42817068099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44897198677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45867896080017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38795566558838</t>
+    <t xml:space="preserve">2.42817091941833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44897174835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45867919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766240119934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3879554271698</t>
   </si>
   <si>
     <t xml:space="preserve">2.37131476402283</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">2.41707682609558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42401075363159</t>
+    <t xml:space="preserve">2.42401051521301</t>
   </si>
   <si>
     <t xml:space="preserve">2.37408828735352</t>
@@ -2333,16 +2333,16 @@
     <t xml:space="preserve">2.2992045879364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31723189353943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34496641159058</t>
+    <t xml:space="preserve">2.31723165512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34496665000916</t>
   </si>
   <si>
     <t xml:space="preserve">2.34635353088379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41153001785278</t>
+    <t xml:space="preserve">2.4115297794342</t>
   </si>
   <si>
     <t xml:space="preserve">2.46977281570435</t>
@@ -2357,13 +2357,13 @@
     <t xml:space="preserve">2.61537981033325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6763961315155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73879909515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70690441131592</t>
+    <t xml:space="preserve">2.67639589309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73879885673523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70690417289734</t>
   </si>
   <si>
     <t xml:space="preserve">2.74711942672729</t>
@@ -2375,28 +2375,28 @@
     <t xml:space="preserve">2.75266647338867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76237368583679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594779968262</t>
+    <t xml:space="preserve">2.76237344741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7859480381012</t>
   </si>
   <si>
     <t xml:space="preserve">2.77208065986633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69581055641174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70413088798523</t>
+    <t xml:space="preserve">2.69581031799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70413064956665</t>
   </si>
   <si>
     <t xml:space="preserve">2.72077178955078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80120205879211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78733491897583</t>
+    <t xml:space="preserve">2.80120229721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78733444213867</t>
   </si>
   <si>
     <t xml:space="preserve">2.82893681526184</t>
@@ -2405,22 +2405,22 @@
     <t xml:space="preserve">2.85528492927551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94680905342102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01614546775818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02724003791809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04804086685181</t>
+    <t xml:space="preserve">2.9468092918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01614594459534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02723979949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04804039001465</t>
   </si>
   <si>
     <t xml:space="preserve">3.0799355506897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13679170608521</t>
+    <t xml:space="preserve">3.13679194450378</t>
   </si>
   <si>
     <t xml:space="preserve">3.14649868011475</t>
@@ -2429,25 +2429,25 @@
     <t xml:space="preserve">3.17562031745911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14511203765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2310893535614</t>
+    <t xml:space="preserve">3.14511179924011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23108959197998</t>
   </si>
   <si>
     <t xml:space="preserve">3.24773049354553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26298451423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26159763336182</t>
+    <t xml:space="preserve">3.26298403739929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2615978717804</t>
   </si>
   <si>
     <t xml:space="preserve">3.2255425453186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18532729148865</t>
+    <t xml:space="preserve">3.18532752990723</t>
   </si>
   <si>
     <t xml:space="preserve">3.18394064903259</t>
@@ -2456,67 +2456,67 @@
     <t xml:space="preserve">3.2560510635376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21028900146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25327706336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22831583023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2019681930542</t>
+    <t xml:space="preserve">3.21028876304626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25327730178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22831630706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20196795463562</t>
   </si>
   <si>
     <t xml:space="preserve">3.24218344688416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26575779914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21306204795837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19919490814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20890164375305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22415614128113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1908745765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20335459709167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06606817245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09241628646851</t>
+    <t xml:space="preserve">3.26575803756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21306180953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19919466972351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20890188217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22415590286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19087433815002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20335483551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06606841087341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09241652488708</t>
   </si>
   <si>
     <t xml:space="preserve">3.14788556098938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20612835884094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17839360237122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17146015167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03694701194763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15343236923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16868710517883</t>
+    <t xml:space="preserve">3.20612859725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17839407920837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17145991325378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03694677352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15343260765076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16868662834167</t>
   </si>
   <si>
     <t xml:space="preserve">2.97038340568542</t>
@@ -2525,19 +2525,19 @@
     <t xml:space="preserve">3.03555989265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14095187187195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12985777854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14927220344543</t>
+    <t xml:space="preserve">3.14095211029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12985801696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14927196502686</t>
   </si>
   <si>
     <t xml:space="preserve">3.17007327079773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12708449363708</t>
+    <t xml:space="preserve">3.12708473205566</t>
   </si>
   <si>
     <t xml:space="preserve">3.10073661804199</t>
@@ -2546,34 +2546,34 @@
     <t xml:space="preserve">3.07854890823364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11044383049011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08964252471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28239893913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34202837944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34896183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93987536430359</t>
+    <t xml:space="preserve">3.11044359207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08964276313782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28239870071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34202861785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34896159172058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93987512588501</t>
   </si>
   <si>
     <t xml:space="preserve">2.97315716743469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.863605260849</t>
+    <t xml:space="preserve">2.86360573768616</t>
   </si>
   <si>
     <t xml:space="preserve">2.73741245269775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58487176895142</t>
+    <t xml:space="preserve">2.58487153053284</t>
   </si>
   <si>
     <t xml:space="preserve">2.55159020423889</t>
@@ -2585,10 +2585,10 @@
     <t xml:space="preserve">2.29227089881897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07039356231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95668148994446</t>
+    <t xml:space="preserve">2.07039332389832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95668125152588</t>
   </si>
   <si>
     <t xml:space="preserve">1.99134945869446</t>
@@ -2597,10 +2597,10 @@
     <t xml:space="preserve">1.69042837619781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78472650051117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65576016902924</t>
+    <t xml:space="preserve">1.7847261428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65576004981995</t>
   </si>
   <si>
     <t xml:space="preserve">1.52818048000336</t>
@@ -2618,61 +2618,61 @@
     <t xml:space="preserve">1.60583758354187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67933452129364</t>
+    <t xml:space="preserve">1.67933440208435</t>
   </si>
   <si>
     <t xml:space="preserve">1.67656099796295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72648358345032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68904173374176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69736194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72371006011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75421822071075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78888618946075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02185773849487</t>
+    <t xml:space="preserve">1.72648346424103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68904185295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69736218452454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72371029853821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75421833992004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78888666629791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02185750007629</t>
   </si>
   <si>
     <t xml:space="preserve">2.06207299232483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05375266075134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99412298202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609543800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96638870239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94142723083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85960972309113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86793041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92339956760406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90121221542358</t>
+    <t xml:space="preserve">2.05375242233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99412274360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609531879425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96638834476471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94142735004425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8596099615097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86793029308319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92339992523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90121185779572</t>
   </si>
   <si>
     <t xml:space="preserve">2.14805054664612</t>
@@ -2684,16 +2684,16 @@
     <t xml:space="preserve">2.23818802833557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22570776939392</t>
+    <t xml:space="preserve">2.22570729255676</t>
   </si>
   <si>
     <t xml:space="preserve">2.13418316841125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28117656707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35744738578796</t>
+    <t xml:space="preserve">2.28117704391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35744714736938</t>
   </si>
   <si>
     <t xml:space="preserve">2.40043592453003</t>
@@ -2711,25 +2711,25 @@
     <t xml:space="preserve">2.51219487190247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49150609970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49741721153259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45456194877625</t>
+    <t xml:space="preserve">2.49150633811951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49741744995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45456218719482</t>
   </si>
   <si>
     <t xml:space="preserve">2.57130527496338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72647047042847</t>
+    <t xml:space="preserve">2.72647023200989</t>
   </si>
   <si>
     <t xml:space="preserve">2.75750350952148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80774712562561</t>
+    <t xml:space="preserve">2.80774736404419</t>
   </si>
   <si>
     <t xml:space="preserve">2.86537981033325</t>
@@ -2738,16 +2738,16 @@
     <t xml:space="preserve">2.87572431564331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86833572387695</t>
+    <t xml:space="preserve">2.86833548545837</t>
   </si>
   <si>
     <t xml:space="preserve">2.97473430633545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20230984687805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16979908943176</t>
+    <t xml:space="preserve">3.20230960845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16979885101318</t>
   </si>
   <si>
     <t xml:space="preserve">3.14024353027344</t>
@@ -2756,10 +2756,10 @@
     <t xml:space="preserve">2.93483448028564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9363124370575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94222402572632</t>
+    <t xml:space="preserve">2.93631267547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94222354888916</t>
   </si>
   <si>
     <t xml:space="preserve">2.99837851524353</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">2.9584789276123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88606858253479</t>
+    <t xml:space="preserve">2.88606834411621</t>
   </si>
   <si>
     <t xml:space="preserve">2.92744588851929</t>
@@ -2792,25 +2792,25 @@
     <t xml:space="preserve">2.82843589782715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86242461204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93779039382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99542284011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03236699104309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04418897628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01906704902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92005705833435</t>
+    <t xml:space="preserve">2.86242437362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93779015541077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99542307853699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03236722946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04418873786926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01906728744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92005681991577</t>
   </si>
   <si>
     <t xml:space="preserve">2.93040156364441</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">2.98212313652039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99394512176514</t>
+    <t xml:space="preserve">2.99394536018372</t>
   </si>
   <si>
     <t xml:space="preserve">2.98951172828674</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">2.95404553413391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95552349090576</t>
+    <t xml:space="preserve">2.95552325248718</t>
   </si>
   <si>
     <t xml:space="preserve">2.94665694236755</t>
@@ -2840,16 +2840,16 @@
     <t xml:space="preserve">3.03384470939636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09591102600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0175895690918</t>
+    <t xml:space="preserve">3.0959107875824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758933067322</t>
   </si>
   <si>
     <t xml:space="preserve">2.99098968505859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93335676193237</t>
+    <t xml:space="preserve">2.93335723876953</t>
   </si>
   <si>
     <t xml:space="preserve">2.91857933998108</t>
@@ -2858,16 +2858,16 @@
     <t xml:space="preserve">2.75602555274963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81365871429443</t>
+    <t xml:space="preserve">2.81365823745728</t>
   </si>
   <si>
     <t xml:space="preserve">2.85503554344177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85355806350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.894935131073</t>
+    <t xml:space="preserve">2.8535578250885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89493536949158</t>
   </si>
   <si>
     <t xml:space="preserve">2.87720203399658</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">2.80479168891907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76784753799438</t>
+    <t xml:space="preserve">2.76784777641296</t>
   </si>
   <si>
     <t xml:space="preserve">2.75307011604309</t>
@@ -2906,28 +2906,28 @@
     <t xml:space="preserve">2.7486367225647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77523636817932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72351503372192</t>
+    <t xml:space="preserve">2.7752366065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7235152721405</t>
   </si>
   <si>
     <t xml:space="preserve">2.76636981964111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79296946525574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73681449890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69987082481384</t>
+    <t xml:space="preserve">2.7929699420929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73681473731995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69987058639526</t>
   </si>
   <si>
     <t xml:space="preserve">2.79592514038086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74272584915161</t>
+    <t xml:space="preserve">2.74272561073303</t>
   </si>
   <si>
     <t xml:space="preserve">2.75454783439636</t>
@@ -2936,19 +2936,19 @@
     <t xml:space="preserve">2.74715900421143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71612620353699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70873737335205</t>
+    <t xml:space="preserve">2.71612596511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70873713493347</t>
   </si>
   <si>
     <t xml:space="preserve">2.70725965499878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61268258094788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57573890686035</t>
+    <t xml:space="preserve">2.6126823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57573866844177</t>
   </si>
   <si>
     <t xml:space="preserve">2.52549457550049</t>
@@ -2963,13 +2963,13 @@
     <t xml:space="preserve">2.5846049785614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52697253227234</t>
+    <t xml:space="preserve">2.52697229385376</t>
   </si>
   <si>
     <t xml:space="preserve">2.47525072097778</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50037312507629</t>
+    <t xml:space="preserve">2.50037288665771</t>
   </si>
   <si>
     <t xml:space="preserve">2.43091797828674</t>
@@ -2978,55 +2978,55 @@
     <t xml:space="preserve">2.52992796897888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6112048625946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54618334770203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55209445953369</t>
+    <t xml:space="preserve">2.61120462417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54618358612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55209469795227</t>
   </si>
   <si>
     <t xml:space="preserve">2.67179322242737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60972738265991</t>
+    <t xml:space="preserve">2.60972714424133</t>
   </si>
   <si>
     <t xml:space="preserve">2.54322791099548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52845001220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47377300262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62893843650818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65701532363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63632678985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60677170753479</t>
+    <t xml:space="preserve">2.52845025062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47377324104309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6289381980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6570155620575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63632702827454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60677194595337</t>
   </si>
   <si>
     <t xml:space="preserve">2.53140616416931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52253913879395</t>
+    <t xml:space="preserve">2.52253937721252</t>
   </si>
   <si>
     <t xml:space="preserve">2.36441874504089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31713032722473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37180781364441</t>
+    <t xml:space="preserve">2.31713008880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37180733680725</t>
   </si>
   <si>
     <t xml:space="preserve">2.51662802696228</t>
@@ -3035,19 +3035,19 @@
     <t xml:space="preserve">2.58312749862671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64223790168762</t>
+    <t xml:space="preserve">2.64223766326904</t>
   </si>
   <si>
     <t xml:space="preserve">2.49298405647278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61563849449158</t>
+    <t xml:space="preserve">2.61563801765442</t>
   </si>
   <si>
     <t xml:space="preserve">2.65258240699768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63041591644287</t>
+    <t xml:space="preserve">2.63041567802429</t>
   </si>
   <si>
     <t xml:space="preserve">2.71317028999329</t>
@@ -3056,10 +3056,10 @@
     <t xml:space="preserve">2.72794795036316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74568128585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83139157295227</t>
+    <t xml:space="preserve">2.74568104743958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83139133453369</t>
   </si>
   <si>
     <t xml:space="preserve">2.79149198532104</t>
@@ -3071,16 +3071,16 @@
     <t xml:space="preserve">2.75898122787476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6836154460907</t>
+    <t xml:space="preserve">2.68361520767212</t>
   </si>
   <si>
     <t xml:space="preserve">2.67031526565552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66440439224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64519357681274</t>
+    <t xml:space="preserve">2.66440415382385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64519333839417</t>
   </si>
   <si>
     <t xml:space="preserve">2.68065977096558</t>
@@ -3095,13 +3095,13 @@
     <t xml:space="preserve">2.6259822845459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65849328041077</t>
+    <t xml:space="preserve">2.65849351882935</t>
   </si>
   <si>
     <t xml:space="preserve">2.7205593585968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85651350021362</t>
+    <t xml:space="preserve">2.85651326179504</t>
   </si>
   <si>
     <t xml:space="preserve">2.92301273345947</t>
@@ -3110,22 +3110,22 @@
     <t xml:space="preserve">2.90380167961121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90084624290466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98064517974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0146336555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03975605964661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07374405860901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11807703971863</t>
+    <t xml:space="preserve">2.90084600448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98064541816711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01463389396667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03975582122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07374429702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11807727813721</t>
   </si>
   <si>
     <t xml:space="preserve">3.06044459342957</t>
@@ -3137,16 +3137,16 @@
     <t xml:space="preserve">3.02941131591797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89345765113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86390209197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90675759315491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87129092216492</t>
+    <t xml:space="preserve">2.89345741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86390233039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90675735473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87129068374634</t>
   </si>
   <si>
     <t xml:space="preserve">2.83434677124023</t>
@@ -3158,28 +3158,28 @@
     <t xml:space="preserve">3.04714465141296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1328547000885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10034394264221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1771879196167</t>
+    <t xml:space="preserve">3.13285446166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10034418106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17718768119812</t>
   </si>
   <si>
     <t xml:space="preserve">3.10625505447388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13581013679504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08408856391907</t>
+    <t xml:space="preserve">3.1358106136322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08408832550049</t>
   </si>
   <si>
     <t xml:space="preserve">3.00133395195007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9451789855957</t>
+    <t xml:space="preserve">2.94517922401428</t>
   </si>
   <si>
     <t xml:space="preserve">2.9998562335968</t>
@@ -3188,31 +3188,31 @@
     <t xml:space="preserve">2.97177839279175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93926787376404</t>
+    <t xml:space="preserve">2.93926811218262</t>
   </si>
   <si>
     <t xml:space="preserve">3.08999991416931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09147763252258</t>
+    <t xml:space="preserve">3.091477394104</t>
   </si>
   <si>
     <t xml:space="preserve">3.07669997215271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08704400062561</t>
+    <t xml:space="preserve">3.08704423904419</t>
   </si>
   <si>
     <t xml:space="preserve">3.08852195739746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12694382667542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24664211273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20526504516602</t>
+    <t xml:space="preserve">3.12694334983826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24664235115051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20526528358459</t>
   </si>
   <si>
     <t xml:space="preserve">3.21856474876404</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">3.33826375007629</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34121918678284</t>
+    <t xml:space="preserve">3.34121942520142</t>
   </si>
   <si>
     <t xml:space="preserve">3.31166410446167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26142048835754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32496380805969</t>
+    <t xml:space="preserve">3.26142024993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32496404647827</t>
   </si>
   <si>
     <t xml:space="preserve">3.30131959915161</t>
@@ -3242,25 +3242,25 @@
     <t xml:space="preserve">3.2924530506134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28801965713501</t>
+    <t xml:space="preserve">3.28801941871643</t>
   </si>
   <si>
     <t xml:space="preserve">3.31609725952148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29393076896667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27324175834656</t>
+    <t xml:space="preserve">3.29393100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27324223518372</t>
   </si>
   <si>
     <t xml:space="preserve">3.24516487121582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32274746894836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30649161338806</t>
+    <t xml:space="preserve">3.32274723052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30649185180664</t>
   </si>
   <si>
     <t xml:space="preserve">3.3101863861084</t>
@@ -3269,28 +3269,28 @@
     <t xml:space="preserve">3.29540872573853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25107550621033</t>
+    <t xml:space="preserve">3.25107574462891</t>
   </si>
   <si>
     <t xml:space="preserve">3.28358626365662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28654193878174</t>
+    <t xml:space="preserve">3.28654170036316</t>
   </si>
   <si>
     <t xml:space="preserve">3.27915358543396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24073171615601</t>
+    <t xml:space="preserve">3.24073147773743</t>
   </si>
   <si>
     <t xml:space="preserve">3.27767539024353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28136944770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18531560897827</t>
+    <t xml:space="preserve">3.28136968612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18531513214111</t>
   </si>
   <si>
     <t xml:space="preserve">3.13433265686035</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">3.10329937934875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16314888000488</t>
+    <t xml:space="preserve">3.16314911842346</t>
   </si>
   <si>
     <t xml:space="preserve">3.13507151603699</t>
@@ -3314,34 +3314,34 @@
     <t xml:space="preserve">3.15354347229004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13654923439026</t>
+    <t xml:space="preserve">3.1365487575531</t>
   </si>
   <si>
     <t xml:space="preserve">3.21043729782104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26511478424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22743153572083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23925352096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24738144874573</t>
+    <t xml:space="preserve">3.26511454582214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2274317741394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23925375938416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24738121032715</t>
   </si>
   <si>
     <t xml:space="preserve">3.31979203224182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33974099159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41362929344177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3205304145813</t>
+    <t xml:space="preserve">3.33974123001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41362953186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32053017616272</t>
   </si>
   <si>
     <t xml:space="preserve">3.32939720153809</t>
@@ -3350,28 +3350,28 @@
     <t xml:space="preserve">3.31535816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38761734962463</t>
+    <t xml:space="preserve">3.38761758804321</t>
   </si>
   <si>
     <t xml:space="preserve">3.31846618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.337890625</t>
+    <t xml:space="preserve">3.33789086341858</t>
   </si>
   <si>
     <t xml:space="preserve">3.33322882652283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33944439888</t>
+    <t xml:space="preserve">3.33944487571716</t>
   </si>
   <si>
     <t xml:space="preserve">3.33633685112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41325759887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.377516746521</t>
+    <t xml:space="preserve">3.41325736045837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37751650810242</t>
   </si>
   <si>
     <t xml:space="preserve">3.40471076965332</t>
@@ -3392,40 +3392,40 @@
     <t xml:space="preserve">3.52203416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51037979125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44200539588928</t>
+    <t xml:space="preserve">3.51037955284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44200563430786</t>
   </si>
   <si>
     <t xml:space="preserve">3.47619247436523</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4497754573822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38917088508606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3402214050293</t>
+    <t xml:space="preserve">3.44977521896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38917112350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34022164344788</t>
   </si>
   <si>
     <t xml:space="preserve">3.32545924186707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34876847267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27417898178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2990415096283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25630807876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26407814025879</t>
+    <t xml:space="preserve">3.34876823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27417874336243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29904174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25630831718445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26407790184021</t>
   </si>
   <si>
     <t xml:space="preserve">3.24776148796082</t>
@@ -3434,40 +3434,40 @@
     <t xml:space="preserve">3.2788405418396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25786185264587</t>
+    <t xml:space="preserve">3.25786209106445</t>
   </si>
   <si>
     <t xml:space="preserve">3.24076867103577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19337320327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25009226799011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28738737106323</t>
+    <t xml:space="preserve">3.19337344169617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25009250640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28738713264465</t>
   </si>
   <si>
     <t xml:space="preserve">3.27184772491455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24620771408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20580458641052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16540217399597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02632331848145</t>
+    <t xml:space="preserve">3.24620747566223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2058048248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16540193557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02632308006287</t>
   </si>
   <si>
     <t xml:space="preserve">3.03098487854004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09158897399902</t>
+    <t xml:space="preserve">3.0915892124176</t>
   </si>
   <si>
     <t xml:space="preserve">3.11956024169922</t>
@@ -3488,10 +3488,10 @@
     <t xml:space="preserve">3.22989130020142</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23066782951355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31458115577698</t>
+    <t xml:space="preserve">3.23066806793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31458139419556</t>
   </si>
   <si>
     <t xml:space="preserve">3.23299884796143</t>
@@ -3500,13 +3500,13 @@
     <t xml:space="preserve">3.28894114494324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30370354652405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37907028198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33556008338928</t>
+    <t xml:space="preserve">3.30370378494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.379070520401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3355598449707</t>
   </si>
   <si>
     <t xml:space="preserve">3.38606309890747</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">3.31302738189697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33478260040283</t>
+    <t xml:space="preserve">3.33478236198425</t>
   </si>
   <si>
     <t xml:space="preserve">3.36120009422302</t>
@@ -3530,10 +3530,10 @@
     <t xml:space="preserve">3.36819291114807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3650848865509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39227890968323</t>
+    <t xml:space="preserve">3.36508464813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39227914810181</t>
   </si>
   <si>
     <t xml:space="preserve">3.41248059272766</t>
@@ -3542,16 +3542,16 @@
     <t xml:space="preserve">3.37207770347595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39150214195251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39849472045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35032200813293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35343027114868</t>
+    <t xml:space="preserve">3.39150190353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39849495887756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35032224655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3534300327301</t>
   </si>
   <si>
     <t xml:space="preserve">3.31535863876343</t>
@@ -3560,13 +3560,13 @@
     <t xml:space="preserve">3.34721422195435</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32157397270203</t>
+    <t xml:space="preserve">3.32157444953918</t>
   </si>
   <si>
     <t xml:space="preserve">3.33089804649353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32312822341919</t>
+    <t xml:space="preserve">3.32312798500061</t>
   </si>
   <si>
     <t xml:space="preserve">3.28971838951111</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">3.19725775718689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2928261756897</t>
+    <t xml:space="preserve">3.29282569885254</t>
   </si>
   <si>
     <t xml:space="preserve">3.28661012649536</t>
@@ -3593,46 +3593,46 @@
     <t xml:space="preserve">3.21279764175415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20891261100769</t>
+    <t xml:space="preserve">3.20891308784485</t>
   </si>
   <si>
     <t xml:space="preserve">3.17627954483032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30758857727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33012104034424</t>
+    <t xml:space="preserve">3.30758881568909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33012080192566</t>
   </si>
   <si>
     <t xml:space="preserve">3.36741590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39461016654968</t>
+    <t xml:space="preserve">3.39460968971252</t>
   </si>
   <si>
     <t xml:space="preserve">3.32623624801636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43268203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4544370174408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48085427284241</t>
+    <t xml:space="preserve">3.43268179893494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45443725585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48085451126099</t>
   </si>
   <si>
     <t xml:space="preserve">3.50183296203613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61682510375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5779767036438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58652329444885</t>
+    <t xml:space="preserve">3.61682558059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57797646522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58652353286743</t>
   </si>
   <si>
     <t xml:space="preserve">3.58963108062744</t>
@@ -3641,58 +3641,58 @@
     <t xml:space="preserve">3.5958468914032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57176041603088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57642245292664</t>
+    <t xml:space="preserve">3.57176065444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57642221450806</t>
   </si>
   <si>
     <t xml:space="preserve">3.566321849823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58108448982239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68753004074097</t>
+    <t xml:space="preserve">3.58108496665955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68752980232239</t>
   </si>
   <si>
     <t xml:space="preserve">3.63469576835632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65178894996643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64246535301208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62070989608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62692642211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62148714065552</t>
+    <t xml:space="preserve">3.65178918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64246559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62071013450623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62692594528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62148690223694</t>
   </si>
   <si>
     <t xml:space="preserve">3.61294031143188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61060905456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57409143447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50260972976685</t>
+    <t xml:space="preserve">3.61060929298401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57409167289734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50260996818542</t>
   </si>
   <si>
     <t xml:space="preserve">3.4482216835022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45132946968079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39694118499756</t>
+    <t xml:space="preserve">3.45132923126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39694094657898</t>
   </si>
   <si>
     <t xml:space="preserve">3.39538669586182</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">3.22833728790283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23999166488647</t>
+    <t xml:space="preserve">3.23999190330505</t>
   </si>
   <si>
     <t xml:space="preserve">3.40004897117615</t>
@@ -3713,13 +3713,13 @@
     <t xml:space="preserve">3.33711385726929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3658618927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37363147735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41791939735413</t>
+    <t xml:space="preserve">3.36586141586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37363171577454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41791963577271</t>
   </si>
   <si>
     <t xml:space="preserve">3.4365668296814</t>
@@ -3728,13 +3728,13 @@
     <t xml:space="preserve">3.31380438804626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.420250415802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42957401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48163151741028</t>
+    <t xml:space="preserve">3.42025017738342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42957425117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4816312789917</t>
   </si>
   <si>
     <t xml:space="preserve">3.4971706867218</t>
@@ -3746,31 +3746,31 @@
     <t xml:space="preserve">3.48862385749817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51814889907837</t>
+    <t xml:space="preserve">3.51814913749695</t>
   </si>
   <si>
     <t xml:space="preserve">3.54145860671997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52436494827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48551654815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49794769287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64635014533997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70151567459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69607663154602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64712738990784</t>
+    <t xml:space="preserve">3.52436470985413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48551607131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49794745445251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64635038375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70151591300964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6960768699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64712715148926</t>
   </si>
   <si>
     <t xml:space="preserve">3.65567398071289</t>
@@ -3779,19 +3779,19 @@
     <t xml:space="preserve">3.56865262985229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52824950218201</t>
+    <t xml:space="preserve">3.52824997901917</t>
   </si>
   <si>
     <t xml:space="preserve">3.49639415740967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35420727729797</t>
+    <t xml:space="preserve">3.35420703887939</t>
   </si>
   <si>
     <t xml:space="preserve">3.40237998962402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4109263420105</t>
+    <t xml:space="preserve">3.41092658042908</t>
   </si>
   <si>
     <t xml:space="preserve">3.41558814048767</t>
@@ -3800,31 +3800,31 @@
     <t xml:space="preserve">3.46531510353088</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48240828514099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49017810821533</t>
+    <t xml:space="preserve">3.48240852355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49017834663391</t>
   </si>
   <si>
     <t xml:space="preserve">3.47075390815735</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45366024971008</t>
+    <t xml:space="preserve">3.45366048812866</t>
   </si>
   <si>
     <t xml:space="preserve">3.54301238059998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56321382522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75978899002075</t>
+    <t xml:space="preserve">3.56321406364441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75978922843933</t>
   </si>
   <si>
     <t xml:space="preserve">3.62614870071411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79708385467529</t>
+    <t xml:space="preserve">3.79708409309387</t>
   </si>
   <si>
     <t xml:space="preserve">3.75124216079712</t>
@@ -3833,22 +3833,22 @@
     <t xml:space="preserve">3.65878200531006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66188931465149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54612064361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55622148513794</t>
+    <t xml:space="preserve">3.66188955307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54612016677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55622100830078</t>
   </si>
   <si>
     <t xml:space="preserve">3.38373231887817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42258143424988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16384816169739</t>
+    <t xml:space="preserve">3.4225811958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16384792327881</t>
   </si>
   <si>
     <t xml:space="preserve">3.06361818313599</t>
@@ -3857,10 +3857,10 @@
     <t xml:space="preserve">2.87481284141541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63395023345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59898614883423</t>
+    <t xml:space="preserve">2.63394999504089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59898638725281</t>
   </si>
   <si>
     <t xml:space="preserve">2.6471586227417</t>
@@ -3878,7 +3878,7 @@
     <t xml:space="preserve">2.93308591842651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91366171836853</t>
+    <t xml:space="preserve">2.91366147994995</t>
   </si>
   <si>
     <t xml:space="preserve">3.0783805847168</t>
@@ -3896,22 +3896,22 @@
     <t xml:space="preserve">3.1622941493988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14131569862366</t>
+    <t xml:space="preserve">3.14131593704224</t>
   </si>
   <si>
     <t xml:space="preserve">3.10246682167053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09780526161194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13199210166931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23843789100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24853873252869</t>
+    <t xml:space="preserve">3.09780502319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13199186325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23843812942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24853849411011</t>
   </si>
   <si>
     <t xml:space="preserve">3.17161750793457</t>
@@ -3920,61 +3920,61 @@
     <t xml:space="preserve">3.20269703865051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09236621856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35498428344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36275410652161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37984752655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40937232971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42335796356201</t>
+    <t xml:space="preserve">3.09236598014832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35498404502869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36275386810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37984728813171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40937256813049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42335820198059</t>
   </si>
   <si>
     <t xml:space="preserve">3.53058123588562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59273910522461</t>
+    <t xml:space="preserve">3.59273934364319</t>
   </si>
   <si>
     <t xml:space="preserve">3.51970338821411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52747321128845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5974006652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6113862991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6937460899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63624906539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6098325252533</t>
+    <t xml:space="preserve">3.52747273445129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59740090370178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61138653755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69374632835388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63624930381775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60983276367188</t>
   </si>
   <si>
     <t xml:space="preserve">3.36430788040161</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30059599876404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38140153884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46686863899231</t>
+    <t xml:space="preserve">3.30059623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38140177726746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46686887741089</t>
   </si>
   <si>
     <t xml:space="preserve">3.51659536361694</t>
@@ -3986,46 +3986,46 @@
     <t xml:space="preserve">3.5507824420929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56942963600159</t>
+    <t xml:space="preserve">3.56942987442017</t>
   </si>
   <si>
     <t xml:space="preserve">3.51193332672119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6394898891449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63783311843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65771198272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71403551101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70740866661072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7587628364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71569228172302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64611625671387</t>
+    <t xml:space="preserve">3.63948941230774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6378333568573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65771150588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71403574943542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70740914344788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75876307487488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71569180488586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64611577987671</t>
   </si>
   <si>
     <t xml:space="preserve">3.64942908287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59310531616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59807515144348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48377180099487</t>
+    <t xml:space="preserve">3.59310555458069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59807538986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48377156257629</t>
   </si>
   <si>
     <t xml:space="preserve">3.38272094726562</t>
@@ -4040,7 +4040,7 @@
     <t xml:space="preserve">3.01993155479431</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08288097381592</t>
+    <t xml:space="preserve">3.0828812122345</t>
   </si>
   <si>
     <t xml:space="preserve">2.97520399093628</t>
@@ -4055,10 +4055,10 @@
     <t xml:space="preserve">2.98514366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00005269050598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96195149421692</t>
+    <t xml:space="preserve">3.0000524520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96195125579834</t>
   </si>
   <si>
     <t xml:space="preserve">3.05968928337097</t>
@@ -4067,22 +4067,22 @@
     <t xml:space="preserve">3.03318405151367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04809331893921</t>
+    <t xml:space="preserve">3.04809308052063</t>
   </si>
   <si>
     <t xml:space="preserve">3.00999212265015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89734530448914</t>
+    <t xml:space="preserve">2.89734482765198</t>
   </si>
   <si>
     <t xml:space="preserve">2.90397143363953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90065860748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69689989089966</t>
+    <t xml:space="preserve">2.90065836906433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69690012931824</t>
   </si>
   <si>
     <t xml:space="preserve">2.6587986946106</t>
@@ -4100,16 +4100,16 @@
     <t xml:space="preserve">2.70683932304382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69193005561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52792978286743</t>
+    <t xml:space="preserve">2.69193029403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52792954444885</t>
   </si>
   <si>
     <t xml:space="preserve">2.64885926246643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71346545219421</t>
+    <t xml:space="preserve">2.71346569061279</t>
   </si>
   <si>
     <t xml:space="preserve">2.81120347976685</t>
@@ -4127,19 +4127,19 @@
     <t xml:space="preserve">2.76813244819641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71843528747559</t>
+    <t xml:space="preserve">2.71843552589417</t>
   </si>
   <si>
     <t xml:space="preserve">2.71677875518799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77475881576538</t>
+    <t xml:space="preserve">2.7747585773468</t>
   </si>
   <si>
     <t xml:space="preserve">2.83108234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83770847320557</t>
+    <t xml:space="preserve">2.83770871162415</t>
   </si>
   <si>
     <t xml:space="preserve">2.84599161148071</t>
@@ -4166,13 +4166,13 @@
     <t xml:space="preserve">2.98183035850525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98017382621765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92219376564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9354465007782</t>
+    <t xml:space="preserve">2.98017406463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92219400405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93544602394104</t>
   </si>
   <si>
     <t xml:space="preserve">2.8542742729187</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">2.79960751533508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78469824790955</t>
+    <t xml:space="preserve">2.78469800949097</t>
   </si>
   <si>
     <t xml:space="preserve">2.8277690410614</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">2.69358682632446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64223289489746</t>
+    <t xml:space="preserve">2.64223313331604</t>
   </si>
   <si>
     <t xml:space="preserve">2.68199062347412</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">2.73168802261353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83439517021179</t>
+    <t xml:space="preserve">2.83439540863037</t>
   </si>
   <si>
     <t xml:space="preserve">2.79629421234131</t>
@@ -4220,22 +4220,22 @@
     <t xml:space="preserve">2.76150631904602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68033409118652</t>
+    <t xml:space="preserve">2.6803343296051</t>
   </si>
   <si>
     <t xml:space="preserve">2.71015238761902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61738467216492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59419226646423</t>
+    <t xml:space="preserve">2.61738443374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59419250488281</t>
   </si>
   <si>
     <t xml:space="preserve">2.57762670516968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51798987388611</t>
+    <t xml:space="preserve">2.51799011230469</t>
   </si>
   <si>
     <t xml:space="preserve">2.53621244430542</t>
@@ -4244,28 +4244,28 @@
     <t xml:space="preserve">2.46663618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44344449043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37221169471741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4268786907196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65051603317261</t>
+    <t xml:space="preserve">2.44344425201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37221193313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42687892913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65051579475403</t>
   </si>
   <si>
     <t xml:space="preserve">2.67702102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58259630203247</t>
+    <t xml:space="preserve">2.58259654045105</t>
   </si>
   <si>
     <t xml:space="preserve">2.54780840873718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53124284744263</t>
+    <t xml:space="preserve">2.53124260902405</t>
   </si>
   <si>
     <t xml:space="preserve">2.52461647987366</t>
@@ -4277,25 +4277,25 @@
     <t xml:space="preserve">2.48651528358459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48154544830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54118204116821</t>
+    <t xml:space="preserve">2.4815456867218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54118227958679</t>
   </si>
   <si>
     <t xml:space="preserve">2.57100057601929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53952527046204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52295970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48817181587219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59750556945801</t>
+    <t xml:space="preserve">2.53952574729919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52295994758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48817157745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59750533103943</t>
   </si>
   <si>
     <t xml:space="preserve">2.62235403060913</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">2.60413193702698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61407136917114</t>
+    <t xml:space="preserve">2.61407113075256</t>
   </si>
   <si>
     <t xml:space="preserve">2.61075806617737</t>
@@ -4313,49 +4313,49 @@
     <t xml:space="preserve">2.61572790145874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68861722946167</t>
+    <t xml:space="preserve">2.68861699104309</t>
   </si>
   <si>
     <t xml:space="preserve">2.84930443763733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86587047576904</t>
+    <t xml:space="preserve">2.86587023735046</t>
   </si>
   <si>
     <t xml:space="preserve">2.95366859436035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9983959197998</t>
+    <t xml:space="preserve">2.99839615821838</t>
   </si>
   <si>
     <t xml:space="preserve">2.99342632293701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03152775764465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98680019378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00170922279358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00833535194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98348712921143</t>
+    <t xml:space="preserve">3.03152751922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98679995536804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00170946121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00833559036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98348665237427</t>
   </si>
   <si>
     <t xml:space="preserve">3.00336575508118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03484058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06631541252136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04478001594543</t>
+    <t xml:space="preserve">3.03484082221985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06631565093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04478025436401</t>
   </si>
   <si>
     <t xml:space="preserve">3.10441660881042</t>
@@ -4364,13 +4364,13 @@
     <t xml:space="preserve">3.08619451522827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94869899749756</t>
+    <t xml:space="preserve">2.94869875907898</t>
   </si>
   <si>
     <t xml:space="preserve">2.91722416877747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86255741119385</t>
+    <t xml:space="preserve">2.86255717277527</t>
   </si>
   <si>
     <t xml:space="preserve">2.89900183677673</t>
@@ -4388,16 +4388,16 @@
     <t xml:space="preserve">3.01496195793152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07791137695312</t>
+    <t xml:space="preserve">3.0779116153717</t>
   </si>
   <si>
     <t xml:space="preserve">3.09944701194763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13754820823669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19055867195129</t>
+    <t xml:space="preserve">3.13754844665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19055843353271</t>
   </si>
   <si>
     <t xml:space="preserve">3.16736626625061</t>
@@ -4409,19 +4409,19 @@
     <t xml:space="preserve">3.2518515586853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22865986824036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22534656524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26013469696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23031640052795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2021541595459</t>
+    <t xml:space="preserve">3.22865962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.225346326828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26013445854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23031616210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20215463638306</t>
   </si>
   <si>
     <t xml:space="preserve">3.20546746253967</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">3.18724536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23528575897217</t>
+    <t xml:space="preserve">3.23528599739075</t>
   </si>
   <si>
     <t xml:space="preserve">3.2816698551178</t>
@@ -4457,19 +4457,19 @@
     <t xml:space="preserve">3.44235777854919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29160928726196</t>
+    <t xml:space="preserve">3.29160952568054</t>
   </si>
   <si>
     <t xml:space="preserve">3.29492235183716</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31811475753784</t>
+    <t xml:space="preserve">3.31811451911926</t>
   </si>
   <si>
     <t xml:space="preserve">3.25516486167908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35124611854553</t>
+    <t xml:space="preserve">3.35124588012695</t>
   </si>
   <si>
     <t xml:space="preserve">3.45395350456238</t>
@@ -4478,7 +4478,7 @@
     <t xml:space="preserve">3.4506402015686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49536752700806</t>
+    <t xml:space="preserve">3.49536776542664</t>
   </si>
   <si>
     <t xml:space="preserve">3.43573093414307</t>
@@ -4490,13 +4490,13 @@
     <t xml:space="preserve">3.31480145454407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40922594070435</t>
+    <t xml:space="preserve">3.40922617912292</t>
   </si>
   <si>
     <t xml:space="preserve">3.34958958625793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38106417655945</t>
+    <t xml:space="preserve">3.38106393814087</t>
   </si>
   <si>
     <t xml:space="preserve">3.387690782547</t>
@@ -4505,10 +4505,10 @@
     <t xml:space="preserve">3.39266037940979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41088247299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42082214355469</t>
+    <t xml:space="preserve">3.41088271141052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42082238197327</t>
   </si>
   <si>
     <t xml:space="preserve">3.42247867584229</t>
@@ -4517,13 +4517,13 @@
     <t xml:space="preserve">3.37609457969666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37775111198425</t>
+    <t xml:space="preserve">3.37775135040283</t>
   </si>
   <si>
     <t xml:space="preserve">3.34130644798279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10276031494141</t>
+    <t xml:space="preserve">3.10276007652283</t>
   </si>
   <si>
     <t xml:space="preserve">3.13092184066772</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">3.07625508308411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17399287223816</t>
+    <t xml:space="preserve">3.17399263381958</t>
   </si>
   <si>
     <t xml:space="preserve">3.13423490524292</t>
@@ -4547,19 +4547,19 @@
     <t xml:space="preserve">3.01164865493774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06465911865234</t>
+    <t xml:space="preserve">3.06465888023376</t>
   </si>
   <si>
     <t xml:space="preserve">3.1093864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07459831237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08453774452209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11269950866699</t>
+    <t xml:space="preserve">3.07459807395935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08453798294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11269927024841</t>
   </si>
   <si>
     <t xml:space="preserve">3.14748764038086</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">3.17233610153198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17730593681335</t>
+    <t xml:space="preserve">3.17730569839478</t>
   </si>
   <si>
     <t xml:space="preserve">3.18393230438232</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">3.14914417266846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19387173652649</t>
+    <t xml:space="preserve">3.19387149810791</t>
   </si>
   <si>
     <t xml:space="preserve">3.19718480110168</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">3.17896270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14583134651184</t>
+    <t xml:space="preserve">3.14583110809326</t>
   </si>
   <si>
     <t xml:space="preserve">3.09779047966003</t>
@@ -4607,31 +4607,31 @@
     <t xml:space="preserve">3.0514063835144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08785080909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05306315422058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04974961280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10612869262695</t>
+    <t xml:space="preserve">3.08785104751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.053062915802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04974985122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10612893104553</t>
   </si>
   <si>
     <t xml:space="preserve">3.05855894088745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96165776252747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9440393447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97751426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93523025512695</t>
+    <t xml:space="preserve">2.96165752410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94403910636902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97751450538635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93523001670837</t>
   </si>
   <si>
     <t xml:space="preserve">2.90351676940918</t>
@@ -4652,7 +4652,7 @@
     <t xml:space="preserve">2.99513268470764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99689435958862</t>
+    <t xml:space="preserve">2.9968945980072</t>
   </si>
   <si>
     <t xml:space="preserve">3.03741693496704</t>
@@ -4664,7 +4664,7 @@
     <t xml:space="preserve">3.0286078453064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03213119506836</t>
+    <t xml:space="preserve">3.03213143348694</t>
   </si>
   <si>
     <t xml:space="preserve">3.06736826896667</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">3.03565526008606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99865651130676</t>
+    <t xml:space="preserve">2.99865627288818</t>
   </si>
   <si>
     <t xml:space="preserve">2.97575235366821</t>
@@ -4691,7 +4691,7 @@
     <t xml:space="preserve">2.90880250930786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88942217826843</t>
+    <t xml:space="preserve">2.88942193984985</t>
   </si>
   <si>
     <t xml:space="preserve">2.92994451522827</t>
@@ -4712,10 +4712,10 @@
     <t xml:space="preserve">2.86299443244934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88413643836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95284867286682</t>
+    <t xml:space="preserve">2.88413667678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95284843444824</t>
   </si>
   <si>
     <t xml:space="preserve">2.9916090965271</t>
@@ -4736,13 +4736,13 @@
     <t xml:space="preserve">2.93170642852783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00922751426697</t>
+    <t xml:space="preserve">3.00922727584839</t>
   </si>
   <si>
     <t xml:space="preserve">3.11317610740662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12198543548584</t>
+    <t xml:space="preserve">3.12198519706726</t>
   </si>
   <si>
     <t xml:space="preserve">3.08851027488708</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">3.25764727592468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32812094688416</t>
+    <t xml:space="preserve">3.32812118530273</t>
   </si>
   <si>
     <t xml:space="preserve">3.32635927200317</t>
@@ -4778,34 +4778,34 @@
     <t xml:space="preserve">3.2840747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22945785522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23121976852417</t>
+    <t xml:space="preserve">3.22945761680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23121953010559</t>
   </si>
   <si>
     <t xml:space="preserve">3.20655393600464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21712470054626</t>
+    <t xml:space="preserve">3.21712493896484</t>
   </si>
   <si>
     <t xml:space="preserve">3.22593402862549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25412344932556</t>
+    <t xml:space="preserve">3.25412368774414</t>
   </si>
   <si>
     <t xml:space="preserve">3.27526569366455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29112219810486</t>
+    <t xml:space="preserve">3.29112243652344</t>
   </si>
   <si>
     <t xml:space="preserve">3.34397768974304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.347501039505</t>
+    <t xml:space="preserve">3.34750127792358</t>
   </si>
   <si>
     <t xml:space="preserve">3.3774528503418</t>
@@ -4820,7 +4820,7 @@
     <t xml:space="preserve">3.29816961288452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32988262176514</t>
+    <t xml:space="preserve">3.32988286018372</t>
   </si>
   <si>
     <t xml:space="preserve">3.39330911636353</t>
@@ -4859,25 +4859,25 @@
     <t xml:space="preserve">3.53954219818115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51487612724304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47083044052124</t>
+    <t xml:space="preserve">3.51487636566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47083020210266</t>
   </si>
   <si>
     <t xml:space="preserve">3.49725794792175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.463782787323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43735527992249</t>
+    <t xml:space="preserve">3.46378302574158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43735504150391</t>
   </si>
   <si>
     <t xml:space="preserve">3.42502236366272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52897119522095</t>
+    <t xml:space="preserve">3.52897095680237</t>
   </si>
   <si>
     <t xml:space="preserve">3.54130387306213</t>
@@ -4892,16 +4892,16 @@
     <t xml:space="preserve">3.48316311836243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4214985370636</t>
+    <t xml:space="preserve">3.42149877548218</t>
   </si>
   <si>
     <t xml:space="preserve">3.4355936050415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39507102966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36159610748291</t>
+    <t xml:space="preserve">3.39507126808167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36159586906433</t>
   </si>
   <si>
     <t xml:space="preserve">3.37569069862366</t>
@@ -4913,13 +4913,13 @@
     <t xml:space="preserve">3.37216711044312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39683294296265</t>
+    <t xml:space="preserve">3.39683270454407</t>
   </si>
   <si>
     <t xml:space="preserve">3.35278677940369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40388011932373</t>
+    <t xml:space="preserve">3.40388035774231</t>
   </si>
   <si>
     <t xml:space="preserve">3.58535027503967</t>
@@ -4931,25 +4931,25 @@
     <t xml:space="preserve">3.53778004646301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45145010948181</t>
+    <t xml:space="preserve">3.45144987106323</t>
   </si>
   <si>
     <t xml:space="preserve">3.5624463558197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54306578636169</t>
+    <t xml:space="preserve">3.54306554794312</t>
   </si>
   <si>
     <t xml:space="preserve">3.58182644844055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58711194992065</t>
+    <t xml:space="preserve">3.58711171150208</t>
   </si>
   <si>
     <t xml:space="preserve">3.55716061592102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51839995384216</t>
+    <t xml:space="preserve">3.51840019226074</t>
   </si>
   <si>
     <t xml:space="preserve">3.46730661392212</t>
@@ -4958,7 +4958,7 @@
     <t xml:space="preserve">3.4690682888031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41621327400208</t>
+    <t xml:space="preserve">3.4162130355835</t>
   </si>
   <si>
     <t xml:space="preserve">3.40211844444275</t>
@@ -4970,10 +4970,10 @@
     <t xml:space="preserve">3.45497369766235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43383169174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4584972858429</t>
+    <t xml:space="preserve">3.43383145332336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45849752426147</t>
   </si>
   <si>
     <t xml:space="preserve">3.42678427696228</t>
@@ -4997,10 +4997,10 @@
     <t xml:space="preserve">3.5677318572998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56420803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55187487602234</t>
+    <t xml:space="preserve">3.5642077922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55187511444092</t>
   </si>
   <si>
     <t xml:space="preserve">3.46554470062256</t>
@@ -5012,7 +5012,7 @@
     <t xml:space="preserve">3.47611594200134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.558922290802</t>
+    <t xml:space="preserve">3.55892252922058</t>
   </si>
   <si>
     <t xml:space="preserve">3.5536367893219</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">3.57301735877991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57654070854187</t>
+    <t xml:space="preserve">3.57654094696045</t>
   </si>
   <si>
     <t xml:space="preserve">3.5483512878418</t>
@@ -5039,7 +5039,7 @@
     <t xml:space="preserve">3.73510646820068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69986963272095</t>
+    <t xml:space="preserve">3.69986987113953</t>
   </si>
   <si>
     <t xml:space="preserve">3.80029511451721</t>
@@ -5048,7 +5048,7 @@
     <t xml:space="preserve">3.72277355194092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71396470069885</t>
+    <t xml:space="preserve">3.71396446228027</t>
   </si>
   <si>
     <t xml:space="preserve">3.66815662384033</t>
@@ -5060,7 +5060,7 @@
     <t xml:space="preserve">3.69458413124084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78796219825745</t>
+    <t xml:space="preserve">3.78796195983887</t>
   </si>
   <si>
     <t xml:space="preserve">3.77210545539856</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">3.64701437950134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70867896080017</t>
+    <t xml:space="preserve">3.70867919921875</t>
   </si>
   <si>
     <t xml:space="preserve">3.64172887802124</t>
@@ -5102,79 +5102,79 @@
     <t xml:space="preserve">3.71220302581787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6857750415802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67168045043945</t>
+    <t xml:space="preserve">3.68577527999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67168068885803</t>
   </si>
   <si>
     <t xml:space="preserve">3.65229988098145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65582394599915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71748805046082</t>
+    <t xml:space="preserve">3.65582370758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71748828887939</t>
   </si>
   <si>
     <t xml:space="preserve">3.69634628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63468146324158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62587237358093</t>
+    <t xml:space="preserve">3.63468170166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62587261199951</t>
   </si>
   <si>
     <t xml:space="preserve">3.70163178443909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72453570365906</t>
+    <t xml:space="preserve">3.72453594207764</t>
   </si>
   <si>
     <t xml:space="preserve">3.72982144355774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76858162879944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81615138053894</t>
+    <t xml:space="preserve">3.76858139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81615114212036</t>
   </si>
   <si>
     <t xml:space="preserve">3.81967520713806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88133955001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85138869285583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83905553817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87781620025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87605428695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84610271453857</t>
+    <t xml:space="preserve">3.88133978843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85138845443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83905529975891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87781572341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87605404853821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84610295295715</t>
   </si>
   <si>
     <t xml:space="preserve">3.89895820617676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82672214508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77915263175964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80205678939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76329588890076</t>
+    <t xml:space="preserve">3.82672262191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77915287017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80205655097961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76329612731934</t>
   </si>
   <si>
     <t xml:space="preserve">3.74920153617859</t>
@@ -5183,28 +5183,28 @@
     <t xml:space="preserve">3.74039196968079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67344236373901</t>
+    <t xml:space="preserve">3.67344212532043</t>
   </si>
   <si>
     <t xml:space="preserve">3.73158311843872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8584361076355</t>
+    <t xml:space="preserve">3.85843563079834</t>
   </si>
   <si>
     <t xml:space="preserve">3.82496070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81086587905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88662552833557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91833829879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90071964263916</t>
+    <t xml:space="preserve">3.81086611747742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88662528991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91833806037903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90071988105774</t>
   </si>
   <si>
     <t xml:space="preserve">4.06633329391479</t>
@@ -71138,7 +71138,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6495138889</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>193931</v>
@@ -71159,6 +71159,32 @@
         <v>1983</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6494560185</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>129653</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>6.22499990463257</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>6.15500020980835</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>6.15500020980835</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>6.17500019073486</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1962</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24674654006958</t>
+    <t xml:space="preserve">4.24674606323242</t>
   </si>
   <si>
     <t xml:space="preserve">ANIM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33184623718262</t>
+    <t xml:space="preserve">4.33184719085693</t>
   </si>
   <si>
     <t xml:space="preserve">4.13419580459595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96948647499084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95301604270935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94203495979309</t>
+    <t xml:space="preserve">3.96948671340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95301580429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94203472137451</t>
   </si>
   <si>
     <t xml:space="preserve">4.07380294799805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93105483055115</t>
+    <t xml:space="preserve">3.93105530738831</t>
   </si>
   <si>
     <t xml:space="preserve">3.8267388343811</t>
@@ -71,172 +71,172 @@
     <t xml:space="preserve">3.76085543632507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67850065231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73889374732971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40398645401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53300809860229</t>
+    <t xml:space="preserve">3.67850089073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73889398574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40398621559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53300738334656</t>
   </si>
   <si>
     <t xml:space="preserve">3.76909065246582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79379773139954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79928755760193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88438749313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67575573921204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70595192909241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64006876945496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57967519760132</t>
+    <t xml:space="preserve">3.79379725456238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79928731918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88438725471497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67575550079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70595240592957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64006853103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5796754360199</t>
   </si>
   <si>
     <t xml:space="preserve">3.35731840133667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4506528377533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37653422355652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06633234024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95652651786804</t>
+    <t xml:space="preserve">3.45065307617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37653470039368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06633162498474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95652627944946</t>
   </si>
   <si>
     <t xml:space="preserve">3.19535446166992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9839780330658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2420220375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20084404945374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4863395690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38202452659607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31065058708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38751482963562</t>
+    <t xml:space="preserve">2.98397827148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24202251434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20084452629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48634028434753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38202476501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31065082550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38751530647278</t>
   </si>
   <si>
     <t xml:space="preserve">3.26672840118408</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11299967765808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08554816246033</t>
+    <t xml:space="preserve">3.1129994392395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08554863929749</t>
   </si>
   <si>
     <t xml:space="preserve">3.07182240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06084203720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15692281723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30241513252258</t>
+    <t xml:space="preserve">3.06084179878235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15692162513733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.302414894104</t>
   </si>
   <si>
     <t xml:space="preserve">3.43967318534851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35182785987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28319954872131</t>
+    <t xml:space="preserve">3.3518283367157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.283198595047</t>
   </si>
   <si>
     <t xml:space="preserve">3.22280597686768</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25300240516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57692980766296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47261476516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46437907218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59065580368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56320524215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61261653900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51653742790222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43418216705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37104392051697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45888924598694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53026270866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32986664772034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2722179889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09103870391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23653149604797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34084701538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28594446182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31888628005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23927664756775</t>
+    <t xml:space="preserve">3.25300216674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57693004608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47261428833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46437954902649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.590656042099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56320548057556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6126172542572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51653671264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4341824054718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37104368209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45888876914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53026294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32986640930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27221846580505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09103846549988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23653173446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34084725379944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28594422340393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31888580322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23927736282349</t>
   </si>
   <si>
     <t xml:space="preserve">3.42594695091248</t>
@@ -245,73 +245,73 @@
     <t xml:space="preserve">3.41771173477173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40947604179382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41496610641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44241809844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46163392066956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44790816307068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49732089042664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39300537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37378931045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26123833656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26947331428528</t>
+    <t xml:space="preserve">3.40947651863098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41496586799622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44241786003113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46163368225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4479079246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49732065200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39300560951233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37378978729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26123809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2694730758667</t>
   </si>
   <si>
     <t xml:space="preserve">3.15417766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16241240501404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01966547966003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94829130172729</t>
+    <t xml:space="preserve">3.16241264343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01966500282288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94829106330872</t>
   </si>
   <si>
     <t xml:space="preserve">2.82201409339905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93182015419006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0690770149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00044894218445</t>
+    <t xml:space="preserve">2.93182039260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06907749176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00044822692871</t>
   </si>
   <si>
     <t xml:space="preserve">2.91809439659119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8741717338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85221028327942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89064288139343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97133851051331</t>
+    <t xml:space="preserve">2.87417149543762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85221076011658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89064264297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97133874893188</t>
   </si>
   <si>
     <t xml:space="preserve">3.06356287002563</t>
@@ -320,64 +320,64 @@
     <t xml:space="preserve">3.23648285865784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24224638938904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29988670349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17884302139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15866875648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04050707817078</t>
+    <t xml:space="preserve">3.2422468662262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29988622665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17884278297424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15866851806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04050731658936</t>
   </si>
   <si>
     <t xml:space="preserve">2.979984998703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96269297599792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0232150554657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00015926361084</t>
+    <t xml:space="preserve">2.96269273757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02321481704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00015902519226</t>
   </si>
   <si>
     <t xml:space="preserve">2.95692849159241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81859254837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7966902256012</t>
+    <t xml:space="preserve">2.81859278678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79668974876404</t>
   </si>
   <si>
     <t xml:space="preserve">2.66988182067871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61454772949219</t>
+    <t xml:space="preserve">2.61454725265503</t>
   </si>
   <si>
     <t xml:space="preserve">2.54768514633179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70331263542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75288343429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90505313873291</t>
+    <t xml:space="preserve">2.70331287384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75288367271423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90505337715149</t>
   </si>
   <si>
     <t xml:space="preserve">2.92234468460083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96845722198486</t>
+    <t xml:space="preserve">2.96845698356628</t>
   </si>
   <si>
     <t xml:space="preserve">2.53615689277649</t>
@@ -386,37 +386,37 @@
     <t xml:space="preserve">2.26179122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49004530906677</t>
+    <t xml:space="preserve">2.49004554748535</t>
   </si>
   <si>
     <t xml:space="preserve">2.41972422599792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4266414642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49235057830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36900115013123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28830575942993</t>
+    <t xml:space="preserve">2.42664122581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49235081672668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3690013885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28830552101135</t>
   </si>
   <si>
     <t xml:space="preserve">2.29752779006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30559778213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35747313499451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43240523338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61108875274658</t>
+    <t xml:space="preserve">2.30559730529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35747289657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4324049949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61108899116516</t>
   </si>
   <si>
     <t xml:space="preserve">2.59379720687866</t>
@@ -425,16 +425,16 @@
     <t xml:space="preserve">2.68025732040405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59725522994995</t>
+    <t xml:space="preserve">2.59725570678711</t>
   </si>
   <si>
     <t xml:space="preserve">2.60647797584534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56958794593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62838053703308</t>
+    <t xml:space="preserve">2.56958818435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62838077545166</t>
   </si>
   <si>
     <t xml:space="preserve">2.62261700630188</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">2.59494972229004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6168532371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54653215408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63414525985718</t>
+    <t xml:space="preserve">2.61685347557068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54653263092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63414549827576</t>
   </si>
   <si>
     <t xml:space="preserve">2.58226919174194</t>
@@ -458,37 +458,37 @@
     <t xml:space="preserve">2.40358519554138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41511344909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43816947937012</t>
+    <t xml:space="preserve">2.4151132106781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4381697177887</t>
   </si>
   <si>
     <t xml:space="preserve">2.55114364624023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58572769165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65143704414368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65489530563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60417246818542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54307436943054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41857147216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37015390396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39321041107178</t>
+    <t xml:space="preserve">2.58572793006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6514368057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65489554405212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.604172706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54307413101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41857171058655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37015414237976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39321064949036</t>
   </si>
   <si>
     <t xml:space="preserve">2.51310157775879</t>
@@ -497,103 +497,103 @@
     <t xml:space="preserve">2.50964260101318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4612250328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44854474067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50733709335327</t>
+    <t xml:space="preserve">2.46122527122498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44854426383972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50733733177185</t>
   </si>
   <si>
     <t xml:space="preserve">2.50157332420349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49696230888367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51540684700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53039360046387</t>
+    <t xml:space="preserve">2.49696207046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51540660858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53039336204529</t>
   </si>
   <si>
     <t xml:space="preserve">2.57304692268372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66181230545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62722826004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73789715766907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83012056350708</t>
+    <t xml:space="preserve">2.66181206703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62722849845886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73789691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83012080192566</t>
   </si>
   <si>
     <t xml:space="preserve">2.79092574119568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67449331283569</t>
+    <t xml:space="preserve">2.67449355125427</t>
   </si>
   <si>
     <t xml:space="preserve">2.65604829788208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64797902107239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65720105171204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6456732749939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5200183391571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51886487007141</t>
+    <t xml:space="preserve">2.64797854423523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65720081329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64567351341248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52001786231995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51886510848999</t>
   </si>
   <si>
     <t xml:space="preserve">2.49580955505371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5211706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52462911605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54192185401917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47275352478027</t>
+    <t xml:space="preserve">2.52117109298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52462887763977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54192161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47275328636169</t>
   </si>
   <si>
     <t xml:space="preserve">2.46929526329041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39436316490173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32173681259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32519483566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24795770645142</t>
+    <t xml:space="preserve">2.39436268806458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32173657417297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32519507408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24795746803284</t>
   </si>
   <si>
     <t xml:space="preserve">2.26524949073792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3263475894928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38629269599915</t>
+    <t xml:space="preserve">2.32634782791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38629341125488</t>
   </si>
   <si>
     <t xml:space="preserve">2.4439332485199</t>
@@ -602,13 +602,13 @@
     <t xml:space="preserve">2.44623875617981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57074117660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57996344566345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56267166137695</t>
+    <t xml:space="preserve">2.5707414150238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57996320724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56267189979553</t>
   </si>
   <si>
     <t xml:space="preserve">2.55806040763855</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">2.55344891548157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70907735824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67910480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58111643791199</t>
+    <t xml:space="preserve">2.70907711982727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67910432815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58111572265625</t>
   </si>
   <si>
     <t xml:space="preserve">2.80130100250244</t>
@@ -650,55 +650,55 @@
     <t xml:space="preserve">2.72291088104248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78285646438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82551002502441</t>
+    <t xml:space="preserve">2.78285622596741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82551026344299</t>
   </si>
   <si>
     <t xml:space="preserve">2.92522668838501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96557426452637</t>
+    <t xml:space="preserve">2.96557450294495</t>
   </si>
   <si>
     <t xml:space="preserve">2.91081690788269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00592255592346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03474283218384</t>
+    <t xml:space="preserve">3.00592231750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03474259376526</t>
   </si>
   <si>
     <t xml:space="preserve">2.99727654457092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98574876785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94828295707703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93963694572449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97422075271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99151277542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01456880569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0318603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16155052185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13849496841431</t>
+    <t xml:space="preserve">2.98574805259705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94828248023987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93963670730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97422170639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99151253700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.014568567276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03186082839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16155099868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13849520683289</t>
   </si>
   <si>
     <t xml:space="preserve">3.11255645751953</t>
@@ -707,31 +707,31 @@
     <t xml:space="preserve">3.12984871864319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20478057861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16443204879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19613432884216</t>
+    <t xml:space="preserve">3.20478081703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16443276405334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19613480567932</t>
   </si>
   <si>
     <t xml:space="preserve">3.1990168094635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12408471107483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14137673377991</t>
+    <t xml:space="preserve">3.12408447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14137697219849</t>
   </si>
   <si>
     <t xml:space="preserve">3.08373713493347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30276846885681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26242017745972</t>
+    <t xml:space="preserve">3.30276918411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26242136955261</t>
   </si>
   <si>
     <t xml:space="preserve">3.18748879432678</t>
@@ -749,100 +749,100 @@
     <t xml:space="preserve">3.24801015853882</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26818442344666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23936438560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09238243103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10102868080139</t>
+    <t xml:space="preserve">3.2681839466095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23936486244202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09238266944885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10102844238281</t>
   </si>
   <si>
     <t xml:space="preserve">3.05491662025452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08085441589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11832046508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15002298355103</t>
+    <t xml:space="preserve">3.08085417747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11832070350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15002250671387</t>
   </si>
   <si>
     <t xml:space="preserve">3.01168704032898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92810893058777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95404672622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78516173362732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91369867324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98863077163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00304079055786</t>
+    <t xml:space="preserve">2.92810845375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95404720306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78516149520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91369891166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98863124847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00304055213928</t>
   </si>
   <si>
     <t xml:space="preserve">3.02609658241272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07797288894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0577986240387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18172454833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17019748687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23360061645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2451286315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25089287757874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27106642723083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27394890785217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28259468078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25665640830994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18460631370544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29412245750427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10391092300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34023451805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44398713111877</t>
+    <t xml:space="preserve">3.07797312736511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05779910087585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18172407150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17019701004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2336003780365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24512839317322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25089263916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27106714248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27394914627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28259444236755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25665616989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1846067905426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29412198066711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10391044616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34023499488831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44398665428162</t>
   </si>
   <si>
     <t xml:space="preserve">3.43245816230774</t>
@@ -851,52 +851,52 @@
     <t xml:space="preserve">3.46416044235229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45839643478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49298024177551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4468686580658</t>
+    <t xml:space="preserve">3.45839667320251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49298048019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44686818122864</t>
   </si>
   <si>
     <t xml:space="preserve">3.50450897216797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60249614715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51603674888611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4699239730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44110465049744</t>
+    <t xml:space="preserve">3.6024968624115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51603627204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46992516517639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44110441207886</t>
   </si>
   <si>
     <t xml:space="preserve">3.42381286621094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41228413581848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39499235153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37193632125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48935270309448</t>
+    <t xml:space="preserve">3.41228461265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39499282836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37193584442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4893524646759</t>
   </si>
   <si>
     <t xml:space="preserve">3.49236297607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5947253704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72117352485657</t>
+    <t xml:space="preserve">3.59472560882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72117328643799</t>
   </si>
   <si>
     <t xml:space="preserve">3.7151517868042</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">3.4682776927948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41107511520386</t>
+    <t xml:space="preserve">3.41107559204102</t>
   </si>
   <si>
     <t xml:space="preserve">3.49838447570801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54053330421448</t>
+    <t xml:space="preserve">3.5405330657959</t>
   </si>
   <si>
     <t xml:space="preserve">3.50440573692322</t>
@@ -923,61 +923,61 @@
     <t xml:space="preserve">3.51644825935364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54956531524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70913004875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72418308258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64891672134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75127935409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72719383239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76332211494446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73923707008362</t>
+    <t xml:space="preserve">3.54956555366516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70912981033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72418403625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64891695976257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75127911567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72719407081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76332235336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7392373085022</t>
   </si>
   <si>
     <t xml:space="preserve">3.74525737762451</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71214127540588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70310878753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75730085372925</t>
+    <t xml:space="preserve">3.71214056015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70310926437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75730109214783</t>
   </si>
   <si>
     <t xml:space="preserve">3.7753643989563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77837562561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84159922599792</t>
+    <t xml:space="preserve">3.77837467193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84160041809082</t>
   </si>
   <si>
     <t xml:space="preserve">3.85966324806213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82654595375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09750556945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14266490936279</t>
+    <t xml:space="preserve">3.82654619216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09750509262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14266538619995</t>
   </si>
   <si>
     <t xml:space="preserve">4.19685697555542</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">4.22094202041626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19986772537231</t>
+    <t xml:space="preserve">4.19986724853516</t>
   </si>
   <si>
     <t xml:space="preserve">4.2450270652771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26911306381226</t>
+    <t xml:space="preserve">4.2691125869751</t>
   </si>
   <si>
     <t xml:space="preserve">4.26309156417847</t>
@@ -1013,31 +1013,31 @@
     <t xml:space="preserve">4.14567613601685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13664436340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.223952293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22696304321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33534717559814</t>
+    <t xml:space="preserve">4.13664388656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22395324707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22696352005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33534669876099</t>
   </si>
   <si>
     <t xml:space="preserve">4.25104904174805</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28717613220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11857986450195</t>
+    <t xml:space="preserve">4.28717660903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11857938766479</t>
   </si>
   <si>
     <t xml:space="preserve">4.25405979156494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09449481964111</t>
+    <t xml:space="preserve">4.09449434280396</t>
   </si>
   <si>
     <t xml:space="preserve">4.08847284317017</t>
@@ -1046,40 +1046,40 @@
     <t xml:space="preserve">4.04030275344849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05234479904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95901489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86267352104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86568450927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94396114349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94697308540344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95600390434265</t>
+    <t xml:space="preserve">4.05234575271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95901536941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86267304420471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86568474769592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94396162033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94697237014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95600414276123</t>
   </si>
   <si>
     <t xml:space="preserve">3.98008990287781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97406792640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07341957092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06438779830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98912167549133</t>
+    <t xml:space="preserve">3.97406840324402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07342004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06438827514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98912119865417</t>
   </si>
   <si>
     <t xml:space="preserve">3.96202564239502</t>
@@ -1088,16 +1088,16 @@
     <t xml:space="preserve">4.01320648193359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03428173065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00417470932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00116395950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90783405303955</t>
+    <t xml:space="preserve">4.0342812538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00417423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00116348266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90783381462097</t>
   </si>
   <si>
     <t xml:space="preserve">3.88976955413818</t>
@@ -1109,40 +1109,40 @@
     <t xml:space="preserve">4.0101957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11255884170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15771865844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06739902496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98611116409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93191885948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9018120765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87471675872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85364174842834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82353448867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579129219055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84762048721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8325674533844</t>
+    <t xml:space="preserve">4.11255836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15771818161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06739854812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9861114025116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93191862106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90181183815002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87471628189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85364127159119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82353496551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579057693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84762072563171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83256769180298</t>
   </si>
   <si>
     <t xml:space="preserve">3.88073778152466</t>
@@ -1151,136 +1151,136 @@
     <t xml:space="preserve">3.88374805450439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92589807510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92890810966492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88675951957703</t>
+    <t xml:space="preserve">3.92589735984802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92890858650208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88675928115845</t>
   </si>
   <si>
     <t xml:space="preserve">3.91385531425476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91084456443787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84460949897766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8205246925354</t>
+    <t xml:space="preserve">3.91084504127502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8446102142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82052516937256</t>
   </si>
   <si>
     <t xml:space="preserve">3.69106650352478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70611906051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55558681488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47429895401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33580899238586</t>
+    <t xml:space="preserve">3.70611953735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55558729171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47429871559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33580875396729</t>
   </si>
   <si>
     <t xml:space="preserve">3.40204310417175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52246952056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54354405403137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53150105476379</t>
+    <t xml:space="preserve">3.52246904373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54354381561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53150153160095</t>
   </si>
   <si>
     <t xml:space="preserve">3.573650598526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60074639320374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57666206359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53752326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55257558822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50139498710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45021390914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51042675971985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48634123802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43817162513733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40806436538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53451228141785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60977816581726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35387229919434</t>
+    <t xml:space="preserve">3.60074615478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5766613483429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53752303123474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55257630348206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50139427185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45021438598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51042652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48634171485901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43817138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4080650806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53451204299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60977864265442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35387253761292</t>
   </si>
   <si>
     <t xml:space="preserve">3.42612838745117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4441921710968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32376575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39000058174133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61278963088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73020529747009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66698050498962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64590692520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.633864402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81450295448303</t>
+    <t xml:space="preserve">3.44419264793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32376551628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39000034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61278986930847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73020482063293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6669807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64590716362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63386368751526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81450319290161</t>
   </si>
   <si>
     <t xml:space="preserve">3.86869549751282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93492984771729</t>
+    <t xml:space="preserve">3.93492960929871</t>
   </si>
   <si>
     <t xml:space="preserve">4.04331350326538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99213194847107</t>
+    <t xml:space="preserve">3.99213171005249</t>
   </si>
   <si>
     <t xml:space="preserve">3.98310017585754</t>
@@ -1295,13 +1295,13 @@
     <t xml:space="preserve">4.160728931427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07040929794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08245229721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80848240852356</t>
+    <t xml:space="preserve">4.07040977478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08245182037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8084819316864</t>
   </si>
   <si>
     <t xml:space="preserve">3.89880180358887</t>
@@ -1310,13 +1310,13 @@
     <t xml:space="preserve">3.91987681388855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78439617156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77235436439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79945015907288</t>
+    <t xml:space="preserve">3.78439593315125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77235460281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79945063591003</t>
   </si>
   <si>
     <t xml:space="preserve">3.73622584342957</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">3.75429081916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76633238792419</t>
+    <t xml:space="preserve">3.76633310317993</t>
   </si>
   <si>
     <t xml:space="preserve">3.63988518714905</t>
@@ -1334,13 +1334,13 @@
     <t xml:space="preserve">3.56160807609558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66999173164368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96503615379333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79342889785767</t>
+    <t xml:space="preserve">3.6699914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96503639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79342865943909</t>
   </si>
   <si>
     <t xml:space="preserve">3.74224758148193</t>
@@ -1349,19 +1349,19 @@
     <t xml:space="preserve">3.79164934158325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77612233161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78854370117188</t>
+    <t xml:space="preserve">3.77612257003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78854322433472</t>
   </si>
   <si>
     <t xml:space="preserve">3.70469880104065</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58359003067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55914235115051</t>
+    <t xml:space="preserve">3.58358955383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55914306640625</t>
   </si>
   <si>
     <t xml:space="preserve">3.55258846282959</t>
@@ -1382,118 +1382,118 @@
     <t xml:space="preserve">3.89998149871826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342737197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85082221031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81149506568909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63779807090759</t>
+    <t xml:space="preserve">3.89342713356018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85082197189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81149458885193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63779830932617</t>
   </si>
   <si>
     <t xml:space="preserve">3.75578093528748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73939418792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86065435409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099006652832</t>
+    <t xml:space="preserve">3.73939371109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86065411567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8409903049469</t>
   </si>
   <si>
     <t xml:space="preserve">3.81804847717285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96552753448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98846888542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93275451660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86720848083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84426760673523</t>
+    <t xml:space="preserve">3.96552801132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98846912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93275499343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86720871925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84426712989807</t>
   </si>
   <si>
     <t xml:space="preserve">3.91309070587158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82132625579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03107357025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04418277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0245189666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98191428184509</t>
+    <t xml:space="preserve">3.8213267326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03107404708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04418325424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02451848983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98191404342651</t>
   </si>
   <si>
     <t xml:space="preserve">3.90653657913208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99830055236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77544450759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76561284065247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71973037719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71645331382751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56897497177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50670671463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46737861633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27467393875122</t>
+    <t xml:space="preserve">3.99830079078674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77544403076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76561236381531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71973085403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71645307540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56897473335266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50670599937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46737909317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27467346191406</t>
   </si>
   <si>
     <t xml:space="preserve">2.93645668029785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03477573394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19077515602112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42149639129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41494202613831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33628678321838</t>
+    <t xml:space="preserve">3.03477597236633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19077491760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42149686813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41494250297546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33628702163696</t>
   </si>
   <si>
     <t xml:space="preserve">3.31662321090698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35595083236694</t>
+    <t xml:space="preserve">3.35595059394836</t>
   </si>
   <si>
     <t xml:space="preserve">3.211749792099</t>
@@ -1502,34 +1502,34 @@
     <t xml:space="preserve">3.30023646354675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32645511627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39855551719666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33956432342529</t>
+    <t xml:space="preserve">3.32645463943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39855575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33956360816956</t>
   </si>
   <si>
     <t xml:space="preserve">3.29040479660034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27729606628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28057289123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18290948867798</t>
+    <t xml:space="preserve">3.27729535102844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28057312965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1829092502594</t>
   </si>
   <si>
     <t xml:space="preserve">3.12260746955872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07148122787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01511192321777</t>
+    <t xml:space="preserve">3.07148146629333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01511216163635</t>
   </si>
   <si>
     <t xml:space="preserve">2.89975070953369</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">3.01380109786987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04919528961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97971701622009</t>
+    <t xml:space="preserve">3.04919576644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97971725463867</t>
   </si>
   <si>
     <t xml:space="preserve">3.02691006660461</t>
@@ -1553,19 +1553,19 @@
     <t xml:space="preserve">3.13440561294556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10425424575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04264116287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00200295448303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00462412834167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98233914375305</t>
+    <t xml:space="preserve">3.10425448417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04264140129089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00200271606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00462460517883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98233890533447</t>
   </si>
   <si>
     <t xml:space="preserve">2.98627185821533</t>
@@ -1574,25 +1574,25 @@
     <t xml:space="preserve">2.92072558403015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92728042602539</t>
+    <t xml:space="preserve">2.92728066444397</t>
   </si>
   <si>
     <t xml:space="preserve">3.00069189071655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01249051094055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03739738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95612025260925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92465829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84469270706177</t>
+    <t xml:space="preserve">3.01248979568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03739714622498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95612049102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92465853691101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84469246864319</t>
   </si>
   <si>
     <t xml:space="preserve">2.97709536552429</t>
@@ -1601,13 +1601,13 @@
     <t xml:space="preserve">3.00724625587463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89057445526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77259206771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79487776756287</t>
+    <t xml:space="preserve">2.89057469367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77259230613708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79487752914429</t>
   </si>
   <si>
     <t xml:space="preserve">2.73064255714417</t>
@@ -1616,37 +1616,37 @@
     <t xml:space="preserve">2.71228957176208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70049142837524</t>
+    <t xml:space="preserve">2.70049118995667</t>
   </si>
   <si>
     <t xml:space="preserve">2.77914643287659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76997017860413</t>
+    <t xml:space="preserve">2.76996994018555</t>
   </si>
   <si>
     <t xml:space="preserve">2.73719716072083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72146606445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6900041103363</t>
+    <t xml:space="preserve">2.7214663028717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69000434875488</t>
   </si>
   <si>
     <t xml:space="preserve">2.63625645637512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64936566352844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.620525598526</t>
+    <t xml:space="preserve">2.64936542510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62052536010742</t>
   </si>
   <si>
     <t xml:space="preserve">2.67689514160156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72015571594238</t>
+    <t xml:space="preserve">2.72015523910522</t>
   </si>
   <si>
     <t xml:space="preserve">2.87615466117859</t>
@@ -1655,37 +1655,37 @@
     <t xml:space="preserve">2.85124707221985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86697816848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93907856941223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91154956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91679310798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92596936225891</t>
+    <t xml:space="preserve">2.86697840690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93907904624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91154932975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91679286956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92596960067749</t>
   </si>
   <si>
     <t xml:space="preserve">2.94170045852661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99807000160217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04133009910583</t>
+    <t xml:space="preserve">2.99806976318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04133033752441</t>
   </si>
   <si>
     <t xml:space="preserve">2.99675917625427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99413704872131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96267509460449</t>
+    <t xml:space="preserve">2.99413728713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96267485618591</t>
   </si>
   <si>
     <t xml:space="preserve">2.96005344390869</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">2.91286015510559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77521395683289</t>
+    <t xml:space="preserve">2.77521371841431</t>
   </si>
   <si>
     <t xml:space="preserve">2.70704627037048</t>
@@ -1703,22 +1703,22 @@
     <t xml:space="preserve">2.68869352340698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70573472976685</t>
+    <t xml:space="preserve">2.705735206604</t>
   </si>
   <si>
     <t xml:space="preserve">2.74244117736816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64674353599548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64150023460388</t>
+    <t xml:space="preserve">2.64674401283264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64150047302246</t>
   </si>
   <si>
     <t xml:space="preserve">2.59692907333374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38193845748901</t>
+    <t xml:space="preserve">2.38193869590759</t>
   </si>
   <si>
     <t xml:space="preserve">2.46714806556702</t>
@@ -1730,61 +1730,61 @@
     <t xml:space="preserve">2.49074459075928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4710807800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48681211471558</t>
+    <t xml:space="preserve">2.47108054161072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48681163787842</t>
   </si>
   <si>
     <t xml:space="preserve">2.41995477676392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31639218330383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25871229171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20365357398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25215744972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28493070602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38587141036987</t>
+    <t xml:space="preserve">2.31639242172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25871205329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20365333557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25215768814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28493046760559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38587117195129</t>
   </si>
   <si>
     <t xml:space="preserve">2.39242577552795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42519879341125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45928239822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54973578453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4723916053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44617366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45797181129456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.475013256073</t>
+    <t xml:space="preserve">2.42519855499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45928287506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54973602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47239208221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44617342948914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4579713344574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47501373291016</t>
   </si>
   <si>
     <t xml:space="preserve">2.54842519760132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43044257164001</t>
+    <t xml:space="preserve">2.43044233322144</t>
   </si>
   <si>
     <t xml:space="preserve">2.40815687179565</t>
@@ -1796,40 +1796,40 @@
     <t xml:space="preserve">2.28886342048645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27968692779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25740122795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17612409591675</t>
+    <t xml:space="preserve">2.27968668937683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25740098953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17612433433533</t>
   </si>
   <si>
     <t xml:space="preserve">2.18661141395569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13155293464661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29410696029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35178732872009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766931533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44748425483704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42388772964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40946769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40029120445251</t>
+    <t xml:space="preserve">2.13155317306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29410719871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35178709030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766955375671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44748449325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42388796806335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40946793556213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40029096603394</t>
   </si>
   <si>
     <t xml:space="preserve">2.21938443183899</t>
@@ -1838,16 +1838,16 @@
     <t xml:space="preserve">2.19447708129883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25477933883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31901407241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32687973976135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26264500617981</t>
+    <t xml:space="preserve">2.25477957725525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31901454925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32687997817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26264452934265</t>
   </si>
   <si>
     <t xml:space="preserve">2.17743539810181</t>
@@ -1859,22 +1859,22 @@
     <t xml:space="preserve">2.14597320556641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12237691879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12368774414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10271286964417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11713314056396</t>
+    <t xml:space="preserve">2.12237668037415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12368750572205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10271263122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11713290214539</t>
   </si>
   <si>
     <t xml:space="preserve">2.14728426933289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15121674537659</t>
+    <t xml:space="preserve">2.15121698379517</t>
   </si>
   <si>
     <t xml:space="preserve">2.23904824256897</t>
@@ -1886,61 +1886,61 @@
     <t xml:space="preserve">2.36489653587341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34785437583923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37407255172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25084614753723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39504790306091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35572004318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41340017318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43306422233582</t>
+    <t xml:space="preserve">2.34785485267639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37407279014587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25084662437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39504766464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35572028160095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41340041160583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43306398391724</t>
   </si>
   <si>
     <t xml:space="preserve">2.44486260414124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44224071502686</t>
+    <t xml:space="preserve">2.44224095344543</t>
   </si>
   <si>
     <t xml:space="preserve">2.43175339698792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38456010818481</t>
+    <t xml:space="preserve">2.38456034660339</t>
   </si>
   <si>
     <t xml:space="preserve">2.35309815406799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34654402732849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35440897941589</t>
+    <t xml:space="preserve">2.34654355049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35440921783447</t>
   </si>
   <si>
     <t xml:space="preserve">2.37145113945007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28755259513855</t>
+    <t xml:space="preserve">2.28755211830139</t>
   </si>
   <si>
     <t xml:space="preserve">2.26788854598999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31114912033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37931680679321</t>
+    <t xml:space="preserve">2.31114888191223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37931656837463</t>
   </si>
   <si>
     <t xml:space="preserve">2.40291309356689</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">2.33605623245239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39898061752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37669491767883</t>
+    <t xml:space="preserve">2.39898037910461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37669467926025</t>
   </si>
   <si>
     <t xml:space="preserve">2.50123190879822</t>
@@ -1967,13 +1967,13 @@
     <t xml:space="preserve">2.54318141937256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52613949775696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5038537979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49336647987366</t>
+    <t xml:space="preserve">2.52613973617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50385355949402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49336624145508</t>
   </si>
   <si>
     <t xml:space="preserve">2.42782044410706</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">2.39635848999023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38718199729919</t>
+    <t xml:space="preserve">2.38718175888062</t>
   </si>
   <si>
     <t xml:space="preserve">2.37276196479797</t>
@@ -1991,22 +1991,22 @@
     <t xml:space="preserve">2.37800574302673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33867788314819</t>
+    <t xml:space="preserve">2.33867812156677</t>
   </si>
   <si>
     <t xml:space="preserve">2.29935026168823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38062739372253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30459403991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38849329948425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45666098594666</t>
+    <t xml:space="preserve">2.38062763214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30459427833557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38849306106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45666074752808</t>
   </si>
   <si>
     <t xml:space="preserve">2.40160250663757</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">2.34130001068115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34392189979553</t>
+    <t xml:space="preserve">2.34392166137695</t>
   </si>
   <si>
     <t xml:space="preserve">2.38324928283691</t>
@@ -2024,52 +2024,52 @@
     <t xml:space="preserve">2.32556867599487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30328345298767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30590486526489</t>
+    <t xml:space="preserve">2.30328321456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30590510368347</t>
   </si>
   <si>
     <t xml:space="preserve">2.34523272514343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32425832748413</t>
+    <t xml:space="preserve">2.32425785064697</t>
   </si>
   <si>
     <t xml:space="preserve">2.30983781814575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21545171737671</t>
+    <t xml:space="preserve">2.21545195579529</t>
   </si>
   <si>
     <t xml:space="preserve">2.19054436683655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0909149646759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08698201179504</t>
+    <t xml:space="preserve">2.09091472625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08698177337646</t>
   </si>
   <si>
     <t xml:space="preserve">1.99783957004547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03978848457336</t>
+    <t xml:space="preserve">2.03978896141052</t>
   </si>
   <si>
     <t xml:space="preserve">1.9768648147583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99128496646881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97817552089691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98996269702911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99966990947723</t>
+    <t xml:space="preserve">1.99128484725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9781756401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98996257781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99967014789581</t>
   </si>
   <si>
     <t xml:space="preserve">1.97470891475677</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">1.94420063495636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9192396402359</t>
+    <t xml:space="preserve">1.91923940181732</t>
   </si>
   <si>
     <t xml:space="preserve">1.89843845367432</t>
@@ -2087,34 +2087,34 @@
     <t xml:space="preserve">1.86377012729645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82632851600647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87625074386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87902426719666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83742225170135</t>
+    <t xml:space="preserve">1.82632839679718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87625086307526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87902414798737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83742237091064</t>
   </si>
   <si>
     <t xml:space="preserve">1.95113444328308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9275598526001</t>
+    <t xml:space="preserve">1.92755973339081</t>
   </si>
   <si>
     <t xml:space="preserve">1.89982509613037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92062628269196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90953242778778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90675866603851</t>
+    <t xml:space="preserve">1.92062616348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90953230857849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9067587852478</t>
   </si>
   <si>
     <t xml:space="preserve">1.88734447956085</t>
@@ -2123,46 +2123,46 @@
     <t xml:space="preserve">1.88873136043549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88179767131805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0287914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98302912712097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03156471252441</t>
+    <t xml:space="preserve">1.88179755210876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02879166603088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98302924633026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03156495094299</t>
   </si>
   <si>
     <t xml:space="preserve">1.98857605457306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95945453643799</t>
+    <t xml:space="preserve">1.95945489406586</t>
   </si>
   <si>
     <t xml:space="preserve">2.00660371780396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00521659851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07177996635437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0939679145813</t>
+    <t xml:space="preserve">2.00521683692932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07178020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09396815299988</t>
   </si>
   <si>
     <t xml:space="preserve">2.14943718910217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22709393501282</t>
+    <t xml:space="preserve">2.22709441184998</t>
   </si>
   <si>
     <t xml:space="preserve">2.25344228744507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25898909568787</t>
+    <t xml:space="preserve">2.25898933410645</t>
   </si>
   <si>
     <t xml:space="preserve">2.26453614234924</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">2.31445860862732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30059146881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30891132354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31307196617126</t>
+    <t xml:space="preserve">2.30059123039246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30891156196594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31307172775269</t>
   </si>
   <si>
     <t xml:space="preserve">2.27424311637878</t>
@@ -2195,19 +2195,19 @@
     <t xml:space="preserve">2.22154760360718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24789571762085</t>
+    <t xml:space="preserve">2.24789524078369</t>
   </si>
   <si>
     <t xml:space="preserve">2.24650859832764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24512219429016</t>
+    <t xml:space="preserve">2.24512195587158</t>
   </si>
   <si>
     <t xml:space="preserve">2.28811049461365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32277917861938</t>
+    <t xml:space="preserve">2.32277870178223</t>
   </si>
   <si>
     <t xml:space="preserve">2.37824845314026</t>
@@ -2216,22 +2216,22 @@
     <t xml:space="preserve">2.30613827705383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23125457763672</t>
+    <t xml:space="preserve">2.23125433921814</t>
   </si>
   <si>
     <t xml:space="preserve">2.18687915802002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17162489891052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17439842224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22432112693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12170243263245</t>
+    <t xml:space="preserve">2.1716251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17439818382263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22432065010071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12170267105103</t>
   </si>
   <si>
     <t xml:space="preserve">2.10783529281616</t>
@@ -2240,13 +2240,13 @@
     <t xml:space="preserve">2.12863612174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09812784194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12724947929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1771719455719</t>
+    <t xml:space="preserve">2.09812831878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1272497177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17717218399048</t>
   </si>
   <si>
     <t xml:space="preserve">2.19103932380676</t>
@@ -2258,31 +2258,31 @@
     <t xml:space="preserve">2.2062931060791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19935989379883</t>
+    <t xml:space="preserve">2.19935965538025</t>
   </si>
   <si>
     <t xml:space="preserve">2.18549227714539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25760245323181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25621581077576</t>
+    <t xml:space="preserve">2.25760293006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25621557235718</t>
   </si>
   <si>
     <t xml:space="preserve">2.23957490921021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35606050491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38102149963379</t>
+    <t xml:space="preserve">2.35606074333191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38102197647095</t>
   </si>
   <si>
     <t xml:space="preserve">2.3671543598175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38379549980164</t>
+    <t xml:space="preserve">2.38379526138306</t>
   </si>
   <si>
     <t xml:space="preserve">2.43510484695435</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">2.49889421463013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42955756187439</t>
+    <t xml:space="preserve">2.42955732345581</t>
   </si>
   <si>
     <t xml:space="preserve">2.42817068099976</t>
@@ -2303,13 +2303,13 @@
     <t xml:space="preserve">2.44897174835205</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45867919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766240119934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38795566558838</t>
+    <t xml:space="preserve">2.45867896080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38795518875122</t>
   </si>
   <si>
     <t xml:space="preserve">2.37131452560425</t>
@@ -2330,31 +2330,31 @@
     <t xml:space="preserve">2.32693934440613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29920434951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31723213195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34496641159058</t>
+    <t xml:space="preserve">2.2992045879364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31723165512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34496665000916</t>
   </si>
   <si>
     <t xml:space="preserve">2.34635353088379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41153001785278</t>
+    <t xml:space="preserve">2.4115297794342</t>
   </si>
   <si>
     <t xml:space="preserve">2.46977281570435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48502707481384</t>
+    <t xml:space="preserve">2.48502683639526</t>
   </si>
   <si>
     <t xml:space="preserve">2.5696177482605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61537981033325</t>
+    <t xml:space="preserve">2.61538004875183</t>
   </si>
   <si>
     <t xml:space="preserve">2.6763961315155</t>
@@ -2366,19 +2366,19 @@
     <t xml:space="preserve">2.70690417289734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74711942672729</t>
+    <t xml:space="preserve">2.74711966514587</t>
   </si>
   <si>
     <t xml:space="preserve">2.72770524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75266623497009</t>
+    <t xml:space="preserve">2.75266647338867</t>
   </si>
   <si>
     <t xml:space="preserve">2.76237368583679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78594827651978</t>
+    <t xml:space="preserve">2.7859480381012</t>
   </si>
   <si>
     <t xml:space="preserve">2.77208089828491</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">2.69581031799316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70413112640381</t>
+    <t xml:space="preserve">2.70413088798523</t>
   </si>
   <si>
     <t xml:space="preserve">2.7207715511322</t>
@@ -2396,61 +2396,61 @@
     <t xml:space="preserve">2.80120205879211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78733491897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82893681526184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85528445243835</t>
+    <t xml:space="preserve">2.78733468055725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82893657684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85528469085693</t>
   </si>
   <si>
     <t xml:space="preserve">2.9468092918396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01614570617676</t>
+    <t xml:space="preserve">3.01614594459534</t>
   </si>
   <si>
     <t xml:space="preserve">3.02723979949951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04804086685181</t>
+    <t xml:space="preserve">3.04804039001465</t>
   </si>
   <si>
     <t xml:space="preserve">3.0799355506897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13679194450378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14649868011475</t>
+    <t xml:space="preserve">3.13679218292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1464991569519</t>
   </si>
   <si>
     <t xml:space="preserve">3.17562031745911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14511179924011</t>
+    <t xml:space="preserve">3.14511203765869</t>
   </si>
   <si>
     <t xml:space="preserve">3.23108959197998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24773025512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26298427581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2615978717804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22554230690002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18532705307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18394088745117</t>
+    <t xml:space="preserve">3.24773073196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26298451423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26159763336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2255425453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18532729148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18394064903259</t>
   </si>
   <si>
     <t xml:space="preserve">3.2560510635376</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">3.22831606864929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20196795463562</t>
+    <t xml:space="preserve">3.2019681930542</t>
   </si>
   <si>
     <t xml:space="preserve">3.24218344688416</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">3.26575803756714</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21306157112122</t>
+    <t xml:space="preserve">3.21306180953979</t>
   </si>
   <si>
     <t xml:space="preserve">3.19919466972351</t>
@@ -2483,85 +2483,85 @@
     <t xml:space="preserve">3.20890164375305</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22415614128113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1908745765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20335507392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06606817245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09241604804993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14788579940796</t>
+    <t xml:space="preserve">3.22415566444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19087433815002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20335483551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06606841087341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09241628646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14788508415222</t>
   </si>
   <si>
     <t xml:space="preserve">3.2061288356781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17839336395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17146015167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03694701194763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15343236923218</t>
+    <t xml:space="preserve">3.17839384078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17145967483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03694677352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15343260765076</t>
   </si>
   <si>
     <t xml:space="preserve">3.16868686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.970383644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03555989265442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14095234870911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12985754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14927220344543</t>
+    <t xml:space="preserve">2.97038316726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03555965423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14095211029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12985777854919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14927244186401</t>
   </si>
   <si>
     <t xml:space="preserve">3.17007327079773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12708425521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10073685646057</t>
+    <t xml:space="preserve">3.12708449363708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10073661804199</t>
   </si>
   <si>
     <t xml:space="preserve">3.07854890823364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11044406890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08964276313782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28239917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34202837944031</t>
+    <t xml:space="preserve">3.11044383049011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08964252471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28239870071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34202814102173</t>
   </si>
   <si>
     <t xml:space="preserve">3.34896206855774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93987512588501</t>
+    <t xml:space="preserve">2.93987536430359</t>
   </si>
   <si>
     <t xml:space="preserve">2.97315740585327</t>
@@ -2573,52 +2573,52 @@
     <t xml:space="preserve">2.73741245269775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58487176895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55159020423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49473404884338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29227066040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07039356231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95668148994446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99134981632233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6904284954071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78472590446472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65575993061066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52818059921265</t>
+    <t xml:space="preserve">2.58487153053284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55158996582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4947338104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29227089881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07039332389832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95668113231659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99134969711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69042825698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7847261428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65576004981995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52818048000336</t>
   </si>
   <si>
     <t xml:space="preserve">1.41030824184418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.485191822052</t>
+    <t xml:space="preserve">1.48519158363342</t>
   </si>
   <si>
     <t xml:space="preserve">1.49489891529083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60583746433258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67933440208435</t>
+    <t xml:space="preserve">1.60583770275116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67933452129364</t>
   </si>
   <si>
     <t xml:space="preserve">1.67656111717224</t>
@@ -2633,49 +2633,49 @@
     <t xml:space="preserve">1.69736206531525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72371017932892</t>
+    <t xml:space="preserve">1.72371029853821</t>
   </si>
   <si>
     <t xml:space="preserve">1.75421822071075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78888654708862</t>
+    <t xml:space="preserve">1.78888630867004</t>
   </si>
   <si>
     <t xml:space="preserve">2.02185773849487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06207299232483</t>
+    <t xml:space="preserve">2.06207323074341</t>
   </si>
   <si>
     <t xml:space="preserve">2.05375266075134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99412286281586</t>
+    <t xml:space="preserve">1.99412298202515</t>
   </si>
   <si>
     <t xml:space="preserve">1.97609543800354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96638834476471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94142735004425</t>
+    <t xml:space="preserve">1.966388463974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94142711162567</t>
   </si>
   <si>
     <t xml:space="preserve">1.8596099615097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86793041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92339944839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90121173858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14805054664612</t>
+    <t xml:space="preserve">1.8679301738739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92339968681335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90121209621429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1480507850647</t>
   </si>
   <si>
     <t xml:space="preserve">2.26730966567993</t>
@@ -2687,10 +2687,10 @@
     <t xml:space="preserve">2.22570776939392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13418316841125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28117728233337</t>
+    <t xml:space="preserve">2.13418340682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28117680549622</t>
   </si>
   <si>
     <t xml:space="preserve">2.35744738578796</t>
@@ -2705,16 +2705,16 @@
     <t xml:space="preserve">2.30752515792847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48411750793457</t>
+    <t xml:space="preserve">2.48411726951599</t>
   </si>
   <si>
     <t xml:space="preserve">2.51219487190247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49150633811951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49741721153259</t>
+    <t xml:space="preserve">2.49150609970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49741744995117</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456218719482</t>
@@ -2723,67 +2723,67 @@
     <t xml:space="preserve">2.57130527496338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72647023200989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75750350952148</t>
+    <t xml:space="preserve">2.72647047042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75750327110291</t>
   </si>
   <si>
     <t xml:space="preserve">2.80774712562561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86538004875183</t>
+    <t xml:space="preserve">2.86537981033325</t>
   </si>
   <si>
     <t xml:space="preserve">2.87572407722473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86833548545837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97473430633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20230984687805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16979885101318</t>
+    <t xml:space="preserve">2.86833524703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97473406791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20230960845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16979908943176</t>
   </si>
   <si>
     <t xml:space="preserve">3.14024376869202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93483448028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93631267547607</t>
+    <t xml:space="preserve">2.93483471870422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9363124370575</t>
   </si>
   <si>
     <t xml:space="preserve">2.94222378730774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99837827682495</t>
+    <t xml:space="preserve">2.99837875366211</t>
   </si>
   <si>
     <t xml:space="preserve">3.00281190872192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9584789276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88606834411621</t>
+    <t xml:space="preserve">2.95847916603088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88606858253479</t>
   </si>
   <si>
     <t xml:space="preserve">2.92744588851929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83582448959351</t>
+    <t xml:space="preserve">2.83582472801208</t>
   </si>
   <si>
     <t xml:space="preserve">2.89050197601318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88459062576294</t>
+    <t xml:space="preserve">2.88459086418152</t>
   </si>
   <si>
     <t xml:space="preserve">2.85946869850159</t>
@@ -2792,10 +2792,10 @@
     <t xml:space="preserve">2.82843589782715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86242461204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93779015541077</t>
+    <t xml:space="preserve">2.86242437362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93779039382935</t>
   </si>
   <si>
     <t xml:space="preserve">2.99542284011841</t>
@@ -2816,13 +2816,13 @@
     <t xml:space="preserve">2.93040132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97916793823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98212313652039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99394512176514</t>
+    <t xml:space="preserve">2.97916769981384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98212289810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99394536018372</t>
   </si>
   <si>
     <t xml:space="preserve">2.98951196670532</t>
@@ -2834,13 +2834,13 @@
     <t xml:space="preserve">2.95552325248718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94665670394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03384447097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0959107875824</t>
+    <t xml:space="preserve">2.94665694236755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03384470939636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09591054916382</t>
   </si>
   <si>
     <t xml:space="preserve">3.0175895690918</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">2.91857957839966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75602555274963</t>
+    <t xml:space="preserve">2.75602579116821</t>
   </si>
   <si>
     <t xml:space="preserve">2.81365847587585</t>
@@ -2867,31 +2867,31 @@
     <t xml:space="preserve">2.8535578250885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89493536949158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87720227241516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92153477668762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96291208267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91266822814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87424635887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84616875648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80479168891907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76784777641296</t>
+    <t xml:space="preserve">2.894935131073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87720203399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9215350151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9629123210907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91266846656799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87424659729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84616899490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80479192733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76784753799438</t>
   </si>
   <si>
     <t xml:space="preserve">2.75307035446167</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">2.7486367225647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77523636817932</t>
+    <t xml:space="preserve">2.7752366065979</t>
   </si>
   <si>
     <t xml:space="preserve">2.72351479530334</t>
@@ -2915,31 +2915,31 @@
     <t xml:space="preserve">2.76636981964111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79296970367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73681449890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69987082481384</t>
+    <t xml:space="preserve">2.79296946525574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73681473731995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69987058639526</t>
   </si>
   <si>
     <t xml:space="preserve">2.79592514038086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74272584915161</t>
+    <t xml:space="preserve">2.74272561073303</t>
   </si>
   <si>
     <t xml:space="preserve">2.75454783439636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74715876579285</t>
+    <t xml:space="preserve">2.74715900421143</t>
   </si>
   <si>
     <t xml:space="preserve">2.71612596511841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70873713493347</t>
+    <t xml:space="preserve">2.70873689651489</t>
   </si>
   <si>
     <t xml:space="preserve">2.70725965499878</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">2.52549481391907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54175019264221</t>
+    <t xml:space="preserve">2.54174995422363</t>
   </si>
   <si>
     <t xml:space="preserve">2.53436136245728</t>
@@ -2972,31 +2972,31 @@
     <t xml:space="preserve">2.50037288665771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43091821670532</t>
+    <t xml:space="preserve">2.43091797828674</t>
   </si>
   <si>
     <t xml:space="preserve">2.52992796897888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61120462417603</t>
+    <t xml:space="preserve">2.6112048625946</t>
   </si>
   <si>
     <t xml:space="preserve">2.54618358612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55209445953369</t>
+    <t xml:space="preserve">2.55209469795227</t>
   </si>
   <si>
     <t xml:space="preserve">2.67179298400879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60972714424133</t>
+    <t xml:space="preserve">2.60972690582275</t>
   </si>
   <si>
     <t xml:space="preserve">2.54322791099548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52845001220703</t>
+    <t xml:space="preserve">2.52845025062561</t>
   </si>
   <si>
     <t xml:space="preserve">2.47377300262451</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">2.63632678985596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60677170753479</t>
+    <t xml:space="preserve">2.60677194595337</t>
   </si>
   <si>
     <t xml:space="preserve">2.53140592575073</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">2.37180757522583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51662826538086</t>
+    <t xml:space="preserve">2.51662802696228</t>
   </si>
   <si>
     <t xml:space="preserve">2.58312749862671</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">2.64223790168762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4929838180542</t>
+    <t xml:space="preserve">2.49298405647278</t>
   </si>
   <si>
     <t xml:space="preserve">2.615638256073</t>
@@ -3047,10 +3047,10 @@
     <t xml:space="preserve">2.6525821685791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63041591644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71317028999329</t>
+    <t xml:space="preserve">2.63041567802429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71317005157471</t>
   </si>
   <si>
     <t xml:space="preserve">2.72794795036316</t>
@@ -3059,19 +3059,19 @@
     <t xml:space="preserve">2.74568128585815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83139157295227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79149198532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78853631019592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75898098945618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68361520767212</t>
+    <t xml:space="preserve">2.83139133453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79149222373962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78853607177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75898122787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6836154460907</t>
   </si>
   <si>
     <t xml:space="preserve">2.67031526565552</t>
@@ -3080,58 +3080,58 @@
     <t xml:space="preserve">2.66440439224243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64519357681274</t>
+    <t xml:space="preserve">2.64519333839417</t>
   </si>
   <si>
     <t xml:space="preserve">2.68065977096558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64962649345398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68213772773743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6259822845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65849351882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72055912017822</t>
+    <t xml:space="preserve">2.64962673187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68213748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62598252296448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65849328041077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7205593585968</t>
   </si>
   <si>
     <t xml:space="preserve">2.85651326179504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92301297187805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90380167961121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90084648132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98064517974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01463389396667</t>
+    <t xml:space="preserve">2.92301273345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90380191802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90084624290466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98064541816711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0146336555481</t>
   </si>
   <si>
     <t xml:space="preserve">3.03975582122803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07374429702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11807727813721</t>
+    <t xml:space="preserve">3.07374405860901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11807703971863</t>
   </si>
   <si>
     <t xml:space="preserve">3.06044459342957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0235002040863</t>
+    <t xml:space="preserve">3.02350044250488</t>
   </si>
   <si>
     <t xml:space="preserve">3.02941131591797</t>
@@ -3140,13 +3140,13 @@
     <t xml:space="preserve">2.89345741271973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8639018535614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90675735473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87129068374634</t>
+    <t xml:space="preserve">2.86390209197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90675711631775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87129092216492</t>
   </si>
   <si>
     <t xml:space="preserve">2.83434677124023</t>
@@ -3155,7 +3155,7 @@
     <t xml:space="preserve">2.91710162162781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04714465141296</t>
+    <t xml:space="preserve">3.04714441299438</t>
   </si>
   <si>
     <t xml:space="preserve">3.13285446166992</t>
@@ -3164,61 +3164,61 @@
     <t xml:space="preserve">3.10034418106079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1771879196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10625529289246</t>
+    <t xml:space="preserve">3.17718768119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10625505447388</t>
   </si>
   <si>
     <t xml:space="preserve">3.13581037521362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08408856391907</t>
+    <t xml:space="preserve">3.08408880233765</t>
   </si>
   <si>
     <t xml:space="preserve">3.00133371353149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9451789855957</t>
+    <t xml:space="preserve">2.94517922401428</t>
   </si>
   <si>
     <t xml:space="preserve">2.9998562335968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97177863121033</t>
+    <t xml:space="preserve">2.97177839279175</t>
   </si>
   <si>
     <t xml:space="preserve">2.93926787376404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08999991416931</t>
+    <t xml:space="preserve">3.08999967575073</t>
   </si>
   <si>
     <t xml:space="preserve">3.09147763252258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07669997215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08704400062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08852171897888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12694382667542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24664235115051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20526504516602</t>
+    <t xml:space="preserve">3.07669973373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08704423904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08852195739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12694334983826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24664258956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20526528358459</t>
   </si>
   <si>
     <t xml:space="preserve">3.21856474876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33235239982605</t>
+    <t xml:space="preserve">3.33235287666321</t>
   </si>
   <si>
     <t xml:space="preserve">3.33826375007629</t>
@@ -3233,13 +3233,13 @@
     <t xml:space="preserve">3.26142024993896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32496404647827</t>
+    <t xml:space="preserve">3.32496380805969</t>
   </si>
   <si>
     <t xml:space="preserve">3.30131959915161</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2924530506134</t>
+    <t xml:space="preserve">3.29245281219482</t>
   </si>
   <si>
     <t xml:space="preserve">3.28801965713501</t>
@@ -3248,10 +3248,10 @@
     <t xml:space="preserve">3.31609725952148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29393076896667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27324175834656</t>
+    <t xml:space="preserve">3.29393100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27324199676514</t>
   </si>
   <si>
     <t xml:space="preserve">3.24516487121582</t>
@@ -3260,13 +3260,13 @@
     <t xml:space="preserve">3.32274746894836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30649161338806</t>
+    <t xml:space="preserve">3.30649185180664</t>
   </si>
   <si>
     <t xml:space="preserve">3.31018614768982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29540848731995</t>
+    <t xml:space="preserve">3.29540872573853</t>
   </si>
   <si>
     <t xml:space="preserve">3.25107574462891</t>
@@ -3275,34 +3275,34 @@
     <t xml:space="preserve">3.28358626365662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28654217720032</t>
+    <t xml:space="preserve">3.28654193878174</t>
   </si>
   <si>
     <t xml:space="preserve">3.27915358543396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24073147773743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27767562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28136968612671</t>
+    <t xml:space="preserve">3.24073123931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27767515182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28136992454529</t>
   </si>
   <si>
     <t xml:space="preserve">3.18531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13433241844177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10329937934875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16314888000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13507175445557</t>
+    <t xml:space="preserve">3.13433265686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10329961776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16314911842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13507151603699</t>
   </si>
   <si>
     <t xml:space="preserve">3.17940425872803</t>
@@ -3311,79 +3311,79 @@
     <t xml:space="preserve">3.09664964675903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15354371070862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13654923439026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21043729782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26511478424072</t>
+    <t xml:space="preserve">3.15354347229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13654899597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21043705940247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26511454582214</t>
   </si>
   <si>
     <t xml:space="preserve">3.2274317741394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23925352096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24738144874573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31979203224182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33974146842957</t>
+    <t xml:space="preserve">3.23925375938416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24738121032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31979179382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33974123001099</t>
   </si>
   <si>
     <t xml:space="preserve">3.41362953186035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3205304145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32939743995667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31535792350769</t>
+    <t xml:space="preserve">3.32053017616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32939720153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31535816192627</t>
   </si>
   <si>
     <t xml:space="preserve">3.38761734962463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31846594810486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33789110183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33322882652283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33944487571716</t>
+    <t xml:space="preserve">3.31846618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33789086341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33322906494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33944439888</t>
   </si>
   <si>
     <t xml:space="preserve">3.33633685112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41325736045837</t>
+    <t xml:space="preserve">3.41325759887695</t>
   </si>
   <si>
     <t xml:space="preserve">3.37751650810242</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40471053123474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60206246376038</t>
+    <t xml:space="preserve">3.40471076965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60206270217896</t>
   </si>
   <si>
     <t xml:space="preserve">3.64868140220642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57098388671875</t>
+    <t xml:space="preserve">3.57098364830017</t>
   </si>
   <si>
     <t xml:space="preserve">3.55855202674866</t>
@@ -3392,10 +3392,10 @@
     <t xml:space="preserve">3.52203392982483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51037955284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4420051574707</t>
+    <t xml:space="preserve">3.51037931442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44200563430786</t>
   </si>
   <si>
     <t xml:space="preserve">3.47619247436523</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">3.44977521896362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38917112350464</t>
+    <t xml:space="preserve">3.38917088508606</t>
   </si>
   <si>
     <t xml:space="preserve">3.34022164344788</t>
@@ -3413,13 +3413,13 @@
     <t xml:space="preserve">3.32545924186707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34876847267151</t>
+    <t xml:space="preserve">3.34876823425293</t>
   </si>
   <si>
     <t xml:space="preserve">3.27417898178101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29904174804688</t>
+    <t xml:space="preserve">3.2990415096283</t>
   </si>
   <si>
     <t xml:space="preserve">3.25630831718445</t>
@@ -3428,22 +3428,22 @@
     <t xml:space="preserve">3.26407814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24776148796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27884030342102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25786232948303</t>
+    <t xml:space="preserve">3.24776124954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2788405418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25786185264587</t>
   </si>
   <si>
     <t xml:space="preserve">3.24076867103577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19337320327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25009226799011</t>
+    <t xml:space="preserve">3.19337344169617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25009250640869</t>
   </si>
   <si>
     <t xml:space="preserve">3.28738713264465</t>
@@ -3455,19 +3455,19 @@
     <t xml:space="preserve">3.24620747566223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20580458641052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16540193557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02632308006287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03098511695862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0915892124176</t>
+    <t xml:space="preserve">3.2058048248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16540169715881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02632331848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03098487854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09158897399902</t>
   </si>
   <si>
     <t xml:space="preserve">3.11956024169922</t>
@@ -3476,13 +3476,13 @@
     <t xml:space="preserve">3.1801643371582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22678303718567</t>
+    <t xml:space="preserve">3.22678327560425</t>
   </si>
   <si>
     <t xml:space="preserve">3.19570398330688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21202063560486</t>
+    <t xml:space="preserve">3.21202039718628</t>
   </si>
   <si>
     <t xml:space="preserve">3.22989130020142</t>
@@ -3491,22 +3491,22 @@
     <t xml:space="preserve">3.23066806793213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31458115577698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23299860954285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28894114494324</t>
+    <t xml:space="preserve">3.31458139419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23299884796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28894090652466</t>
   </si>
   <si>
     <t xml:space="preserve">3.30370378494263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37907028198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3355598449707</t>
+    <t xml:space="preserve">3.379070520401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33555960655212</t>
   </si>
   <si>
     <t xml:space="preserve">3.38606309890747</t>
@@ -3527,49 +3527,49 @@
     <t xml:space="preserve">3.34954524040222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36819267272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36508512496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39227962493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41248059272766</t>
+    <t xml:space="preserve">3.36819291114807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36508464813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39227914810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41248083114624</t>
   </si>
   <si>
     <t xml:space="preserve">3.37207770347595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39150214195251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39849472045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35032200813293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3534300327301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31535840034485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3472146987915</t>
+    <t xml:space="preserve">3.39150166511536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39849495887756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35032224655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35343027114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31535863876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34721446037292</t>
   </si>
   <si>
     <t xml:space="preserve">3.32157444953918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33089804649353</t>
+    <t xml:space="preserve">3.33089828491211</t>
   </si>
   <si>
     <t xml:space="preserve">3.32312822341919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28971815109253</t>
+    <t xml:space="preserve">3.28971862792969</t>
   </si>
   <si>
     <t xml:space="preserve">3.18715739250183</t>
@@ -3578,10 +3578,10 @@
     <t xml:space="preserve">3.19725775718689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2928261756897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28661012649536</t>
+    <t xml:space="preserve">3.29282593727112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28661036491394</t>
   </si>
   <si>
     <t xml:space="preserve">3.22056722640991</t>
@@ -3593,22 +3593,22 @@
     <t xml:space="preserve">3.21279764175415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20891284942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1762797832489</t>
+    <t xml:space="preserve">3.20891261100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17627930641174</t>
   </si>
   <si>
     <t xml:space="preserve">3.30758857727051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33012104034424</t>
+    <t xml:space="preserve">3.33012080192566</t>
   </si>
   <si>
     <t xml:space="preserve">3.36741590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39461016654968</t>
+    <t xml:space="preserve">3.3946099281311</t>
   </si>
   <si>
     <t xml:space="preserve">3.32623624801636</t>
@@ -3620,10 +3620,10 @@
     <t xml:space="preserve">3.45443749427795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48085451126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50183272361755</t>
+    <t xml:space="preserve">3.48085427284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50183296203613</t>
   </si>
   <si>
     <t xml:space="preserve">3.61682558059692</t>
@@ -3632,22 +3632,22 @@
     <t xml:space="preserve">3.57797646522522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58652353286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58963108062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5958468914032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57176041603088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57642221450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56632161140442</t>
+    <t xml:space="preserve">3.58652329444885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58963084220886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59584665298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57176089286804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57642245292664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.566321849823</t>
   </si>
   <si>
     <t xml:space="preserve">3.58108448982239</t>
@@ -3659,28 +3659,28 @@
     <t xml:space="preserve">3.63469576835632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65178918838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64246559143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62071013450623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62692618370056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6214873790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61294054985046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61060881614685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57409143447876</t>
+    <t xml:space="preserve">3.65178894996643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64246535301208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62070989608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62692594528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62148690223694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61294031143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61060953140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57409167289734</t>
   </si>
   <si>
     <t xml:space="preserve">3.50260972976685</t>
@@ -3692,37 +3692,37 @@
     <t xml:space="preserve">3.45132899284363</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39694094657898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3953869342804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26330089569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22833728790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23999190330505</t>
+    <t xml:space="preserve">3.39694118499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39538669586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2633011341095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22833704948425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23999166488647</t>
   </si>
   <si>
     <t xml:space="preserve">3.40004897117615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33711361885071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3658618927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37363195419312</t>
+    <t xml:space="preserve">3.33711385726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36586141586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37363171577454</t>
   </si>
   <si>
     <t xml:space="preserve">3.41791963577271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4365668296814</t>
+    <t xml:space="preserve">3.43656659126282</t>
   </si>
   <si>
     <t xml:space="preserve">3.31380438804626</t>
@@ -3731,37 +3731,37 @@
     <t xml:space="preserve">3.42025017738342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42957425117493</t>
+    <t xml:space="preserve">3.42957401275635</t>
   </si>
   <si>
     <t xml:space="preserve">3.4816312789917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49717092514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48707008361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48862409591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51814937591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54145884513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52436518669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48551630973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49794793128967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64634990692139</t>
+    <t xml:space="preserve">3.49717116355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48707032203674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48862385749817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51814913749695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54145860671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52436494827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48551607131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49794769287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64635014533997</t>
   </si>
   <si>
     <t xml:space="preserve">3.70151591300964</t>
@@ -3773,28 +3773,28 @@
     <t xml:space="preserve">3.64712738990784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65567398071289</t>
+    <t xml:space="preserve">3.65567374229431</t>
   </si>
   <si>
     <t xml:space="preserve">3.56865286827087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52824997901917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49639368057251</t>
+    <t xml:space="preserve">3.52824974060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49639391899109</t>
   </si>
   <si>
     <t xml:space="preserve">3.35420703887939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40237998962402</t>
+    <t xml:space="preserve">3.40237975120544</t>
   </si>
   <si>
     <t xml:space="preserve">3.41092658042908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41558790206909</t>
+    <t xml:space="preserve">3.41558814048767</t>
   </si>
   <si>
     <t xml:space="preserve">3.46531510353088</t>
@@ -3815,16 +3815,16 @@
     <t xml:space="preserve">3.54301261901855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56321358680725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75978875160217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62614893913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79708361625671</t>
+    <t xml:space="preserve">3.56321382522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75978899002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62614870071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79708385467529</t>
   </si>
   <si>
     <t xml:space="preserve">3.75124216079712</t>
@@ -3833,31 +3833,31 @@
     <t xml:space="preserve">3.65878224372864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66188979148865</t>
+    <t xml:space="preserve">3.66188955307007</t>
   </si>
   <si>
     <t xml:space="preserve">3.54612016677856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55622100830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38373255729675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4225811958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16384816169739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06361794471741</t>
+    <t xml:space="preserve">3.55622148513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38373231887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42258143424988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16384792327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06361818313599</t>
   </si>
   <si>
     <t xml:space="preserve">2.87481284141541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63394999504089</t>
+    <t xml:space="preserve">2.63395023345947</t>
   </si>
   <si>
     <t xml:space="preserve">2.59898614883423</t>
@@ -3869,25 +3869,25 @@
     <t xml:space="preserve">2.83751797676086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7450578212738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82042455673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93308591842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91366171836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07838034629822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05118632316589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05895614624023</t>
+    <t xml:space="preserve">2.74505758285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8204243183136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93308615684509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91366147994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0783805847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05118656158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05895638465881</t>
   </si>
   <si>
     <t xml:space="preserve">3.06284117698669</t>
@@ -3896,13 +3896,13 @@
     <t xml:space="preserve">3.1622941493988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14131569862366</t>
+    <t xml:space="preserve">3.14131593704224</t>
   </si>
   <si>
     <t xml:space="preserve">3.10246706008911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09780502319336</t>
+    <t xml:space="preserve">3.09780478477478</t>
   </si>
   <si>
     <t xml:space="preserve">3.13199186325073</t>
@@ -3911,55 +3911,55 @@
     <t xml:space="preserve">3.23843789100647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24853873252869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17161750793457</t>
+    <t xml:space="preserve">3.24853849411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17161774635315</t>
   </si>
   <si>
     <t xml:space="preserve">3.20269703865051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09236598014832</t>
+    <t xml:space="preserve">3.09236621856689</t>
   </si>
   <si>
     <t xml:space="preserve">3.35498404502869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36275386810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37984704971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40937280654907</t>
+    <t xml:space="preserve">3.36275410652161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37984752655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40937256813049</t>
   </si>
   <si>
     <t xml:space="preserve">3.42335820198059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53058075904846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59273910522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51970362663269</t>
+    <t xml:space="preserve">3.53058099746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59273934364319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51970338821411</t>
   </si>
   <si>
     <t xml:space="preserve">3.52747273445129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59740114212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61138606071472</t>
+    <t xml:space="preserve">3.59740090370178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6113862991333</t>
   </si>
   <si>
     <t xml:space="preserve">3.6937460899353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63624906539917</t>
+    <t xml:space="preserve">3.63624930381775</t>
   </si>
   <si>
     <t xml:space="preserve">3.60983228683472</t>
@@ -3968,22 +3968,22 @@
     <t xml:space="preserve">3.36430811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30059623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3814013004303</t>
+    <t xml:space="preserve">3.30059599876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38140177726746</t>
   </si>
   <si>
     <t xml:space="preserve">3.46686887741089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51659536361694</t>
+    <t xml:space="preserve">3.51659512519836</t>
   </si>
   <si>
     <t xml:space="preserve">3.53524303436279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5507824420929</t>
+    <t xml:space="preserve">3.55078268051147</t>
   </si>
   <si>
     <t xml:space="preserve">3.56942963600159</t>
@@ -3992,34 +3992,34 @@
     <t xml:space="preserve">3.51193332672119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63948941230774</t>
+    <t xml:space="preserve">3.63948965072632</t>
   </si>
   <si>
     <t xml:space="preserve">3.6378333568573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65771198272705</t>
+    <t xml:space="preserve">3.65771174430847</t>
   </si>
   <si>
     <t xml:space="preserve">3.71403574943542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7074089050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75876259803772</t>
+    <t xml:space="preserve">3.70740914344788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75876307487488</t>
   </si>
   <si>
     <t xml:space="preserve">3.71569180488586</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64611601829529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64942932128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59310531616211</t>
+    <t xml:space="preserve">3.64611577987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64942908287048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59310579299927</t>
   </si>
   <si>
     <t xml:space="preserve">3.59807538986206</t>
@@ -4031,13 +4031,13 @@
     <t xml:space="preserve">3.38272094726562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12595224380493</t>
+    <t xml:space="preserve">3.12595200538635</t>
   </si>
   <si>
     <t xml:space="preserve">2.97686076164246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01993155479431</t>
+    <t xml:space="preserve">3.01993131637573</t>
   </si>
   <si>
     <t xml:space="preserve">3.0828812122345</t>
@@ -4046,13 +4046,13 @@
     <t xml:space="preserve">2.97520422935486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96692109107971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01330542564392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98514366149902</t>
+    <t xml:space="preserve">2.96692132949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01330518722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98514342308044</t>
   </si>
   <si>
     <t xml:space="preserve">3.00005269050598</t>
@@ -4067,25 +4067,25 @@
     <t xml:space="preserve">3.03318405151367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04809308052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00999188423157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89734482765198</t>
+    <t xml:space="preserve">3.04809331893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00999212265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89734506607056</t>
   </si>
   <si>
     <t xml:space="preserve">2.90397143363953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90065860748291</t>
+    <t xml:space="preserve">2.90065836906433</t>
   </si>
   <si>
     <t xml:space="preserve">2.69690012931824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65879893302917</t>
+    <t xml:space="preserve">2.6587986946106</t>
   </si>
   <si>
     <t xml:space="preserve">2.73500108718872</t>
@@ -4100,22 +4100,22 @@
     <t xml:space="preserve">2.70683932304382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69193029403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52792978286743</t>
+    <t xml:space="preserve">2.69193005561829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52792954444885</t>
   </si>
   <si>
     <t xml:space="preserve">2.64885926246643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71346569061279</t>
+    <t xml:space="preserve">2.71346545219421</t>
   </si>
   <si>
     <t xml:space="preserve">2.81120347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78138518333435</t>
+    <t xml:space="preserve">2.78138494491577</t>
   </si>
   <si>
     <t xml:space="preserve">2.79132437705994</t>
@@ -4130,28 +4130,28 @@
     <t xml:space="preserve">2.71843552589417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71677875518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77475881576538</t>
+    <t xml:space="preserve">2.71677851676941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7747585773468</t>
   </si>
   <si>
     <t xml:space="preserve">2.83108234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83770847320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84599161148071</t>
+    <t xml:space="preserve">2.83770871162415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84599137306213</t>
   </si>
   <si>
     <t xml:space="preserve">2.92385029792786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9735472202301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95035529136658</t>
+    <t xml:space="preserve">2.97354745864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95035576820374</t>
   </si>
   <si>
     <t xml:space="preserve">2.91225433349609</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">2.93047666549683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98183035850525</t>
+    <t xml:space="preserve">2.98183012008667</t>
   </si>
   <si>
     <t xml:space="preserve">2.98017382621765</t>
@@ -4172,22 +4172,22 @@
     <t xml:space="preserve">2.92219400405884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93544602394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8542742729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75984978675842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7996072769165</t>
+    <t xml:space="preserve">2.93544626235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85427451133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75984954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79960751533508</t>
   </si>
   <si>
     <t xml:space="preserve">2.78469800949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82776927947998</t>
+    <t xml:space="preserve">2.8277690410614</t>
   </si>
   <si>
     <t xml:space="preserve">2.81617307662964</t>
@@ -4196,10 +4196,10 @@
     <t xml:space="preserve">2.81286001205444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68696022033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69358658790588</t>
+    <t xml:space="preserve">2.68696045875549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69358706474304</t>
   </si>
   <si>
     <t xml:space="preserve">2.64223313331604</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">2.68199062347412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73168778419495</t>
+    <t xml:space="preserve">2.73168802261353</t>
   </si>
   <si>
     <t xml:space="preserve">2.83439540863037</t>
@@ -4238,7 +4238,7 @@
     <t xml:space="preserve">2.51799011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53621220588684</t>
+    <t xml:space="preserve">2.536212682724</t>
   </si>
   <si>
     <t xml:space="preserve">2.46663618087769</t>
@@ -4247,19 +4247,19 @@
     <t xml:space="preserve">2.44344449043274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37221169471741</t>
+    <t xml:space="preserve">2.37221193313599</t>
   </si>
   <si>
     <t xml:space="preserve">2.4268786907196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65051579475403</t>
+    <t xml:space="preserve">2.65051603317261</t>
   </si>
   <si>
     <t xml:space="preserve">2.67702126502991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58259630203247</t>
+    <t xml:space="preserve">2.58259654045105</t>
   </si>
   <si>
     <t xml:space="preserve">2.54780840873718</t>
@@ -4268,7 +4268,7 @@
     <t xml:space="preserve">2.53124260902405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52461647987366</t>
+    <t xml:space="preserve">2.52461624145508</t>
   </si>
   <si>
     <t xml:space="preserve">2.42190909385681</t>
@@ -4286,10 +4286,10 @@
     <t xml:space="preserve">2.57100057601929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53952550888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52295970916748</t>
+    <t xml:space="preserve">2.53952574729919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52295994758606</t>
   </si>
   <si>
     <t xml:space="preserve">2.48817157745361</t>
@@ -4298,7 +4298,7 @@
     <t xml:space="preserve">2.59750533103943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62235403060913</t>
+    <t xml:space="preserve">2.62235426902771</t>
   </si>
   <si>
     <t xml:space="preserve">2.60413193702698</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">2.61407113075256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61075830459595</t>
+    <t xml:space="preserve">2.61075806617737</t>
   </si>
   <si>
     <t xml:space="preserve">2.61572790145874</t>
@@ -4316,16 +4316,16 @@
     <t xml:space="preserve">2.68861699104309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84930467605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86587047576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95366859436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99839615821838</t>
+    <t xml:space="preserve">2.84930443763733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86587023735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95366883277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9983959197998</t>
   </si>
   <si>
     <t xml:space="preserve">2.99342632293701</t>
@@ -4355,25 +4355,25 @@
     <t xml:space="preserve">3.06631541252136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04478025436401</t>
+    <t xml:space="preserve">3.04478001594543</t>
   </si>
   <si>
     <t xml:space="preserve">3.10441660881042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08619427680969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94869899749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91722416877747</t>
+    <t xml:space="preserve">3.08619475364685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94869875907898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91722393035889</t>
   </si>
   <si>
     <t xml:space="preserve">2.86255717277527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89900159835815</t>
+    <t xml:space="preserve">2.89900183677673</t>
   </si>
   <si>
     <t xml:space="preserve">2.99176979064941</t>
@@ -4394,7 +4394,7 @@
     <t xml:space="preserve">3.09944701194763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13754820823669</t>
+    <t xml:space="preserve">3.13754844665527</t>
   </si>
   <si>
     <t xml:space="preserve">3.19055843353271</t>
@@ -4403,10 +4403,10 @@
     <t xml:space="preserve">3.16736626625061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21375036239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2518515586853</t>
+    <t xml:space="preserve">3.21375060081482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25185179710388</t>
   </si>
   <si>
     <t xml:space="preserve">3.22865962982178</t>
@@ -4415,13 +4415,13 @@
     <t xml:space="preserve">3.22534656524658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26013469696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23031616210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20215463638306</t>
+    <t xml:space="preserve">3.26013445854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23031640052795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20215439796448</t>
   </si>
   <si>
     <t xml:space="preserve">3.20546746253967</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">3.18724536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23528599739075</t>
+    <t xml:space="preserve">3.23528575897217</t>
   </si>
   <si>
     <t xml:space="preserve">3.2816698551178</t>
@@ -4439,37 +4439,37 @@
     <t xml:space="preserve">3.29657912254333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34627628326416</t>
+    <t xml:space="preserve">3.34627652168274</t>
   </si>
   <si>
     <t xml:space="preserve">3.32805395126343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34793281555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37443804740906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43904423713684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44235777854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29160952568054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29492235183716</t>
+    <t xml:space="preserve">3.34793257713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37443780899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43904447555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44235754013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29160928726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29492259025574</t>
   </si>
   <si>
     <t xml:space="preserve">3.31811451911926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25516510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35124611854553</t>
+    <t xml:space="preserve">3.25516486167908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35124588012695</t>
   </si>
   <si>
     <t xml:space="preserve">3.45395350456238</t>
@@ -4478,10 +4478,10 @@
     <t xml:space="preserve">3.4506402015686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49536752700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43573093414307</t>
+    <t xml:space="preserve">3.49536776542664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43573117256165</t>
   </si>
   <si>
     <t xml:space="preserve">3.38437747955322</t>
@@ -4496,13 +4496,13 @@
     <t xml:space="preserve">3.34958958625793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38106393814087</t>
+    <t xml:space="preserve">3.38106417655945</t>
   </si>
   <si>
     <t xml:space="preserve">3.387690782547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39266037940979</t>
+    <t xml:space="preserve">3.39266061782837</t>
   </si>
   <si>
     <t xml:space="preserve">3.41088271141052</t>
@@ -4529,28 +4529,28 @@
     <t xml:space="preserve">3.13092184066772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02324485778809</t>
+    <t xml:space="preserve">3.02324461936951</t>
   </si>
   <si>
     <t xml:space="preserve">3.07625508308411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17399287223816</t>
+    <t xml:space="preserve">3.17399263381958</t>
   </si>
   <si>
     <t xml:space="preserve">3.13423490524292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1060733795166</t>
+    <t xml:space="preserve">3.10607314109802</t>
   </si>
   <si>
     <t xml:space="preserve">3.01164865493774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06465888023376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1093864440918</t>
+    <t xml:space="preserve">3.06465911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10938620567322</t>
   </si>
   <si>
     <t xml:space="preserve">3.07459831237793</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">3.08453774452209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11269950866699</t>
+    <t xml:space="preserve">3.11269927024841</t>
   </si>
   <si>
     <t xml:space="preserve">3.14748764038086</t>
@@ -4583,10 +4583,10 @@
     <t xml:space="preserve">3.19387149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19718456268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17896246910095</t>
+    <t xml:space="preserve">3.19718480110168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17896270751953</t>
   </si>
   <si>
     <t xml:space="preserve">3.14583110809326</t>
@@ -4598,19 +4598,19 @@
     <t xml:space="preserve">3.11932587623596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04146695137024</t>
+    <t xml:space="preserve">3.04146671295166</t>
   </si>
   <si>
     <t xml:space="preserve">3.07294201850891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05140662193298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08785104751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05306315422058</t>
+    <t xml:space="preserve">3.0514063835144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08785080909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.053062915802</t>
   </si>
   <si>
     <t xml:space="preserve">3.04974985122681</t>
@@ -71216,7 +71216,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.650787037</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>108829</v>
@@ -71237,6 +71237,32 @@
         <v>1984</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6912268518</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>68771</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>6.21999979019165</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>6.21999979019165</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1977</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24674606323242</t>
+    <t xml:space="preserve">4.24674701690674</t>
   </si>
   <si>
     <t xml:space="preserve">ANIM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33184719085693</t>
+    <t xml:space="preserve">4.33184623718262</t>
   </si>
   <si>
     <t xml:space="preserve">4.13419580459595</t>
@@ -53,46 +53,46 @@
     <t xml:space="preserve">3.96948671340942</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95301580429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94203472137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07380294799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93105530738831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8267388343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76085543632507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67850089073181</t>
+    <t xml:space="preserve">3.95301628112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94203495979309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07380199432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93105483055115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82673859596252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76085567474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67850065231323</t>
   </si>
   <si>
     <t xml:space="preserve">3.73889398574829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40398621559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53300738334656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76909065246582</t>
+    <t xml:space="preserve">3.40398645401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53300786018372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76909017562866</t>
   </si>
   <si>
     <t xml:space="preserve">3.79379725456238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79928731918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88438725471497</t>
+    <t xml:space="preserve">3.79928684234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88438749313354</t>
   </si>
   <si>
     <t xml:space="preserve">3.67575550079346</t>
@@ -101,43 +101,43 @@
     <t xml:space="preserve">3.70595240592957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64006853103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5796754360199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35731840133667</t>
+    <t xml:space="preserve">3.6400682926178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57967567443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35731816291809</t>
   </si>
   <si>
     <t xml:space="preserve">3.45065307617188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37653470039368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06633162498474</t>
+    <t xml:space="preserve">3.3765344619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06633257865906</t>
   </si>
   <si>
     <t xml:space="preserve">2.95652627944946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19535446166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98397827148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24202251434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20084452629089</t>
+    <t xml:space="preserve">3.1953547000885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98397755622864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24202179908752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20084404945374</t>
   </si>
   <si>
     <t xml:space="preserve">3.48634028434753</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38202476501465</t>
+    <t xml:space="preserve">3.38202381134033</t>
   </si>
   <si>
     <t xml:space="preserve">3.31065082550049</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">3.38751530647278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26672840118408</t>
+    <t xml:space="preserve">3.2667281627655</t>
   </si>
   <si>
     <t xml:space="preserve">3.1129994392395</t>
@@ -158,25 +158,25 @@
     <t xml:space="preserve">3.07182240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06084179878235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15692162513733</t>
+    <t xml:space="preserve">3.06084156036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15692186355591</t>
   </si>
   <si>
     <t xml:space="preserve">3.302414894104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43967318534851</t>
+    <t xml:space="preserve">3.43967270851135</t>
   </si>
   <si>
     <t xml:space="preserve">3.3518283367157</t>
   </si>
   <si>
-    <t xml:space="preserve">3.283198595047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22280597686768</t>
+    <t xml:space="preserve">3.28319907188416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22280621528625</t>
   </si>
   <si>
     <t xml:space="preserve">3.25300216674805</t>
@@ -185,118 +185,118 @@
     <t xml:space="preserve">3.57693004608154</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47261428833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46437954902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.590656042099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56320548057556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6126172542572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51653671264648</t>
+    <t xml:space="preserve">3.47261500358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46437907218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59065556526184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5632050037384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61261677742004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51653742790222</t>
   </si>
   <si>
     <t xml:space="preserve">3.4341824054718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37104368209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45888876914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53026294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32986640930176</t>
+    <t xml:space="preserve">3.37104344367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45888924598694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5302631855011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32986617088318</t>
   </si>
   <si>
     <t xml:space="preserve">3.27221846580505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09103846549988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23653173446655</t>
+    <t xml:space="preserve">3.09103894233704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23653149604797</t>
   </si>
   <si>
     <t xml:space="preserve">3.34084725379944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28594422340393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31888580322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23927736282349</t>
+    <t xml:space="preserve">3.28594470024109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31888628005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23927617073059</t>
   </si>
   <si>
     <t xml:space="preserve">3.42594695091248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41771173477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40947651863098</t>
+    <t xml:space="preserve">3.41771125793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4094762802124</t>
   </si>
   <si>
     <t xml:space="preserve">3.41496586799622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44241786003113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46163368225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4479079246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49732065200806</t>
+    <t xml:space="preserve">3.44241738319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46163439750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44790863990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49732041358948</t>
   </si>
   <si>
     <t xml:space="preserve">3.39300560951233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37378978729248</t>
+    <t xml:space="preserve">3.37378907203674</t>
   </si>
   <si>
     <t xml:space="preserve">3.26123809814453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2694730758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15417766571045</t>
+    <t xml:space="preserve">3.26947402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15417742729187</t>
   </si>
   <si>
     <t xml:space="preserve">3.16241264343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01966500282288</t>
+    <t xml:space="preserve">3.0196647644043</t>
   </si>
   <si>
     <t xml:space="preserve">2.94829106330872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82201409339905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93182039260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06907749176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00044822692871</t>
+    <t xml:space="preserve">2.82201433181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93182063102722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06907773017883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00044941902161</t>
   </si>
   <si>
     <t xml:space="preserve">2.91809439659119</t>
@@ -305,79 +305,79 @@
     <t xml:space="preserve">2.87417149543762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85221076011658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89064264297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97133874893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06356287002563</t>
+    <t xml:space="preserve">2.85221028327942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89064288139343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97133898735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06356310844421</t>
   </si>
   <si>
     <t xml:space="preserve">3.23648285865784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2422468662262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29988622665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17884278297424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15866851806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04050731658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.979984998703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96269273757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02321481704712</t>
+    <t xml:space="preserve">3.24224638938904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29988670349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17884254455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15866875648499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0405068397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97998476028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96269297599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02321434020996</t>
   </si>
   <si>
     <t xml:space="preserve">3.00015902519226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95692849159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81859278678894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79668974876404</t>
+    <t xml:space="preserve">2.95692873001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81859302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79668998718262</t>
   </si>
   <si>
     <t xml:space="preserve">2.66988182067871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61454725265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54768514633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70331287384033</t>
+    <t xml:space="preserve">2.61454749107361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54768490791321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70331239700317</t>
   </si>
   <si>
     <t xml:space="preserve">2.75288367271423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90505337715149</t>
+    <t xml:space="preserve">2.90505290031433</t>
   </si>
   <si>
     <t xml:space="preserve">2.92234468460083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96845698356628</t>
+    <t xml:space="preserve">2.96845674514771</t>
   </si>
   <si>
     <t xml:space="preserve">2.53615689277649</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">2.49004554748535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41972422599792</t>
+    <t xml:space="preserve">2.4197244644165</t>
   </si>
   <si>
     <t xml:space="preserve">2.42664122581482</t>
@@ -398,61 +398,61 @@
     <t xml:space="preserve">2.49235081672668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3690013885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28830552101135</t>
+    <t xml:space="preserve">2.36900162696838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28830575942993</t>
   </si>
   <si>
     <t xml:space="preserve">2.29752779006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30559730529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35747289657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4324049949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61108899116516</t>
+    <t xml:space="preserve">2.30559778213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35747313499451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43240523338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61108875274658</t>
   </si>
   <si>
     <t xml:space="preserve">2.59379720687866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68025732040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59725570678711</t>
+    <t xml:space="preserve">2.68025708198547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59725522994995</t>
   </si>
   <si>
     <t xml:space="preserve">2.60647797584534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56958818435669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62838077545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62261700630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59494972229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61685347557068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54653263092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63414549827576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58226919174194</t>
+    <t xml:space="preserve">2.56958794593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62838125228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62261724472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5949501991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61685371398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54653239250183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63414525985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58226895332336</t>
   </si>
   <si>
     <t xml:space="preserve">2.40358519554138</t>
@@ -467,82 +467,82 @@
     <t xml:space="preserve">2.55114364624023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58572793006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6514368057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65489554405212</t>
+    <t xml:space="preserve">2.58572816848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65143728256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65489506721497</t>
   </si>
   <si>
     <t xml:space="preserve">2.604172706604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54307413101196</t>
+    <t xml:space="preserve">2.54307436943054</t>
   </si>
   <si>
     <t xml:space="preserve">2.41857171058655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37015414237976</t>
+    <t xml:space="preserve">2.37015438079834</t>
   </si>
   <si>
     <t xml:space="preserve">2.39321064949036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51310157775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50964260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46122527122498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44854426383972</t>
+    <t xml:space="preserve">2.51310133934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50964283943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4612250328064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4485445022583</t>
   </si>
   <si>
     <t xml:space="preserve">2.50733733177185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50157332420349</t>
+    <t xml:space="preserve">2.50157356262207</t>
   </si>
   <si>
     <t xml:space="preserve">2.49696207046509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51540660858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53039336204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57304692268372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66181206703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62722849845886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73789691925049</t>
+    <t xml:space="preserve">2.5154070854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53039360046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57304716110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6618127822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62722826004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73789715766907</t>
   </si>
   <si>
     <t xml:space="preserve">2.83012080192566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79092574119568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67449355125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65604829788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64797854423523</t>
+    <t xml:space="preserve">2.7909255027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67449331283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6560480594635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64797902107239</t>
   </si>
   <si>
     <t xml:space="preserve">2.65720081329346</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">2.64567351341248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52001786231995</t>
+    <t xml:space="preserve">2.52001810073853</t>
   </si>
   <si>
     <t xml:space="preserve">2.51886510848999</t>
@@ -566,16 +566,16 @@
     <t xml:space="preserve">2.52462887763977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54192161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47275328636169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46929526329041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39436268806458</t>
+    <t xml:space="preserve">2.54192137718201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47275352478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46929502487183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39436340332031</t>
   </si>
   <si>
     <t xml:space="preserve">2.32173657417297</t>
@@ -584,322 +584,322 @@
     <t xml:space="preserve">2.32519507408142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24795746803284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26524949073792</t>
+    <t xml:space="preserve">2.24795770645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26524925231934</t>
   </si>
   <si>
     <t xml:space="preserve">2.32634782791138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38629341125488</t>
+    <t xml:space="preserve">2.38629293441772</t>
   </si>
   <si>
     <t xml:space="preserve">2.4439332485199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44623875617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5707414150238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57996320724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56267189979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55806040763855</t>
+    <t xml:space="preserve">2.44623851776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57074093818665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57996344566345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56267142295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55806064605713</t>
   </si>
   <si>
     <t xml:space="preserve">2.5038788318634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50503134727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38168239593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60993599891663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59956073760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55344891548157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70907711982727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67910432815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58111572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80130100250244</t>
+    <t xml:space="preserve">2.50503158569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38168215751648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60993623733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59956097602844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55344867706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70907735824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67910408973694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58111596107483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80130124092102</t>
   </si>
   <si>
     <t xml:space="preserve">2.81282925605774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72291088104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78285622596741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82551026344299</t>
+    <t xml:space="preserve">2.7229106426239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78285646438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82551002502441</t>
   </si>
   <si>
     <t xml:space="preserve">2.92522668838501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96557450294495</t>
+    <t xml:space="preserve">2.96557402610779</t>
   </si>
   <si>
     <t xml:space="preserve">2.91081690788269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00592231750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03474259376526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99727654457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98574805259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94828248023987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93963670730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97422170639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99151253700256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.014568567276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03186082839966</t>
+    <t xml:space="preserve">3.00592279434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03474283218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99727630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98574876785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94828319549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93963694572449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97422099113464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9915132522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01456880569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03186058998108</t>
   </si>
   <si>
     <t xml:space="preserve">3.16155099868774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13849520683289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11255645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12984871864319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20478081703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16443276405334</t>
+    <t xml:space="preserve">3.13849496841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11255669593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12984824180603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2047803401947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16443228721619</t>
   </si>
   <si>
     <t xml:space="preserve">3.19613480567932</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1990168094635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12408447265625</t>
+    <t xml:space="preserve">3.19901704788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12408494949341</t>
   </si>
   <si>
     <t xml:space="preserve">3.14137697219849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08373713493347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30276918411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26242136955261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18748879432678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28547596931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22783660888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17596054077148</t>
+    <t xml:space="preserve">3.08373665809631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30276870727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26242065429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18748927116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28547620773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22783637046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17595982551575</t>
   </si>
   <si>
     <t xml:space="preserve">3.24801015853882</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2681839466095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23936486244202</t>
+    <t xml:space="preserve">3.26818418502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23936462402344</t>
   </si>
   <si>
     <t xml:space="preserve">3.09238266944885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10102844238281</t>
+    <t xml:space="preserve">3.10102891921997</t>
   </si>
   <si>
     <t xml:space="preserve">3.05491662025452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08085417747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11832070350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15002250671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01168704032898</t>
+    <t xml:space="preserve">3.08085441589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11832046508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15002274513245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01168727874756</t>
   </si>
   <si>
     <t xml:space="preserve">2.92810845375061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95404720306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78516149520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91369891166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98863124847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00304055213928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02609658241272</t>
+    <t xml:space="preserve">2.95404672622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7851619720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91369843482971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98863101005554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00304007530212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02609634399414</t>
   </si>
   <si>
     <t xml:space="preserve">3.07797312736511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05779910087585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18172407150269</t>
+    <t xml:space="preserve">3.05779886245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18172430992126</t>
   </si>
   <si>
     <t xml:space="preserve">3.17019701004028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2336003780365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24512839317322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25089263916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27106714248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27394914627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28259444236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25665616989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1846067905426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29412198066711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10391044616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34023499488831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44398665428162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43245816230774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46416044235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45839667320251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49298048019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44686818122864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50450897216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6024968624115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51603627204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46992516517639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44110441207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42381286621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41228461265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39499282836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37193584442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4893524646759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49236297607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59472560882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72117328643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7151517868042</t>
+    <t xml:space="preserve">3.23360085487366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24512910842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25089287757874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27106690406799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27394866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28259491920471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25665640830994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18460607528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29412269592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10391116142273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34023451805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44398641586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4324586391449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46415948867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45839595794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49298024177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44686794281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50450825691223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60249614715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51603603363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46992444992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44110465049744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4238121509552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41228413581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39499306678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37193608283997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48935270309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49236249923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59472513198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72117304801941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71515202522278</t>
   </si>
   <si>
     <t xml:space="preserve">3.58870363235474</t>
@@ -908,85 +908,85 @@
     <t xml:space="preserve">3.4682776927948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41107559204102</t>
+    <t xml:space="preserve">3.41107511520386</t>
   </si>
   <si>
     <t xml:space="preserve">3.49838447570801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5405330657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50440573692322</t>
+    <t xml:space="preserve">3.54053282737732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50440549850464</t>
   </si>
   <si>
     <t xml:space="preserve">3.51644825935364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54956555366516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70912981033325</t>
+    <t xml:space="preserve">3.54956531524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70913028717041</t>
   </si>
   <si>
     <t xml:space="preserve">3.72418403625488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64891695976257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75127911567688</t>
+    <t xml:space="preserve">3.64891743659973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75127983093262</t>
   </si>
   <si>
     <t xml:space="preserve">3.72719407081604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76332235336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7392373085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74525737762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71214056015015</t>
+    <t xml:space="preserve">3.76332187652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73923659324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74525785446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71214151382446</t>
   </si>
   <si>
     <t xml:space="preserve">3.70310926437378</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75730109214783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7753643989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77837467193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84160041809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85966324806213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82654619216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09750509262085</t>
+    <t xml:space="preserve">3.75730037689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77536392211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77837610244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8415994644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85966300964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82654595375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09750556945801</t>
   </si>
   <si>
     <t xml:space="preserve">4.14266538619995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19685697555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17277193069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19083595275879</t>
+    <t xml:space="preserve">4.19685649871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17277240753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19083547592163</t>
   </si>
   <si>
     <t xml:space="preserve">4.22094202041626</t>
@@ -998,10 +998,10 @@
     <t xml:space="preserve">4.2450270652771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2691125869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26309156417847</t>
+    <t xml:space="preserve">4.26911306381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26309204101562</t>
   </si>
   <si>
     <t xml:space="preserve">4.21492099761963</t>
@@ -1010,31 +1010,31 @@
     <t xml:space="preserve">4.15470790863037</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14567613601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13664388656616</t>
+    <t xml:space="preserve">4.14567565917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13664436340332</t>
   </si>
   <si>
     <t xml:space="preserve">4.22395324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22696352005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33534669876099</t>
+    <t xml:space="preserve">4.22696304321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33534717559814</t>
   </si>
   <si>
     <t xml:space="preserve">4.25104904174805</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28717660903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11857938766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25405979156494</t>
+    <t xml:space="preserve">4.28717613220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11857986450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25405883789062</t>
   </si>
   <si>
     <t xml:space="preserve">4.09449434280396</t>
@@ -1046,28 +1046,28 @@
     <t xml:space="preserve">4.04030275344849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05234575271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95901536941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86267304420471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86568474769592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94396162033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94697237014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95600414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98008990287781</t>
+    <t xml:space="preserve">4.05234479904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95901417732239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86267352104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86568427085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94396138191223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94697284698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95600390434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98008966445923</t>
   </si>
   <si>
     <t xml:space="preserve">3.97406840324402</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">4.06438827514648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98912119865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96202564239502</t>
+    <t xml:space="preserve">3.98912143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96202516555786</t>
   </si>
   <si>
     <t xml:space="preserve">4.01320648193359</t>
@@ -1091,70 +1091,70 @@
     <t xml:space="preserve">4.0342812538147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00417423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00116348266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90783381462097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88976955413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95299386978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0101957321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11255836486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15771818161011</t>
+    <t xml:space="preserve">4.00417470932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00116300582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90783357620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88976979255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95299339294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01019620895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11255884170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15771865844727</t>
   </si>
   <si>
     <t xml:space="preserve">4.06739854812622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9861114025116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93191862106323</t>
+    <t xml:space="preserve">3.98611044883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93191885948181</t>
   </si>
   <si>
     <t xml:space="preserve">3.90181183815002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87471628189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85364127159119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82353496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579057693481</t>
+    <t xml:space="preserve">3.87471699714661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85364174842834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82353472709656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579105377197</t>
   </si>
   <si>
     <t xml:space="preserve">3.84762072563171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83256769180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88073778152466</t>
+    <t xml:space="preserve">3.83256793022156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88073825836182</t>
   </si>
   <si>
     <t xml:space="preserve">3.88374805450439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92589735984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92890858650208</t>
+    <t xml:space="preserve">3.9258975982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92890906333923</t>
   </si>
   <si>
     <t xml:space="preserve">3.88675928115845</t>
@@ -1163,139 +1163,139 @@
     <t xml:space="preserve">3.91385531425476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91084504127502</t>
+    <t xml:space="preserve">3.91084480285645</t>
   </si>
   <si>
     <t xml:space="preserve">3.8446102142334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82052516937256</t>
+    <t xml:space="preserve">3.82052493095398</t>
   </si>
   <si>
     <t xml:space="preserve">3.69106650352478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70611953735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55558729171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47429871559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33580875396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40204310417175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52246904373169</t>
+    <t xml:space="preserve">3.70611929893494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55558657646179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47429895401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33580851554871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40204334259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52246928215027</t>
   </si>
   <si>
     <t xml:space="preserve">3.54354381561279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53150153160095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.573650598526</t>
+    <t xml:space="preserve">3.53150129318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57365083694458</t>
   </si>
   <si>
     <t xml:space="preserve">3.60074615478516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5766613483429</t>
+    <t xml:space="preserve">3.57666182518005</t>
   </si>
   <si>
     <t xml:space="preserve">3.53752303123474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55257630348206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50139427185059</t>
+    <t xml:space="preserve">3.5525758266449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50139451026917</t>
   </si>
   <si>
     <t xml:space="preserve">3.45021438598633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51042652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48634171485901</t>
+    <t xml:space="preserve">3.51042628288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48634195327759</t>
   </si>
   <si>
     <t xml:space="preserve">3.43817138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4080650806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53451204299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60977864265442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35387253761292</t>
+    <t xml:space="preserve">3.40806484222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53451180458069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60977840423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35387277603149</t>
   </si>
   <si>
     <t xml:space="preserve">3.42612838745117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44419264793396</t>
+    <t xml:space="preserve">3.44419240951538</t>
   </si>
   <si>
     <t xml:space="preserve">3.32376551628113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39000034332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61278986930847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73020482063293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6669807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64590716362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63386368751526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81450319290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86869549751282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93492960929871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04331350326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99213171005249</t>
+    <t xml:space="preserve">3.39000058174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61278939247131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73020505905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66698026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64590692520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63386416435242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81450271606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86869525909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93492984771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04331302642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99213123321533</t>
   </si>
   <si>
     <t xml:space="preserve">3.98310017585754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06137752532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12460136413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.160728931427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07040977478027</t>
+    <t xml:space="preserve">4.06137704849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1246018409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16072940826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07040929794312</t>
   </si>
   <si>
     <t xml:space="preserve">4.08245182037354</t>
@@ -1310,31 +1310,31 @@
     <t xml:space="preserve">3.91987681388855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78439593315125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77235460281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79945063591003</t>
+    <t xml:space="preserve">3.78439688682556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77235436439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79945015907288</t>
   </si>
   <si>
     <t xml:space="preserve">3.73622584342957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75429081916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76633310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63988518714905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56160807609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6699914932251</t>
+    <t xml:space="preserve">3.75429010391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76633262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63988542556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56160759925842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66999173164368</t>
   </si>
   <si>
     <t xml:space="preserve">3.96503639221191</t>
@@ -1343,52 +1343,52 @@
     <t xml:space="preserve">3.79342865943909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74224758148193</t>
+    <t xml:space="preserve">3.74224781990051</t>
   </si>
   <si>
     <t xml:space="preserve">3.79164934158325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77612257003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78854322433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70469880104065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58358955383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55914306640625</t>
+    <t xml:space="preserve">3.77612209320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78854370117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70469856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58358979225159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55914258956909</t>
   </si>
   <si>
     <t xml:space="preserve">3.55258846282959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51326084136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61158013343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58536124229431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7688901424408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89998149871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89342713356018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85082197189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81149458885193</t>
+    <t xml:space="preserve">3.51326155662537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61157989501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58536100387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76888990402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89998126029968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89342737197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85082244873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81149482727051</t>
   </si>
   <si>
     <t xml:space="preserve">3.63779830932617</t>
@@ -1403,13 +1403,13 @@
     <t xml:space="preserve">3.86065411567688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8409903049469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81804847717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96552801132202</t>
+    <t xml:space="preserve">3.84099054336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81804871559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96552777290344</t>
   </si>
   <si>
     <t xml:space="preserve">3.98846912384033</t>
@@ -1418,37 +1418,37 @@
     <t xml:space="preserve">3.93275499343872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86720871925354</t>
+    <t xml:space="preserve">3.86720895767212</t>
   </si>
   <si>
     <t xml:space="preserve">3.84426712989807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91309070587158</t>
+    <t xml:space="preserve">3.91309094429016</t>
   </si>
   <si>
     <t xml:space="preserve">3.8213267326355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03107404708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04418325424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02451848983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98191404342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90653657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99830079078674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77544403076172</t>
+    <t xml:space="preserve">4.03107357025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04418230056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0245189666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98191380500793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90653610229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99830055236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77544474601746</t>
   </si>
   <si>
     <t xml:space="preserve">3.76561236381531</t>
@@ -1457,94 +1457,94 @@
     <t xml:space="preserve">3.71973085403442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71645307540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56897473335266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50670599937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46737909317017</t>
+    <t xml:space="preserve">3.71645283699036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56897497177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50670647621155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46737837791443</t>
   </si>
   <si>
     <t xml:space="preserve">3.27467346191406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93645668029785</t>
+    <t xml:space="preserve">2.93645691871643</t>
   </si>
   <si>
     <t xml:space="preserve">3.03477597236633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19077491760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42149686813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41494250297546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33628702163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31662321090698</t>
+    <t xml:space="preserve">3.19077467918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42149639129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41494226455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33628678321838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3166229724884</t>
   </si>
   <si>
     <t xml:space="preserve">3.35595059394836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.211749792099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30023646354675</t>
+    <t xml:space="preserve">3.21175003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30023670196533</t>
   </si>
   <si>
     <t xml:space="preserve">3.32645463943481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39855575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33956360816956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29040479660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27729535102844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28057312965393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1829092502594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12260746955872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07148146629333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01511216163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89975070953369</t>
+    <t xml:space="preserve">3.39855527877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33956384658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29040455818176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27729558944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28057289123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18290901184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12260723114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07148098945618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01511168479919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89975094795227</t>
   </si>
   <si>
     <t xml:space="preserve">3.01904463768005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01380109786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04919576644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97971725463867</t>
+    <t xml:space="preserve">3.01380085945129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0491955280304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97971701622009</t>
   </si>
   <si>
     <t xml:space="preserve">3.02691006660461</t>
@@ -1553,58 +1553,58 @@
     <t xml:space="preserve">3.13440561294556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10425448417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04264140129089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00200271606445</t>
+    <t xml:space="preserve">3.10425424575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04264163970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00200247764587</t>
   </si>
   <si>
     <t xml:space="preserve">3.00462460517883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98233890533447</t>
+    <t xml:space="preserve">2.98233914375305</t>
   </si>
   <si>
     <t xml:space="preserve">2.98627185821533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92072558403015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92728066444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00069189071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01248979568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03739714622498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95612049102783</t>
+    <t xml:space="preserve">2.92072582244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92728042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00069165229797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01249027252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03739762306213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95612025260925</t>
   </si>
   <si>
     <t xml:space="preserve">2.92465853691101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84469246864319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97709536552429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00724625587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89057469367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77259230613708</t>
+    <t xml:space="preserve">2.84469270706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97709512710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00724601745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89057445526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77259206771851</t>
   </si>
   <si>
     <t xml:space="preserve">2.79487752914429</t>
@@ -1613,22 +1613,22 @@
     <t xml:space="preserve">2.73064255714417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71228957176208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70049118995667</t>
+    <t xml:space="preserve">2.71228981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70049142837524</t>
   </si>
   <si>
     <t xml:space="preserve">2.77914643287659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76996994018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73719716072083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7214663028717</t>
+    <t xml:space="preserve">2.76997041702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7371973991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72146606445312</t>
   </si>
   <si>
     <t xml:space="preserve">2.69000434875488</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">2.72015523910522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87615466117859</t>
+    <t xml:space="preserve">2.87615442276001</t>
   </si>
   <si>
     <t xml:space="preserve">2.85124707221985</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">2.86697840690613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93907904624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91154932975769</t>
+    <t xml:space="preserve">2.93907880783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91154956817627</t>
   </si>
   <si>
     <t xml:space="preserve">2.91679286956787</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">2.92596960067749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94170045852661</t>
+    <t xml:space="preserve">2.94170069694519</t>
   </si>
   <si>
     <t xml:space="preserve">2.99806976318359</t>
@@ -1679,13 +1679,13 @@
     <t xml:space="preserve">3.04133033752441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99675917625427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99413728713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96267485618591</t>
+    <t xml:space="preserve">2.99675893783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99413704872131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96267533302307</t>
   </si>
   <si>
     <t xml:space="preserve">2.96005344390869</t>
@@ -1694,10 +1694,10 @@
     <t xml:space="preserve">2.91286015510559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77521371841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70704627037048</t>
+    <t xml:space="preserve">2.77521419525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7070460319519</t>
   </si>
   <si>
     <t xml:space="preserve">2.68869352340698</t>
@@ -1706,37 +1706,37 @@
     <t xml:space="preserve">2.705735206604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74244117736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64674401283264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64150047302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59692907333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38193869590759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46714806556702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44879531860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49074459075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47108054161072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48681163787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41995477676392</t>
+    <t xml:space="preserve">2.74244070053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64674377441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64150023460388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59692883491516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38193845748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46714782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44879508018494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4907443523407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4710807800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48681211471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4199550151825</t>
   </si>
   <si>
     <t xml:space="preserve">2.31639242172241</t>
@@ -1760,67 +1760,67 @@
     <t xml:space="preserve">2.39242577552795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42519855499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45928287506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54973602294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47239208221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44617342948914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4579713344574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47501373291016</t>
+    <t xml:space="preserve">2.42519879341125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45928239822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54973578453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4723916053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44617319107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45797157287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.475013256073</t>
   </si>
   <si>
     <t xml:space="preserve">2.54842519760132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43044233322144</t>
+    <t xml:space="preserve">2.43044257164001</t>
   </si>
   <si>
     <t xml:space="preserve">2.40815687179565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33998918533325</t>
+    <t xml:space="preserve">2.33998894691467</t>
   </si>
   <si>
     <t xml:space="preserve">2.28886342048645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27968668937683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25740098953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17612433433533</t>
+    <t xml:space="preserve">2.27968692779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25740122795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17612409591675</t>
   </si>
   <si>
     <t xml:space="preserve">2.18661141395569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13155317306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29410719871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35178709030151</t>
+    <t xml:space="preserve">2.13155293464661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29410696029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35178732872009</t>
   </si>
   <si>
     <t xml:space="preserve">2.39766955375671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44748449325562</t>
+    <t xml:space="preserve">2.44748425483704</t>
   </si>
   <si>
     <t xml:space="preserve">2.42388796806335</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">2.40029096603394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21938443183899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19447708129883</t>
+    <t xml:space="preserve">2.21938467025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19447684288025</t>
   </si>
   <si>
     <t xml:space="preserve">2.25477957725525</t>
@@ -1844,19 +1844,19 @@
     <t xml:space="preserve">2.31901454925537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32687997817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26264452934265</t>
+    <t xml:space="preserve">2.32687973976135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26264476776123</t>
   </si>
   <si>
     <t xml:space="preserve">2.17743539810181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12893104553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14597320556641</t>
+    <t xml:space="preserve">2.12893128395081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14597296714783</t>
   </si>
   <si>
     <t xml:space="preserve">2.12237668037415</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">2.12368750572205</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10271263122559</t>
+    <t xml:space="preserve">2.10271310806274</t>
   </si>
   <si>
     <t xml:space="preserve">2.11713290214539</t>
@@ -1880,43 +1880,43 @@
     <t xml:space="preserve">2.23904824256897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20758628845215</t>
+    <t xml:space="preserve">2.20758605003357</t>
   </si>
   <si>
     <t xml:space="preserve">2.36489653587341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34785485267639</t>
+    <t xml:space="preserve">2.34785461425781</t>
   </si>
   <si>
     <t xml:space="preserve">2.37407279014587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25084662437439</t>
+    <t xml:space="preserve">2.25084638595581</t>
   </si>
   <si>
     <t xml:space="preserve">2.39504766464233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35572028160095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41340041160583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43306398391724</t>
+    <t xml:space="preserve">2.35572004318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41340017318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43306422233582</t>
   </si>
   <si>
     <t xml:space="preserve">2.44486260414124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44224095344543</t>
+    <t xml:space="preserve">2.44224071502686</t>
   </si>
   <si>
     <t xml:space="preserve">2.43175339698792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38456034660339</t>
+    <t xml:space="preserve">2.38456010818481</t>
   </si>
   <si>
     <t xml:space="preserve">2.35309815406799</t>
@@ -1928,10 +1928,10 @@
     <t xml:space="preserve">2.35440921783447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37145113945007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28755211830139</t>
+    <t xml:space="preserve">2.37145090103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28755235671997</t>
   </si>
   <si>
     <t xml:space="preserve">2.26788854598999</t>
@@ -1949,10 +1949,10 @@
     <t xml:space="preserve">2.40553498268127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37014007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33605623245239</t>
+    <t xml:space="preserve">2.37014031410217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33605599403381</t>
   </si>
   <si>
     <t xml:space="preserve">2.39898037910461</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">2.54318141937256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52613973617554</t>
+    <t xml:space="preserve">2.52613925933838</t>
   </si>
   <si>
     <t xml:space="preserve">2.50385355949402</t>
@@ -1976,13 +1976,13 @@
     <t xml:space="preserve">2.49336624145508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42782044410706</t>
+    <t xml:space="preserve">2.42782068252563</t>
   </si>
   <si>
     <t xml:space="preserve">2.39635848999023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38718175888062</t>
+    <t xml:space="preserve">2.38718199729919</t>
   </si>
   <si>
     <t xml:space="preserve">2.37276196479797</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">2.33867812156677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29935026168823</t>
+    <t xml:space="preserve">2.29935050010681</t>
   </si>
   <si>
     <t xml:space="preserve">2.38062763214111</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">2.45666074752808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40160250663757</t>
+    <t xml:space="preserve">2.40160226821899</t>
   </si>
   <si>
     <t xml:space="preserve">2.34130001068115</t>
@@ -2018,22 +2018,22 @@
     <t xml:space="preserve">2.34392166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38324928283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32556867599487</t>
+    <t xml:space="preserve">2.38324952125549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32556891441345</t>
   </si>
   <si>
     <t xml:space="preserve">2.30328321456909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30590510368347</t>
+    <t xml:space="preserve">2.30590534210205</t>
   </si>
   <si>
     <t xml:space="preserve">2.34523272514343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32425785064697</t>
+    <t xml:space="preserve">2.32425808906555</t>
   </si>
   <si>
     <t xml:space="preserve">2.30983781814575</t>
@@ -2045,88 +2045,88 @@
     <t xml:space="preserve">2.19054436683655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09091472625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08698177337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99783957004547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03978896141052</t>
+    <t xml:space="preserve">2.09091448783875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08698201179504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99783968925476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03978872299194</t>
   </si>
   <si>
     <t xml:space="preserve">1.9768648147583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99128484725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9781756401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98996257781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99967014789581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97470891475677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94420063495636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91923940181732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89843845367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86377012729645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82632839679718</t>
+    <t xml:space="preserve">1.99128472805023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97817528247833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98996269702911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99966990947723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97470915317535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94420051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91923952102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89843821525574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86377024650574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82632827758789</t>
   </si>
   <si>
     <t xml:space="preserve">1.87625086307526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87902414798737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83742237091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95113444328308</t>
+    <t xml:space="preserve">1.87902426719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83742213249207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9511342048645</t>
   </si>
   <si>
     <t xml:space="preserve">1.92755973339081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89982509613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92062616348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90953230857849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9067587852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88734447956085</t>
+    <t xml:space="preserve">1.89982521533966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92062604427338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90953242778778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90675890445709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88734459877014</t>
   </si>
   <si>
     <t xml:space="preserve">1.88873136043549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88179755210876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02879166603088</t>
+    <t xml:space="preserve">1.88179790973663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0287914276123</t>
   </si>
   <si>
     <t xml:space="preserve">1.98302924633026</t>
@@ -2135,19 +2135,19 @@
     <t xml:space="preserve">2.03156495094299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98857605457306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95945489406586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00660371780396</t>
+    <t xml:space="preserve">1.98857617378235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95945477485657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00660395622253</t>
   </si>
   <si>
     <t xml:space="preserve">2.00521683692932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07178020477295</t>
+    <t xml:space="preserve">2.07177996635437</t>
   </si>
   <si>
     <t xml:space="preserve">2.09396815299988</t>
@@ -2162,25 +2162,25 @@
     <t xml:space="preserve">2.25344228744507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25898933410645</t>
+    <t xml:space="preserve">2.25898909568787</t>
   </si>
   <si>
     <t xml:space="preserve">2.26453614234924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21461391448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21184039115906</t>
+    <t xml:space="preserve">2.21461367607117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21184015274048</t>
   </si>
   <si>
     <t xml:space="preserve">2.24928212165833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31445860862732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30059123039246</t>
+    <t xml:space="preserve">2.3144588470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30059146881104</t>
   </si>
   <si>
     <t xml:space="preserve">2.30891156196594</t>
@@ -2189,13 +2189,13 @@
     <t xml:space="preserve">2.31307172775269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27424311637878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22154760360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24789524078369</t>
+    <t xml:space="preserve">2.27424335479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2215473651886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24789547920227</t>
   </si>
   <si>
     <t xml:space="preserve">2.24650859832764</t>
@@ -2207,28 +2207,28 @@
     <t xml:space="preserve">2.28811049461365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32277870178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37824845314026</t>
+    <t xml:space="preserve">2.32277894020081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37824821472168</t>
   </si>
   <si>
     <t xml:space="preserve">2.30613827705383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23125433921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18687915802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1716251373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17439818382263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22432065010071</t>
+    <t xml:space="preserve">2.23125457763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18687891960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17162489891052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17439842224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22432112693787</t>
   </si>
   <si>
     <t xml:space="preserve">2.12170267105103</t>
@@ -2240,13 +2240,13 @@
     <t xml:space="preserve">2.12863612174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09812831878662</t>
+    <t xml:space="preserve">2.09812808036804</t>
   </si>
   <si>
     <t xml:space="preserve">2.1272497177124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17717218399048</t>
+    <t xml:space="preserve">2.1771719455719</t>
   </si>
   <si>
     <t xml:space="preserve">2.19103932380676</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">2.23680138587952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2062931060791</t>
+    <t xml:space="preserve">2.20629334449768</t>
   </si>
   <si>
     <t xml:space="preserve">2.19935965538025</t>
@@ -2264,28 +2264,28 @@
     <t xml:space="preserve">2.18549227714539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25760293006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25621557235718</t>
+    <t xml:space="preserve">2.25760269165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25621581077576</t>
   </si>
   <si>
     <t xml:space="preserve">2.23957490921021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35606074333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38102197647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3671543598175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38379526138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43510484695435</t>
+    <t xml:space="preserve">2.35606050491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38102149963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36715459823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38379502296448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43510460853577</t>
   </si>
   <si>
     <t xml:space="preserve">2.51553511619568</t>
@@ -2294,10 +2294,10 @@
     <t xml:space="preserve">2.49889421463013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42955732345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42817068099976</t>
+    <t xml:space="preserve">2.42955756187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42817091941833</t>
   </si>
   <si>
     <t xml:space="preserve">2.44897174835205</t>
@@ -2306,16 +2306,16 @@
     <t xml:space="preserve">2.45867896080017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39766263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38795518875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37131452560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.382408618927</t>
+    <t xml:space="preserve">2.39766240119934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3879554271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37131476402283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38240885734558</t>
   </si>
   <si>
     <t xml:space="preserve">2.41707682609558</t>
@@ -2324,16 +2324,16 @@
     <t xml:space="preserve">2.42401051521301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37408804893494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32693934440613</t>
+    <t xml:space="preserve">2.37408828735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32693886756897</t>
   </si>
   <si>
     <t xml:space="preserve">2.2992045879364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31723165512085</t>
+    <t xml:space="preserve">2.31723213195801</t>
   </si>
   <si>
     <t xml:space="preserve">2.34496665000916</t>
@@ -2342,52 +2342,52 @@
     <t xml:space="preserve">2.34635353088379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4115297794342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46977281570435</t>
+    <t xml:space="preserve">2.41153001785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46977257728577</t>
   </si>
   <si>
     <t xml:space="preserve">2.48502683639526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5696177482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61538004875183</t>
+    <t xml:space="preserve">2.56961798667908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61537981033325</t>
   </si>
   <si>
     <t xml:space="preserve">2.6763961315155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73879933357239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70690417289734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74711966514587</t>
+    <t xml:space="preserve">2.73879885673523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70690441131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74711942672729</t>
   </si>
   <si>
     <t xml:space="preserve">2.72770524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75266647338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76237368583679</t>
+    <t xml:space="preserve">2.75266623497009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76237344741821</t>
   </si>
   <si>
     <t xml:space="preserve">2.7859480381012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77208089828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69581031799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70413088798523</t>
+    <t xml:space="preserve">2.77208042144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69581055641174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70413112640381</t>
   </si>
   <si>
     <t xml:space="preserve">2.7207715511322</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">2.78733468055725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82893657684326</t>
+    <t xml:space="preserve">2.82893681526184</t>
   </si>
   <si>
     <t xml:space="preserve">2.85528469085693</t>
@@ -2408,34 +2408,34 @@
     <t xml:space="preserve">2.9468092918396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01614594459534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02723979949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04804039001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0799355506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13679218292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1464991569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17562031745911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14511203765869</t>
+    <t xml:space="preserve">3.01614570617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02723956108093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04804086685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07993578910828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13679194450378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14649868011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17562007904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14511227607727</t>
   </si>
   <si>
     <t xml:space="preserve">3.23108959197998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24773073196411</t>
+    <t xml:space="preserve">3.24773049354553</t>
   </si>
   <si>
     <t xml:space="preserve">3.26298451423645</t>
@@ -2444,13 +2444,13 @@
     <t xml:space="preserve">3.26159763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2255425453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18532729148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18394064903259</t>
+    <t xml:space="preserve">3.22554230690002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18532705307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18394088745117</t>
   </si>
   <si>
     <t xml:space="preserve">3.2560510635376</t>
@@ -2459,88 +2459,88 @@
     <t xml:space="preserve">3.21028876304626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25327730178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22831606864929</t>
+    <t xml:space="preserve">3.25327706336975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22831630706787</t>
   </si>
   <si>
     <t xml:space="preserve">3.2019681930542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24218344688416</t>
+    <t xml:space="preserve">3.24218368530273</t>
   </si>
   <si>
     <t xml:space="preserve">3.26575803756714</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21306180953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19919466972351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20890164375305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22415566444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19087433815002</t>
+    <t xml:space="preserve">3.21306204795837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19919443130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20890140533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22415614128113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19087481498718</t>
   </si>
   <si>
     <t xml:space="preserve">3.20335483551025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06606841087341</t>
+    <t xml:space="preserve">3.06606817245483</t>
   </si>
   <si>
     <t xml:space="preserve">3.09241628646851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14788508415222</t>
+    <t xml:space="preserve">3.14788579940796</t>
   </si>
   <si>
     <t xml:space="preserve">3.2061288356781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17839384078979</t>
+    <t xml:space="preserve">3.17839360237122</t>
   </si>
   <si>
     <t xml:space="preserve">3.17145967483521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03694677352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15343260765076</t>
+    <t xml:space="preserve">3.03694701194763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15343236923218</t>
   </si>
   <si>
     <t xml:space="preserve">3.16868686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97038316726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03555965423584</t>
+    <t xml:space="preserve">2.970383644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03555989265442</t>
   </si>
   <si>
     <t xml:space="preserve">3.14095211029053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12985777854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14927244186401</t>
+    <t xml:space="preserve">3.12985801696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14927196502686</t>
   </si>
   <si>
     <t xml:space="preserve">3.17007327079773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12708449363708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10073661804199</t>
+    <t xml:space="preserve">3.12708425521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10073709487915</t>
   </si>
   <si>
     <t xml:space="preserve">3.07854890823364</t>
@@ -2549,13 +2549,13 @@
     <t xml:space="preserve">3.11044383049011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08964252471924</t>
+    <t xml:space="preserve">3.08964276313782</t>
   </si>
   <si>
     <t xml:space="preserve">3.28239870071411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34202814102173</t>
+    <t xml:space="preserve">3.34202861785889</t>
   </si>
   <si>
     <t xml:space="preserve">3.34896206855774</t>
@@ -2576,76 +2576,76 @@
     <t xml:space="preserve">2.58487153053284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55158996582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4947338104248</t>
+    <t xml:space="preserve">2.55159020423889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49473404884338</t>
   </si>
   <si>
     <t xml:space="preserve">2.29227089881897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07039332389832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95668113231659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99134969711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69042825698853</t>
+    <t xml:space="preserve">2.07039356231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95668137073517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99134945869446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69042861461639</t>
   </si>
   <si>
     <t xml:space="preserve">1.7847261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65576004981995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52818048000336</t>
+    <t xml:space="preserve">1.65575993061066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52818059921265</t>
   </si>
   <si>
     <t xml:space="preserve">1.41030824184418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48519158363342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49489891529083</t>
+    <t xml:space="preserve">1.485191822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49489903450012</t>
   </si>
   <si>
     <t xml:space="preserve">1.60583770275116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67933452129364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67656111717224</t>
+    <t xml:space="preserve">1.67933440208435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67656123638153</t>
   </si>
   <si>
     <t xml:space="preserve">1.72648358345032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68904161453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69736206531525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72371029853821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75421822071075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78888630867004</t>
+    <t xml:space="preserve">1.68904173374176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69736194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72371017932892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75421810150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78888642787933</t>
   </si>
   <si>
     <t xml:space="preserve">2.02185773849487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06207323074341</t>
+    <t xml:space="preserve">2.06207299232483</t>
   </si>
   <si>
     <t xml:space="preserve">2.05375266075134</t>
@@ -2657,40 +2657,40 @@
     <t xml:space="preserve">1.97609543800354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.966388463974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94142711162567</t>
+    <t xml:space="preserve">1.96638822555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94142699241638</t>
   </si>
   <si>
     <t xml:space="preserve">1.8596099615097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8679301738739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92339968681335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90121209621429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1480507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26730966567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23818802833557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22570776939392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13418340682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28117680549622</t>
+    <t xml:space="preserve">1.86793053150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92339944839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.901211977005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14805054664612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26730990409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23818826675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22570753097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13418316841125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28117728233337</t>
   </si>
   <si>
     <t xml:space="preserve">2.35744738578796</t>
@@ -2702,10 +2702,10 @@
     <t xml:space="preserve">2.3435800075531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30752515792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48411726951599</t>
+    <t xml:space="preserve">2.30752491950989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48411750793457</t>
   </si>
   <si>
     <t xml:space="preserve">2.51219487190247</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">2.49150609970093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49741744995117</t>
+    <t xml:space="preserve">2.49741721153259</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456218719482</t>
@@ -2726,28 +2726,28 @@
     <t xml:space="preserve">2.72647047042847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75750327110291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80774712562561</t>
+    <t xml:space="preserve">2.75750350952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80774736404419</t>
   </si>
   <si>
     <t xml:space="preserve">2.86537981033325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87572407722473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86833524703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97473406791687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20230960845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16979908943176</t>
+    <t xml:space="preserve">2.87572431564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86833548545837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97473430633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20230984687805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1697986125946</t>
   </si>
   <si>
     <t xml:space="preserve">3.14024376869202</t>
@@ -2756,22 +2756,22 @@
     <t xml:space="preserve">2.93483471870422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9363124370575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94222378730774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99837875366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00281190872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95847916603088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88606858253479</t>
+    <t xml:space="preserve">2.93631267547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94222354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99837851524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00281167030334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9584789276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88606834411621</t>
   </si>
   <si>
     <t xml:space="preserve">2.92744588851929</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">2.85946869850159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82843589782715</t>
+    <t xml:space="preserve">2.82843613624573</t>
   </si>
   <si>
     <t xml:space="preserve">2.86242437362671</t>
@@ -2798,7 +2798,7 @@
     <t xml:space="preserve">2.93779039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99542284011841</t>
+    <t xml:space="preserve">2.99542307853699</t>
   </si>
   <si>
     <t xml:space="preserve">3.03236699104309</t>
@@ -2813,55 +2813,55 @@
     <t xml:space="preserve">2.92005681991577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93040132522583</t>
+    <t xml:space="preserve">2.93040156364441</t>
   </si>
   <si>
     <t xml:space="preserve">2.97916769981384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98212289810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99394536018372</t>
+    <t xml:space="preserve">2.98212313652039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99394512176514</t>
   </si>
   <si>
     <t xml:space="preserve">2.98951196670532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95404577255249</t>
+    <t xml:space="preserve">2.95404553413391</t>
   </si>
   <si>
     <t xml:space="preserve">2.95552325248718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94665694236755</t>
+    <t xml:space="preserve">2.94665670394897</t>
   </si>
   <si>
     <t xml:space="preserve">3.03384470939636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09591054916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0175895690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99098944664001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93335700035095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91857957839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75602579116821</t>
+    <t xml:space="preserve">3.09591102600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758933067322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99098968505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93335676193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91857933998108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75602555274963</t>
   </si>
   <si>
     <t xml:space="preserve">2.81365847587585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85503578186035</t>
+    <t xml:space="preserve">2.85503554344177</t>
   </si>
   <si>
     <t xml:space="preserve">2.8535578250885</t>
@@ -2870,10 +2870,10 @@
     <t xml:space="preserve">2.894935131073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87720203399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9215350151062</t>
+    <t xml:space="preserve">2.87720227241516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92153477668762</t>
   </si>
   <si>
     <t xml:space="preserve">2.9629123210907</t>
@@ -2882,19 +2882,19 @@
     <t xml:space="preserve">2.91266846656799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87424659729004</t>
+    <t xml:space="preserve">2.87424635887146</t>
   </si>
   <si>
     <t xml:space="preserve">2.84616899490356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80479192733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76784753799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75307035446167</t>
+    <t xml:space="preserve">2.80479168891907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76784777641296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75307011604309</t>
   </si>
   <si>
     <t xml:space="preserve">2.78410291671753</t>
@@ -2906,28 +2906,28 @@
     <t xml:space="preserve">2.7486367225647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7752366065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72351479530334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76636981964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79296946525574</t>
+    <t xml:space="preserve">2.77523636817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72351503372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76636958122253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79296970367432</t>
   </si>
   <si>
     <t xml:space="preserve">2.73681473731995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69987058639526</t>
+    <t xml:space="preserve">2.69987082481384</t>
   </si>
   <si>
     <t xml:space="preserve">2.79592514038086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74272561073303</t>
+    <t xml:space="preserve">2.74272537231445</t>
   </si>
   <si>
     <t xml:space="preserve">2.75454783439636</t>
@@ -2939,10 +2939,10 @@
     <t xml:space="preserve">2.71612596511841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70873689651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70725965499878</t>
+    <t xml:space="preserve">2.70873737335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70725917816162</t>
   </si>
   <si>
     <t xml:space="preserve">2.61268281936646</t>
@@ -2951,49 +2951,49 @@
     <t xml:space="preserve">2.57573866844177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52549481391907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54174995422363</t>
+    <t xml:space="preserve">2.52549457550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54175019264221</t>
   </si>
   <si>
     <t xml:space="preserve">2.53436136245728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58460521697998</t>
+    <t xml:space="preserve">2.5846049785614</t>
   </si>
   <si>
     <t xml:space="preserve">2.52697253227234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47525072097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50037288665771</t>
+    <t xml:space="preserve">2.47525095939636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50037264823914</t>
   </si>
   <si>
     <t xml:space="preserve">2.43091797828674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52992796897888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6112048625946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54618358612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55209469795227</t>
+    <t xml:space="preserve">2.52992820739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61120462417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54618334770203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55209422111511</t>
   </si>
   <si>
     <t xml:space="preserve">2.67179298400879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60972690582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54322791099548</t>
+    <t xml:space="preserve">2.60972714424133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5432276725769</t>
   </si>
   <si>
     <t xml:space="preserve">2.52845025062561</t>
@@ -3008,28 +3008,28 @@
     <t xml:space="preserve">2.6570155620575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63632678985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60677194595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53140592575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52253913879395</t>
+    <t xml:space="preserve">2.63632702827454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60677170753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53140616416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52253937721252</t>
   </si>
   <si>
     <t xml:space="preserve">2.36441874504089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31713032722473</t>
+    <t xml:space="preserve">2.31713056564331</t>
   </si>
   <si>
     <t xml:space="preserve">2.37180757522583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51662802696228</t>
+    <t xml:space="preserve">2.51662826538086</t>
   </si>
   <si>
     <t xml:space="preserve">2.58312749862671</t>
@@ -3047,31 +3047,31 @@
     <t xml:space="preserve">2.6525821685791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63041567802429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71317005157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72794795036316</t>
+    <t xml:space="preserve">2.63041591644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71317052841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72794771194458</t>
   </si>
   <si>
     <t xml:space="preserve">2.74568128585815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83139133453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79149222373962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78853607177734</t>
+    <t xml:space="preserve">2.83139157295227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79149174690247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78853631019592</t>
   </si>
   <si>
     <t xml:space="preserve">2.75898122787476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6836154460907</t>
+    <t xml:space="preserve">2.68361520767212</t>
   </si>
   <si>
     <t xml:space="preserve">2.67031526565552</t>
@@ -3080,13 +3080,13 @@
     <t xml:space="preserve">2.66440439224243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64519333839417</t>
+    <t xml:space="preserve">2.64519357681274</t>
   </si>
   <si>
     <t xml:space="preserve">2.68065977096558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64962673187256</t>
+    <t xml:space="preserve">2.64962697029114</t>
   </si>
   <si>
     <t xml:space="preserve">2.68213748931885</t>
@@ -3107,25 +3107,25 @@
     <t xml:space="preserve">2.92301273345947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90380191802979</t>
+    <t xml:space="preserve">2.90380167961121</t>
   </si>
   <si>
     <t xml:space="preserve">2.90084624290466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98064541816711</t>
+    <t xml:space="preserve">2.98064517974854</t>
   </si>
   <si>
     <t xml:space="preserve">3.0146336555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03975582122803</t>
+    <t xml:space="preserve">3.03975558280945</t>
   </si>
   <si>
     <t xml:space="preserve">3.07374405860901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11807703971863</t>
+    <t xml:space="preserve">3.11807727813721</t>
   </si>
   <si>
     <t xml:space="preserve">3.06044459342957</t>
@@ -3134,19 +3134,19 @@
     <t xml:space="preserve">3.02350044250488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02941131591797</t>
+    <t xml:space="preserve">3.02941107749939</t>
   </si>
   <si>
     <t xml:space="preserve">2.89345741271973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86390209197998</t>
+    <t xml:space="preserve">2.86390233039856</t>
   </si>
   <si>
     <t xml:space="preserve">2.90675711631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87129092216492</t>
+    <t xml:space="preserve">2.87129068374634</t>
   </si>
   <si>
     <t xml:space="preserve">2.83434677124023</t>
@@ -3155,7 +3155,7 @@
     <t xml:space="preserve">2.91710162162781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04714441299438</t>
+    <t xml:space="preserve">3.04714465141296</t>
   </si>
   <si>
     <t xml:space="preserve">3.13285446166992</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">3.10034418106079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17718768119812</t>
+    <t xml:space="preserve">3.17718815803528</t>
   </si>
   <si>
     <t xml:space="preserve">3.10625505447388</t>
@@ -3173,61 +3173,61 @@
     <t xml:space="preserve">3.13581037521362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08408880233765</t>
+    <t xml:space="preserve">3.08408856391907</t>
   </si>
   <si>
     <t xml:space="preserve">3.00133371353149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94517922401428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9998562335968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97177839279175</t>
+    <t xml:space="preserve">2.9451789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99985647201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97177886962891</t>
   </si>
   <si>
     <t xml:space="preserve">2.93926787376404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08999967575073</t>
+    <t xml:space="preserve">3.08999991416931</t>
   </si>
   <si>
     <t xml:space="preserve">3.09147763252258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07669973373413</t>
+    <t xml:space="preserve">3.07669997215271</t>
   </si>
   <si>
     <t xml:space="preserve">3.08704423904419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08852195739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12694334983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24664258956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20526528358459</t>
+    <t xml:space="preserve">3.0885214805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12694382667542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24664235115051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20526480674744</t>
   </si>
   <si>
     <t xml:space="preserve">3.21856474876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33235287666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33826375007629</t>
+    <t xml:space="preserve">3.33235263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33826351165771</t>
   </si>
   <si>
     <t xml:space="preserve">3.34121918678284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31166386604309</t>
+    <t xml:space="preserve">3.31166410446167</t>
   </si>
   <si>
     <t xml:space="preserve">3.26142024993896</t>
@@ -3236,19 +3236,19 @@
     <t xml:space="preserve">3.32496380805969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30131959915161</t>
+    <t xml:space="preserve">3.30131936073303</t>
   </si>
   <si>
     <t xml:space="preserve">3.29245281219482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28801965713501</t>
+    <t xml:space="preserve">3.28801941871643</t>
   </si>
   <si>
     <t xml:space="preserve">3.31609725952148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29393100738525</t>
+    <t xml:space="preserve">3.29393076896667</t>
   </si>
   <si>
     <t xml:space="preserve">3.27324199676514</t>
@@ -3257,10 +3257,10 @@
     <t xml:space="preserve">3.24516487121582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32274746894836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30649185180664</t>
+    <t xml:space="preserve">3.32274723052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30649161338806</t>
   </si>
   <si>
     <t xml:space="preserve">3.31018614768982</t>
@@ -3275,31 +3275,31 @@
     <t xml:space="preserve">3.28358626365662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28654193878174</t>
+    <t xml:space="preserve">3.2865424156189</t>
   </si>
   <si>
     <t xml:space="preserve">3.27915358543396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24073123931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27767515182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28136992454529</t>
+    <t xml:space="preserve">3.24073171615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27767539024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28136968612671</t>
   </si>
   <si>
     <t xml:space="preserve">3.18531537055969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13433265686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10329961776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16314911842346</t>
+    <t xml:space="preserve">3.13433241844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10329937934875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16314888000488</t>
   </si>
   <si>
     <t xml:space="preserve">3.13507151603699</t>
@@ -3311,43 +3311,43 @@
     <t xml:space="preserve">3.09664964675903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15354347229004</t>
+    <t xml:space="preserve">3.15354371070862</t>
   </si>
   <si>
     <t xml:space="preserve">3.13654899597168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21043705940247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26511454582214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2274317741394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23925375938416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24738121032715</t>
+    <t xml:space="preserve">3.21043729782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26511478424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22743201255798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.239253282547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24738144874573</t>
   </si>
   <si>
     <t xml:space="preserve">3.31979179382324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33974123001099</t>
+    <t xml:space="preserve">3.33974146842957</t>
   </si>
   <si>
     <t xml:space="preserve">3.41362953186035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32053017616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32939720153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31535816192627</t>
+    <t xml:space="preserve">3.3205304145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32939696311951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31535840034485</t>
   </si>
   <si>
     <t xml:space="preserve">3.38761734962463</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">3.33789086341858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33322906494141</t>
+    <t xml:space="preserve">3.33322882652283</t>
   </si>
   <si>
     <t xml:space="preserve">3.33944439888</t>
@@ -3368,7 +3368,7 @@
     <t xml:space="preserve">3.33633685112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41325759887695</t>
+    <t xml:space="preserve">3.41325736045837</t>
   </si>
   <si>
     <t xml:space="preserve">3.37751650810242</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">3.40471076965332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60206270217896</t>
+    <t xml:space="preserve">3.60206246376038</t>
   </si>
   <si>
     <t xml:space="preserve">3.64868140220642</t>
@@ -3389,10 +3389,10 @@
     <t xml:space="preserve">3.55855202674866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52203392982483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51037931442261</t>
+    <t xml:space="preserve">3.52203416824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51037955284119</t>
   </si>
   <si>
     <t xml:space="preserve">3.44200563430786</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">3.44977521896362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38917088508606</t>
+    <t xml:space="preserve">3.38917112350464</t>
   </si>
   <si>
     <t xml:space="preserve">3.34022164344788</t>
@@ -3422,10 +3422,10 @@
     <t xml:space="preserve">3.2990415096283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25630831718445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26407814025879</t>
+    <t xml:space="preserve">3.25630807876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26407790184021</t>
   </si>
   <si>
     <t xml:space="preserve">3.24776124954224</t>
@@ -3446,10 +3446,10 @@
     <t xml:space="preserve">3.25009250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28738713264465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27184772491455</t>
+    <t xml:space="preserve">3.28738737106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27184748649597</t>
   </si>
   <si>
     <t xml:space="preserve">3.24620747566223</t>
@@ -3458,16 +3458,16 @@
     <t xml:space="preserve">3.2058048248291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16540169715881</t>
+    <t xml:space="preserve">3.16540193557739</t>
   </si>
   <si>
     <t xml:space="preserve">3.02632331848145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03098487854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09158897399902</t>
+    <t xml:space="preserve">3.03098511695862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0915892124176</t>
   </si>
   <si>
     <t xml:space="preserve">3.11956024169922</t>
@@ -3482,13 +3482,13 @@
     <t xml:space="preserve">3.19570398330688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21202039718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22989130020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23066806793213</t>
+    <t xml:space="preserve">3.21202063560486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22989106178284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23066782951355</t>
   </si>
   <si>
     <t xml:space="preserve">3.31458139419556</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">3.379070520401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33555960655212</t>
+    <t xml:space="preserve">3.3355598449707</t>
   </si>
   <si>
     <t xml:space="preserve">3.38606309890747</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">3.33478260040283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36120009422302</t>
+    <t xml:space="preserve">3.3612003326416</t>
   </si>
   <si>
     <t xml:space="preserve">3.34954524040222</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">3.36819291114807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36508464813232</t>
+    <t xml:space="preserve">3.36508440971375</t>
   </si>
   <si>
     <t xml:space="preserve">3.39227914810181</t>
@@ -3563,19 +3563,19 @@
     <t xml:space="preserve">3.32157444953918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33089828491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32312822341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28971862792969</t>
+    <t xml:space="preserve">3.33089804649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32312798500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28971838951111</t>
   </si>
   <si>
     <t xml:space="preserve">3.18715739250183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19725775718689</t>
+    <t xml:space="preserve">3.19725751876831</t>
   </si>
   <si>
     <t xml:space="preserve">3.29282593727112</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">3.28661036491394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22056722640991</t>
+    <t xml:space="preserve">3.22056746482849</t>
   </si>
   <si>
     <t xml:space="preserve">3.21745920181274</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">3.21279764175415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20891261100769</t>
+    <t xml:space="preserve">3.20891284942627</t>
   </si>
   <si>
     <t xml:space="preserve">3.17627930641174</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">3.48085427284241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50183296203613</t>
+    <t xml:space="preserve">3.50183272361755</t>
   </si>
   <si>
     <t xml:space="preserve">3.61682558059692</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">3.58652329444885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58963084220886</t>
+    <t xml:space="preserve">3.58963108062744</t>
   </si>
   <si>
     <t xml:space="preserve">3.59584665298462</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">3.57642245292664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.566321849823</t>
+    <t xml:space="preserve">3.56632208824158</t>
   </si>
   <si>
     <t xml:space="preserve">3.58108448982239</t>
@@ -3656,7 +3656,7 @@
     <t xml:space="preserve">3.68753004074097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63469576835632</t>
+    <t xml:space="preserve">3.63469552993774</t>
   </si>
   <si>
     <t xml:space="preserve">3.65178894996643</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">3.62692594528198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62148690223694</t>
+    <t xml:space="preserve">3.62148666381836</t>
   </si>
   <si>
     <t xml:space="preserve">3.61294031143188</t>
@@ -3683,7 +3683,7 @@
     <t xml:space="preserve">3.57409167289734</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50260972976685</t>
+    <t xml:space="preserve">3.50260996818542</t>
   </si>
   <si>
     <t xml:space="preserve">3.4482216835022</t>
@@ -3695,19 +3695,19 @@
     <t xml:space="preserve">3.39694118499756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39538669586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2633011341095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22833704948425</t>
+    <t xml:space="preserve">3.3953869342804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26330089569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22833728790283</t>
   </si>
   <si>
     <t xml:space="preserve">3.23999166488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40004897117615</t>
+    <t xml:space="preserve">3.40004873275757</t>
   </si>
   <si>
     <t xml:space="preserve">3.33711385726929</t>
@@ -3716,34 +3716,34 @@
     <t xml:space="preserve">3.36586141586304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37363171577454</t>
+    <t xml:space="preserve">3.37363147735596</t>
   </si>
   <si>
     <t xml:space="preserve">3.41791963577271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43656659126282</t>
+    <t xml:space="preserve">3.4365668296814</t>
   </si>
   <si>
     <t xml:space="preserve">3.31380438804626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42025017738342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42957401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4816312789917</t>
+    <t xml:space="preserve">3.42024993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42957425117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48163151741028</t>
   </si>
   <si>
     <t xml:space="preserve">3.49717116355896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48707032203674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48862385749817</t>
+    <t xml:space="preserve">3.48707008361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48862409591675</t>
   </si>
   <si>
     <t xml:space="preserve">3.51814913749695</t>
@@ -3776,19 +3776,19 @@
     <t xml:space="preserve">3.65567374229431</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56865286827087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52824974060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49639391899109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35420703887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40237975120544</t>
+    <t xml:space="preserve">3.56865262985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52824950218201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49639415740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35420727729797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40237998962402</t>
   </si>
   <si>
     <t xml:space="preserve">3.41092658042908</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">3.41558814048767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46531510353088</t>
+    <t xml:space="preserve">3.4653148651123</t>
   </si>
   <si>
     <t xml:space="preserve">3.48240828514099</t>
@@ -3815,25 +3815,25 @@
     <t xml:space="preserve">3.54301261901855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56321382522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75978899002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62614870071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79708385467529</t>
+    <t xml:space="preserve">3.56321406364441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75978922843933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62614893913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79708361625671</t>
   </si>
   <si>
     <t xml:space="preserve">3.75124216079712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65878224372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66188955307007</t>
+    <t xml:space="preserve">3.65878248214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66188931465149</t>
   </si>
   <si>
     <t xml:space="preserve">3.54612016677856</t>
@@ -3842,25 +3842,25 @@
     <t xml:space="preserve">3.55622148513794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38373231887817</t>
+    <t xml:space="preserve">3.38373208045959</t>
   </si>
   <si>
     <t xml:space="preserve">3.42258143424988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16384792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06361818313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87481284141541</t>
+    <t xml:space="preserve">3.16384768486023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06361794471741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87481260299683</t>
   </si>
   <si>
     <t xml:space="preserve">2.63395023345947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59898614883423</t>
+    <t xml:space="preserve">2.59898638725281</t>
   </si>
   <si>
     <t xml:space="preserve">2.64715886116028</t>
@@ -3884,13 +3884,13 @@
     <t xml:space="preserve">3.0783805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05118656158447</t>
+    <t xml:space="preserve">3.05118680000305</t>
   </si>
   <si>
     <t xml:space="preserve">3.05895638465881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06284117698669</t>
+    <t xml:space="preserve">3.06284093856812</t>
   </si>
   <si>
     <t xml:space="preserve">3.1622941493988</t>
@@ -3899,13 +3899,13 @@
     <t xml:space="preserve">3.14131593704224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10246706008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09780478477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13199186325073</t>
+    <t xml:space="preserve">3.10246682167053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09780502319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13199210166931</t>
   </si>
   <si>
     <t xml:space="preserve">3.23843789100647</t>
@@ -3917,19 +3917,19 @@
     <t xml:space="preserve">3.17161774635315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20269703865051</t>
+    <t xml:space="preserve">3.20269727706909</t>
   </si>
   <si>
     <t xml:space="preserve">3.09236621856689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35498404502869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36275410652161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37984752655029</t>
+    <t xml:space="preserve">3.35498428344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36275434494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37984728813171</t>
   </si>
   <si>
     <t xml:space="preserve">3.40937256813049</t>
@@ -3947,10 +3947,10 @@
     <t xml:space="preserve">3.51970338821411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52747273445129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59740090370178</t>
+    <t xml:space="preserve">3.52747249603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59740114212036</t>
   </si>
   <si>
     <t xml:space="preserve">3.6113862991333</t>
@@ -3965,7 +3965,7 @@
     <t xml:space="preserve">3.60983228683472</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36430811882019</t>
+    <t xml:space="preserve">3.36430788040161</t>
   </si>
   <si>
     <t xml:space="preserve">3.30059599876404</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">3.51659512519836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53524303436279</t>
+    <t xml:space="preserve">3.53524279594421</t>
   </si>
   <si>
     <t xml:space="preserve">3.55078268051147</t>
@@ -71242,7 +71242,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6912268518</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>68771</v>
@@ -71263,6 +71263,32 @@
         <v>1977</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6910763889</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>71425</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>6.21500015258789</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>6.18499994277954</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>6.20499992370605</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1961</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -38,64 +38,64 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24674701690674</t>
+    <t xml:space="preserve">4.24674654006958</t>
   </si>
   <si>
     <t xml:space="preserve">ANIM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33184623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13419580459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96948671340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95301628112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94203495979309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07380199432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93105483055115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82673859596252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76085567474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67850065231323</t>
+    <t xml:space="preserve">4.33184671401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13419628143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96948599815369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95301604270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94203543663025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07380294799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93105506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82673931121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76085543632507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67850041389465</t>
   </si>
   <si>
     <t xml:space="preserve">3.73889398574829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40398645401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53300786018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76909017562866</t>
+    <t xml:space="preserve">3.40398621559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53300762176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76909112930298</t>
   </si>
   <si>
     <t xml:space="preserve">3.79379725456238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79928684234619</t>
+    <t xml:space="preserve">3.79928755760193</t>
   </si>
   <si>
     <t xml:space="preserve">3.88438749313354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67575550079346</t>
+    <t xml:space="preserve">3.67575573921204</t>
   </si>
   <si>
     <t xml:space="preserve">3.70595240592957</t>
@@ -104,46 +104,46 @@
     <t xml:space="preserve">3.6400682926178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57967567443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35731816291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45065307617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3765344619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06633257865906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95652627944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1953547000885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98397755622864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24202179908752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20084404945374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48634028434753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38202381134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31065082550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38751530647278</t>
+    <t xml:space="preserve">3.57967495918274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35731840133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45065259933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37653398513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06633234024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95652651786804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19535422325134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98397779464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2420220375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20084476470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48633980751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38202428817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31065034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3875150680542</t>
   </si>
   <si>
     <t xml:space="preserve">3.2667281627655</t>
@@ -155,160 +155,160 @@
     <t xml:space="preserve">3.08554863929749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07182240486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06084156036377</t>
+    <t xml:space="preserve">3.07182264328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06084227561951</t>
   </si>
   <si>
     <t xml:space="preserve">3.15692186355591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.302414894104</t>
+    <t xml:space="preserve">3.30241465568542</t>
   </si>
   <si>
     <t xml:space="preserve">3.43967270851135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3518283367157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28319907188416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22280621528625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25300216674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57693004608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47261500358582</t>
+    <t xml:space="preserve">3.35182809829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28319931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22280526161194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25300240516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57692956924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4726140499115</t>
   </si>
   <si>
     <t xml:space="preserve">3.46437907218933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59065556526184</t>
+    <t xml:space="preserve">3.590656042099</t>
   </si>
   <si>
     <t xml:space="preserve">3.5632050037384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61261677742004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51653742790222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4341824054718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37104344367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45888924598694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5302631855011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32986617088318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27221846580505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09103894233704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23653149604797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34084725379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28594470024109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31888628005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23927617073059</t>
+    <t xml:space="preserve">3.6126172542572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51653671264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43418216705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37104320526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45888876914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53026247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32986640930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2722179889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09103870391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23653125762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34084749221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28594422340393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31888556480408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23927664756775</t>
   </si>
   <si>
     <t xml:space="preserve">3.42594695091248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41771125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4094762802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41496586799622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44241738319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46163439750671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44790863990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49732041358948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39300560951233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37378907203674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26123809814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26947402954102</t>
+    <t xml:space="preserve">3.41771101951599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40947580337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41496658325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44241762161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4616334438324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44790816307068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49732089042664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39300489425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37378931045532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26123762130737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2694730758667</t>
   </si>
   <si>
     <t xml:space="preserve">3.15417742729187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16241264343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0196647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94829106330872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82201433181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93182063102722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06907773017883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00044941902161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91809439659119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87417149543762</t>
+    <t xml:space="preserve">3.16241216659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01966524124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94829058647156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82201409339905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93182015419006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06907796859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00044870376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91809415817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87417197227478</t>
   </si>
   <si>
     <t xml:space="preserve">2.85221028327942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89064288139343</t>
+    <t xml:space="preserve">2.89064240455627</t>
   </si>
   <si>
     <t xml:space="preserve">2.97133898735046</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">3.06356310844421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23648285865784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24224638938904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29988670349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17884254455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15866875648499</t>
+    <t xml:space="preserve">3.23648262023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2422468662262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29988646507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17884278297424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15866899490356</t>
   </si>
   <si>
     <t xml:space="preserve">3.0405068397522</t>
@@ -338,43 +338,43 @@
     <t xml:space="preserve">2.97998476028442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96269297599792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02321434020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00015902519226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95692873001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81859302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79668998718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66988182067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61454749107361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54768490791321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70331239700317</t>
+    <t xml:space="preserve">2.9626932144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02321481704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00015950202942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95692849159241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81859278678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79668974876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66988158226013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61454725265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54768466949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70331287384033</t>
   </si>
   <si>
     <t xml:space="preserve">2.75288367271423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90505290031433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92234468460083</t>
+    <t xml:space="preserve">2.90505313873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92234492301941</t>
   </si>
   <si>
     <t xml:space="preserve">2.96845674514771</t>
@@ -386,40 +386,40 @@
     <t xml:space="preserve">2.26179122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49004554748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4197244644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42664122581482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49235081672668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36900162696838</t>
+    <t xml:space="preserve">2.49004530906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41972422599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4266414642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49235057830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3690013885498</t>
   </si>
   <si>
     <t xml:space="preserve">2.28830575942993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29752779006958</t>
+    <t xml:space="preserve">2.297527551651</t>
   </si>
   <si>
     <t xml:space="preserve">2.30559778213501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35747313499451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43240523338318</t>
+    <t xml:space="preserve">2.35747337341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43240547180176</t>
   </si>
   <si>
     <t xml:space="preserve">2.61108875274658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59379720687866</t>
+    <t xml:space="preserve">2.59379744529724</t>
   </si>
   <si>
     <t xml:space="preserve">2.68025708198547</t>
@@ -428,22 +428,22 @@
     <t xml:space="preserve">2.59725522994995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60647797584534</t>
+    <t xml:space="preserve">2.60647821426392</t>
   </si>
   <si>
     <t xml:space="preserve">2.56958794593811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62838125228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62261724472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5949501991272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61685371398926</t>
+    <t xml:space="preserve">2.62838077545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62261700630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59494996070862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6168532371521</t>
   </si>
   <si>
     <t xml:space="preserve">2.54653239250183</t>
@@ -452,70 +452,70 @@
     <t xml:space="preserve">2.63414525985718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58226895332336</t>
+    <t xml:space="preserve">2.58226919174194</t>
   </si>
   <si>
     <t xml:space="preserve">2.40358519554138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4151132106781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4381697177887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55114364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58572816848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65143728256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65489506721497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.604172706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54307436943054</t>
+    <t xml:space="preserve">2.41511344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43816947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55114340782166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58572769165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65143704414368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65489554405212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60417246818542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54307413101196</t>
   </si>
   <si>
     <t xml:space="preserve">2.41857171058655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37015438079834</t>
+    <t xml:space="preserve">2.37015390396118</t>
   </si>
   <si>
     <t xml:space="preserve">2.39321064949036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51310133934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50964283943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4612250328064</t>
+    <t xml:space="preserve">2.51310157775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50964260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46122527122498</t>
   </si>
   <si>
     <t xml:space="preserve">2.4485445022583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50733733177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50157356262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49696207046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5154070854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53039360046387</t>
+    <t xml:space="preserve">2.50733685493469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50157332420349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49696230888367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51540684700012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53039336204529</t>
   </si>
   <si>
     <t xml:space="preserve">2.57304716110229</t>
@@ -524,61 +524,61 @@
     <t xml:space="preserve">2.6618127822876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62722826004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73789715766907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83012080192566</t>
+    <t xml:space="preserve">2.62722778320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73789691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83012104034424</t>
   </si>
   <si>
     <t xml:space="preserve">2.7909255027771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67449331283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6560480594635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64797902107239</t>
+    <t xml:space="preserve">2.67449355125427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65604829788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64797878265381</t>
   </si>
   <si>
     <t xml:space="preserve">2.65720081329346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64567351341248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52001810073853</t>
+    <t xml:space="preserve">2.64567375183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52001786231995</t>
   </si>
   <si>
     <t xml:space="preserve">2.51886510848999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49580955505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52117109298706</t>
+    <t xml:space="preserve">2.49580907821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52117085456848</t>
   </si>
   <si>
     <t xml:space="preserve">2.52462887763977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54192137718201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47275352478027</t>
+    <t xml:space="preserve">2.54192161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47275328636169</t>
   </si>
   <si>
     <t xml:space="preserve">2.46929502487183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39436340332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32173657417297</t>
+    <t xml:space="preserve">2.39436292648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32173705101013</t>
   </si>
   <si>
     <t xml:space="preserve">2.32519507408142</t>
@@ -590,58 +590,58 @@
     <t xml:space="preserve">2.26524925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32634782791138</t>
+    <t xml:space="preserve">2.3263475894928</t>
   </si>
   <si>
     <t xml:space="preserve">2.38629293441772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4439332485199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44623851776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57074093818665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57996344566345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56267142295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55806064605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5038788318634</t>
+    <t xml:space="preserve">2.44393301010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44623875617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57074117660522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57996320724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56267166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55806040763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50387835502625</t>
   </si>
   <si>
     <t xml:space="preserve">2.50503158569336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38168215751648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60993623733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59956097602844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55344867706299</t>
+    <t xml:space="preserve">2.38168239593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60993599891663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59956073760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55344891548157</t>
   </si>
   <si>
     <t xml:space="preserve">2.70907735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67910408973694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58111596107483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80130124092102</t>
+    <t xml:space="preserve">2.67910432815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58111619949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80130100250244</t>
   </si>
   <si>
     <t xml:space="preserve">2.81282925605774</t>
@@ -653,31 +653,31 @@
     <t xml:space="preserve">2.78285646438599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82551002502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92522668838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96557402610779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91081690788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00592279434204</t>
+    <t xml:space="preserve">2.82550978660583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92522692680359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96557426452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91081666946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00592255592346</t>
   </si>
   <si>
     <t xml:space="preserve">3.03474283218384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99727630615234</t>
+    <t xml:space="preserve">2.99727654457092</t>
   </si>
   <si>
     <t xml:space="preserve">2.98574876785278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94828319549561</t>
+    <t xml:space="preserve">2.94828248023987</t>
   </si>
   <si>
     <t xml:space="preserve">2.93963694572449</t>
@@ -689,16 +689,16 @@
     <t xml:space="preserve">2.9915132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01456880569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03186058998108</t>
+    <t xml:space="preserve">3.014568567276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0318603515625</t>
   </si>
   <si>
     <t xml:space="preserve">3.16155099868774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13849496841431</t>
+    <t xml:space="preserve">3.13849472999573</t>
   </si>
   <si>
     <t xml:space="preserve">3.11255669593811</t>
@@ -707,97 +707,97 @@
     <t xml:space="preserve">3.12984824180603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2047803401947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16443228721619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19613480567932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19901704788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12408494949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14137697219849</t>
+    <t xml:space="preserve">3.20478057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16443204879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19613456726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1990168094635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12408518791199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14137649536133</t>
   </si>
   <si>
     <t xml:space="preserve">3.08373665809631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30276870727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26242065429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18748927116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28547620773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22783637046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17595982551575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24801015853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26818418502808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23936462402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09238266944885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10102891921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05491662025452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08085441589355</t>
+    <t xml:space="preserve">3.30276846885681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2624204158783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18748879432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28547644615173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2278368473053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17596054077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2480103969574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26818442344666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23936414718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09238219261169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10102868080139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0549168586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08085417747498</t>
   </si>
   <si>
     <t xml:space="preserve">3.11832046508789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15002274513245</t>
+    <t xml:space="preserve">3.15002250671387</t>
   </si>
   <si>
     <t xml:space="preserve">3.01168727874756</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92810845375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95404672622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7851619720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91369843482971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98863101005554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00304007530212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02609634399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07797312736511</t>
+    <t xml:space="preserve">2.92810893058777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95404720306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78516173362732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91369867324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98863124847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00304079055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02609658241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07797265052795</t>
   </si>
   <si>
     <t xml:space="preserve">3.05779886245728</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">3.18172430992126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17019701004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23360085487366</t>
+    <t xml:space="preserve">3.17019724845886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23360061645508</t>
   </si>
   <si>
     <t xml:space="preserve">3.24512910842896</t>
@@ -818,88 +818,88 @@
     <t xml:space="preserve">3.25089287757874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27106690406799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27394866943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28259491920471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25665640830994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18460607528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29412269592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10391116142273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34023451805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44398641586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4324586391449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46415948867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45839595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49298024177551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44686794281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50450825691223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60249614715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51603603363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46992444992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44110465049744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4238121509552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41228413581848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39499306678772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37193608283997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48935270309448</t>
+    <t xml:space="preserve">3.27106666564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27394843101501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28259468078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25665616989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18460655212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29412245750427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10391139984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34023475646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4439868927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43245887756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46416044235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45839619636536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49298000335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44686841964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50450873374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60249638557434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51603674888611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46992468833923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44110441207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42381262779236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41228485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39499258995056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37193584442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4893524646759</t>
   </si>
   <si>
     <t xml:space="preserve">3.49236249923706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59472513198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72117304801941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71515202522278</t>
+    <t xml:space="preserve">3.59472560882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72117233276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71515154838562</t>
   </si>
   <si>
     <t xml:space="preserve">3.58870363235474</t>
@@ -908,91 +908,91 @@
     <t xml:space="preserve">3.4682776927948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41107511520386</t>
+    <t xml:space="preserve">3.41107535362244</t>
   </si>
   <si>
     <t xml:space="preserve">3.49838447570801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54053282737732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50440549850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51644825935364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54956531524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70913028717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72418403625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64891743659973</t>
+    <t xml:space="preserve">3.54053354263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50440573692322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51644802093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54956579208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70913004875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72418355941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64891695976257</t>
   </si>
   <si>
     <t xml:space="preserve">3.75127983093262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72719407081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76332187652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73923659324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74525785446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71214151382446</t>
+    <t xml:space="preserve">3.72719383239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76332259178162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73923683166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74525809288025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71214079856873</t>
   </si>
   <si>
     <t xml:space="preserve">3.70310926437378</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75730037689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77536392211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77837610244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8415994644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85966300964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82654595375061</t>
+    <t xml:space="preserve">3.75730085372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77536487579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77837514877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84159922599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85966348648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82654619216919</t>
   </si>
   <si>
     <t xml:space="preserve">4.09750556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14266538619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19685649871826</t>
+    <t xml:space="preserve">4.14266443252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19685697555542</t>
   </si>
   <si>
     <t xml:space="preserve">4.17277240753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19083547592163</t>
+    <t xml:space="preserve">4.19083595275879</t>
   </si>
   <si>
     <t xml:space="preserve">4.22094202041626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19986724853516</t>
+    <t xml:space="preserve">4.199866771698</t>
   </si>
   <si>
     <t xml:space="preserve">4.2450270652771</t>
@@ -1001,31 +1001,31 @@
     <t xml:space="preserve">4.26911306381226</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26309204101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21492099761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15470790863037</t>
+    <t xml:space="preserve">4.26309108734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21492147445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15470743179321</t>
   </si>
   <si>
     <t xml:space="preserve">4.14567565917969</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13664436340332</t>
+    <t xml:space="preserve">4.136643409729</t>
   </si>
   <si>
     <t xml:space="preserve">4.22395324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22696304321289</t>
+    <t xml:space="preserve">4.22696352005005</t>
   </si>
   <si>
     <t xml:space="preserve">4.33534717559814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25104904174805</t>
+    <t xml:space="preserve">4.25104856491089</t>
   </si>
   <si>
     <t xml:space="preserve">4.28717613220215</t>
@@ -1034,43 +1034,43 @@
     <t xml:space="preserve">4.11857986450195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25405883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09449434280396</t>
+    <t xml:space="preserve">4.25405979156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09449481964111</t>
   </si>
   <si>
     <t xml:space="preserve">4.08847284317017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04030275344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05234479904175</t>
+    <t xml:space="preserve">4.04030227661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05234575271606</t>
   </si>
   <si>
     <t xml:space="preserve">3.95901417732239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86267352104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86568427085876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94396138191223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94697284698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95600390434265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98008966445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97406840324402</t>
+    <t xml:space="preserve">3.86267304420471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86568403244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94396185874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94697237014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95600414276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98009014129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97406816482544</t>
   </si>
   <si>
     <t xml:space="preserve">4.07342004776001</t>
@@ -1079,106 +1079,106 @@
     <t xml:space="preserve">4.06438827514648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98912143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96202516555786</t>
+    <t xml:space="preserve">3.98912215232849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96202564239502</t>
   </si>
   <si>
     <t xml:space="preserve">4.01320648193359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0342812538147</t>
+    <t xml:space="preserve">4.03428077697754</t>
   </si>
   <si>
     <t xml:space="preserve">4.00417470932007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00116300582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90783357620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88976979255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95299339294434</t>
+    <t xml:space="preserve">4.00116443634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90783381462097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8897705078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95299363136292</t>
   </si>
   <si>
     <t xml:space="preserve">4.01019620895386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11255884170532</t>
+    <t xml:space="preserve">4.11255788803101</t>
   </si>
   <si>
     <t xml:space="preserve">4.15771865844727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06739854812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98611044883728</t>
+    <t xml:space="preserve">4.06739902496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98611116409302</t>
   </si>
   <si>
     <t xml:space="preserve">3.93191885948181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90181183815002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87471699714661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85364174842834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82353472709656</t>
+    <t xml:space="preserve">3.9018120765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87471604347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85364151000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82353520393372</t>
   </si>
   <si>
     <t xml:space="preserve">3.89579105377197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84762072563171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83256793022156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88073825836182</t>
+    <t xml:space="preserve">3.84762096405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83256769180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88073801994324</t>
   </si>
   <si>
     <t xml:space="preserve">3.88374805450439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9258975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92890906333923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88675928115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91385531425476</t>
+    <t xml:space="preserve">3.92589783668518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92890882492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88675904273987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9138548374176</t>
   </si>
   <si>
     <t xml:space="preserve">3.91084480285645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8446102142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82052493095398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69106650352478</t>
+    <t xml:space="preserve">3.84460973739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82052516937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69106602668762</t>
   </si>
   <si>
     <t xml:space="preserve">3.70611929893494</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55558657646179</t>
+    <t xml:space="preserve">3.55558705329895</t>
   </si>
   <si>
     <t xml:space="preserve">3.47429895401001</t>
@@ -1187,13 +1187,13 @@
     <t xml:space="preserve">3.33580851554871</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40204334259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52246928215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54354381561279</t>
+    <t xml:space="preserve">3.40204286575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52246880531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54354429244995</t>
   </si>
   <si>
     <t xml:space="preserve">3.53150129318237</t>
@@ -1202,85 +1202,85 @@
     <t xml:space="preserve">3.57365083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60074615478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57666182518005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53752303123474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5525758266449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50139451026917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45021438598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51042628288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48634195327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43817138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40806484222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53451180458069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60977840423584</t>
+    <t xml:space="preserve">3.60074663162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5766613483429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53752279281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55257630348206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50139474868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45021390914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51042652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48634171485901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43817162513733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40806460380554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53451204299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60977816581726</t>
   </si>
   <si>
     <t xml:space="preserve">3.35387277603149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42612838745117</t>
+    <t xml:space="preserve">3.42612862586975</t>
   </si>
   <si>
     <t xml:space="preserve">3.44419240951538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32376551628113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39000058174133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61278939247131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73020505905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66698026657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64590692520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63386416435242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81450271606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86869525909424</t>
+    <t xml:space="preserve">3.32376575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39000129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61278891563416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73020458221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66698050498962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64590668678284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63386392593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81450319290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86869549751282</t>
   </si>
   <si>
     <t xml:space="preserve">3.93492984771729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04331302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99213123321533</t>
+    <t xml:space="preserve">4.04331398010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99213171005249</t>
   </si>
   <si>
     <t xml:space="preserve">3.98310017585754</t>
@@ -1289,28 +1289,28 @@
     <t xml:space="preserve">4.06137704849243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1246018409729</t>
+    <t xml:space="preserve">4.12460136413574</t>
   </si>
   <si>
     <t xml:space="preserve">4.16072940826416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07040929794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08245182037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8084819316864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89880180358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91987681388855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78439688682556</t>
+    <t xml:space="preserve">4.07040882110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08245134353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80848217010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89880156517029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91987633705139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78439664840698</t>
   </si>
   <si>
     <t xml:space="preserve">3.77235436439514</t>
@@ -1319,100 +1319,100 @@
     <t xml:space="preserve">3.79945015907288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73622584342957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75429010391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76633262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63988542556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56160759925842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66999173164368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96503639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79342865943909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74224781990051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79164934158325</t>
+    <t xml:space="preserve">3.73622608184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75429058074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76633238792419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63988518714905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56160807609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66999197006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96503663063049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79342937469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74224734306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79164958000183</t>
   </si>
   <si>
     <t xml:space="preserve">3.77612209320068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78854370117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70469856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58358979225159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55914258956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55258846282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51326155662537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61157989501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58536100387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76888990402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89998126029968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89342737197876</t>
+    <t xml:space="preserve">3.78854417800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70469903945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58358955383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55914282798767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55258893966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51326084136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61157965660095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58536124229431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76888966560364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89998173713684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89342713356018</t>
   </si>
   <si>
     <t xml:space="preserve">3.85082244873047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81149482727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63779830932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75578093528748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73939371109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86065411567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099054336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81804871559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96552777290344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98846912384033</t>
+    <t xml:space="preserve">3.81149506568909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63779807090759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75578045845032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73939442634583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86065435409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099102020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81804919242859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9655282497406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98846864700317</t>
   </si>
   <si>
     <t xml:space="preserve">3.93275499343872</t>
@@ -1421,124 +1421,124 @@
     <t xml:space="preserve">3.86720895767212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84426712989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91309094429016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8213267326355</t>
+    <t xml:space="preserve">3.84426784515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.913090467453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82132697105408</t>
   </si>
   <si>
     <t xml:space="preserve">4.03107357025146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04418230056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0245189666748</t>
+    <t xml:space="preserve">4.04418325424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02451848983765</t>
   </si>
   <si>
     <t xml:space="preserve">3.98191380500793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90653610229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99830055236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77544474601746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76561236381531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71973085403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71645283699036</t>
+    <t xml:space="preserve">3.90653657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99830102920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77544450759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76561260223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71973037719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71645379066467</t>
   </si>
   <si>
     <t xml:space="preserve">3.56897497177124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50670647621155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46737837791443</t>
+    <t xml:space="preserve">3.50670576095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46737909317017</t>
   </si>
   <si>
     <t xml:space="preserve">3.27467346191406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93645691871643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03477597236633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19077467918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42149639129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41494226455688</t>
+    <t xml:space="preserve">2.93645668029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03477573394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19077491760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42149662971497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41494178771973</t>
   </si>
   <si>
     <t xml:space="preserve">3.33628678321838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3166229724884</t>
+    <t xml:space="preserve">3.31662273406982</t>
   </si>
   <si>
     <t xml:space="preserve">3.35595059394836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21175003051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30023670196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32645463943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39855527877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33956384658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29040455818176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27729558944702</t>
+    <t xml:space="preserve">3.21174955368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30023622512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32645487785339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39855551719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33956408500671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29040479660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27729535102844</t>
   </si>
   <si>
     <t xml:space="preserve">3.28057289123535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18290901184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12260723114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07148098945618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01511168479919</t>
+    <t xml:space="preserve">3.18290972709656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12260699272156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07148122787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01511144638062</t>
   </si>
   <si>
     <t xml:space="preserve">2.89975094795227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01904463768005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01380085945129</t>
+    <t xml:space="preserve">3.01904511451721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01380109786987</t>
   </si>
   <si>
     <t xml:space="preserve">3.0491955280304</t>
@@ -1547,67 +1547,67 @@
     <t xml:space="preserve">2.97971701622009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02691006660461</t>
+    <t xml:space="preserve">3.02690982818604</t>
   </si>
   <si>
     <t xml:space="preserve">3.13440561294556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10425424575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04264163970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00200247764587</t>
+    <t xml:space="preserve">3.10425400733948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04264140129089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00200271606445</t>
   </si>
   <si>
     <t xml:space="preserve">3.00462460517883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98233914375305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98627185821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92072582244873</t>
+    <t xml:space="preserve">2.98233890533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98627161979675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92072558403015</t>
   </si>
   <si>
     <t xml:space="preserve">2.92728042602539</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00069165229797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01249027252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03739762306213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95612025260925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92465853691101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84469270706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97709512710571</t>
+    <t xml:space="preserve">3.00069189071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01249003410339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03739714622498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95612072944641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92465829849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84469246864319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97709488868713</t>
   </si>
   <si>
     <t xml:space="preserve">3.00724601745605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89057445526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77259206771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79487752914429</t>
+    <t xml:space="preserve">2.89057469367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77259230613708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79487776756287</t>
   </si>
   <si>
     <t xml:space="preserve">2.73064255714417</t>
@@ -1619,16 +1619,16 @@
     <t xml:space="preserve">2.70049142837524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77914643287659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76997041702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7371973991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72146606445312</t>
+    <t xml:space="preserve">2.77914667129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76997017860413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73719763755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7214663028717</t>
   </si>
   <si>
     <t xml:space="preserve">2.69000434875488</t>
@@ -1640,22 +1640,22 @@
     <t xml:space="preserve">2.64936542510986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62052536010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67689514160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72015523910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87615442276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85124707221985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86697840690613</t>
+    <t xml:space="preserve">2.620525598526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67689490318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7201554775238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87615466117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85124731063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86697816848755</t>
   </si>
   <si>
     <t xml:space="preserve">2.93907880783081</t>
@@ -1664,49 +1664,49 @@
     <t xml:space="preserve">2.91154956817627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91679286956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92596960067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94170069694519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99806976318359</t>
+    <t xml:space="preserve">2.91679263114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92596983909607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94170045852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99807000160217</t>
   </si>
   <si>
     <t xml:space="preserve">3.04133033752441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99675893783569</t>
+    <t xml:space="preserve">2.99675917625427</t>
   </si>
   <si>
     <t xml:space="preserve">2.99413704872131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96267533302307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96005344390869</t>
+    <t xml:space="preserve">2.96267509460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96005296707153</t>
   </si>
   <si>
     <t xml:space="preserve">2.91286015510559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77521419525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7070460319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68869352340698</t>
+    <t xml:space="preserve">2.77521395683289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70704650878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6886932849884</t>
   </si>
   <si>
     <t xml:space="preserve">2.705735206604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74244070053101</t>
+    <t xml:space="preserve">2.74244093894958</t>
   </si>
   <si>
     <t xml:space="preserve">2.64674377441406</t>
@@ -1727,19 +1727,19 @@
     <t xml:space="preserve">2.44879508018494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4907443523407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4710807800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48681211471558</t>
+    <t xml:space="preserve">2.49074482917786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47108101844788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.486811876297</t>
   </si>
   <si>
     <t xml:space="preserve">2.4199550151825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31639242172241</t>
+    <t xml:space="preserve">2.31639266014099</t>
   </si>
   <si>
     <t xml:space="preserve">2.25871205329895</t>
@@ -1763,34 +1763,34 @@
     <t xml:space="preserve">2.42519879341125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45928239822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54973578453064</t>
+    <t xml:space="preserve">2.45928263664246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54973602294922</t>
   </si>
   <si>
     <t xml:space="preserve">2.4723916053772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44617319107056</t>
+    <t xml:space="preserve">2.44617366790771</t>
   </si>
   <si>
     <t xml:space="preserve">2.45797157287598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.475013256073</t>
+    <t xml:space="preserve">2.47501349449158</t>
   </si>
   <si>
     <t xml:space="preserve">2.54842519760132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43044257164001</t>
+    <t xml:space="preserve">2.43044233322144</t>
   </si>
   <si>
     <t xml:space="preserve">2.40815687179565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33998894691467</t>
+    <t xml:space="preserve">2.33998870849609</t>
   </si>
   <si>
     <t xml:space="preserve">2.28886342048645</t>
@@ -1814,10 +1814,10 @@
     <t xml:space="preserve">2.29410696029663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35178732872009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766955375671</t>
+    <t xml:space="preserve">2.35178709030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766931533813</t>
   </si>
   <si>
     <t xml:space="preserve">2.44748425483704</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">2.42388796806335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40946793556213</t>
+    <t xml:space="preserve">2.40946769714355</t>
   </si>
   <si>
     <t xml:space="preserve">2.40029096603394</t>
@@ -1835,25 +1835,25 @@
     <t xml:space="preserve">2.21938467025757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19447684288025</t>
+    <t xml:space="preserve">2.19447731971741</t>
   </si>
   <si>
     <t xml:space="preserve">2.25477957725525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31901454925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32687973976135</t>
+    <t xml:space="preserve">2.31901431083679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32687997817993</t>
   </si>
   <si>
     <t xml:space="preserve">2.26264476776123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17743539810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12893128395081</t>
+    <t xml:space="preserve">2.17743515968323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12893104553223</t>
   </si>
   <si>
     <t xml:space="preserve">2.14597296714783</t>
@@ -1862,10 +1862,10 @@
     <t xml:space="preserve">2.12237668037415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12368750572205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10271310806274</t>
+    <t xml:space="preserve">2.12368726730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10271263122559</t>
   </si>
   <si>
     <t xml:space="preserve">2.11713290214539</t>
@@ -1874,37 +1874,37 @@
     <t xml:space="preserve">2.14728426933289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15121698379517</t>
+    <t xml:space="preserve">2.15121674537659</t>
   </si>
   <si>
     <t xml:space="preserve">2.23904824256897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20758605003357</t>
+    <t xml:space="preserve">2.20758628845215</t>
   </si>
   <si>
     <t xml:space="preserve">2.36489653587341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34785461425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37407279014587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25084638595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39504766464233</t>
+    <t xml:space="preserve">2.34785485267639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37407302856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25084686279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39504742622375</t>
   </si>
   <si>
     <t xml:space="preserve">2.35572004318237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41340017318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43306422233582</t>
+    <t xml:space="preserve">2.41340041160583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43306398391724</t>
   </si>
   <si>
     <t xml:space="preserve">2.44486260414124</t>
@@ -1922,19 +1922,19 @@
     <t xml:space="preserve">2.35309815406799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34654355049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35440921783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37145090103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28755235671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26788854598999</t>
+    <t xml:space="preserve">2.34654331207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35440897941589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37145113945007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28755211830139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26788878440857</t>
   </si>
   <si>
     <t xml:space="preserve">2.31114888191223</t>
@@ -1943,40 +1943,40 @@
     <t xml:space="preserve">2.37931656837463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40291309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40553498268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37014031410217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33605599403381</t>
+    <t xml:space="preserve">2.40291285514832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4055347442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37014007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33605623245239</t>
   </si>
   <si>
     <t xml:space="preserve">2.39898037910461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37669467926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50123190879822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54318141937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52613925933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50385355949402</t>
+    <t xml:space="preserve">2.37669491767883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5012321472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54318189620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52613949775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5038537979126</t>
   </si>
   <si>
     <t xml:space="preserve">2.49336624145508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42782068252563</t>
+    <t xml:space="preserve">2.42782044410706</t>
   </si>
   <si>
     <t xml:space="preserve">2.39635848999023</t>
@@ -1997,13 +1997,13 @@
     <t xml:space="preserve">2.29935050010681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38062763214111</t>
+    <t xml:space="preserve">2.38062739372253</t>
   </si>
   <si>
     <t xml:space="preserve">2.30459427833557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38849306106567</t>
+    <t xml:space="preserve">2.38849329948425</t>
   </si>
   <si>
     <t xml:space="preserve">2.45666074752808</t>
@@ -2027,70 +2027,70 @@
     <t xml:space="preserve">2.30328321456909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30590534210205</t>
+    <t xml:space="preserve">2.30590510368347</t>
   </si>
   <si>
     <t xml:space="preserve">2.34523272514343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32425808906555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30983781814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21545195579529</t>
+    <t xml:space="preserve">2.32425785064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30983805656433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21545147895813</t>
   </si>
   <si>
     <t xml:space="preserve">2.19054436683655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09091448783875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08698201179504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99783968925476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03978872299194</t>
+    <t xml:space="preserve">2.09091472625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08698177337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99783957004547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03978896141052</t>
   </si>
   <si>
     <t xml:space="preserve">1.9768648147583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99128472805023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97817528247833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98996269702911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99966990947723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97470915317535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94420051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91923952102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89843821525574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86377024650574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82632827758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87625086307526</t>
+    <t xml:space="preserve">1.99128460884094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97817552089691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98996245861053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99967014789581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97470891475677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94420075416565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91923928260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89843845367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86377012729645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82632851600647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87625074386597</t>
   </si>
   <si>
     <t xml:space="preserve">1.87902426719666</t>
@@ -2099,58 +2099,58 @@
     <t xml:space="preserve">1.83742213249207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9511342048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92755973339081</t>
+    <t xml:space="preserve">1.95113408565521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92755997180939</t>
   </si>
   <si>
     <t xml:space="preserve">1.89982521533966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92062604427338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90953242778778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90675890445709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88734459877014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88873136043549</t>
+    <t xml:space="preserve">1.92062640190125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90953254699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90675866603851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88734436035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88873112201691</t>
   </si>
   <si>
     <t xml:space="preserve">1.88179790973663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0287914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98302924633026</t>
+    <t xml:space="preserve">2.02879166603088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98302912712097</t>
   </si>
   <si>
     <t xml:space="preserve">2.03156495094299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98857617378235</t>
+    <t xml:space="preserve">1.98857605457306</t>
   </si>
   <si>
     <t xml:space="preserve">1.95945477485657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00660395622253</t>
+    <t xml:space="preserve">2.00660371780396</t>
   </si>
   <si>
     <t xml:space="preserve">2.00521683692932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07177996635437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09396815299988</t>
+    <t xml:space="preserve">2.07178020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0939679145813</t>
   </si>
   <si>
     <t xml:space="preserve">2.14943718910217</t>
@@ -2159,22 +2159,22 @@
     <t xml:space="preserve">2.22709441184998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25344228744507</t>
+    <t xml:space="preserve">2.25344204902649</t>
   </si>
   <si>
     <t xml:space="preserve">2.25898909568787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26453614234924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21461367607117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21184015274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24928212165833</t>
+    <t xml:space="preserve">2.26453638076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21461343765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21184039115906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24928188323975</t>
   </si>
   <si>
     <t xml:space="preserve">2.3144588470459</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">2.31307172775269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27424335479736</t>
+    <t xml:space="preserve">2.27424311637878</t>
   </si>
   <si>
     <t xml:space="preserve">2.2215473651886</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">2.24512195587158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28811049461365</t>
+    <t xml:space="preserve">2.28811073303223</t>
   </si>
   <si>
     <t xml:space="preserve">2.32277894020081</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">2.23125457763672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18687891960144</t>
+    <t xml:space="preserve">2.18687915802002</t>
   </si>
   <si>
     <t xml:space="preserve">2.17162489891052</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">2.17439842224121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22432112693787</t>
+    <t xml:space="preserve">2.22432088851929</t>
   </si>
   <si>
     <t xml:space="preserve">2.12170267105103</t>
@@ -2237,58 +2237,58 @@
     <t xml:space="preserve">2.10783529281616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12863612174988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09812808036804</t>
+    <t xml:space="preserve">2.1286358833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09812831878662</t>
   </si>
   <si>
     <t xml:space="preserve">2.1272497177124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1771719455719</t>
+    <t xml:space="preserve">2.17717218399048</t>
   </si>
   <si>
     <t xml:space="preserve">2.19103932380676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23680138587952</t>
+    <t xml:space="preserve">2.2368016242981</t>
   </si>
   <si>
     <t xml:space="preserve">2.20629334449768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19935965538025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18549227714539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25760269165039</t>
+    <t xml:space="preserve">2.19935941696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18549251556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25760245323181</t>
   </si>
   <si>
     <t xml:space="preserve">2.25621581077576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23957490921021</t>
+    <t xml:space="preserve">2.23957514762878</t>
   </si>
   <si>
     <t xml:space="preserve">2.35606050491333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38102149963379</t>
+    <t xml:space="preserve">2.38102173805237</t>
   </si>
   <si>
     <t xml:space="preserve">2.36715459823608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38379502296448</t>
+    <t xml:space="preserve">2.38379549980164</t>
   </si>
   <si>
     <t xml:space="preserve">2.43510460853577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51553511619568</t>
+    <t xml:space="preserve">2.51553535461426</t>
   </si>
   <si>
     <t xml:space="preserve">2.49889421463013</t>
@@ -2297,16 +2297,16 @@
     <t xml:space="preserve">2.42955756187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42817091941833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44897174835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45867896080017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766240119934</t>
+    <t xml:space="preserve">2.42817068099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44897198677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45867872238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3976628780365</t>
   </si>
   <si>
     <t xml:space="preserve">2.3879554271698</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">2.37131476402283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38240885734558</t>
+    <t xml:space="preserve">2.382408618927</t>
   </si>
   <si>
     <t xml:space="preserve">2.41707682609558</t>
@@ -2327,16 +2327,16 @@
     <t xml:space="preserve">2.37408828735352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32693886756897</t>
+    <t xml:space="preserve">2.32693910598755</t>
   </si>
   <si>
     <t xml:space="preserve">2.2992045879364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31723213195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34496665000916</t>
+    <t xml:space="preserve">2.31723189353943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34496641159058</t>
   </si>
   <si>
     <t xml:space="preserve">2.34635353088379</t>
@@ -2345,34 +2345,34 @@
     <t xml:space="preserve">2.41153001785278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46977257728577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48502683639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56961798667908</t>
+    <t xml:space="preserve">2.46977281570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48502707481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5696177482605</t>
   </si>
   <si>
     <t xml:space="preserve">2.61537981033325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6763961315155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73879885673523</t>
+    <t xml:space="preserve">2.67639589309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73879909515381</t>
   </si>
   <si>
     <t xml:space="preserve">2.70690441131592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74711942672729</t>
+    <t xml:space="preserve">2.74711918830872</t>
   </si>
   <si>
     <t xml:space="preserve">2.72770524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75266623497009</t>
+    <t xml:space="preserve">2.75266647338867</t>
   </si>
   <si>
     <t xml:space="preserve">2.76237344741821</t>
@@ -2381,16 +2381,16 @@
     <t xml:space="preserve">2.7859480381012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77208042144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69581055641174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70413112640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7207715511322</t>
+    <t xml:space="preserve">2.77208065986633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69581007957458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70413064956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72077202796936</t>
   </si>
   <si>
     <t xml:space="preserve">2.80120205879211</t>
@@ -2408,16 +2408,16 @@
     <t xml:space="preserve">2.9468092918396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01614570617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02723956108093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04804086685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07993578910828</t>
+    <t xml:space="preserve">3.01614618301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02723979949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04804062843323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0799355506897</t>
   </si>
   <si>
     <t xml:space="preserve">3.13679194450378</t>
@@ -2426,28 +2426,28 @@
     <t xml:space="preserve">3.14649868011475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17562007904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14511227607727</t>
+    <t xml:space="preserve">3.17562031745911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14511179924011</t>
   </si>
   <si>
     <t xml:space="preserve">3.23108959197998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24773049354553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26298451423645</t>
+    <t xml:space="preserve">3.24773025512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26298427581787</t>
   </si>
   <si>
     <t xml:space="preserve">3.26159763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22554230690002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18532705307007</t>
+    <t xml:space="preserve">3.22554278373718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18532729148865</t>
   </si>
   <si>
     <t xml:space="preserve">3.18394088745117</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">3.21028876304626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25327706336975</t>
+    <t xml:space="preserve">3.25327730178833</t>
   </si>
   <si>
     <t xml:space="preserve">3.22831630706787</t>
@@ -2468,19 +2468,19 @@
     <t xml:space="preserve">3.2019681930542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24218368530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26575803756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21306204795837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19919443130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20890140533447</t>
+    <t xml:space="preserve">3.24218344688416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26575779914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21306180953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19919490814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20890212059021</t>
   </si>
   <si>
     <t xml:space="preserve">3.22415614128113</t>
@@ -2492,7 +2492,7 @@
     <t xml:space="preserve">3.20335483551025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06606817245483</t>
+    <t xml:space="preserve">3.06606841087341</t>
   </si>
   <si>
     <t xml:space="preserve">3.09241628646851</t>
@@ -2501,76 +2501,76 @@
     <t xml:space="preserve">3.14788579940796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2061288356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17839360237122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17145967483521</t>
+    <t xml:space="preserve">3.20612835884094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17839384078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17145991325378</t>
   </si>
   <si>
     <t xml:space="preserve">3.03694701194763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15343236923218</t>
+    <t xml:space="preserve">3.15343260765076</t>
   </si>
   <si>
     <t xml:space="preserve">3.16868686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.970383644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03555989265442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14095211029053</t>
+    <t xml:space="preserve">2.97038388252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.035560131073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14095187187195</t>
   </si>
   <si>
     <t xml:space="preserve">3.12985801696777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14927196502686</t>
+    <t xml:space="preserve">3.14927244186401</t>
   </si>
   <si>
     <t xml:space="preserve">3.17007327079773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12708425521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10073709487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07854890823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11044383049011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08964276313782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28239870071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34202861785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34896206855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93987536430359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97315740585327</t>
+    <t xml:space="preserve">3.12708497047424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10073661804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07854914665222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11044406890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0896430015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28239917755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34202837944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34896159172058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93987512588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97315716743469</t>
   </si>
   <si>
     <t xml:space="preserve">2.863605260849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73741245269775</t>
+    <t xml:space="preserve">2.73741221427917</t>
   </si>
   <si>
     <t xml:space="preserve">2.58487153053284</t>
@@ -2588,115 +2588,115 @@
     <t xml:space="preserve">2.07039356231689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95668137073517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99134945869446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69042861461639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7847261428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65575993061066</t>
+    <t xml:space="preserve">1.95668148994446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99134981632233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69042837619781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78472626209259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65576016902924</t>
   </si>
   <si>
     <t xml:space="preserve">1.52818059921265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41030824184418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.485191822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49489903450012</t>
+    <t xml:space="preserve">1.4103080034256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48519194126129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49489879608154</t>
   </si>
   <si>
     <t xml:space="preserve">1.60583770275116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67933440208435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67656123638153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72648358345032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68904173374176</t>
+    <t xml:space="preserve">1.67933464050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67656099796295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72648346424103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68904185295105</t>
   </si>
   <si>
     <t xml:space="preserve">1.69736194610596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72371017932892</t>
+    <t xml:space="preserve">1.72371029853821</t>
   </si>
   <si>
     <t xml:space="preserve">1.75421810150146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78888642787933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02185773849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06207299232483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05375266075134</t>
+    <t xml:space="preserve">1.78888654708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02185750007629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06207323074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05375242233276</t>
   </si>
   <si>
     <t xml:space="preserve">1.99412298202515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97609543800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96638822555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94142699241638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8596099615097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86793053150177</t>
+    <t xml:space="preserve">1.97609555721283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96638810634613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94142735004425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85960984230042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86793041229248</t>
   </si>
   <si>
     <t xml:space="preserve">1.92339944839478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.901211977005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14805054664612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26730990409851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23818826675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22570753097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13418316841125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28117728233337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35744738578796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40043592453003</t>
+    <t xml:space="preserve">1.90121209621429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1480507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26730966567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23818778991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22570729255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13418340682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28117680549622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35744714736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40043568611145</t>
   </si>
   <si>
     <t xml:space="preserve">2.3435800075531</t>
@@ -2705,16 +2705,16 @@
     <t xml:space="preserve">2.30752491950989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48411750793457</t>
+    <t xml:space="preserve">2.48411726951599</t>
   </si>
   <si>
     <t xml:space="preserve">2.51219487190247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49150609970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49741721153259</t>
+    <t xml:space="preserve">2.49150633811951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49741744995117</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456218719482</t>
@@ -2729,43 +2729,43 @@
     <t xml:space="preserve">2.75750350952148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80774736404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86537981033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87572431564331</t>
+    <t xml:space="preserve">2.80774712562561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86538004875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87572407722473</t>
   </si>
   <si>
     <t xml:space="preserve">2.86833548545837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97473430633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20230984687805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1697986125946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14024376869202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93483471870422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93631267547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94222354888916</t>
+    <t xml:space="preserve">2.97473454475403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20230960845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16979885101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14024353027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93483448028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9363124370575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94222378730774</t>
   </si>
   <si>
     <t xml:space="preserve">2.99837851524353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00281167030334</t>
+    <t xml:space="preserve">3.00281190872192</t>
   </si>
   <si>
     <t xml:space="preserve">2.9584789276123</t>
@@ -2780,49 +2780,49 @@
     <t xml:space="preserve">2.83582472801208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89050197601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88459086418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85946869850159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82843613624573</t>
+    <t xml:space="preserve">2.89050149917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88459134101868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85946893692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82843589782715</t>
   </si>
   <si>
     <t xml:space="preserve">2.86242437362671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93779039382935</t>
+    <t xml:space="preserve">2.93779015541077</t>
   </si>
   <si>
     <t xml:space="preserve">2.99542307853699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03236699104309</t>
+    <t xml:space="preserve">3.03236722946167</t>
   </si>
   <si>
     <t xml:space="preserve">3.04418897628784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01906704902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92005681991577</t>
+    <t xml:space="preserve">3.01906728744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92005705833435</t>
   </si>
   <si>
     <t xml:space="preserve">2.93040156364441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97916769981384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98212313652039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99394512176514</t>
+    <t xml:space="preserve">2.97916746139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98212289810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99394536018372</t>
   </si>
   <si>
     <t xml:space="preserve">2.98951196670532</t>
@@ -2834,13 +2834,13 @@
     <t xml:space="preserve">2.95552325248718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94665670394897</t>
+    <t xml:space="preserve">2.94665694236755</t>
   </si>
   <si>
     <t xml:space="preserve">3.03384470939636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09591102600098</t>
+    <t xml:space="preserve">3.09591054916382</t>
   </si>
   <si>
     <t xml:space="preserve">3.01758933067322</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">2.99098968505859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93335676193237</t>
+    <t xml:space="preserve">2.93335700035095</t>
   </si>
   <si>
     <t xml:space="preserve">2.91857933998108</t>
@@ -2858,31 +2858,31 @@
     <t xml:space="preserve">2.75602555274963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81365847587585</t>
+    <t xml:space="preserve">2.81365823745728</t>
   </si>
   <si>
     <t xml:space="preserve">2.85503554344177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8535578250885</t>
+    <t xml:space="preserve">2.85355806350708</t>
   </si>
   <si>
     <t xml:space="preserve">2.894935131073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87720227241516</t>
+    <t xml:space="preserve">2.87720203399658</t>
   </si>
   <si>
     <t xml:space="preserve">2.92153477668762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9629123210907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91266846656799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87424635887146</t>
+    <t xml:space="preserve">2.96291208267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91266822814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87424683570862</t>
   </si>
   <si>
     <t xml:space="preserve">2.84616899490356</t>
@@ -2903,16 +2903,16 @@
     <t xml:space="preserve">2.79888081550598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7486367225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77523636817932</t>
+    <t xml:space="preserve">2.74863696098328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7752366065979</t>
   </si>
   <si>
     <t xml:space="preserve">2.72351503372192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76636958122253</t>
+    <t xml:space="preserve">2.76636981964111</t>
   </si>
   <si>
     <t xml:space="preserve">2.79296970367432</t>
@@ -2921,16 +2921,16 @@
     <t xml:space="preserve">2.73681473731995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69987082481384</t>
+    <t xml:space="preserve">2.69987058639526</t>
   </si>
   <si>
     <t xml:space="preserve">2.79592514038086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74272537231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75454783439636</t>
+    <t xml:space="preserve">2.74272561073303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75454759597778</t>
   </si>
   <si>
     <t xml:space="preserve">2.74715900421143</t>
@@ -2939,10 +2939,10 @@
     <t xml:space="preserve">2.71612596511841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70873737335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70725917816162</t>
+    <t xml:space="preserve">2.70873713493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7072594165802</t>
   </si>
   <si>
     <t xml:space="preserve">2.61268281936646</t>
@@ -2951,94 +2951,94 @@
     <t xml:space="preserve">2.57573866844177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52549457550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54175019264221</t>
+    <t xml:space="preserve">2.52549505233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54174995422363</t>
   </si>
   <si>
     <t xml:space="preserve">2.53436136245728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5846049785614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52697253227234</t>
+    <t xml:space="preserve">2.58460521697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52697229385376</t>
   </si>
   <si>
     <t xml:space="preserve">2.47525095939636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50037264823914</t>
+    <t xml:space="preserve">2.50037288665771</t>
   </si>
   <si>
     <t xml:space="preserve">2.43091797828674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52992820739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61120462417603</t>
+    <t xml:space="preserve">2.52992796897888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6112048625946</t>
   </si>
   <si>
     <t xml:space="preserve">2.54618334770203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55209422111511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67179298400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60972714424133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5432276725769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52845025062561</t>
+    <t xml:space="preserve">2.55209445953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67179322242737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60972690582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54322791099548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52845001220703</t>
   </si>
   <si>
     <t xml:space="preserve">2.47377300262451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6289381980896</t>
+    <t xml:space="preserve">2.62893795967102</t>
   </si>
   <si>
     <t xml:space="preserve">2.6570155620575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63632702827454</t>
+    <t xml:space="preserve">2.63632678985596</t>
   </si>
   <si>
     <t xml:space="preserve">2.60677170753479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53140616416931</t>
+    <t xml:space="preserve">2.53140592575073</t>
   </si>
   <si>
     <t xml:space="preserve">2.52253937721252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36441874504089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31713056564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37180757522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51662826538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58312749862671</t>
+    <t xml:space="preserve">2.36441898345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31713032722473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37180733680725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51662802696228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58312773704529</t>
   </si>
   <si>
     <t xml:space="preserve">2.64223790168762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49298405647278</t>
+    <t xml:space="preserve">2.4929838180542</t>
   </si>
   <si>
     <t xml:space="preserve">2.615638256073</t>
@@ -3047,16 +3047,16 @@
     <t xml:space="preserve">2.6525821685791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63041591644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71317052841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72794771194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74568128585815</t>
+    <t xml:space="preserve">2.63041567802429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71317076683044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72794818878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74568104743958</t>
   </si>
   <si>
     <t xml:space="preserve">2.83139157295227</t>
@@ -3068,25 +3068,25 @@
     <t xml:space="preserve">2.78853631019592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75898122787476</t>
+    <t xml:space="preserve">2.75898146629333</t>
   </si>
   <si>
     <t xml:space="preserve">2.68361520767212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67031526565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66440439224243</t>
+    <t xml:space="preserve">2.6703155040741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66440415382385</t>
   </si>
   <si>
     <t xml:space="preserve">2.64519357681274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68065977096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64962697029114</t>
+    <t xml:space="preserve">2.68066000938416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64962673187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.68213748931885</t>
@@ -3095,13 +3095,13 @@
     <t xml:space="preserve">2.62598252296448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65849328041077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7205593585968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85651326179504</t>
+    <t xml:space="preserve">2.65849351882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72055912017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85651302337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.92301273345947</t>
@@ -3110,22 +3110,22 @@
     <t xml:space="preserve">2.90380167961121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90084624290466</t>
+    <t xml:space="preserve">2.90084600448608</t>
   </si>
   <si>
     <t xml:space="preserve">2.98064517974854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0146336555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03975558280945</t>
+    <t xml:space="preserve">3.01463389396667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03975582122803</t>
   </si>
   <si>
     <t xml:space="preserve">3.07374405860901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11807727813721</t>
+    <t xml:space="preserve">3.11807703971863</t>
   </si>
   <si>
     <t xml:space="preserve">3.06044459342957</t>
@@ -3134,7 +3134,7 @@
     <t xml:space="preserve">3.02350044250488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02941107749939</t>
+    <t xml:space="preserve">3.02941155433655</t>
   </si>
   <si>
     <t xml:space="preserve">2.89345741271973</t>
@@ -3143,13 +3143,13 @@
     <t xml:space="preserve">2.86390233039856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90675711631775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87129068374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83434677124023</t>
+    <t xml:space="preserve">2.90675735473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87129092216492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83434700965881</t>
   </si>
   <si>
     <t xml:space="preserve">2.91710162162781</t>
@@ -3158,97 +3158,97 @@
     <t xml:space="preserve">3.04714465141296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13285446166992</t>
+    <t xml:space="preserve">3.1328547000885</t>
   </si>
   <si>
     <t xml:space="preserve">3.10034418106079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17718815803528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10625505447388</t>
+    <t xml:space="preserve">3.1771879196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1062548160553</t>
   </si>
   <si>
     <t xml:space="preserve">3.13581037521362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08408856391907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00133371353149</t>
+    <t xml:space="preserve">3.08408832550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00133395195007</t>
   </si>
   <si>
     <t xml:space="preserve">2.9451789855957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99985647201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97177886962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93926787376404</t>
+    <t xml:space="preserve">2.9998562335968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97177863121033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93926811218262</t>
   </si>
   <si>
     <t xml:space="preserve">3.08999991416931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09147763252258</t>
+    <t xml:space="preserve">3.091477394104</t>
   </si>
   <si>
     <t xml:space="preserve">3.07669997215271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08704423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0885214805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12694382667542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24664235115051</t>
+    <t xml:space="preserve">3.08704447746277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08852195739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12694358825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24664258956909</t>
   </si>
   <si>
     <t xml:space="preserve">3.20526480674744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21856474876404</t>
+    <t xml:space="preserve">3.21856498718262</t>
   </si>
   <si>
     <t xml:space="preserve">3.33235263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33826351165771</t>
+    <t xml:space="preserve">3.33826398849487</t>
   </si>
   <si>
     <t xml:space="preserve">3.34121918678284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31166410446167</t>
+    <t xml:space="preserve">3.31166386604309</t>
   </si>
   <si>
     <t xml:space="preserve">3.26142024993896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32496380805969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30131936073303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29245281219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28801941871643</t>
+    <t xml:space="preserve">3.32496404647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30131959915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2924530506134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28801918029785</t>
   </si>
   <si>
     <t xml:space="preserve">3.31609725952148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29393076896667</t>
+    <t xml:space="preserve">3.29393100738525</t>
   </si>
   <si>
     <t xml:space="preserve">3.27324199676514</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">3.32274723052979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30649161338806</t>
+    <t xml:space="preserve">3.30649185180664</t>
   </si>
   <si>
     <t xml:space="preserve">3.31018614768982</t>
@@ -3269,73 +3269,73 @@
     <t xml:space="preserve">3.29540872573853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25107574462891</t>
+    <t xml:space="preserve">3.25107598304749</t>
   </si>
   <si>
     <t xml:space="preserve">3.28358626365662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2865424156189</t>
+    <t xml:space="preserve">3.28654217720032</t>
   </si>
   <si>
     <t xml:space="preserve">3.27915358543396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24073171615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27767539024353</t>
+    <t xml:space="preserve">3.24073147773743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27767515182495</t>
   </si>
   <si>
     <t xml:space="preserve">3.28136968612671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18531537055969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13433241844177</t>
+    <t xml:space="preserve">3.18531489372253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13433265686035</t>
   </si>
   <si>
     <t xml:space="preserve">3.10329937934875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16314888000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13507151603699</t>
+    <t xml:space="preserve">3.16314911842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13507127761841</t>
   </si>
   <si>
     <t xml:space="preserve">3.17940425872803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09664964675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15354371070862</t>
+    <t xml:space="preserve">3.09664940834045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15354347229004</t>
   </si>
   <si>
     <t xml:space="preserve">3.13654899597168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21043729782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26511478424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22743201255798</t>
+    <t xml:space="preserve">3.21043705940247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2651150226593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2274317741394</t>
   </si>
   <si>
     <t xml:space="preserve">3.239253282547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24738144874573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31979179382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33974146842957</t>
+    <t xml:space="preserve">3.24738121032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31979203224182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33974123001099</t>
   </si>
   <si>
     <t xml:space="preserve">3.41362953186035</t>
@@ -3347,22 +3347,22 @@
     <t xml:space="preserve">3.32939696311951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31535840034485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38761734962463</t>
+    <t xml:space="preserve">3.31535816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38761711120605</t>
   </si>
   <si>
     <t xml:space="preserve">3.31846618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33789086341858</t>
+    <t xml:space="preserve">3.337890625</t>
   </si>
   <si>
     <t xml:space="preserve">3.33322882652283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33944439888</t>
+    <t xml:space="preserve">3.33944463729858</t>
   </si>
   <si>
     <t xml:space="preserve">3.33633685112</t>
@@ -3371,7 +3371,7 @@
     <t xml:space="preserve">3.41325736045837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37751650810242</t>
+    <t xml:space="preserve">3.377516746521</t>
   </si>
   <si>
     <t xml:space="preserve">3.40471076965332</t>
@@ -3383,7 +3383,7 @@
     <t xml:space="preserve">3.64868140220642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57098364830017</t>
+    <t xml:space="preserve">3.57098388671875</t>
   </si>
   <si>
     <t xml:space="preserve">3.55855202674866</t>
@@ -3392,46 +3392,46 @@
     <t xml:space="preserve">3.52203416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51037955284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44200563430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47619247436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44977521896362</t>
+    <t xml:space="preserve">3.51037979125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44200539588928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47619271278381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4497754573822</t>
   </si>
   <si>
     <t xml:space="preserve">3.38917112350464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34022164344788</t>
+    <t xml:space="preserve">3.3402214050293</t>
   </si>
   <si>
     <t xml:space="preserve">3.32545924186707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34876823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27417898178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2990415096283</t>
+    <t xml:space="preserve">3.34876847267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27417874336243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29904174804688</t>
   </si>
   <si>
     <t xml:space="preserve">3.25630807876587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26407790184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24776124954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2788405418396</t>
+    <t xml:space="preserve">3.26407837867737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24776148796082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27884030342102</t>
   </si>
   <si>
     <t xml:space="preserve">3.25786185264587</t>
@@ -3440,7 +3440,7 @@
     <t xml:space="preserve">3.24076867103577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19337344169617</t>
+    <t xml:space="preserve">3.19337320327759</t>
   </si>
   <si>
     <t xml:space="preserve">3.25009250640869</t>
@@ -3449,16 +3449,16 @@
     <t xml:space="preserve">3.28738737106323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27184748649597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24620747566223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2058048248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16540193557739</t>
+    <t xml:space="preserve">3.27184772491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24620771408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20580458641052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16540217399597</t>
   </si>
   <si>
     <t xml:space="preserve">3.02632331848145</t>
@@ -3473,10 +3473,10 @@
     <t xml:space="preserve">3.11956024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1801643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22678327560425</t>
+    <t xml:space="preserve">3.18016457557678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22678303718567</t>
   </si>
   <si>
     <t xml:space="preserve">3.19570398330688</t>
@@ -3485,28 +3485,28 @@
     <t xml:space="preserve">3.21202063560486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22989106178284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23066782951355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31458139419556</t>
+    <t xml:space="preserve">3.22989130020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23066806793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3145809173584</t>
   </si>
   <si>
     <t xml:space="preserve">3.23299884796143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28894090652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30370378494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.379070520401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3355598449707</t>
+    <t xml:space="preserve">3.28894114494324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30370354652405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37907028198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33556032180786</t>
   </si>
   <si>
     <t xml:space="preserve">3.38606309890747</t>
@@ -3515,40 +3515,40 @@
     <t xml:space="preserve">3.33245182037354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31302738189697</t>
+    <t xml:space="preserve">3.31302762031555</t>
   </si>
   <si>
     <t xml:space="preserve">3.33478260040283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3612003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34954524040222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36819291114807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36508440971375</t>
+    <t xml:space="preserve">3.36119985580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34954500198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36819267272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3650848865509</t>
   </si>
   <si>
     <t xml:space="preserve">3.39227914810181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41248083114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37207770347595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39150166511536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39849495887756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35032224655151</t>
+    <t xml:space="preserve">3.41248059272766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37207746505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39150190353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39849472045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35032200813293</t>
   </si>
   <si>
     <t xml:space="preserve">3.35343027114868</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">3.34721446037292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32157444953918</t>
+    <t xml:space="preserve">3.32157421112061</t>
   </si>
   <si>
     <t xml:space="preserve">3.33089804649353</t>
@@ -3569,22 +3569,22 @@
     <t xml:space="preserve">3.32312798500061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28971838951111</t>
+    <t xml:space="preserve">3.28971815109253</t>
   </si>
   <si>
     <t xml:space="preserve">3.18715739250183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19725751876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29282593727112</t>
+    <t xml:space="preserve">3.19725775718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2928261756897</t>
   </si>
   <si>
     <t xml:space="preserve">3.28661036491394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22056746482849</t>
+    <t xml:space="preserve">3.22056722640991</t>
   </si>
   <si>
     <t xml:space="preserve">3.21745920181274</t>
@@ -3593,13 +3593,13 @@
     <t xml:space="preserve">3.21279764175415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20891284942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17627930641174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30758857727051</t>
+    <t xml:space="preserve">3.20891261100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17627954483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30758833885193</t>
   </si>
   <si>
     <t xml:space="preserve">3.33012080192566</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">3.36741590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3946099281311</t>
+    <t xml:space="preserve">3.39461016654968</t>
   </si>
   <si>
     <t xml:space="preserve">3.32623624801636</t>
@@ -3617,19 +3617,19 @@
     <t xml:space="preserve">3.43268179893494</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45443749427795</t>
+    <t xml:space="preserve">3.4544370174408</t>
   </si>
   <si>
     <t xml:space="preserve">3.48085427284241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50183272361755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61682558059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57797646522522</t>
+    <t xml:space="preserve">3.50183296203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61682510375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5779767036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.58652329444885</t>
@@ -3638,16 +3638,16 @@
     <t xml:space="preserve">3.58963108062744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59584665298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57176089286804</t>
+    <t xml:space="preserve">3.5958468914032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57176041603088</t>
   </si>
   <si>
     <t xml:space="preserve">3.57642245292664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56632208824158</t>
+    <t xml:space="preserve">3.56632161140442</t>
   </si>
   <si>
     <t xml:space="preserve">3.58108448982239</t>
@@ -3656,40 +3656,40 @@
     <t xml:space="preserve">3.68753004074097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63469552993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65178894996643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64246535301208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62070989608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62692594528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62148666381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61294031143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61060953140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57409167289734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50260996818542</t>
+    <t xml:space="preserve">3.63469576835632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65178918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64246582984924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62071013450623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62692618370056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62148690223694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61294054985046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61060929298401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57409119606018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50260972976685</t>
   </si>
   <si>
     <t xml:space="preserve">3.4482216835022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45132899284363</t>
+    <t xml:space="preserve">3.45132946968079</t>
   </si>
   <si>
     <t xml:space="preserve">3.39694118499756</t>
@@ -3707,46 +3707,46 @@
     <t xml:space="preserve">3.23999166488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40004873275757</t>
+    <t xml:space="preserve">3.40004897117615</t>
   </si>
   <si>
     <t xml:space="preserve">3.33711385726929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36586141586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37363147735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41791963577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4365668296814</t>
+    <t xml:space="preserve">3.3658618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37363171577454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41791939735413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43656659126282</t>
   </si>
   <si>
     <t xml:space="preserve">3.31380438804626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42024993896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42957425117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48163151741028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49717116355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48707008361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48862409591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51814913749695</t>
+    <t xml:space="preserve">3.420250415802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42957401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4816312789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4971706867218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48707032203674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48862361907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51814889907837</t>
   </si>
   <si>
     <t xml:space="preserve">3.54145860671997</t>
@@ -3755,31 +3755,31 @@
     <t xml:space="preserve">3.52436494827271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48551607131958</t>
+    <t xml:space="preserve">3.48551654815674</t>
   </si>
   <si>
     <t xml:space="preserve">3.49794769287109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64635014533997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70151591300964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6960768699646</t>
+    <t xml:space="preserve">3.64635038375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70151567459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69607663154602</t>
   </si>
   <si>
     <t xml:space="preserve">3.64712738990784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65567374229431</t>
+    <t xml:space="preserve">3.65567398071289</t>
   </si>
   <si>
     <t xml:space="preserve">3.56865262985229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52824950218201</t>
+    <t xml:space="preserve">3.52824974060059</t>
   </si>
   <si>
     <t xml:space="preserve">3.49639415740967</t>
@@ -3791,13 +3791,13 @@
     <t xml:space="preserve">3.40237998962402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41092658042908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41558814048767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4653148651123</t>
+    <t xml:space="preserve">3.4109263420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41558837890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46531510353088</t>
   </si>
   <si>
     <t xml:space="preserve">3.48240828514099</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">3.49017834663391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47075390815735</t>
+    <t xml:space="preserve">3.47075366973877</t>
   </si>
   <si>
     <t xml:space="preserve">3.45366048812866</t>
@@ -3815,61 +3815,61 @@
     <t xml:space="preserve">3.54301261901855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56321406364441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75978922843933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62614893913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79708361625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75124216079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65878248214722</t>
+    <t xml:space="preserve">3.56321382522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75978899002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62614870071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79708385467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7512423992157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65878200531006</t>
   </si>
   <si>
     <t xml:space="preserve">3.66188931465149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54612016677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55622148513794</t>
+    <t xml:space="preserve">3.54612040519714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55622124671936</t>
   </si>
   <si>
     <t xml:space="preserve">3.38373208045959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42258143424988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16384768486023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06361794471741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87481260299683</t>
+    <t xml:space="preserve">3.42258167266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16384816169739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06361818313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87481284141541</t>
   </si>
   <si>
     <t xml:space="preserve">2.63395023345947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59898638725281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64715886116028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83751797676086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74505758285522</t>
+    <t xml:space="preserve">2.59898614883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6471586227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83751773834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7450578212738</t>
   </si>
   <si>
     <t xml:space="preserve">2.8204243183136</t>
@@ -3878,16 +3878,16 @@
     <t xml:space="preserve">2.93308615684509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91366147994995</t>
+    <t xml:space="preserve">2.91366171836853</t>
   </si>
   <si>
     <t xml:space="preserve">3.0783805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05118680000305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05895638465881</t>
+    <t xml:space="preserve">3.05118656158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05895590782166</t>
   </si>
   <si>
     <t xml:space="preserve">3.06284093856812</t>
@@ -3896,10 +3896,10 @@
     <t xml:space="preserve">3.1622941493988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14131593704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10246682167053</t>
+    <t xml:space="preserve">3.14131569862366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10246706008911</t>
   </si>
   <si>
     <t xml:space="preserve">3.09780502319336</t>
@@ -3911,13 +3911,13 @@
     <t xml:space="preserve">3.23843789100647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24853849411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17161774635315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20269727706909</t>
+    <t xml:space="preserve">3.24853873252869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17161750793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20269680023193</t>
   </si>
   <si>
     <t xml:space="preserve">3.09236621856689</t>
@@ -3926,31 +3926,31 @@
     <t xml:space="preserve">3.35498428344727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36275434494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37984728813171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40937256813049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42335820198059</t>
+    <t xml:space="preserve">3.36275410652161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37984752655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40937232971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42335796356201</t>
   </si>
   <si>
     <t xml:space="preserve">3.53058099746704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59273934364319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51970338821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52747249603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59740114212036</t>
+    <t xml:space="preserve">3.59273910522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51970314979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52747297286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5974006652832</t>
   </si>
   <si>
     <t xml:space="preserve">3.6113862991333</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">3.6937460899353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63624930381775</t>
+    <t xml:space="preserve">3.63624906539917</t>
   </si>
   <si>
     <t xml:space="preserve">3.60983228683472</t>
@@ -3968,19 +3968,19 @@
     <t xml:space="preserve">3.36430788040161</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30059599876404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38140177726746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46686887741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51659512519836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53524279594421</t>
+    <t xml:space="preserve">3.30059576034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38140153884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46686863899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51659560203552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53524303436279</t>
   </si>
   <si>
     <t xml:space="preserve">3.55078268051147</t>
@@ -3992,40 +3992,40 @@
     <t xml:space="preserve">3.51193332672119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63948965072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6378333568573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65771174430847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71403574943542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70740914344788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75876307487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71569180488586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64611577987671</t>
+    <t xml:space="preserve">3.6394898891449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63783311843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65771198272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71403551101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70740866661072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7587628364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71569228172302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64611625671387</t>
   </si>
   <si>
     <t xml:space="preserve">3.64942908287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59310579299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59807538986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48377156257629</t>
+    <t xml:space="preserve">3.59310531616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59807515144348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48377180099487</t>
   </si>
   <si>
     <t xml:space="preserve">3.38272094726562</t>
@@ -4037,13 +4037,13 @@
     <t xml:space="preserve">2.97686076164246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01993131637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0828812122345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97520422935486</t>
+    <t xml:space="preserve">3.01993155479431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08288097381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97520399093628</t>
   </si>
   <si>
     <t xml:space="preserve">2.96692132949829</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">3.01330518722534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98514342308044</t>
+    <t xml:space="preserve">2.98514366149902</t>
   </si>
   <si>
     <t xml:space="preserve">3.00005269050598</t>
@@ -4073,16 +4073,16 @@
     <t xml:space="preserve">3.00999212265015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89734506607056</t>
+    <t xml:space="preserve">2.89734530448914</t>
   </si>
   <si>
     <t xml:space="preserve">2.90397143363953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90065836906433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69690012931824</t>
+    <t xml:space="preserve">2.90065860748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69689989089966</t>
   </si>
   <si>
     <t xml:space="preserve">2.6587986946106</t>
@@ -4094,7 +4094,7 @@
     <t xml:space="preserve">2.80457711219788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71512246131897</t>
+    <t xml:space="preserve">2.71512222290039</t>
   </si>
   <si>
     <t xml:space="preserve">2.70683932304382</t>
@@ -4103,7 +4103,7 @@
     <t xml:space="preserve">2.69193005561829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52792954444885</t>
+    <t xml:space="preserve">2.52792978286743</t>
   </si>
   <si>
     <t xml:space="preserve">2.64885926246643</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">2.81120347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78138494491577</t>
+    <t xml:space="preserve">2.78138518333435</t>
   </si>
   <si>
     <t xml:space="preserve">2.79132437705994</t>
@@ -4127,22 +4127,22 @@
     <t xml:space="preserve">2.76813244819641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71843552589417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71677851676941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7747585773468</t>
+    <t xml:space="preserve">2.71843528747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71677875518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77475881576538</t>
   </si>
   <si>
     <t xml:space="preserve">2.83108234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83770871162415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84599137306213</t>
+    <t xml:space="preserve">2.83770847320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84599161148071</t>
   </si>
   <si>
     <t xml:space="preserve">2.92385029792786</t>
@@ -4151,7 +4151,7 @@
     <t xml:space="preserve">2.97354745864868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95035576820374</t>
+    <t xml:space="preserve">2.95035552978516</t>
   </si>
   <si>
     <t xml:space="preserve">2.91225433349609</t>
@@ -4163,28 +4163,28 @@
     <t xml:space="preserve">2.93047666549683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98183012008667</t>
+    <t xml:space="preserve">2.98183035850525</t>
   </si>
   <si>
     <t xml:space="preserve">2.98017382621765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92219400405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93544626235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85427451133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75984954833984</t>
+    <t xml:space="preserve">2.92219376564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9354465007782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8542742729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75984978675842</t>
   </si>
   <si>
     <t xml:space="preserve">2.79960751533508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78469800949097</t>
+    <t xml:space="preserve">2.78469824790955</t>
   </si>
   <si>
     <t xml:space="preserve">2.8277690410614</t>
@@ -4199,10 +4199,10 @@
     <t xml:space="preserve">2.68696045875549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69358706474304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64223313331604</t>
+    <t xml:space="preserve">2.69358682632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64223289489746</t>
   </si>
   <si>
     <t xml:space="preserve">2.68199062347412</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">2.73168802261353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83439540863037</t>
+    <t xml:space="preserve">2.83439517021179</t>
   </si>
   <si>
     <t xml:space="preserve">2.79629421234131</t>
@@ -4220,25 +4220,25 @@
     <t xml:space="preserve">2.76150631904602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6803343296051</t>
+    <t xml:space="preserve">2.68033409118652</t>
   </si>
   <si>
     <t xml:space="preserve">2.71015238761902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61738443374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59419250488281</t>
+    <t xml:space="preserve">2.61738467216492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59419226646423</t>
   </si>
   <si>
     <t xml:space="preserve">2.57762670516968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51799011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.536212682724</t>
+    <t xml:space="preserve">2.51798987388611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53621244430542</t>
   </si>
   <si>
     <t xml:space="preserve">2.46663618087769</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">2.44344449043274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37221193313599</t>
+    <t xml:space="preserve">2.37221169471741</t>
   </si>
   <si>
     <t xml:space="preserve">2.4268786907196</t>
@@ -4256,55 +4256,55 @@
     <t xml:space="preserve">2.65051603317261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67702126502991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58259654045105</t>
+    <t xml:space="preserve">2.67702102661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58259630203247</t>
   </si>
   <si>
     <t xml:space="preserve">2.54780840873718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53124260902405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52461624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42190909385681</t>
+    <t xml:space="preserve">2.53124284744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52461647987366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42190885543823</t>
   </si>
   <si>
     <t xml:space="preserve">2.48651528358459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4815456867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54118227958679</t>
+    <t xml:space="preserve">2.48154544830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54118204116821</t>
   </si>
   <si>
     <t xml:space="preserve">2.57100057601929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53952574729919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52295994758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48817157745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59750533103943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62235426902771</t>
+    <t xml:space="preserve">2.53952527046204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52295970916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48817181587219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59750556945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62235403060913</t>
   </si>
   <si>
     <t xml:space="preserve">2.60413193702698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61407113075256</t>
+    <t xml:space="preserve">2.61407136917114</t>
   </si>
   <si>
     <t xml:space="preserve">2.61075806617737</t>
@@ -4313,16 +4313,16 @@
     <t xml:space="preserve">2.61572790145874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68861699104309</t>
+    <t xml:space="preserve">2.68861722946167</t>
   </si>
   <si>
     <t xml:space="preserve">2.84930443763733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86587023735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95366883277893</t>
+    <t xml:space="preserve">2.86587047576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95366859436035</t>
   </si>
   <si>
     <t xml:space="preserve">2.9983959197998</t>
@@ -4331,25 +4331,25 @@
     <t xml:space="preserve">2.99342632293701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03152751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98679995536804</t>
+    <t xml:space="preserve">3.03152775764465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98680019378662</t>
   </si>
   <si>
     <t xml:space="preserve">3.00170922279358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00833559036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98348689079285</t>
+    <t xml:space="preserve">3.00833535194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98348712921143</t>
   </si>
   <si>
     <t xml:space="preserve">3.00336575508118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03484082221985</t>
+    <t xml:space="preserve">3.03484058380127</t>
   </si>
   <si>
     <t xml:space="preserve">3.06631541252136</t>
@@ -4361,16 +4361,16 @@
     <t xml:space="preserve">3.10441660881042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08619475364685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94869875907898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91722393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86255717277527</t>
+    <t xml:space="preserve">3.08619451522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94869899749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91722416877747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86255741119385</t>
   </si>
   <si>
     <t xml:space="preserve">2.89900183677673</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">2.99176979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99673962593079</t>
+    <t xml:space="preserve">2.99673938751221</t>
   </si>
   <si>
     <t xml:space="preserve">3.03649711608887</t>
@@ -4388,16 +4388,16 @@
     <t xml:space="preserve">3.01496195793152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0779116153717</t>
+    <t xml:space="preserve">3.07791137695312</t>
   </si>
   <si>
     <t xml:space="preserve">3.09944701194763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13754844665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19055843353271</t>
+    <t xml:space="preserve">3.13754820823669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19055867195129</t>
   </si>
   <si>
     <t xml:space="preserve">3.16736626625061</t>
@@ -4406,22 +4406,22 @@
     <t xml:space="preserve">3.21375060081482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25185179710388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22865962982178</t>
+    <t xml:space="preserve">3.2518515586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22865986824036</t>
   </si>
   <si>
     <t xml:space="preserve">3.22534656524658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26013445854187</t>
+    <t xml:space="preserve">3.26013469696045</t>
   </si>
   <si>
     <t xml:space="preserve">3.23031640052795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20215439796448</t>
+    <t xml:space="preserve">3.2021541595459</t>
   </si>
   <si>
     <t xml:space="preserve">3.20546746253967</t>
@@ -4439,37 +4439,37 @@
     <t xml:space="preserve">3.29657912254333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34627652168274</t>
+    <t xml:space="preserve">3.34627628326416</t>
   </si>
   <si>
     <t xml:space="preserve">3.32805395126343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34793257713318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37443780899048</t>
+    <t xml:space="preserve">3.34793281555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37443804740906</t>
   </si>
   <si>
     <t xml:space="preserve">3.43904447555542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44235754013062</t>
+    <t xml:space="preserve">3.44235777854919</t>
   </si>
   <si>
     <t xml:space="preserve">3.29160928726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29492259025574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31811451911926</t>
+    <t xml:space="preserve">3.29492235183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31811475753784</t>
   </si>
   <si>
     <t xml:space="preserve">3.25516486167908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35124588012695</t>
+    <t xml:space="preserve">3.35124611854553</t>
   </si>
   <si>
     <t xml:space="preserve">3.45395350456238</t>
@@ -4478,10 +4478,10 @@
     <t xml:space="preserve">3.4506402015686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49536776542664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43573117256165</t>
+    <t xml:space="preserve">3.49536752700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43573093414307</t>
   </si>
   <si>
     <t xml:space="preserve">3.38437747955322</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">3.31480145454407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40922617912292</t>
+    <t xml:space="preserve">3.40922594070435</t>
   </si>
   <si>
     <t xml:space="preserve">3.34958958625793</t>
@@ -4502,10 +4502,10 @@
     <t xml:space="preserve">3.387690782547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39266061782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41088271141052</t>
+    <t xml:space="preserve">3.39266037940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41088247299194</t>
   </si>
   <si>
     <t xml:space="preserve">3.42082214355469</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">3.42247867584229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37609481811523</t>
+    <t xml:space="preserve">3.37609457969666</t>
   </si>
   <si>
     <t xml:space="preserve">3.37775111198425</t>
@@ -4523,25 +4523,25 @@
     <t xml:space="preserve">3.34130644798279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10276007652283</t>
+    <t xml:space="preserve">3.10276031494141</t>
   </si>
   <si>
     <t xml:space="preserve">3.13092184066772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02324461936951</t>
+    <t xml:space="preserve">3.02324485778809</t>
   </si>
   <si>
     <t xml:space="preserve">3.07625508308411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17399263381958</t>
+    <t xml:space="preserve">3.17399287223816</t>
   </si>
   <si>
     <t xml:space="preserve">3.13423490524292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10607314109802</t>
+    <t xml:space="preserve">3.1060733795166</t>
   </si>
   <si>
     <t xml:space="preserve">3.01164865493774</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">3.06465911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10938620567322</t>
+    <t xml:space="preserve">3.1093864440918</t>
   </si>
   <si>
     <t xml:space="preserve">3.07459831237793</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">3.08453774452209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11269927024841</t>
+    <t xml:space="preserve">3.11269950866699</t>
   </si>
   <si>
     <t xml:space="preserve">3.14748764038086</t>
@@ -4568,19 +4568,19 @@
     <t xml:space="preserve">3.17233610153198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17730569839478</t>
+    <t xml:space="preserve">3.17730593681335</t>
   </si>
   <si>
     <t xml:space="preserve">3.18393230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20381116867065</t>
+    <t xml:space="preserve">3.20381093025208</t>
   </si>
   <si>
     <t xml:space="preserve">3.14914417266846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19387149810791</t>
+    <t xml:space="preserve">3.19387173652649</t>
   </si>
   <si>
     <t xml:space="preserve">3.19718480110168</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">3.17896270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14583110809326</t>
+    <t xml:space="preserve">3.14583134651184</t>
   </si>
   <si>
     <t xml:space="preserve">3.09779047966003</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">3.11932587623596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04146671295166</t>
+    <t xml:space="preserve">3.04146695137024</t>
   </si>
   <si>
     <t xml:space="preserve">3.07294201850891</t>
@@ -4610,28 +4610,28 @@
     <t xml:space="preserve">3.08785080909729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.053062915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04974985122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10612893104553</t>
+    <t xml:space="preserve">3.05306315422058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04974961280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10612869262695</t>
   </si>
   <si>
     <t xml:space="preserve">3.05855894088745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96165752410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94403910636902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97751450538635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93523001670837</t>
+    <t xml:space="preserve">2.96165776252747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9440393447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97751426696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93523025512695</t>
   </si>
   <si>
     <t xml:space="preserve">2.90351676940918</t>
@@ -4652,7 +4652,7 @@
     <t xml:space="preserve">2.99513268470764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9968945980072</t>
+    <t xml:space="preserve">2.99689435958862</t>
   </si>
   <si>
     <t xml:space="preserve">3.03741693496704</t>
@@ -4664,7 +4664,7 @@
     <t xml:space="preserve">3.0286078453064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03213143348694</t>
+    <t xml:space="preserve">3.03213119506836</t>
   </si>
   <si>
     <t xml:space="preserve">3.06736826896667</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">3.03565526008606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99865627288818</t>
+    <t xml:space="preserve">2.99865651130676</t>
   </si>
   <si>
     <t xml:space="preserve">2.97575235366821</t>
@@ -4691,7 +4691,7 @@
     <t xml:space="preserve">2.90880250930786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88942193984985</t>
+    <t xml:space="preserve">2.88942217826843</t>
   </si>
   <si>
     <t xml:space="preserve">2.92994451522827</t>
@@ -4712,10 +4712,10 @@
     <t xml:space="preserve">2.86299443244934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88413667678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95284843444824</t>
+    <t xml:space="preserve">2.88413643836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95284867286682</t>
   </si>
   <si>
     <t xml:space="preserve">2.9916090965271</t>
@@ -4736,13 +4736,13 @@
     <t xml:space="preserve">2.93170642852783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00922727584839</t>
+    <t xml:space="preserve">3.00922751426697</t>
   </si>
   <si>
     <t xml:space="preserve">3.11317610740662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12198519706726</t>
+    <t xml:space="preserve">3.12198543548584</t>
   </si>
   <si>
     <t xml:space="preserve">3.08851027488708</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">3.25764727592468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32812118530273</t>
+    <t xml:space="preserve">3.32812094688416</t>
   </si>
   <si>
     <t xml:space="preserve">3.32635927200317</t>
@@ -4778,34 +4778,34 @@
     <t xml:space="preserve">3.2840747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22945761680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23121953010559</t>
+    <t xml:space="preserve">3.22945785522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23121976852417</t>
   </si>
   <si>
     <t xml:space="preserve">3.20655393600464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21712493896484</t>
+    <t xml:space="preserve">3.21712470054626</t>
   </si>
   <si>
     <t xml:space="preserve">3.22593402862549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25412368774414</t>
+    <t xml:space="preserve">3.25412344932556</t>
   </si>
   <si>
     <t xml:space="preserve">3.27526569366455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29112243652344</t>
+    <t xml:space="preserve">3.29112219810486</t>
   </si>
   <si>
     <t xml:space="preserve">3.34397768974304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34750127792358</t>
+    <t xml:space="preserve">3.347501039505</t>
   </si>
   <si>
     <t xml:space="preserve">3.3774528503418</t>
@@ -4820,7 +4820,7 @@
     <t xml:space="preserve">3.29816961288452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32988286018372</t>
+    <t xml:space="preserve">3.32988262176514</t>
   </si>
   <si>
     <t xml:space="preserve">3.39330911636353</t>
@@ -4859,25 +4859,25 @@
     <t xml:space="preserve">3.53954219818115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51487636566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47083020210266</t>
+    <t xml:space="preserve">3.51487612724304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47083044052124</t>
   </si>
   <si>
     <t xml:space="preserve">3.49725794792175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46378302574158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43735504150391</t>
+    <t xml:space="preserve">3.463782787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43735527992249</t>
   </si>
   <si>
     <t xml:space="preserve">3.42502236366272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52897095680237</t>
+    <t xml:space="preserve">3.52897119522095</t>
   </si>
   <si>
     <t xml:space="preserve">3.54130387306213</t>
@@ -4892,16 +4892,16 @@
     <t xml:space="preserve">3.48316311836243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42149877548218</t>
+    <t xml:space="preserve">3.4214985370636</t>
   </si>
   <si>
     <t xml:space="preserve">3.4355936050415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39507126808167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36159586906433</t>
+    <t xml:space="preserve">3.39507102966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36159610748291</t>
   </si>
   <si>
     <t xml:space="preserve">3.37569069862366</t>
@@ -4913,13 +4913,13 @@
     <t xml:space="preserve">3.37216711044312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39683270454407</t>
+    <t xml:space="preserve">3.39683294296265</t>
   </si>
   <si>
     <t xml:space="preserve">3.35278677940369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40388035774231</t>
+    <t xml:space="preserve">3.40388011932373</t>
   </si>
   <si>
     <t xml:space="preserve">3.58535027503967</t>
@@ -4931,25 +4931,25 @@
     <t xml:space="preserve">3.53778004646301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45144987106323</t>
+    <t xml:space="preserve">3.45145010948181</t>
   </si>
   <si>
     <t xml:space="preserve">3.5624463558197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54306554794312</t>
+    <t xml:space="preserve">3.54306578636169</t>
   </si>
   <si>
     <t xml:space="preserve">3.58182644844055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58711171150208</t>
+    <t xml:space="preserve">3.58711194992065</t>
   </si>
   <si>
     <t xml:space="preserve">3.55716061592102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51840019226074</t>
+    <t xml:space="preserve">3.51839995384216</t>
   </si>
   <si>
     <t xml:space="preserve">3.46730661392212</t>
@@ -4958,7 +4958,7 @@
     <t xml:space="preserve">3.4690682888031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4162130355835</t>
+    <t xml:space="preserve">3.41621327400208</t>
   </si>
   <si>
     <t xml:space="preserve">3.40211844444275</t>
@@ -4970,10 +4970,10 @@
     <t xml:space="preserve">3.45497369766235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43383145332336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45849752426147</t>
+    <t xml:space="preserve">3.43383169174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4584972858429</t>
   </si>
   <si>
     <t xml:space="preserve">3.42678427696228</t>
@@ -4997,10 +4997,10 @@
     <t xml:space="preserve">3.5677318572998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5642077922821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55187511444092</t>
+    <t xml:space="preserve">3.56420803070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55187487602234</t>
   </si>
   <si>
     <t xml:space="preserve">3.46554470062256</t>
@@ -5012,7 +5012,7 @@
     <t xml:space="preserve">3.47611594200134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55892252922058</t>
+    <t xml:space="preserve">3.558922290802</t>
   </si>
   <si>
     <t xml:space="preserve">3.5536367893219</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">3.57301735877991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57654094696045</t>
+    <t xml:space="preserve">3.57654070854187</t>
   </si>
   <si>
     <t xml:space="preserve">3.5483512878418</t>
@@ -5039,7 +5039,7 @@
     <t xml:space="preserve">3.73510646820068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69986987113953</t>
+    <t xml:space="preserve">3.69986963272095</t>
   </si>
   <si>
     <t xml:space="preserve">3.80029511451721</t>
@@ -5048,7 +5048,7 @@
     <t xml:space="preserve">3.72277355194092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71396446228027</t>
+    <t xml:space="preserve">3.71396470069885</t>
   </si>
   <si>
     <t xml:space="preserve">3.66815662384033</t>
@@ -5060,7 +5060,7 @@
     <t xml:space="preserve">3.69458413124084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78796195983887</t>
+    <t xml:space="preserve">3.78796219825745</t>
   </si>
   <si>
     <t xml:space="preserve">3.77210545539856</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">3.64701437950134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70867919921875</t>
+    <t xml:space="preserve">3.70867896080017</t>
   </si>
   <si>
     <t xml:space="preserve">3.64172887802124</t>
@@ -5102,79 +5102,79 @@
     <t xml:space="preserve">3.71220302581787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68577527999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67168068885803</t>
+    <t xml:space="preserve">3.6857750415802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67168045043945</t>
   </si>
   <si>
     <t xml:space="preserve">3.65229988098145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65582370758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71748828887939</t>
+    <t xml:space="preserve">3.65582394599915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71748805046082</t>
   </si>
   <si>
     <t xml:space="preserve">3.69634628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63468170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62587261199951</t>
+    <t xml:space="preserve">3.63468146324158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62587237358093</t>
   </si>
   <si>
     <t xml:space="preserve">3.70163178443909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72453594207764</t>
+    <t xml:space="preserve">3.72453570365906</t>
   </si>
   <si>
     <t xml:space="preserve">3.72982144355774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76858139038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81615114212036</t>
+    <t xml:space="preserve">3.76858162879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81615138053894</t>
   </si>
   <si>
     <t xml:space="preserve">3.81967520713806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88133978843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85138845443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83905529975891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87781572341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87605404853821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84610295295715</t>
+    <t xml:space="preserve">3.88133955001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85138869285583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83905553817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87781620025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87605428695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84610271453857</t>
   </si>
   <si>
     <t xml:space="preserve">3.89895820617676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82672262191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77915287017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80205655097961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76329612731934</t>
+    <t xml:space="preserve">3.82672214508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77915263175964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80205678939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76329588890076</t>
   </si>
   <si>
     <t xml:space="preserve">3.74920153617859</t>
@@ -5183,28 +5183,28 @@
     <t xml:space="preserve">3.74039196968079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67344212532043</t>
+    <t xml:space="preserve">3.67344236373901</t>
   </si>
   <si>
     <t xml:space="preserve">3.73158311843872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85843563079834</t>
+    <t xml:space="preserve">3.8584361076355</t>
   </si>
   <si>
     <t xml:space="preserve">3.82496070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81086611747742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88662528991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91833806037903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90071988105774</t>
+    <t xml:space="preserve">3.81086587905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88662552833557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91833829879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90071964263916</t>
   </si>
   <si>
     <t xml:space="preserve">4.06633329391479</t>
@@ -71268,7 +71268,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6910763889</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>71425</v>
@@ -71289,6 +71289,32 @@
         <v>1961</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6911342593</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>136079</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>6.15999984741211</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>6.15500020980835</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1978</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -44,76 +44,76 @@
     <t xml:space="preserve">ANIM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33184671401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13419628143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96948599815369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95301604270935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94203543663025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07380294799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93105506896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82673931121826</t>
+    <t xml:space="preserve">4.33184623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13419532775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96948647499084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95301580429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94203448295593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07380247116089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93105435371399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82673811912537</t>
   </si>
   <si>
     <t xml:space="preserve">3.76085543632507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67850041389465</t>
+    <t xml:space="preserve">3.67850065231323</t>
   </si>
   <si>
     <t xml:space="preserve">3.73889398574829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40398621559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53300762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76909112930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79379725456238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79928755760193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88438749313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67575573921204</t>
+    <t xml:space="preserve">3.40398645401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53300809860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76909065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79379653930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79928660392761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88438773155212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67575550079346</t>
   </si>
   <si>
     <t xml:space="preserve">3.70595240592957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6400682926178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57967495918274</t>
+    <t xml:space="preserve">3.64006853103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57967448234558</t>
   </si>
   <si>
     <t xml:space="preserve">3.35731840133667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45065259933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37653398513794</t>
+    <t xml:space="preserve">3.45065236091614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3765344619751</t>
   </si>
   <si>
     <t xml:space="preserve">3.06633234024048</t>
@@ -122,154 +122,154 @@
     <t xml:space="preserve">2.95652651786804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19535422325134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98397779464722</t>
+    <t xml:space="preserve">3.19535446166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98397755622864</t>
   </si>
   <si>
     <t xml:space="preserve">3.2420220375061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20084476470947</t>
+    <t xml:space="preserve">3.20084452629089</t>
   </si>
   <si>
     <t xml:space="preserve">3.48633980751038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38202428817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31065034866333</t>
+    <t xml:space="preserve">3.38202452659607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31065106391907</t>
   </si>
   <si>
     <t xml:space="preserve">3.3875150680542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2667281627655</t>
+    <t xml:space="preserve">3.26672840118408</t>
   </si>
   <si>
     <t xml:space="preserve">3.1129994392395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08554863929749</t>
+    <t xml:space="preserve">3.08554816246033</t>
   </si>
   <si>
     <t xml:space="preserve">3.07182264328003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06084227561951</t>
+    <t xml:space="preserve">3.06084203720093</t>
   </si>
   <si>
     <t xml:space="preserve">3.15692186355591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30241465568542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43967270851135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35182809829712</t>
+    <t xml:space="preserve">3.302414894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43967294692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35182857513428</t>
   </si>
   <si>
     <t xml:space="preserve">3.28319931030273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22280526161194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25300240516663</t>
+    <t xml:space="preserve">3.22280597686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25300264358521</t>
   </si>
   <si>
     <t xml:space="preserve">3.57692956924438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4726140499115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46437907218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.590656042099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5632050037384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6126172542572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51653671264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43418216705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37104320526123</t>
+    <t xml:space="preserve">3.47261476516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46437931060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59065628051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56320452690125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61261677742004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51653695106506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43418264389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37104392051697</t>
   </si>
   <si>
     <t xml:space="preserve">3.45888876914978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53026247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32986640930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2722179889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09103870391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23653125762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34084749221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28594422340393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31888556480408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23927664756775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42594695091248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41771101951599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40947580337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41496658325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44241762161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4616334438324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44790816307068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49732089042664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39300489425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37378931045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26123762130737</t>
+    <t xml:space="preserve">3.5302631855011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32986664772034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27221775054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09103894233704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23653173446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34084725379944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28594470024109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31888628005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23927593231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42594647407532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41771125793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40947556495667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41496610641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44241738319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46163415908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44790863990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49732065200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39300537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3737895488739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26123809814453</t>
   </si>
   <si>
     <t xml:space="preserve">3.2694730758667</t>
@@ -278,22 +278,22 @@
     <t xml:space="preserve">3.15417742729187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16241216659546</t>
+    <t xml:space="preserve">3.16241240501404</t>
   </si>
   <si>
     <t xml:space="preserve">3.01966524124146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94829058647156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82201409339905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93182015419006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06907796859741</t>
+    <t xml:space="preserve">2.94829130172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82201385498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93181991577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0690770149231</t>
   </si>
   <si>
     <t xml:space="preserve">3.00044870376587</t>
@@ -302,10 +302,10 @@
     <t xml:space="preserve">2.91809415817261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87417197227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85221028327942</t>
+    <t xml:space="preserve">2.87417149543762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85221076011658</t>
   </si>
   <si>
     <t xml:space="preserve">2.89064240455627</t>
@@ -314,76 +314,76 @@
     <t xml:space="preserve">2.97133898735046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06356310844421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23648262023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2422468662262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29988646507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17884278297424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15866899490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0405068397522</t>
+    <t xml:space="preserve">3.06356263160706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23648238182068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24224662780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29988622665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1788432598114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15866875648499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04050707817078</t>
   </si>
   <si>
     <t xml:space="preserve">2.97998476028442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9626932144165</t>
+    <t xml:space="preserve">2.96269297599792</t>
   </si>
   <si>
     <t xml:space="preserve">3.02321481704712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00015950202942</t>
+    <t xml:space="preserve">3.00015902519226</t>
   </si>
   <si>
     <t xml:space="preserve">2.95692849159241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81859278678894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79668974876404</t>
+    <t xml:space="preserve">2.8185932636261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79668998718262</t>
   </si>
   <si>
     <t xml:space="preserve">2.66988158226013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61454725265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54768466949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70331287384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75288367271423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90505313873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92234492301941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96845674514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53615689277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26179122924805</t>
+    <t xml:space="preserve">2.61454749107361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54768538475037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70331263542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75288391113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90505337715149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92234468460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96845698356628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53615713119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26179146766663</t>
   </si>
   <si>
     <t xml:space="preserve">2.49004530906677</t>
@@ -392,34 +392,34 @@
     <t xml:space="preserve">2.41972422599792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4266414642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49235057830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3690013885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28830575942993</t>
+    <t xml:space="preserve">2.42664122581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49235105514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36900115013123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28830552101135</t>
   </si>
   <si>
     <t xml:space="preserve">2.297527551651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30559778213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35747337341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43240547180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61108875274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59379744529724</t>
+    <t xml:space="preserve">2.30559754371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35747313499451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4324049949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61108899116516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59379720687866</t>
   </si>
   <si>
     <t xml:space="preserve">2.68025708198547</t>
@@ -434,37 +434,37 @@
     <t xml:space="preserve">2.56958794593811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62838077545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62261700630188</t>
+    <t xml:space="preserve">2.62838125228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62261724472046</t>
   </si>
   <si>
     <t xml:space="preserve">2.59494996070862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6168532371521</t>
+    <t xml:space="preserve">2.61685371398926</t>
   </si>
   <si>
     <t xml:space="preserve">2.54653239250183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63414525985718</t>
+    <t xml:space="preserve">2.63414549827576</t>
   </si>
   <si>
     <t xml:space="preserve">2.58226919174194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40358519554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41511344909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43816947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55114340782166</t>
+    <t xml:space="preserve">2.4035849571228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41511297225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4381697177887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55114364624023</t>
   </si>
   <si>
     <t xml:space="preserve">2.58572769165039</t>
@@ -473,22 +473,22 @@
     <t xml:space="preserve">2.65143704414368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65489554405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60417246818542</t>
+    <t xml:space="preserve">2.65489506721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.604172706604</t>
   </si>
   <si>
     <t xml:space="preserve">2.54307413101196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41857171058655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37015390396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39321064949036</t>
+    <t xml:space="preserve">2.41857147216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37015414237976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39320993423462</t>
   </si>
   <si>
     <t xml:space="preserve">2.51310157775879</t>
@@ -497,34 +497,34 @@
     <t xml:space="preserve">2.50964260101318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46122527122498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4485445022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50733685493469</t>
+    <t xml:space="preserve">2.4612250328064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44854426383972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50733661651611</t>
   </si>
   <si>
     <t xml:space="preserve">2.50157332420349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49696230888367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51540684700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53039336204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57304716110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6618127822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62722778320312</t>
+    <t xml:space="preserve">2.49696207046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51540732383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53039360046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57304739952087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66181254386902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62722826004028</t>
   </si>
   <si>
     <t xml:space="preserve">2.73789691925049</t>
@@ -533,13 +533,13 @@
     <t xml:space="preserve">2.83012104034424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7909255027771</t>
+    <t xml:space="preserve">2.79092526435852</t>
   </si>
   <si>
     <t xml:space="preserve">2.67449355125427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65604829788208</t>
+    <t xml:space="preserve">2.6560480594635</t>
   </si>
   <si>
     <t xml:space="preserve">2.64797878265381</t>
@@ -548,22 +548,22 @@
     <t xml:space="preserve">2.65720081329346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64567375183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52001786231995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51886510848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49580907821655</t>
+    <t xml:space="preserve">2.64567303657532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52001810073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51886487007141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49580931663513</t>
   </si>
   <si>
     <t xml:space="preserve">2.52117085456848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52462887763977</t>
+    <t xml:space="preserve">2.52462911605835</t>
   </si>
   <si>
     <t xml:space="preserve">2.54192161560059</t>
@@ -572,10 +572,10 @@
     <t xml:space="preserve">2.47275328636169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46929502487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39436292648315</t>
+    <t xml:space="preserve">2.46929526329041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39436316490173</t>
   </si>
   <si>
     <t xml:space="preserve">2.32173705101013</t>
@@ -584,25 +584,25 @@
     <t xml:space="preserve">2.32519507408142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24795770645142</t>
+    <t xml:space="preserve">2.24795794487</t>
   </si>
   <si>
     <t xml:space="preserve">2.26524925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3263475894928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38629293441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44393301010132</t>
+    <t xml:space="preserve">2.32634806632996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38629341125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4439332485199</t>
   </si>
   <si>
     <t xml:space="preserve">2.44623875617981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57074117660522</t>
+    <t xml:space="preserve">2.5707414150238</t>
   </si>
   <si>
     <t xml:space="preserve">2.57996320724487</t>
@@ -611,91 +611,91 @@
     <t xml:space="preserve">2.56267166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55806040763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50387835502625</t>
+    <t xml:space="preserve">2.55806064605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50387859344482</t>
   </si>
   <si>
     <t xml:space="preserve">2.50503158569336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38168239593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60993599891663</t>
+    <t xml:space="preserve">2.38168215751648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60993623733521</t>
   </si>
   <si>
     <t xml:space="preserve">2.59956073760986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55344891548157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70907735824585</t>
+    <t xml:space="preserve">2.55344915390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70907688140869</t>
   </si>
   <si>
     <t xml:space="preserve">2.67910432815552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58111619949341</t>
+    <t xml:space="preserve">2.58111572265625</t>
   </si>
   <si>
     <t xml:space="preserve">2.80130100250244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81282925605774</t>
+    <t xml:space="preserve">2.81282949447632</t>
   </si>
   <si>
     <t xml:space="preserve">2.7229106426239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78285646438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82550978660583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92522692680359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96557426452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91081666946411</t>
+    <t xml:space="preserve">2.78285622596741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82551026344299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92522716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96557450294495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91081690788269</t>
   </si>
   <si>
     <t xml:space="preserve">3.00592255592346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03474283218384</t>
+    <t xml:space="preserve">3.03474259376526</t>
   </si>
   <si>
     <t xml:space="preserve">2.99727654457092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98574876785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94828248023987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93963694572449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97422099113464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9915132522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.014568567276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0318603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16155099868774</t>
+    <t xml:space="preserve">2.98574829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94828271865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93963670730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97422122955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99151277542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01456880569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03186058998108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16155076026917</t>
   </si>
   <si>
     <t xml:space="preserve">3.13849472999573</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">3.11255669593811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12984824180603</t>
+    <t xml:space="preserve">3.12984848022461</t>
   </si>
   <si>
     <t xml:space="preserve">3.20478057861328</t>
@@ -713,88 +713,88 @@
     <t xml:space="preserve">3.16443204879761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19613456726074</t>
+    <t xml:space="preserve">3.19613480567932</t>
   </si>
   <si>
     <t xml:space="preserve">3.1990168094635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12408518791199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14137649536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08373665809631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30276846885681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2624204158783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18748879432678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28547644615173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2278368473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17596054077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2480103969574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26818442344666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23936414718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09238219261169</t>
+    <t xml:space="preserve">3.12408494949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14137625694275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08373713493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30276870727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26242089271545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18748903274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28547668457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22783660888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17596006393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24801015853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2681839466095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23936438560486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09238243103027</t>
   </si>
   <si>
     <t xml:space="preserve">3.10102868080139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0549168586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08085417747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11832046508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15002250671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01168727874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92810893058777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95404720306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78516173362732</t>
+    <t xml:space="preserve">3.05491709709167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08085489273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11832070350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15002274513245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0116868019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92810869216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95404696464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78516149520874</t>
   </si>
   <si>
     <t xml:space="preserve">2.91369867324829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98863124847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00304079055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02609658241272</t>
+    <t xml:space="preserve">2.98863101005554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0030403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0260968208313</t>
   </si>
   <si>
     <t xml:space="preserve">3.07797265052795</t>
@@ -803,16 +803,16 @@
     <t xml:space="preserve">3.05779886245728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18172430992126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17019724845886</t>
+    <t xml:space="preserve">3.18172454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17019701004028</t>
   </si>
   <si>
     <t xml:space="preserve">3.23360061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24512910842896</t>
+    <t xml:space="preserve">3.2451286315918</t>
   </si>
   <si>
     <t xml:space="preserve">3.25089287757874</t>
@@ -821,91 +821,91 @@
     <t xml:space="preserve">3.27106666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27394843101501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28259468078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25665616989136</t>
+    <t xml:space="preserve">3.27394866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28259491920471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2566556930542</t>
   </si>
   <si>
     <t xml:space="preserve">3.18460655212402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29412245750427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10391139984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34023475646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4439868927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43245887756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46416044235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45839619636536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49298000335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44686841964722</t>
+    <t xml:space="preserve">3.29412221908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10391068458557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34023499488831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44398641586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43245816230774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46415996551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45839643478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49298024177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4468686580658</t>
   </si>
   <si>
     <t xml:space="preserve">3.50450873374939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60249638557434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51603674888611</t>
+    <t xml:space="preserve">3.60249614715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51603627204895</t>
   </si>
   <si>
     <t xml:space="preserve">3.46992468833923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44110441207886</t>
+    <t xml:space="preserve">3.44110488891602</t>
   </si>
   <si>
     <t xml:space="preserve">3.42381262779236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41228485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39499258995056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37193584442139</t>
+    <t xml:space="preserve">3.41228461265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39499282836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37193608283997</t>
   </si>
   <si>
     <t xml:space="preserve">3.4893524646759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49236249923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59472560882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72117233276367</t>
+    <t xml:space="preserve">3.49236273765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5947253704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72117280960083</t>
   </si>
   <si>
     <t xml:space="preserve">3.71515154838562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58870363235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4682776927948</t>
+    <t xml:space="preserve">3.58870387077332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46827745437622</t>
   </si>
   <si>
     <t xml:space="preserve">3.41107535362244</t>
@@ -914,163 +914,163 @@
     <t xml:space="preserve">3.49838447570801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54053354263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50440573692322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51644802093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54956579208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70913004875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72418355941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64891695976257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75127983093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72719383239746</t>
+    <t xml:space="preserve">3.54053330421448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50440549850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51644849777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54956555366516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70913052558899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72418403625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64891743659973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75127935409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72719430923462</t>
   </si>
   <si>
     <t xml:space="preserve">3.76332259178162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73923683166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74525809288025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71214079856873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70310926437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75730085372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77536487579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77837514877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84159922599792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85966348648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82654619216919</t>
+    <t xml:space="preserve">3.73923707008362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74525785446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71214127540588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7031090259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75730037689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77536463737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77837491035461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8415994644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85966324806213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82654547691345</t>
   </si>
   <si>
     <t xml:space="preserve">4.09750556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14266443252563</t>
+    <t xml:space="preserve">4.14266538619995</t>
   </si>
   <si>
     <t xml:space="preserve">4.19685697555542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17277240753174</t>
+    <t xml:space="preserve">4.17277193069458</t>
   </si>
   <si>
     <t xml:space="preserve">4.19083595275879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22094202041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.199866771698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2450270652771</t>
+    <t xml:space="preserve">4.22094249725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19986724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24502754211426</t>
   </si>
   <si>
     <t xml:space="preserve">4.26911306381226</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26309108734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21492147445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15470743179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14567565917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.136643409729</t>
+    <t xml:space="preserve">4.26309156417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21492099761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15470790863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14567613601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13664436340332</t>
   </si>
   <si>
     <t xml:space="preserve">4.22395324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22696352005005</t>
+    <t xml:space="preserve">4.22696399688721</t>
   </si>
   <si>
     <t xml:space="preserve">4.33534717559814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25104856491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28717613220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11857986450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25405979156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09449481964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08847284317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04030227661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05234575271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95901417732239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86267304420471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86568403244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94396185874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94697237014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95600414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98009014129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97406816482544</t>
+    <t xml:space="preserve">4.25104904174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28717660903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11857938766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25405931472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09449434280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08847332000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04030275344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05234479904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95901489257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86267328262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86568450927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94396114349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94697260856628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95600438117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98009037971497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9740686416626</t>
   </si>
   <si>
     <t xml:space="preserve">4.07342004776001</t>
@@ -1079,46 +1079,46 @@
     <t xml:space="preserve">4.06438827514648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98912215232849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96202564239502</t>
+    <t xml:space="preserve">3.98912143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96202540397644</t>
   </si>
   <si>
     <t xml:space="preserve">4.01320648193359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03428077697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00417470932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00116443634033</t>
+    <t xml:space="preserve">4.03428173065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00417423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00116395950317</t>
   </si>
   <si>
     <t xml:space="preserve">3.90783381462097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8897705078125</t>
+    <t xml:space="preserve">3.88976955413818</t>
   </si>
   <si>
     <t xml:space="preserve">3.95299363136292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01019620895386</t>
+    <t xml:space="preserve">4.01019668579102</t>
   </si>
   <si>
     <t xml:space="preserve">4.11255788803101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15771865844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06739902496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98611116409302</t>
+    <t xml:space="preserve">4.15771818161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06739807128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98611092567444</t>
   </si>
   <si>
     <t xml:space="preserve">3.93191885948181</t>
@@ -1127,37 +1127,37 @@
     <t xml:space="preserve">3.9018120765686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87471604347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85364151000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82353520393372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579105377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84762096405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83256769180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88073801994324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88374805450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92589783668518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92890882492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88675904273987</t>
+    <t xml:space="preserve">3.87471652030945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8536422252655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82353472709656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579057693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84762048721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83256793022156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88073778152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88374781608582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9258975982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9289083480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88675928115845</t>
   </si>
   <si>
     <t xml:space="preserve">3.9138548374176</t>
@@ -1172,34 +1172,34 @@
     <t xml:space="preserve">3.82052516937256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69106602668762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70611929893494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55558705329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47429895401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33580851554871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40204286575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52246880531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54354429244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53150129318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57365083694458</t>
+    <t xml:space="preserve">3.69106674194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70611977577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55558657646179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47429919242859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33580875396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40204334259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52246952056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54354453086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53150081634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57365036010742</t>
   </si>
   <si>
     <t xml:space="preserve">3.60074663162231</t>
@@ -1208,16 +1208,16 @@
     <t xml:space="preserve">3.5766613483429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53752279281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55257630348206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50139474868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45021390914917</t>
+    <t xml:space="preserve">3.5375235080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55257606506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50139451026917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45021438598633</t>
   </si>
   <si>
     <t xml:space="preserve">3.51042652130127</t>
@@ -1232,37 +1232,37 @@
     <t xml:space="preserve">3.40806460380554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53451204299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60977816581726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35387277603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42612862586975</t>
+    <t xml:space="preserve">3.53451180458069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60977840423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35387229919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42612886428833</t>
   </si>
   <si>
     <t xml:space="preserve">3.44419240951538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32376575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39000129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61278891563416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73020458221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66698050498962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64590668678284</t>
+    <t xml:space="preserve">3.32376551628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39000058174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61278867721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73020434379578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66698026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64590716362</t>
   </si>
   <si>
     <t xml:space="preserve">3.63386392593384</t>
@@ -1271,19 +1271,19 @@
     <t xml:space="preserve">3.81450319290161</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86869549751282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93492984771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04331398010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99213171005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98310017585754</t>
+    <t xml:space="preserve">3.86869525909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93492937088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04331302642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99213194847107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98310041427612</t>
   </si>
   <si>
     <t xml:space="preserve">4.06137704849243</t>
@@ -1292,103 +1292,103 @@
     <t xml:space="preserve">4.12460136413574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16072940826416</t>
+    <t xml:space="preserve">4.16072845458984</t>
   </si>
   <si>
     <t xml:space="preserve">4.07040882110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08245134353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80848217010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89880156517029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91987633705139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78439664840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77235436439514</t>
+    <t xml:space="preserve">4.08245277404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80848264694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8988025188446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91987657546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78439617156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77235460281372</t>
   </si>
   <si>
     <t xml:space="preserve">3.79945015907288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73622608184814</t>
+    <t xml:space="preserve">3.73622560501099</t>
   </si>
   <si>
     <t xml:space="preserve">3.75429058074951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76633238792419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63988518714905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56160807609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66999197006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96503663063049</t>
+    <t xml:space="preserve">3.76633310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63988447189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56160831451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6699914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96503686904907</t>
   </si>
   <si>
     <t xml:space="preserve">3.79342937469482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74224734306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79164958000183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77612209320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78854417800903</t>
+    <t xml:space="preserve">3.74224758148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79164934158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77612233161926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7885434627533</t>
   </si>
   <si>
     <t xml:space="preserve">3.70469903945923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58358955383301</t>
+    <t xml:space="preserve">3.58358979225159</t>
   </si>
   <si>
     <t xml:space="preserve">3.55914282798767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55258893966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51326084136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61157965660095</t>
+    <t xml:space="preserve">3.55258798599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51326131820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61158013343811</t>
   </si>
   <si>
     <t xml:space="preserve">3.58536124229431</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76888966560364</t>
+    <t xml:space="preserve">3.76888990402222</t>
   </si>
   <si>
     <t xml:space="preserve">3.89998173713684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342713356018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85082244873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81149506568909</t>
+    <t xml:space="preserve">3.89342641830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85082197189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81149482727051</t>
   </si>
   <si>
     <t xml:space="preserve">3.63779807090759</t>
@@ -1397,40 +1397,40 @@
     <t xml:space="preserve">3.75578045845032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73939442634583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86065435409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099102020264</t>
+    <t xml:space="preserve">3.73939418792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86065459251404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099078178406</t>
   </si>
   <si>
     <t xml:space="preserve">3.81804919242859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9655282497406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98846864700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93275499343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86720895767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84426784515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.913090467453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82132697105408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03107357025146</t>
+    <t xml:space="preserve">3.96552777290344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98846840858459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93275451660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86720871925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84426760673523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91309070587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82132649421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03107309341431</t>
   </si>
   <si>
     <t xml:space="preserve">4.04418325424194</t>
@@ -1439,121 +1439,121 @@
     <t xml:space="preserve">4.02451848983765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98191380500793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90653657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99830102920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77544450759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76561260223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71973037719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71645379066467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56897497177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50670576095581</t>
+    <t xml:space="preserve">3.98191404342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90653681755066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99830055236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77544474601746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76561307907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71973085403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71645283699036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56897521018982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50670623779297</t>
   </si>
   <si>
     <t xml:space="preserve">3.46737909317017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27467346191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93645668029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03477573394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19077491760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42149662971497</t>
+    <t xml:space="preserve">3.27467370033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93645691871643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03477597236633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19077515602112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42149639129639</t>
   </si>
   <si>
     <t xml:space="preserve">3.41494178771973</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33628678321838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31662273406982</t>
+    <t xml:space="preserve">3.33628726005554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31662344932556</t>
   </si>
   <si>
     <t xml:space="preserve">3.35595059394836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21174955368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30023622512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32645487785339</t>
+    <t xml:space="preserve">3.21175003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30023694038391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32645463943481</t>
   </si>
   <si>
     <t xml:space="preserve">3.39855551719666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33956408500671</t>
+    <t xml:space="preserve">3.33956384658813</t>
   </si>
   <si>
     <t xml:space="preserve">3.29040479660034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27729535102844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28057289123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18290972709656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12260699272156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07148122787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01511144638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89975094795227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01904511451721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01380109786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0491955280304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97971701622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02690982818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13440561294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10425400733948</t>
+    <t xml:space="preserve">3.2772958278656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28057312965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18290948867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12260770797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07148146629333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01511192321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89975070953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01904463768005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01380133628845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04919576644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97971749305725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02691006660461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13440537452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10425424575806</t>
   </si>
   <si>
     <t xml:space="preserve">3.04264140129089</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">3.00200271606445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00462460517883</t>
+    <t xml:space="preserve">3.00462436676025</t>
   </si>
   <si>
     <t xml:space="preserve">2.98233890533447</t>
@@ -1577,19 +1577,19 @@
     <t xml:space="preserve">2.92728042602539</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00069189071655</t>
+    <t xml:space="preserve">3.00069212913513</t>
   </si>
   <si>
     <t xml:space="preserve">3.01249003410339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03739714622498</t>
+    <t xml:space="preserve">3.0373969078064</t>
   </si>
   <si>
     <t xml:space="preserve">2.95612072944641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92465829849243</t>
+    <t xml:space="preserve">2.92465877532959</t>
   </si>
   <si>
     <t xml:space="preserve">2.84469246864319</t>
@@ -1598,16 +1598,16 @@
     <t xml:space="preserve">2.97709488868713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00724601745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89057469367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77259230613708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79487776756287</t>
+    <t xml:space="preserve">3.00724649429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89057445526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77259182929993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79487729072571</t>
   </si>
   <si>
     <t xml:space="preserve">2.73064255714417</t>
@@ -1625,172 +1625,172 @@
     <t xml:space="preserve">2.76997017860413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73719763755798</t>
+    <t xml:space="preserve">2.7371973991394</t>
   </si>
   <si>
     <t xml:space="preserve">2.7214663028717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69000434875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63625645637512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64936542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.620525598526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67689490318298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7201554775238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87615466117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85124731063843</t>
+    <t xml:space="preserve">2.6900041103363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63625597953796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64936566352844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62052536010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67689514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72015523910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87615442276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85124707221985</t>
   </si>
   <si>
     <t xml:space="preserve">2.86697816848755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93907880783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91154956817627</t>
+    <t xml:space="preserve">2.93907904624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91154909133911</t>
   </si>
   <si>
     <t xml:space="preserve">2.91679263114929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92596983909607</t>
+    <t xml:space="preserve">2.92596960067749</t>
   </si>
   <si>
     <t xml:space="preserve">2.94170045852661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99807000160217</t>
+    <t xml:space="preserve">2.99806976318359</t>
   </si>
   <si>
     <t xml:space="preserve">3.04133033752441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99675917625427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99413704872131</t>
+    <t xml:space="preserve">2.99675869941711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99413752555847</t>
   </si>
   <si>
     <t xml:space="preserve">2.96267509460449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96005296707153</t>
+    <t xml:space="preserve">2.96005344390869</t>
   </si>
   <si>
     <t xml:space="preserve">2.91286015510559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77521395683289</t>
+    <t xml:space="preserve">2.77521371841431</t>
   </si>
   <si>
     <t xml:space="preserve">2.70704650878906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6886932849884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.705735206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74244093894958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64674377441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64150023460388</t>
+    <t xml:space="preserve">2.68869352340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70573472976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74244070053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64674401283264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64150047302246</t>
   </si>
   <si>
     <t xml:space="preserve">2.59692883491516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38193845748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46714782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44879508018494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49074482917786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47108101844788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.486811876297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4199550151825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31639266014099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25871205329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20365333557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25215768814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28493046760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38587117195129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39242577552795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42519879341125</t>
+    <t xml:space="preserve">2.38193869590759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46714806556702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44879555702209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49074459075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4710807800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48681163787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41995477676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31639242172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25871229171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20365357398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25215744972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28493022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38587164878845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39242553710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42519855499268</t>
   </si>
   <si>
     <t xml:space="preserve">2.45928263664246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54973602294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4723916053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44617366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45797157287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47501349449158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54842519760132</t>
+    <t xml:space="preserve">2.5497362613678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47239184379578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44617342948914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4579713344574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47501373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54842495918274</t>
   </si>
   <si>
     <t xml:space="preserve">2.43044233322144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40815687179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33998870849609</t>
+    <t xml:space="preserve">2.40815663337708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33998894691467</t>
   </si>
   <si>
     <t xml:space="preserve">2.28886342048645</t>
@@ -1799,43 +1799,43 @@
     <t xml:space="preserve">2.27968692779541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25740122795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17612409591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18661141395569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13155293464661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29410696029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35178709030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766931533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44748425483704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42388796806335</t>
+    <t xml:space="preserve">2.25740098953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17612385749817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18661165237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13155341148376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29410719871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35178732872009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766955375671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44748449325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42388772964478</t>
   </si>
   <si>
     <t xml:space="preserve">2.40946769714355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40029096603394</t>
+    <t xml:space="preserve">2.40029144287109</t>
   </si>
   <si>
     <t xml:space="preserve">2.21938467025757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19447731971741</t>
+    <t xml:space="preserve">2.19447708129883</t>
   </si>
   <si>
     <t xml:space="preserve">2.25477957725525</t>
@@ -1844,10 +1844,10 @@
     <t xml:space="preserve">2.31901431083679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32687997817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26264476776123</t>
+    <t xml:space="preserve">2.32687973976135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26264500617981</t>
   </si>
   <si>
     <t xml:space="preserve">2.17743515968323</t>
@@ -1856,31 +1856,31 @@
     <t xml:space="preserve">2.12893104553223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14597296714783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12237668037415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12368726730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10271263122559</t>
+    <t xml:space="preserve">2.14597320556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12237644195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12368774414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10271286964417</t>
   </si>
   <si>
     <t xml:space="preserve">2.11713290214539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14728426933289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15121674537659</t>
+    <t xml:space="preserve">2.14728403091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15121698379517</t>
   </si>
   <si>
     <t xml:space="preserve">2.23904824256897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20758628845215</t>
+    <t xml:space="preserve">2.20758652687073</t>
   </si>
   <si>
     <t xml:space="preserve">2.36489653587341</t>
@@ -1889,22 +1889,22 @@
     <t xml:space="preserve">2.34785485267639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37407302856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25084686279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39504742622375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35572004318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41340041160583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43306398391724</t>
+    <t xml:space="preserve">2.37407255172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25084662437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39504766464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35572028160095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41340065002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43306422233582</t>
   </si>
   <si>
     <t xml:space="preserve">2.44486260414124</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">2.35309815406799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34654331207275</t>
+    <t xml:space="preserve">2.34654355049133</t>
   </si>
   <si>
     <t xml:space="preserve">2.35440897941589</t>
@@ -1934,16 +1934,16 @@
     <t xml:space="preserve">2.28755211830139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26788878440857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31114888191223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37931656837463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40291285514832</t>
+    <t xml:space="preserve">2.26788830757141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31114864349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37931680679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40291309356689</t>
   </si>
   <si>
     <t xml:space="preserve">2.4055347442627</t>
@@ -1952,19 +1952,19 @@
     <t xml:space="preserve">2.37014007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33605623245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39898037910461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37669491767883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5012321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54318189620972</t>
+    <t xml:space="preserve">2.33605599403381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39898061752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37669467926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50123167037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54318141937256</t>
   </si>
   <si>
     <t xml:space="preserve">2.52613949775696</t>
@@ -1982,19 +1982,19 @@
     <t xml:space="preserve">2.39635848999023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38718199729919</t>
+    <t xml:space="preserve">2.38718223571777</t>
   </si>
   <si>
     <t xml:space="preserve">2.37276196479797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37800574302673</t>
+    <t xml:space="preserve">2.37800550460815</t>
   </si>
   <si>
     <t xml:space="preserve">2.33867812156677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29935050010681</t>
+    <t xml:space="preserve">2.29935026168823</t>
   </si>
   <si>
     <t xml:space="preserve">2.38062739372253</t>
@@ -2003,13 +2003,13 @@
     <t xml:space="preserve">2.30459427833557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38849329948425</t>
+    <t xml:space="preserve">2.38849282264709</t>
   </si>
   <si>
     <t xml:space="preserve">2.45666074752808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40160226821899</t>
+    <t xml:space="preserve">2.40160250663757</t>
   </si>
   <si>
     <t xml:space="preserve">2.34130001068115</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">2.38324952125549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32556891441345</t>
+    <t xml:space="preserve">2.32556915283203</t>
   </si>
   <si>
     <t xml:space="preserve">2.30328321456909</t>
@@ -2033,16 +2033,16 @@
     <t xml:space="preserve">2.34523272514343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32425785064697</t>
+    <t xml:space="preserve">2.32425832748413</t>
   </si>
   <si>
     <t xml:space="preserve">2.30983805656433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21545147895813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19054436683655</t>
+    <t xml:space="preserve">2.21545195579529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19054412841797</t>
   </si>
   <si>
     <t xml:space="preserve">2.09091472625732</t>
@@ -2051,94 +2051,94 @@
     <t xml:space="preserve">2.08698177337646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99783957004547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03978896141052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9768648147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99128460884094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97817552089691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98996245861053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99967014789581</t>
+    <t xml:space="preserve">1.99783945083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03978848457336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97686457633972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99128472805023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97817540168762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98996293544769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9996702671051</t>
   </si>
   <si>
     <t xml:space="preserve">1.97470891475677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94420075416565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91923928260803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89843845367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86377012729645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82632851600647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87625074386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87902426719666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83742213249207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95113408565521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92755997180939</t>
+    <t xml:space="preserve">1.94420051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91923952102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89843833446503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86377000808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82632863521576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87625086307526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87902390956879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83742249011993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9511342048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92755973339081</t>
   </si>
   <si>
     <t xml:space="preserve">1.89982521533966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92062640190125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90953254699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90675866603851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88734436035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88873112201691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88179790973663</t>
+    <t xml:space="preserve">1.92062628269196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90953230857849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90675914287567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88734471797943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88873147964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88179755210876</t>
   </si>
   <si>
     <t xml:space="preserve">2.02879166603088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98302912712097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03156495094299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98857605457306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95945477485657</t>
+    <t xml:space="preserve">1.98302924633026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03156518936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98857629299164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95945453643799</t>
   </si>
   <si>
     <t xml:space="preserve">2.00660371780396</t>
@@ -2147,34 +2147,34 @@
     <t xml:space="preserve">2.00521683692932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07178020477295</t>
+    <t xml:space="preserve">2.07177996635437</t>
   </si>
   <si>
     <t xml:space="preserve">2.0939679145813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14943718910217</t>
+    <t xml:space="preserve">2.14943742752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.22709441184998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25344204902649</t>
+    <t xml:space="preserve">2.25344228744507</t>
   </si>
   <si>
     <t xml:space="preserve">2.25898909568787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26453638076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21461343765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21184039115906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24928188323975</t>
+    <t xml:space="preserve">2.26453614234924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21461391448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21184062957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24928212165833</t>
   </si>
   <si>
     <t xml:space="preserve">2.3144588470459</t>
@@ -2183,13 +2183,13 @@
     <t xml:space="preserve">2.30059146881104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30891156196594</t>
+    <t xml:space="preserve">2.30891180038452</t>
   </si>
   <si>
     <t xml:space="preserve">2.31307172775269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27424311637878</t>
+    <t xml:space="preserve">2.27424335479736</t>
   </si>
   <si>
     <t xml:space="preserve">2.2215473651886</t>
@@ -2198,34 +2198,34 @@
     <t xml:space="preserve">2.24789547920227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24650859832764</t>
+    <t xml:space="preserve">2.24650883674622</t>
   </si>
   <si>
     <t xml:space="preserve">2.24512195587158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28811073303223</t>
+    <t xml:space="preserve">2.28811049461365</t>
   </si>
   <si>
     <t xml:space="preserve">2.32277894020081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37824821472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30613827705383</t>
+    <t xml:space="preserve">2.37824845314026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30613803863525</t>
   </si>
   <si>
     <t xml:space="preserve">2.23125457763672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18687915802002</t>
+    <t xml:space="preserve">2.18687891960144</t>
   </si>
   <si>
     <t xml:space="preserve">2.17162489891052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17439842224121</t>
+    <t xml:space="preserve">2.17439818382263</t>
   </si>
   <si>
     <t xml:space="preserve">2.22432088851929</t>
@@ -2237,13 +2237,13 @@
     <t xml:space="preserve">2.10783529281616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1286358833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09812831878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1272497177124</t>
+    <t xml:space="preserve">2.12863612174988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09812808036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12724947929382</t>
   </si>
   <si>
     <t xml:space="preserve">2.17717218399048</t>
@@ -2252,67 +2252,67 @@
     <t xml:space="preserve">2.19103932380676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2368016242981</t>
+    <t xml:space="preserve">2.23680114746094</t>
   </si>
   <si>
     <t xml:space="preserve">2.20629334449768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19935941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18549251556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25760245323181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25621581077576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23957514762878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35606050491333</t>
+    <t xml:space="preserve">2.19935965538025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18549227714539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25760269165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25621557235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23957490921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35606074333191</t>
   </si>
   <si>
     <t xml:space="preserve">2.38102173805237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36715459823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38379549980164</t>
+    <t xml:space="preserve">2.3671543598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38379526138306</t>
   </si>
   <si>
     <t xml:space="preserve">2.43510460853577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51553535461426</t>
+    <t xml:space="preserve">2.5155348777771</t>
   </si>
   <si>
     <t xml:space="preserve">2.49889421463013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42955756187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42817068099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44897198677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45867872238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3976628780365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3879554271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37131476402283</t>
+    <t xml:space="preserve">2.42955732345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42817091941833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44897150993347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45867896080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38795518875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37131452560425</t>
   </si>
   <si>
     <t xml:space="preserve">2.382408618927</t>
@@ -2321,31 +2321,31 @@
     <t xml:space="preserve">2.41707682609558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42401051521301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37408828735352</t>
+    <t xml:space="preserve">2.42401075363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37408804893494</t>
   </si>
   <si>
     <t xml:space="preserve">2.32693910598755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2992045879364</t>
+    <t xml:space="preserve">2.29920434951782</t>
   </si>
   <si>
     <t xml:space="preserve">2.31723189353943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34496641159058</t>
+    <t xml:space="preserve">2.34496665000916</t>
   </si>
   <si>
     <t xml:space="preserve">2.34635353088379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41153001785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46977281570435</t>
+    <t xml:space="preserve">2.41153025627136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46977305412292</t>
   </si>
   <si>
     <t xml:space="preserve">2.48502707481384</t>
@@ -2363,19 +2363,19 @@
     <t xml:space="preserve">2.73879909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70690441131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74711918830872</t>
+    <t xml:space="preserve">2.70690417289734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74711942672729</t>
   </si>
   <si>
     <t xml:space="preserve">2.72770524024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75266647338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76237344741821</t>
+    <t xml:space="preserve">2.75266671180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76237368583679</t>
   </si>
   <si>
     <t xml:space="preserve">2.7859480381012</t>
@@ -2384,16 +2384,16 @@
     <t xml:space="preserve">2.77208065986633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69581007957458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70413064956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72077202796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80120205879211</t>
+    <t xml:space="preserve">2.69581031799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70413088798523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7207715511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80120229721069</t>
   </si>
   <si>
     <t xml:space="preserve">2.78733468055725</t>
@@ -2402,19 +2402,19 @@
     <t xml:space="preserve">2.82893681526184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85528469085693</t>
+    <t xml:space="preserve">2.85528492927551</t>
   </si>
   <si>
     <t xml:space="preserve">2.9468092918396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01614618301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02723979949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04804062843323</t>
+    <t xml:space="preserve">3.01614570617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02724003791809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04804086685181</t>
   </si>
   <si>
     <t xml:space="preserve">3.0799355506897</t>
@@ -2423,19 +2423,19 @@
     <t xml:space="preserve">3.13679194450378</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14649868011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17562031745911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14511179924011</t>
+    <t xml:space="preserve">3.14649891853333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17562007904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14511203765869</t>
   </si>
   <si>
     <t xml:space="preserve">3.23108959197998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24773025512695</t>
+    <t xml:space="preserve">3.24773049354553</t>
   </si>
   <si>
     <t xml:space="preserve">3.26298427581787</t>
@@ -2453,13 +2453,13 @@
     <t xml:space="preserve">3.18394088745117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2560510635376</t>
+    <t xml:space="preserve">3.25605082511902</t>
   </si>
   <si>
     <t xml:space="preserve">3.21028876304626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25327730178833</t>
+    <t xml:space="preserve">3.25327754020691</t>
   </si>
   <si>
     <t xml:space="preserve">3.22831630706787</t>
@@ -2474,19 +2474,19 @@
     <t xml:space="preserve">3.26575779914856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21306180953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19919490814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20890212059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22415614128113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19087481498718</t>
+    <t xml:space="preserve">3.21306157112122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19919466972351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20890188217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22415590286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1908745765686</t>
   </si>
   <si>
     <t xml:space="preserve">3.20335483551025</t>
@@ -2498,133 +2498,133 @@
     <t xml:space="preserve">3.09241628646851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14788579940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20612835884094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17839384078979</t>
+    <t xml:space="preserve">3.1478853225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2061288356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17839360237122</t>
   </si>
   <si>
     <t xml:space="preserve">3.17145991325378</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03694701194763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15343260765076</t>
+    <t xml:space="preserve">3.03694677352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1534321308136</t>
   </si>
   <si>
     <t xml:space="preserve">3.16868686676025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97038388252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.035560131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14095187187195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12985801696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14927244186401</t>
+    <t xml:space="preserve">2.970383644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03555965423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14095211029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12985825538635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14927196502686</t>
   </si>
   <si>
     <t xml:space="preserve">3.17007327079773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12708497047424</t>
+    <t xml:space="preserve">3.12708449363708</t>
   </si>
   <si>
     <t xml:space="preserve">3.10073661804199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07854914665222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11044406890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0896430015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28239917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34202837944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34896159172058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93987512588501</t>
+    <t xml:space="preserve">3.07854866981506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11044383049011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08964252471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28239893913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34202814102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34896183013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93987536430359</t>
   </si>
   <si>
     <t xml:space="preserve">2.97315716743469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.863605260849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73741221427917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58487153053284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55159020423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49473404884338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29227089881897</t>
+    <t xml:space="preserve">2.86360549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73741245269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58487176895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55158996582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49473428726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29227113723755</t>
   </si>
   <si>
     <t xml:space="preserve">2.07039356231689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95668148994446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99134981632233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69042837619781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78472626209259</t>
+    <t xml:space="preserve">1.95668137073517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99134945869446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69042813777924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7847261428833</t>
   </si>
   <si>
     <t xml:space="preserve">1.65576016902924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52818059921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4103080034256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48519194126129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49489879608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60583770275116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67933464050293</t>
+    <t xml:space="preserve">1.52818048000336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41030824184418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.485191822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49489891529083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60583782196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67933440208435</t>
   </si>
   <si>
     <t xml:space="preserve">1.67656099796295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72648346424103</t>
+    <t xml:space="preserve">1.72648358345032</t>
   </si>
   <si>
     <t xml:space="preserve">1.68904185295105</t>
@@ -2633,88 +2633,88 @@
     <t xml:space="preserve">1.69736194610596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72371029853821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75421810150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78888654708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02185750007629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06207323074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05375242233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99412298202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609555721283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96638810634613</t>
+    <t xml:space="preserve">1.72371006011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75421833992004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78888642787933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02185773849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06207299232483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05375289916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99412274360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609531879425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.966388463974</t>
   </si>
   <si>
     <t xml:space="preserve">1.94142735004425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85960984230042</t>
+    <t xml:space="preserve">1.85960972309113</t>
   </si>
   <si>
     <t xml:space="preserve">1.86793041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92339944839478</t>
+    <t xml:space="preserve">1.92339992523193</t>
   </si>
   <si>
     <t xml:space="preserve">1.90121209621429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1480507850647</t>
+    <t xml:space="preserve">2.14805054664612</t>
   </si>
   <si>
     <t xml:space="preserve">2.26730966567993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23818778991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22570729255676</t>
+    <t xml:space="preserve">2.23818826675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22570753097534</t>
   </si>
   <si>
     <t xml:space="preserve">2.13418340682983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28117680549622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35744714736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40043568611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3435800075531</t>
+    <t xml:space="preserve">2.28117728233337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35744738578796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40043616294861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34358048439026</t>
   </si>
   <si>
     <t xml:space="preserve">2.30752491950989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48411726951599</t>
+    <t xml:space="preserve">2.48411750793457</t>
   </si>
   <si>
     <t xml:space="preserve">2.51219487190247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49150633811951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49741744995117</t>
+    <t xml:space="preserve">2.49150609970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49741768836975</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456218719482</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">2.57130527496338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72647047042847</t>
+    <t xml:space="preserve">2.72647023200989</t>
   </si>
   <si>
     <t xml:space="preserve">2.75750350952148</t>
@@ -2732,16 +2732,16 @@
     <t xml:space="preserve">2.80774712562561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86538004875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87572407722473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86833548545837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97473454475403</t>
+    <t xml:space="preserve">2.86537981033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87572431564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86833524703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97473430633545</t>
   </si>
   <si>
     <t xml:space="preserve">3.20230960845947</t>
@@ -2750,19 +2750,19 @@
     <t xml:space="preserve">3.16979885101318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14024353027344</t>
+    <t xml:space="preserve">3.14024376869202</t>
   </si>
   <si>
     <t xml:space="preserve">2.93483448028564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9363124370575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94222378730774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99837851524353</t>
+    <t xml:space="preserve">2.93631267547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94222354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99837875366211</t>
   </si>
   <si>
     <t xml:space="preserve">3.00281190872192</t>
@@ -2780,25 +2780,25 @@
     <t xml:space="preserve">2.83582472801208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89050149917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88459134101868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85946893692017</t>
+    <t xml:space="preserve">2.89050197601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88459086418152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85946869850159</t>
   </si>
   <si>
     <t xml:space="preserve">2.82843589782715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86242437362671</t>
+    <t xml:space="preserve">2.86242461204529</t>
   </si>
   <si>
     <t xml:space="preserve">2.93779015541077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99542307853699</t>
+    <t xml:space="preserve">2.99542284011841</t>
   </si>
   <si>
     <t xml:space="preserve">3.03236722946167</t>
@@ -2816,16 +2816,16 @@
     <t xml:space="preserve">2.93040156364441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97916746139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98212289810181</t>
+    <t xml:space="preserve">2.97916769981384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98212313652039</t>
   </si>
   <si>
     <t xml:space="preserve">2.99394536018372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98951196670532</t>
+    <t xml:space="preserve">2.98951172828674</t>
   </si>
   <si>
     <t xml:space="preserve">2.95404553413391</t>
@@ -2834,13 +2834,13 @@
     <t xml:space="preserve">2.95552325248718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94665694236755</t>
+    <t xml:space="preserve">2.94665670394897</t>
   </si>
   <si>
     <t xml:space="preserve">3.03384470939636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09591054916382</t>
+    <t xml:space="preserve">3.0959107875824</t>
   </si>
   <si>
     <t xml:space="preserve">3.01758933067322</t>
@@ -2849,37 +2849,37 @@
     <t xml:space="preserve">2.99098968505859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93335700035095</t>
+    <t xml:space="preserve">2.93335723876953</t>
   </si>
   <si>
     <t xml:space="preserve">2.91857933998108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75602555274963</t>
+    <t xml:space="preserve">2.75602579116821</t>
   </si>
   <si>
     <t xml:space="preserve">2.81365823745728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85503554344177</t>
+    <t xml:space="preserve">2.85503578186035</t>
   </si>
   <si>
     <t xml:space="preserve">2.85355806350708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.894935131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87720203399658</t>
+    <t xml:space="preserve">2.89493536949158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.877201795578</t>
   </si>
   <si>
     <t xml:space="preserve">2.92153477668762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96291208267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91266822814941</t>
+    <t xml:space="preserve">2.9629123210907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91266846656799</t>
   </si>
   <si>
     <t xml:space="preserve">2.87424683570862</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">2.84616899490356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80479168891907</t>
+    <t xml:space="preserve">2.80479192733765</t>
   </si>
   <si>
     <t xml:space="preserve">2.76784777641296</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">2.79888081550598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74863696098328</t>
+    <t xml:space="preserve">2.7486367225647</t>
   </si>
   <si>
     <t xml:space="preserve">2.7752366065979</t>
@@ -2930,7 +2930,7 @@
     <t xml:space="preserve">2.74272561073303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75454759597778</t>
+    <t xml:space="preserve">2.75454783439636</t>
   </si>
   <si>
     <t xml:space="preserve">2.74715900421143</t>
@@ -2942,37 +2942,37 @@
     <t xml:space="preserve">2.70873713493347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7072594165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61268281936646</t>
+    <t xml:space="preserve">2.70725965499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61268258094788</t>
   </si>
   <si>
     <t xml:space="preserve">2.57573866844177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52549505233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54174995422363</t>
+    <t xml:space="preserve">2.52549481391907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54175019264221</t>
   </si>
   <si>
     <t xml:space="preserve">2.53436136245728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58460521697998</t>
+    <t xml:space="preserve">2.5846049785614</t>
   </si>
   <si>
     <t xml:space="preserve">2.52697229385376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47525095939636</t>
+    <t xml:space="preserve">2.47525072097778</t>
   </si>
   <si>
     <t xml:space="preserve">2.50037288665771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43091797828674</t>
+    <t xml:space="preserve">2.43091821670532</t>
   </si>
   <si>
     <t xml:space="preserve">2.52992796897888</t>
@@ -2981,10 +2981,10 @@
     <t xml:space="preserve">2.6112048625946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54618334770203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55209445953369</t>
+    <t xml:space="preserve">2.54618358612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55209469795227</t>
   </si>
   <si>
     <t xml:space="preserve">2.67179322242737</t>
@@ -2996,70 +2996,70 @@
     <t xml:space="preserve">2.54322791099548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52845001220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47377300262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62893795967102</t>
+    <t xml:space="preserve">2.52845025062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47377324104309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6289381980896</t>
   </si>
   <si>
     <t xml:space="preserve">2.6570155620575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63632678985596</t>
+    <t xml:space="preserve">2.63632702827454</t>
   </si>
   <si>
     <t xml:space="preserve">2.60677170753479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53140592575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52253937721252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36441898345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31713032722473</t>
+    <t xml:space="preserve">2.53140616416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52253913879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36441850662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31713008880615</t>
   </si>
   <si>
     <t xml:space="preserve">2.37180733680725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51662802696228</t>
+    <t xml:space="preserve">2.51662826538086</t>
   </si>
   <si>
     <t xml:space="preserve">2.58312773704529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64223790168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4929838180542</t>
+    <t xml:space="preserve">2.64223766326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49298405647278</t>
   </si>
   <si>
     <t xml:space="preserve">2.615638256073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6525821685791</t>
+    <t xml:space="preserve">2.65258240699768</t>
   </si>
   <si>
     <t xml:space="preserve">2.63041567802429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71317076683044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72794818878174</t>
+    <t xml:space="preserve">2.71317028999329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72794795036316</t>
   </si>
   <si>
     <t xml:space="preserve">2.74568104743958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83139157295227</t>
+    <t xml:space="preserve">2.83139109611511</t>
   </si>
   <si>
     <t xml:space="preserve">2.79149174690247</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">2.78853631019592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75898146629333</t>
+    <t xml:space="preserve">2.75898122787476</t>
   </si>
   <si>
     <t xml:space="preserve">2.68361520767212</t>
@@ -3080,31 +3080,31 @@
     <t xml:space="preserve">2.66440415382385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64519357681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68066000938416</t>
+    <t xml:space="preserve">2.64519333839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.680659532547</t>
   </si>
   <si>
     <t xml:space="preserve">2.64962673187256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68213748931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62598252296448</t>
+    <t xml:space="preserve">2.68213772773743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6259822845459</t>
   </si>
   <si>
     <t xml:space="preserve">2.65849351882935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72055912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85651302337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92301273345947</t>
+    <t xml:space="preserve">2.7205593585968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85651326179504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92301249504089</t>
   </si>
   <si>
     <t xml:space="preserve">2.90380167961121</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">2.90084600448608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98064517974854</t>
+    <t xml:space="preserve">2.98064541816711</t>
   </si>
   <si>
     <t xml:space="preserve">3.01463389396667</t>
@@ -3122,19 +3122,19 @@
     <t xml:space="preserve">3.03975582122803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07374405860901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11807703971863</t>
+    <t xml:space="preserve">3.07374429702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11807727813721</t>
   </si>
   <si>
     <t xml:space="preserve">3.06044459342957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02350044250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02941155433655</t>
+    <t xml:space="preserve">3.0235002040863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02941131591797</t>
   </si>
   <si>
     <t xml:space="preserve">2.89345741271973</t>
@@ -3143,13 +3143,13 @@
     <t xml:space="preserve">2.86390233039856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90675735473633</t>
+    <t xml:space="preserve">2.90675711631775</t>
   </si>
   <si>
     <t xml:space="preserve">2.87129092216492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83434700965881</t>
+    <t xml:space="preserve">2.83434677124023</t>
   </si>
   <si>
     <t xml:space="preserve">2.91710162162781</t>
@@ -3164,31 +3164,31 @@
     <t xml:space="preserve">3.10034418106079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1771879196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1062548160553</t>
+    <t xml:space="preserve">3.17718744277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10625505447388</t>
   </si>
   <si>
     <t xml:space="preserve">3.13581037521362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08408832550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00133395195007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9451789855957</t>
+    <t xml:space="preserve">3.08408856391907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00133419036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94517922401428</t>
   </si>
   <si>
     <t xml:space="preserve">2.9998562335968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97177863121033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93926811218262</t>
+    <t xml:space="preserve">2.97177839279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93926787376404</t>
   </si>
   <si>
     <t xml:space="preserve">3.08999991416931</t>
@@ -3200,31 +3200,31 @@
     <t xml:space="preserve">3.07669997215271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08704447746277</t>
+    <t xml:space="preserve">3.08704423904419</t>
   </si>
   <si>
     <t xml:space="preserve">3.08852195739746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12694358825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24664258956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20526480674744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21856498718262</t>
+    <t xml:space="preserve">3.12694334983826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24664235115051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20526504516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21856474876404</t>
   </si>
   <si>
     <t xml:space="preserve">3.33235263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33826398849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34121918678284</t>
+    <t xml:space="preserve">3.33826375007629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34121894836426</t>
   </si>
   <si>
     <t xml:space="preserve">3.31166386604309</t>
@@ -3233,16 +3233,16 @@
     <t xml:space="preserve">3.26142024993896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32496404647827</t>
+    <t xml:space="preserve">3.32496380805969</t>
   </si>
   <si>
     <t xml:space="preserve">3.30131959915161</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2924530506134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28801918029785</t>
+    <t xml:space="preserve">3.29245281219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28801941871643</t>
   </si>
   <si>
     <t xml:space="preserve">3.31609725952148</t>
@@ -3251,10 +3251,10 @@
     <t xml:space="preserve">3.29393100738525</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27324199676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24516487121582</t>
+    <t xml:space="preserve">3.27324223518372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2451651096344</t>
   </si>
   <si>
     <t xml:space="preserve">3.32274723052979</t>
@@ -3263,19 +3263,19 @@
     <t xml:space="preserve">3.30649185180664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31018614768982</t>
+    <t xml:space="preserve">3.3101863861084</t>
   </si>
   <si>
     <t xml:space="preserve">3.29540872573853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25107598304749</t>
+    <t xml:space="preserve">3.25107550621033</t>
   </si>
   <si>
     <t xml:space="preserve">3.28358626365662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28654217720032</t>
+    <t xml:space="preserve">3.28654193878174</t>
   </si>
   <si>
     <t xml:space="preserve">3.27915358543396</t>
@@ -3284,13 +3284,13 @@
     <t xml:space="preserve">3.24073147773743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27767515182495</t>
+    <t xml:space="preserve">3.27767539024353</t>
   </si>
   <si>
     <t xml:space="preserve">3.28136968612671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18531489372253</t>
+    <t xml:space="preserve">3.18531513214111</t>
   </si>
   <si>
     <t xml:space="preserve">3.13433265686035</t>
@@ -3302,31 +3302,31 @@
     <t xml:space="preserve">3.16314911842346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13507127761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17940425872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09664940834045</t>
+    <t xml:space="preserve">3.13507151603699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17940449714661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09664964675903</t>
   </si>
   <si>
     <t xml:space="preserve">3.15354347229004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13654899597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21043705940247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2651150226593</t>
+    <t xml:space="preserve">3.1365487575531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21043729782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26511478424072</t>
   </si>
   <si>
     <t xml:space="preserve">3.2274317741394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.239253282547</t>
+    <t xml:space="preserve">3.23925352096558</t>
   </si>
   <si>
     <t xml:space="preserve">3.24738121032715</t>
@@ -3344,25 +3344,25 @@
     <t xml:space="preserve">3.3205304145813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32939696311951</t>
+    <t xml:space="preserve">3.32939720153809</t>
   </si>
   <si>
     <t xml:space="preserve">3.31535816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38761711120605</t>
+    <t xml:space="preserve">3.38761758804321</t>
   </si>
   <si>
     <t xml:space="preserve">3.31846618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.337890625</t>
+    <t xml:space="preserve">3.33789086341858</t>
   </si>
   <si>
     <t xml:space="preserve">3.33322882652283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33944463729858</t>
+    <t xml:space="preserve">3.33944487571716</t>
   </si>
   <si>
     <t xml:space="preserve">3.33633685112</t>
@@ -3371,103 +3371,103 @@
     <t xml:space="preserve">3.41325736045837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.377516746521</t>
+    <t xml:space="preserve">3.37751650810242</t>
   </si>
   <si>
     <t xml:space="preserve">3.40471076965332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60206246376038</t>
+    <t xml:space="preserve">3.60206270217896</t>
   </si>
   <si>
     <t xml:space="preserve">3.64868140220642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57098388671875</t>
+    <t xml:space="preserve">3.57098364830017</t>
   </si>
   <si>
     <t xml:space="preserve">3.55855202674866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52203416824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51037979125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44200539588928</t>
+    <t xml:space="preserve">3.52203369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51037955284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44200563430786</t>
   </si>
   <si>
     <t xml:space="preserve">3.47619271278381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4497754573822</t>
+    <t xml:space="preserve">3.44977521896362</t>
   </si>
   <si>
     <t xml:space="preserve">3.38917112350464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3402214050293</t>
+    <t xml:space="preserve">3.34022164344788</t>
   </si>
   <si>
     <t xml:space="preserve">3.32545924186707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34876847267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27417874336243</t>
+    <t xml:space="preserve">3.34876823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27417898178101</t>
   </si>
   <si>
     <t xml:space="preserve">3.29904174804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25630807876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26407837867737</t>
+    <t xml:space="preserve">3.25630831718445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26407790184021</t>
   </si>
   <si>
     <t xml:space="preserve">3.24776148796082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27884030342102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25786185264587</t>
+    <t xml:space="preserve">3.2788405418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25786209106445</t>
   </si>
   <si>
     <t xml:space="preserve">3.24076867103577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19337320327759</t>
+    <t xml:space="preserve">3.19337344169617</t>
   </si>
   <si>
     <t xml:space="preserve">3.25009250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28738737106323</t>
+    <t xml:space="preserve">3.28738713264465</t>
   </si>
   <si>
     <t xml:space="preserve">3.27184772491455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24620771408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20580458641052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16540217399597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02632331848145</t>
+    <t xml:space="preserve">3.24620747566223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2058048248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16540193557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02632308006287</t>
   </si>
   <si>
     <t xml:space="preserve">3.03098511695862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0915892124176</t>
+    <t xml:space="preserve">3.09158945083618</t>
   </si>
   <si>
     <t xml:space="preserve">3.11956024169922</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">3.19570398330688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21202063560486</t>
+    <t xml:space="preserve">3.21202039718628</t>
   </si>
   <si>
     <t xml:space="preserve">3.22989130020142</t>
@@ -3491,22 +3491,22 @@
     <t xml:space="preserve">3.23066806793213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3145809173584</t>
+    <t xml:space="preserve">3.31458139419556</t>
   </si>
   <si>
     <t xml:space="preserve">3.23299884796143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28894114494324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30370354652405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37907028198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33556032180786</t>
+    <t xml:space="preserve">3.28894090652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30370378494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.379070520401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3355598449707</t>
   </si>
   <si>
     <t xml:space="preserve">3.38606309890747</t>
@@ -3515,43 +3515,43 @@
     <t xml:space="preserve">3.33245182037354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31302762031555</t>
+    <t xml:space="preserve">3.31302738189697</t>
   </si>
   <si>
     <t xml:space="preserve">3.33478260040283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36119985580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34954500198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36819267272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3650848865509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39227914810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41248059272766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37207746505737</t>
+    <t xml:space="preserve">3.36120009422302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34954524040222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36819291114807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36508464813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39227938652039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41248083114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37207770347595</t>
   </si>
   <si>
     <t xml:space="preserve">3.39150190353394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39849472045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35032200813293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35343027114868</t>
+    <t xml:space="preserve">3.39849495887756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35032224655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3534300327301</t>
   </si>
   <si>
     <t xml:space="preserve">3.31535863876343</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">3.34721446037292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32157421112061</t>
+    <t xml:space="preserve">3.32157444953918</t>
   </si>
   <si>
     <t xml:space="preserve">3.33089804649353</t>
@@ -3572,34 +3572,34 @@
     <t xml:space="preserve">3.28971815109253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18715739250183</t>
+    <t xml:space="preserve">3.18715763092041</t>
   </si>
   <si>
     <t xml:space="preserve">3.19725775718689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2928261756897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28661036491394</t>
+    <t xml:space="preserve">3.29282569885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28661012649536</t>
   </si>
   <si>
     <t xml:space="preserve">3.22056722640991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21745920181274</t>
+    <t xml:space="preserve">3.21745944023132</t>
   </si>
   <si>
     <t xml:space="preserve">3.21279764175415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20891261100769</t>
+    <t xml:space="preserve">3.20891308784485</t>
   </si>
   <si>
     <t xml:space="preserve">3.17627954483032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30758833885193</t>
+    <t xml:space="preserve">3.30758881568909</t>
   </si>
   <si>
     <t xml:space="preserve">3.33012080192566</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">3.36741590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39461016654968</t>
+    <t xml:space="preserve">3.39460968971252</t>
   </si>
   <si>
     <t xml:space="preserve">3.32623624801636</t>
@@ -3617,19 +3617,19 @@
     <t xml:space="preserve">3.43268179893494</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4544370174408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48085427284241</t>
+    <t xml:space="preserve">3.45443725585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48085451126099</t>
   </si>
   <si>
     <t xml:space="preserve">3.50183296203613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61682510375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5779767036438</t>
+    <t xml:space="preserve">3.61682558059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57797622680664</t>
   </si>
   <si>
     <t xml:space="preserve">3.58652329444885</t>
@@ -3641,37 +3641,37 @@
     <t xml:space="preserve">3.5958468914032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57176041603088</t>
+    <t xml:space="preserve">3.57176089286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.57642245292664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56632161140442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58108448982239</t>
+    <t xml:space="preserve">3.566321849823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58108496665955</t>
   </si>
   <si>
     <t xml:space="preserve">3.68753004074097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63469576835632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65178918838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64246582984924</t>
+    <t xml:space="preserve">3.63469552993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65178894996643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64246535301208</t>
   </si>
   <si>
     <t xml:space="preserve">3.62071013450623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62692618370056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62148690223694</t>
+    <t xml:space="preserve">3.62692594528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62148714065552</t>
   </si>
   <si>
     <t xml:space="preserve">3.61294054985046</t>
@@ -3680,19 +3680,19 @@
     <t xml:space="preserve">3.61060929298401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57409119606018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50260972976685</t>
+    <t xml:space="preserve">3.57409167289734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50260996818542</t>
   </si>
   <si>
     <t xml:space="preserve">3.4482216835022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45132946968079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39694118499756</t>
+    <t xml:space="preserve">3.45132899284363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39694094657898</t>
   </si>
   <si>
     <t xml:space="preserve">3.3953869342804</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">3.26330089569092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22833728790283</t>
+    <t xml:space="preserve">3.22833704948425</t>
   </si>
   <si>
     <t xml:space="preserve">3.23999166488647</t>
@@ -3710,28 +3710,28 @@
     <t xml:space="preserve">3.40004897117615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33711385726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3658618927002</t>
+    <t xml:space="preserve">3.33711361885071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36586141586304</t>
   </si>
   <si>
     <t xml:space="preserve">3.37363171577454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41791939735413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43656659126282</t>
+    <t xml:space="preserve">3.41791963577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4365668296814</t>
   </si>
   <si>
     <t xml:space="preserve">3.31380438804626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.420250415802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42957401275635</t>
+    <t xml:space="preserve">3.42025017738342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42957425117493</t>
   </si>
   <si>
     <t xml:space="preserve">3.4816312789917</t>
@@ -3740,13 +3740,13 @@
     <t xml:space="preserve">3.4971706867218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48707032203674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48862361907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51814889907837</t>
+    <t xml:space="preserve">3.48707008361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48862385749817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51814913749695</t>
   </si>
   <si>
     <t xml:space="preserve">3.54145860671997</t>
@@ -3755,19 +3755,19 @@
     <t xml:space="preserve">3.52436494827271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48551654815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49794769287109</t>
+    <t xml:space="preserve">3.48551630973816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49794745445251</t>
   </si>
   <si>
     <t xml:space="preserve">3.64635038375854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70151567459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69607663154602</t>
+    <t xml:space="preserve">3.70151615142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6960768699646</t>
   </si>
   <si>
     <t xml:space="preserve">3.64712738990784</t>
@@ -3782,16 +3782,16 @@
     <t xml:space="preserve">3.52824974060059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49639415740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35420727729797</t>
+    <t xml:space="preserve">3.49639391899109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35420680046082</t>
   </si>
   <si>
     <t xml:space="preserve">3.40237998962402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4109263420105</t>
+    <t xml:space="preserve">3.41092658042908</t>
   </si>
   <si>
     <t xml:space="preserve">3.41558837890625</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">3.48240828514099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49017834663391</t>
+    <t xml:space="preserve">3.49017810821533</t>
   </si>
   <si>
     <t xml:space="preserve">3.47075366973877</t>
@@ -3812,73 +3812,73 @@
     <t xml:space="preserve">3.45366048812866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54301261901855</t>
+    <t xml:space="preserve">3.54301238059998</t>
   </si>
   <si>
     <t xml:space="preserve">3.56321382522583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75978899002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62614870071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79708385467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7512423992157</t>
+    <t xml:space="preserve">3.75978922843933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62614846229553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79708361625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75124216079712</t>
   </si>
   <si>
     <t xml:space="preserve">3.65878200531006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66188931465149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54612040519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55622124671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38373208045959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42258167266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16384816169739</t>
+    <t xml:space="preserve">3.66188979148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54612016677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55622148513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38373231887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4225811958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16384768486023</t>
   </si>
   <si>
     <t xml:space="preserve">3.06361818313599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87481284141541</t>
+    <t xml:space="preserve">2.87481260299683</t>
   </si>
   <si>
     <t xml:space="preserve">2.63395023345947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59898614883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6471586227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83751773834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7450578212738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8204243183136</t>
+    <t xml:space="preserve">2.59898638725281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64715886116028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83751797676086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74505758285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82042455673218</t>
   </si>
   <si>
     <t xml:space="preserve">2.93308615684509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91366171836853</t>
+    <t xml:space="preserve">2.91366147994995</t>
   </si>
   <si>
     <t xml:space="preserve">3.0783805847168</t>
@@ -3887,22 +3887,22 @@
     <t xml:space="preserve">3.05118656158447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05895590782166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06284093856812</t>
+    <t xml:space="preserve">3.05895614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06284117698669</t>
   </si>
   <si>
     <t xml:space="preserve">3.1622941493988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14131569862366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10246706008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09780502319336</t>
+    <t xml:space="preserve">3.14131593704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10246682167053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09780478477478</t>
   </si>
   <si>
     <t xml:space="preserve">3.13199210166931</t>
@@ -3911,13 +3911,13 @@
     <t xml:space="preserve">3.23843789100647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24853873252869</t>
+    <t xml:space="preserve">3.24853849411011</t>
   </si>
   <si>
     <t xml:space="preserve">3.17161750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20269680023193</t>
+    <t xml:space="preserve">3.20269703865051</t>
   </si>
   <si>
     <t xml:space="preserve">3.09236621856689</t>
@@ -3926,61 +3926,61 @@
     <t xml:space="preserve">3.35498428344727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36275410652161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37984752655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40937232971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42335796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53058099746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59273910522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51970314979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52747297286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5974006652832</t>
+    <t xml:space="preserve">3.36275386810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37984728813171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40937256813049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42335820198059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53058075904846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59273934364319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51970362663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52747273445129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59740114212036</t>
   </si>
   <si>
     <t xml:space="preserve">3.6113862991333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6937460899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63624906539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60983228683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36430788040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30059576034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38140153884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46686863899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51659560203552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53524303436279</t>
+    <t xml:space="preserve">3.69374632835388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63624954223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6098325252533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36430811882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30059599876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38140177726746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46686887741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51659536361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53524279594421</t>
   </si>
   <si>
     <t xml:space="preserve">3.55078268051147</t>
@@ -3992,40 +3992,40 @@
     <t xml:space="preserve">3.51193332672119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6394898891449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63783311843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65771198272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71403551101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70740866661072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7587628364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71569228172302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64611625671387</t>
+    <t xml:space="preserve">3.63948941230774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6378333568573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65771150588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71403574943542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70740914344788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75876307487488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71569180488586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64611577987671</t>
   </si>
   <si>
     <t xml:space="preserve">3.64942908287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59310531616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59807515144348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48377180099487</t>
+    <t xml:space="preserve">3.59310555458069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59807538986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48377156257629</t>
   </si>
   <si>
     <t xml:space="preserve">3.38272094726562</t>
@@ -4040,7 +4040,7 @@
     <t xml:space="preserve">3.01993155479431</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08288097381592</t>
+    <t xml:space="preserve">3.0828812122345</t>
   </si>
   <si>
     <t xml:space="preserve">2.97520399093628</t>
@@ -4055,10 +4055,10 @@
     <t xml:space="preserve">2.98514366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00005269050598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96195149421692</t>
+    <t xml:space="preserve">3.0000524520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96195125579834</t>
   </si>
   <si>
     <t xml:space="preserve">3.05968928337097</t>
@@ -4067,22 +4067,22 @@
     <t xml:space="preserve">3.03318405151367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04809331893921</t>
+    <t xml:space="preserve">3.04809308052063</t>
   </si>
   <si>
     <t xml:space="preserve">3.00999212265015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89734530448914</t>
+    <t xml:space="preserve">2.89734482765198</t>
   </si>
   <si>
     <t xml:space="preserve">2.90397143363953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90065860748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69689989089966</t>
+    <t xml:space="preserve">2.90065836906433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69690012931824</t>
   </si>
   <si>
     <t xml:space="preserve">2.6587986946106</t>
@@ -4100,16 +4100,16 @@
     <t xml:space="preserve">2.70683932304382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69193005561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52792978286743</t>
+    <t xml:space="preserve">2.69193029403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52792954444885</t>
   </si>
   <si>
     <t xml:space="preserve">2.64885926246643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71346545219421</t>
+    <t xml:space="preserve">2.71346569061279</t>
   </si>
   <si>
     <t xml:space="preserve">2.81120347976685</t>
@@ -4127,19 +4127,19 @@
     <t xml:space="preserve">2.76813244819641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71843528747559</t>
+    <t xml:space="preserve">2.71843552589417</t>
   </si>
   <si>
     <t xml:space="preserve">2.71677875518799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77475881576538</t>
+    <t xml:space="preserve">2.7747585773468</t>
   </si>
   <si>
     <t xml:space="preserve">2.83108234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83770847320557</t>
+    <t xml:space="preserve">2.83770871162415</t>
   </si>
   <si>
     <t xml:space="preserve">2.84599161148071</t>
@@ -4166,13 +4166,13 @@
     <t xml:space="preserve">2.98183035850525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98017382621765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92219376564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9354465007782</t>
+    <t xml:space="preserve">2.98017406463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92219400405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93544602394104</t>
   </si>
   <si>
     <t xml:space="preserve">2.8542742729187</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">2.79960751533508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78469824790955</t>
+    <t xml:space="preserve">2.78469800949097</t>
   </si>
   <si>
     <t xml:space="preserve">2.8277690410614</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">2.69358682632446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64223289489746</t>
+    <t xml:space="preserve">2.64223313331604</t>
   </si>
   <si>
     <t xml:space="preserve">2.68199062347412</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">2.73168802261353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83439517021179</t>
+    <t xml:space="preserve">2.83439540863037</t>
   </si>
   <si>
     <t xml:space="preserve">2.79629421234131</t>
@@ -4220,22 +4220,22 @@
     <t xml:space="preserve">2.76150631904602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68033409118652</t>
+    <t xml:space="preserve">2.6803343296051</t>
   </si>
   <si>
     <t xml:space="preserve">2.71015238761902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61738467216492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59419226646423</t>
+    <t xml:space="preserve">2.61738443374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59419250488281</t>
   </si>
   <si>
     <t xml:space="preserve">2.57762670516968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51798987388611</t>
+    <t xml:space="preserve">2.51799011230469</t>
   </si>
   <si>
     <t xml:space="preserve">2.53621244430542</t>
@@ -4244,28 +4244,28 @@
     <t xml:space="preserve">2.46663618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44344449043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37221169471741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4268786907196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65051603317261</t>
+    <t xml:space="preserve">2.44344425201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37221193313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42687892913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65051579475403</t>
   </si>
   <si>
     <t xml:space="preserve">2.67702102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58259630203247</t>
+    <t xml:space="preserve">2.58259654045105</t>
   </si>
   <si>
     <t xml:space="preserve">2.54780840873718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53124284744263</t>
+    <t xml:space="preserve">2.53124260902405</t>
   </si>
   <si>
     <t xml:space="preserve">2.52461647987366</t>
@@ -4277,25 +4277,25 @@
     <t xml:space="preserve">2.48651528358459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48154544830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54118204116821</t>
+    <t xml:space="preserve">2.4815456867218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54118227958679</t>
   </si>
   <si>
     <t xml:space="preserve">2.57100057601929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53952527046204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52295970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48817181587219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59750556945801</t>
+    <t xml:space="preserve">2.53952574729919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52295994758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48817157745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59750533103943</t>
   </si>
   <si>
     <t xml:space="preserve">2.62235403060913</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">2.60413193702698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61407136917114</t>
+    <t xml:space="preserve">2.61407113075256</t>
   </si>
   <si>
     <t xml:space="preserve">2.61075806617737</t>
@@ -4313,49 +4313,49 @@
     <t xml:space="preserve">2.61572790145874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68861722946167</t>
+    <t xml:space="preserve">2.68861699104309</t>
   </si>
   <si>
     <t xml:space="preserve">2.84930443763733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86587047576904</t>
+    <t xml:space="preserve">2.86587023735046</t>
   </si>
   <si>
     <t xml:space="preserve">2.95366859436035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9983959197998</t>
+    <t xml:space="preserve">2.99839615821838</t>
   </si>
   <si>
     <t xml:space="preserve">2.99342632293701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03152775764465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98680019378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00170922279358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00833535194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98348712921143</t>
+    <t xml:space="preserve">3.03152751922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98679995536804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00170946121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00833559036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98348665237427</t>
   </si>
   <si>
     <t xml:space="preserve">3.00336575508118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03484058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06631541252136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04478001594543</t>
+    <t xml:space="preserve">3.03484082221985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06631565093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04478025436401</t>
   </si>
   <si>
     <t xml:space="preserve">3.10441660881042</t>
@@ -4364,13 +4364,13 @@
     <t xml:space="preserve">3.08619451522827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94869899749756</t>
+    <t xml:space="preserve">2.94869875907898</t>
   </si>
   <si>
     <t xml:space="preserve">2.91722416877747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86255741119385</t>
+    <t xml:space="preserve">2.86255717277527</t>
   </si>
   <si>
     <t xml:space="preserve">2.89900183677673</t>
@@ -4388,16 +4388,16 @@
     <t xml:space="preserve">3.01496195793152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07791137695312</t>
+    <t xml:space="preserve">3.0779116153717</t>
   </si>
   <si>
     <t xml:space="preserve">3.09944701194763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13754820823669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19055867195129</t>
+    <t xml:space="preserve">3.13754844665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19055843353271</t>
   </si>
   <si>
     <t xml:space="preserve">3.16736626625061</t>
@@ -4409,19 +4409,19 @@
     <t xml:space="preserve">3.2518515586853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22865986824036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22534656524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26013469696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23031640052795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2021541595459</t>
+    <t xml:space="preserve">3.22865962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.225346326828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26013445854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23031616210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20215463638306</t>
   </si>
   <si>
     <t xml:space="preserve">3.20546746253967</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">3.18724536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23528575897217</t>
+    <t xml:space="preserve">3.23528599739075</t>
   </si>
   <si>
     <t xml:space="preserve">3.2816698551178</t>
@@ -4457,19 +4457,19 @@
     <t xml:space="preserve">3.44235777854919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29160928726196</t>
+    <t xml:space="preserve">3.29160952568054</t>
   </si>
   <si>
     <t xml:space="preserve">3.29492235183716</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31811475753784</t>
+    <t xml:space="preserve">3.31811451911926</t>
   </si>
   <si>
     <t xml:space="preserve">3.25516486167908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35124611854553</t>
+    <t xml:space="preserve">3.35124588012695</t>
   </si>
   <si>
     <t xml:space="preserve">3.45395350456238</t>
@@ -4478,7 +4478,7 @@
     <t xml:space="preserve">3.4506402015686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49536752700806</t>
+    <t xml:space="preserve">3.49536776542664</t>
   </si>
   <si>
     <t xml:space="preserve">3.43573093414307</t>
@@ -4490,13 +4490,13 @@
     <t xml:space="preserve">3.31480145454407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40922594070435</t>
+    <t xml:space="preserve">3.40922617912292</t>
   </si>
   <si>
     <t xml:space="preserve">3.34958958625793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38106417655945</t>
+    <t xml:space="preserve">3.38106393814087</t>
   </si>
   <si>
     <t xml:space="preserve">3.387690782547</t>
@@ -4505,10 +4505,10 @@
     <t xml:space="preserve">3.39266037940979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41088247299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42082214355469</t>
+    <t xml:space="preserve">3.41088271141052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42082238197327</t>
   </si>
   <si>
     <t xml:space="preserve">3.42247867584229</t>
@@ -4517,13 +4517,13 @@
     <t xml:space="preserve">3.37609457969666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37775111198425</t>
+    <t xml:space="preserve">3.37775135040283</t>
   </si>
   <si>
     <t xml:space="preserve">3.34130644798279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10276031494141</t>
+    <t xml:space="preserve">3.10276007652283</t>
   </si>
   <si>
     <t xml:space="preserve">3.13092184066772</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">3.07625508308411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17399287223816</t>
+    <t xml:space="preserve">3.17399263381958</t>
   </si>
   <si>
     <t xml:space="preserve">3.13423490524292</t>
@@ -4547,19 +4547,19 @@
     <t xml:space="preserve">3.01164865493774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06465911865234</t>
+    <t xml:space="preserve">3.06465888023376</t>
   </si>
   <si>
     <t xml:space="preserve">3.1093864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07459831237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08453774452209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11269950866699</t>
+    <t xml:space="preserve">3.07459807395935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08453798294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11269927024841</t>
   </si>
   <si>
     <t xml:space="preserve">3.14748764038086</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">3.17233610153198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17730593681335</t>
+    <t xml:space="preserve">3.17730569839478</t>
   </si>
   <si>
     <t xml:space="preserve">3.18393230438232</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">3.14914417266846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19387173652649</t>
+    <t xml:space="preserve">3.19387149810791</t>
   </si>
   <si>
     <t xml:space="preserve">3.19718480110168</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">3.17896270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14583134651184</t>
+    <t xml:space="preserve">3.14583110809326</t>
   </si>
   <si>
     <t xml:space="preserve">3.09779047966003</t>
@@ -4607,31 +4607,31 @@
     <t xml:space="preserve">3.0514063835144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08785080909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05306315422058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04974961280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10612869262695</t>
+    <t xml:space="preserve">3.08785104751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.053062915802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04974985122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10612893104553</t>
   </si>
   <si>
     <t xml:space="preserve">3.05855894088745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96165776252747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9440393447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97751426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93523025512695</t>
+    <t xml:space="preserve">2.96165752410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94403910636902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97751450538635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93523001670837</t>
   </si>
   <si>
     <t xml:space="preserve">2.90351676940918</t>
@@ -4652,7 +4652,7 @@
     <t xml:space="preserve">2.99513268470764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99689435958862</t>
+    <t xml:space="preserve">2.9968945980072</t>
   </si>
   <si>
     <t xml:space="preserve">3.03741693496704</t>
@@ -4664,7 +4664,7 @@
     <t xml:space="preserve">3.0286078453064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03213119506836</t>
+    <t xml:space="preserve">3.03213143348694</t>
   </si>
   <si>
     <t xml:space="preserve">3.06736826896667</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">3.03565526008606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99865651130676</t>
+    <t xml:space="preserve">2.99865627288818</t>
   </si>
   <si>
     <t xml:space="preserve">2.97575235366821</t>
@@ -4691,7 +4691,7 @@
     <t xml:space="preserve">2.90880250930786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88942217826843</t>
+    <t xml:space="preserve">2.88942193984985</t>
   </si>
   <si>
     <t xml:space="preserve">2.92994451522827</t>
@@ -4712,10 +4712,10 @@
     <t xml:space="preserve">2.86299443244934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88413643836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95284867286682</t>
+    <t xml:space="preserve">2.88413667678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95284843444824</t>
   </si>
   <si>
     <t xml:space="preserve">2.9916090965271</t>
@@ -4736,13 +4736,13 @@
     <t xml:space="preserve">2.93170642852783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00922751426697</t>
+    <t xml:space="preserve">3.00922727584839</t>
   </si>
   <si>
     <t xml:space="preserve">3.11317610740662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12198543548584</t>
+    <t xml:space="preserve">3.12198519706726</t>
   </si>
   <si>
     <t xml:space="preserve">3.08851027488708</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">3.25764727592468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32812094688416</t>
+    <t xml:space="preserve">3.32812118530273</t>
   </si>
   <si>
     <t xml:space="preserve">3.32635927200317</t>
@@ -4778,34 +4778,34 @@
     <t xml:space="preserve">3.2840747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22945785522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23121976852417</t>
+    <t xml:space="preserve">3.22945761680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23121953010559</t>
   </si>
   <si>
     <t xml:space="preserve">3.20655393600464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21712470054626</t>
+    <t xml:space="preserve">3.21712493896484</t>
   </si>
   <si>
     <t xml:space="preserve">3.22593402862549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25412344932556</t>
+    <t xml:space="preserve">3.25412368774414</t>
   </si>
   <si>
     <t xml:space="preserve">3.27526569366455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29112219810486</t>
+    <t xml:space="preserve">3.29112243652344</t>
   </si>
   <si>
     <t xml:space="preserve">3.34397768974304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.347501039505</t>
+    <t xml:space="preserve">3.34750127792358</t>
   </si>
   <si>
     <t xml:space="preserve">3.3774528503418</t>
@@ -4820,7 +4820,7 @@
     <t xml:space="preserve">3.29816961288452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32988262176514</t>
+    <t xml:space="preserve">3.32988286018372</t>
   </si>
   <si>
     <t xml:space="preserve">3.39330911636353</t>
@@ -4859,25 +4859,25 @@
     <t xml:space="preserve">3.53954219818115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51487612724304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47083044052124</t>
+    <t xml:space="preserve">3.51487636566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47083020210266</t>
   </si>
   <si>
     <t xml:space="preserve">3.49725794792175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.463782787323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43735527992249</t>
+    <t xml:space="preserve">3.46378302574158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43735504150391</t>
   </si>
   <si>
     <t xml:space="preserve">3.42502236366272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52897119522095</t>
+    <t xml:space="preserve">3.52897095680237</t>
   </si>
   <si>
     <t xml:space="preserve">3.54130387306213</t>
@@ -4892,16 +4892,16 @@
     <t xml:space="preserve">3.48316311836243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4214985370636</t>
+    <t xml:space="preserve">3.42149877548218</t>
   </si>
   <si>
     <t xml:space="preserve">3.4355936050415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39507102966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36159610748291</t>
+    <t xml:space="preserve">3.39507126808167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36159586906433</t>
   </si>
   <si>
     <t xml:space="preserve">3.37569069862366</t>
@@ -4913,13 +4913,13 @@
     <t xml:space="preserve">3.37216711044312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39683294296265</t>
+    <t xml:space="preserve">3.39683270454407</t>
   </si>
   <si>
     <t xml:space="preserve">3.35278677940369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40388011932373</t>
+    <t xml:space="preserve">3.40388035774231</t>
   </si>
   <si>
     <t xml:space="preserve">3.58535027503967</t>
@@ -4931,25 +4931,25 @@
     <t xml:space="preserve">3.53778004646301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45145010948181</t>
+    <t xml:space="preserve">3.45144987106323</t>
   </si>
   <si>
     <t xml:space="preserve">3.5624463558197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54306578636169</t>
+    <t xml:space="preserve">3.54306554794312</t>
   </si>
   <si>
     <t xml:space="preserve">3.58182644844055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58711194992065</t>
+    <t xml:space="preserve">3.58711171150208</t>
   </si>
   <si>
     <t xml:space="preserve">3.55716061592102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51839995384216</t>
+    <t xml:space="preserve">3.51840019226074</t>
   </si>
   <si>
     <t xml:space="preserve">3.46730661392212</t>
@@ -4958,7 +4958,7 @@
     <t xml:space="preserve">3.4690682888031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41621327400208</t>
+    <t xml:space="preserve">3.4162130355835</t>
   </si>
   <si>
     <t xml:space="preserve">3.40211844444275</t>
@@ -4970,10 +4970,10 @@
     <t xml:space="preserve">3.45497369766235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43383169174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4584972858429</t>
+    <t xml:space="preserve">3.43383145332336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45849752426147</t>
   </si>
   <si>
     <t xml:space="preserve">3.42678427696228</t>
@@ -4997,10 +4997,10 @@
     <t xml:space="preserve">3.5677318572998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56420803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55187487602234</t>
+    <t xml:space="preserve">3.5642077922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55187511444092</t>
   </si>
   <si>
     <t xml:space="preserve">3.46554470062256</t>
@@ -5012,7 +5012,7 @@
     <t xml:space="preserve">3.47611594200134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.558922290802</t>
+    <t xml:space="preserve">3.55892252922058</t>
   </si>
   <si>
     <t xml:space="preserve">3.5536367893219</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">3.57301735877991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57654070854187</t>
+    <t xml:space="preserve">3.57654094696045</t>
   </si>
   <si>
     <t xml:space="preserve">3.5483512878418</t>
@@ -5039,7 +5039,7 @@
     <t xml:space="preserve">3.73510646820068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69986963272095</t>
+    <t xml:space="preserve">3.69986987113953</t>
   </si>
   <si>
     <t xml:space="preserve">3.80029511451721</t>
@@ -5048,7 +5048,7 @@
     <t xml:space="preserve">3.72277355194092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71396470069885</t>
+    <t xml:space="preserve">3.71396446228027</t>
   </si>
   <si>
     <t xml:space="preserve">3.66815662384033</t>
@@ -5060,7 +5060,7 @@
     <t xml:space="preserve">3.69458413124084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78796219825745</t>
+    <t xml:space="preserve">3.78796195983887</t>
   </si>
   <si>
     <t xml:space="preserve">3.77210545539856</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">3.64701437950134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70867896080017</t>
+    <t xml:space="preserve">3.70867919921875</t>
   </si>
   <si>
     <t xml:space="preserve">3.64172887802124</t>
@@ -5102,79 +5102,79 @@
     <t xml:space="preserve">3.71220302581787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6857750415802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67168045043945</t>
+    <t xml:space="preserve">3.68577527999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67168068885803</t>
   </si>
   <si>
     <t xml:space="preserve">3.65229988098145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65582394599915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71748805046082</t>
+    <t xml:space="preserve">3.65582370758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71748828887939</t>
   </si>
   <si>
     <t xml:space="preserve">3.69634628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63468146324158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62587237358093</t>
+    <t xml:space="preserve">3.63468170166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62587261199951</t>
   </si>
   <si>
     <t xml:space="preserve">3.70163178443909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72453570365906</t>
+    <t xml:space="preserve">3.72453594207764</t>
   </si>
   <si>
     <t xml:space="preserve">3.72982144355774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76858162879944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81615138053894</t>
+    <t xml:space="preserve">3.76858139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81615114212036</t>
   </si>
   <si>
     <t xml:space="preserve">3.81967520713806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88133955001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85138869285583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83905553817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87781620025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87605428695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84610271453857</t>
+    <t xml:space="preserve">3.88133978843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85138845443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83905529975891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87781572341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87605404853821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84610295295715</t>
   </si>
   <si>
     <t xml:space="preserve">3.89895820617676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82672214508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77915263175964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80205678939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76329588890076</t>
+    <t xml:space="preserve">3.82672262191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77915287017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80205655097961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76329612731934</t>
   </si>
   <si>
     <t xml:space="preserve">3.74920153617859</t>
@@ -5183,28 +5183,28 @@
     <t xml:space="preserve">3.74039196968079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67344236373901</t>
+    <t xml:space="preserve">3.67344212532043</t>
   </si>
   <si>
     <t xml:space="preserve">3.73158311843872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8584361076355</t>
+    <t xml:space="preserve">3.85843563079834</t>
   </si>
   <si>
     <t xml:space="preserve">3.82496070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81086587905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88662552833557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91833829879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90071964263916</t>
+    <t xml:space="preserve">3.81086611747742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88662528991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91833806037903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90071988105774</t>
   </si>
   <si>
     <t xml:space="preserve">4.06633329391479</t>
@@ -71294,7 +71294,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6911342593</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>136079</v>
@@ -71303,7 +71303,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="D2500" t="n">
-        <v>6.15999984741211</v>
+        <v>6.15500020980835</v>
       </c>
       <c r="E2500" t="n">
         <v>6.19999980926514</v>
@@ -71315,6 +71315,32 @@
         <v>1978</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6910185185</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>69253</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>6.19500017166138</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>6.1399998664856</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>6.19500017166138</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>6.13500022888184</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>1981</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -47,70 +47,70 @@
     <t xml:space="preserve">4.33184623718262</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13419532775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96948647499084</t>
+    <t xml:space="preserve">4.13419485092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96948623657227</t>
   </si>
   <si>
     <t xml:space="preserve">3.95301580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94203448295593</t>
+    <t xml:space="preserve">3.94203495979309</t>
   </si>
   <si>
     <t xml:space="preserve">4.07380247116089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93105435371399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82673811912537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76085543632507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67850065231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73889398574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40398645401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53300809860229</t>
+    <t xml:space="preserve">3.93105483055115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82673764228821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76085567474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67850136756897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73889422416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40398597717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53300762176514</t>
   </si>
   <si>
     <t xml:space="preserve">3.76909065246582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79379653930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79928660392761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88438773155212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67575550079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70595240592957</t>
+    <t xml:space="preserve">3.79379725456238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79928684234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88438749313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67575573921204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70595216751099</t>
   </si>
   <si>
     <t xml:space="preserve">3.64006853103638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57967448234558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35731840133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45065236091614</t>
+    <t xml:space="preserve">3.57967591285706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35731816291809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4506528377533</t>
   </si>
   <si>
     <t xml:space="preserve">3.3765344619751</t>
@@ -119,136 +119,136 @@
     <t xml:space="preserve">3.06633234024048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95652651786804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19535446166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98397755622864</t>
+    <t xml:space="preserve">2.95652723312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19535422325134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98397779464722</t>
   </si>
   <si>
     <t xml:space="preserve">3.2420220375061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20084452629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48633980751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38202452659607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31065106391907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3875150680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26672840118408</t>
+    <t xml:space="preserve">3.20084381103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48634028434753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38202428817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31065082550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38751554489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26672863960266</t>
   </si>
   <si>
     <t xml:space="preserve">3.1129994392395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08554816246033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07182264328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06084203720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15692186355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.302414894104</t>
+    <t xml:space="preserve">3.08554840087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07182216644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06084179878235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15692210197449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30241513252258</t>
   </si>
   <si>
     <t xml:space="preserve">3.43967294692993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35182857513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28319931030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22280597686768</t>
+    <t xml:space="preserve">3.3518283367157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28319907188416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22280621528625</t>
   </si>
   <si>
     <t xml:space="preserve">3.25300264358521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57692956924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47261476516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46437931060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59065628051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56320452690125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61261677742004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51653695106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43418264389038</t>
+    <t xml:space="preserve">3.57693004608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47261500358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46437883377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.590656042099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56320476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61261701583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51653718948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43418216705322</t>
   </si>
   <si>
     <t xml:space="preserve">3.37104392051697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45888876914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5302631855011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32986664772034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27221775054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09103894233704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23653173446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34084725379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28594470024109</t>
+    <t xml:space="preserve">3.45888948440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53026270866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32986688613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27221846580505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09103870391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23653125762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3408477306366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28594422340393</t>
   </si>
   <si>
     <t xml:space="preserve">3.31888628005981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23927593231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42594647407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41771125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40947556495667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41496610641479</t>
+    <t xml:space="preserve">3.23927688598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42594695091248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41771101951599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40947532653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41496634483337</t>
   </si>
   <si>
     <t xml:space="preserve">3.44241738319397</t>
@@ -257,58 +257,58 @@
     <t xml:space="preserve">3.46163415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44790863990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49732065200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39300537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3737895488739</t>
+    <t xml:space="preserve">3.44790816307068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49732041358948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39300513267517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37378978729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.26123809814453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2694730758667</t>
+    <t xml:space="preserve">3.26947355270386</t>
   </si>
   <si>
     <t xml:space="preserve">3.15417742729187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16241240501404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01966524124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94829130172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82201385498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93181991577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0690770149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00044870376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91809415817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87417149543762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85221076011658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89064240455627</t>
+    <t xml:space="preserve">3.16241335868835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0196647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94829154014587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82201409339905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93182039260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06907773017883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00044846534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91809439659119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87417125701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85221028327942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8906421661377</t>
   </si>
   <si>
     <t xml:space="preserve">2.97133898735046</t>
@@ -317,70 +317,70 @@
     <t xml:space="preserve">3.06356263160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23648238182068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24224662780762</t>
+    <t xml:space="preserve">3.23648262023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24224638938904</t>
   </si>
   <si>
     <t xml:space="preserve">3.29988622665405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1788432598114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15866875648499</t>
+    <t xml:space="preserve">3.17884278297424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15866899490356</t>
   </si>
   <si>
     <t xml:space="preserve">3.04050707817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97998476028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96269297599792</t>
+    <t xml:space="preserve">2.979984998703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96269249916077</t>
   </si>
   <si>
     <t xml:space="preserve">3.02321481704712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00015902519226</t>
+    <t xml:space="preserve">3.00015878677368</t>
   </si>
   <si>
     <t xml:space="preserve">2.95692849159241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8185932636261</t>
+    <t xml:space="preserve">2.81859278678894</t>
   </si>
   <si>
     <t xml:space="preserve">2.79668998718262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66988158226013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61454749107361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54768538475037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70331263542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75288391113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90505337715149</t>
+    <t xml:space="preserve">2.66988182067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61454725265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54768514633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70331311225891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75288367271423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90505290031433</t>
   </si>
   <si>
     <t xml:space="preserve">2.92234468460083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96845698356628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53615713119507</t>
+    <t xml:space="preserve">2.96845674514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53615665435791</t>
   </si>
   <si>
     <t xml:space="preserve">2.26179146766663</t>
@@ -389,22 +389,22 @@
     <t xml:space="preserve">2.49004530906677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41972422599792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42664122581482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49235105514526</t>
+    <t xml:space="preserve">2.4197244644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4266414642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49235081672668</t>
   </si>
   <si>
     <t xml:space="preserve">2.36900115013123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28830552101135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.297527551651</t>
+    <t xml:space="preserve">2.28830599784851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29752779006958</t>
   </si>
   <si>
     <t xml:space="preserve">2.30559754371643</t>
@@ -413,13 +413,13 @@
     <t xml:space="preserve">2.35747313499451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4324049949646</t>
+    <t xml:space="preserve">2.43240523338318</t>
   </si>
   <si>
     <t xml:space="preserve">2.61108899116516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59379720687866</t>
+    <t xml:space="preserve">2.59379696846008</t>
   </si>
   <si>
     <t xml:space="preserve">2.68025708198547</t>
@@ -428,58 +428,58 @@
     <t xml:space="preserve">2.59725522994995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60647821426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56958794593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62838125228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62261724472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59494996070862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61685371398926</t>
+    <t xml:space="preserve">2.60647797584534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56958818435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62838077545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62261700630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5949501991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61685347557068</t>
   </si>
   <si>
     <t xml:space="preserve">2.54653239250183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63414549827576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58226919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4035849571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41511297225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4381697177887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55114364624023</t>
+    <t xml:space="preserve">2.63414525985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58226895332336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40358519554138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41511344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43816947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55114388465881</t>
   </si>
   <si>
     <t xml:space="preserve">2.58572769165039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65143704414368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65489506721497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.604172706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54307413101196</t>
+    <t xml:space="preserve">2.65143728256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65489482879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60417246818542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54307436943054</t>
   </si>
   <si>
     <t xml:space="preserve">2.41857147216797</t>
@@ -488,10 +488,10 @@
     <t xml:space="preserve">2.37015414237976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39320993423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51310157775879</t>
+    <t xml:space="preserve">2.3932101726532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51310133934021</t>
   </si>
   <si>
     <t xml:space="preserve">2.50964260101318</t>
@@ -500,64 +500,64 @@
     <t xml:space="preserve">2.4612250328064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44854426383972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50733661651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50157332420349</t>
+    <t xml:space="preserve">2.44854402542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50733709335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50157308578491</t>
   </si>
   <si>
     <t xml:space="preserve">2.49696207046509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51540732383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53039360046387</t>
+    <t xml:space="preserve">2.5154070854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53039336204529</t>
   </si>
   <si>
     <t xml:space="preserve">2.57304739952087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66181254386902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62722826004028</t>
+    <t xml:space="preserve">2.6618127822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62722849845886</t>
   </si>
   <si>
     <t xml:space="preserve">2.73789691925049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83012104034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79092526435852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67449355125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6560480594635</t>
+    <t xml:space="preserve">2.83012080192566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79092574119568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67449307441711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65604829788208</t>
   </si>
   <si>
     <t xml:space="preserve">2.64797878265381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65720081329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64567303657532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52001810073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51886487007141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49580931663513</t>
+    <t xml:space="preserve">2.65720152854919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64567375183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52001786231995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51886510848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49580955505371</t>
   </si>
   <si>
     <t xml:space="preserve">2.52117085456848</t>
@@ -566,55 +566,55 @@
     <t xml:space="preserve">2.52462911605835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54192161560059</t>
+    <t xml:space="preserve">2.54192137718201</t>
   </si>
   <si>
     <t xml:space="preserve">2.47275328636169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46929526329041</t>
+    <t xml:space="preserve">2.46929502487183</t>
   </si>
   <si>
     <t xml:space="preserve">2.39436316490173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32173705101013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32519507408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24795794487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26524925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32634806632996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38629341125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4439332485199</t>
+    <t xml:space="preserve">2.32173681259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32519483566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24795746803284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26524949073792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32634782791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3862931728363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44393301010132</t>
   </si>
   <si>
     <t xml:space="preserve">2.44623875617981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5707414150238</t>
+    <t xml:space="preserve">2.57074117660522</t>
   </si>
   <si>
     <t xml:space="preserve">2.57996320724487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56267166137695</t>
+    <t xml:space="preserve">2.56267189979553</t>
   </si>
   <si>
     <t xml:space="preserve">2.55806064605713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50387859344482</t>
+    <t xml:space="preserve">2.5038788318634</t>
   </si>
   <si>
     <t xml:space="preserve">2.50503158569336</t>
@@ -632,49 +632,49 @@
     <t xml:space="preserve">2.55344915390015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70907688140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67910432815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58111572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80130100250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81282949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7229106426239</t>
+    <t xml:space="preserve">2.70907735824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6791045665741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58111619949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80130124092102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81282877922058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72291111946106</t>
   </si>
   <si>
     <t xml:space="preserve">2.78285622596741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82551026344299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92522716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96557450294495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91081690788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00592255592346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03474259376526</t>
+    <t xml:space="preserve">2.82551002502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92522668838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96557426452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91081666946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00592279434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03474235534668</t>
   </si>
   <si>
     <t xml:space="preserve">2.99727654457092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98574829101562</t>
+    <t xml:space="preserve">2.9857485294342</t>
   </si>
   <si>
     <t xml:space="preserve">2.94828271865845</t>
@@ -683,28 +683,28 @@
     <t xml:space="preserve">2.93963670730591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97422122955322</t>
+    <t xml:space="preserve">2.97422099113464</t>
   </si>
   <si>
     <t xml:space="preserve">2.99151277542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01456880569458</t>
+    <t xml:space="preserve">3.014568567276</t>
   </si>
   <si>
     <t xml:space="preserve">3.03186058998108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16155076026917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13849472999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11255669593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12984848022461</t>
+    <t xml:space="preserve">3.16155099868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13849449157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11255645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12984895706177</t>
   </si>
   <si>
     <t xml:space="preserve">3.20478057861328</t>
@@ -722,73 +722,73 @@
     <t xml:space="preserve">3.12408494949341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14137625694275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08373713493347</t>
+    <t xml:space="preserve">3.14137649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08373689651489</t>
   </si>
   <si>
     <t xml:space="preserve">3.30276870727539</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26242089271545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18748903274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28547668457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22783660888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17596006393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24801015853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2681839466095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23936438560486</t>
+    <t xml:space="preserve">3.26242017745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18748879432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28547644615173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2278368473053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17596054077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2480103969574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26818466186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23936462402344</t>
   </si>
   <si>
     <t xml:space="preserve">3.09238243103027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10102868080139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05491709709167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08085489273071</t>
+    <t xml:space="preserve">3.10102844238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0549168586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08085441589355</t>
   </si>
   <si>
     <t xml:space="preserve">3.11832070350647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15002274513245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0116868019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92810869216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95404696464539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78516149520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91369867324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98863101005554</t>
+    <t xml:space="preserve">3.15002250671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01168727874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92810845375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95404672622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7851619720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91369891166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98863053321838</t>
   </si>
   <si>
     <t xml:space="preserve">3.0030403137207</t>
@@ -797,142 +797,142 @@
     <t xml:space="preserve">3.0260968208313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07797265052795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05779886245728</t>
+    <t xml:space="preserve">3.07797288894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05779933929443</t>
   </si>
   <si>
     <t xml:space="preserve">3.18172454833984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17019701004028</t>
+    <t xml:space="preserve">3.17019653320312</t>
   </si>
   <si>
     <t xml:space="preserve">3.23360061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2451286315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25089287757874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27106666564941</t>
+    <t xml:space="preserve">3.24512887001038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25089240074158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27106714248657</t>
   </si>
   <si>
     <t xml:space="preserve">3.27394866943359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28259491920471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2566556930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18460655212402</t>
+    <t xml:space="preserve">3.28259468078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25665616989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18460607528687</t>
   </si>
   <si>
     <t xml:space="preserve">3.29412221908569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10391068458557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34023499488831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44398641586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43245816230774</t>
+    <t xml:space="preserve">3.10391139984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34023451805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4439868927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4324586391449</t>
   </si>
   <si>
     <t xml:space="preserve">3.46415996551514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45839643478394</t>
+    <t xml:space="preserve">3.45839667320251</t>
   </si>
   <si>
     <t xml:space="preserve">3.49298024177551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4468686580658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50450873374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60249614715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51603627204895</t>
+    <t xml:space="preserve">3.44686818122864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50450825691223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60249590873718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51603674888611</t>
   </si>
   <si>
     <t xml:space="preserve">3.46992468833923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44110488891602</t>
+    <t xml:space="preserve">3.44110441207886</t>
   </si>
   <si>
     <t xml:space="preserve">3.42381262779236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41228461265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39499282836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37193608283997</t>
+    <t xml:space="preserve">3.41228413581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39499258995056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37193632125854</t>
   </si>
   <si>
     <t xml:space="preserve">3.4893524646759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49236273765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5947253704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72117280960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71515154838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58870387077332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46827745437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41107535362244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49838447570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54053330421448</t>
+    <t xml:space="preserve">3.49236249923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59472513198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72117257118225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71515250205994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58870363235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46827816963196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41107511520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49838376045227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54053282737732</t>
   </si>
   <si>
     <t xml:space="preserve">3.50440549850464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51644849777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54956555366516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70913052558899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72418403625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64891743659973</t>
+    <t xml:space="preserve">3.51644825935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.549565076828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70912981033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72418355941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64891695976257</t>
   </si>
   <si>
     <t xml:space="preserve">3.75127935409546</t>
@@ -941,70 +941,70 @@
     <t xml:space="preserve">3.72719430923462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76332259178162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73923707008362</t>
+    <t xml:space="preserve">3.76332187652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73923683166504</t>
   </si>
   <si>
     <t xml:space="preserve">3.74525785446167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71214127540588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7031090259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75730037689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77536463737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77837491035461</t>
+    <t xml:space="preserve">3.71214151382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70310974121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75730109214783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77536392211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77837562561035</t>
   </si>
   <si>
     <t xml:space="preserve">3.8415994644165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85966324806213</t>
+    <t xml:space="preserve">3.85966348648071</t>
   </si>
   <si>
     <t xml:space="preserve">3.82654547691345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09750556945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14266538619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19685697555542</t>
+    <t xml:space="preserve">4.09750509262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14266586303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19685649871826</t>
   </si>
   <si>
     <t xml:space="preserve">4.17277193069458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19083595275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22094249725342</t>
+    <t xml:space="preserve">4.19083547592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22094202041626</t>
   </si>
   <si>
     <t xml:space="preserve">4.19986724853516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24502754211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26911306381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26309156417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21492099761963</t>
+    <t xml:space="preserve">4.2450270652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2691125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26309204101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21492052078247</t>
   </si>
   <si>
     <t xml:space="preserve">4.15470790863037</t>
@@ -1013,22 +1013,22 @@
     <t xml:space="preserve">4.14567613601685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13664436340332</t>
+    <t xml:space="preserve">4.13664388656616</t>
   </si>
   <si>
     <t xml:space="preserve">4.22395324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22696399688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33534717559814</t>
+    <t xml:space="preserve">4.22696304321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33534669876099</t>
   </si>
   <si>
     <t xml:space="preserve">4.25104904174805</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28717660903931</t>
+    <t xml:space="preserve">4.28717613220215</t>
   </si>
   <si>
     <t xml:space="preserve">4.11857938766479</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">4.09449434280396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08847332000732</t>
+    <t xml:space="preserve">4.08847284317017</t>
   </si>
   <si>
     <t xml:space="preserve">4.04030275344849</t>
@@ -1049,178 +1049,178 @@
     <t xml:space="preserve">4.05234479904175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95901489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86267328262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86568450927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94396114349365</t>
+    <t xml:space="preserve">3.95901465415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86267352104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86568427085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94396138191223</t>
   </si>
   <si>
     <t xml:space="preserve">3.94697260856628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95600438117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98009037971497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9740686416626</t>
+    <t xml:space="preserve">3.95600390434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98008966445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97406840324402</t>
   </si>
   <si>
     <t xml:space="preserve">4.07342004776001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06438827514648</t>
+    <t xml:space="preserve">4.06438779830933</t>
   </si>
   <si>
     <t xml:space="preserve">3.98912143707275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96202540397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01320648193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03428173065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00417423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00116395950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90783381462097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88976955413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95299363136292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01019668579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11255788803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15771818161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06739807128906</t>
+    <t xml:space="preserve">3.96202516555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01320600509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03428077697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00417470932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00116348266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90783405303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88976979255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95299386978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01019525527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11255836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15771865844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06739854812622</t>
   </si>
   <si>
     <t xml:space="preserve">3.98611092567444</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93191885948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9018120765686</t>
+    <t xml:space="preserve">3.93191933631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90181231498718</t>
   </si>
   <si>
     <t xml:space="preserve">3.87471652030945</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8536422252655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82353472709656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89579057693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84762048721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83256793022156</t>
+    <t xml:space="preserve">3.85364198684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82353520393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89579153060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84762072563171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83256769180298</t>
   </si>
   <si>
     <t xml:space="preserve">3.88073778152466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88374781608582</t>
+    <t xml:space="preserve">3.88374805450439</t>
   </si>
   <si>
     <t xml:space="preserve">3.9258975982666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9289083480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88675928115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9138548374176</t>
+    <t xml:space="preserve">3.92890858650208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88675951957703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91385507583618</t>
   </si>
   <si>
     <t xml:space="preserve">3.91084480285645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84460973739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82052516937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69106674194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70611977577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55558657646179</t>
+    <t xml:space="preserve">3.8446102142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82052493095398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69106650352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70611953735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55558705329895</t>
   </si>
   <si>
     <t xml:space="preserve">3.47429919242859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33580875396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40204334259033</t>
+    <t xml:space="preserve">3.33580851554871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40204262733459</t>
   </si>
   <si>
     <t xml:space="preserve">3.52246952056885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54354453086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53150081634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57365036010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60074663162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5766613483429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5375235080719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55257606506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50139451026917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45021438598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51042652130127</t>
+    <t xml:space="preserve">3.54354381561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53150129318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57365083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60074639320374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57666182518005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53752255439758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55257558822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50139474868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45021390914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51042675971985</t>
   </si>
   <si>
     <t xml:space="preserve">3.48634171485901</t>
@@ -1229,10 +1229,10 @@
     <t xml:space="preserve">3.43817162513733</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40806460380554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53451180458069</t>
+    <t xml:space="preserve">3.40806412696838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53451204299927</t>
   </si>
   <si>
     <t xml:space="preserve">3.60977840423584</t>
@@ -1241,31 +1241,31 @@
     <t xml:space="preserve">3.35387229919434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42612886428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44419240951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32376551628113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39000058174133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61278867721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73020434379578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66698026657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64590716362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63386392593384</t>
+    <t xml:space="preserve">3.42612862586975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44419264793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32376575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39000082015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61278939247131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73020458221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6669807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64590644836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63386368751526</t>
   </si>
   <si>
     <t xml:space="preserve">3.81450319290161</t>
@@ -1280,40 +1280,40 @@
     <t xml:space="preserve">4.04331302642822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99213194847107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98310041427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06137704849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12460136413574</t>
+    <t xml:space="preserve">3.99213171005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98309969902039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06137752532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1246018409729</t>
   </si>
   <si>
     <t xml:space="preserve">4.16072845458984</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07040882110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08245277404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80848264694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8988025188446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91987657546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78439617156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77235460281372</t>
+    <t xml:space="preserve">4.07040929794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08245229721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80848240852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89880228042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91987705230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7843964099884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77235388755798</t>
   </si>
   <si>
     <t xml:space="preserve">3.79945015907288</t>
@@ -1325,34 +1325,34 @@
     <t xml:space="preserve">3.75429058074951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76633310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63988447189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56160831451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6699914932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96503686904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79342937469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74224758148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79164934158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77612233161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7885434627533</t>
+    <t xml:space="preserve">3.76633262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63988494873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56160807609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66999173164368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96503639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79342913627625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74224734306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79164886474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77612209320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78854393959045</t>
   </si>
   <si>
     <t xml:space="preserve">3.70469903945923</t>
@@ -1361,19 +1361,19 @@
     <t xml:space="preserve">3.58358979225159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55914282798767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55258798599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51326131820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61158013343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58536124229431</t>
+    <t xml:space="preserve">3.55914306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55258846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51326084136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61158037185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58536100387573</t>
   </si>
   <si>
     <t xml:space="preserve">3.76888990402222</t>
@@ -1382,67 +1382,67 @@
     <t xml:space="preserve">3.89998173713684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342641830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85082197189331</t>
+    <t xml:space="preserve">3.8934268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85082244873047</t>
   </si>
   <si>
     <t xml:space="preserve">3.81149482727051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63779807090759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75578045845032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73939418792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86065459251404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099078178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81804919242859</t>
+    <t xml:space="preserve">3.63779783248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75578093528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73939371109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86065411567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099054336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81804871559143</t>
   </si>
   <si>
     <t xml:space="preserve">3.96552777290344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98846840858459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93275451660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86720871925354</t>
+    <t xml:space="preserve">3.98846912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93275499343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86720895767212</t>
   </si>
   <si>
     <t xml:space="preserve">3.84426760673523</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91309070587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82132649421692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03107309341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04418325424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02451848983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98191404342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90653681755066</t>
+    <t xml:space="preserve">3.913090467453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82132625579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03107357025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04418277740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0245189666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98191380500793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90653657913208</t>
   </si>
   <si>
     <t xml:space="preserve">3.99830055236816</t>
@@ -1451,25 +1451,25 @@
     <t xml:space="preserve">3.77544474601746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76561307907104</t>
+    <t xml:space="preserve">3.76561212539673</t>
   </si>
   <si>
     <t xml:space="preserve">3.71973085403442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71645283699036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56897521018982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50670623779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46737909317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27467370033264</t>
+    <t xml:space="preserve">3.71645331382751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56897449493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50670599937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46737861633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27467346191406</t>
   </si>
   <si>
     <t xml:space="preserve">2.93645691871643</t>
@@ -1478,79 +1478,79 @@
     <t xml:space="preserve">3.03477597236633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19077515602112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42149639129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41494178771973</t>
+    <t xml:space="preserve">3.19077467918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42149615287781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41494226455688</t>
   </si>
   <si>
     <t xml:space="preserve">3.33628726005554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31662344932556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35595059394836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21175003051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30023694038391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32645463943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39855551719666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33956384658813</t>
+    <t xml:space="preserve">3.31662273406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35595083236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.211749792099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30023670196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32645487785339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39855527877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33956408500671</t>
   </si>
   <si>
     <t xml:space="preserve">3.29040479660034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2772958278656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28057312965393</t>
+    <t xml:space="preserve">3.27729535102844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28057265281677</t>
   </si>
   <si>
     <t xml:space="preserve">3.18290948867798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12260770797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07148146629333</t>
+    <t xml:space="preserve">3.12260723114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07148098945618</t>
   </si>
   <si>
     <t xml:space="preserve">3.01511192321777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89975070953369</t>
+    <t xml:space="preserve">2.89975094795227</t>
   </si>
   <si>
     <t xml:space="preserve">3.01904463768005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01380133628845</t>
+    <t xml:space="preserve">3.01380109786987</t>
   </si>
   <si>
     <t xml:space="preserve">3.04919576644897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97971749305725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02691006660461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13440537452698</t>
+    <t xml:space="preserve">2.97971725463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02690982818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13440561294556</t>
   </si>
   <si>
     <t xml:space="preserve">3.10425424575806</t>
@@ -1562,67 +1562,67 @@
     <t xml:space="preserve">3.00200271606445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00462436676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98233890533447</t>
+    <t xml:space="preserve">3.00462508201599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98233914375305</t>
   </si>
   <si>
     <t xml:space="preserve">2.98627161979675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92072558403015</t>
+    <t xml:space="preserve">2.92072582244873</t>
   </si>
   <si>
     <t xml:space="preserve">2.92728042602539</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00069212913513</t>
+    <t xml:space="preserve">3.00069189071655</t>
   </si>
   <si>
     <t xml:space="preserve">3.01249003410339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0373969078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95612072944641</t>
+    <t xml:space="preserve">3.03739738464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95612049102783</t>
   </si>
   <si>
     <t xml:space="preserve">2.92465877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84469246864319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97709488868713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00724649429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89057445526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77259182929993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79487729072571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73064255714417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71228981018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70049142837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77914667129517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76997017860413</t>
+    <t xml:space="preserve">2.84469270706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97709512710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00724625587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89057421684265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77259206771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79487776756287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73064279556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71228957176208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70049118995667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77914643287659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76997041702271</t>
   </si>
   <si>
     <t xml:space="preserve">2.7371973991394</t>
@@ -1631,16 +1631,16 @@
     <t xml:space="preserve">2.7214663028717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6900041103363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63625597953796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64936566352844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62052536010742</t>
+    <t xml:space="preserve">2.69000434875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63625621795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64936542510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.620525598526</t>
   </si>
   <si>
     <t xml:space="preserve">2.67689514160156</t>
@@ -1655,25 +1655,25 @@
     <t xml:space="preserve">2.85124707221985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86697816848755</t>
+    <t xml:space="preserve">2.86697840690613</t>
   </si>
   <si>
     <t xml:space="preserve">2.93907904624939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91154909133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91679263114929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92596960067749</t>
+    <t xml:space="preserve">2.91154932975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91679286956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92596936225891</t>
   </si>
   <si>
     <t xml:space="preserve">2.94170045852661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99806976318359</t>
+    <t xml:space="preserve">2.99806952476501</t>
   </si>
   <si>
     <t xml:space="preserve">3.04133033752441</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">2.99675869941711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99413752555847</t>
+    <t xml:space="preserve">2.99413681030273</t>
   </si>
   <si>
     <t xml:space="preserve">2.96267509460449</t>
@@ -1694,22 +1694,22 @@
     <t xml:space="preserve">2.91286015510559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77521371841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70704650878906</t>
+    <t xml:space="preserve">2.77521395683289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70704627037048</t>
   </si>
   <si>
     <t xml:space="preserve">2.68869352340698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70573472976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74244070053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64674401283264</t>
+    <t xml:space="preserve">2.705735206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74244093894958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64674377441406</t>
   </si>
   <si>
     <t xml:space="preserve">2.64150047302246</t>
@@ -1718,22 +1718,22 @@
     <t xml:space="preserve">2.59692883491516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38193869590759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46714806556702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44879555702209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49074459075928</t>
+    <t xml:space="preserve">2.38193821907043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4671483039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44879531860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49074482917786</t>
   </si>
   <si>
     <t xml:space="preserve">2.4710807800293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48681163787842</t>
+    <t xml:space="preserve">2.486811876297</t>
   </si>
   <si>
     <t xml:space="preserve">2.41995477676392</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">2.25871229171753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20365357398987</t>
+    <t xml:space="preserve">2.20365333557129</t>
   </si>
   <si>
     <t xml:space="preserve">2.25215744972229</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">2.28493022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38587164878845</t>
+    <t xml:space="preserve">2.38587141036987</t>
   </si>
   <si>
     <t xml:space="preserve">2.39242553710938</t>
@@ -1766,16 +1766,16 @@
     <t xml:space="preserve">2.45928263664246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5497362613678</t>
+    <t xml:space="preserve">2.54973578453064</t>
   </si>
   <si>
     <t xml:space="preserve">2.47239184379578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44617342948914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4579713344574</t>
+    <t xml:space="preserve">2.44617319107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45797157287598</t>
   </si>
   <si>
     <t xml:space="preserve">2.47501373291016</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">2.43044233322144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40815663337708</t>
+    <t xml:space="preserve">2.40815687179565</t>
   </si>
   <si>
     <t xml:space="preserve">2.33998894691467</t>
@@ -1796,28 +1796,28 @@
     <t xml:space="preserve">2.28886342048645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27968692779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25740098953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17612385749817</t>
+    <t xml:space="preserve">2.27968668937683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25740122795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17612433433533</t>
   </si>
   <si>
     <t xml:space="preserve">2.18661165237427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13155341148376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29410719871521</t>
+    <t xml:space="preserve">2.13155317306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29410696029663</t>
   </si>
   <si>
     <t xml:space="preserve">2.35178732872009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39766955375671</t>
+    <t xml:space="preserve">2.39766931533813</t>
   </si>
   <si>
     <t xml:space="preserve">2.44748449325562</t>
@@ -1826,40 +1826,40 @@
     <t xml:space="preserve">2.42388772964478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40946769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40029144287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21938467025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19447708129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25477957725525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31901431083679</t>
+    <t xml:space="preserve">2.40946793556213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40029096603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21938443183899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19447731971741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25477933883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31901454925537</t>
   </si>
   <si>
     <t xml:space="preserve">2.32687973976135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26264500617981</t>
+    <t xml:space="preserve">2.26264452934265</t>
   </si>
   <si>
     <t xml:space="preserve">2.17743515968323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12893104553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14597320556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12237644195557</t>
+    <t xml:space="preserve">2.12893152236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14597296714783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12237668037415</t>
   </si>
   <si>
     <t xml:space="preserve">2.12368774414062</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">2.10271286964417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11713290214539</t>
+    <t xml:space="preserve">2.11713266372681</t>
   </si>
   <si>
     <t xml:space="preserve">2.14728403091431</t>
@@ -1880,34 +1880,34 @@
     <t xml:space="preserve">2.23904824256897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20758652687073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36489653587341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34785485267639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37407255172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25084662437439</t>
+    <t xml:space="preserve">2.20758628845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36489677429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34785461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37407279014587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25084686279297</t>
   </si>
   <si>
     <t xml:space="preserve">2.39504766464233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35572028160095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41340065002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43306422233582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44486260414124</t>
+    <t xml:space="preserve">2.35572004318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41340017318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43306398391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44486236572266</t>
   </si>
   <si>
     <t xml:space="preserve">2.44224071502686</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">2.43175339698792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38456010818481</t>
+    <t xml:space="preserve">2.38456034660339</t>
   </si>
   <si>
     <t xml:space="preserve">2.35309815406799</t>
@@ -1928,25 +1928,25 @@
     <t xml:space="preserve">2.35440897941589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37145113945007</t>
+    <t xml:space="preserve">2.37145090103149</t>
   </si>
   <si>
     <t xml:space="preserve">2.28755211830139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26788830757141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31114864349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37931680679321</t>
+    <t xml:space="preserve">2.26788854598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31114888191223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37931632995605</t>
   </si>
   <si>
     <t xml:space="preserve">2.40291309356689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4055347442627</t>
+    <t xml:space="preserve">2.40553498268127</t>
   </si>
   <si>
     <t xml:space="preserve">2.37014007568359</t>
@@ -1955,13 +1955,13 @@
     <t xml:space="preserve">2.33605599403381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39898061752319</t>
+    <t xml:space="preserve">2.39898037910461</t>
   </si>
   <si>
     <t xml:space="preserve">2.37669467926025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50123167037964</t>
+    <t xml:space="preserve">2.50123190879822</t>
   </si>
   <si>
     <t xml:space="preserve">2.54318141937256</t>
@@ -1970,16 +1970,16 @@
     <t xml:space="preserve">2.52613949775696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5038537979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49336624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42782044410706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39635848999023</t>
+    <t xml:space="preserve">2.50385355949402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49336647987366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42782068252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39635872840881</t>
   </si>
   <si>
     <t xml:space="preserve">2.38718223571777</t>
@@ -1988,13 +1988,13 @@
     <t xml:space="preserve">2.37276196479797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37800550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33867812156677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29935026168823</t>
+    <t xml:space="preserve">2.37800574302673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33867835998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29935097694397</t>
   </si>
   <si>
     <t xml:space="preserve">2.38062739372253</t>
@@ -2003,19 +2003,19 @@
     <t xml:space="preserve">2.30459427833557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38849282264709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45666074752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40160250663757</t>
+    <t xml:space="preserve">2.38849329948425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4566605091095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40160226821899</t>
   </si>
   <si>
     <t xml:space="preserve">2.34130001068115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34392166137695</t>
+    <t xml:space="preserve">2.34392189979553</t>
   </si>
   <si>
     <t xml:space="preserve">2.38324952125549</t>
@@ -2024,142 +2024,142 @@
     <t xml:space="preserve">2.32556915283203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30328321456909</t>
+    <t xml:space="preserve">2.30328345298767</t>
   </si>
   <si>
     <t xml:space="preserve">2.30590510368347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34523272514343</t>
+    <t xml:space="preserve">2.34523296356201</t>
   </si>
   <si>
     <t xml:space="preserve">2.32425832748413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30983805656433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21545195579529</t>
+    <t xml:space="preserve">2.30983781814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21545219421387</t>
   </si>
   <si>
     <t xml:space="preserve">2.19054412841797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09091472625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08698177337646</t>
+    <t xml:space="preserve">2.09091448783875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08698201179504</t>
   </si>
   <si>
     <t xml:space="preserve">1.99783945083618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03978848457336</t>
+    <t xml:space="preserve">2.03978872299194</t>
   </si>
   <si>
     <t xml:space="preserve">1.97686457633972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99128472805023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97817540168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98996293544769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9996702671051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97470891475677</t>
+    <t xml:space="preserve">1.99128496646881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97817552089691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98996269702911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99967014789581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97470915317535</t>
   </si>
   <si>
     <t xml:space="preserve">1.94420051574707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91923952102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89843833446503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86377000808716</t>
+    <t xml:space="preserve">1.91923928260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89843845367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86377012729645</t>
   </si>
   <si>
     <t xml:space="preserve">1.82632863521576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87625086307526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87902390956879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83742249011993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9511342048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92755973339081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89982521533966</t>
+    <t xml:space="preserve">1.87625074386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87902426719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83742237091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95113444328308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92755997180939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89982497692108</t>
   </si>
   <si>
     <t xml:space="preserve">1.92062628269196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90953230857849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90675914287567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88734471797943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88873147964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88179755210876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02879166603088</t>
+    <t xml:space="preserve">1.90953242778778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90675890445709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88734436035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88873136043549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88179767131805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0287914276123</t>
   </si>
   <si>
     <t xml:space="preserve">1.98302924633026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03156518936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98857629299164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95945453643799</t>
+    <t xml:space="preserve">2.03156495094299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98857605457306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95945477485657</t>
   </si>
   <si>
     <t xml:space="preserve">2.00660371780396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00521683692932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07177996635437</t>
+    <t xml:space="preserve">2.00521731376648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07178020477295</t>
   </si>
   <si>
     <t xml:space="preserve">2.0939679145813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14943742752075</t>
+    <t xml:space="preserve">2.14943718910217</t>
   </si>
   <si>
     <t xml:space="preserve">2.22709441184998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25344228744507</t>
+    <t xml:space="preserve">2.25344252586365</t>
   </si>
   <si>
     <t xml:space="preserve">2.25898909568787</t>
@@ -2168,28 +2168,28 @@
     <t xml:space="preserve">2.26453614234924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21461391448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21184062957764</t>
+    <t xml:space="preserve">2.21461367607117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21184015274048</t>
   </si>
   <si>
     <t xml:space="preserve">2.24928212165833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3144588470459</t>
+    <t xml:space="preserve">2.31445860862732</t>
   </si>
   <si>
     <t xml:space="preserve">2.30059146881104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30891180038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31307172775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27424335479736</t>
+    <t xml:space="preserve">2.30891156196594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31307196617126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27424359321594</t>
   </si>
   <si>
     <t xml:space="preserve">2.2215473651886</t>
@@ -2204,43 +2204,43 @@
     <t xml:space="preserve">2.24512195587158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28811049461365</t>
+    <t xml:space="preserve">2.28811073303223</t>
   </si>
   <si>
     <t xml:space="preserve">2.32277894020081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37824845314026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30613803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23125457763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18687891960144</t>
+    <t xml:space="preserve">2.37824869155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30613827705383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2312548160553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18687915802002</t>
   </si>
   <si>
     <t xml:space="preserve">2.17162489891052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17439818382263</t>
+    <t xml:space="preserve">2.17439842224121</t>
   </si>
   <si>
     <t xml:space="preserve">2.22432088851929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12170267105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10783529281616</t>
+    <t xml:space="preserve">2.12170243263245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10783505439758</t>
   </si>
   <si>
     <t xml:space="preserve">2.12863612174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09812808036804</t>
+    <t xml:space="preserve">2.09812831878662</t>
   </si>
   <si>
     <t xml:space="preserve">2.12724947929382</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">2.23680114746094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20629334449768</t>
+    <t xml:space="preserve">2.20629358291626</t>
   </si>
   <si>
     <t xml:space="preserve">2.19935965538025</t>
@@ -2264,22 +2264,22 @@
     <t xml:space="preserve">2.18549227714539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25760269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25621557235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23957490921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35606074333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38102173805237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3671543598175</t>
+    <t xml:space="preserve">2.25760245323181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25621581077576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23957467079163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35606050491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38102197647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36715483665466</t>
   </si>
   <si>
     <t xml:space="preserve">2.38379526138306</t>
@@ -2288,28 +2288,28 @@
     <t xml:space="preserve">2.43510460853577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5155348777771</t>
+    <t xml:space="preserve">2.51553511619568</t>
   </si>
   <si>
     <t xml:space="preserve">2.49889421463013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42955732345581</t>
+    <t xml:space="preserve">2.42955756187439</t>
   </si>
   <si>
     <t xml:space="preserve">2.42817091941833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44897150993347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45867896080017</t>
+    <t xml:space="preserve">2.44897174835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45867919921875</t>
   </si>
   <si>
     <t xml:space="preserve">2.39766263961792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38795518875122</t>
+    <t xml:space="preserve">2.3879554271698</t>
   </si>
   <si>
     <t xml:space="preserve">2.37131452560425</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">2.41707682609558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42401075363159</t>
+    <t xml:space="preserve">2.42401051521301</t>
   </si>
   <si>
     <t xml:space="preserve">2.37408804893494</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">2.32693910598755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29920434951782</t>
+    <t xml:space="preserve">2.29920482635498</t>
   </si>
   <si>
     <t xml:space="preserve">2.31723189353943</t>
@@ -2342,34 +2342,34 @@
     <t xml:space="preserve">2.34635353088379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41153025627136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46977305412292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48502707481384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5696177482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61537981033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67639589309692</t>
+    <t xml:space="preserve">2.4115297794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46977281570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48502659797668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56961798667908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61538004875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6763961315155</t>
   </si>
   <si>
     <t xml:space="preserve">2.73879909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70690417289734</t>
+    <t xml:space="preserve">2.70690441131592</t>
   </si>
   <si>
     <t xml:space="preserve">2.74711942672729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72770524024963</t>
+    <t xml:space="preserve">2.72770547866821</t>
   </si>
   <si>
     <t xml:space="preserve">2.75266671180725</t>
@@ -2387,49 +2387,49 @@
     <t xml:space="preserve">2.69581031799316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70413088798523</t>
+    <t xml:space="preserve">2.70413112640381</t>
   </si>
   <si>
     <t xml:space="preserve">2.7207715511322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80120229721069</t>
+    <t xml:space="preserve">2.80120182037354</t>
   </si>
   <si>
     <t xml:space="preserve">2.78733468055725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82893681526184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85528492927551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9468092918396</t>
+    <t xml:space="preserve">2.82893657684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85528469085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94680905342102</t>
   </si>
   <si>
     <t xml:space="preserve">3.01614570617676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02724003791809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04804086685181</t>
+    <t xml:space="preserve">3.02723979949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04804062843323</t>
   </si>
   <si>
     <t xml:space="preserve">3.0799355506897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13679194450378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14649891853333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17562007904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14511203765869</t>
+    <t xml:space="preserve">3.13679218292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14649868011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17562031745911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14511179924011</t>
   </si>
   <si>
     <t xml:space="preserve">3.23108959197998</t>
@@ -2438,16 +2438,16 @@
     <t xml:space="preserve">3.24773049354553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26298427581787</t>
+    <t xml:space="preserve">3.26298451423645</t>
   </si>
   <si>
     <t xml:space="preserve">3.26159763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22554278373718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18532729148865</t>
+    <t xml:space="preserve">3.2255425453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18532752990723</t>
   </si>
   <si>
     <t xml:space="preserve">3.18394088745117</t>
@@ -2459,34 +2459,34 @@
     <t xml:space="preserve">3.21028876304626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25327754020691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22831630706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2019681930542</t>
+    <t xml:space="preserve">3.25327730178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22831654548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20196795463562</t>
   </si>
   <si>
     <t xml:space="preserve">3.24218344688416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26575779914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21306157112122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19919466972351</t>
+    <t xml:space="preserve">3.26575827598572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21306180953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19919443130493</t>
   </si>
   <si>
     <t xml:space="preserve">3.20890188217163</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22415590286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1908745765686</t>
+    <t xml:space="preserve">3.22415566444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19087433815002</t>
   </si>
   <si>
     <t xml:space="preserve">3.20335483551025</t>
@@ -2504,28 +2504,28 @@
     <t xml:space="preserve">3.2061288356781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17839360237122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17145991325378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03694677352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1534321308136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16868686676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.970383644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03555965423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14095211029053</t>
+    <t xml:space="preserve">3.17839407920837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17145943641663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03694701194763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15343236923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16868662834167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97038340568542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03555989265442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14095187187195</t>
   </si>
   <si>
     <t xml:space="preserve">3.12985825538635</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">3.14927196502686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17007327079773</t>
+    <t xml:space="preserve">3.17007303237915</t>
   </si>
   <si>
     <t xml:space="preserve">3.12708449363708</t>
@@ -2543,19 +2543,19 @@
     <t xml:space="preserve">3.10073661804199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07854866981506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11044383049011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08964252471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28239893913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34202814102173</t>
+    <t xml:space="preserve">3.07854890823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11044359207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08964276313782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28239846229553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34202861785889</t>
   </si>
   <si>
     <t xml:space="preserve">3.34896183013916</t>
@@ -2573,28 +2573,28 @@
     <t xml:space="preserve">2.73741245269775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58487176895142</t>
+    <t xml:space="preserve">2.58487153053284</t>
   </si>
   <si>
     <t xml:space="preserve">2.55158996582031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49473428726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29227113723755</t>
+    <t xml:space="preserve">2.49473404884338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29227089881897</t>
   </si>
   <si>
     <t xml:space="preserve">2.07039356231689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95668137073517</t>
+    <t xml:space="preserve">1.95668113231659</t>
   </si>
   <si>
     <t xml:space="preserve">1.99134945869446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69042813777924</t>
+    <t xml:space="preserve">1.69042837619781</t>
   </si>
   <si>
     <t xml:space="preserve">1.7847261428833</t>
@@ -2603,19 +2603,19 @@
     <t xml:space="preserve">1.65576016902924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52818048000336</t>
+    <t xml:space="preserve">1.52818036079407</t>
   </si>
   <si>
     <t xml:space="preserve">1.41030824184418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.485191822052</t>
+    <t xml:space="preserve">1.48519170284271</t>
   </si>
   <si>
     <t xml:space="preserve">1.49489891529083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60583782196045</t>
+    <t xml:space="preserve">1.60583770275116</t>
   </si>
   <si>
     <t xml:space="preserve">1.67933440208435</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">1.68904185295105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69736194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72371006011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75421833992004</t>
+    <t xml:space="preserve">1.69736218452454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72371029853821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75421798229218</t>
   </si>
   <si>
     <t xml:space="preserve">1.78888642787933</t>
@@ -2648,31 +2648,31 @@
     <t xml:space="preserve">2.06207299232483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05375289916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99412274360657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609531879425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.966388463974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94142735004425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85960972309113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86793041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92339992523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90121209621429</t>
+    <t xml:space="preserve">2.05375242233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99412298202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609567642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96638822555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94142699241638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8596099615097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8679301738739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92339968681335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.901211977005</t>
   </si>
   <si>
     <t xml:space="preserve">2.14805054664612</t>
@@ -2681,16 +2681,16 @@
     <t xml:space="preserve">2.26730966567993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23818826675415</t>
+    <t xml:space="preserve">2.23818802833557</t>
   </si>
   <si>
     <t xml:space="preserve">2.22570753097534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13418340682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28117728233337</t>
+    <t xml:space="preserve">2.13418316841125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28117704391479</t>
   </si>
   <si>
     <t xml:space="preserve">2.35744738578796</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">2.40043616294861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34358048439026</t>
+    <t xml:space="preserve">2.34358024597168</t>
   </si>
   <si>
     <t xml:space="preserve">2.30752491950989</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">2.49150609970093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49741768836975</t>
+    <t xml:space="preserve">2.49741744995117</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456218719482</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">2.57130527496338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72647023200989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75750350952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80774712562561</t>
+    <t xml:space="preserve">2.72647047042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75750327110291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80774760246277</t>
   </si>
   <si>
     <t xml:space="preserve">2.86537981033325</t>
@@ -2738,34 +2738,34 @@
     <t xml:space="preserve">2.87572431564331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86833524703979</t>
+    <t xml:space="preserve">2.86833548545837</t>
   </si>
   <si>
     <t xml:space="preserve">2.97473430633545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20230960845947</t>
+    <t xml:space="preserve">3.20230984687805</t>
   </si>
   <si>
     <t xml:space="preserve">3.16979885101318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14024376869202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93483448028564</t>
+    <t xml:space="preserve">3.14024353027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93483471870422</t>
   </si>
   <si>
     <t xml:space="preserve">2.93631267547607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94222354888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99837875366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00281190872192</t>
+    <t xml:space="preserve">2.94222378730774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99837851524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00281167030334</t>
   </si>
   <si>
     <t xml:space="preserve">2.9584789276123</t>
@@ -2792,16 +2792,16 @@
     <t xml:space="preserve">2.82843589782715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86242461204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93779015541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99542284011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03236722946167</t>
+    <t xml:space="preserve">2.86242437362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93779039382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99542307853699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03236699104309</t>
   </si>
   <si>
     <t xml:space="preserve">3.04418897628784</t>
@@ -2810,7 +2810,7 @@
     <t xml:space="preserve">3.01906728744507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92005705833435</t>
+    <t xml:space="preserve">2.92005681991577</t>
   </si>
   <si>
     <t xml:space="preserve">2.93040156364441</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">2.97916769981384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98212313652039</t>
+    <t xml:space="preserve">2.98212289810181</t>
   </si>
   <si>
     <t xml:space="preserve">2.99394536018372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98951172828674</t>
+    <t xml:space="preserve">2.98951196670532</t>
   </si>
   <si>
     <t xml:space="preserve">2.95404553413391</t>
@@ -2837,10 +2837,10 @@
     <t xml:space="preserve">2.94665670394897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03384470939636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0959107875824</t>
+    <t xml:space="preserve">3.03384494781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09591102600098</t>
   </si>
   <si>
     <t xml:space="preserve">3.01758933067322</t>
@@ -2849,40 +2849,40 @@
     <t xml:space="preserve">2.99098968505859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93335723876953</t>
+    <t xml:space="preserve">2.93335700035095</t>
   </si>
   <si>
     <t xml:space="preserve">2.91857933998108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75602579116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81365823745728</t>
+    <t xml:space="preserve">2.75602555274963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8136579990387</t>
   </si>
   <si>
     <t xml:space="preserve">2.85503578186035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85355806350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89493536949158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.877201795578</t>
+    <t xml:space="preserve">2.8535578250885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.894935131073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87720203399658</t>
   </si>
   <si>
     <t xml:space="preserve">2.92153477668762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9629123210907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91266846656799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87424683570862</t>
+    <t xml:space="preserve">2.96291255950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91266822814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87424635887146</t>
   </si>
   <si>
     <t xml:space="preserve">2.84616899490356</t>
@@ -2903,13 +2903,13 @@
     <t xml:space="preserve">2.79888081550598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7486367225647</t>
+    <t xml:space="preserve">2.74863696098328</t>
   </si>
   <si>
     <t xml:space="preserve">2.7752366065979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72351503372192</t>
+    <t xml:space="preserve">2.7235152721405</t>
   </si>
   <si>
     <t xml:space="preserve">2.76636981964111</t>
@@ -2921,19 +2921,19 @@
     <t xml:space="preserve">2.73681473731995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69987058639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79592514038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74272561073303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75454783439636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74715900421143</t>
+    <t xml:space="preserve">2.69987082481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79592537879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74272537231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75454759597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74715924263</t>
   </si>
   <si>
     <t xml:space="preserve">2.71612596511841</t>
@@ -2942,22 +2942,22 @@
     <t xml:space="preserve">2.70873713493347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70725965499878</t>
+    <t xml:space="preserve">2.7072594165802</t>
   </si>
   <si>
     <t xml:space="preserve">2.61268258094788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57573866844177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52549481391907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54175019264221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53436136245728</t>
+    <t xml:space="preserve">2.57573843002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52549457550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54174995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53436160087585</t>
   </si>
   <si>
     <t xml:space="preserve">2.5846049785614</t>
@@ -2972,25 +2972,25 @@
     <t xml:space="preserve">2.50037288665771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43091821670532</t>
+    <t xml:space="preserve">2.43091797828674</t>
   </si>
   <si>
     <t xml:space="preserve">2.52992796897888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6112048625946</t>
+    <t xml:space="preserve">2.61120462417603</t>
   </si>
   <si>
     <t xml:space="preserve">2.54618358612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55209469795227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67179322242737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60972690582275</t>
+    <t xml:space="preserve">2.55209445953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67179298400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60972714424133</t>
   </si>
   <si>
     <t xml:space="preserve">2.54322791099548</t>
@@ -3005,37 +3005,37 @@
     <t xml:space="preserve">2.6289381980896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6570155620575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63632702827454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60677170753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53140616416931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52253913879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36441850662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31713008880615</t>
+    <t xml:space="preserve">2.65701532363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63632678985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60677194595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53140592575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52253937721252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36441898345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31713032722473</t>
   </si>
   <si>
     <t xml:space="preserve">2.37180733680725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51662826538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58312773704529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64223766326904</t>
+    <t xml:space="preserve">2.51662802696228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58312749862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64223790168762</t>
   </si>
   <si>
     <t xml:space="preserve">2.49298405647278</t>
@@ -3056,16 +3056,16 @@
     <t xml:space="preserve">2.72794795036316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74568104743958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83139109611511</t>
+    <t xml:space="preserve">2.74568128585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83139157295227</t>
   </si>
   <si>
     <t xml:space="preserve">2.79149174690247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78853631019592</t>
+    <t xml:space="preserve">2.78853607177734</t>
   </si>
   <si>
     <t xml:space="preserve">2.75898122787476</t>
@@ -3074,49 +3074,49 @@
     <t xml:space="preserve">2.68361520767212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6703155040741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66440415382385</t>
+    <t xml:space="preserve">2.67031526565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66440439224243</t>
   </si>
   <si>
     <t xml:space="preserve">2.64519333839417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.680659532547</t>
+    <t xml:space="preserve">2.68065977096558</t>
   </si>
   <si>
     <t xml:space="preserve">2.64962673187256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68213772773743</t>
+    <t xml:space="preserve">2.68213725090027</t>
   </si>
   <si>
     <t xml:space="preserve">2.6259822845459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65849351882935</t>
+    <t xml:space="preserve">2.65849328041077</t>
   </si>
   <si>
     <t xml:space="preserve">2.7205593585968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85651326179504</t>
+    <t xml:space="preserve">2.85651350021362</t>
   </si>
   <si>
     <t xml:space="preserve">2.92301249504089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90380167961121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90084600448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98064541816711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01463389396667</t>
+    <t xml:space="preserve">2.90380191802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90084624290466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98064517974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0146336555481</t>
   </si>
   <si>
     <t xml:space="preserve">3.03975582122803</t>
@@ -3131,31 +3131,31 @@
     <t xml:space="preserve">3.06044459342957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0235002040863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02941131591797</t>
+    <t xml:space="preserve">3.02350068092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02941107749939</t>
   </si>
   <si>
     <t xml:space="preserve">2.89345741271973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86390233039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90675711631775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87129092216492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83434677124023</t>
+    <t xml:space="preserve">2.86390209197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90675735473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87129068374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83434700965881</t>
   </si>
   <si>
     <t xml:space="preserve">2.91710162162781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04714465141296</t>
+    <t xml:space="preserve">3.04714488983154</t>
   </si>
   <si>
     <t xml:space="preserve">3.1328547000885</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">3.10034418106079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17718744277954</t>
+    <t xml:space="preserve">3.17718768119812</t>
   </si>
   <si>
     <t xml:space="preserve">3.10625505447388</t>
@@ -3173,46 +3173,46 @@
     <t xml:space="preserve">3.13581037521362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08408856391907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00133419036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94517922401428</t>
+    <t xml:space="preserve">3.08408832550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00133371353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9451789855957</t>
   </si>
   <si>
     <t xml:space="preserve">2.9998562335968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97177839279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93926787376404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08999991416931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.091477394104</t>
+    <t xml:space="preserve">2.97177863121033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9392683506012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08999967575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09147763252258</t>
   </si>
   <si>
     <t xml:space="preserve">3.07669997215271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08704423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08852195739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12694334983826</t>
+    <t xml:space="preserve">3.08704400062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08852171897888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12694358825684</t>
   </si>
   <si>
     <t xml:space="preserve">3.24664235115051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20526504516602</t>
+    <t xml:space="preserve">3.20526528358459</t>
   </si>
   <si>
     <t xml:space="preserve">3.21856474876404</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">3.33826375007629</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34121894836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31166386604309</t>
+    <t xml:space="preserve">3.34121918678284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31166410446167</t>
   </si>
   <si>
     <t xml:space="preserve">3.26142024993896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32496380805969</t>
+    <t xml:space="preserve">3.32496404647827</t>
   </si>
   <si>
     <t xml:space="preserve">3.30131959915161</t>
@@ -3242,22 +3242,22 @@
     <t xml:space="preserve">3.29245281219482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28801941871643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31609725952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29393100738525</t>
+    <t xml:space="preserve">3.28801965713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31609702110291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29393076896667</t>
   </si>
   <si>
     <t xml:space="preserve">3.27324223518372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2451651096344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32274723052979</t>
+    <t xml:space="preserve">3.24516487121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32274770736694</t>
   </si>
   <si>
     <t xml:space="preserve">3.30649185180664</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">3.29540872573853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25107550621033</t>
+    <t xml:space="preserve">3.25107574462891</t>
   </si>
   <si>
     <t xml:space="preserve">3.28358626365662</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">3.27915358543396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24073147773743</t>
+    <t xml:space="preserve">3.24073123931885</t>
   </si>
   <si>
     <t xml:space="preserve">3.27767539024353</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">3.13433265686035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10329937934875</t>
+    <t xml:space="preserve">3.10329961776733</t>
   </si>
   <si>
     <t xml:space="preserve">3.16314911842346</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">3.13507151603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17940449714661</t>
+    <t xml:space="preserve">3.17940425872803</t>
   </si>
   <si>
     <t xml:space="preserve">3.09664964675903</t>
@@ -3320,19 +3320,19 @@
     <t xml:space="preserve">3.21043729782104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26511478424072</t>
+    <t xml:space="preserve">3.26511454582214</t>
   </si>
   <si>
     <t xml:space="preserve">3.2274317741394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23925352096558</t>
+    <t xml:space="preserve">3.23925375938416</t>
   </si>
   <si>
     <t xml:space="preserve">3.24738121032715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31979203224182</t>
+    <t xml:space="preserve">3.31979179382324</t>
   </si>
   <si>
     <t xml:space="preserve">3.33974123001099</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">3.3205304145813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32939720153809</t>
+    <t xml:space="preserve">3.32939696311951</t>
   </si>
   <si>
     <t xml:space="preserve">3.31535816192627</t>
@@ -3362,19 +3362,19 @@
     <t xml:space="preserve">3.33322882652283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33944487571716</t>
+    <t xml:space="preserve">3.33944463729858</t>
   </si>
   <si>
     <t xml:space="preserve">3.33633685112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41325736045837</t>
+    <t xml:space="preserve">3.41325759887695</t>
   </si>
   <si>
     <t xml:space="preserve">3.37751650810242</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40471076965332</t>
+    <t xml:space="preserve">3.4047110080719</t>
   </si>
   <si>
     <t xml:space="preserve">3.60206270217896</t>
@@ -3389,16 +3389,16 @@
     <t xml:space="preserve">3.55855202674866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52203369140625</t>
+    <t xml:space="preserve">3.52203416824341</t>
   </si>
   <si>
     <t xml:space="preserve">3.51037955284119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44200563430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47619271278381</t>
+    <t xml:space="preserve">3.44200539588928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47619247436523</t>
   </si>
   <si>
     <t xml:space="preserve">3.44977521896362</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">3.38917112350464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34022164344788</t>
+    <t xml:space="preserve">3.3402214050293</t>
   </si>
   <si>
     <t xml:space="preserve">3.32545924186707</t>
@@ -3416,25 +3416,25 @@
     <t xml:space="preserve">3.34876823425293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27417898178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29904174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25630831718445</t>
+    <t xml:space="preserve">3.27417874336243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2990415096283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25630807876587</t>
   </si>
   <si>
     <t xml:space="preserve">3.26407790184021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24776148796082</t>
+    <t xml:space="preserve">3.24776124954224</t>
   </si>
   <si>
     <t xml:space="preserve">3.2788405418396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25786209106445</t>
+    <t xml:space="preserve">3.25786185264587</t>
   </si>
   <si>
     <t xml:space="preserve">3.24076867103577</t>
@@ -3464,16 +3464,16 @@
     <t xml:space="preserve">3.02632308006287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03098511695862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09158945083618</t>
+    <t xml:space="preserve">3.03098487854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0915892124176</t>
   </si>
   <si>
     <t xml:space="preserve">3.11956024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18016457557678</t>
+    <t xml:space="preserve">3.1801643371582</t>
   </si>
   <si>
     <t xml:space="preserve">3.22678303718567</t>
@@ -3485,10 +3485,10 @@
     <t xml:space="preserve">3.21202039718628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22989130020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23066806793213</t>
+    <t xml:space="preserve">3.22989106178284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23066782951355</t>
   </si>
   <si>
     <t xml:space="preserve">3.31458139419556</t>
@@ -3512,13 +3512,13 @@
     <t xml:space="preserve">3.38606309890747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33245182037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31302738189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33478260040283</t>
+    <t xml:space="preserve">3.33245205879211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31302762031555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33478236198425</t>
   </si>
   <si>
     <t xml:space="preserve">3.36120009422302</t>
@@ -3533,13 +3533,13 @@
     <t xml:space="preserve">3.36508464813232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39227938652039</t>
+    <t xml:space="preserve">3.39227914810181</t>
   </si>
   <si>
     <t xml:space="preserve">3.41248083114624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37207770347595</t>
+    <t xml:space="preserve">3.37207794189453</t>
   </si>
   <si>
     <t xml:space="preserve">3.39150190353394</t>
@@ -3569,22 +3569,22 @@
     <t xml:space="preserve">3.32312798500061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28971815109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18715763092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19725775718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29282569885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28661012649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22056722640991</t>
+    <t xml:space="preserve">3.28971838951111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18715739250183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19725751876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29282593727112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28661036491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22056746482849</t>
   </si>
   <si>
     <t xml:space="preserve">3.21745944023132</t>
@@ -3593,13 +3593,13 @@
     <t xml:space="preserve">3.21279764175415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20891308784485</t>
+    <t xml:space="preserve">3.20891284942627</t>
   </si>
   <si>
     <t xml:space="preserve">3.17627954483032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30758881568909</t>
+    <t xml:space="preserve">3.30758857727051</t>
   </si>
   <si>
     <t xml:space="preserve">3.33012080192566</t>
@@ -3614,10 +3614,10 @@
     <t xml:space="preserve">3.32623624801636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43268179893494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45443725585938</t>
+    <t xml:space="preserve">3.43268203735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45443749427795</t>
   </si>
   <si>
     <t xml:space="preserve">3.48085451126099</t>
@@ -3629,10 +3629,10 @@
     <t xml:space="preserve">3.61682558059692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57797622680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58652329444885</t>
+    <t xml:space="preserve">3.57797646522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58652353286743</t>
   </si>
   <si>
     <t xml:space="preserve">3.58963108062744</t>
@@ -3641,13 +3641,13 @@
     <t xml:space="preserve">3.5958468914032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57176089286804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57642245292664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.566321849823</t>
+    <t xml:space="preserve">3.57176065444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57642221450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56632208824158</t>
   </si>
   <si>
     <t xml:space="preserve">3.58108496665955</t>
@@ -3656,13 +3656,13 @@
     <t xml:space="preserve">3.68753004074097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63469552993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65178894996643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64246535301208</t>
+    <t xml:space="preserve">3.63469576835632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65178918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64246559143066</t>
   </si>
   <si>
     <t xml:space="preserve">3.62071013450623</t>
@@ -3671,10 +3671,10 @@
     <t xml:space="preserve">3.62692594528198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62148714065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61294054985046</t>
+    <t xml:space="preserve">3.62148666381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61294007301331</t>
   </si>
   <si>
     <t xml:space="preserve">3.61060929298401</t>
@@ -3689,19 +3689,19 @@
     <t xml:space="preserve">3.4482216835022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45132899284363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39694094657898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3953869342804</t>
+    <t xml:space="preserve">3.45132923126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39694118499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39538669586182</t>
   </si>
   <si>
     <t xml:space="preserve">3.26330089569092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22833704948425</t>
+    <t xml:space="preserve">3.22833728790283</t>
   </si>
   <si>
     <t xml:space="preserve">3.23999166488647</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">3.40004897117615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33711361885071</t>
+    <t xml:space="preserve">3.33711385726929</t>
   </si>
   <si>
     <t xml:space="preserve">3.36586141586304</t>
@@ -3737,13 +3737,13 @@
     <t xml:space="preserve">3.4816312789917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4971706867218</t>
+    <t xml:space="preserve">3.49717092514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.48707008361816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48862385749817</t>
+    <t xml:space="preserve">3.48862409591675</t>
   </si>
   <si>
     <t xml:space="preserve">3.51814913749695</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">3.52436494827271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48551630973816</t>
+    <t xml:space="preserve">3.48551607131958</t>
   </si>
   <si>
     <t xml:space="preserve">3.49794745445251</t>
@@ -3764,49 +3764,49 @@
     <t xml:space="preserve">3.64635038375854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70151615142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6960768699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64712738990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65567398071289</t>
+    <t xml:space="preserve">3.70151591300964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69607710838318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64712715148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65567374229431</t>
   </si>
   <si>
     <t xml:space="preserve">3.56865262985229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52824974060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49639391899109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35420680046082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40237998962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41092658042908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41558837890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46531510353088</t>
+    <t xml:space="preserve">3.52824997901917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49639415740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35420727729797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40237975120544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4109263420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41558814048767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4653148651123</t>
   </si>
   <si>
     <t xml:space="preserve">3.48240828514099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49017810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47075366973877</t>
+    <t xml:space="preserve">3.49017834663391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47075390815735</t>
   </si>
   <si>
     <t xml:space="preserve">3.45366048812866</t>
@@ -3815,40 +3815,40 @@
     <t xml:space="preserve">3.54301238059998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56321382522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75978922843933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62614846229553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79708361625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75124216079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65878200531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66188979148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54612016677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55622148513794</t>
+    <t xml:space="preserve">3.56321406364441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75978899002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62614893913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79708409309387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75124192237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65878224372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66188955307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54612040519714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55622124671936</t>
   </si>
   <si>
     <t xml:space="preserve">3.38373231887817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4225811958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16384768486023</t>
+    <t xml:space="preserve">3.42258143424988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16384792327881</t>
   </si>
   <si>
     <t xml:space="preserve">3.06361818313599</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">2.59898638725281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64715886116028</t>
+    <t xml:space="preserve">2.6471586227417</t>
   </si>
   <si>
     <t xml:space="preserve">2.83751797676086</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">2.74505758285522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82042455673218</t>
+    <t xml:space="preserve">2.8204243183136</t>
   </si>
   <si>
     <t xml:space="preserve">2.93308615684509</t>
@@ -3881,16 +3881,16 @@
     <t xml:space="preserve">2.91366147994995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0783805847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05118656158447</t>
+    <t xml:space="preserve">3.07838034629822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05118680000305</t>
   </si>
   <si>
     <t xml:space="preserve">3.05895614624023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06284117698669</t>
+    <t xml:space="preserve">3.06284093856812</t>
   </si>
   <si>
     <t xml:space="preserve">3.1622941493988</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">3.10246682167053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09780478477478</t>
+    <t xml:space="preserve">3.09780502319336</t>
   </si>
   <si>
     <t xml:space="preserve">3.13199210166931</t>
@@ -3917,34 +3917,34 @@
     <t xml:space="preserve">3.17161750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20269703865051</t>
+    <t xml:space="preserve">3.20269727706909</t>
   </si>
   <si>
     <t xml:space="preserve">3.09236621856689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35498428344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36275386810303</t>
+    <t xml:space="preserve">3.35498404502869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36275410652161</t>
   </si>
   <si>
     <t xml:space="preserve">3.37984728813171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40937256813049</t>
+    <t xml:space="preserve">3.40937232971191</t>
   </si>
   <si>
     <t xml:space="preserve">3.42335820198059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53058075904846</t>
+    <t xml:space="preserve">3.53058123588562</t>
   </si>
   <si>
     <t xml:space="preserve">3.59273934364319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51970362663269</t>
+    <t xml:space="preserve">3.51970314979553</t>
   </si>
   <si>
     <t xml:space="preserve">3.52747273445129</t>
@@ -3956,25 +3956,25 @@
     <t xml:space="preserve">3.6113862991333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69374632835388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63624954223633</t>
+    <t xml:space="preserve">3.6937460899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63624906539917</t>
   </si>
   <si>
     <t xml:space="preserve">3.6098325252533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36430811882019</t>
+    <t xml:space="preserve">3.36430788040161</t>
   </si>
   <si>
     <t xml:space="preserve">3.30059599876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38140177726746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46686887741089</t>
+    <t xml:space="preserve">3.38140153884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46686863899231</t>
   </si>
   <si>
     <t xml:space="preserve">3.51659536361694</t>
@@ -3983,22 +3983,22 @@
     <t xml:space="preserve">3.53524279594421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55078268051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56942963600159</t>
+    <t xml:space="preserve">3.55078220367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56942987442017</t>
   </si>
   <si>
     <t xml:space="preserve">3.51193332672119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63948941230774</t>
+    <t xml:space="preserve">3.63948965072632</t>
   </si>
   <si>
     <t xml:space="preserve">3.6378333568573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65771150588989</t>
+    <t xml:space="preserve">3.65771174430847</t>
   </si>
   <si>
     <t xml:space="preserve">3.71403574943542</t>
@@ -4019,7 +4019,7 @@
     <t xml:space="preserve">3.64942908287048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59310555458069</t>
+    <t xml:space="preserve">3.59310579299927</t>
   </si>
   <si>
     <t xml:space="preserve">3.59807538986206</t>
@@ -4037,13 +4037,13 @@
     <t xml:space="preserve">2.97686076164246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01993155479431</t>
+    <t xml:space="preserve">3.01993131637573</t>
   </si>
   <si>
     <t xml:space="preserve">3.0828812122345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97520399093628</t>
+    <t xml:space="preserve">2.97520422935486</t>
   </si>
   <si>
     <t xml:space="preserve">2.96692132949829</t>
@@ -4052,13 +4052,13 @@
     <t xml:space="preserve">3.01330518722534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98514366149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0000524520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96195125579834</t>
+    <t xml:space="preserve">2.98514342308044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00005269050598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96195149421692</t>
   </si>
   <si>
     <t xml:space="preserve">3.05968928337097</t>
@@ -4067,13 +4067,13 @@
     <t xml:space="preserve">3.03318405151367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04809308052063</t>
+    <t xml:space="preserve">3.04809331893921</t>
   </si>
   <si>
     <t xml:space="preserve">3.00999212265015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89734482765198</t>
+    <t xml:space="preserve">2.89734506607056</t>
   </si>
   <si>
     <t xml:space="preserve">2.90397143363953</t>
@@ -4094,13 +4094,13 @@
     <t xml:space="preserve">2.80457711219788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71512222290039</t>
+    <t xml:space="preserve">2.71512246131897</t>
   </si>
   <si>
     <t xml:space="preserve">2.70683932304382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69193029403687</t>
+    <t xml:space="preserve">2.69193005561829</t>
   </si>
   <si>
     <t xml:space="preserve">2.52792954444885</t>
@@ -4109,13 +4109,13 @@
     <t xml:space="preserve">2.64885926246643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71346569061279</t>
+    <t xml:space="preserve">2.71346545219421</t>
   </si>
   <si>
     <t xml:space="preserve">2.81120347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78138518333435</t>
+    <t xml:space="preserve">2.78138494491577</t>
   </si>
   <si>
     <t xml:space="preserve">2.79132437705994</t>
@@ -4130,7 +4130,7 @@
     <t xml:space="preserve">2.71843552589417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71677875518799</t>
+    <t xml:space="preserve">2.71677851676941</t>
   </si>
   <si>
     <t xml:space="preserve">2.7747585773468</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">2.83770871162415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84599161148071</t>
+    <t xml:space="preserve">2.84599137306213</t>
   </si>
   <si>
     <t xml:space="preserve">2.92385029792786</t>
@@ -4151,7 +4151,7 @@
     <t xml:space="preserve">2.97354745864868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95035552978516</t>
+    <t xml:space="preserve">2.95035576820374</t>
   </si>
   <si>
     <t xml:space="preserve">2.91225433349609</t>
@@ -4163,22 +4163,22 @@
     <t xml:space="preserve">2.93047666549683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98183035850525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98017406463623</t>
+    <t xml:space="preserve">2.98183012008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98017382621765</t>
   </si>
   <si>
     <t xml:space="preserve">2.92219400405884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93544602394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8542742729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75984978675842</t>
+    <t xml:space="preserve">2.93544626235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85427451133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75984954833984</t>
   </si>
   <si>
     <t xml:space="preserve">2.79960751533508</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">2.68696045875549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69358682632446</t>
+    <t xml:space="preserve">2.69358706474304</t>
   </si>
   <si>
     <t xml:space="preserve">2.64223313331604</t>
@@ -4238,25 +4238,25 @@
     <t xml:space="preserve">2.51799011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53621244430542</t>
+    <t xml:space="preserve">2.536212682724</t>
   </si>
   <si>
     <t xml:space="preserve">2.46663618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44344425201416</t>
+    <t xml:space="preserve">2.44344449043274</t>
   </si>
   <si>
     <t xml:space="preserve">2.37221193313599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42687892913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65051579475403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67702102661133</t>
+    <t xml:space="preserve">2.4268786907196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65051603317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67702126502991</t>
   </si>
   <si>
     <t xml:space="preserve">2.58259654045105</t>
@@ -4268,10 +4268,10 @@
     <t xml:space="preserve">2.53124260902405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52461647987366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42190885543823</t>
+    <t xml:space="preserve">2.52461624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42190909385681</t>
   </si>
   <si>
     <t xml:space="preserve">2.48651528358459</t>
@@ -4298,7 +4298,7 @@
     <t xml:space="preserve">2.59750533103943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62235403060913</t>
+    <t xml:space="preserve">2.62235426902771</t>
   </si>
   <si>
     <t xml:space="preserve">2.60413193702698</t>
@@ -4322,10 +4322,10 @@
     <t xml:space="preserve">2.86587023735046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95366859436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99839615821838</t>
+    <t xml:space="preserve">2.95366883277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9983959197998</t>
   </si>
   <si>
     <t xml:space="preserve">2.99342632293701</t>
@@ -4337,13 +4337,13 @@
     <t xml:space="preserve">2.98679995536804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00170946121216</t>
+    <t xml:space="preserve">3.00170922279358</t>
   </si>
   <si>
     <t xml:space="preserve">3.00833559036255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98348665237427</t>
+    <t xml:space="preserve">2.98348689079285</t>
   </si>
   <si>
     <t xml:space="preserve">3.00336575508118</t>
@@ -4352,22 +4352,22 @@
     <t xml:space="preserve">3.03484082221985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06631565093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04478025436401</t>
+    <t xml:space="preserve">3.06631541252136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04478001594543</t>
   </si>
   <si>
     <t xml:space="preserve">3.10441660881042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08619451522827</t>
+    <t xml:space="preserve">3.08619475364685</t>
   </si>
   <si>
     <t xml:space="preserve">2.94869875907898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91722416877747</t>
+    <t xml:space="preserve">2.91722393035889</t>
   </si>
   <si>
     <t xml:space="preserve">2.86255717277527</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">2.99176979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99673938751221</t>
+    <t xml:space="preserve">2.99673962593079</t>
   </si>
   <si>
     <t xml:space="preserve">3.03649711608887</t>
@@ -4406,22 +4406,22 @@
     <t xml:space="preserve">3.21375060081482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2518515586853</t>
+    <t xml:space="preserve">3.25185179710388</t>
   </si>
   <si>
     <t xml:space="preserve">3.22865962982178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.225346326828</t>
+    <t xml:space="preserve">3.22534656524658</t>
   </si>
   <si>
     <t xml:space="preserve">3.26013445854187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23031616210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20215463638306</t>
+    <t xml:space="preserve">3.23031640052795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20215439796448</t>
   </si>
   <si>
     <t xml:space="preserve">3.20546746253967</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">3.18724536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23528599739075</t>
+    <t xml:space="preserve">3.23528575897217</t>
   </si>
   <si>
     <t xml:space="preserve">3.2816698551178</t>
@@ -4439,28 +4439,28 @@
     <t xml:space="preserve">3.29657912254333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34627628326416</t>
+    <t xml:space="preserve">3.34627652168274</t>
   </si>
   <si>
     <t xml:space="preserve">3.32805395126343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34793281555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37443804740906</t>
+    <t xml:space="preserve">3.34793257713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37443780899048</t>
   </si>
   <si>
     <t xml:space="preserve">3.43904447555542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44235777854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29160952568054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29492235183716</t>
+    <t xml:space="preserve">3.44235754013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29160928726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29492259025574</t>
   </si>
   <si>
     <t xml:space="preserve">3.31811451911926</t>
@@ -4481,7 +4481,7 @@
     <t xml:space="preserve">3.49536776542664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43573093414307</t>
+    <t xml:space="preserve">3.43573117256165</t>
   </si>
   <si>
     <t xml:space="preserve">3.38437747955322</t>
@@ -4496,28 +4496,28 @@
     <t xml:space="preserve">3.34958958625793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38106393814087</t>
+    <t xml:space="preserve">3.38106417655945</t>
   </si>
   <si>
     <t xml:space="preserve">3.387690782547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39266037940979</t>
+    <t xml:space="preserve">3.39266061782837</t>
   </si>
   <si>
     <t xml:space="preserve">3.41088271141052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42082238197327</t>
+    <t xml:space="preserve">3.42082214355469</t>
   </si>
   <si>
     <t xml:space="preserve">3.42247867584229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37609457969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37775135040283</t>
+    <t xml:space="preserve">3.37609481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37775111198425</t>
   </si>
   <si>
     <t xml:space="preserve">3.34130644798279</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">3.13092184066772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02324485778809</t>
+    <t xml:space="preserve">3.02324461936951</t>
   </si>
   <si>
     <t xml:space="preserve">3.07625508308411</t>
@@ -4541,22 +4541,22 @@
     <t xml:space="preserve">3.13423490524292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1060733795166</t>
+    <t xml:space="preserve">3.10607314109802</t>
   </si>
   <si>
     <t xml:space="preserve">3.01164865493774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06465888023376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1093864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07459807395935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08453798294067</t>
+    <t xml:space="preserve">3.06465911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10938620567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07459831237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08453774452209</t>
   </si>
   <si>
     <t xml:space="preserve">3.11269927024841</t>
@@ -4574,7 +4574,7 @@
     <t xml:space="preserve">3.18393230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20381093025208</t>
+    <t xml:space="preserve">3.20381116867065</t>
   </si>
   <si>
     <t xml:space="preserve">3.14914417266846</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">3.11932587623596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04146695137024</t>
+    <t xml:space="preserve">3.04146671295166</t>
   </si>
   <si>
     <t xml:space="preserve">3.07294201850891</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">3.0514063835144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08785104751587</t>
+    <t xml:space="preserve">3.08785080909729</t>
   </si>
   <si>
     <t xml:space="preserve">3.053062915802</t>
@@ -71320,7 +71320,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6910185185</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>69253</v>
@@ -71329,7 +71329,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="D2501" t="n">
-        <v>6.1399998664856</v>
+        <v>6.13500022888184</v>
       </c>
       <c r="E2501" t="n">
         <v>6.19500017166138</v>
@@ -71341,6 +71341,32 @@
         <v>1981</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6911342593</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>140468</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>6.15999984741211</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>6.09000015258789</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>6.1399998664856</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>6.1399998664856</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1970</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="1990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="1991">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24674606323242</t>
+    <t xml:space="preserve">4.24674701690674</t>
   </si>
   <si>
     <t xml:space="preserve">ANIM.MI</t>
@@ -50,19 +50,19 @@
     <t xml:space="preserve">4.13419532775879</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96948671340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95301556587219</t>
+    <t xml:space="preserve">3.96948647499084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95301628112793</t>
   </si>
   <si>
     <t xml:space="preserve">3.94203495979309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07380247116089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93105459213257</t>
+    <t xml:space="preserve">4.07380342483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93105483055115</t>
   </si>
   <si>
     <t xml:space="preserve">3.82673907279968</t>
@@ -71,19 +71,19 @@
     <t xml:space="preserve">3.76085567474365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67850065231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73889374732971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40398621559143</t>
+    <t xml:space="preserve">3.67850041389465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73889398574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40398597717285</t>
   </si>
   <si>
     <t xml:space="preserve">3.53300786018372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76909041404724</t>
+    <t xml:space="preserve">3.76909112930298</t>
   </si>
   <si>
     <t xml:space="preserve">3.79379725456238</t>
@@ -92,73 +92,73 @@
     <t xml:space="preserve">3.79928731918335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88438630104065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67575573921204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70595192909241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6400682926178</t>
+    <t xml:space="preserve">3.88438725471497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67575550079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70595264434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64006853103638</t>
   </si>
   <si>
     <t xml:space="preserve">3.57967495918274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35731792449951</t>
+    <t xml:space="preserve">3.35731816291809</t>
   </si>
   <si>
     <t xml:space="preserve">3.4506528377533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37653493881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06633186340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9565269947052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19535446166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98397827148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24202227592468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20084428787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4863395690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38202404975891</t>
+    <t xml:space="preserve">3.3765344619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0663321018219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95652604103088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19535422325134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98397779464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24202275276184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20084452629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48633980751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38202428817749</t>
   </si>
   <si>
     <t xml:space="preserve">3.31065058708191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3875150680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26672792434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11299991607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08554840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07182264328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06084203720093</t>
+    <t xml:space="preserve">3.38751530647278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26672840118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11299967765808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08554816246033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07182288169861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06084156036377</t>
   </si>
   <si>
     <t xml:space="preserve">3.15692210197449</t>
@@ -167,94 +167,94 @@
     <t xml:space="preserve">3.30241537094116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43967318534851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35182857513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28319907188416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2228057384491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25300216674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57693028450012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47261476516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46437883377075</t>
+    <t xml:space="preserve">3.43967294692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3518283367157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.283198595047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22280597686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25300240516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57693004608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47261452674866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46437907218933</t>
   </si>
   <si>
     <t xml:space="preserve">3.590656042099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56320476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61261749267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51653695106506</t>
+    <t xml:space="preserve">3.56320381164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61261701583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51653718948364</t>
   </si>
   <si>
     <t xml:space="preserve">3.43418216705322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37104368209839</t>
+    <t xml:space="preserve">3.37104344367981</t>
   </si>
   <si>
     <t xml:space="preserve">3.45888876914978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53026342391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32986640930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27221846580505</t>
+    <t xml:space="preserve">3.53026270866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3298671245575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2722179889679</t>
   </si>
   <si>
     <t xml:space="preserve">3.09103894233704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23653173446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34084701538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28594446182251</t>
+    <t xml:space="preserve">3.23653149604797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34084725379944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28594470024109</t>
   </si>
   <si>
     <t xml:space="preserve">3.31888604164124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23927664756775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42594742774963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41771173477173</t>
+    <t xml:space="preserve">3.23927640914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4259467124939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41771149635315</t>
   </si>
   <si>
     <t xml:space="preserve">3.40947580337524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41496610641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44241690635681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46163320541382</t>
+    <t xml:space="preserve">3.41496634483337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44241762161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46163415908813</t>
   </si>
   <si>
     <t xml:space="preserve">3.44790863990784</t>
@@ -263,43 +263,43 @@
     <t xml:space="preserve">3.49732065200806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39300560951233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37378931045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26123762130737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2694730758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15417766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16241264343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01966500282288</t>
+    <t xml:space="preserve">3.39300513267517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3737895488739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26123809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26947402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15417718887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1624128818512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01966452598572</t>
   </si>
   <si>
     <t xml:space="preserve">2.94829082489014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82201385498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93181991577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0690770149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00044894218445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91809415817261</t>
+    <t xml:space="preserve">2.82201409339905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93182015419006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06907725334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00044918060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91809439659119</t>
   </si>
   <si>
     <t xml:space="preserve">2.8741717338562</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">2.85221028327942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89064264297485</t>
+    <t xml:space="preserve">2.89064288139343</t>
   </si>
   <si>
     <t xml:space="preserve">2.97133898735046</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">3.23648285865784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24224710464478</t>
+    <t xml:space="preserve">3.24224662780762</t>
   </si>
   <si>
     <t xml:space="preserve">3.29988646507263</t>
@@ -329,34 +329,34 @@
     <t xml:space="preserve">3.17884302139282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15866875648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04050755500793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97998428344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96269273757935</t>
+    <t xml:space="preserve">3.15866899490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04050707817078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97998452186584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9626932144165</t>
   </si>
   <si>
     <t xml:space="preserve">3.02321457862854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00015926361084</t>
+    <t xml:space="preserve">3.00015902519226</t>
   </si>
   <si>
     <t xml:space="preserve">2.95692849159241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81859254837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7966902256012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66988205909729</t>
+    <t xml:space="preserve">2.81859278678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79668974876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66988182067871</t>
   </si>
   <si>
     <t xml:space="preserve">2.61454749107361</t>
@@ -374,34 +374,34 @@
     <t xml:space="preserve">2.90505313873291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92234468460083</t>
+    <t xml:space="preserve">2.92234492301941</t>
   </si>
   <si>
     <t xml:space="preserve">2.96845650672913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53615689277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26179122924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49004507064819</t>
+    <t xml:space="preserve">2.53615713119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26179146766663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49004530906677</t>
   </si>
   <si>
     <t xml:space="preserve">2.41972422599792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4266414642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49235081672668</t>
+    <t xml:space="preserve">2.42664122581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49235057830811</t>
   </si>
   <si>
     <t xml:space="preserve">2.36900115013123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28830552101135</t>
+    <t xml:space="preserve">2.28830575942993</t>
   </si>
   <si>
     <t xml:space="preserve">2.29752779006958</t>
@@ -410,67 +410,67 @@
     <t xml:space="preserve">2.30559754371643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35747337341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4324049949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61108899116516</t>
+    <t xml:space="preserve">2.35747313499451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43240523338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61108875274658</t>
   </si>
   <si>
     <t xml:space="preserve">2.59379744529724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68025708198547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59725522994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60647773742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56958794593811</t>
+    <t xml:space="preserve">2.68025732040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59725546836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60647797584534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56958770751953</t>
   </si>
   <si>
     <t xml:space="preserve">2.62838125228882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6226167678833</t>
+    <t xml:space="preserve">2.62261700630188</t>
   </si>
   <si>
     <t xml:space="preserve">2.59494996070862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6168532371521</t>
+    <t xml:space="preserve">2.61685371398926</t>
   </si>
   <si>
     <t xml:space="preserve">2.54653239250183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63414525985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58226895332336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40358519554138</t>
+    <t xml:space="preserve">2.6341450214386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58226919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4035849571228</t>
   </si>
   <si>
     <t xml:space="preserve">2.4151132106781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43816947937012</t>
+    <t xml:space="preserve">2.43816924095154</t>
   </si>
   <si>
     <t xml:space="preserve">2.55114364624023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58572793006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6514368057251</t>
+    <t xml:space="preserve">2.58572769165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65143704414368</t>
   </si>
   <si>
     <t xml:space="preserve">2.65489530563354</t>
@@ -482,64 +482,64 @@
     <t xml:space="preserve">2.54307436943054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41857147216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37015414237976</t>
+    <t xml:space="preserve">2.41857123374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37015390396118</t>
   </si>
   <si>
     <t xml:space="preserve">2.3932101726532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51310133934021</t>
+    <t xml:space="preserve">2.51310157775879</t>
   </si>
   <si>
     <t xml:space="preserve">2.50964283943176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46122527122498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44854426383972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50733709335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50157308578491</t>
+    <t xml:space="preserve">2.4612250328064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44854402542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50733685493469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50157356262207</t>
   </si>
   <si>
     <t xml:space="preserve">2.49696230888367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51540660858154</t>
+    <t xml:space="preserve">2.5154070854187</t>
   </si>
   <si>
     <t xml:space="preserve">2.53039360046387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57304692268372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66181206703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62722826004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73789715766907</t>
+    <t xml:space="preserve">2.57304716110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66181254386902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6272280216217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73789739608765</t>
   </si>
   <si>
     <t xml:space="preserve">2.83012080192566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79092574119568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67449331283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65604853630066</t>
+    <t xml:space="preserve">2.79092597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67449355125427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65604829788208</t>
   </si>
   <si>
     <t xml:space="preserve">2.64797878265381</t>
@@ -554,217 +554,217 @@
     <t xml:space="preserve">2.52001786231995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51886487007141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49580955505371</t>
+    <t xml:space="preserve">2.51886534690857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49580931663513</t>
   </si>
   <si>
     <t xml:space="preserve">2.5211706161499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52462887763977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54192161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47275352478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46929526329041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39436268806458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32173657417297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32519507408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24795722961426</t>
+    <t xml:space="preserve">2.52462911605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54192137718201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47275304794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46929550170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39436316490173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32173633575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32519483566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24795770645142</t>
   </si>
   <si>
     <t xml:space="preserve">2.26524949073792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32634830474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38629341125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4439332485199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44623875617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5707414150238</t>
+    <t xml:space="preserve">2.32634735107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3862931728363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44393301010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44623899459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57074093818665</t>
   </si>
   <si>
     <t xml:space="preserve">2.57996344566345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56267142295837</t>
+    <t xml:space="preserve">2.56267166137695</t>
   </si>
   <si>
     <t xml:space="preserve">2.55806064605713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5038788318634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50503158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38168239593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60993647575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59956097602844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55344915390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70907711982727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67910432815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58111596107483</t>
+    <t xml:space="preserve">2.50387907028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50503134727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38168215751648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60993599891663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59956073760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55344891548157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70907759666443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67910408973694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58111619949341</t>
   </si>
   <si>
     <t xml:space="preserve">2.80130124092102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81282925605774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7229106426239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78285646438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82551002502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92522692680359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96557450294495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91081690788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00592279434204</t>
+    <t xml:space="preserve">2.81282901763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72291088104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78285622596741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82551050186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92522716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96557474136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91081643104553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00592255592346</t>
   </si>
   <si>
     <t xml:space="preserve">3.03474283218384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99727725982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98574805259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94828248023987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93963718414307</t>
+    <t xml:space="preserve">2.99727654457092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98574829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94828271865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93963670730591</t>
   </si>
   <si>
     <t xml:space="preserve">2.97422122955322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99151301383972</t>
+    <t xml:space="preserve">2.9915132522583</t>
   </si>
   <si>
     <t xml:space="preserve">3.014568567276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0318603515625</t>
+    <t xml:space="preserve">3.03186082839966</t>
   </si>
   <si>
     <t xml:space="preserve">3.16155076026917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13849472999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11255645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12984824180603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20478081703186</t>
+    <t xml:space="preserve">3.13849449157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11255669593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12984871864319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2047803401947</t>
   </si>
   <si>
     <t xml:space="preserve">3.16443252563477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19613432884216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19901728630066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12408518791199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14137673377991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08373737335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30276894569397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26242089271545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18748879432678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28547596931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22783660888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17596006393433</t>
+    <t xml:space="preserve">3.19613456726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19901704788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12408542633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14137649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08373713493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30276918411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26242065429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18748927116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28547620773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2278368473053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17596030235291</t>
   </si>
   <si>
     <t xml:space="preserve">3.24800992012024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26818466186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23936462402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09238243103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10102844238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0549168586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08085441589355</t>
+    <t xml:space="preserve">3.26818442344666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23936438560486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09238290786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10102868080139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05491709709167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08085489273071</t>
   </si>
   <si>
     <t xml:space="preserve">3.11832094192505</t>
@@ -773,40 +773,40 @@
     <t xml:space="preserve">3.15002298355103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0116868019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92810869216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95404648780823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78516221046448</t>
+    <t xml:space="preserve">3.01168704032898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92810893058777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95404696464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7851619720459</t>
   </si>
   <si>
     <t xml:space="preserve">2.91369867324829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9886314868927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00304079055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0260968208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07797265052795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05779910087585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18172478675842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1701967716217</t>
+    <t xml:space="preserve">2.98863101005554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0030403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02609634399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07797312736511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05779886245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18172454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17019653320312</t>
   </si>
   <si>
     <t xml:space="preserve">3.23360061645508</t>
@@ -815,55 +815,55 @@
     <t xml:space="preserve">3.24512887001038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25089240074158</t>
+    <t xml:space="preserve">3.25089311599731</t>
   </si>
   <si>
     <t xml:space="preserve">3.27106690406799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27394843101501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28259468078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25665616989136</t>
+    <t xml:space="preserve">3.27394914627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28259444236755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2566556930542</t>
   </si>
   <si>
     <t xml:space="preserve">3.18460655212402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29412198066711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10391116142273</t>
+    <t xml:space="preserve">3.29412221908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10391068458557</t>
   </si>
   <si>
     <t xml:space="preserve">3.34023451805115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44398713111877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43245816230774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46415996551514</t>
+    <t xml:space="preserve">3.44398641586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43245911598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46415972709656</t>
   </si>
   <si>
     <t xml:space="preserve">3.45839643478394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49298000335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44686818122864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50450801849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6024968624115</t>
+    <t xml:space="preserve">3.49298024177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44686794281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50450825691223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60249614715576</t>
   </si>
   <si>
     <t xml:space="preserve">3.51603627204895</t>
@@ -875,46 +875,46 @@
     <t xml:space="preserve">3.44110417366028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4238121509552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41228461265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39499282836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37193608283997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48935294151306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49236297607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59472489356995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72117352485657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71515130996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58870387077332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46827793121338</t>
+    <t xml:space="preserve">3.42381238937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41228437423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39499235153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37193584442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48935174942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49236249923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5947253704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72117304801941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71515202522278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58870363235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46827721595764</t>
   </si>
   <si>
     <t xml:space="preserve">3.41107535362244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49838399887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54053330421448</t>
+    <t xml:space="preserve">3.49838447570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54053354263306</t>
   </si>
   <si>
     <t xml:space="preserve">3.50440573692322</t>
@@ -923,10 +923,10 @@
     <t xml:space="preserve">3.51644825935364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54956531524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70912957191467</t>
+    <t xml:space="preserve">3.549565076828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70913004875183</t>
   </si>
   <si>
     <t xml:space="preserve">3.7241837978363</t>
@@ -935,43 +935,43 @@
     <t xml:space="preserve">3.64891695976257</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75127959251404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72719407081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76332259178162</t>
+    <t xml:space="preserve">3.75127911567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72719430923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76332211494446</t>
   </si>
   <si>
     <t xml:space="preserve">3.73923635482788</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74525833129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7121410369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70310974121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75730061531067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7753643989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77837538719177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8415994644165</t>
+    <t xml:space="preserve">3.74525737762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71214151382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70310926437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75730085372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77536463737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77837610244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84160017967224</t>
   </si>
   <si>
     <t xml:space="preserve">3.85966348648071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82654595375061</t>
+    <t xml:space="preserve">3.82654547691345</t>
   </si>
   <si>
     <t xml:space="preserve">4.09750556945801</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">4.17277193069458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19083595275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22094297409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.199866771698</t>
+    <t xml:space="preserve">4.19083547592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22094249725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19986772537231</t>
   </si>
   <si>
     <t xml:space="preserve">4.2450270652771</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">4.21492147445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15470790863037</t>
+    <t xml:space="preserve">4.15470743179321</t>
   </si>
   <si>
     <t xml:space="preserve">4.14567613601685</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">4.13664436340332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22395372390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22696304321289</t>
+    <t xml:space="preserve">4.22395277023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22696352005005</t>
   </si>
   <si>
     <t xml:space="preserve">4.33534717559814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25104856491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28717660903931</t>
+    <t xml:space="preserve">4.25104951858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28717565536499</t>
   </si>
   <si>
     <t xml:space="preserve">4.11857986450195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25405931472778</t>
+    <t xml:space="preserve">4.25405979156494</t>
   </si>
   <si>
     <t xml:space="preserve">4.09449481964111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08847332000732</t>
+    <t xml:space="preserve">4.08847284317017</t>
   </si>
   <si>
     <t xml:space="preserve">4.04030275344849</t>
@@ -1049,70 +1049,70 @@
     <t xml:space="preserve">4.05234527587891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95901489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86267328262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86568403244019</t>
+    <t xml:space="preserve">3.95901536941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86267375946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86568427085876</t>
   </si>
   <si>
     <t xml:space="preserve">3.94396162033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94697260856628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95600461959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98008966445923</t>
+    <t xml:space="preserve">3.94697213172913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95600438117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98009014129639</t>
   </si>
   <si>
     <t xml:space="preserve">3.9740686416626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07341957092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06438779830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98912167549133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96202516555786</t>
+    <t xml:space="preserve">4.07342004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06438827514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98912191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9620258808136</t>
   </si>
   <si>
     <t xml:space="preserve">4.01320600509644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0342812538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00417518615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00116395950317</t>
+    <t xml:space="preserve">4.03428077697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00417470932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00116443634033</t>
   </si>
   <si>
     <t xml:space="preserve">3.90783381462097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88977026939392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95299363136292</t>
+    <t xml:space="preserve">3.88976955413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95299410820007</t>
   </si>
   <si>
     <t xml:space="preserve">4.0101957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11255788803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15771818161011</t>
+    <t xml:space="preserve">4.11255836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15771865844727</t>
   </si>
   <si>
     <t xml:space="preserve">4.06739902496338</t>
@@ -1124,16 +1124,16 @@
     <t xml:space="preserve">3.93191885948181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9018120765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87471652030945</t>
+    <t xml:space="preserve">3.90181231498718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87471675872803</t>
   </si>
   <si>
     <t xml:space="preserve">3.8536422252655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82353496551514</t>
+    <t xml:space="preserve">3.82353448867798</t>
   </si>
   <si>
     <t xml:space="preserve">3.89579153060913</t>
@@ -1142,28 +1142,28 @@
     <t xml:space="preserve">3.84762024879456</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8325674533844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88073825836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88374805450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92589712142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92890810966492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88675951957703</t>
+    <t xml:space="preserve">3.83256816864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88073778152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88374829292297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9258975982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9289083480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88675928115845</t>
   </si>
   <si>
     <t xml:space="preserve">3.9138548374176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91084408760071</t>
+    <t xml:space="preserve">3.91084432601929</t>
   </si>
   <si>
     <t xml:space="preserve">3.84460973739624</t>
@@ -1172,31 +1172,31 @@
     <t xml:space="preserve">3.82052516937256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69106650352478</t>
+    <t xml:space="preserve">3.69106674194336</t>
   </si>
   <si>
     <t xml:space="preserve">3.70611953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55558705329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47429895401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33580851554871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40204286575317</t>
+    <t xml:space="preserve">3.55558681488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47429871559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33580875396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40204334259033</t>
   </si>
   <si>
     <t xml:space="preserve">3.52246928215027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54354405403137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53150081634521</t>
+    <t xml:space="preserve">3.54354381561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53150153160095</t>
   </si>
   <si>
     <t xml:space="preserve">3.57365083694458</t>
@@ -1214,16 +1214,16 @@
     <t xml:space="preserve">3.55257630348206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50139427185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45021367073059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51042675971985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48634195327759</t>
+    <t xml:space="preserve">3.50139474868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45021390914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51042699813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48634147644043</t>
   </si>
   <si>
     <t xml:space="preserve">3.43817114830017</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">3.40806460380554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53451204299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60977816581726</t>
+    <t xml:space="preserve">3.53451180458069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6097776889801</t>
   </si>
   <si>
     <t xml:space="preserve">3.35387253761292</t>
@@ -1244,37 +1244,37 @@
     <t xml:space="preserve">3.42612814903259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4441921710968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32376599311829</t>
+    <t xml:space="preserve">3.44419264793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32376623153687</t>
   </si>
   <si>
     <t xml:space="preserve">3.39000082015991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61278939247131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73020505905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66698050498962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64590644836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63386392593384</t>
+    <t xml:space="preserve">3.61278891563416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73020434379578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66698026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64590716362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63386368751526</t>
   </si>
   <si>
     <t xml:space="preserve">3.81450295448303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8686945438385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93492913246155</t>
+    <t xml:space="preserve">3.86869502067566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93492937088013</t>
   </si>
   <si>
     <t xml:space="preserve">4.04331350326538</t>
@@ -1283,31 +1283,31 @@
     <t xml:space="preserve">3.99213194847107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98309993743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06137752532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1246018409729</t>
+    <t xml:space="preserve">3.98310041427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06137704849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12460088729858</t>
   </si>
   <si>
     <t xml:space="preserve">4.160728931427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07040929794312</t>
+    <t xml:space="preserve">4.07040882110596</t>
   </si>
   <si>
     <t xml:space="preserve">4.08245182037354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80848240852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89880228042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91987657546997</t>
+    <t xml:space="preserve">3.8084819316864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89880156517029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91987609863281</t>
   </si>
   <si>
     <t xml:space="preserve">3.78439617156982</t>
@@ -1316,58 +1316,58 @@
     <t xml:space="preserve">3.77235412597656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7994499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7362265586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75429058074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76633286476135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63988542556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.561607837677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66999197006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96503615379333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7934296131134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74224758148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79164981842041</t>
+    <t xml:space="preserve">3.79945063591003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73622632026672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75429081916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76633214950562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63988518714905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56160807609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66999173164368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96503639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79342889785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74224734306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79164934158325</t>
   </si>
   <si>
     <t xml:space="preserve">3.77612209320068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78854417800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70469903945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58358979225159</t>
+    <t xml:space="preserve">3.78854322433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70469856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58358931541443</t>
   </si>
   <si>
     <t xml:space="preserve">3.55914258956909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55258822441101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51326107978821</t>
+    <t xml:space="preserve">3.55258846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51326060295105</t>
   </si>
   <si>
     <t xml:space="preserve">3.61157989501953</t>
@@ -1376,46 +1376,46 @@
     <t xml:space="preserve">3.58536100387573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7688901424408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89998197555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8934268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85082221031189</t>
+    <t xml:space="preserve">3.76888990402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89998126029968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89342737197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85082244873047</t>
   </si>
   <si>
     <t xml:space="preserve">3.81149482727051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63779878616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7557806968689</t>
+    <t xml:space="preserve">3.63779830932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75578045845032</t>
   </si>
   <si>
     <t xml:space="preserve">3.73939418792725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86065435409546</t>
+    <t xml:space="preserve">3.86065411567688</t>
   </si>
   <si>
     <t xml:space="preserve">3.84099054336548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81804943084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96552753448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98846840858459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93275499343872</t>
+    <t xml:space="preserve">3.81804919242859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96552777290344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98846864700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93275451660156</t>
   </si>
   <si>
     <t xml:space="preserve">3.86720895767212</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">3.84426760673523</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91309022903442</t>
+    <t xml:space="preserve">3.913090467453</t>
   </si>
   <si>
     <t xml:space="preserve">3.8213267326355</t>
@@ -1433,52 +1433,52 @@
     <t xml:space="preserve">4.03107357025146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04418277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02451848983765</t>
+    <t xml:space="preserve">4.04418230056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02451944351196</t>
   </si>
   <si>
     <t xml:space="preserve">3.98191380500793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90653610229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99830102920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77544450759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76561260223389</t>
+    <t xml:space="preserve">3.90653657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99830055236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77544474601746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76561212539673</t>
   </si>
   <si>
     <t xml:space="preserve">3.71973085403442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71645283699036</t>
+    <t xml:space="preserve">3.71645331382751</t>
   </si>
   <si>
     <t xml:space="preserve">3.56897497177124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50670647621155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46737861633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27467393875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93645668029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03477549552917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19077491760254</t>
+    <t xml:space="preserve">3.50670599937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46737837791443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27467322349548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93645691871643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03477621078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19077444076538</t>
   </si>
   <si>
     <t xml:space="preserve">3.42149662971497</t>
@@ -1493,19 +1493,19 @@
     <t xml:space="preserve">3.3166229724884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35595083236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21174955368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30023670196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32645511627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3985550403595</t>
+    <t xml:space="preserve">3.35595059394836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.211749792099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30023646354675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32645463943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39855480194092</t>
   </si>
   <si>
     <t xml:space="preserve">3.33956432342529</t>
@@ -1514,34 +1514,34 @@
     <t xml:space="preserve">3.29040503501892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27729558944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28057312965393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18290901184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12260699272156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07148146629333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01511168479919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89975094795227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01904487609863</t>
+    <t xml:space="preserve">3.27729535102844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28057289123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1829092502594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12260723114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07148122787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01511192321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89975118637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01904463768005</t>
   </si>
   <si>
     <t xml:space="preserve">3.01380085945129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04919600486755</t>
+    <t xml:space="preserve">3.04919576644897</t>
   </si>
   <si>
     <t xml:space="preserve">2.97971725463867</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">3.02691006660461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13440585136414</t>
+    <t xml:space="preserve">3.13440561294556</t>
   </si>
   <si>
     <t xml:space="preserve">3.10425424575806</t>
@@ -1559,34 +1559,34 @@
     <t xml:space="preserve">3.04264140129089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00200247764587</t>
+    <t xml:space="preserve">3.00200295448303</t>
   </si>
   <si>
     <t xml:space="preserve">3.00462460517883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98233914375305</t>
+    <t xml:space="preserve">2.98233938217163</t>
   </si>
   <si>
     <t xml:space="preserve">2.98627185821533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92072534561157</t>
+    <t xml:space="preserve">2.92072582244873</t>
   </si>
   <si>
     <t xml:space="preserve">2.92728042602539</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00069165229797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01249003410339</t>
+    <t xml:space="preserve">3.00069189071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01249027252197</t>
   </si>
   <si>
     <t xml:space="preserve">3.03739762306213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95612096786499</t>
+    <t xml:space="preserve">2.95612072944641</t>
   </si>
   <si>
     <t xml:space="preserve">2.92465853691101</t>
@@ -1595,13 +1595,13 @@
     <t xml:space="preserve">2.84469270706177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97709512710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00724625587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89057445526123</t>
+    <t xml:space="preserve">2.97709536552429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00724601745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89057469367981</t>
   </si>
   <si>
     <t xml:space="preserve">2.77259206771851</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">2.71228981018066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70049142837524</t>
+    <t xml:space="preserve">2.70049118995667</t>
   </si>
   <si>
     <t xml:space="preserve">2.77914643287659</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">2.76997017860413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73719763755798</t>
+    <t xml:space="preserve">2.73719716072083</t>
   </si>
   <si>
     <t xml:space="preserve">2.72146606445312</t>
@@ -1637,10 +1637,10 @@
     <t xml:space="preserve">2.63625645637512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64936566352844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62052536010742</t>
+    <t xml:space="preserve">2.64936542510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.620525598526</t>
   </si>
   <si>
     <t xml:space="preserve">2.67689514160156</t>
@@ -1652,67 +1652,67 @@
     <t xml:space="preserve">2.87615466117859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85124731063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86697816848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93907928466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91154932975769</t>
+    <t xml:space="preserve">2.85124683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86697840690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93907880783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91154956817627</t>
   </si>
   <si>
     <t xml:space="preserve">2.91679286956787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92596960067749</t>
+    <t xml:space="preserve">2.92596983909607</t>
   </si>
   <si>
     <t xml:space="preserve">2.94170045852661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99806928634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04133009910583</t>
+    <t xml:space="preserve">2.99807024002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04133033752441</t>
   </si>
   <si>
     <t xml:space="preserve">2.99675893783569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99413681030273</t>
+    <t xml:space="preserve">2.99413704872131</t>
   </si>
   <si>
     <t xml:space="preserve">2.96267533302307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96005320549011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91286015510559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77521371841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70704627037048</t>
+    <t xml:space="preserve">2.96005344390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91285991668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77521419525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7070460319519</t>
   </si>
   <si>
     <t xml:space="preserve">2.68869352340698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.705735206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74244117736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64674401283264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64150047302246</t>
+    <t xml:space="preserve">2.70573496818542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74244070053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64674377441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64150023460388</t>
   </si>
   <si>
     <t xml:space="preserve">2.59692883491516</t>
@@ -1721,10 +1721,10 @@
     <t xml:space="preserve">2.38193845748901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46714806556702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44879531860352</t>
+    <t xml:space="preserve">2.4671483039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44879508018494</t>
   </si>
   <si>
     <t xml:space="preserve">2.49074459075928</t>
@@ -1736,31 +1736,31 @@
     <t xml:space="preserve">2.48681211471558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41995525360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31639266014099</t>
+    <t xml:space="preserve">2.4199550151825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31639242172241</t>
   </si>
   <si>
     <t xml:space="preserve">2.25871205329895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20365333557129</t>
+    <t xml:space="preserve">2.20365357398987</t>
   </si>
   <si>
     <t xml:space="preserve">2.25215744972229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28493070602417</t>
+    <t xml:space="preserve">2.28493046760559</t>
   </si>
   <si>
     <t xml:space="preserve">2.38587117195129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39242601394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42519879341125</t>
+    <t xml:space="preserve">2.39242577552795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42519903182983</t>
   </si>
   <si>
     <t xml:space="preserve">2.45928263664246</t>
@@ -1781,25 +1781,25 @@
     <t xml:space="preserve">2.47501349449158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54842495918274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43044233322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40815687179565</t>
+    <t xml:space="preserve">2.54842519760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43044257164001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40815663337708</t>
   </si>
   <si>
     <t xml:space="preserve">2.33998894691467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28886342048645</t>
+    <t xml:space="preserve">2.28886318206787</t>
   </si>
   <si>
     <t xml:space="preserve">2.27968692779541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25740098953247</t>
+    <t xml:space="preserve">2.25740122795105</t>
   </si>
   <si>
     <t xml:space="preserve">2.17612409591675</t>
@@ -1820,31 +1820,31 @@
     <t xml:space="preserve">2.39766931533813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44748425483704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4238874912262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40946769714355</t>
+    <t xml:space="preserve">2.44748449325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42388796806335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40946817398071</t>
   </si>
   <si>
     <t xml:space="preserve">2.40029096603394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21938443183899</t>
+    <t xml:space="preserve">2.21938467025757</t>
   </si>
   <si>
     <t xml:space="preserve">2.19447708129883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25477933883667</t>
+    <t xml:space="preserve">2.25477957725525</t>
   </si>
   <si>
     <t xml:space="preserve">2.31901454925537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32687997817993</t>
+    <t xml:space="preserve">2.32687973976135</t>
   </si>
   <si>
     <t xml:space="preserve">2.26264452934265</t>
@@ -1853,49 +1853,49 @@
     <t xml:space="preserve">2.17743515968323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12893104553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14597320556641</t>
+    <t xml:space="preserve">2.12893152236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14597296714783</t>
   </si>
   <si>
     <t xml:space="preserve">2.12237668037415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12368750572205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10271286964417</t>
+    <t xml:space="preserve">2.12368774414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10271310806274</t>
   </si>
   <si>
     <t xml:space="preserve">2.11713314056396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14728403091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15121674537659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23904800415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20758652687073</t>
+    <t xml:space="preserve">2.14728426933289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15121698379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23904824256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20758605003357</t>
   </si>
   <si>
     <t xml:space="preserve">2.36489629745483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34785437583923</t>
+    <t xml:space="preserve">2.34785485267639</t>
   </si>
   <si>
     <t xml:space="preserve">2.37407279014587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25084662437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39504766464233</t>
+    <t xml:space="preserve">2.25084638595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39504742622375</t>
   </si>
   <si>
     <t xml:space="preserve">2.35572004318237</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">2.44224047660828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43175339698792</t>
+    <t xml:space="preserve">2.43175315856934</t>
   </si>
   <si>
     <t xml:space="preserve">2.38456010818481</t>
@@ -1922,22 +1922,22 @@
     <t xml:space="preserve">2.35309815406799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34654331207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35440921783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37145066261292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28755235671997</t>
+    <t xml:space="preserve">2.34654355049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35440897941589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37145113945007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28755211830139</t>
   </si>
   <si>
     <t xml:space="preserve">2.26788854598999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31114912033081</t>
+    <t xml:space="preserve">2.31114888191223</t>
   </si>
   <si>
     <t xml:space="preserve">2.37931656837463</t>
@@ -1946,37 +1946,37 @@
     <t xml:space="preserve">2.40291309356689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40553498268127</t>
+    <t xml:space="preserve">2.4055347442627</t>
   </si>
   <si>
     <t xml:space="preserve">2.37014007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33605623245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39898014068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37669444084167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50123190879822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54318141937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52613949775696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5038537979126</t>
+    <t xml:space="preserve">2.33605599403381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39898037910461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37669467926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5012321472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54318165779114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52613925933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50385355949402</t>
   </si>
   <si>
     <t xml:space="preserve">2.49336647987366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42782068252563</t>
+    <t xml:space="preserve">2.42782044410706</t>
   </si>
   <si>
     <t xml:space="preserve">2.39635848999023</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">2.38718199729919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37276172637939</t>
+    <t xml:space="preserve">2.37276196479797</t>
   </si>
   <si>
     <t xml:space="preserve">2.37800574302673</t>
@@ -1997,25 +1997,25 @@
     <t xml:space="preserve">2.29935050010681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38062739372253</t>
+    <t xml:space="preserve">2.38062763214111</t>
   </si>
   <si>
     <t xml:space="preserve">2.30459427833557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38849282264709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45666074752808</t>
+    <t xml:space="preserve">2.38849306106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45666098594666</t>
   </si>
   <si>
     <t xml:space="preserve">2.40160226821899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34130001068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34392189979553</t>
+    <t xml:space="preserve">2.34129977226257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34392166137695</t>
   </si>
   <si>
     <t xml:space="preserve">2.38324928283691</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">2.32556915283203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30328369140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30590510368347</t>
+    <t xml:space="preserve">2.30328321456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30590534210205</t>
   </si>
   <si>
     <t xml:space="preserve">2.34523272514343</t>
@@ -2039,13 +2039,13 @@
     <t xml:space="preserve">2.30983781814575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21545171737671</t>
+    <t xml:space="preserve">2.21545195579529</t>
   </si>
   <si>
     <t xml:space="preserve">2.19054436683655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09091472625732</t>
+    <t xml:space="preserve">2.09091448783875</t>
   </si>
   <si>
     <t xml:space="preserve">2.08698177337646</t>
@@ -2060,73 +2060,73 @@
     <t xml:space="preserve">1.97686457633972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9912850856781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97817540168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98996305465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99967038631439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97470903396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94420063495636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9192396402359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89843821525574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86377012729645</t>
+    <t xml:space="preserve">1.99128496646881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97817528247833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98996269702911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99966990947723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97470891475677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94420051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91923928260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89843845367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86377000808716</t>
   </si>
   <si>
     <t xml:space="preserve">1.82632827758789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87625110149384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87902414798737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83742225170135</t>
+    <t xml:space="preserve">1.87625086307526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87902426719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83742213249207</t>
   </si>
   <si>
     <t xml:space="preserve">1.9511342048645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92755997180939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89982521533966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92062640190125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90953230857849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9067587852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88734447956085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88873136043549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88179779052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02879118919373</t>
+    <t xml:space="preserve">1.92755973339081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89982497692108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92062604427338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90953242778778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90675890445709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88734459877014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88873112201691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88179767131805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02879166603088</t>
   </si>
   <si>
     <t xml:space="preserve">1.98302924633026</t>
@@ -2135,34 +2135,34 @@
     <t xml:space="preserve">2.03156495094299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98857629299164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95945465564728</t>
+    <t xml:space="preserve">1.98857617378235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95945477485657</t>
   </si>
   <si>
     <t xml:space="preserve">2.00660371780396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0052170753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07178020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0939679145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14943742752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22709441184998</t>
+    <t xml:space="preserve">2.00521683692932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07177996635437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09396815299988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14943718910217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22709465026855</t>
   </si>
   <si>
     <t xml:space="preserve">2.25344228744507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25898933410645</t>
+    <t xml:space="preserve">2.25898909568787</t>
   </si>
   <si>
     <t xml:space="preserve">2.26453614234924</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">2.21461391448975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21184039115906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24928212165833</t>
+    <t xml:space="preserve">2.21184015274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2492823600769</t>
   </si>
   <si>
     <t xml:space="preserve">2.31445860862732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30059146881104</t>
+    <t xml:space="preserve">2.30059123039246</t>
   </si>
   <si>
     <t xml:space="preserve">2.30891156196594</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">2.24789547920227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24650859832764</t>
+    <t xml:space="preserve">2.24650883674622</t>
   </si>
   <si>
     <t xml:space="preserve">2.24512195587158</t>
@@ -2213,10 +2213,10 @@
     <t xml:space="preserve">2.37824845314026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30613803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2312548160553</t>
+    <t xml:space="preserve">2.30613827705383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23125457763672</t>
   </si>
   <si>
     <t xml:space="preserve">2.18687915802002</t>
@@ -2228,40 +2228,40 @@
     <t xml:space="preserve">2.17439842224121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22432088851929</t>
+    <t xml:space="preserve">2.22432112693787</t>
   </si>
   <si>
     <t xml:space="preserve">2.12170267105103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10783553123474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12863612174988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09812808036804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12724947929382</t>
+    <t xml:space="preserve">2.10783505439758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12863636016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09812831878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1272497177124</t>
   </si>
   <si>
     <t xml:space="preserve">2.17717218399048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19103932380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23680138587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2062931060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19935965538025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18549251556396</t>
+    <t xml:space="preserve">2.19103956222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2368016242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20629334449768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19935989379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18549227714539</t>
   </si>
   <si>
     <t xml:space="preserve">2.25760269165039</t>
@@ -2273,43 +2273,43 @@
     <t xml:space="preserve">2.23957514762878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35606074333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38102173805237</t>
+    <t xml:space="preserve">2.35606050491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38102149963379</t>
   </si>
   <si>
     <t xml:space="preserve">2.36715459823608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38379526138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43510484695435</t>
+    <t xml:space="preserve">2.38379502296448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43510437011719</t>
   </si>
   <si>
     <t xml:space="preserve">2.51553511619568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49889397621155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42955732345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42817068099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44897198677063</t>
+    <t xml:space="preserve">2.49889421463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42955756187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42817091941833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44897174835205</t>
   </si>
   <si>
     <t xml:space="preserve">2.45867896080017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39766263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38795518875122</t>
+    <t xml:space="preserve">2.39766240119934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3879554271698</t>
   </si>
   <si>
     <t xml:space="preserve">2.37131476402283</t>
@@ -2318,16 +2318,16 @@
     <t xml:space="preserve">2.382408618927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41707706451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42401075363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37408804893494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32693934440613</t>
+    <t xml:space="preserve">2.41707682609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42401051521301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37408828735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32693886756897</t>
   </si>
   <si>
     <t xml:space="preserve">2.29920434951782</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">2.31723213195801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34496688842773</t>
+    <t xml:space="preserve">2.34496665000916</t>
   </si>
   <si>
     <t xml:space="preserve">2.34635353088379</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">2.5696177482605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61537981033325</t>
+    <t xml:space="preserve">2.61538004875183</t>
   </si>
   <si>
     <t xml:space="preserve">2.6763961315155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73879909515381</t>
+    <t xml:space="preserve">2.73879933357239</t>
   </si>
   <si>
     <t xml:space="preserve">2.70690441131592</t>
@@ -2369,34 +2369,34 @@
     <t xml:space="preserve">2.74711942672729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72770524024963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75266647338867</t>
+    <t xml:space="preserve">2.72770547866821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75266671180725</t>
   </si>
   <si>
     <t xml:space="preserve">2.76237368583679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78594827651978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77208065986633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69581031799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70413064956665</t>
+    <t xml:space="preserve">2.7859480381012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77208089828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69581055641174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70413088798523</t>
   </si>
   <si>
     <t xml:space="preserve">2.7207715511322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80120229721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78733491897583</t>
+    <t xml:space="preserve">2.80120182037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78733468055725</t>
   </si>
   <si>
     <t xml:space="preserve">2.82893657684326</t>
@@ -2408,64 +2408,64 @@
     <t xml:space="preserve">2.94680905342102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01614594459534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02724027633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04804062843323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0799355506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13679218292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1464991569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17562007904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14511203765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23108959197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24773049354553</t>
+    <t xml:space="preserve">3.01614546775818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02724003791809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04804039001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07993578910828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13679194450378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14649868011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17562031745911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14511227607727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2310893535614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24773073196411</t>
   </si>
   <si>
     <t xml:space="preserve">3.26298451423645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26159811019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22554278373718</t>
+    <t xml:space="preserve">3.26159763336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2255425453186</t>
   </si>
   <si>
     <t xml:space="preserve">3.18532705307007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18394041061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25605082511902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21028828620911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25327730178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22831630706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20196795463562</t>
+    <t xml:space="preserve">3.18394064903259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2560510635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21028900146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25327706336975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22831606864929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2019681930542</t>
   </si>
   <si>
     <t xml:space="preserve">3.24218368530273</t>
@@ -2477,22 +2477,22 @@
     <t xml:space="preserve">3.21306204795837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19919443130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20890188217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22415614128113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1908745765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20335459709167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06606841087341</t>
+    <t xml:space="preserve">3.19919514656067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20890164375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22415637969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19087481498718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2033543586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06606817245483</t>
   </si>
   <si>
     <t xml:space="preserve">3.09241628646851</t>
@@ -2504,61 +2504,61 @@
     <t xml:space="preserve">3.20612835884094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17839384078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17145943641663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03694701194763</t>
+    <t xml:space="preserve">3.17839360237122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17146015167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03694677352905</t>
   </si>
   <si>
     <t xml:space="preserve">3.15343260765076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16868662834167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.970383644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.035560131073</t>
+    <t xml:space="preserve">3.16868686676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97038340568542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03555989265442</t>
   </si>
   <si>
     <t xml:space="preserve">3.14095211029053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12985801696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14927220344543</t>
+    <t xml:space="preserve">3.12985825538635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14927244186401</t>
   </si>
   <si>
     <t xml:space="preserve">3.17007327079773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12708497047424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10073661804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07854866981506</t>
+    <t xml:space="preserve">3.12708473205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10073685646057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07854890823364</t>
   </si>
   <si>
     <t xml:space="preserve">3.11044383049011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08964228630066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28239893913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34202861785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34896183013916</t>
+    <t xml:space="preserve">3.08964276313782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28239870071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34202814102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34896159172058</t>
   </si>
   <si>
     <t xml:space="preserve">2.93987536430359</t>
@@ -2573,43 +2573,43 @@
     <t xml:space="preserve">2.73741245269775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58487176895142</t>
+    <t xml:space="preserve">2.58487153053284</t>
   </si>
   <si>
     <t xml:space="preserve">2.55159020423889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4947338104248</t>
+    <t xml:space="preserve">2.49473404884338</t>
   </si>
   <si>
     <t xml:space="preserve">2.29227089881897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07039356231689</t>
+    <t xml:space="preserve">2.07039332389832</t>
   </si>
   <si>
     <t xml:space="preserve">1.95668137073517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99134969711304</t>
+    <t xml:space="preserve">1.99134945869446</t>
   </si>
   <si>
     <t xml:space="preserve">1.6904284954071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78472626209259</t>
+    <t xml:space="preserve">1.7847261428833</t>
   </si>
   <si>
     <t xml:space="preserve">1.65576004981995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52818059921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41030824184418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.485191822052</t>
+    <t xml:space="preserve">1.52818048000336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41030812263489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48519170284271</t>
   </si>
   <si>
     <t xml:space="preserve">1.49489879608154</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">1.60583770275116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67933464050293</t>
+    <t xml:space="preserve">1.67933452129364</t>
   </si>
   <si>
     <t xml:space="preserve">1.67656099796295</t>
@@ -2627,19 +2627,19 @@
     <t xml:space="preserve">1.72648358345032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68904173374176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69736194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72371006011963</t>
+    <t xml:space="preserve">1.68904185295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69736206531525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72371017932892</t>
   </si>
   <si>
     <t xml:space="preserve">1.75421810150146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78888642787933</t>
+    <t xml:space="preserve">1.78888630867004</t>
   </si>
   <si>
     <t xml:space="preserve">2.02185773849487</t>
@@ -2660,10 +2660,10 @@
     <t xml:space="preserve">1.966388463974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94142711162567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8596099615097</t>
+    <t xml:space="preserve">1.94142723083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85960972309113</t>
   </si>
   <si>
     <t xml:space="preserve">1.86793029308319</t>
@@ -2672,28 +2672,28 @@
     <t xml:space="preserve">1.92339944839478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90121209621429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14805054664612</t>
+    <t xml:space="preserve">1.90121221542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1480507850647</t>
   </si>
   <si>
     <t xml:space="preserve">2.26730966567993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23818826675415</t>
+    <t xml:space="preserve">2.23818850517273</t>
   </si>
   <si>
     <t xml:space="preserve">2.22570776939392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13418340682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28117680549622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35744714736938</t>
+    <t xml:space="preserve">2.13418364524841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28117704391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35744738578796</t>
   </si>
   <si>
     <t xml:space="preserve">2.40043592453003</t>
@@ -2711,10 +2711,10 @@
     <t xml:space="preserve">2.51219487190247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49150609970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49741721153259</t>
+    <t xml:space="preserve">2.49150586128235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49741744995117</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456218719482</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">2.75750350952148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80774712562561</t>
+    <t xml:space="preserve">2.80774736404419</t>
   </si>
   <si>
     <t xml:space="preserve">2.86537981033325</t>
@@ -2741,31 +2741,31 @@
     <t xml:space="preserve">2.86833548545837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97473454475403</t>
+    <t xml:space="preserve">2.97473406791687</t>
   </si>
   <si>
     <t xml:space="preserve">3.20230960845947</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1697986125946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14024353027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93483448028564</t>
+    <t xml:space="preserve">3.16979885101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14024376869202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93483471870422</t>
   </si>
   <si>
     <t xml:space="preserve">2.93631267547607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94222378730774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99837875366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00281190872192</t>
+    <t xml:space="preserve">2.94222354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99837851524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00281167030334</t>
   </si>
   <si>
     <t xml:space="preserve">2.95847916603088</t>
@@ -2774,16 +2774,16 @@
     <t xml:space="preserve">2.88606858253479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92744588851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83582472801208</t>
+    <t xml:space="preserve">2.92744612693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83582496643066</t>
   </si>
   <si>
     <t xml:space="preserve">2.89050197601318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8845911026001</t>
+    <t xml:space="preserve">2.88459086418152</t>
   </si>
   <si>
     <t xml:space="preserve">2.85946869850159</t>
@@ -2792,79 +2792,79 @@
     <t xml:space="preserve">2.82843589782715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86242461204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93779039382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99542284011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03236699104309</t>
+    <t xml:space="preserve">2.86242437362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93779015541077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99542307853699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03236722946167</t>
   </si>
   <si>
     <t xml:space="preserve">3.04418897628784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01906704902649</t>
+    <t xml:space="preserve">3.01906728744507</t>
   </si>
   <si>
     <t xml:space="preserve">2.92005681991577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93040132522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97916769981384</t>
+    <t xml:space="preserve">2.93040156364441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97916746139526</t>
   </si>
   <si>
     <t xml:space="preserve">2.98212289810181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99394536018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9895122051239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95404553413391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95552349090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94665694236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03384447097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09591102600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0175895690918</t>
+    <t xml:space="preserve">2.99394512176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98951172828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95404577255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95552325248718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94665670394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03384494781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0959107875824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758933067322</t>
   </si>
   <si>
     <t xml:space="preserve">2.99098968505859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93335700035095</t>
+    <t xml:space="preserve">2.93335676193237</t>
   </si>
   <si>
     <t xml:space="preserve">2.91857933998108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75602579116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81365847587585</t>
+    <t xml:space="preserve">2.75602555274963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81365823745728</t>
   </si>
   <si>
     <t xml:space="preserve">2.85503554344177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8535578250885</t>
+    <t xml:space="preserve">2.85355806350708</t>
   </si>
   <si>
     <t xml:space="preserve">2.894935131073</t>
@@ -2876,67 +2876,67 @@
     <t xml:space="preserve">2.92153477668762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96291255950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91266798973083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87424659729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84616899490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80479168891907</t>
+    <t xml:space="preserve">2.9629123210907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91266846656799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87424635887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84616875648499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80479192733765</t>
   </si>
   <si>
     <t xml:space="preserve">2.76784777641296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75307011604309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78410291671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7988805770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7486367225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77523636817932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72351503372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76637005805969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79296946525574</t>
+    <t xml:space="preserve">2.75307035446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78410315513611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79888105392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74863696098328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7752366065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72351479530334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76636981964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79296970367432</t>
   </si>
   <si>
     <t xml:space="preserve">2.73681473731995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69987058639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79592490196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74272561073303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75454807281494</t>
+    <t xml:space="preserve">2.69987082481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79592514038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74272537231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75454759597778</t>
   </si>
   <si>
     <t xml:space="preserve">2.74715900421143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71612620353699</t>
+    <t xml:space="preserve">2.71612596511841</t>
   </si>
   <si>
     <t xml:space="preserve">2.70873713493347</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">2.61268281936646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57573890686035</t>
+    <t xml:space="preserve">2.57573843002319</t>
   </si>
   <si>
     <t xml:space="preserve">2.52549481391907</t>
@@ -2960,43 +2960,43 @@
     <t xml:space="preserve">2.53436136245728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58460521697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52697277069092</t>
+    <t xml:space="preserve">2.5846049785614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52697253227234</t>
   </si>
   <si>
     <t xml:space="preserve">2.47525072097778</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50037312507629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43091773986816</t>
+    <t xml:space="preserve">2.50037264823914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43091797828674</t>
   </si>
   <si>
     <t xml:space="preserve">2.52992796897888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6112048625946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54618334770203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55209445953369</t>
+    <t xml:space="preserve">2.61120462417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54618358612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55209422111511</t>
   </si>
   <si>
     <t xml:space="preserve">2.67179298400879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60972714424133</t>
+    <t xml:space="preserve">2.60972690582275</t>
   </si>
   <si>
     <t xml:space="preserve">2.54322791099548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52845048904419</t>
+    <t xml:space="preserve">2.52845025062561</t>
   </si>
   <si>
     <t xml:space="preserve">2.47377300262451</t>
@@ -3008,13 +3008,13 @@
     <t xml:space="preserve">2.65701532363892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63632702827454</t>
+    <t xml:space="preserve">2.63632678985596</t>
   </si>
   <si>
     <t xml:space="preserve">2.60677170753479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53140592575073</t>
+    <t xml:space="preserve">2.53140616416931</t>
   </si>
   <si>
     <t xml:space="preserve">2.52253937721252</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">2.36441874504089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31713032722473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37180757522583</t>
+    <t xml:space="preserve">2.31713008880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37180733680725</t>
   </si>
   <si>
     <t xml:space="preserve">2.51662826538086</t>
@@ -3038,25 +3038,25 @@
     <t xml:space="preserve">2.64223790168762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4929838180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.615638256073</t>
+    <t xml:space="preserve">2.49298405647278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61563801765442</t>
   </si>
   <si>
     <t xml:space="preserve">2.6525821685791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63041591644287</t>
+    <t xml:space="preserve">2.63041567802429</t>
   </si>
   <si>
     <t xml:space="preserve">2.71317028999329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72794818878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74568128585815</t>
+    <t xml:space="preserve">2.72794771194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74568152427673</t>
   </si>
   <si>
     <t xml:space="preserve">2.83139157295227</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">2.78853607177734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75898098945618</t>
+    <t xml:space="preserve">2.75898122787476</t>
   </si>
   <si>
     <t xml:space="preserve">2.68361520767212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6703155040741</t>
+    <t xml:space="preserve">2.67031526565552</t>
   </si>
   <si>
     <t xml:space="preserve">2.66440415382385</t>
@@ -3092,28 +3092,28 @@
     <t xml:space="preserve">2.68213748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6259822845459</t>
+    <t xml:space="preserve">2.62598252296448</t>
   </si>
   <si>
     <t xml:space="preserve">2.65849328041077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72055912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85651350021362</t>
+    <t xml:space="preserve">2.7205593585968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85651326179504</t>
   </si>
   <si>
     <t xml:space="preserve">2.92301273345947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90380167961121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90084600448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98064541816711</t>
+    <t xml:space="preserve">2.90380191802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90084624290466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98064517974854</t>
   </si>
   <si>
     <t xml:space="preserve">3.0146336555481</t>
@@ -3125,13 +3125,13 @@
     <t xml:space="preserve">3.07374405860901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11807703971863</t>
+    <t xml:space="preserve">3.11807727813721</t>
   </si>
   <si>
     <t xml:space="preserve">3.06044459342957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0235002040863</t>
+    <t xml:space="preserve">3.02350044250488</t>
   </si>
   <si>
     <t xml:space="preserve">3.02941131591797</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">2.89345741271973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86390209197998</t>
+    <t xml:space="preserve">2.86390233039856</t>
   </si>
   <si>
     <t xml:space="preserve">2.90675711631775</t>
@@ -3149,25 +3149,25 @@
     <t xml:space="preserve">2.87129092216492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83434700965881</t>
+    <t xml:space="preserve">2.83434677124023</t>
   </si>
   <si>
     <t xml:space="preserve">2.91710162162781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04714441299438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1328547000885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10034394264221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1771879196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10625529289246</t>
+    <t xml:space="preserve">3.04714465141296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13285446166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10034418106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17718768119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10625505447388</t>
   </si>
   <si>
     <t xml:space="preserve">3.13581037521362</t>
@@ -3176,19 +3176,19 @@
     <t xml:space="preserve">3.08408856391907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00133395195007</t>
+    <t xml:space="preserve">3.00133371353149</t>
   </si>
   <si>
     <t xml:space="preserve">2.94517922401428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9998562335968</t>
+    <t xml:space="preserve">2.99985647201538</t>
   </si>
   <si>
     <t xml:space="preserve">2.97177863121033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93926763534546</t>
+    <t xml:space="preserve">2.93926811218262</t>
   </si>
   <si>
     <t xml:space="preserve">3.08999967575073</t>
@@ -3197,13 +3197,13 @@
     <t xml:space="preserve">3.09147763252258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07669997215271</t>
+    <t xml:space="preserve">3.07669973373413</t>
   </si>
   <si>
     <t xml:space="preserve">3.08704423904419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08852195739746</t>
+    <t xml:space="preserve">3.08852171897888</t>
   </si>
   <si>
     <t xml:space="preserve">3.12694358825684</t>
@@ -3212,31 +3212,31 @@
     <t xml:space="preserve">3.24664235115051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20526480674744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2185652256012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33235311508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33826375007629</t>
+    <t xml:space="preserve">3.20526528358459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21856474876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33235287666321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33826351165771</t>
   </si>
   <si>
     <t xml:space="preserve">3.34121918678284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31166362762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26142001152039</t>
+    <t xml:space="preserve">3.31166386604309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26142024993896</t>
   </si>
   <si>
     <t xml:space="preserve">3.32496380805969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30131959915161</t>
+    <t xml:space="preserve">3.30131936073303</t>
   </si>
   <si>
     <t xml:space="preserve">3.29245257377625</t>
@@ -3245,28 +3245,28 @@
     <t xml:space="preserve">3.28801941871643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31609725952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29393124580383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27324175834656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24516463279724</t>
+    <t xml:space="preserve">3.31609702110291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29393076896667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27324247360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2451651096344</t>
   </si>
   <si>
     <t xml:space="preserve">3.32274746894836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30649209022522</t>
+    <t xml:space="preserve">3.30649185180664</t>
   </si>
   <si>
     <t xml:space="preserve">3.31018614768982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29540872573853</t>
+    <t xml:space="preserve">3.2954089641571</t>
   </si>
   <si>
     <t xml:space="preserve">3.25107550621033</t>
@@ -3284,283 +3284,286 @@
     <t xml:space="preserve">3.24073147773743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27767515182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28136992454529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18531537055969</t>
+    <t xml:space="preserve">3.27767562866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28136968612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18531513214111</t>
   </si>
   <si>
     <t xml:space="preserve">3.13433265686035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10329937934875</t>
+    <t xml:space="preserve">3.10329961776733</t>
   </si>
   <si>
     <t xml:space="preserve">3.16314911842346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13507127761841</t>
+    <t xml:space="preserve">3.13507151603699</t>
   </si>
   <si>
     <t xml:space="preserve">3.17940425872803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09664940834045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15354371070862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13654923439026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21043705940247</t>
+    <t xml:space="preserve">3.09664964675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15354347229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1365487575531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21043729782104</t>
   </si>
   <si>
     <t xml:space="preserve">3.26511454582214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22743153572083</t>
+    <t xml:space="preserve">3.2274317741394</t>
   </si>
   <si>
     <t xml:space="preserve">3.23925375938416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24738121032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31979203224182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33974146842957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41362929344177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32053065299988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32939720153809</t>
+    <t xml:space="preserve">3.24738144874573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31979179382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33974123001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41362953186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32053017616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32939696311951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31535816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38761734962463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31846618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33789086341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33322882652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33944439888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33633685112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41325736045837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37751650810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40471076965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60206246376038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64868140220642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57098364830017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55855202674866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52203416824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51037955284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44200563430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47619247436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44977521896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38917112350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34022164344788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32545924186707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34876823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27417898178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2990415096283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25630807876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26407790184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24776124954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2788405418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25786185264587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24076867103577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19337344169617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25009250640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28738737106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27184748649597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24620747566223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2058048248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16540193557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02632331848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03098511695862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0915892124176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11956024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1801643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22678327560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19570398330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21202063560486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22989106178284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23066782951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31458139419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23299884796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28894090652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30370378494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.379070520401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3355598449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38606309890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33245182037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31302738189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33478260040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3612003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34954524040222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36819291114807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36508440971375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39227914810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41248083114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37207770347595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39150166511536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39849495887756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35032224655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35343027114868</t>
   </si>
   <si>
     <t xml:space="preserve">3.31535863876343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38761734962463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31846618652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.337890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33322882652283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33944463729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33633708953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41325759887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.377516746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40471076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60206270217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64868116378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57098388671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55855226516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52203416824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51037931442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44200539588928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47619271278381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44977521896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38917112350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3402214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32545924186707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34876823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27417874336243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29904174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25630831718445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26407814025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24776124954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27884030342102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25786185264587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24076890945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19337344169617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25009226799011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28738689422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27184796333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24620747566223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20580458641052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16540193557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02632331848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03098487854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0915892124176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11956024169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1801643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22678303718567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19570398330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21202039718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22989106178284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23066830635071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31458115577698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23299860954285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28894114494324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30370354652405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.379070520401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3355598449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38606309890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33245182037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31302738189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33478260040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36120009422302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3495454788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36819267272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3650848865509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39227938652039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41248083114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37207818031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39150166511536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39849472045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35032224655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35343027114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3472146987915</t>
+    <t xml:space="preserve">3.34721446037292</t>
   </si>
   <si>
     <t xml:space="preserve">3.32157444953918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33089828491211</t>
+    <t xml:space="preserve">3.33089804649353</t>
   </si>
   <si>
     <t xml:space="preserve">3.32312798500061</t>
@@ -3572,25 +3575,25 @@
     <t xml:space="preserve">3.18715739250183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19725775718689</t>
+    <t xml:space="preserve">3.19725751876831</t>
   </si>
   <si>
     <t xml:space="preserve">3.29282593727112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28661060333252</t>
+    <t xml:space="preserve">3.28661036491394</t>
   </si>
   <si>
     <t xml:space="preserve">3.22056746482849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21745896339417</t>
+    <t xml:space="preserve">3.21745920181274</t>
   </si>
   <si>
     <t xml:space="preserve">3.21279764175415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20891261100769</t>
+    <t xml:space="preserve">3.20891284942627</t>
   </si>
   <si>
     <t xml:space="preserve">3.17627930641174</t>
@@ -3599,34 +3602,34 @@
     <t xml:space="preserve">3.30758857727051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33012056350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36741614341736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39461016654968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32623648643494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43268203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4544370174408</t>
+    <t xml:space="preserve">3.33012080192566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36741590499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3946099281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32623624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43268179893494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45443749427795</t>
   </si>
   <si>
     <t xml:space="preserve">3.48085427284241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50183296203613</t>
+    <t xml:space="preserve">3.50183272361755</t>
   </si>
   <si>
     <t xml:space="preserve">3.61682558059692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5779767036438</t>
+    <t xml:space="preserve">3.57797646522522</t>
   </si>
   <si>
     <t xml:space="preserve">3.58652329444885</t>
@@ -3635,58 +3638,58 @@
     <t xml:space="preserve">3.58963108062744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5958468914032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57176041603088</t>
+    <t xml:space="preserve">3.59584665298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57176089286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.57642245292664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56632137298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58108472824097</t>
+    <t xml:space="preserve">3.56632208824158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58108448982239</t>
   </si>
   <si>
     <t xml:space="preserve">3.68753004074097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63469576835632</t>
+    <t xml:space="preserve">3.63469552993774</t>
   </si>
   <si>
     <t xml:space="preserve">3.65178894996643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64246582984924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62071013450623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62692642211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62148714065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61294054985046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61060929298401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57409119606018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50260972976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44822144508362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45132923126221</t>
+    <t xml:space="preserve">3.64246535301208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62070989608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62692594528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62148666381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61294031143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61060953140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57409167289734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50260996818542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4482216835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45132899284363</t>
   </si>
   <si>
     <t xml:space="preserve">3.39694118499756</t>
@@ -3698,7 +3701,7 @@
     <t xml:space="preserve">3.26330089569092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22833704948425</t>
+    <t xml:space="preserve">3.22833728790283</t>
   </si>
   <si>
     <t xml:space="preserve">3.23999166488647</t>
@@ -3707,7 +3710,7 @@
     <t xml:space="preserve">3.40004873275757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33711361885071</t>
+    <t xml:space="preserve">3.33711385726929</t>
   </si>
   <si>
     <t xml:space="preserve">3.36586141586304</t>
@@ -3716,31 +3719,31 @@
     <t xml:space="preserve">3.37363147735596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41791939735413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43656635284424</t>
+    <t xml:space="preserve">3.41791963577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4365668296814</t>
   </si>
   <si>
     <t xml:space="preserve">3.31380438804626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.420250415802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42957377433777</t>
+    <t xml:space="preserve">3.42024993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42957425117493</t>
   </si>
   <si>
     <t xml:space="preserve">3.48163151741028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49717092514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48707056045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48862385749817</t>
+    <t xml:space="preserve">3.49717116355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48707008361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48862409591675</t>
   </si>
   <si>
     <t xml:space="preserve">3.51814913749695</t>
@@ -3755,13 +3758,13 @@
     <t xml:space="preserve">3.48551607131958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49794793128967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64634990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70151543617249</t>
+    <t xml:space="preserve">3.49794769287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64635014533997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70151591300964</t>
   </si>
   <si>
     <t xml:space="preserve">3.6960768699646</t>
@@ -3773,16 +3776,16 @@
     <t xml:space="preserve">3.65567374229431</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56865286827087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52824974060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49639391899109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35420703887939</t>
+    <t xml:space="preserve">3.56865262985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52824950218201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49639415740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35420727729797</t>
   </si>
   <si>
     <t xml:space="preserve">3.40237998962402</t>
@@ -3791,19 +3794,19 @@
     <t xml:space="preserve">3.41092658042908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41558837890625</t>
+    <t xml:space="preserve">3.41558814048767</t>
   </si>
   <si>
     <t xml:space="preserve">3.4653148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48240804672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49017810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47075366973877</t>
+    <t xml:space="preserve">3.48240828514099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49017834663391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47075390815735</t>
   </si>
   <si>
     <t xml:space="preserve">3.45366048812866</t>
@@ -3812,43 +3815,43 @@
     <t xml:space="preserve">3.54301261901855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56321382522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75978851318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62614846229553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79708385467529</t>
+    <t xml:space="preserve">3.56321406364441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75978922843933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62614893913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79708361625671</t>
   </si>
   <si>
     <t xml:space="preserve">3.75124216079712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65878224372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66188979148865</t>
+    <t xml:space="preserve">3.65878248214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66188931465149</t>
   </si>
   <si>
     <t xml:space="preserve">3.54612016677856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55622100830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38373231887817</t>
+    <t xml:space="preserve">3.55622148513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38373208045959</t>
   </si>
   <si>
     <t xml:space="preserve">3.42258143424988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16384816169739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06361818313599</t>
+    <t xml:space="preserve">3.16384768486023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06361794471741</t>
   </si>
   <si>
     <t xml:space="preserve">2.87481260299683</t>
@@ -3857,34 +3860,34 @@
     <t xml:space="preserve">2.63395023345947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59898614883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6471586227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83751773834229</t>
+    <t xml:space="preserve">2.59898638725281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64715886116028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83751797676086</t>
   </si>
   <si>
     <t xml:space="preserve">2.74505758285522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82042455673218</t>
+    <t xml:space="preserve">2.8204243183136</t>
   </si>
   <si>
     <t xml:space="preserve">2.93308615684509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91366171836853</t>
+    <t xml:space="preserve">2.91366147994995</t>
   </si>
   <si>
     <t xml:space="preserve">3.0783805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05118656158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05895614624023</t>
+    <t xml:space="preserve">3.05118680000305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05895638465881</t>
   </si>
   <si>
     <t xml:space="preserve">3.06284093856812</t>
@@ -3911,112 +3914,112 @@
     <t xml:space="preserve">3.24853849411011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17161750793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20269680023193</t>
+    <t xml:space="preserve">3.17161774635315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20269727706909</t>
   </si>
   <si>
     <t xml:space="preserve">3.09236621856689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35498380661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36275386810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37984752655029</t>
+    <t xml:space="preserve">3.35498428344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36275434494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37984728813171</t>
   </si>
   <si>
     <t xml:space="preserve">3.40937256813049</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42335844039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53058075904846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59273910522461</t>
+    <t xml:space="preserve">3.42335820198059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53058099746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59273934364319</t>
   </si>
   <si>
     <t xml:space="preserve">3.51970338821411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52747321128845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5974006652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61138606071472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69374585151672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63624954223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6098325252533</t>
+    <t xml:space="preserve">3.52747249603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59740114212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6113862991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6937460899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63624930381775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60983228683472</t>
   </si>
   <si>
     <t xml:space="preserve">3.36430788040161</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30059623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38140153884888</t>
+    <t xml:space="preserve">3.30059599876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38140177726746</t>
   </si>
   <si>
     <t xml:space="preserve">3.46686887741089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51659536361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53524327278137</t>
+    <t xml:space="preserve">3.51659512519836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53524279594421</t>
   </si>
   <si>
     <t xml:space="preserve">3.55078268051147</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56942987442017</t>
+    <t xml:space="preserve">3.56942963600159</t>
   </si>
   <si>
     <t xml:space="preserve">3.51193332672119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63948941230774</t>
+    <t xml:space="preserve">3.63948965072632</t>
   </si>
   <si>
     <t xml:space="preserve">3.6378333568573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65771198272705</t>
+    <t xml:space="preserve">3.65771174430847</t>
   </si>
   <si>
     <t xml:space="preserve">3.71403574943542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7074089050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75876259803772</t>
+    <t xml:space="preserve">3.70740914344788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75876307487488</t>
   </si>
   <si>
     <t xml:space="preserve">3.71569180488586</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64611601829529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64942932128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59310531616211</t>
+    <t xml:space="preserve">3.64611577987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64942908287048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59310579299927</t>
   </si>
   <si>
     <t xml:space="preserve">3.59807538986206</t>
@@ -4028,13 +4031,13 @@
     <t xml:space="preserve">3.38272094726562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12595224380493</t>
+    <t xml:space="preserve">3.12595200538635</t>
   </si>
   <si>
     <t xml:space="preserve">2.97686076164246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01993155479431</t>
+    <t xml:space="preserve">3.01993131637573</t>
   </si>
   <si>
     <t xml:space="preserve">3.0828812122345</t>
@@ -4043,13 +4046,13 @@
     <t xml:space="preserve">2.97520422935486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96692109107971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01330542564392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98514366149902</t>
+    <t xml:space="preserve">2.96692132949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01330518722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98514342308044</t>
   </si>
   <si>
     <t xml:space="preserve">3.00005269050598</t>
@@ -4064,25 +4067,25 @@
     <t xml:space="preserve">3.03318405151367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04809308052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00999188423157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89734482765198</t>
+    <t xml:space="preserve">3.04809331893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00999212265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89734506607056</t>
   </si>
   <si>
     <t xml:space="preserve">2.90397143363953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90065860748291</t>
+    <t xml:space="preserve">2.90065836906433</t>
   </si>
   <si>
     <t xml:space="preserve">2.69690012931824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65879893302917</t>
+    <t xml:space="preserve">2.6587986946106</t>
   </si>
   <si>
     <t xml:space="preserve">2.73500108718872</t>
@@ -4097,22 +4100,22 @@
     <t xml:space="preserve">2.70683932304382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69193029403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52792978286743</t>
+    <t xml:space="preserve">2.69193005561829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52792954444885</t>
   </si>
   <si>
     <t xml:space="preserve">2.64885926246643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71346569061279</t>
+    <t xml:space="preserve">2.71346545219421</t>
   </si>
   <si>
     <t xml:space="preserve">2.81120347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78138518333435</t>
+    <t xml:space="preserve">2.78138494491577</t>
   </si>
   <si>
     <t xml:space="preserve">2.79132437705994</t>
@@ -4127,28 +4130,28 @@
     <t xml:space="preserve">2.71843552589417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71677875518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77475881576538</t>
+    <t xml:space="preserve">2.71677851676941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7747585773468</t>
   </si>
   <si>
     <t xml:space="preserve">2.83108234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83770847320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84599161148071</t>
+    <t xml:space="preserve">2.83770871162415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84599137306213</t>
   </si>
   <si>
     <t xml:space="preserve">2.92385029792786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9735472202301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95035529136658</t>
+    <t xml:space="preserve">2.97354745864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95035576820374</t>
   </si>
   <si>
     <t xml:space="preserve">2.91225433349609</t>
@@ -4160,7 +4163,7 @@
     <t xml:space="preserve">2.93047666549683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98183035850525</t>
+    <t xml:space="preserve">2.98183012008667</t>
   </si>
   <si>
     <t xml:space="preserve">2.98017382621765</t>
@@ -4169,22 +4172,22 @@
     <t xml:space="preserve">2.92219400405884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93544602394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8542742729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75984978675842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7996072769165</t>
+    <t xml:space="preserve">2.93544626235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85427451133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75984954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79960751533508</t>
   </si>
   <si>
     <t xml:space="preserve">2.78469800949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82776927947998</t>
+    <t xml:space="preserve">2.8277690410614</t>
   </si>
   <si>
     <t xml:space="preserve">2.81617307662964</t>
@@ -4193,10 +4196,10 @@
     <t xml:space="preserve">2.81286001205444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68696022033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69358658790588</t>
+    <t xml:space="preserve">2.68696045875549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69358706474304</t>
   </si>
   <si>
     <t xml:space="preserve">2.64223313331604</t>
@@ -4205,7 +4208,7 @@
     <t xml:space="preserve">2.68199062347412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73168778419495</t>
+    <t xml:space="preserve">2.73168802261353</t>
   </si>
   <si>
     <t xml:space="preserve">2.83439540863037</t>
@@ -4235,7 +4238,7 @@
     <t xml:space="preserve">2.51799011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53621220588684</t>
+    <t xml:space="preserve">2.536212682724</t>
   </si>
   <si>
     <t xml:space="preserve">2.46663618087769</t>
@@ -4244,19 +4247,19 @@
     <t xml:space="preserve">2.44344449043274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37221169471741</t>
+    <t xml:space="preserve">2.37221193313599</t>
   </si>
   <si>
     <t xml:space="preserve">2.4268786907196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65051579475403</t>
+    <t xml:space="preserve">2.65051603317261</t>
   </si>
   <si>
     <t xml:space="preserve">2.67702126502991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58259630203247</t>
+    <t xml:space="preserve">2.58259654045105</t>
   </si>
   <si>
     <t xml:space="preserve">2.54780840873718</t>
@@ -4265,7 +4268,7 @@
     <t xml:space="preserve">2.53124260902405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52461647987366</t>
+    <t xml:space="preserve">2.52461624145508</t>
   </si>
   <si>
     <t xml:space="preserve">2.42190909385681</t>
@@ -4283,10 +4286,10 @@
     <t xml:space="preserve">2.57100057601929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53952550888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52295970916748</t>
+    <t xml:space="preserve">2.53952574729919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52295994758606</t>
   </si>
   <si>
     <t xml:space="preserve">2.48817157745361</t>
@@ -4295,7 +4298,7 @@
     <t xml:space="preserve">2.59750533103943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62235403060913</t>
+    <t xml:space="preserve">2.62235426902771</t>
   </si>
   <si>
     <t xml:space="preserve">2.60413193702698</t>
@@ -4304,7 +4307,7 @@
     <t xml:space="preserve">2.61407113075256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61075830459595</t>
+    <t xml:space="preserve">2.61075806617737</t>
   </si>
   <si>
     <t xml:space="preserve">2.61572790145874</t>
@@ -4313,16 +4316,16 @@
     <t xml:space="preserve">2.68861699104309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84930467605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86587047576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95366859436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99839615821838</t>
+    <t xml:space="preserve">2.84930443763733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86587023735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95366883277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9983959197998</t>
   </si>
   <si>
     <t xml:space="preserve">2.99342632293701</t>
@@ -4352,25 +4355,25 @@
     <t xml:space="preserve">3.06631541252136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04478025436401</t>
+    <t xml:space="preserve">3.04478001594543</t>
   </si>
   <si>
     <t xml:space="preserve">3.10441660881042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08619427680969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94869899749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91722416877747</t>
+    <t xml:space="preserve">3.08619475364685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94869875907898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91722393035889</t>
   </si>
   <si>
     <t xml:space="preserve">2.86255717277527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89900159835815</t>
+    <t xml:space="preserve">2.89900183677673</t>
   </si>
   <si>
     <t xml:space="preserve">2.99176979064941</t>
@@ -4391,7 +4394,7 @@
     <t xml:space="preserve">3.09944701194763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13754820823669</t>
+    <t xml:space="preserve">3.13754844665527</t>
   </si>
   <si>
     <t xml:space="preserve">3.19055843353271</t>
@@ -4400,10 +4403,10 @@
     <t xml:space="preserve">3.16736626625061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21375036239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2518515586853</t>
+    <t xml:space="preserve">3.21375060081482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25185179710388</t>
   </si>
   <si>
     <t xml:space="preserve">3.22865962982178</t>
@@ -4412,13 +4415,13 @@
     <t xml:space="preserve">3.22534656524658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26013469696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23031616210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20215463638306</t>
+    <t xml:space="preserve">3.26013445854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23031640052795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20215439796448</t>
   </si>
   <si>
     <t xml:space="preserve">3.20546746253967</t>
@@ -4427,7 +4430,7 @@
     <t xml:space="preserve">3.18724536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23528599739075</t>
+    <t xml:space="preserve">3.23528575897217</t>
   </si>
   <si>
     <t xml:space="preserve">3.2816698551178</t>
@@ -4436,40 +4439,37 @@
     <t xml:space="preserve">3.29657912254333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34627628326416</t>
+    <t xml:space="preserve">3.34627652168274</t>
   </si>
   <si>
     <t xml:space="preserve">3.32805395126343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33633685112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34793281555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37443804740906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43904423713684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44235777854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29160952568054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29492235183716</t>
+    <t xml:space="preserve">3.34793257713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37443780899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43904447555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44235754013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29160928726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29492259025574</t>
   </si>
   <si>
     <t xml:space="preserve">3.31811451911926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25516510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35124611854553</t>
+    <t xml:space="preserve">3.25516486167908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35124588012695</t>
   </si>
   <si>
     <t xml:space="preserve">3.45395350456238</t>
@@ -4478,10 +4478,10 @@
     <t xml:space="preserve">3.4506402015686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49536752700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43573093414307</t>
+    <t xml:space="preserve">3.49536776542664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43573117256165</t>
   </si>
   <si>
     <t xml:space="preserve">3.38437747955322</t>
@@ -4496,13 +4496,13 @@
     <t xml:space="preserve">3.34958958625793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38106393814087</t>
+    <t xml:space="preserve">3.38106417655945</t>
   </si>
   <si>
     <t xml:space="preserve">3.387690782547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39266037940979</t>
+    <t xml:space="preserve">3.39266061782837</t>
   </si>
   <si>
     <t xml:space="preserve">3.41088271141052</t>
@@ -4529,28 +4529,28 @@
     <t xml:space="preserve">3.13092184066772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02324485778809</t>
+    <t xml:space="preserve">3.02324461936951</t>
   </si>
   <si>
     <t xml:space="preserve">3.07625508308411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17399287223816</t>
+    <t xml:space="preserve">3.17399263381958</t>
   </si>
   <si>
     <t xml:space="preserve">3.13423490524292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1060733795166</t>
+    <t xml:space="preserve">3.10607314109802</t>
   </si>
   <si>
     <t xml:space="preserve">3.01164865493774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06465888023376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1093864440918</t>
+    <t xml:space="preserve">3.06465911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10938620567322</t>
   </si>
   <si>
     <t xml:space="preserve">3.07459831237793</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">3.08453774452209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11269950866699</t>
+    <t xml:space="preserve">3.11269927024841</t>
   </si>
   <si>
     <t xml:space="preserve">3.14748764038086</t>
@@ -4583,10 +4583,10 @@
     <t xml:space="preserve">3.19387149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19718456268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17896246910095</t>
+    <t xml:space="preserve">3.19718480110168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17896270751953</t>
   </si>
   <si>
     <t xml:space="preserve">3.14583110809326</t>
@@ -4598,19 +4598,19 @@
     <t xml:space="preserve">3.11932587623596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04146695137024</t>
+    <t xml:space="preserve">3.04146671295166</t>
   </si>
   <si>
     <t xml:space="preserve">3.07294201850891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05140662193298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08785104751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05306315422058</t>
+    <t xml:space="preserve">3.0514063835144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08785080909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.053062915802</t>
   </si>
   <si>
     <t xml:space="preserve">3.04974985122681</t>
@@ -5982,6 +5982,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.10500001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11499977111816</t>
   </si>
 </sst>
 </file>
@@ -43960,7 +43963,7 @@
         <v>4.26700019836426</v>
       </c>
       <c r="G1448" t="s">
-        <v>1111</v>
+        <v>1180</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -43986,7 +43989,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G1449" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -44012,7 +44015,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1450" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -44038,7 +44041,7 @@
         <v>4.28700017929077</v>
       </c>
       <c r="G1451" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -44064,7 +44067,7 @@
         <v>4.27699995040894</v>
       </c>
       <c r="G1452" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -44090,7 +44093,7 @@
         <v>4.23400020599365</v>
       </c>
       <c r="G1453" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -44116,7 +44119,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G1454" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -44142,7 +44145,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1455" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -44194,7 +44197,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G1457" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -44220,7 +44223,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1458" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -44272,7 +44275,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1460" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -44298,7 +44301,7 @@
         <v>4.14099979400635</v>
       </c>
       <c r="G1461" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -44324,7 +44327,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1462" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -44350,7 +44353,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1463" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -44376,7 +44379,7 @@
         <v>4.08799982070923</v>
       </c>
       <c r="G1464" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -44402,7 +44405,7 @@
         <v>4.25699996948242</v>
       </c>
       <c r="G1465" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -44428,7 +44431,7 @@
         <v>4.28599977493286</v>
       </c>
       <c r="G1466" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -44454,7 +44457,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G1467" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -44480,7 +44483,7 @@
         <v>4.36899995803833</v>
       </c>
       <c r="G1468" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -44506,7 +44509,7 @@
         <v>4.2810001373291</v>
       </c>
       <c r="G1469" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -44532,7 +44535,7 @@
         <v>4.41800022125244</v>
       </c>
       <c r="G1470" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -44584,7 +44587,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G1472" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -44610,7 +44613,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1473" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -44636,7 +44639,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1474" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -44662,7 +44665,7 @@
         <v>4.50699996948242</v>
       </c>
       <c r="G1475" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -44688,7 +44691,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G1476" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -44714,7 +44717,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G1477" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -44740,7 +44743,7 @@
         <v>4.61600017547607</v>
       </c>
       <c r="G1478" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -44766,7 +44769,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1479" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -44792,7 +44795,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G1480" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -44818,7 +44821,7 @@
         <v>4.59700012207031</v>
       </c>
       <c r="G1481" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -44844,7 +44847,7 @@
         <v>4.60300016403198</v>
       </c>
       <c r="G1482" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -44870,7 +44873,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1483" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -44896,7 +44899,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G1484" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -44922,7 +44925,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1485" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -44948,7 +44951,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G1486" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -44974,7 +44977,7 @@
         <v>4.67799997329712</v>
       </c>
       <c r="G1487" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -45000,7 +45003,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1488" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -45026,7 +45029,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G1489" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -45052,7 +45055,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1490" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -45078,7 +45081,7 @@
         <v>4.66800022125244</v>
       </c>
       <c r="G1491" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -45104,7 +45107,7 @@
         <v>4.67799997329712</v>
       </c>
       <c r="G1492" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -45130,7 +45133,7 @@
         <v>4.66099977493286</v>
       </c>
       <c r="G1493" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -45156,7 +45159,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1494" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -45182,7 +45185,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1495" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -45208,7 +45211,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1496" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -45234,7 +45237,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G1497" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -45260,7 +45263,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G1498" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -45286,7 +45289,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G1499" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -45312,7 +45315,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G1500" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -45338,7 +45341,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G1501" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -45364,7 +45367,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1502" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -45390,7 +45393,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1503" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -45442,7 +45445,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G1505" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -45468,7 +45471,7 @@
         <v>4.26700019836426</v>
       </c>
       <c r="G1506" t="s">
-        <v>1111</v>
+        <v>1180</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -45520,7 +45523,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1508" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -45572,7 +45575,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G1510" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -45624,7 +45627,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G1512" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -45676,7 +45679,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1514" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -45702,7 +45705,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G1515" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -45728,7 +45731,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G1516" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -45754,7 +45757,7 @@
         <v>4.39900016784668</v>
       </c>
       <c r="G1517" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -45780,7 +45783,7 @@
         <v>4.4229998588562</v>
       </c>
       <c r="G1518" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -45806,7 +45809,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G1519" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -45832,7 +45835,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G1520" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -45858,7 +45861,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G1521" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -45884,7 +45887,7 @@
         <v>4.41400003433228</v>
       </c>
       <c r="G1522" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -45910,7 +45913,7 @@
         <v>4.48099994659424</v>
       </c>
       <c r="G1523" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -45936,7 +45939,7 @@
         <v>4.50099992752075</v>
       </c>
       <c r="G1524" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -45962,7 +45965,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G1525" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -45988,7 +45991,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1526" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -46014,7 +46017,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G1527" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -46040,7 +46043,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G1528" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -46066,7 +46069,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G1529" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -46118,7 +46121,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G1531" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -46144,7 +46147,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G1532" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -46170,7 +46173,7 @@
         <v>4.69299983978271</v>
       </c>
       <c r="G1533" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -46196,7 +46199,7 @@
         <v>4.76399993896484</v>
       </c>
       <c r="G1534" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -46222,7 +46225,7 @@
         <v>4.75699996948242</v>
       </c>
       <c r="G1535" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -46248,7 +46251,7 @@
         <v>4.69399976730347</v>
       </c>
       <c r="G1536" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -46274,7 +46277,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G1537" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -46300,7 +46303,7 @@
         <v>4.59299993515015</v>
       </c>
       <c r="G1538" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -46326,7 +46329,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G1539" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -46352,7 +46355,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G1540" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -46378,7 +46381,7 @@
         <v>4.5</v>
       </c>
       <c r="G1541" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -46404,7 +46407,7 @@
         <v>4.31699991226196</v>
       </c>
       <c r="G1542" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -46430,7 +46433,7 @@
         <v>4.28700017929077</v>
       </c>
       <c r="G1543" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -46456,7 +46459,7 @@
         <v>4.37900018692017</v>
       </c>
       <c r="G1544" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -46482,7 +46485,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1545" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -46508,7 +46511,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G1546" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -46534,7 +46537,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1547" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -46560,7 +46563,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G1548" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -46586,7 +46589,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G1549" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -46612,7 +46615,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G1550" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -46638,7 +46641,7 @@
         <v>4.46700000762939</v>
       </c>
       <c r="G1551" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -46664,7 +46667,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1552" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -46690,7 +46693,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G1553" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -46716,7 +46719,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1554" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -46742,7 +46745,7 @@
         <v>4.58599996566772</v>
       </c>
       <c r="G1555" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -46768,7 +46771,7 @@
         <v>4.83900022506714</v>
       </c>
       <c r="G1556" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -46794,7 +46797,7 @@
         <v>4.66699981689453</v>
       </c>
       <c r="G1557" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -46820,7 +46823,7 @@
         <v>4.88700008392334</v>
       </c>
       <c r="G1558" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -46846,7 +46849,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G1559" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -46872,7 +46875,7 @@
         <v>4.70900011062622</v>
       </c>
       <c r="G1560" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -46898,7 +46901,7 @@
         <v>4.71299982070923</v>
       </c>
       <c r="G1561" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -46924,7 +46927,7 @@
         <v>4.56400012969971</v>
       </c>
       <c r="G1562" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -46950,7 +46953,7 @@
         <v>4.5770001411438</v>
       </c>
       <c r="G1563" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -46976,7 +46979,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1564" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -47002,7 +47005,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G1565" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -47028,7 +47031,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G1566" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -47054,7 +47057,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1567" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -47080,7 +47083,7 @@
         <v>4.07200002670288</v>
       </c>
       <c r="G1568" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -47106,7 +47109,7 @@
         <v>3.94300007820129</v>
       </c>
       <c r="G1569" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -47132,7 +47135,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1570" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -47158,7 +47161,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1571" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -47184,7 +47187,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1572" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -47210,7 +47213,7 @@
         <v>3.40700006484985</v>
       </c>
       <c r="G1573" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -47236,7 +47239,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G1574" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -47262,7 +47265,7 @@
         <v>3.53299999237061</v>
       </c>
       <c r="G1575" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -47288,7 +47291,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1576" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -47314,7 +47317,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1577" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -47340,7 +47343,7 @@
         <v>3.75</v>
       </c>
       <c r="G1578" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -47366,7 +47369,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G1579" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -47392,7 +47395,7 @@
         <v>3.92700004577637</v>
       </c>
       <c r="G1580" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -47418,7 +47421,7 @@
         <v>3.93700003623962</v>
       </c>
       <c r="G1581" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -47444,7 +47447,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G1582" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -47470,7 +47473,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1583" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -47496,7 +47499,7 @@
         <v>4.04300022125244</v>
       </c>
       <c r="G1584" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -47522,7 +47525,7 @@
         <v>3.99300003051758</v>
       </c>
       <c r="G1585" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -47548,7 +47551,7 @@
         <v>3.98699998855591</v>
       </c>
       <c r="G1586" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -47574,7 +47577,7 @@
         <v>4.0310001373291</v>
       </c>
       <c r="G1587" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -47600,7 +47603,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G1588" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -47626,7 +47629,7 @@
         <v>4.18100023269653</v>
       </c>
       <c r="G1589" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -47652,7 +47655,7 @@
         <v>4.08199977874756</v>
       </c>
       <c r="G1590" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -47678,7 +47681,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1591" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -47704,7 +47707,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G1592" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -47730,7 +47733,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1593" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -47756,7 +47759,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G1594" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -47782,7 +47785,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1595" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -47834,7 +47837,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G1597" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -47860,7 +47863,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G1598" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -47886,7 +47889,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1599" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -47912,7 +47915,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G1600" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -47938,7 +47941,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G1601" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -47964,7 +47967,7 @@
         <v>4.54400014877319</v>
       </c>
       <c r="G1602" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -47990,7 +47993,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G1603" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -48016,7 +48019,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1604" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -48042,7 +48045,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1605" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -48068,7 +48071,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1606" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -48094,7 +48097,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G1607" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -48120,7 +48123,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G1608" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -48146,7 +48149,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1609" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -48172,7 +48175,7 @@
         <v>4.66800022125244</v>
       </c>
       <c r="G1610" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -48198,7 +48201,7 @@
         <v>4.64599990844727</v>
       </c>
       <c r="G1611" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -48224,7 +48227,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G1612" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -48250,7 +48253,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1613" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -48276,7 +48279,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G1614" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -48302,7 +48305,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G1615" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -48328,7 +48331,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G1616" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -48354,7 +48357,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G1617" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -48380,7 +48383,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G1618" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -48406,7 +48409,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1619" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -48432,7 +48435,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1620" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -48458,7 +48461,7 @@
         <v>4.5939998626709</v>
       </c>
       <c r="G1621" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -48484,7 +48487,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1622" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -48510,7 +48513,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G1623" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -48536,7 +48539,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1624" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -48562,7 +48565,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G1625" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -48588,7 +48591,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G1626" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -48614,7 +48617,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G1627" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -48640,7 +48643,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G1628" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -48666,7 +48669,7 @@
         <v>4.47599983215332</v>
       </c>
       <c r="G1629" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -48692,7 +48695,7 @@
         <v>4.53800010681152</v>
       </c>
       <c r="G1630" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -48718,7 +48721,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G1631" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -48744,7 +48747,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G1632" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -48770,7 +48773,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G1633" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -48796,7 +48799,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G1634" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -48822,7 +48825,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G1635" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -48848,7 +48851,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G1636" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -48874,7 +48877,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G1637" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -48900,7 +48903,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G1638" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -48926,7 +48929,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1639" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -48952,7 +48955,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G1640" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -48978,7 +48981,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G1641" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -49004,7 +49007,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G1642" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -49030,7 +49033,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G1643" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -49056,7 +49059,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G1644" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -49082,7 +49085,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1645" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -49108,7 +49111,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G1646" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -49134,7 +49137,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G1647" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -49160,7 +49163,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G1648" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -49186,7 +49189,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G1649" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -49212,7 +49215,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G1650" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -49238,7 +49241,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1651" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -49264,7 +49267,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G1652" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -49290,7 +49293,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G1653" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -49316,7 +49319,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G1654" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -49342,7 +49345,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G1655" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -49368,7 +49371,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G1656" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -49394,7 +49397,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1657" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -49420,7 +49423,7 @@
         <v>3.30200004577637</v>
       </c>
       <c r="G1658" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -49446,7 +49449,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G1659" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -49472,7 +49475,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G1660" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -49498,7 +49501,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G1661" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -49524,7 +49527,7 @@
         <v>3.25</v>
       </c>
       <c r="G1662" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -49550,7 +49553,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G1663" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -49576,7 +49579,7 @@
         <v>3.19799995422363</v>
       </c>
       <c r="G1664" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -49602,7 +49605,7 @@
         <v>3.27600002288818</v>
       </c>
       <c r="G1665" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -49628,7 +49631,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G1666" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -49654,7 +49657,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G1667" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -49680,7 +49683,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1668" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -49706,7 +49709,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G1669" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -49732,7 +49735,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G1670" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -49758,7 +49761,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G1671" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -49784,7 +49787,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1672" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -49810,7 +49813,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1673" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -49836,7 +49839,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G1674" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -49862,7 +49865,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G1675" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -49888,7 +49891,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G1676" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -49914,7 +49917,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1677" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -49940,7 +49943,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1678" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -49966,7 +49969,7 @@
         <v>3.56200003623962</v>
       </c>
       <c r="G1679" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -49992,7 +49995,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G1680" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -50018,7 +50021,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G1681" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -50044,7 +50047,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G1682" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -50070,7 +50073,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G1683" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -50096,7 +50099,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1684" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -50122,7 +50125,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1685" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -50148,7 +50151,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G1686" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -50174,7 +50177,7 @@
         <v>3.54399991035461</v>
       </c>
       <c r="G1687" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -50200,7 +50203,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G1688" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -50226,7 +50229,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G1689" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -50252,7 +50255,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1690" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -50278,7 +50281,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G1691" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -50304,7 +50307,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1692" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -50330,7 +50333,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G1693" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -50356,7 +50359,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G1694" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -50382,7 +50385,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G1695" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -50408,7 +50411,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1696" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -50434,7 +50437,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1697" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -50460,7 +50463,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G1698" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -50486,7 +50489,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G1699" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -50512,7 +50515,7 @@
         <v>3.25200009346008</v>
       </c>
       <c r="G1700" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -50538,7 +50541,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1701" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -50564,7 +50567,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G1702" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -50590,7 +50593,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G1703" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -50616,7 +50619,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G1704" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -50642,7 +50645,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G1705" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -50668,7 +50671,7 @@
         <v>3.33400011062622</v>
       </c>
       <c r="G1706" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -50694,7 +50697,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G1707" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -50720,7 +50723,7 @@
         <v>3.25</v>
       </c>
       <c r="G1708" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -50746,7 +50749,7 @@
         <v>3.2720000743866</v>
       </c>
       <c r="G1709" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -50772,7 +50775,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1710" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -50798,7 +50801,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G1711" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -50824,7 +50827,7 @@
         <v>3.11199998855591</v>
       </c>
       <c r="G1712" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -50850,7 +50853,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1713" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -50876,7 +50879,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G1714" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -50902,7 +50905,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G1715" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -50928,7 +50931,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1716" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -50954,7 +50957,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G1717" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -50980,7 +50983,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1718" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -51006,7 +51009,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G1719" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -51032,7 +51035,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1720" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -51058,7 +51061,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G1721" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -51084,7 +51087,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G1722" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -51110,7 +51113,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G1723" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -51136,7 +51139,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G1724" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -51162,7 +51165,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G1725" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -51188,7 +51191,7 @@
         <v>2.92400002479553</v>
       </c>
       <c r="G1726" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -51214,7 +51217,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G1727" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -51240,7 +51243,7 @@
         <v>2.99600005149841</v>
       </c>
       <c r="G1728" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -51266,7 +51269,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G1729" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -51292,7 +51295,7 @@
         <v>3.10400009155273</v>
       </c>
       <c r="G1730" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -51318,7 +51321,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G1731" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -51344,7 +51347,7 @@
         <v>3.0460000038147</v>
       </c>
       <c r="G1732" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -51370,7 +51373,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G1733" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -51396,7 +51399,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G1734" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -51422,7 +51425,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G1735" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -51448,7 +51451,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G1736" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -51474,7 +51477,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G1737" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -51500,7 +51503,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G1738" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -51526,7 +51529,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G1739" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -51552,7 +51555,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G1740" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -51578,7 +51581,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G1741" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -51604,7 +51607,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G1742" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -51630,7 +51633,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G1743" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -51656,7 +51659,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1744" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -51682,7 +51685,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1745" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -51708,7 +51711,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1746" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -51734,7 +51737,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G1747" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -51760,7 +51763,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G1748" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -51786,7 +51789,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1749" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -51812,7 +51815,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1750" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -51838,7 +51841,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G1751" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -51864,7 +51867,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G1752" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -51890,7 +51893,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G1753" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -51916,7 +51919,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1754" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -51942,7 +51945,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G1755" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -51968,7 +51971,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1756" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -51994,7 +51997,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G1757" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -52020,7 +52023,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1758" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -52046,7 +52049,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G1759" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -52072,7 +52075,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G1760" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -52098,7 +52101,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G1761" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -52124,7 +52127,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G1762" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -52150,7 +52153,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1763" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -52176,7 +52179,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1764" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -52202,7 +52205,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1765" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -52228,7 +52231,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G1766" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -52254,7 +52257,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G1767" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -52280,7 +52283,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1768" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -52306,7 +52309,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G1769" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -52332,7 +52335,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G1770" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -52358,7 +52361,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G1771" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -52384,7 +52387,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1772" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -52410,7 +52413,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G1773" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -52436,7 +52439,7 @@
         <v>3.45600008964539</v>
       </c>
       <c r="G1774" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -52462,7 +52465,7 @@
         <v>3.5</v>
       </c>
       <c r="G1775" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -52488,7 +52491,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G1776" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -52514,7 +52517,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G1777" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -52540,7 +52543,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G1778" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -52566,7 +52569,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G1779" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -52592,7 +52595,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1780" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -52618,7 +52621,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1781" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -52644,7 +52647,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G1782" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -52670,7 +52673,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1783" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -52696,7 +52699,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G1784" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -52722,7 +52725,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1785" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -52748,7 +52751,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1786" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -52774,7 +52777,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1787" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -52800,7 +52803,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G1788" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -52826,7 +52829,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G1789" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -52852,7 +52855,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G1790" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -52878,7 +52881,7 @@
         <v>3.93600010871887</v>
       </c>
       <c r="G1791" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -52904,7 +52907,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1792" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -52930,7 +52933,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1793" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -52956,7 +52959,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G1794" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -52982,7 +52985,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1795" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -53008,7 +53011,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G1796" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -53034,7 +53037,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G1797" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -53060,7 +53063,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G1798" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -53086,7 +53089,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1799" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -53112,7 +53115,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1800" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -53138,7 +53141,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -53164,7 +53167,7 @@
         <v>4.01800012588501</v>
       </c>
       <c r="G1802" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -53190,7 +53193,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G1803" t="s">
-        <v>1476</v>
+        <v>1117</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -53424,7 +53427,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1812" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -53944,7 +53947,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G1832" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -54022,7 +54025,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1835" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -54074,7 +54077,7 @@
         <v>3.56200003623962</v>
       </c>
       <c r="G1837" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -54204,7 +54207,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G1842" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -54230,7 +54233,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G1843" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -54386,7 +54389,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G1849" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -54932,7 +54935,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G1870" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -54984,7 +54987,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1872" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -55010,7 +55013,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G1873" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -55062,7 +55065,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1875" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -55088,7 +55091,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G1876" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -55114,7 +55117,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1877" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -71372,7 +71375,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6911574074</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>115685</v>
@@ -71393,6 +71396,32 @@
         <v>1970</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6909953704</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>142006</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>6.13500022888184</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>6.07499980926514</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>6.1100001335144</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>6.11499977111816</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1990</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -38,133 +38,133 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24674701690674</t>
+    <t xml:space="preserve">4.24674606323242</t>
   </si>
   <si>
     <t xml:space="preserve">ANIM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33184623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13419532775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96948647499084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95301628112793</t>
+    <t xml:space="preserve">4.33184671401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13419580459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96948623657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95301580429077</t>
   </si>
   <si>
     <t xml:space="preserve">3.94203495979309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07380342483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93105483055115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82673907279968</t>
+    <t xml:space="preserve">4.07380247116089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93105530738831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82673859596252</t>
   </si>
   <si>
     <t xml:space="preserve">3.76085567474365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67850041389465</t>
+    <t xml:space="preserve">3.67850136756897</t>
   </si>
   <si>
     <t xml:space="preserve">3.73889398574829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40398597717285</t>
+    <t xml:space="preserve">3.40398645401001</t>
   </si>
   <si>
     <t xml:space="preserve">3.53300786018372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76909112930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79379725456238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79928731918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88438725471497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67575550079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70595264434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64006853103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57967495918274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35731816291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4506528377533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3765344619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0663321018219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95652604103088</t>
+    <t xml:space="preserve">3.76909065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79379677772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79928636550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88438701629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67575573921204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70595216751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64006876945496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57967519760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35731863975525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45065307617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37653422355652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06633234024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95652627944946</t>
   </si>
   <si>
     <t xml:space="preserve">3.19535422325134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98397779464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24202275276184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20084452629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48633980751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38202428817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31065058708191</t>
+    <t xml:space="preserve">2.98397827148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24202227592468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20084428787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48634004592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38202452659607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31065082550049</t>
   </si>
   <si>
     <t xml:space="preserve">3.38751530647278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26672840118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11299967765808</t>
+    <t xml:space="preserve">3.26672887802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11299991607666</t>
   </si>
   <si>
     <t xml:space="preserve">3.08554816246033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07182288169861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06084156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15692210197449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30241537094116</t>
+    <t xml:space="preserve">3.07182240486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06084132194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15692186355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30241513252258</t>
   </si>
   <si>
     <t xml:space="preserve">3.43967294692993</t>
@@ -173,55 +173,55 @@
     <t xml:space="preserve">3.3518283367157</t>
   </si>
   <si>
-    <t xml:space="preserve">3.283198595047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22280597686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25300240516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57693004608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47261452674866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46437907218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.590656042099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56320381164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61261701583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51653718948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43418216705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37104344367981</t>
+    <t xml:space="preserve">3.28319907188416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22280550003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25300264358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57692980766296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47261476516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46437978744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59065628051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56320476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61261677742004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51653671264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4341824054718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37104320526123</t>
   </si>
   <si>
     <t xml:space="preserve">3.45888876914978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53026270866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3298671245575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2722179889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09103894233704</t>
+    <t xml:space="preserve">3.5302631855011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32986688613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27221846580505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09103870391846</t>
   </si>
   <si>
     <t xml:space="preserve">3.23653149604797</t>
@@ -230,130 +230,130 @@
     <t xml:space="preserve">3.34084725379944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28594470024109</t>
+    <t xml:space="preserve">3.28594398498535</t>
   </si>
   <si>
     <t xml:space="preserve">3.31888604164124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23927640914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4259467124939</t>
+    <t xml:space="preserve">3.23927688598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42594647407532</t>
   </si>
   <si>
     <t xml:space="preserve">3.41771149635315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40947580337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41496634483337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44241762161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46163415908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44790863990784</t>
+    <t xml:space="preserve">3.40947651863098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41496586799622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44241738319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4616334438324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44790840148926</t>
   </si>
   <si>
     <t xml:space="preserve">3.49732065200806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39300513267517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3737895488739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26123809814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26947402954102</t>
+    <t xml:space="preserve">3.39300537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37378907203674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26123785972595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26947331428528</t>
   </si>
   <si>
     <t xml:space="preserve">3.15417718887329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1624128818512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01966452598572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94829082489014</t>
+    <t xml:space="preserve">3.16241264343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01966500282288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94829106330872</t>
   </si>
   <si>
     <t xml:space="preserve">2.82201409339905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93182015419006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06907725334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00044918060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91809439659119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8741717338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85221028327942</t>
+    <t xml:space="preserve">2.93182039260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06907749176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00044870376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91809463500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87417149543762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.852210521698</t>
   </si>
   <si>
     <t xml:space="preserve">2.89064288139343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97133898735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06356287002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23648285865784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24224662780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29988646507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17884302139282</t>
+    <t xml:space="preserve">2.97133874893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06356310844421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23648262023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2422468662262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29988598823547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17884254455566</t>
   </si>
   <si>
     <t xml:space="preserve">3.15866899490356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04050707817078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97998452186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9626932144165</t>
+    <t xml:space="preserve">3.04050731658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.979984998703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96269297599792</t>
   </si>
   <si>
     <t xml:space="preserve">3.02321457862854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00015902519226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95692849159241</t>
+    <t xml:space="preserve">3.00015878677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95692825317383</t>
   </si>
   <si>
     <t xml:space="preserve">2.81859278678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79668974876404</t>
+    <t xml:space="preserve">2.7966902256012</t>
   </si>
   <si>
     <t xml:space="preserve">2.66988182067871</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">2.61454749107361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54768514633179</t>
+    <t xml:space="preserve">2.54768538475037</t>
   </si>
   <si>
     <t xml:space="preserve">2.70331287384033</t>
@@ -371,70 +371,70 @@
     <t xml:space="preserve">2.75288367271423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90505313873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92234492301941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96845650672913</t>
+    <t xml:space="preserve">2.90505337715149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92234468460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96845698356628</t>
   </si>
   <si>
     <t xml:space="preserve">2.53615713119507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26179146766663</t>
+    <t xml:space="preserve">2.26179122924805</t>
   </si>
   <si>
     <t xml:space="preserve">2.49004530906677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41972422599792</t>
+    <t xml:space="preserve">2.4197244644165</t>
   </si>
   <si>
     <t xml:space="preserve">2.42664122581482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49235057830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36900115013123</t>
+    <t xml:space="preserve">2.49235081672668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3690013885498</t>
   </si>
   <si>
     <t xml:space="preserve">2.28830575942993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29752779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30559754371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35747313499451</t>
+    <t xml:space="preserve">2.297527551651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30559802055359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35747337341309</t>
   </si>
   <si>
     <t xml:space="preserve">2.43240523338318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61108875274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59379744529724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68025732040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59725546836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60647797584534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56958770751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62838125228882</t>
+    <t xml:space="preserve">2.61108899116516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59379696846008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68025708198547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59725522994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60647821426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56958818435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62838101387024</t>
   </si>
   <si>
     <t xml:space="preserve">2.62261700630188</t>
@@ -443,34 +443,34 @@
     <t xml:space="preserve">2.59494996070862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61685371398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54653239250183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6341450214386</t>
+    <t xml:space="preserve">2.61685347557068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54653215408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63414597511292</t>
   </si>
   <si>
     <t xml:space="preserve">2.58226919174194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4035849571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4151132106781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43816924095154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55114364624023</t>
+    <t xml:space="preserve">2.40358519554138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41511344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4381697177887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55114388465881</t>
   </si>
   <si>
     <t xml:space="preserve">2.58572769165039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65143704414368</t>
+    <t xml:space="preserve">2.6514368057251</t>
   </si>
   <si>
     <t xml:space="preserve">2.65489530563354</t>
@@ -482,40 +482,40 @@
     <t xml:space="preserve">2.54307436943054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41857123374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37015390396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3932101726532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51310157775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50964283943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4612250328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44854402542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50733685493469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50157356262207</t>
+    <t xml:space="preserve">2.41857171058655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3701536655426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39321041107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51310133934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50964260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46122527122498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4485445022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50733709335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50157308578491</t>
   </si>
   <si>
     <t xml:space="preserve">2.49696230888367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5154070854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53039360046387</t>
+    <t xml:space="preserve">2.51540684700012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53039336204529</t>
   </si>
   <si>
     <t xml:space="preserve">2.57304716110229</t>
@@ -524,22 +524,22 @@
     <t xml:space="preserve">2.66181254386902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6272280216217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73789739608765</t>
+    <t xml:space="preserve">2.62722826004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73789691925049</t>
   </si>
   <si>
     <t xml:space="preserve">2.83012080192566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79092597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67449355125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65604829788208</t>
+    <t xml:space="preserve">2.79092574119568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67449331283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6560480594635</t>
   </si>
   <si>
     <t xml:space="preserve">2.64797878265381</t>
@@ -548,40 +548,40 @@
     <t xml:space="preserve">2.65720081329346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64567351341248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52001786231995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51886534690857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49580931663513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5211706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52462911605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54192137718201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47275304794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46929550170898</t>
+    <t xml:space="preserve">2.6456732749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52001810073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51886487007141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49580907821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52117109298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52462887763977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54192161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47275328636169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46929502487183</t>
   </si>
   <si>
     <t xml:space="preserve">2.39436316490173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32173633575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32519483566284</t>
+    <t xml:space="preserve">2.32173657417297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32519507408142</t>
   </si>
   <si>
     <t xml:space="preserve">2.24795770645142</t>
@@ -590,31 +590,31 @@
     <t xml:space="preserve">2.26524949073792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32634735107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3862931728363</t>
+    <t xml:space="preserve">2.3263475894928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38629341125488</t>
   </si>
   <si>
     <t xml:space="preserve">2.44393301010132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44623899459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57074093818665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57996344566345</t>
+    <t xml:space="preserve">2.44623875617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5707414150238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57996320724487</t>
   </si>
   <si>
     <t xml:space="preserve">2.56267166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55806064605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50387907028198</t>
+    <t xml:space="preserve">2.55806016921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5038788318634</t>
   </si>
   <si>
     <t xml:space="preserve">2.50503134727478</t>
@@ -623,19 +623,19 @@
     <t xml:space="preserve">2.38168215751648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60993599891663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59956073760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55344891548157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70907759666443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67910408973694</t>
+    <t xml:space="preserve">2.60993647575378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59956097602844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55344915390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70907711982727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
     <t xml:space="preserve">2.58111619949341</t>
@@ -647,139 +647,139 @@
     <t xml:space="preserve">2.81282901763916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72291088104248</t>
+    <t xml:space="preserve">2.72291111946106</t>
   </si>
   <si>
     <t xml:space="preserve">2.78285622596741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82551050186157</t>
+    <t xml:space="preserve">2.82551002502441</t>
   </si>
   <si>
     <t xml:space="preserve">2.92522716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96557474136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91081643104553</t>
+    <t xml:space="preserve">2.96557426452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91081714630127</t>
   </si>
   <si>
     <t xml:space="preserve">3.00592255592346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03474283218384</t>
+    <t xml:space="preserve">3.03474259376526</t>
   </si>
   <si>
     <t xml:space="preserve">2.99727654457092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98574829101562</t>
+    <t xml:space="preserve">2.98574781417847</t>
   </si>
   <si>
     <t xml:space="preserve">2.94828271865845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93963670730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97422122955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9915132522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.014568567276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03186082839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16155076026917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13849449157715</t>
+    <t xml:space="preserve">2.93963694572449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9742214679718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99151301383972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01456880569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03186058998108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16155099868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13849496841431</t>
   </si>
   <si>
     <t xml:space="preserve">3.11255669593811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12984871864319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2047803401947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16443252563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19613456726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19901704788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12408542633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14137649536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08373713493347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30276918411255</t>
+    <t xml:space="preserve">3.12984848022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20478057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16443204879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19613480567932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1990168094635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12408471107483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14137697219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08373689651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30276870727539</t>
   </si>
   <si>
     <t xml:space="preserve">3.26242065429688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18748927116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28547620773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2278368473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17596030235291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24800992012024</t>
+    <t xml:space="preserve">3.18748903274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28547596931458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22783660888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17596101760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2480103969574</t>
   </si>
   <si>
     <t xml:space="preserve">3.26818442344666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23936438560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09238290786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10102868080139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05491709709167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08085489273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11832094192505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15002298355103</t>
+    <t xml:space="preserve">3.23936414718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09238243103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10102891921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05491638183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08085417747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11832022666931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15002250671387</t>
   </si>
   <si>
     <t xml:space="preserve">3.01168704032898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92810893058777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95404696464539</t>
+    <t xml:space="preserve">2.92810821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95404672622681</t>
   </si>
   <si>
     <t xml:space="preserve">2.7851619720459</t>
@@ -788,49 +788,49 @@
     <t xml:space="preserve">2.91369867324829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98863101005554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0030403137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02609634399414</t>
+    <t xml:space="preserve">2.98863124847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00304055213928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0260968208313</t>
   </si>
   <si>
     <t xml:space="preserve">3.07797312736511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05779886245728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18172454833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17019653320312</t>
+    <t xml:space="preserve">3.0577986240387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18172407150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17019701004028</t>
   </si>
   <si>
     <t xml:space="preserve">3.23360061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24512887001038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25089311599731</t>
+    <t xml:space="preserve">3.2451286315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25089263916016</t>
   </si>
   <si>
     <t xml:space="preserve">3.27106690406799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27394914627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28259444236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2566556930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18460655212402</t>
+    <t xml:space="preserve">3.27394866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28259420394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25665593147278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18460631370544</t>
   </si>
   <si>
     <t xml:space="preserve">3.29412221908569</t>
@@ -839,40 +839,40 @@
     <t xml:space="preserve">3.10391068458557</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34023451805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44398641586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43245911598206</t>
+    <t xml:space="preserve">3.34023523330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44398665428162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43245840072632</t>
   </si>
   <si>
     <t xml:space="preserve">3.46415972709656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45839643478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49298024177551</t>
+    <t xml:space="preserve">3.45839667320251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49297976493835</t>
   </si>
   <si>
     <t xml:space="preserve">3.44686794281006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50450825691223</t>
+    <t xml:space="preserve">3.50450873374939</t>
   </si>
   <si>
     <t xml:space="preserve">3.60249614715576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51603627204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46992468833923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44110417366028</t>
+    <t xml:space="preserve">3.51603603363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46992444992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44110441207886</t>
   </si>
   <si>
     <t xml:space="preserve">3.42381238937378</t>
@@ -881,16 +881,16 @@
     <t xml:space="preserve">3.41228437423706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39499235153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37193584442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48935174942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49236249923706</t>
+    <t xml:space="preserve">3.39499282836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37193655967712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48935294151306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49236226081848</t>
   </si>
   <si>
     <t xml:space="preserve">3.5947253704071</t>
@@ -902,28 +902,28 @@
     <t xml:space="preserve">3.71515202522278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58870363235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46827721595764</t>
+    <t xml:space="preserve">3.58870387077332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4682776927948</t>
   </si>
   <si>
     <t xml:space="preserve">3.41107535362244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49838447570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54053354263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50440573692322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51644825935364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.549565076828</t>
+    <t xml:space="preserve">3.49838423728943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54053282737732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50440549850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5164487361908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54956531524658</t>
   </si>
   <si>
     <t xml:space="preserve">3.70913004875183</t>
@@ -932,67 +932,67 @@
     <t xml:space="preserve">3.7241837978363</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64891695976257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75127911567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72719430923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76332211494446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73923635482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74525737762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71214151382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70310926437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75730085372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77536463737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77837610244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84160017967224</t>
+    <t xml:space="preserve">3.64891672134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7512800693512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72719407081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76332187652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73923707008362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74525761604309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7121410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7031090259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75730061531067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7753643989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77837562561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8415994644165</t>
   </si>
   <si>
     <t xml:space="preserve">3.85966348648071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82654547691345</t>
+    <t xml:space="preserve">3.82654595375061</t>
   </si>
   <si>
     <t xml:space="preserve">4.09750556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14266538619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19685649871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17277193069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19083547592163</t>
+    <t xml:space="preserve">4.14266586303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19685697555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17277145385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19083595275879</t>
   </si>
   <si>
     <t xml:space="preserve">4.22094249725342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19986772537231</t>
+    <t xml:space="preserve">4.19986724853516</t>
   </si>
   <si>
     <t xml:space="preserve">4.2450270652771</t>
@@ -1001,34 +1001,34 @@
     <t xml:space="preserve">4.2691125869751</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26309156417847</t>
+    <t xml:space="preserve">4.26309108734131</t>
   </si>
   <si>
     <t xml:space="preserve">4.21492147445679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15470743179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14567613601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13664436340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22395277023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22696352005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33534717559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25104951858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28717565536499</t>
+    <t xml:space="preserve">4.15470790863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.145676612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13664388656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22395324707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22696304321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33534669876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25104904174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28717756271362</t>
   </si>
   <si>
     <t xml:space="preserve">4.11857986450195</t>
@@ -1040,70 +1040,70 @@
     <t xml:space="preserve">4.09449481964111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08847284317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04030275344849</t>
+    <t xml:space="preserve">4.08847332000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04030227661133</t>
   </si>
   <si>
     <t xml:space="preserve">4.05234527587891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95901536941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86267375946045</t>
+    <t xml:space="preserve">3.95901465415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86267352104187</t>
   </si>
   <si>
     <t xml:space="preserve">3.86568427085876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94396162033081</t>
+    <t xml:space="preserve">3.94396138191223</t>
   </si>
   <si>
     <t xml:space="preserve">3.94697213172913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95600438117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98009014129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9740686416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07342004776001</t>
+    <t xml:space="preserve">3.95600390434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98008966445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97406840324402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07341957092285</t>
   </si>
   <si>
     <t xml:space="preserve">4.06438827514648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98912191390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9620258808136</t>
+    <t xml:space="preserve">3.98912143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96202516555786</t>
   </si>
   <si>
     <t xml:space="preserve">4.01320600509644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03428077697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00417470932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00116443634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90783381462097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88976955413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95299410820007</t>
+    <t xml:space="preserve">4.03428173065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00417518615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00116395950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90783405303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88976979255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95299386978149</t>
   </si>
   <si>
     <t xml:space="preserve">4.0101957321167</t>
@@ -1115,52 +1115,52 @@
     <t xml:space="preserve">4.15771865844727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06739902496338</t>
+    <t xml:space="preserve">4.06739854812622</t>
   </si>
   <si>
     <t xml:space="preserve">3.98611092567444</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93191885948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90181231498718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87471675872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8536422252655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82353448867798</t>
+    <t xml:space="preserve">3.93191838264465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90181183815002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87471652030945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85364127159119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82353472709656</t>
   </si>
   <si>
     <t xml:space="preserve">3.89579153060913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84762024879456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83256816864014</t>
+    <t xml:space="preserve">3.84762072563171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83256793022156</t>
   </si>
   <si>
     <t xml:space="preserve">3.88073778152466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88374829292297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9258975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9289083480835</t>
+    <t xml:space="preserve">3.88374757766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92589807510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92890810966492</t>
   </si>
   <si>
     <t xml:space="preserve">3.88675928115845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9138548374176</t>
+    <t xml:space="preserve">3.91385459899902</t>
   </si>
   <si>
     <t xml:space="preserve">3.91084432601929</t>
@@ -1169,37 +1169,37 @@
     <t xml:space="preserve">3.84460973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82052516937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69106674194336</t>
+    <t xml:space="preserve">3.82052445411682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69106650352478</t>
   </si>
   <si>
     <t xml:space="preserve">3.70611953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55558681488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47429871559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33580875396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40204334259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52246928215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54354381561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53150153160095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57365083694458</t>
+    <t xml:space="preserve">3.55558705329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47429895401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33580851554871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40204262733459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52246952056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54354405403137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53150129318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57365036010742</t>
   </si>
   <si>
     <t xml:space="preserve">3.60074615478516</t>
@@ -1208,70 +1208,70 @@
     <t xml:space="preserve">3.57666158676147</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5375235080719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55257630348206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50139474868774</t>
+    <t xml:space="preserve">3.53752279281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55257606506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50139451026917</t>
   </si>
   <si>
     <t xml:space="preserve">3.45021390914917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51042699813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48634147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43817114830017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40806460380554</t>
+    <t xml:space="preserve">3.51042675971985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48634171485901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43817186355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40806484222412</t>
   </si>
   <si>
     <t xml:space="preserve">3.53451180458069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6097776889801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35387253761292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42612814903259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44419264793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32376623153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39000082015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61278891563416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73020434379578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66698026657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64590716362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63386368751526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81450295448303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86869502067566</t>
+    <t xml:space="preserve">3.609778881073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35387206077576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42612838745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4441921710968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32376551628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39000058174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61278939247131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73020482063293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6669807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64590668678284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63386392593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81450319290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86869525909424</t>
   </si>
   <si>
     <t xml:space="preserve">3.93492937088013</t>
@@ -1280,55 +1280,55 @@
     <t xml:space="preserve">4.04331350326538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99213194847107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98310041427612</t>
+    <t xml:space="preserve">3.99213218688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98309969902039</t>
   </si>
   <si>
     <t xml:space="preserve">4.06137704849243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12460088729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.160728931427</t>
+    <t xml:space="preserve">4.12460136413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16072845458984</t>
   </si>
   <si>
     <t xml:space="preserve">4.07040882110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08245182037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8084819316864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89880156517029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91987609863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78439617156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77235412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79945063591003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73622632026672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75429081916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76633214950562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63988518714905</t>
+    <t xml:space="preserve">4.08245229721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80848240852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89880228042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91987681388855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78439688682556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77235436439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79945039749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73622584342957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75429129600525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76633262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63988494873047</t>
   </si>
   <si>
     <t xml:space="preserve">3.56160807609558</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">3.96503639221191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79342889785767</t>
+    <t xml:space="preserve">3.79342865943909</t>
   </si>
   <si>
     <t xml:space="preserve">3.74224734306335</t>
@@ -1349,40 +1349,40 @@
     <t xml:space="preserve">3.79164934158325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77612209320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78854322433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70469856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58358931541443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55914258956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55258846282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51326060295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61157989501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58536100387573</t>
+    <t xml:space="preserve">3.77612257003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78854370117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70469903945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58358955383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55914282798767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55258798599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51326107978821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61158013343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58536124229431</t>
   </si>
   <si>
     <t xml:space="preserve">3.76888990402222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89998126029968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89342737197876</t>
+    <t xml:space="preserve">3.89998173713684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8934268951416</t>
   </si>
   <si>
     <t xml:space="preserve">3.85082244873047</t>
@@ -1391,34 +1391,34 @@
     <t xml:space="preserve">3.81149482727051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63779830932617</t>
+    <t xml:space="preserve">3.63779807090759</t>
   </si>
   <si>
     <t xml:space="preserve">3.75578045845032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73939418792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86065411567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099054336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81804919242859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96552777290344</t>
+    <t xml:space="preserve">3.73939394950867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8606538772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8409903049469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81804871559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9655282497406</t>
   </si>
   <si>
     <t xml:space="preserve">3.98846864700317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93275451660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86720895767212</t>
+    <t xml:space="preserve">3.93275547027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86720848083496</t>
   </si>
   <si>
     <t xml:space="preserve">3.84426760673523</t>
@@ -1430,16 +1430,16 @@
     <t xml:space="preserve">3.8213267326355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03107357025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04418230056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02451944351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98191380500793</t>
+    <t xml:space="preserve">4.03107309341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04418277740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0245189666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98191428184509</t>
   </si>
   <si>
     <t xml:space="preserve">3.90653657913208</t>
@@ -1451,13 +1451,13 @@
     <t xml:space="preserve">3.77544474601746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76561212539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71973085403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71645331382751</t>
+    <t xml:space="preserve">3.76561236381531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71973061561584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71645355224609</t>
   </si>
   <si>
     <t xml:space="preserve">3.56897497177124</t>
@@ -1466,73 +1466,73 @@
     <t xml:space="preserve">3.50670599937439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46737837791443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27467322349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93645691871643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03477621078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19077444076538</t>
+    <t xml:space="preserve">3.46737861633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27467346191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93645668029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03477597236633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19077491760254</t>
   </si>
   <si>
     <t xml:space="preserve">3.42149662971497</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41494178771973</t>
+    <t xml:space="preserve">3.41494202613831</t>
   </si>
   <si>
     <t xml:space="preserve">3.33628702163696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3166229724884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35595059394836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.211749792099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30023646354675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32645463943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39855480194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33956432342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29040503501892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27729535102844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28057289123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1829092502594</t>
+    <t xml:space="preserve">3.31662344932556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35595035552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21174955368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30023670196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32645487785339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39855527877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33956408500671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29040455818176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27729511260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28057312965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18290948867798</t>
   </si>
   <si>
     <t xml:space="preserve">3.12260723114014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07148122787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01511192321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89975118637085</t>
+    <t xml:space="preserve">3.07148146629333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01511216163635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89975070953369</t>
   </si>
   <si>
     <t xml:space="preserve">3.01904463768005</t>
@@ -1547,31 +1547,31 @@
     <t xml:space="preserve">2.97971725463867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02691006660461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13440561294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10425424575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04264140129089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00200295448303</t>
+    <t xml:space="preserve">3.02690982818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1344051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10425448417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04264116287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00200271606445</t>
   </si>
   <si>
     <t xml:space="preserve">3.00462460517883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98233938217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98627185821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92072582244873</t>
+    <t xml:space="preserve">2.98233914375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98627161979675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92072558403015</t>
   </si>
   <si>
     <t xml:space="preserve">2.92728042602539</t>
@@ -1583,58 +1583,58 @@
     <t xml:space="preserve">3.01249027252197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03739762306213</t>
+    <t xml:space="preserve">3.03739738464355</t>
   </si>
   <si>
     <t xml:space="preserve">2.95612072944641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92465853691101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84469270706177</t>
+    <t xml:space="preserve">2.92465877532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84469246864319</t>
   </si>
   <si>
     <t xml:space="preserve">2.97709536552429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00724601745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89057469367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77259206771851</t>
+    <t xml:space="preserve">3.00724625587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89057445526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77259182929993</t>
   </si>
   <si>
     <t xml:space="preserve">2.79487752914429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73064279556274</t>
+    <t xml:space="preserve">2.73064231872559</t>
   </si>
   <si>
     <t xml:space="preserve">2.71228981018066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70049118995667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77914643287659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76997017860413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73719716072083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72146606445312</t>
+    <t xml:space="preserve">2.70049142837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77914667129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76996994018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7371973991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72146654129028</t>
   </si>
   <si>
     <t xml:space="preserve">2.69000434875488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63625645637512</t>
+    <t xml:space="preserve">2.63625621795654</t>
   </si>
   <si>
     <t xml:space="preserve">2.64936542510986</t>
@@ -1646,37 +1646,37 @@
     <t xml:space="preserve">2.67689514160156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7201554775238</t>
+    <t xml:space="preserve">2.72015523910522</t>
   </si>
   <si>
     <t xml:space="preserve">2.87615466117859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85124683380127</t>
+    <t xml:space="preserve">2.85124707221985</t>
   </si>
   <si>
     <t xml:space="preserve">2.86697840690613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93907880783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91154956817627</t>
+    <t xml:space="preserve">2.93907904624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91154909133911</t>
   </si>
   <si>
     <t xml:space="preserve">2.91679286956787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92596983909607</t>
+    <t xml:space="preserve">2.92596936225891</t>
   </si>
   <si>
     <t xml:space="preserve">2.94170045852661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99807024002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04133033752441</t>
+    <t xml:space="preserve">2.99806976318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04133057594299</t>
   </si>
   <si>
     <t xml:space="preserve">2.99675893783569</t>
@@ -1685,46 +1685,46 @@
     <t xml:space="preserve">2.99413704872131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96267533302307</t>
+    <t xml:space="preserve">2.96267509460449</t>
   </si>
   <si>
     <t xml:space="preserve">2.96005344390869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91285991668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77521419525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7070460319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68869352340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70573496818542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74244070053101</t>
+    <t xml:space="preserve">2.91286015510559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77521395683289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70704627037048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6886932849884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70573544502258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74244093894958</t>
   </si>
   <si>
     <t xml:space="preserve">2.64674377441406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64150023460388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59692883491516</t>
+    <t xml:space="preserve">2.64150047302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59692907333374</t>
   </si>
   <si>
     <t xml:space="preserve">2.38193845748901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4671483039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44879508018494</t>
+    <t xml:space="preserve">2.46714782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44879531860352</t>
   </si>
   <si>
     <t xml:space="preserve">2.49074459075928</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">2.4710807800293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48681211471558</t>
+    <t xml:space="preserve">2.486811876297</t>
   </si>
   <si>
     <t xml:space="preserve">2.4199550151825</t>
@@ -1751,19 +1751,19 @@
     <t xml:space="preserve">2.25215744972229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28493046760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38587117195129</t>
+    <t xml:space="preserve">2.28493022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38587141036987</t>
   </si>
   <si>
     <t xml:space="preserve">2.39242577552795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42519903182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45928263664246</t>
+    <t xml:space="preserve">2.42519879341125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45928239822388</t>
   </si>
   <si>
     <t xml:space="preserve">2.54973602294922</t>
@@ -1772,22 +1772,22 @@
     <t xml:space="preserve">2.47239184379578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44617342948914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45797181129456</t>
+    <t xml:space="preserve">2.44617319107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45797157287598</t>
   </si>
   <si>
     <t xml:space="preserve">2.47501349449158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54842519760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43044257164001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40815663337708</t>
+    <t xml:space="preserve">2.54842495918274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43044233322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40815687179565</t>
   </si>
   <si>
     <t xml:space="preserve">2.33998894691467</t>
@@ -1796,16 +1796,16 @@
     <t xml:space="preserve">2.28886318206787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27968692779541</t>
+    <t xml:space="preserve">2.27968668937683</t>
   </si>
   <si>
     <t xml:space="preserve">2.25740122795105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17612409591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18661141395569</t>
+    <t xml:space="preserve">2.17612433433533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18661165237427</t>
   </si>
   <si>
     <t xml:space="preserve">2.13155317306519</t>
@@ -1817,19 +1817,19 @@
     <t xml:space="preserve">2.35178732872009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39766931533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44748449325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42388796806335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40946817398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40029096603394</t>
+    <t xml:space="preserve">2.39766955375671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44748425483704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42388772964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40946793556213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40029120445251</t>
   </si>
   <si>
     <t xml:space="preserve">2.21938467025757</t>
@@ -1841,19 +1841,19 @@
     <t xml:space="preserve">2.25477957725525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31901454925537</t>
+    <t xml:space="preserve">2.31901431083679</t>
   </si>
   <si>
     <t xml:space="preserve">2.32687973976135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26264452934265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17743515968323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12893152236938</t>
+    <t xml:space="preserve">2.26264476776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17743539810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12893128395081</t>
   </si>
   <si>
     <t xml:space="preserve">2.14597296714783</t>
@@ -1862,16 +1862,16 @@
     <t xml:space="preserve">2.12237668037415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12368774414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10271310806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11713314056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14728426933289</t>
+    <t xml:space="preserve">2.12368726730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10271286964417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11713290214539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14728403091431</t>
   </si>
   <si>
     <t xml:space="preserve">2.15121698379517</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">2.23904824256897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20758605003357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36489629745483</t>
+    <t xml:space="preserve">2.20758628845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36489653587341</t>
   </si>
   <si>
     <t xml:space="preserve">2.34785485267639</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">2.37407279014587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25084638595581</t>
+    <t xml:space="preserve">2.25084662437439</t>
   </si>
   <si>
     <t xml:space="preserve">2.39504742622375</t>
@@ -1904,16 +1904,16 @@
     <t xml:space="preserve">2.41340017318726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43306422233582</t>
+    <t xml:space="preserve">2.43306398391724</t>
   </si>
   <si>
     <t xml:space="preserve">2.44486260414124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44224047660828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43175315856934</t>
+    <t xml:space="preserve">2.44224071502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43175363540649</t>
   </si>
   <si>
     <t xml:space="preserve">2.38456010818481</t>
@@ -1925,10 +1925,10 @@
     <t xml:space="preserve">2.34654355049133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35440897941589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37145113945007</t>
+    <t xml:space="preserve">2.35440945625305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37145090103149</t>
   </si>
   <si>
     <t xml:space="preserve">2.28755211830139</t>
@@ -1937,55 +1937,55 @@
     <t xml:space="preserve">2.26788854598999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31114888191223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37931656837463</t>
+    <t xml:space="preserve">2.31114864349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37931632995605</t>
   </si>
   <si>
     <t xml:space="preserve">2.40291309356689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4055347442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37014007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33605599403381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39898037910461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37669467926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5012321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54318165779114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52613925933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50385355949402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49336647987366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42782044410706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39635848999023</t>
+    <t xml:space="preserve">2.40553522109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37014031410217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33605623245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39898061752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37669444084167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50123167037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54318141937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52613949775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50385332107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49336624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42782068252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39635872840881</t>
   </si>
   <si>
     <t xml:space="preserve">2.38718199729919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37276196479797</t>
+    <t xml:space="preserve">2.37276172637939</t>
   </si>
   <si>
     <t xml:space="preserve">2.37800574302673</t>
@@ -2000,22 +2000,22 @@
     <t xml:space="preserve">2.38062763214111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30459427833557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38849306106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45666098594666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40160226821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34129977226257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34392166137695</t>
+    <t xml:space="preserve">2.30459403991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38849329948425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4566605091095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40160250663757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34130024909973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34392189979553</t>
   </si>
   <si>
     <t xml:space="preserve">2.38324928283691</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">2.30328321456909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30590534210205</t>
+    <t xml:space="preserve">2.30590510368347</t>
   </si>
   <si>
     <t xml:space="preserve">2.34523272514343</t>
@@ -2039,31 +2039,31 @@
     <t xml:space="preserve">2.30983781814575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21545195579529</t>
+    <t xml:space="preserve">2.21545219421387</t>
   </si>
   <si>
     <t xml:space="preserve">2.19054436683655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09091448783875</t>
+    <t xml:space="preserve">2.09091472625732</t>
   </si>
   <si>
     <t xml:space="preserve">2.08698177337646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99783945083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03978872299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97686457633972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99128496646881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97817528247833</t>
+    <t xml:space="preserve">1.99783933162689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03978896141052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9768648147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99128472805023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97817552089691</t>
   </si>
   <si>
     <t xml:space="preserve">1.98996269702911</t>
@@ -2084,25 +2084,25 @@
     <t xml:space="preserve">1.89843845367432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86377000808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82632827758789</t>
+    <t xml:space="preserve">1.86377012729645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82632851600647</t>
   </si>
   <si>
     <t xml:space="preserve">1.87625086307526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87902426719666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83742213249207</t>
+    <t xml:space="preserve">1.87902414798737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83742225170135</t>
   </si>
   <si>
     <t xml:space="preserve">1.9511342048645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92755973339081</t>
+    <t xml:space="preserve">1.92755997180939</t>
   </si>
   <si>
     <t xml:space="preserve">1.89982497692108</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">1.88734459877014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88873112201691</t>
+    <t xml:space="preserve">1.88873136043549</t>
   </si>
   <si>
     <t xml:space="preserve">1.88179767131805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02879166603088</t>
+    <t xml:space="preserve">2.0287914276123</t>
   </si>
   <si>
     <t xml:space="preserve">1.98302924633026</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">2.03156495094299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98857617378235</t>
+    <t xml:space="preserve">1.98857605457306</t>
   </si>
   <si>
     <t xml:space="preserve">1.95945477485657</t>
@@ -2150,19 +2150,19 @@
     <t xml:space="preserve">2.07177996635437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09396815299988</t>
+    <t xml:space="preserve">2.0939679145813</t>
   </si>
   <si>
     <t xml:space="preserve">2.14943718910217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22709465026855</t>
+    <t xml:space="preserve">2.22709441184998</t>
   </si>
   <si>
     <t xml:space="preserve">2.25344228744507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25898909568787</t>
+    <t xml:space="preserve">2.25898933410645</t>
   </si>
   <si>
     <t xml:space="preserve">2.26453614234924</t>
@@ -2171,10 +2171,10 @@
     <t xml:space="preserve">2.21461391448975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21184015274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2492823600769</t>
+    <t xml:space="preserve">2.21184062957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24928212165833</t>
   </si>
   <si>
     <t xml:space="preserve">2.31445860862732</t>
@@ -2183,22 +2183,22 @@
     <t xml:space="preserve">2.30059123039246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30891156196594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31307172775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27424335479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22154760360718</t>
+    <t xml:space="preserve">2.30891180038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31307196617126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2742431